--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G20">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G37">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N37">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G43">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G60">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G61">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G72">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G73">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G88">
@@ -14649,7 +14649,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N88">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G89">
@@ -14812,7 +14812,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N89">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Muğlaspor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G99">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Muğlaspor</t>
         </is>
       </c>
       <c r="G100">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G139">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,13 +25085,13 @@
         </is>
       </c>
       <c r="N152">
-        <v>2.17</v>
+        <v>2.45</v>
       </c>
       <c r="O152">
-        <v>3.3</v>
+        <v>3.21</v>
       </c>
       <c r="P152">
-        <v>3.6</v>
+        <v>3.11</v>
       </c>
       <c r="Q152">
         <v>0</v>
@@ -25124,10 +25124,10 @@
         <v>0</v>
       </c>
       <c r="AA152">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB152">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AC152">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,13 +25248,13 @@
         </is>
       </c>
       <c r="N153">
-        <v>2.45</v>
+        <v>2.17</v>
       </c>
       <c r="O153">
-        <v>3.21</v>
+        <v>3.3</v>
       </c>
       <c r="P153">
-        <v>3.11</v>
+        <v>3.6</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -25287,10 +25287,10 @@
         <v>0</v>
       </c>
       <c r="AA153">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB153">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AC153">
         <v>0</v>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU162"/>
+  <dimension ref="A1:AU166"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G60">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G62">
@@ -19664,7 +19664,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G119">
@@ -19827,22 +19827,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G120">
@@ -19990,22 +19990,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G123">
@@ -20479,22 +20479,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G124">
@@ -20642,22 +20642,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G126">
@@ -20963,12 +20963,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G127">
@@ -21114,7 +21114,7 @@
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>2026-08-09 15:15:00</t>
+          <t>2026-08-09 15:00:00</t>
         </is>
       </c>
     </row>
@@ -21126,12 +21126,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G128">
@@ -21277,7 +21277,7 @@
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>2026-08-09 15:15:00</t>
+          <t>2026-08-09 15:00:00</t>
         </is>
       </c>
     </row>
@@ -21294,7 +21294,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G129">
@@ -21457,7 +21457,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="G130">
@@ -21615,12 +21615,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G131">
@@ -21766,7 +21766,7 @@
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>2026-08-09 15:30:00</t>
+          <t>2026-08-09 15:15:00</t>
         </is>
       </c>
     </row>
@@ -21778,12 +21778,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G132">
@@ -21929,7 +21929,7 @@
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>2026-08-09 15:30:00</t>
+          <t>2026-08-09 15:15:00</t>
         </is>
       </c>
     </row>
@@ -21946,7 +21946,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,13 +21988,13 @@
         </is>
       </c>
       <c r="N133">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="O133">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P133">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q133">
         <v>0</v>
@@ -22104,27 +22104,27 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="G134">
@@ -22255,7 +22255,7 @@
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>2026-08-09 16:00:00</t>
+          <t>2026-08-09 15:30:00</t>
         </is>
       </c>
     </row>
@@ -22267,12 +22267,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,13 +22314,13 @@
         </is>
       </c>
       <c r="N135">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="O135">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P135">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q135">
         <v>0</v>
@@ -22418,7 +22418,7 @@
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>2026-08-09 16:00:00</t>
+          <t>2026-08-09 15:30:00</t>
         </is>
       </c>
     </row>
@@ -22435,7 +22435,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,13 +22477,13 @@
         </is>
       </c>
       <c r="N136">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O136">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="P136">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AA136">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB136">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC136">
         <v>0</v>
@@ -22598,22 +22598,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,13 +22640,13 @@
         </is>
       </c>
       <c r="N137">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O137">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="P137">
-        <v>6.63</v>
+        <v>0</v>
       </c>
       <c r="Q137">
         <v>0</v>
@@ -22679,10 +22679,10 @@
         <v>0</v>
       </c>
       <c r="AA137">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB137">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC137">
         <v>0</v>
@@ -22761,7 +22761,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G138">
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="N138">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O138">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="P138">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="Q138">
         <v>0</v>
@@ -22842,10 +22842,10 @@
         <v>0</v>
       </c>
       <c r="AA138">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB138">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC138">
         <v>0</v>
@@ -22924,7 +22924,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,13 +22966,13 @@
         </is>
       </c>
       <c r="N139">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O139">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="P139">
-        <v>0</v>
+        <v>6.63</v>
       </c>
       <c r="Q139">
         <v>0</v>
@@ -23005,10 +23005,10 @@
         <v>0</v>
       </c>
       <c r="AA139">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB139">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC139">
         <v>0</v>
@@ -23087,7 +23087,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G140">
@@ -23250,7 +23250,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G141">
@@ -23413,22 +23413,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G142">
@@ -23576,7 +23576,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,13 +23618,13 @@
         </is>
       </c>
       <c r="N143">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O143">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P143">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -23657,10 +23657,10 @@
         <v>0</v>
       </c>
       <c r="AA143">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB143">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC143">
         <v>0</v>
@@ -23739,22 +23739,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,13 +23781,13 @@
         </is>
       </c>
       <c r="N144">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O144">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P144">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q144">
         <v>0</v>
@@ -23820,10 +23820,10 @@
         <v>0</v>
       </c>
       <c r="AA144">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB144">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AC144">
         <v>0</v>
@@ -23897,27 +23897,27 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G145">
@@ -24048,7 +24048,7 @@
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>2026-08-09 16:15:00</t>
+          <t>2026-08-09 16:00:00</t>
         </is>
       </c>
     </row>
@@ -24060,12 +24060,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,13 +24107,13 @@
         </is>
       </c>
       <c r="N146">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="O146">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="P146">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="Q146">
         <v>0</v>
@@ -24146,10 +24146,10 @@
         <v>0</v>
       </c>
       <c r="AA146">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB146">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC146">
         <v>0</v>
@@ -24211,7 +24211,7 @@
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>2026-08-09 16:30:00</t>
+          <t>2026-08-09 16:00:00</t>
         </is>
       </c>
     </row>
@@ -24223,12 +24223,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,13 +24270,13 @@
         </is>
       </c>
       <c r="N147">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O147">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P147">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q147">
         <v>0</v>
@@ -24309,10 +24309,10 @@
         <v>0</v>
       </c>
       <c r="AA147">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB147">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC147">
         <v>0</v>
@@ -24374,7 +24374,7 @@
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>2026-08-09 17:00:00</t>
+          <t>2026-08-09 16:00:00</t>
         </is>
       </c>
     </row>
@@ -24386,12 +24386,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,13 +24433,13 @@
         </is>
       </c>
       <c r="N148">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O148">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P148">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q148">
         <v>0</v>
@@ -24472,10 +24472,10 @@
         <v>0</v>
       </c>
       <c r="AA148">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB148">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC148">
         <v>0</v>
@@ -24537,7 +24537,7 @@
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>2026-08-09 18:00:00</t>
+          <t>2026-08-09 16:00:00</t>
         </is>
       </c>
     </row>
@@ -24549,12 +24549,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G149">
@@ -24700,7 +24700,7 @@
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>2026-08-09 18:00:00</t>
+          <t>2026-08-09 16:15:00</t>
         </is>
       </c>
     </row>
@@ -24712,27 +24712,27 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G150">
@@ -24759,13 +24759,13 @@
         </is>
       </c>
       <c r="N150">
-        <v>2.47</v>
+        <v>1.76</v>
       </c>
       <c r="O150">
-        <v>2.92</v>
+        <v>3.89</v>
       </c>
       <c r="P150">
-        <v>3.06</v>
+        <v>4.89</v>
       </c>
       <c r="Q150">
         <v>0</v>
@@ -24792,16 +24792,16 @@
         <v>0</v>
       </c>
       <c r="Y150">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z150">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA150">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB150">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC150">
         <v>0</v>
@@ -24863,7 +24863,7 @@
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>2026-08-09 18:00:00</t>
+          <t>2026-08-09 16:30:00</t>
         </is>
       </c>
     </row>
@@ -24875,12 +24875,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G151">
@@ -25026,7 +25026,7 @@
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>2026-08-09 18:15:00</t>
+          <t>2026-08-09 17:00:00</t>
         </is>
       </c>
     </row>
@@ -25038,12 +25038,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,13 +25085,13 @@
         </is>
       </c>
       <c r="N152">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O152">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="P152">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="Q152">
         <v>0</v>
@@ -25124,10 +25124,10 @@
         <v>0</v>
       </c>
       <c r="AA152">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB152">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC152">
         <v>0</v>
@@ -25189,7 +25189,7 @@
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>2026-08-09 18:30:00</t>
+          <t>2026-08-09 18:00:00</t>
         </is>
       </c>
     </row>
@@ -25201,12 +25201,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,13 +25248,13 @@
         </is>
       </c>
       <c r="N153">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O153">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P153">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -25287,10 +25287,10 @@
         <v>0</v>
       </c>
       <c r="AA153">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB153">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC153">
         <v>0</v>
@@ -25352,7 +25352,7 @@
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>2026-08-09 18:30:00</t>
+          <t>2026-08-09 18:00:00</t>
         </is>
       </c>
     </row>
@@ -25364,12 +25364,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="N154">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O154">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="P154">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q154">
         <v>0</v>
@@ -25444,10 +25444,10 @@
         <v>0</v>
       </c>
       <c r="Y154">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z154">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA154">
         <v>0</v>
@@ -25515,7 +25515,7 @@
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>2026-08-09 18:30:00</t>
+          <t>2026-08-09 18:00:00</t>
         </is>
       </c>
     </row>
@@ -25527,12 +25527,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G155">
@@ -25678,7 +25678,7 @@
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>2026-08-09 18:30:00</t>
+          <t>2026-08-09 18:15:00</t>
         </is>
       </c>
     </row>
@@ -25695,7 +25695,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,13 +25737,13 @@
         </is>
       </c>
       <c r="N156">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O156">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="P156">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q156">
         <v>0</v>
@@ -25776,10 +25776,10 @@
         <v>0</v>
       </c>
       <c r="AA156">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB156">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC156">
         <v>0</v>
@@ -25853,7 +25853,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,13 +25900,13 @@
         </is>
       </c>
       <c r="N157">
-        <v>1.3</v>
+        <v>2.17</v>
       </c>
       <c r="O157">
-        <v>5.48</v>
+        <v>3.3</v>
       </c>
       <c r="P157">
-        <v>11.3</v>
+        <v>3.6</v>
       </c>
       <c r="Q157">
         <v>0</v>
@@ -25939,10 +25939,10 @@
         <v>0</v>
       </c>
       <c r="AA157">
-        <v>1.63</v>
+        <v>2.15</v>
       </c>
       <c r="AB157">
-        <v>2.1</v>
+        <v>1.61</v>
       </c>
       <c r="AC157">
         <v>0</v>
@@ -26004,7 +26004,7 @@
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>2026-08-09 19:30:00</t>
+          <t>2026-08-09 18:30:00</t>
         </is>
       </c>
     </row>
@@ -26016,12 +26016,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G158">
@@ -26167,7 +26167,7 @@
       </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>2026-08-09 20:00:00</t>
+          <t>2026-08-09 18:30:00</t>
         </is>
       </c>
     </row>
@@ -26179,12 +26179,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G159">
@@ -26330,7 +26330,7 @@
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>2026-08-09 20:30:00</t>
+          <t>2026-08-09 18:30:00</t>
         </is>
       </c>
     </row>
@@ -26342,7 +26342,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G160">
@@ -26493,7 +26493,7 @@
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>2026-08-09 21:00:00</t>
+          <t>2026-08-09 18:30:00</t>
         </is>
       </c>
     </row>
@@ -26505,12 +26505,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,13 +26552,13 @@
         </is>
       </c>
       <c r="N161">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O161">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="P161">
-        <v>0</v>
+        <v>11.3</v>
       </c>
       <c r="Q161">
         <v>0</v>
@@ -26591,10 +26591,10 @@
         <v>0</v>
       </c>
       <c r="AA161">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB161">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC161">
         <v>0</v>
@@ -26656,7 +26656,7 @@
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>2026-08-09 21:00:00</t>
+          <t>2026-08-09 19:30:00</t>
         </is>
       </c>
     </row>
@@ -26668,156 +26668,808 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Chicago Red Stars</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Bay</t>
+        </is>
+      </c>
+      <c r="G162">
+        <v>0</v>
+      </c>
+      <c r="H162">
+        <v>0</v>
+      </c>
+      <c r="I162">
+        <v>0</v>
+      </c>
+      <c r="J162">
+        <v>0</v>
+      </c>
+      <c r="K162">
+        <v>0</v>
+      </c>
+      <c r="L162">
+        <v>0</v>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N162">
+        <v>0</v>
+      </c>
+      <c r="O162">
+        <v>0</v>
+      </c>
+      <c r="P162">
+        <v>0</v>
+      </c>
+      <c r="Q162">
+        <v>0</v>
+      </c>
+      <c r="R162">
+        <v>0</v>
+      </c>
+      <c r="S162">
+        <v>0</v>
+      </c>
+      <c r="T162">
+        <v>0</v>
+      </c>
+      <c r="U162">
+        <v>0</v>
+      </c>
+      <c r="V162">
+        <v>0</v>
+      </c>
+      <c r="W162">
+        <v>0</v>
+      </c>
+      <c r="X162">
+        <v>0</v>
+      </c>
+      <c r="Y162">
+        <v>0</v>
+      </c>
+      <c r="Z162">
+        <v>0</v>
+      </c>
+      <c r="AA162">
+        <v>0</v>
+      </c>
+      <c r="AB162">
+        <v>0</v>
+      </c>
+      <c r="AC162">
+        <v>0</v>
+      </c>
+      <c r="AD162">
+        <v>0</v>
+      </c>
+      <c r="AE162">
+        <v>0</v>
+      </c>
+      <c r="AF162">
+        <v>0</v>
+      </c>
+      <c r="AG162">
+        <v>0</v>
+      </c>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ162">
+        <v>0</v>
+      </c>
+      <c r="AK162">
+        <v>0</v>
+      </c>
+      <c r="AL162">
+        <v>0</v>
+      </c>
+      <c r="AM162">
+        <v>-1</v>
+      </c>
+      <c r="AN162">
+        <v>-1</v>
+      </c>
+      <c r="AO162">
+        <v>-1</v>
+      </c>
+      <c r="AP162">
+        <v>-1</v>
+      </c>
+      <c r="AQ162">
+        <v>0</v>
+      </c>
+      <c r="AR162">
+        <v>0</v>
+      </c>
+      <c r="AS162">
+        <v>0</v>
+      </c>
+      <c r="AT162">
+        <v>0</v>
+      </c>
+      <c r="AU162" t="inlineStr">
+        <is>
+          <t>2026-08-09 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Universitario de Vinto</t>
+        </is>
+      </c>
+      <c r="G163">
+        <v>0</v>
+      </c>
+      <c r="H163">
+        <v>0</v>
+      </c>
+      <c r="I163">
+        <v>0</v>
+      </c>
+      <c r="J163">
+        <v>0</v>
+      </c>
+      <c r="K163">
+        <v>0</v>
+      </c>
+      <c r="L163">
+        <v>0</v>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N163">
+        <v>0</v>
+      </c>
+      <c r="O163">
+        <v>0</v>
+      </c>
+      <c r="P163">
+        <v>0</v>
+      </c>
+      <c r="Q163">
+        <v>0</v>
+      </c>
+      <c r="R163">
+        <v>0</v>
+      </c>
+      <c r="S163">
+        <v>0</v>
+      </c>
+      <c r="T163">
+        <v>0</v>
+      </c>
+      <c r="U163">
+        <v>0</v>
+      </c>
+      <c r="V163">
+        <v>0</v>
+      </c>
+      <c r="W163">
+        <v>0</v>
+      </c>
+      <c r="X163">
+        <v>0</v>
+      </c>
+      <c r="Y163">
+        <v>0</v>
+      </c>
+      <c r="Z163">
+        <v>0</v>
+      </c>
+      <c r="AA163">
+        <v>0</v>
+      </c>
+      <c r="AB163">
+        <v>0</v>
+      </c>
+      <c r="AC163">
+        <v>0</v>
+      </c>
+      <c r="AD163">
+        <v>0</v>
+      </c>
+      <c r="AE163">
+        <v>0</v>
+      </c>
+      <c r="AF163">
+        <v>0</v>
+      </c>
+      <c r="AG163">
+        <v>0</v>
+      </c>
+      <c r="AH163" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ163">
+        <v>0</v>
+      </c>
+      <c r="AK163">
+        <v>0</v>
+      </c>
+      <c r="AL163">
+        <v>0</v>
+      </c>
+      <c r="AM163">
+        <v>-1</v>
+      </c>
+      <c r="AN163">
+        <v>-1</v>
+      </c>
+      <c r="AO163">
+        <v>-1</v>
+      </c>
+      <c r="AP163">
+        <v>-1</v>
+      </c>
+      <c r="AQ163">
+        <v>0</v>
+      </c>
+      <c r="AR163">
+        <v>0</v>
+      </c>
+      <c r="AS163">
+        <v>0</v>
+      </c>
+      <c r="AT163">
+        <v>0</v>
+      </c>
+      <c r="AU163" t="inlineStr">
+        <is>
+          <t>2026-08-09 20:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Universidad Chile</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Palestino</t>
+        </is>
+      </c>
+      <c r="G164">
+        <v>0</v>
+      </c>
+      <c r="H164">
+        <v>0</v>
+      </c>
+      <c r="I164">
+        <v>0</v>
+      </c>
+      <c r="J164">
+        <v>0</v>
+      </c>
+      <c r="K164">
+        <v>0</v>
+      </c>
+      <c r="L164">
+        <v>0</v>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N164">
+        <v>0</v>
+      </c>
+      <c r="O164">
+        <v>0</v>
+      </c>
+      <c r="P164">
+        <v>0</v>
+      </c>
+      <c r="Q164">
+        <v>0</v>
+      </c>
+      <c r="R164">
+        <v>0</v>
+      </c>
+      <c r="S164">
+        <v>0</v>
+      </c>
+      <c r="T164">
+        <v>0</v>
+      </c>
+      <c r="U164">
+        <v>0</v>
+      </c>
+      <c r="V164">
+        <v>0</v>
+      </c>
+      <c r="W164">
+        <v>0</v>
+      </c>
+      <c r="X164">
+        <v>0</v>
+      </c>
+      <c r="Y164">
+        <v>0</v>
+      </c>
+      <c r="Z164">
+        <v>0</v>
+      </c>
+      <c r="AA164">
+        <v>0</v>
+      </c>
+      <c r="AB164">
+        <v>0</v>
+      </c>
+      <c r="AC164">
+        <v>0</v>
+      </c>
+      <c r="AD164">
+        <v>0</v>
+      </c>
+      <c r="AE164">
+        <v>0</v>
+      </c>
+      <c r="AF164">
+        <v>0</v>
+      </c>
+      <c r="AG164">
+        <v>0</v>
+      </c>
+      <c r="AH164" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI164" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ164">
+        <v>0</v>
+      </c>
+      <c r="AK164">
+        <v>0</v>
+      </c>
+      <c r="AL164">
+        <v>0</v>
+      </c>
+      <c r="AM164">
+        <v>-1</v>
+      </c>
+      <c r="AN164">
+        <v>-1</v>
+      </c>
+      <c r="AO164">
+        <v>-1</v>
+      </c>
+      <c r="AP164">
+        <v>-1</v>
+      </c>
+      <c r="AQ164">
+        <v>0</v>
+      </c>
+      <c r="AR164">
+        <v>0</v>
+      </c>
+      <c r="AS164">
+        <v>0</v>
+      </c>
+      <c r="AT164">
+        <v>0</v>
+      </c>
+      <c r="AU164" t="inlineStr">
+        <is>
+          <t>2026-08-09 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Guayaquil City FC</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="G165">
+        <v>0</v>
+      </c>
+      <c r="H165">
+        <v>0</v>
+      </c>
+      <c r="I165">
+        <v>0</v>
+      </c>
+      <c r="J165">
+        <v>0</v>
+      </c>
+      <c r="K165">
+        <v>0</v>
+      </c>
+      <c r="L165">
+        <v>0</v>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N165">
+        <v>0</v>
+      </c>
+      <c r="O165">
+        <v>0</v>
+      </c>
+      <c r="P165">
+        <v>0</v>
+      </c>
+      <c r="Q165">
+        <v>0</v>
+      </c>
+      <c r="R165">
+        <v>0</v>
+      </c>
+      <c r="S165">
+        <v>0</v>
+      </c>
+      <c r="T165">
+        <v>0</v>
+      </c>
+      <c r="U165">
+        <v>0</v>
+      </c>
+      <c r="V165">
+        <v>0</v>
+      </c>
+      <c r="W165">
+        <v>0</v>
+      </c>
+      <c r="X165">
+        <v>0</v>
+      </c>
+      <c r="Y165">
+        <v>0</v>
+      </c>
+      <c r="Z165">
+        <v>0</v>
+      </c>
+      <c r="AA165">
+        <v>0</v>
+      </c>
+      <c r="AB165">
+        <v>0</v>
+      </c>
+      <c r="AC165">
+        <v>0</v>
+      </c>
+      <c r="AD165">
+        <v>0</v>
+      </c>
+      <c r="AE165">
+        <v>0</v>
+      </c>
+      <c r="AF165">
+        <v>0</v>
+      </c>
+      <c r="AG165">
+        <v>0</v>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI165" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ165">
+        <v>0</v>
+      </c>
+      <c r="AK165">
+        <v>0</v>
+      </c>
+      <c r="AL165">
+        <v>0</v>
+      </c>
+      <c r="AM165">
+        <v>-1</v>
+      </c>
+      <c r="AN165">
+        <v>-1</v>
+      </c>
+      <c r="AO165">
+        <v>-1</v>
+      </c>
+      <c r="AP165">
+        <v>-1</v>
+      </c>
+      <c r="AQ165">
+        <v>0</v>
+      </c>
+      <c r="AR165">
+        <v>0</v>
+      </c>
+      <c r="AS165">
+        <v>0</v>
+      </c>
+      <c r="AT165">
+        <v>0</v>
+      </c>
+      <c r="AU165" t="inlineStr">
+        <is>
+          <t>2026-08-09 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr">
+      <c r="C166" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr">
+      <c r="D166" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr">
+      <c r="E166" t="inlineStr">
         <is>
           <t>Seattle Reign</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr">
+      <c r="F166" t="inlineStr">
         <is>
           <t>Angel City</t>
         </is>
       </c>
-      <c r="G162">
-        <v>0</v>
-      </c>
-      <c r="H162">
-        <v>0</v>
-      </c>
-      <c r="I162">
-        <v>0</v>
-      </c>
-      <c r="J162">
-        <v>0</v>
-      </c>
-      <c r="K162">
-        <v>0</v>
-      </c>
-      <c r="L162">
-        <v>0</v>
-      </c>
-      <c r="M162" t="inlineStr">
+      <c r="G166">
+        <v>0</v>
+      </c>
+      <c r="H166">
+        <v>0</v>
+      </c>
+      <c r="I166">
+        <v>0</v>
+      </c>
+      <c r="J166">
+        <v>0</v>
+      </c>
+      <c r="K166">
+        <v>0</v>
+      </c>
+      <c r="L166">
+        <v>0</v>
+      </c>
+      <c r="M166" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N162">
-        <v>0</v>
-      </c>
-      <c r="O162">
-        <v>0</v>
-      </c>
-      <c r="P162">
-        <v>0</v>
-      </c>
-      <c r="Q162">
-        <v>0</v>
-      </c>
-      <c r="R162">
-        <v>0</v>
-      </c>
-      <c r="S162">
-        <v>0</v>
-      </c>
-      <c r="T162">
-        <v>0</v>
-      </c>
-      <c r="U162">
-        <v>0</v>
-      </c>
-      <c r="V162">
-        <v>0</v>
-      </c>
-      <c r="W162">
-        <v>0</v>
-      </c>
-      <c r="X162">
-        <v>0</v>
-      </c>
-      <c r="Y162">
-        <v>0</v>
-      </c>
-      <c r="Z162">
-        <v>0</v>
-      </c>
-      <c r="AA162">
-        <v>0</v>
-      </c>
-      <c r="AB162">
-        <v>0</v>
-      </c>
-      <c r="AC162">
-        <v>0</v>
-      </c>
-      <c r="AD162">
-        <v>0</v>
-      </c>
-      <c r="AE162">
-        <v>0</v>
-      </c>
-      <c r="AF162">
-        <v>0</v>
-      </c>
-      <c r="AG162">
-        <v>0</v>
-      </c>
-      <c r="AH162" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI162" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ162">
-        <v>0</v>
-      </c>
-      <c r="AK162">
-        <v>0</v>
-      </c>
-      <c r="AL162">
-        <v>0</v>
-      </c>
-      <c r="AM162">
-        <v>-1</v>
-      </c>
-      <c r="AN162">
-        <v>-1</v>
-      </c>
-      <c r="AO162">
-        <v>-1</v>
-      </c>
-      <c r="AP162">
-        <v>-1</v>
-      </c>
-      <c r="AQ162">
-        <v>0</v>
-      </c>
-      <c r="AR162">
-        <v>0</v>
-      </c>
-      <c r="AS162">
-        <v>0</v>
-      </c>
-      <c r="AT162">
-        <v>0</v>
-      </c>
-      <c r="AU162" t="inlineStr">
+      <c r="N166">
+        <v>0</v>
+      </c>
+      <c r="O166">
+        <v>0</v>
+      </c>
+      <c r="P166">
+        <v>0</v>
+      </c>
+      <c r="Q166">
+        <v>0</v>
+      </c>
+      <c r="R166">
+        <v>0</v>
+      </c>
+      <c r="S166">
+        <v>0</v>
+      </c>
+      <c r="T166">
+        <v>0</v>
+      </c>
+      <c r="U166">
+        <v>0</v>
+      </c>
+      <c r="V166">
+        <v>0</v>
+      </c>
+      <c r="W166">
+        <v>0</v>
+      </c>
+      <c r="X166">
+        <v>0</v>
+      </c>
+      <c r="Y166">
+        <v>0</v>
+      </c>
+      <c r="Z166">
+        <v>0</v>
+      </c>
+      <c r="AA166">
+        <v>0</v>
+      </c>
+      <c r="AB166">
+        <v>0</v>
+      </c>
+      <c r="AC166">
+        <v>0</v>
+      </c>
+      <c r="AD166">
+        <v>0</v>
+      </c>
+      <c r="AE166">
+        <v>0</v>
+      </c>
+      <c r="AF166">
+        <v>0</v>
+      </c>
+      <c r="AG166">
+        <v>0</v>
+      </c>
+      <c r="AH166" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI166" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ166">
+        <v>0</v>
+      </c>
+      <c r="AK166">
+        <v>0</v>
+      </c>
+      <c r="AL166">
+        <v>0</v>
+      </c>
+      <c r="AM166">
+        <v>-1</v>
+      </c>
+      <c r="AN166">
+        <v>-1</v>
+      </c>
+      <c r="AO166">
+        <v>-1</v>
+      </c>
+      <c r="AP166">
+        <v>-1</v>
+      </c>
+      <c r="AQ166">
+        <v>0</v>
+      </c>
+      <c r="AR166">
+        <v>0</v>
+      </c>
+      <c r="AS166">
+        <v>0</v>
+      </c>
+      <c r="AT166">
+        <v>0</v>
+      </c>
+      <c r="AU166" t="inlineStr">
         <is>
           <t>2026-08-09 22:00:00</t>
         </is>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G60">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G61">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G80">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G82">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G83">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G84">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G85">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G113">

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G36">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G37">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N37">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G62">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G72">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G73">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G83">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G84">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G85">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G134">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G138">
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="N138">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="O138">
-        <v>3.67</v>
+        <v>3.91</v>
       </c>
       <c r="P138">
-        <v>4.48</v>
+        <v>6.63</v>
       </c>
       <c r="Q138">
         <v>0</v>
@@ -22842,10 +22842,10 @@
         <v>0</v>
       </c>
       <c r="AA138">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="AB138">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AC138">
         <v>0</v>
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,13 +22966,13 @@
         </is>
       </c>
       <c r="N139">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="O139">
-        <v>3.91</v>
+        <v>3.67</v>
       </c>
       <c r="P139">
-        <v>6.63</v>
+        <v>4.48</v>
       </c>
       <c r="Q139">
         <v>0</v>
@@ -23005,10 +23005,10 @@
         <v>0</v>
       </c>
       <c r="AA139">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="AB139">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="AC139">
         <v>0</v>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1000,10 +1000,10 @@
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC4">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4260,10 +4260,10 @@
         <v>0</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC24">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>6.06</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q65">
         <v>0</v>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -13883,10 +13883,10 @@
         <v>0</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE83">
         <v>0</v>
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14046,10 +14046,10 @@
         <v>0</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE84">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Muğlaspor</t>
         </is>
       </c>
       <c r="G99">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Muğlaspor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G100">
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O101">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q101">
         <v>0</v>
@@ -16811,10 +16811,10 @@
         <v>0</v>
       </c>
       <c r="AA101">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB101">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC101">
         <v>0</v>
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G130">

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13557,10 +13557,10 @@
         <v>0</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="O82">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="P82">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O83">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P83">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -13883,10 +13883,10 @@
         <v>0</v>
       </c>
       <c r="AC83">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD83">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>5.58</v>
+        <v>1.81</v>
       </c>
       <c r="O84">
-        <v>4.9</v>
+        <v>3.88</v>
       </c>
       <c r="P84">
-        <v>1.45</v>
+        <v>3.8</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14046,10 +14046,10 @@
         <v>0</v>
       </c>
       <c r="AC84">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD84">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AE84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -14209,10 +14209,10 @@
         <v>0</v>
       </c>
       <c r="AC85">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD85">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE85">
         <v>0</v>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="O28">
-        <v>4.25</v>
+        <v>4.7</v>
       </c>
       <c r="P28">
-        <v>5.34</v>
+        <v>5</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="O29">
-        <v>4.7</v>
+        <v>4.25</v>
       </c>
       <c r="P29">
-        <v>5</v>
+        <v>5.34</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O77">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -12899,10 +12899,10 @@
         <v>0</v>
       </c>
       <c r="AA77">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC77">
         <v>0</v>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q78">
         <v>0</v>
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q109">
         <v>0</v>
@@ -18115,10 +18115,10 @@
         <v>0</v>
       </c>
       <c r="AA109">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB109">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC109">
         <v>0</v>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2473,10 +2473,10 @@
         <v>0</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE13">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3282,10 +3282,10 @@
         <v>0</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC18">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3445,10 +3445,10 @@
         <v>0</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC19">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3614,10 +3614,10 @@
         <v>0</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE20">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="O28">
-        <v>4.7</v>
+        <v>4.25</v>
       </c>
       <c r="P28">
-        <v>5</v>
+        <v>5.34</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="O29">
-        <v>4.25</v>
+        <v>4.7</v>
       </c>
       <c r="P29">
-        <v>5.34</v>
+        <v>5</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5896,10 +5896,10 @@
         <v>0</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE34">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6053,10 +6053,10 @@
         <v>0</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC35">
         <v>0</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>5.09</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6216,10 +6216,10 @@
         <v>0</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC36">
         <v>0</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11275,10 +11275,10 @@
         <v>0</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE67">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="O77">
-        <v>3.32</v>
+        <v>3.68</v>
       </c>
       <c r="P77">
-        <v>2.42</v>
+        <v>2.03</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -12899,10 +12899,10 @@
         <v>0</v>
       </c>
       <c r="AA77">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB77">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="O78">
-        <v>3.68</v>
+        <v>3.32</v>
       </c>
       <c r="P78">
-        <v>2.03</v>
+        <v>2.42</v>
       </c>
       <c r="Q78">
         <v>0</v>
@@ -13062,10 +13062,10 @@
         <v>0</v>
       </c>
       <c r="AA78">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB78">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC78">
         <v>0</v>
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="N131">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O131">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P131">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q131">
         <v>0</v>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="O18">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P18">
-        <v>4.5</v>
+        <v>3.84</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3282,7 +3282,7 @@
         <v>0</v>
       </c>
       <c r="AA18">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AB18">
         <v>2.1</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="O19">
-        <v>3.75</v>
+        <v>3.66</v>
       </c>
       <c r="P19">
-        <v>3.84</v>
+        <v>2.17</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3445,16 +3445,16 @@
         <v>0</v>
       </c>
       <c r="AA19">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB19">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>3</v>
+        <v>1.68</v>
       </c>
       <c r="O20">
-        <v>3.66</v>
+        <v>4</v>
       </c>
       <c r="P20">
-        <v>2.17</v>
+        <v>4.5</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3608,16 +3608,16 @@
         <v>0</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC20">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD20">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE20">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>3.36</v>
+        <v>1.94</v>
       </c>
       <c r="O58">
-        <v>3.58</v>
+        <v>3.48</v>
       </c>
       <c r="P58">
-        <v>2.13</v>
+        <v>4.07</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -9802,10 +9802,10 @@
         <v>0</v>
       </c>
       <c r="AA58">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AB58">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="AC58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.94</v>
+        <v>3.36</v>
       </c>
       <c r="O59">
-        <v>3.48</v>
+        <v>3.58</v>
       </c>
       <c r="P59">
-        <v>4.07</v>
+        <v>2.13</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -9965,10 +9965,10 @@
         <v>0</v>
       </c>
       <c r="AA59">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AB59">
-        <v>1.77</v>
+        <v>1.98</v>
       </c>
       <c r="AC59">
         <v>0</v>
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q94">
         <v>0</v>
@@ -15670,10 +15670,10 @@
         <v>0</v>
       </c>
       <c r="AA94">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB94">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC94">
         <v>0</v>
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O97">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="O114">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P114">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -20195,13 +20195,13 @@
         </is>
       </c>
       <c r="N122">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O122">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="P122">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q122">
         <v>0</v>
@@ -20240,10 +20240,10 @@
         <v>0</v>
       </c>
       <c r="AC122">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD122">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE122">
         <v>0</v>
@@ -24922,13 +24922,13 @@
         </is>
       </c>
       <c r="N151">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O151">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P151">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q151">
         <v>0</v>
@@ -25085,13 +25085,13 @@
         </is>
       </c>
       <c r="N152">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O152">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P152">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q152">
         <v>0</v>
@@ -25248,13 +25248,13 @@
         </is>
       </c>
       <c r="N153">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O153">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P153">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -26715,13 +26715,13 @@
         </is>
       </c>
       <c r="N162">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="O162">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P162">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q162">
         <v>0</v>
@@ -27204,13 +27204,13 @@
         </is>
       </c>
       <c r="N165">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O165">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P165">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q165">
         <v>0</v>
@@ -27367,13 +27367,13 @@
         </is>
       </c>
       <c r="N166">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O166">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P166">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q166">
         <v>0</v>
@@ -27406,10 +27406,10 @@
         <v>0</v>
       </c>
       <c r="AA166">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB166">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC166">
         <v>0</v>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="O18">
-        <v>3.75</v>
+        <v>3.66</v>
       </c>
       <c r="P18">
-        <v>3.84</v>
+        <v>2.17</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3282,16 +3282,16 @@
         <v>0</v>
       </c>
       <c r="AA18">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB18">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>3</v>
+        <v>1.68</v>
       </c>
       <c r="O19">
-        <v>3.66</v>
+        <v>4</v>
       </c>
       <c r="P19">
-        <v>2.17</v>
+        <v>4.5</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3445,16 +3445,16 @@
         <v>0</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC19">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD19">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="O20">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P20">
-        <v>4.5</v>
+        <v>3.84</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3608,7 +3608,7 @@
         <v>0</v>
       </c>
       <c r="AA20">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AB20">
         <v>2.1</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G128">
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G158">
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G159">

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -10297,10 +10297,10 @@
         <v>0</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE61">
         <v>0</v>
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>7.49</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -13883,10 +13883,10 @@
         <v>0</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE83">
         <v>0</v>
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q98">
         <v>0</v>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -10134,10 +10134,10 @@
         <v>0</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O61">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P61">
-        <v>5.61</v>
+        <v>0</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -10297,10 +10297,10 @@
         <v>0</v>
       </c>
       <c r="AC61">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD61">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE61">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>1.4</v>
+        <v>1.81</v>
       </c>
       <c r="O80">
-        <v>5.2</v>
+        <v>3.88</v>
       </c>
       <c r="P80">
-        <v>5.97</v>
+        <v>3.8</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.46</v>
+        <v>1.4</v>
       </c>
       <c r="O81">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="P81">
-        <v>2.4</v>
+        <v>5.97</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13557,10 +13557,10 @@
         <v>0</v>
       </c>
       <c r="AC81">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD81">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.31</v>
+        <v>2.46</v>
       </c>
       <c r="O82">
-        <v>5.65</v>
+        <v>3.9</v>
       </c>
       <c r="P82">
-        <v>7.49</v>
+        <v>2.4</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -13720,10 +13720,10 @@
         <v>0</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD82">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.8</v>
+        <v>1.31</v>
       </c>
       <c r="O83">
-        <v>3.94</v>
+        <v>5.65</v>
       </c>
       <c r="P83">
-        <v>2.16</v>
+        <v>7.49</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -13883,10 +13883,10 @@
         <v>0</v>
       </c>
       <c r="AC83">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD83">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.81</v>
+        <v>2.8</v>
       </c>
       <c r="O84">
-        <v>3.88</v>
+        <v>3.94</v>
       </c>
       <c r="P84">
-        <v>3.8</v>
+        <v>2.16</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14046,10 +14046,10 @@
         <v>0</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE84">
         <v>0</v>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="O81">
-        <v>5.2</v>
+        <v>3.94</v>
       </c>
       <c r="P81">
-        <v>5.97</v>
+        <v>2.16</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13557,10 +13557,10 @@
         <v>0</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.46</v>
+        <v>1.4</v>
       </c>
       <c r="O82">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="P82">
-        <v>2.4</v>
+        <v>5.97</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -13720,10 +13720,10 @@
         <v>0</v>
       </c>
       <c r="AC82">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD82">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.31</v>
+        <v>2.46</v>
       </c>
       <c r="O83">
-        <v>5.65</v>
+        <v>3.9</v>
       </c>
       <c r="P83">
-        <v>7.49</v>
+        <v>2.4</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -13883,10 +13883,10 @@
         <v>0</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.8</v>
+        <v>1.31</v>
       </c>
       <c r="O84">
-        <v>3.94</v>
+        <v>5.65</v>
       </c>
       <c r="P84">
-        <v>2.16</v>
+        <v>7.49</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14046,10 +14046,10 @@
         <v>0</v>
       </c>
       <c r="AC84">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD84">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE84">
         <v>0</v>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -10297,10 +10297,10 @@
         <v>0</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE61">
         <v>0</v>
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="Q89">
         <v>0</v>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU166"/>
+  <dimension ref="A1:AU181"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5238,10 +5238,10 @@
         <v>0</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC30">
         <v>0</v>
@@ -7923,27 +7923,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O47">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P47">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8009,10 +8009,10 @@
         <v>0</v>
       </c>
       <c r="AA47">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB47">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC47">
         <v>0</v>
@@ -8074,7 +8074,7 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>2026-08-09 11:00:00</t>
+          <t>2026-08-09 10:30:00</t>
         </is>
       </c>
     </row>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>4.98</v>
+        <v>1.78</v>
       </c>
       <c r="O48">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="P48">
-        <v>1.63</v>
+        <v>4.94</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8172,10 +8172,10 @@
         <v>0</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC48">
         <v>0</v>
@@ -8254,22 +8254,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8417,22 +8417,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G50">
@@ -8580,22 +8580,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="O51">
-        <v>6.74</v>
+        <v>0</v>
       </c>
       <c r="P51">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>6.74</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G53">
@@ -9069,22 +9069,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G54">
@@ -9232,22 +9232,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O55">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="P55">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9395,22 +9395,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O57">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="P57">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9633,10 +9633,10 @@
         <v>0</v>
       </c>
       <c r="Y57">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z57">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA57">
         <v>0</v>
@@ -9721,22 +9721,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.94</v>
+        <v>2.89</v>
       </c>
       <c r="O58">
-        <v>3.48</v>
+        <v>2.86</v>
       </c>
       <c r="P58">
-        <v>4.07</v>
+        <v>2.61</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -9796,16 +9796,16 @@
         <v>0</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA58">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB58">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>3.36</v>
+        <v>1.94</v>
       </c>
       <c r="O59">
-        <v>3.58</v>
+        <v>3.48</v>
       </c>
       <c r="P59">
-        <v>2.13</v>
+        <v>4.07</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -9965,10 +9965,10 @@
         <v>0</v>
       </c>
       <c r="AA59">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AB59">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="AC59">
         <v>0</v>
@@ -10042,12 +10042,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.5</v>
+        <v>3.36</v>
       </c>
       <c r="O60">
-        <v>4.5</v>
+        <v>3.58</v>
       </c>
       <c r="P60">
-        <v>5.61</v>
+        <v>2.13</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -10128,16 +10128,16 @@
         <v>0</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC60">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD60">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE60">
         <v>0</v>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>2026-08-09 11:30:00</t>
+          <t>2026-08-09 11:00:00</t>
         </is>
       </c>
     </row>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.09</v>
+        <v>1.5</v>
       </c>
       <c r="O61">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="P61">
-        <v>3.1</v>
+        <v>5.61</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -10297,10 +10297,10 @@
         <v>0</v>
       </c>
       <c r="AC61">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AD61">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AE61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="O62">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P62">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10460,10 +10460,10 @@
         <v>0</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE62">
         <v>0</v>
@@ -10536,7 +10536,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G64">
@@ -10862,22 +10862,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="O65">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P65">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.23</v>
+        <v>4.36</v>
       </c>
       <c r="O66">
-        <v>3.46</v>
+        <v>3.8</v>
       </c>
       <c r="P66">
-        <v>3.03</v>
+        <v>1.74</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11183,27 +11183,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>3.13</v>
+        <v>2.23</v>
       </c>
       <c r="O67">
-        <v>3.89</v>
+        <v>3.46</v>
       </c>
       <c r="P67">
-        <v>2.15</v>
+        <v>3.03</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11275,10 +11275,10 @@
         <v>0</v>
       </c>
       <c r="AC67">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD67">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE67">
         <v>0</v>
@@ -11334,7 +11334,7 @@
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>2026-08-09 11:45:00</t>
+          <t>2026-08-09 11:30:00</t>
         </is>
       </c>
     </row>
@@ -11351,7 +11351,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -11438,10 +11438,10 @@
         <v>0</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE68">
         <v>0</v>
@@ -11509,12 +11509,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G69">
@@ -11660,7 +11660,7 @@
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>2026-08-09 12:00:00</t>
+          <t>2026-08-09 11:45:00</t>
         </is>
       </c>
     </row>
@@ -11677,7 +11677,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="G70">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G71">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G72">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G73">
@@ -12329,7 +12329,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G74">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G88">
@@ -14649,17 +14649,17 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G89">
@@ -14812,17 +14812,17 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N89">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="O89">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="P89">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.64</v>
+        <v>2.55</v>
       </c>
       <c r="O90">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="P90">
-        <v>5.01</v>
+        <v>2.75</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S90">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T90">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U90">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V90">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W90">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X90">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y90">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z90">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA90">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB90">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC90">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD90">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG90">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK90">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15100,7 +15100,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G91">
@@ -15258,27 +15258,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G92">
@@ -15409,7 +15409,7 @@
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>2026-08-09 12:45:00</t>
+          <t>2026-08-09 12:30:00</t>
         </is>
       </c>
     </row>
@@ -15421,27 +15421,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G93">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>2026-08-09 13:00:00</t>
+          <t>2026-08-09 12:30:00</t>
         </is>
       </c>
     </row>
@@ -15584,27 +15584,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="O94">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P94">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q94">
         <v>0</v>
@@ -15670,10 +15670,10 @@
         <v>0</v>
       </c>
       <c r="AA94">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB94">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC94">
         <v>0</v>
@@ -15735,7 +15735,7 @@
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>2026-08-09 13:00:00</t>
+          <t>2026-08-09 12:30:00</t>
         </is>
       </c>
     </row>
@@ -15747,27 +15747,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Veles</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Leningradets</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G95">
@@ -15898,7 +15898,7 @@
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>2026-08-09 13:00:00</t>
+          <t>2026-08-09 12:45:00</t>
         </is>
       </c>
     </row>
@@ -15915,22 +15915,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G96">
@@ -16078,22 +16078,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.51</v>
+        <v>3.03</v>
       </c>
       <c r="O97">
-        <v>2.8</v>
+        <v>3.32</v>
       </c>
       <c r="P97">
-        <v>2.8</v>
+        <v>2.29</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -16159,10 +16159,10 @@
         <v>0</v>
       </c>
       <c r="AA97">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB97">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC97">
         <v>0</v>
@@ -16241,22 +16241,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Veles</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Leningradets</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="O98">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="P98">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -16404,7 +16404,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Muğlaspor</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G99">
@@ -16567,7 +16567,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O100">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q100">
         <v>0</v>
@@ -16730,22 +16730,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Horsens</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>4.6</v>
+        <v>1.12</v>
       </c>
       <c r="O101">
-        <v>3.84</v>
+        <v>7.2</v>
       </c>
       <c r="P101">
-        <v>1.7</v>
+        <v>20</v>
       </c>
       <c r="Q101">
         <v>0</v>
@@ -16811,10 +16811,10 @@
         <v>0</v>
       </c>
       <c r="AA101">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB101">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC101">
         <v>0</v>
@@ -16893,7 +16893,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Muğlaspor</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="O102">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P102">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -17051,27 +17051,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G103">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>2026-08-09 13:15:00</t>
+          <t>2026-08-09 13:00:00</t>
         </is>
       </c>
     </row>
@@ -17214,27 +17214,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Horsens</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17300,10 +17300,10 @@
         <v>0</v>
       </c>
       <c r="AA104">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB104">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC104">
         <v>0</v>
@@ -17365,7 +17365,7 @@
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>2026-08-09 13:30:00</t>
+          <t>2026-08-09 13:00:00</t>
         </is>
       </c>
     </row>
@@ -17377,27 +17377,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="O105">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q105">
         <v>0</v>
@@ -17528,7 +17528,7 @@
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>2026-08-09 13:30:00</t>
+          <t>2026-08-09 13:00:00</t>
         </is>
       </c>
     </row>
@@ -17540,27 +17540,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G106">
@@ -17691,7 +17691,7 @@
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>2026-08-09 13:30:00</t>
+          <t>2026-08-09 13:15:00</t>
         </is>
       </c>
     </row>
@@ -17708,22 +17708,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G107">
@@ -17871,22 +17871,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,13 +17913,13 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="O108">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P108">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Q108">
         <v>0</v>
@@ -17952,10 +17952,10 @@
         <v>0</v>
       </c>
       <c r="AA108">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB108">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC108">
         <v>0</v>
@@ -18029,12 +18029,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="O109">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P109">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q109">
         <v>0</v>
@@ -18115,10 +18115,10 @@
         <v>0</v>
       </c>
       <c r="AA109">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB109">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC109">
         <v>0</v>
@@ -18180,7 +18180,7 @@
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>2026-08-09 14:00:00</t>
+          <t>2026-08-09 13:30:00</t>
         </is>
       </c>
     </row>
@@ -18192,12 +18192,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O110">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="P110">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Q110">
         <v>0</v>
@@ -18343,7 +18343,7 @@
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>2026-08-09 14:00:00</t>
+          <t>2026-08-09 13:30:00</t>
         </is>
       </c>
     </row>
@@ -18355,12 +18355,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.19</v>
+        <v>1.81</v>
       </c>
       <c r="O111">
-        <v>7.35</v>
+        <v>3.6</v>
       </c>
       <c r="P111">
-        <v>17.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q111">
         <v>0</v>
@@ -18441,16 +18441,16 @@
         <v>0</v>
       </c>
       <c r="AA111">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB111">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC111">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD111">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE111">
         <v>0</v>
@@ -18506,7 +18506,7 @@
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>2026-08-09 14:00:00</t>
+          <t>2026-08-09 13:30:00</t>
         </is>
       </c>
     </row>
@@ -18523,22 +18523,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18604,10 +18604,10 @@
         <v>0</v>
       </c>
       <c r="AA112">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB112">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC112">
         <v>0</v>
@@ -18686,7 +18686,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O113">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P113">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -18767,10 +18767,10 @@
         <v>0</v>
       </c>
       <c r="AA113">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB113">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC113">
         <v>0</v>
@@ -18844,27 +18844,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>4.25</v>
+        <v>2.28</v>
       </c>
       <c r="O114">
-        <v>4.15</v>
+        <v>3.81</v>
       </c>
       <c r="P114">
-        <v>1.75</v>
+        <v>3.18</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -18995,7 +18995,7 @@
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>2026-08-09 14:15:00</t>
+          <t>2026-08-09 14:00:00</t>
         </is>
       </c>
     </row>
@@ -19007,12 +19007,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="O115">
-        <v>0</v>
+        <v>7.35</v>
       </c>
       <c r="P115">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19099,10 +19099,10 @@
         <v>0</v>
       </c>
       <c r="AC115">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD115">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE115">
         <v>0</v>
@@ -19158,7 +19158,7 @@
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>2026-08-09 14:15:00</t>
+          <t>2026-08-09 14:00:00</t>
         </is>
       </c>
     </row>
@@ -19170,27 +19170,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="O116">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -19321,7 +19321,7 @@
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>2026-08-09 14:30:00</t>
+          <t>2026-08-09 14:15:00</t>
         </is>
       </c>
     </row>
@@ -19333,12 +19333,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G117">
@@ -19484,7 +19484,7 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>2026-08-09 14:30:00</t>
+          <t>2026-08-09 14:15:00</t>
         </is>
       </c>
     </row>
@@ -19501,22 +19501,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>1.79</v>
+        <v>2.72</v>
       </c>
       <c r="O118">
-        <v>3.89</v>
+        <v>2.5</v>
       </c>
       <c r="P118">
-        <v>4.99</v>
+        <v>2.8</v>
       </c>
       <c r="Q118">
         <v>0</v>
@@ -19582,10 +19582,10 @@
         <v>0</v>
       </c>
       <c r="AA118">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB118">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC118">
         <v>0</v>
@@ -19659,12 +19659,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G119">
@@ -19810,7 +19810,7 @@
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>2026-08-09 15:00:00</t>
+          <t>2026-08-09 14:30:00</t>
         </is>
       </c>
     </row>
@@ -19822,12 +19822,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G120">
@@ -19973,7 +19973,7 @@
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>2026-08-09 15:00:00</t>
+          <t>2026-08-09 14:30:00</t>
         </is>
       </c>
     </row>
@@ -19985,12 +19985,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,13 +20032,13 @@
         </is>
       </c>
       <c r="N121">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O121">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="P121">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="Q121">
         <v>0</v>
@@ -20136,7 +20136,7 @@
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>2026-08-09 15:00:00</t>
+          <t>2026-08-09 14:30:00</t>
         </is>
       </c>
     </row>
@@ -20153,22 +20153,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,13 +20195,13 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O122">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="P122">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q122">
         <v>0</v>
@@ -20240,10 +20240,10 @@
         <v>0</v>
       </c>
       <c r="AC122">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD122">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE122">
         <v>0</v>
@@ -20316,22 +20316,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G123">
@@ -20479,7 +20479,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O124">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P124">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q124">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R124">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S124">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="T124">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U124">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V124">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W124">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X124">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y124">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z124">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AA124">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB124">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC124">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AD124">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE124">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF124">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG124">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK124">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20642,7 +20642,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O125">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P125">
-        <v>0</v>
+        <v>8.15</v>
       </c>
       <c r="Q125">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="R125">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S125">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T125">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U125">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="V125">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W125">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X125">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y125">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z125">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA125">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB125">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC125">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD125">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE125">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF125">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AG125">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK125">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20805,7 +20805,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G126">
@@ -20968,22 +20968,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,13 +21010,13 @@
         </is>
       </c>
       <c r="N127">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O127">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="P127">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q127">
         <v>0</v>
@@ -21055,10 +21055,10 @@
         <v>0</v>
       </c>
       <c r="AC127">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD127">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE127">
         <v>0</v>
@@ -21131,22 +21131,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G128">
@@ -21289,27 +21289,27 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G129">
@@ -21440,7 +21440,7 @@
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>2026-08-09 15:15:00</t>
+          <t>2026-08-09 15:00:00</t>
         </is>
       </c>
     </row>
@@ -21452,27 +21452,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G130">
@@ -21603,7 +21603,7 @@
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>2026-08-09 15:15:00</t>
+          <t>2026-08-09 15:00:00</t>
         </is>
       </c>
     </row>
@@ -21615,12 +21615,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="N131">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O131">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P131">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -21766,7 +21766,7 @@
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>2026-08-09 15:15:00</t>
+          <t>2026-08-09 15:00:00</t>
         </is>
       </c>
     </row>
@@ -21778,12 +21778,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G132">
@@ -21929,7 +21929,7 @@
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>2026-08-09 15:15:00</t>
+          <t>2026-08-09 15:00:00</t>
         </is>
       </c>
     </row>
@@ -21941,12 +21941,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G133">
@@ -22092,7 +22092,7 @@
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>2026-08-09 15:30:00</t>
+          <t>2026-08-09 15:00:00</t>
         </is>
       </c>
     </row>
@@ -22104,12 +22104,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G134">
@@ -22255,7 +22255,7 @@
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>2026-08-09 15:30:00</t>
+          <t>2026-08-09 15:00:00</t>
         </is>
       </c>
     </row>
@@ -22267,12 +22267,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,13 +22314,13 @@
         </is>
       </c>
       <c r="N135">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="O135">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P135">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q135">
         <v>0</v>
@@ -22418,7 +22418,7 @@
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>2026-08-09 15:30:00</t>
+          <t>2026-08-09 15:15:00</t>
         </is>
       </c>
     </row>
@@ -22430,27 +22430,27 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G136">
@@ -22581,7 +22581,7 @@
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>2026-08-09 16:00:00</t>
+          <t>2026-08-09 15:15:00</t>
         </is>
       </c>
     </row>
@@ -22593,12 +22593,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,13 +22640,13 @@
         </is>
       </c>
       <c r="N137">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O137">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P137">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q137">
         <v>0</v>
@@ -22744,7 +22744,7 @@
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>2026-08-09 16:00:00</t>
+          <t>2026-08-09 15:15:00</t>
         </is>
       </c>
     </row>
@@ -22756,27 +22756,27 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G138">
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="N138">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O138">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="P138">
-        <v>6.63</v>
+        <v>0</v>
       </c>
       <c r="Q138">
         <v>0</v>
@@ -22842,10 +22842,10 @@
         <v>0</v>
       </c>
       <c r="AA138">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB138">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC138">
         <v>0</v>
@@ -22907,7 +22907,7 @@
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>2026-08-09 16:00:00</t>
+          <t>2026-08-09 15:15:00</t>
         </is>
       </c>
     </row>
@@ -22919,12 +22919,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,13 +22966,13 @@
         </is>
       </c>
       <c r="N139">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O139">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="P139">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="Q139">
         <v>0</v>
@@ -23005,10 +23005,10 @@
         <v>0</v>
       </c>
       <c r="AA139">
-        <v>1.81</v>
+        <v>2.4</v>
       </c>
       <c r="AB139">
-        <v>1.94</v>
+        <v>1.53</v>
       </c>
       <c r="AC139">
         <v>0</v>
@@ -23070,7 +23070,7 @@
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>2026-08-09 16:00:00</t>
+          <t>2026-08-09 15:30:00</t>
         </is>
       </c>
     </row>
@@ -23082,27 +23082,27 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="G140">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>2026-08-09 16:00:00</t>
+          <t>2026-08-09 15:30:00</t>
         </is>
       </c>
     </row>
@@ -23245,27 +23245,27 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G141">
@@ -23396,7 +23396,7 @@
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>2026-08-09 16:00:00</t>
+          <t>2026-08-09 15:30:00</t>
         </is>
       </c>
     </row>
@@ -23408,27 +23408,27 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G142">
@@ -23455,64 +23455,64 @@
         </is>
       </c>
       <c r="N142">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O142">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P142">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="Q142">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="R142">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S142">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T142">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U142">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V142">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W142">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X142">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y142">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z142">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA142">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB142">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC142">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD142">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE142">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF142">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG142">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23525,10 +23525,10 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK142">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23559,7 +23559,7 @@
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>2026-08-09 16:00:00</t>
+          <t>2026-08-09 15:30:00</t>
         </is>
       </c>
     </row>
@@ -23576,7 +23576,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G143">
@@ -23739,7 +23739,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="G144">
@@ -23902,22 +23902,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,13 +23944,13 @@
         </is>
       </c>
       <c r="N145">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O145">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="P145">
-        <v>0</v>
+        <v>6.63</v>
       </c>
       <c r="Q145">
         <v>0</v>
@@ -23983,10 +23983,10 @@
         <v>0</v>
       </c>
       <c r="AA145">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB145">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC145">
         <v>0</v>
@@ -24065,22 +24065,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,13 +24107,13 @@
         </is>
       </c>
       <c r="N146">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O146">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="P146">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="Q146">
         <v>0</v>
@@ -24146,10 +24146,10 @@
         <v>0</v>
       </c>
       <c r="AA146">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB146">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC146">
         <v>0</v>
@@ -24228,7 +24228,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,13 +24270,13 @@
         </is>
       </c>
       <c r="N147">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O147">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P147">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q147">
         <v>0</v>
@@ -24309,10 +24309,10 @@
         <v>0</v>
       </c>
       <c r="AA147">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB147">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC147">
         <v>0</v>
@@ -24391,7 +24391,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,13 +24433,13 @@
         </is>
       </c>
       <c r="N148">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O148">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P148">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q148">
         <v>0</v>
@@ -24472,10 +24472,10 @@
         <v>0</v>
       </c>
       <c r="AA148">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB148">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AC148">
         <v>0</v>
@@ -24549,12 +24549,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G149">
@@ -24700,7 +24700,7 @@
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>2026-08-09 16:15:00</t>
+          <t>2026-08-09 16:00:00</t>
         </is>
       </c>
     </row>
@@ -24712,27 +24712,27 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G150">
@@ -24759,13 +24759,13 @@
         </is>
       </c>
       <c r="N150">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="O150">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="P150">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="Q150">
         <v>0</v>
@@ -24798,10 +24798,10 @@
         <v>0</v>
       </c>
       <c r="AA150">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB150">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC150">
         <v>0</v>
@@ -24863,7 +24863,7 @@
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>2026-08-09 16:30:00</t>
+          <t>2026-08-09 16:00:00</t>
         </is>
       </c>
     </row>
@@ -24875,27 +24875,27 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,13 +24922,13 @@
         </is>
       </c>
       <c r="N151">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O151">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P151">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q151">
         <v>0</v>
@@ -25026,7 +25026,7 @@
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>2026-08-09 17:00:00</t>
+          <t>2026-08-09 16:00:00</t>
         </is>
       </c>
     </row>
@@ -25038,27 +25038,27 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,13 +25085,13 @@
         </is>
       </c>
       <c r="N152">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O152">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="P152">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q152">
         <v>0</v>
@@ -25189,7 +25189,7 @@
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>2026-08-09 18:00:00</t>
+          <t>2026-08-09 16:00:00</t>
         </is>
       </c>
     </row>
@@ -25201,12 +25201,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,13 +25248,13 @@
         </is>
       </c>
       <c r="N153">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="O153">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="P153">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -25287,10 +25287,10 @@
         <v>0</v>
       </c>
       <c r="AA153">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB153">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC153">
         <v>0</v>
@@ -25352,7 +25352,7 @@
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>2026-08-09 18:00:00</t>
+          <t>2026-08-09 16:00:00</t>
         </is>
       </c>
     </row>
@@ -25364,12 +25364,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="N154">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="O154">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="P154">
-        <v>3.06</v>
+        <v>3.55</v>
       </c>
       <c r="Q154">
         <v>0</v>
@@ -25444,16 +25444,16 @@
         <v>0</v>
       </c>
       <c r="Y154">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z154">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA154">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB154">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC154">
         <v>0</v>
@@ -25515,7 +25515,7 @@
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>2026-08-09 18:00:00</t>
+          <t>2026-08-09 16:00:00</t>
         </is>
       </c>
     </row>
@@ -25527,27 +25527,27 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G155">
@@ -25678,7 +25678,7 @@
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>2026-08-09 18:15:00</t>
+          <t>2026-08-09 16:00:00</t>
         </is>
       </c>
     </row>
@@ -25690,12 +25690,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,13 +25737,13 @@
         </is>
       </c>
       <c r="N156">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="O156">
-        <v>3.21</v>
+        <v>3.15</v>
       </c>
       <c r="P156">
-        <v>3.11</v>
+        <v>3.16</v>
       </c>
       <c r="Q156">
         <v>0</v>
@@ -25776,10 +25776,10 @@
         <v>0</v>
       </c>
       <c r="AA156">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AB156">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AC156">
         <v>0</v>
@@ -25841,7 +25841,7 @@
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>2026-08-09 18:30:00</t>
+          <t>2026-08-09 16:00:00</t>
         </is>
       </c>
     </row>
@@ -25853,12 +25853,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,13 +25900,13 @@
         </is>
       </c>
       <c r="N157">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="O157">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P157">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="Q157">
         <v>0</v>
@@ -25939,10 +25939,10 @@
         <v>0</v>
       </c>
       <c r="AA157">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="AB157">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AC157">
         <v>0</v>
@@ -26004,7 +26004,7 @@
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>2026-08-09 18:30:00</t>
+          <t>2026-08-09 16:00:00</t>
         </is>
       </c>
     </row>
@@ -26016,12 +26016,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O158">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P158">
-        <v>0</v>
+        <v>5.96</v>
       </c>
       <c r="Q158">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R158">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S158">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T158">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U158">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V158">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W158">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X158">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y158">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z158">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA158">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB158">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC158">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD158">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE158">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF158">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG158">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK158">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26167,7 +26167,7 @@
       </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>2026-08-09 18:30:00</t>
+          <t>2026-08-09 16:30:00</t>
         </is>
       </c>
     </row>
@@ -26179,27 +26179,27 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,64 +26226,64 @@
         </is>
       </c>
       <c r="N159">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="O159">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P159">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q159">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R159">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S159">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T159">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U159">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V159">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W159">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X159">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y159">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z159">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA159">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB159">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC159">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="AD159">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE159">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF159">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG159">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26296,10 +26296,10 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AK159">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26330,7 +26330,7 @@
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>2026-08-09 18:30:00</t>
+          <t>2026-08-09 16:30:00</t>
         </is>
       </c>
     </row>
@@ -26342,27 +26342,27 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,64 +26389,64 @@
         </is>
       </c>
       <c r="N160">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="O160">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="P160">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q160">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R160">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S160">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T160">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="U160">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V160">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="W160">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X160">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y160">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z160">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA160">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB160">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC160">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD160">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE160">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF160">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AG160">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26459,10 +26459,10 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK160">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -26493,7 +26493,7 @@
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>2026-08-09 18:30:00</t>
+          <t>2026-08-09 16:30:00</t>
         </is>
       </c>
     </row>
@@ -26505,27 +26505,27 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,13 +26552,13 @@
         </is>
       </c>
       <c r="N161">
-        <v>1.3</v>
+        <v>1.76</v>
       </c>
       <c r="O161">
-        <v>5.48</v>
+        <v>3.89</v>
       </c>
       <c r="P161">
-        <v>11.3</v>
+        <v>4.89</v>
       </c>
       <c r="Q161">
         <v>0</v>
@@ -26591,10 +26591,10 @@
         <v>0</v>
       </c>
       <c r="AA161">
-        <v>1.63</v>
+        <v>1.89</v>
       </c>
       <c r="AB161">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AC161">
         <v>0</v>
@@ -26656,7 +26656,7 @@
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>2026-08-09 19:30:00</t>
+          <t>2026-08-09 16:30:00</t>
         </is>
       </c>
     </row>
@@ -26668,12 +26668,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G162">
@@ -26715,13 +26715,13 @@
         </is>
       </c>
       <c r="N162">
-        <v>4.52</v>
+        <v>1.58</v>
       </c>
       <c r="O162">
-        <v>3.92</v>
+        <v>3.1</v>
       </c>
       <c r="P162">
-        <v>1.6</v>
+        <v>6</v>
       </c>
       <c r="Q162">
         <v>0</v>
@@ -26754,10 +26754,10 @@
         <v>0</v>
       </c>
       <c r="AA162">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB162">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC162">
         <v>0</v>
@@ -26819,7 +26819,7 @@
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>2026-08-09 20:00:00</t>
+          <t>2026-08-09 17:00:00</t>
         </is>
       </c>
     </row>
@@ -26831,12 +26831,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G163">
@@ -26878,13 +26878,13 @@
         </is>
       </c>
       <c r="N163">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O163">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P163">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q163">
         <v>0</v>
@@ -26982,7 +26982,7 @@
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>2026-08-09 20:30:00</t>
+          <t>2026-08-09 17:00:00</t>
         </is>
       </c>
     </row>
@@ -26994,12 +26994,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G164">
@@ -27145,7 +27145,7 @@
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>2026-08-09 21:00:00</t>
+          <t>2026-08-09 17:15:00</t>
         </is>
       </c>
     </row>
@@ -27157,12 +27157,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G165">
@@ -27204,64 +27204,64 @@
         </is>
       </c>
       <c r="N165">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="O165">
+        <v>2.8</v>
+      </c>
+      <c r="P165">
+        <v>3.6</v>
+      </c>
+      <c r="Q165">
         <v>3</v>
       </c>
-      <c r="P165">
-        <v>2.8</v>
-      </c>
-      <c r="Q165">
-        <v>0</v>
-      </c>
       <c r="R165">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S165">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T165">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U165">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V165">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W165">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X165">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y165">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z165">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA165">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB165">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC165">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AD165">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE165">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF165">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG165">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
@@ -27274,10 +27274,10 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK165">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27308,7 +27308,7 @@
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>2026-08-09 21:00:00</t>
+          <t>2026-08-09 17:30:00</t>
         </is>
       </c>
     </row>
@@ -27320,156 +27320,2601 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Indy Eleven</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Hartford Athletic</t>
+        </is>
+      </c>
+      <c r="G166">
+        <v>0</v>
+      </c>
+      <c r="H166">
+        <v>0</v>
+      </c>
+      <c r="I166">
+        <v>0</v>
+      </c>
+      <c r="J166">
+        <v>0</v>
+      </c>
+      <c r="K166">
+        <v>0</v>
+      </c>
+      <c r="L166">
+        <v>0</v>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N166">
+        <v>1.77</v>
+      </c>
+      <c r="O166">
+        <v>3.78</v>
+      </c>
+      <c r="P166">
+        <v>3.7</v>
+      </c>
+      <c r="Q166">
+        <v>0</v>
+      </c>
+      <c r="R166">
+        <v>0</v>
+      </c>
+      <c r="S166">
+        <v>0</v>
+      </c>
+      <c r="T166">
+        <v>0</v>
+      </c>
+      <c r="U166">
+        <v>0</v>
+      </c>
+      <c r="V166">
+        <v>0</v>
+      </c>
+      <c r="W166">
+        <v>0</v>
+      </c>
+      <c r="X166">
+        <v>0</v>
+      </c>
+      <c r="Y166">
+        <v>0</v>
+      </c>
+      <c r="Z166">
+        <v>0</v>
+      </c>
+      <c r="AA166">
+        <v>0</v>
+      </c>
+      <c r="AB166">
+        <v>0</v>
+      </c>
+      <c r="AC166">
+        <v>0</v>
+      </c>
+      <c r="AD166">
+        <v>0</v>
+      </c>
+      <c r="AE166">
+        <v>0</v>
+      </c>
+      <c r="AF166">
+        <v>0</v>
+      </c>
+      <c r="AG166">
+        <v>0</v>
+      </c>
+      <c r="AH166" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI166" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ166">
+        <v>0</v>
+      </c>
+      <c r="AK166">
+        <v>0</v>
+      </c>
+      <c r="AL166">
+        <v>0</v>
+      </c>
+      <c r="AM166">
+        <v>-1</v>
+      </c>
+      <c r="AN166">
+        <v>-1</v>
+      </c>
+      <c r="AO166">
+        <v>-1</v>
+      </c>
+      <c r="AP166">
+        <v>-1</v>
+      </c>
+      <c r="AQ166">
+        <v>0</v>
+      </c>
+      <c r="AR166">
+        <v>0</v>
+      </c>
+      <c r="AS166">
+        <v>0</v>
+      </c>
+      <c r="AT166">
+        <v>0</v>
+      </c>
+      <c r="AU166" t="inlineStr">
+        <is>
+          <t>2026-08-09 18:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>San Martín Tucumán</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>San Martín San Juan</t>
+        </is>
+      </c>
+      <c r="G167">
+        <v>0</v>
+      </c>
+      <c r="H167">
+        <v>0</v>
+      </c>
+      <c r="I167">
+        <v>0</v>
+      </c>
+      <c r="J167">
+        <v>0</v>
+      </c>
+      <c r="K167">
+        <v>0</v>
+      </c>
+      <c r="L167">
+        <v>0</v>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N167">
+        <v>0</v>
+      </c>
+      <c r="O167">
+        <v>0</v>
+      </c>
+      <c r="P167">
+        <v>0</v>
+      </c>
+      <c r="Q167">
+        <v>0</v>
+      </c>
+      <c r="R167">
+        <v>0</v>
+      </c>
+      <c r="S167">
+        <v>0</v>
+      </c>
+      <c r="T167">
+        <v>0</v>
+      </c>
+      <c r="U167">
+        <v>0</v>
+      </c>
+      <c r="V167">
+        <v>0</v>
+      </c>
+      <c r="W167">
+        <v>0</v>
+      </c>
+      <c r="X167">
+        <v>0</v>
+      </c>
+      <c r="Y167">
+        <v>0</v>
+      </c>
+      <c r="Z167">
+        <v>0</v>
+      </c>
+      <c r="AA167">
+        <v>2.87</v>
+      </c>
+      <c r="AB167">
+        <v>1.4</v>
+      </c>
+      <c r="AC167">
+        <v>0</v>
+      </c>
+      <c r="AD167">
+        <v>0</v>
+      </c>
+      <c r="AE167">
+        <v>0</v>
+      </c>
+      <c r="AF167">
+        <v>0</v>
+      </c>
+      <c r="AG167">
+        <v>0</v>
+      </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ167">
+        <v>0</v>
+      </c>
+      <c r="AK167">
+        <v>0</v>
+      </c>
+      <c r="AL167">
+        <v>0</v>
+      </c>
+      <c r="AM167">
+        <v>-1</v>
+      </c>
+      <c r="AN167">
+        <v>-1</v>
+      </c>
+      <c r="AO167">
+        <v>-1</v>
+      </c>
+      <c r="AP167">
+        <v>-1</v>
+      </c>
+      <c r="AQ167">
+        <v>0</v>
+      </c>
+      <c r="AR167">
+        <v>0</v>
+      </c>
+      <c r="AS167">
+        <v>0</v>
+      </c>
+      <c r="AT167">
+        <v>0</v>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>2026-08-09 18:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Delfin SC</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Orense SC</t>
+        </is>
+      </c>
+      <c r="G168">
+        <v>0</v>
+      </c>
+      <c r="H168">
+        <v>0</v>
+      </c>
+      <c r="I168">
+        <v>0</v>
+      </c>
+      <c r="J168">
+        <v>0</v>
+      </c>
+      <c r="K168">
+        <v>0</v>
+      </c>
+      <c r="L168">
+        <v>0</v>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N168">
+        <v>2.38</v>
+      </c>
+      <c r="O168">
+        <v>3</v>
+      </c>
+      <c r="P168">
+        <v>3</v>
+      </c>
+      <c r="Q168">
+        <v>0</v>
+      </c>
+      <c r="R168">
+        <v>0</v>
+      </c>
+      <c r="S168">
+        <v>0</v>
+      </c>
+      <c r="T168">
+        <v>0</v>
+      </c>
+      <c r="U168">
+        <v>0</v>
+      </c>
+      <c r="V168">
+        <v>0</v>
+      </c>
+      <c r="W168">
+        <v>0</v>
+      </c>
+      <c r="X168">
+        <v>0</v>
+      </c>
+      <c r="Y168">
+        <v>0</v>
+      </c>
+      <c r="Z168">
+        <v>0</v>
+      </c>
+      <c r="AA168">
+        <v>0</v>
+      </c>
+      <c r="AB168">
+        <v>0</v>
+      </c>
+      <c r="AC168">
+        <v>0</v>
+      </c>
+      <c r="AD168">
+        <v>0</v>
+      </c>
+      <c r="AE168">
+        <v>0</v>
+      </c>
+      <c r="AF168">
+        <v>0</v>
+      </c>
+      <c r="AG168">
+        <v>0</v>
+      </c>
+      <c r="AH168" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI168" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ168">
+        <v>0</v>
+      </c>
+      <c r="AK168">
+        <v>0</v>
+      </c>
+      <c r="AL168">
+        <v>0</v>
+      </c>
+      <c r="AM168">
+        <v>-1</v>
+      </c>
+      <c r="AN168">
+        <v>-1</v>
+      </c>
+      <c r="AO168">
+        <v>-1</v>
+      </c>
+      <c r="AP168">
+        <v>-1</v>
+      </c>
+      <c r="AQ168">
+        <v>0</v>
+      </c>
+      <c r="AR168">
+        <v>0</v>
+      </c>
+      <c r="AS168">
+        <v>0</v>
+      </c>
+      <c r="AT168">
+        <v>0</v>
+      </c>
+      <c r="AU168" t="inlineStr">
+        <is>
+          <t>2026-08-09 18:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="G169">
+        <v>0</v>
+      </c>
+      <c r="H169">
+        <v>0</v>
+      </c>
+      <c r="I169">
+        <v>0</v>
+      </c>
+      <c r="J169">
+        <v>0</v>
+      </c>
+      <c r="K169">
+        <v>0</v>
+      </c>
+      <c r="L169">
+        <v>0</v>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N169">
+        <v>2.47</v>
+      </c>
+      <c r="O169">
+        <v>2.92</v>
+      </c>
+      <c r="P169">
+        <v>3.06</v>
+      </c>
+      <c r="Q169">
+        <v>0</v>
+      </c>
+      <c r="R169">
+        <v>0</v>
+      </c>
+      <c r="S169">
+        <v>0</v>
+      </c>
+      <c r="T169">
+        <v>0</v>
+      </c>
+      <c r="U169">
+        <v>0</v>
+      </c>
+      <c r="V169">
+        <v>0</v>
+      </c>
+      <c r="W169">
+        <v>0</v>
+      </c>
+      <c r="X169">
+        <v>0</v>
+      </c>
+      <c r="Y169">
+        <v>1.51</v>
+      </c>
+      <c r="Z169">
+        <v>2.37</v>
+      </c>
+      <c r="AA169">
+        <v>0</v>
+      </c>
+      <c r="AB169">
+        <v>0</v>
+      </c>
+      <c r="AC169">
+        <v>0</v>
+      </c>
+      <c r="AD169">
+        <v>0</v>
+      </c>
+      <c r="AE169">
+        <v>0</v>
+      </c>
+      <c r="AF169">
+        <v>0</v>
+      </c>
+      <c r="AG169">
+        <v>0</v>
+      </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ169">
+        <v>0</v>
+      </c>
+      <c r="AK169">
+        <v>0</v>
+      </c>
+      <c r="AL169">
+        <v>0</v>
+      </c>
+      <c r="AM169">
+        <v>-1</v>
+      </c>
+      <c r="AN169">
+        <v>-1</v>
+      </c>
+      <c r="AO169">
+        <v>-1</v>
+      </c>
+      <c r="AP169">
+        <v>-1</v>
+      </c>
+      <c r="AQ169">
+        <v>0</v>
+      </c>
+      <c r="AR169">
+        <v>0</v>
+      </c>
+      <c r="AS169">
+        <v>0</v>
+      </c>
+      <c r="AT169">
+        <v>0</v>
+      </c>
+      <c r="AU169" t="inlineStr">
+        <is>
+          <t>2026-08-09 18:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Real Potosí</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Blooming</t>
+        </is>
+      </c>
+      <c r="G170">
+        <v>0</v>
+      </c>
+      <c r="H170">
+        <v>0</v>
+      </c>
+      <c r="I170">
+        <v>0</v>
+      </c>
+      <c r="J170">
+        <v>0</v>
+      </c>
+      <c r="K170">
+        <v>0</v>
+      </c>
+      <c r="L170">
+        <v>0</v>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N170">
+        <v>0</v>
+      </c>
+      <c r="O170">
+        <v>0</v>
+      </c>
+      <c r="P170">
+        <v>0</v>
+      </c>
+      <c r="Q170">
+        <v>0</v>
+      </c>
+      <c r="R170">
+        <v>0</v>
+      </c>
+      <c r="S170">
+        <v>0</v>
+      </c>
+      <c r="T170">
+        <v>0</v>
+      </c>
+      <c r="U170">
+        <v>0</v>
+      </c>
+      <c r="V170">
+        <v>0</v>
+      </c>
+      <c r="W170">
+        <v>0</v>
+      </c>
+      <c r="X170">
+        <v>0</v>
+      </c>
+      <c r="Y170">
+        <v>0</v>
+      </c>
+      <c r="Z170">
+        <v>0</v>
+      </c>
+      <c r="AA170">
+        <v>0</v>
+      </c>
+      <c r="AB170">
+        <v>0</v>
+      </c>
+      <c r="AC170">
+        <v>0</v>
+      </c>
+      <c r="AD170">
+        <v>0</v>
+      </c>
+      <c r="AE170">
+        <v>0</v>
+      </c>
+      <c r="AF170">
+        <v>0</v>
+      </c>
+      <c r="AG170">
+        <v>0</v>
+      </c>
+      <c r="AH170" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI170" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ170">
+        <v>0</v>
+      </c>
+      <c r="AK170">
+        <v>0</v>
+      </c>
+      <c r="AL170">
+        <v>0</v>
+      </c>
+      <c r="AM170">
+        <v>-1</v>
+      </c>
+      <c r="AN170">
+        <v>-1</v>
+      </c>
+      <c r="AO170">
+        <v>-1</v>
+      </c>
+      <c r="AP170">
+        <v>-1</v>
+      </c>
+      <c r="AQ170">
+        <v>0</v>
+      </c>
+      <c r="AR170">
+        <v>0</v>
+      </c>
+      <c r="AS170">
+        <v>0</v>
+      </c>
+      <c r="AT170">
+        <v>0</v>
+      </c>
+      <c r="AU170" t="inlineStr">
+        <is>
+          <t>2026-08-09 18:15:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Atlético PR</t>
+        </is>
+      </c>
+      <c r="G171">
+        <v>0</v>
+      </c>
+      <c r="H171">
+        <v>0</v>
+      </c>
+      <c r="I171">
+        <v>0</v>
+      </c>
+      <c r="J171">
+        <v>0</v>
+      </c>
+      <c r="K171">
+        <v>0</v>
+      </c>
+      <c r="L171">
+        <v>0</v>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N171">
+        <v>2.45</v>
+      </c>
+      <c r="O171">
+        <v>3.21</v>
+      </c>
+      <c r="P171">
+        <v>3.11</v>
+      </c>
+      <c r="Q171">
+        <v>0</v>
+      </c>
+      <c r="R171">
+        <v>0</v>
+      </c>
+      <c r="S171">
+        <v>0</v>
+      </c>
+      <c r="T171">
+        <v>0</v>
+      </c>
+      <c r="U171">
+        <v>0</v>
+      </c>
+      <c r="V171">
+        <v>0</v>
+      </c>
+      <c r="W171">
+        <v>0</v>
+      </c>
+      <c r="X171">
+        <v>0</v>
+      </c>
+      <c r="Y171">
+        <v>0</v>
+      </c>
+      <c r="Z171">
+        <v>0</v>
+      </c>
+      <c r="AA171">
+        <v>2.1</v>
+      </c>
+      <c r="AB171">
+        <v>1.63</v>
+      </c>
+      <c r="AC171">
+        <v>0</v>
+      </c>
+      <c r="AD171">
+        <v>0</v>
+      </c>
+      <c r="AE171">
+        <v>0</v>
+      </c>
+      <c r="AF171">
+        <v>0</v>
+      </c>
+      <c r="AG171">
+        <v>0</v>
+      </c>
+      <c r="AH171" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI171" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ171">
+        <v>0</v>
+      </c>
+      <c r="AK171">
+        <v>0</v>
+      </c>
+      <c r="AL171">
+        <v>0</v>
+      </c>
+      <c r="AM171">
+        <v>-1</v>
+      </c>
+      <c r="AN171">
+        <v>-1</v>
+      </c>
+      <c r="AO171">
+        <v>-1</v>
+      </c>
+      <c r="AP171">
+        <v>-1</v>
+      </c>
+      <c r="AQ171">
+        <v>0</v>
+      </c>
+      <c r="AR171">
+        <v>0</v>
+      </c>
+      <c r="AS171">
+        <v>0</v>
+      </c>
+      <c r="AT171">
+        <v>0</v>
+      </c>
+      <c r="AU171" t="inlineStr">
+        <is>
+          <t>2026-08-09 18:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Bragantino</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="G172">
+        <v>0</v>
+      </c>
+      <c r="H172">
+        <v>0</v>
+      </c>
+      <c r="I172">
+        <v>0</v>
+      </c>
+      <c r="J172">
+        <v>0</v>
+      </c>
+      <c r="K172">
+        <v>0</v>
+      </c>
+      <c r="L172">
+        <v>0</v>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N172">
+        <v>2.17</v>
+      </c>
+      <c r="O172">
+        <v>3.3</v>
+      </c>
+      <c r="P172">
+        <v>3.6</v>
+      </c>
+      <c r="Q172">
+        <v>0</v>
+      </c>
+      <c r="R172">
+        <v>0</v>
+      </c>
+      <c r="S172">
+        <v>0</v>
+      </c>
+      <c r="T172">
+        <v>0</v>
+      </c>
+      <c r="U172">
+        <v>0</v>
+      </c>
+      <c r="V172">
+        <v>0</v>
+      </c>
+      <c r="W172">
+        <v>0</v>
+      </c>
+      <c r="X172">
+        <v>0</v>
+      </c>
+      <c r="Y172">
+        <v>0</v>
+      </c>
+      <c r="Z172">
+        <v>0</v>
+      </c>
+      <c r="AA172">
+        <v>2.15</v>
+      </c>
+      <c r="AB172">
+        <v>1.61</v>
+      </c>
+      <c r="AC172">
+        <v>0</v>
+      </c>
+      <c r="AD172">
+        <v>0</v>
+      </c>
+      <c r="AE172">
+        <v>0</v>
+      </c>
+      <c r="AF172">
+        <v>0</v>
+      </c>
+      <c r="AG172">
+        <v>0</v>
+      </c>
+      <c r="AH172" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI172" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ172">
+        <v>0</v>
+      </c>
+      <c r="AK172">
+        <v>0</v>
+      </c>
+      <c r="AL172">
+        <v>0</v>
+      </c>
+      <c r="AM172">
+        <v>-1</v>
+      </c>
+      <c r="AN172">
+        <v>-1</v>
+      </c>
+      <c r="AO172">
+        <v>-1</v>
+      </c>
+      <c r="AP172">
+        <v>-1</v>
+      </c>
+      <c r="AQ172">
+        <v>0</v>
+      </c>
+      <c r="AR172">
+        <v>0</v>
+      </c>
+      <c r="AS172">
+        <v>0</v>
+      </c>
+      <c r="AT172">
+        <v>0</v>
+      </c>
+      <c r="AU172" t="inlineStr">
+        <is>
+          <t>2026-08-09 18:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Itabaiana</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Caxias</t>
+        </is>
+      </c>
+      <c r="G173">
+        <v>0</v>
+      </c>
+      <c r="H173">
+        <v>0</v>
+      </c>
+      <c r="I173">
+        <v>0</v>
+      </c>
+      <c r="J173">
+        <v>0</v>
+      </c>
+      <c r="K173">
+        <v>0</v>
+      </c>
+      <c r="L173">
+        <v>0</v>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N173">
+        <v>0</v>
+      </c>
+      <c r="O173">
+        <v>0</v>
+      </c>
+      <c r="P173">
+        <v>0</v>
+      </c>
+      <c r="Q173">
+        <v>0</v>
+      </c>
+      <c r="R173">
+        <v>0</v>
+      </c>
+      <c r="S173">
+        <v>0</v>
+      </c>
+      <c r="T173">
+        <v>0</v>
+      </c>
+      <c r="U173">
+        <v>0</v>
+      </c>
+      <c r="V173">
+        <v>0</v>
+      </c>
+      <c r="W173">
+        <v>0</v>
+      </c>
+      <c r="X173">
+        <v>0</v>
+      </c>
+      <c r="Y173">
+        <v>0</v>
+      </c>
+      <c r="Z173">
+        <v>0</v>
+      </c>
+      <c r="AA173">
+        <v>0</v>
+      </c>
+      <c r="AB173">
+        <v>0</v>
+      </c>
+      <c r="AC173">
+        <v>0</v>
+      </c>
+      <c r="AD173">
+        <v>0</v>
+      </c>
+      <c r="AE173">
+        <v>0</v>
+      </c>
+      <c r="AF173">
+        <v>0</v>
+      </c>
+      <c r="AG173">
+        <v>0</v>
+      </c>
+      <c r="AH173" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI173" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ173">
+        <v>0</v>
+      </c>
+      <c r="AK173">
+        <v>0</v>
+      </c>
+      <c r="AL173">
+        <v>0</v>
+      </c>
+      <c r="AM173">
+        <v>-1</v>
+      </c>
+      <c r="AN173">
+        <v>-1</v>
+      </c>
+      <c r="AO173">
+        <v>-1</v>
+      </c>
+      <c r="AP173">
+        <v>-1</v>
+      </c>
+      <c r="AQ173">
+        <v>0</v>
+      </c>
+      <c r="AR173">
+        <v>0</v>
+      </c>
+      <c r="AS173">
+        <v>0</v>
+      </c>
+      <c r="AT173">
+        <v>0</v>
+      </c>
+      <c r="AU173" t="inlineStr">
+        <is>
+          <t>2026-08-09 18:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Maranhão</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Brusque</t>
+        </is>
+      </c>
+      <c r="G174">
+        <v>0</v>
+      </c>
+      <c r="H174">
+        <v>0</v>
+      </c>
+      <c r="I174">
+        <v>0</v>
+      </c>
+      <c r="J174">
+        <v>0</v>
+      </c>
+      <c r="K174">
+        <v>0</v>
+      </c>
+      <c r="L174">
+        <v>0</v>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N174">
+        <v>0</v>
+      </c>
+      <c r="O174">
+        <v>0</v>
+      </c>
+      <c r="P174">
+        <v>0</v>
+      </c>
+      <c r="Q174">
+        <v>0</v>
+      </c>
+      <c r="R174">
+        <v>0</v>
+      </c>
+      <c r="S174">
+        <v>0</v>
+      </c>
+      <c r="T174">
+        <v>0</v>
+      </c>
+      <c r="U174">
+        <v>0</v>
+      </c>
+      <c r="V174">
+        <v>0</v>
+      </c>
+      <c r="W174">
+        <v>0</v>
+      </c>
+      <c r="X174">
+        <v>0</v>
+      </c>
+      <c r="Y174">
+        <v>0</v>
+      </c>
+      <c r="Z174">
+        <v>0</v>
+      </c>
+      <c r="AA174">
+        <v>0</v>
+      </c>
+      <c r="AB174">
+        <v>0</v>
+      </c>
+      <c r="AC174">
+        <v>0</v>
+      </c>
+      <c r="AD174">
+        <v>0</v>
+      </c>
+      <c r="AE174">
+        <v>0</v>
+      </c>
+      <c r="AF174">
+        <v>0</v>
+      </c>
+      <c r="AG174">
+        <v>0</v>
+      </c>
+      <c r="AH174" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI174" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ174">
+        <v>0</v>
+      </c>
+      <c r="AK174">
+        <v>0</v>
+      </c>
+      <c r="AL174">
+        <v>0</v>
+      </c>
+      <c r="AM174">
+        <v>-1</v>
+      </c>
+      <c r="AN174">
+        <v>-1</v>
+      </c>
+      <c r="AO174">
+        <v>-1</v>
+      </c>
+      <c r="AP174">
+        <v>-1</v>
+      </c>
+      <c r="AQ174">
+        <v>0</v>
+      </c>
+      <c r="AR174">
+        <v>0</v>
+      </c>
+      <c r="AS174">
+        <v>0</v>
+      </c>
+      <c r="AT174">
+        <v>0</v>
+      </c>
+      <c r="AU174" t="inlineStr">
+        <is>
+          <t>2026-08-09 18:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Unión La Calera</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Colo-Colo</t>
+        </is>
+      </c>
+      <c r="G175">
+        <v>0</v>
+      </c>
+      <c r="H175">
+        <v>0</v>
+      </c>
+      <c r="I175">
+        <v>0</v>
+      </c>
+      <c r="J175">
+        <v>0</v>
+      </c>
+      <c r="K175">
+        <v>0</v>
+      </c>
+      <c r="L175">
+        <v>0</v>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N175">
+        <v>0</v>
+      </c>
+      <c r="O175">
+        <v>0</v>
+      </c>
+      <c r="P175">
+        <v>0</v>
+      </c>
+      <c r="Q175">
+        <v>0</v>
+      </c>
+      <c r="R175">
+        <v>0</v>
+      </c>
+      <c r="S175">
+        <v>0</v>
+      </c>
+      <c r="T175">
+        <v>0</v>
+      </c>
+      <c r="U175">
+        <v>0</v>
+      </c>
+      <c r="V175">
+        <v>0</v>
+      </c>
+      <c r="W175">
+        <v>0</v>
+      </c>
+      <c r="X175">
+        <v>0</v>
+      </c>
+      <c r="Y175">
+        <v>0</v>
+      </c>
+      <c r="Z175">
+        <v>0</v>
+      </c>
+      <c r="AA175">
+        <v>0</v>
+      </c>
+      <c r="AB175">
+        <v>0</v>
+      </c>
+      <c r="AC175">
+        <v>0</v>
+      </c>
+      <c r="AD175">
+        <v>0</v>
+      </c>
+      <c r="AE175">
+        <v>0</v>
+      </c>
+      <c r="AF175">
+        <v>0</v>
+      </c>
+      <c r="AG175">
+        <v>0</v>
+      </c>
+      <c r="AH175" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI175" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ175">
+        <v>0</v>
+      </c>
+      <c r="AK175">
+        <v>0</v>
+      </c>
+      <c r="AL175">
+        <v>0</v>
+      </c>
+      <c r="AM175">
+        <v>-1</v>
+      </c>
+      <c r="AN175">
+        <v>-1</v>
+      </c>
+      <c r="AO175">
+        <v>-1</v>
+      </c>
+      <c r="AP175">
+        <v>-1</v>
+      </c>
+      <c r="AQ175">
+        <v>0</v>
+      </c>
+      <c r="AR175">
+        <v>0</v>
+      </c>
+      <c r="AS175">
+        <v>0</v>
+      </c>
+      <c r="AT175">
+        <v>0</v>
+      </c>
+      <c r="AU175" t="inlineStr">
+        <is>
+          <t>2026-08-09 18:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="G176">
+        <v>0</v>
+      </c>
+      <c r="H176">
+        <v>0</v>
+      </c>
+      <c r="I176">
+        <v>0</v>
+      </c>
+      <c r="J176">
+        <v>0</v>
+      </c>
+      <c r="K176">
+        <v>0</v>
+      </c>
+      <c r="L176">
+        <v>0</v>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N176">
+        <v>1.3</v>
+      </c>
+      <c r="O176">
+        <v>5.48</v>
+      </c>
+      <c r="P176">
+        <v>11.3</v>
+      </c>
+      <c r="Q176">
+        <v>0</v>
+      </c>
+      <c r="R176">
+        <v>0</v>
+      </c>
+      <c r="S176">
+        <v>0</v>
+      </c>
+      <c r="T176">
+        <v>0</v>
+      </c>
+      <c r="U176">
+        <v>0</v>
+      </c>
+      <c r="V176">
+        <v>0</v>
+      </c>
+      <c r="W176">
+        <v>0</v>
+      </c>
+      <c r="X176">
+        <v>0</v>
+      </c>
+      <c r="Y176">
+        <v>0</v>
+      </c>
+      <c r="Z176">
+        <v>0</v>
+      </c>
+      <c r="AA176">
+        <v>1.63</v>
+      </c>
+      <c r="AB176">
+        <v>2.1</v>
+      </c>
+      <c r="AC176">
+        <v>0</v>
+      </c>
+      <c r="AD176">
+        <v>0</v>
+      </c>
+      <c r="AE176">
+        <v>0</v>
+      </c>
+      <c r="AF176">
+        <v>0</v>
+      </c>
+      <c r="AG176">
+        <v>0</v>
+      </c>
+      <c r="AH176" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI176" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ176">
+        <v>0</v>
+      </c>
+      <c r="AK176">
+        <v>0</v>
+      </c>
+      <c r="AL176">
+        <v>0</v>
+      </c>
+      <c r="AM176">
+        <v>-1</v>
+      </c>
+      <c r="AN176">
+        <v>-1</v>
+      </c>
+      <c r="AO176">
+        <v>-1</v>
+      </c>
+      <c r="AP176">
+        <v>-1</v>
+      </c>
+      <c r="AQ176">
+        <v>0</v>
+      </c>
+      <c r="AR176">
+        <v>0</v>
+      </c>
+      <c r="AS176">
+        <v>0</v>
+      </c>
+      <c r="AT176">
+        <v>0</v>
+      </c>
+      <c r="AU176" t="inlineStr">
+        <is>
+          <t>2026-08-09 19:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Chicago Red Stars</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Bay</t>
+        </is>
+      </c>
+      <c r="G177">
+        <v>0</v>
+      </c>
+      <c r="H177">
+        <v>0</v>
+      </c>
+      <c r="I177">
+        <v>0</v>
+      </c>
+      <c r="J177">
+        <v>0</v>
+      </c>
+      <c r="K177">
+        <v>0</v>
+      </c>
+      <c r="L177">
+        <v>0</v>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N177">
+        <v>4.52</v>
+      </c>
+      <c r="O177">
+        <v>3.92</v>
+      </c>
+      <c r="P177">
+        <v>1.6</v>
+      </c>
+      <c r="Q177">
+        <v>0</v>
+      </c>
+      <c r="R177">
+        <v>0</v>
+      </c>
+      <c r="S177">
+        <v>0</v>
+      </c>
+      <c r="T177">
+        <v>0</v>
+      </c>
+      <c r="U177">
+        <v>0</v>
+      </c>
+      <c r="V177">
+        <v>0</v>
+      </c>
+      <c r="W177">
+        <v>0</v>
+      </c>
+      <c r="X177">
+        <v>0</v>
+      </c>
+      <c r="Y177">
+        <v>0</v>
+      </c>
+      <c r="Z177">
+        <v>0</v>
+      </c>
+      <c r="AA177">
+        <v>0</v>
+      </c>
+      <c r="AB177">
+        <v>0</v>
+      </c>
+      <c r="AC177">
+        <v>0</v>
+      </c>
+      <c r="AD177">
+        <v>0</v>
+      </c>
+      <c r="AE177">
+        <v>0</v>
+      </c>
+      <c r="AF177">
+        <v>0</v>
+      </c>
+      <c r="AG177">
+        <v>0</v>
+      </c>
+      <c r="AH177" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI177" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ177">
+        <v>0</v>
+      </c>
+      <c r="AK177">
+        <v>0</v>
+      </c>
+      <c r="AL177">
+        <v>0</v>
+      </c>
+      <c r="AM177">
+        <v>-1</v>
+      </c>
+      <c r="AN177">
+        <v>-1</v>
+      </c>
+      <c r="AO177">
+        <v>-1</v>
+      </c>
+      <c r="AP177">
+        <v>-1</v>
+      </c>
+      <c r="AQ177">
+        <v>0</v>
+      </c>
+      <c r="AR177">
+        <v>0</v>
+      </c>
+      <c r="AS177">
+        <v>0</v>
+      </c>
+      <c r="AT177">
+        <v>0</v>
+      </c>
+      <c r="AU177" t="inlineStr">
+        <is>
+          <t>2026-08-09 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Universitario de Vinto</t>
+        </is>
+      </c>
+      <c r="G178">
+        <v>0</v>
+      </c>
+      <c r="H178">
+        <v>0</v>
+      </c>
+      <c r="I178">
+        <v>0</v>
+      </c>
+      <c r="J178">
+        <v>0</v>
+      </c>
+      <c r="K178">
+        <v>0</v>
+      </c>
+      <c r="L178">
+        <v>0</v>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N178">
+        <v>0</v>
+      </c>
+      <c r="O178">
+        <v>0</v>
+      </c>
+      <c r="P178">
+        <v>0</v>
+      </c>
+      <c r="Q178">
+        <v>0</v>
+      </c>
+      <c r="R178">
+        <v>0</v>
+      </c>
+      <c r="S178">
+        <v>0</v>
+      </c>
+      <c r="T178">
+        <v>0</v>
+      </c>
+      <c r="U178">
+        <v>0</v>
+      </c>
+      <c r="V178">
+        <v>0</v>
+      </c>
+      <c r="W178">
+        <v>0</v>
+      </c>
+      <c r="X178">
+        <v>0</v>
+      </c>
+      <c r="Y178">
+        <v>0</v>
+      </c>
+      <c r="Z178">
+        <v>0</v>
+      </c>
+      <c r="AA178">
+        <v>0</v>
+      </c>
+      <c r="AB178">
+        <v>0</v>
+      </c>
+      <c r="AC178">
+        <v>0</v>
+      </c>
+      <c r="AD178">
+        <v>0</v>
+      </c>
+      <c r="AE178">
+        <v>0</v>
+      </c>
+      <c r="AF178">
+        <v>0</v>
+      </c>
+      <c r="AG178">
+        <v>0</v>
+      </c>
+      <c r="AH178" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI178" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ178">
+        <v>0</v>
+      </c>
+      <c r="AK178">
+        <v>0</v>
+      </c>
+      <c r="AL178">
+        <v>0</v>
+      </c>
+      <c r="AM178">
+        <v>-1</v>
+      </c>
+      <c r="AN178">
+        <v>-1</v>
+      </c>
+      <c r="AO178">
+        <v>-1</v>
+      </c>
+      <c r="AP178">
+        <v>-1</v>
+      </c>
+      <c r="AQ178">
+        <v>0</v>
+      </c>
+      <c r="AR178">
+        <v>0</v>
+      </c>
+      <c r="AS178">
+        <v>0</v>
+      </c>
+      <c r="AT178">
+        <v>0</v>
+      </c>
+      <c r="AU178" t="inlineStr">
+        <is>
+          <t>2026-08-09 20:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Universidad Chile</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Palestino</t>
+        </is>
+      </c>
+      <c r="G179">
+        <v>0</v>
+      </c>
+      <c r="H179">
+        <v>0</v>
+      </c>
+      <c r="I179">
+        <v>0</v>
+      </c>
+      <c r="J179">
+        <v>0</v>
+      </c>
+      <c r="K179">
+        <v>0</v>
+      </c>
+      <c r="L179">
+        <v>0</v>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N179">
+        <v>0</v>
+      </c>
+      <c r="O179">
+        <v>0</v>
+      </c>
+      <c r="P179">
+        <v>0</v>
+      </c>
+      <c r="Q179">
+        <v>0</v>
+      </c>
+      <c r="R179">
+        <v>0</v>
+      </c>
+      <c r="S179">
+        <v>0</v>
+      </c>
+      <c r="T179">
+        <v>0</v>
+      </c>
+      <c r="U179">
+        <v>0</v>
+      </c>
+      <c r="V179">
+        <v>0</v>
+      </c>
+      <c r="W179">
+        <v>0</v>
+      </c>
+      <c r="X179">
+        <v>0</v>
+      </c>
+      <c r="Y179">
+        <v>0</v>
+      </c>
+      <c r="Z179">
+        <v>0</v>
+      </c>
+      <c r="AA179">
+        <v>0</v>
+      </c>
+      <c r="AB179">
+        <v>0</v>
+      </c>
+      <c r="AC179">
+        <v>0</v>
+      </c>
+      <c r="AD179">
+        <v>0</v>
+      </c>
+      <c r="AE179">
+        <v>0</v>
+      </c>
+      <c r="AF179">
+        <v>0</v>
+      </c>
+      <c r="AG179">
+        <v>0</v>
+      </c>
+      <c r="AH179" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI179" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ179">
+        <v>0</v>
+      </c>
+      <c r="AK179">
+        <v>0</v>
+      </c>
+      <c r="AL179">
+        <v>0</v>
+      </c>
+      <c r="AM179">
+        <v>-1</v>
+      </c>
+      <c r="AN179">
+        <v>-1</v>
+      </c>
+      <c r="AO179">
+        <v>-1</v>
+      </c>
+      <c r="AP179">
+        <v>-1</v>
+      </c>
+      <c r="AQ179">
+        <v>0</v>
+      </c>
+      <c r="AR179">
+        <v>0</v>
+      </c>
+      <c r="AS179">
+        <v>0</v>
+      </c>
+      <c r="AT179">
+        <v>0</v>
+      </c>
+      <c r="AU179" t="inlineStr">
+        <is>
+          <t>2026-08-09 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Guayaquil City FC</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="G180">
+        <v>0</v>
+      </c>
+      <c r="H180">
+        <v>0</v>
+      </c>
+      <c r="I180">
+        <v>0</v>
+      </c>
+      <c r="J180">
+        <v>0</v>
+      </c>
+      <c r="K180">
+        <v>0</v>
+      </c>
+      <c r="L180">
+        <v>0</v>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N180">
+        <v>2.5</v>
+      </c>
+      <c r="O180">
+        <v>3</v>
+      </c>
+      <c r="P180">
+        <v>2.8</v>
+      </c>
+      <c r="Q180">
+        <v>0</v>
+      </c>
+      <c r="R180">
+        <v>0</v>
+      </c>
+      <c r="S180">
+        <v>0</v>
+      </c>
+      <c r="T180">
+        <v>0</v>
+      </c>
+      <c r="U180">
+        <v>0</v>
+      </c>
+      <c r="V180">
+        <v>0</v>
+      </c>
+      <c r="W180">
+        <v>0</v>
+      </c>
+      <c r="X180">
+        <v>0</v>
+      </c>
+      <c r="Y180">
+        <v>0</v>
+      </c>
+      <c r="Z180">
+        <v>0</v>
+      </c>
+      <c r="AA180">
+        <v>0</v>
+      </c>
+      <c r="AB180">
+        <v>0</v>
+      </c>
+      <c r="AC180">
+        <v>0</v>
+      </c>
+      <c r="AD180">
+        <v>0</v>
+      </c>
+      <c r="AE180">
+        <v>0</v>
+      </c>
+      <c r="AF180">
+        <v>0</v>
+      </c>
+      <c r="AG180">
+        <v>0</v>
+      </c>
+      <c r="AH180" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI180" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ180">
+        <v>0</v>
+      </c>
+      <c r="AK180">
+        <v>0</v>
+      </c>
+      <c r="AL180">
+        <v>0</v>
+      </c>
+      <c r="AM180">
+        <v>-1</v>
+      </c>
+      <c r="AN180">
+        <v>-1</v>
+      </c>
+      <c r="AO180">
+        <v>-1</v>
+      </c>
+      <c r="AP180">
+        <v>-1</v>
+      </c>
+      <c r="AQ180">
+        <v>0</v>
+      </c>
+      <c r="AR180">
+        <v>0</v>
+      </c>
+      <c r="AS180">
+        <v>0</v>
+      </c>
+      <c r="AT180">
+        <v>0</v>
+      </c>
+      <c r="AU180" t="inlineStr">
+        <is>
+          <t>2026-08-09 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
+      <c r="C181" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr">
+      <c r="D181" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr">
+      <c r="E181" t="inlineStr">
         <is>
           <t>Seattle Reign</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr">
+      <c r="F181" t="inlineStr">
         <is>
           <t>Angel City</t>
         </is>
       </c>
-      <c r="G166">
-        <v>0</v>
-      </c>
-      <c r="H166">
-        <v>0</v>
-      </c>
-      <c r="I166">
-        <v>0</v>
-      </c>
-      <c r="J166">
-        <v>0</v>
-      </c>
-      <c r="K166">
-        <v>0</v>
-      </c>
-      <c r="L166">
-        <v>0</v>
-      </c>
-      <c r="M166" t="inlineStr">
+      <c r="G181">
+        <v>0</v>
+      </c>
+      <c r="H181">
+        <v>0</v>
+      </c>
+      <c r="I181">
+        <v>0</v>
+      </c>
+      <c r="J181">
+        <v>0</v>
+      </c>
+      <c r="K181">
+        <v>0</v>
+      </c>
+      <c r="L181">
+        <v>0</v>
+      </c>
+      <c r="M181" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N166">
+      <c r="N181">
         <v>2.42</v>
       </c>
-      <c r="O166">
+      <c r="O181">
         <v>3.2</v>
       </c>
-      <c r="P166">
+      <c r="P181">
         <v>2.58</v>
       </c>
-      <c r="Q166">
-        <v>0</v>
-      </c>
-      <c r="R166">
-        <v>0</v>
-      </c>
-      <c r="S166">
-        <v>0</v>
-      </c>
-      <c r="T166">
-        <v>0</v>
-      </c>
-      <c r="U166">
-        <v>0</v>
-      </c>
-      <c r="V166">
-        <v>0</v>
-      </c>
-      <c r="W166">
-        <v>0</v>
-      </c>
-      <c r="X166">
-        <v>0</v>
-      </c>
-      <c r="Y166">
-        <v>0</v>
-      </c>
-      <c r="Z166">
-        <v>0</v>
-      </c>
-      <c r="AA166">
+      <c r="Q181">
+        <v>0</v>
+      </c>
+      <c r="R181">
+        <v>0</v>
+      </c>
+      <c r="S181">
+        <v>0</v>
+      </c>
+      <c r="T181">
+        <v>0</v>
+      </c>
+      <c r="U181">
+        <v>0</v>
+      </c>
+      <c r="V181">
+        <v>0</v>
+      </c>
+      <c r="W181">
+        <v>0</v>
+      </c>
+      <c r="X181">
+        <v>0</v>
+      </c>
+      <c r="Y181">
+        <v>0</v>
+      </c>
+      <c r="Z181">
+        <v>0</v>
+      </c>
+      <c r="AA181">
         <v>1.94</v>
       </c>
-      <c r="AB166">
+      <c r="AB181">
         <v>1.73</v>
       </c>
-      <c r="AC166">
-        <v>0</v>
-      </c>
-      <c r="AD166">
-        <v>0</v>
-      </c>
-      <c r="AE166">
-        <v>0</v>
-      </c>
-      <c r="AF166">
-        <v>0</v>
-      </c>
-      <c r="AG166">
-        <v>0</v>
-      </c>
-      <c r="AH166" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI166" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ166">
-        <v>0</v>
-      </c>
-      <c r="AK166">
-        <v>0</v>
-      </c>
-      <c r="AL166">
-        <v>0</v>
-      </c>
-      <c r="AM166">
-        <v>-1</v>
-      </c>
-      <c r="AN166">
-        <v>-1</v>
-      </c>
-      <c r="AO166">
-        <v>-1</v>
-      </c>
-      <c r="AP166">
-        <v>-1</v>
-      </c>
-      <c r="AQ166">
-        <v>0</v>
-      </c>
-      <c r="AR166">
-        <v>0</v>
-      </c>
-      <c r="AS166">
-        <v>0</v>
-      </c>
-      <c r="AT166">
-        <v>0</v>
-      </c>
-      <c r="AU166" t="inlineStr">
+      <c r="AC181">
+        <v>0</v>
+      </c>
+      <c r="AD181">
+        <v>0</v>
+      </c>
+      <c r="AE181">
+        <v>0</v>
+      </c>
+      <c r="AF181">
+        <v>0</v>
+      </c>
+      <c r="AG181">
+        <v>0</v>
+      </c>
+      <c r="AH181" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI181" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ181">
+        <v>0</v>
+      </c>
+      <c r="AK181">
+        <v>0</v>
+      </c>
+      <c r="AL181">
+        <v>0</v>
+      </c>
+      <c r="AM181">
+        <v>-1</v>
+      </c>
+      <c r="AN181">
+        <v>-1</v>
+      </c>
+      <c r="AO181">
+        <v>-1</v>
+      </c>
+      <c r="AP181">
+        <v>-1</v>
+      </c>
+      <c r="AQ181">
+        <v>0</v>
+      </c>
+      <c r="AR181">
+        <v>0</v>
+      </c>
+      <c r="AS181">
+        <v>0</v>
+      </c>
+      <c r="AT181">
+        <v>0</v>
+      </c>
+      <c r="AU181" t="inlineStr">
         <is>
           <t>2026-08-09 22:00:00</t>
         </is>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>4.36</v>
+        <v>2.23</v>
       </c>
       <c r="O66">
-        <v>3.8</v>
+        <v>3.46</v>
       </c>
       <c r="P66">
-        <v>1.74</v>
+        <v>3.03</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.23</v>
+        <v>4.36</v>
       </c>
       <c r="O67">
-        <v>3.46</v>
+        <v>3.8</v>
       </c>
       <c r="P67">
-        <v>3.03</v>
+        <v>1.74</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>1.81</v>
+        <v>1.31</v>
       </c>
       <c r="O80">
-        <v>3.88</v>
+        <v>5.65</v>
       </c>
       <c r="P80">
-        <v>3.8</v>
+        <v>7.49</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.8</v>
+        <v>1.81</v>
       </c>
       <c r="O81">
-        <v>3.94</v>
+        <v>3.88</v>
       </c>
       <c r="P81">
-        <v>2.16</v>
+        <v>3.8</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13557,10 +13557,10 @@
         <v>0</v>
       </c>
       <c r="AC81">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD81">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="O82">
-        <v>5.2</v>
+        <v>3.94</v>
       </c>
       <c r="P82">
-        <v>5.97</v>
+        <v>2.16</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -13720,10 +13720,10 @@
         <v>0</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD82">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.46</v>
+        <v>1.4</v>
       </c>
       <c r="O83">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="P83">
-        <v>2.4</v>
+        <v>5.97</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -13883,10 +13883,10 @@
         <v>0</v>
       </c>
       <c r="AC83">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD83">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.31</v>
+        <v>2.46</v>
       </c>
       <c r="O84">
-        <v>5.65</v>
+        <v>3.9</v>
       </c>
       <c r="P84">
-        <v>7.49</v>
+        <v>2.4</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14046,10 +14046,10 @@
         <v>0</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE84">
         <v>0</v>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.23</v>
+        <v>4.36</v>
       </c>
       <c r="O66">
-        <v>3.46</v>
+        <v>3.8</v>
       </c>
       <c r="P66">
-        <v>3.03</v>
+        <v>1.74</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>4.36</v>
+        <v>2.23</v>
       </c>
       <c r="O67">
-        <v>3.8</v>
+        <v>3.46</v>
       </c>
       <c r="P67">
-        <v>1.74</v>
+        <v>3.03</v>
       </c>
       <c r="Q67">
         <v>0</v>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -644,55 +644,55 @@
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -970,34 +970,34 @@
         <v>2.65</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA4">
         <v>1.87</v>
@@ -1006,19 +1006,19 @@
         <v>1.81</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1296,55 +1296,55 @@
         <v>2.16</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1785,55 +1785,55 @@
         <v>2.68</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2111,55 +2111,55 @@
         <v>2.5</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2437,40 +2437,40 @@
         <v>1.84</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC13">
         <v>2.1</v>
@@ -2479,13 +2479,13 @@
         <v>1.63</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>3</v>
+        <v>1.68</v>
       </c>
       <c r="O18">
-        <v>3.66</v>
+        <v>4</v>
       </c>
       <c r="P18">
-        <v>2.17</v>
+        <v>4.5</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC18">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AD18">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="O19">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P19">
-        <v>4.5</v>
+        <v>3.84</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA19">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AB19">
         <v>2.1</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="O20">
-        <v>3.75</v>
+        <v>3.66</v>
       </c>
       <c r="P20">
-        <v>3.84</v>
+        <v>2.17</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA20">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AB20">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3741,55 +3741,55 @@
         <v>6.61</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4556,55 +4556,55 @@
         <v>6.06</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -5208,34 +5208,34 @@
         <v>3.91</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA30">
         <v>1.9</v>
@@ -5244,19 +5244,19 @@
         <v>1.78</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5534,55 +5534,55 @@
         <v>1.3</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5860,40 +5860,40 @@
         <v>1.75</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC34">
         <v>2.2</v>
@@ -5902,13 +5902,13 @@
         <v>1.58</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6023,34 +6023,34 @@
         <v>2.81</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA35">
         <v>1.71</v>
@@ -6059,19 +6059,19 @@
         <v>2</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6186,34 +6186,34 @@
         <v>5.09</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA36">
         <v>1.86</v>
@@ -6222,19 +6222,19 @@
         <v>1.84</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7490,55 +7490,55 @@
         <v>0</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7653,55 +7653,55 @@
         <v>0</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8468,55 +8468,55 @@
         <v>0</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8794,55 +8794,55 @@
         <v>15.5</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X52">
         <v>0</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK53">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9446,55 +9446,55 @@
         <v>4.84</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9609,55 +9609,55 @@
         <v>0</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK57">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9772,28 +9772,28 @@
         <v>2.61</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y58">
         <v>1.53</v>
@@ -9802,25 +9802,25 @@
         <v>2.3</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.94</v>
+        <v>3.36</v>
       </c>
       <c r="O59">
-        <v>3.48</v>
+        <v>3.58</v>
       </c>
       <c r="P59">
-        <v>4.07</v>
+        <v>2.13</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -9965,10 +9965,10 @@
         <v>0</v>
       </c>
       <c r="AA59">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AB59">
-        <v>1.77</v>
+        <v>1.98</v>
       </c>
       <c r="AC59">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>3.36</v>
+        <v>1.94</v>
       </c>
       <c r="O60">
-        <v>3.58</v>
+        <v>3.48</v>
       </c>
       <c r="P60">
-        <v>2.13</v>
+        <v>4.07</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -10128,10 +10128,10 @@
         <v>0</v>
       </c>
       <c r="AA60">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AB60">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="AC60">
         <v>0</v>
@@ -10261,40 +10261,40 @@
         <v>5.61</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC61">
         <v>2.2</v>
@@ -10303,13 +10303,13 @@
         <v>1.58</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK61">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10424,40 +10424,40 @@
         <v>3.1</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AC62">
         <v>2</v>
@@ -10466,13 +10466,13 @@
         <v>1.7</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10587,55 +10587,55 @@
         <v>3.05</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -10780,10 +10780,10 @@
         <v>0</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC64">
         <v>0</v>
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11402,40 +11402,40 @@
         <v>2.15</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AC68">
         <v>2.15</v>
@@ -11444,13 +11444,13 @@
         <v>1.61</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T69">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="U69">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V69">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W69">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y69">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z69">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD69">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE69">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF69">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK69">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T70">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U70">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V70">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W70">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y70">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z70">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF70">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK70">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G73">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S74">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T74">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U74">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V74">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W74">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X74">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y74">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z74">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC74">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD74">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE74">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF74">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG74">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK74">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12869,55 +12869,55 @@
         <v>2.03</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S77">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T77">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U77">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V77">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W77">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X77">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y77">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z77">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA77">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC77">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD77">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK77">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13032,34 +13032,34 @@
         <v>2.42</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S78">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T78">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U78">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V78">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W78">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y78">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z78">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA78">
         <v>1.98</v>
@@ -13068,19 +13068,19 @@
         <v>1.75</v>
       </c>
       <c r="AC78">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="AD78">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG78">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AK78">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13225,10 +13225,10 @@
         <v>0</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>1.31</v>
+        <v>1.81</v>
       </c>
       <c r="O80">
-        <v>5.65</v>
+        <v>3.88</v>
       </c>
       <c r="P80">
-        <v>7.49</v>
+        <v>3.8</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.81</v>
+        <v>2.8</v>
       </c>
       <c r="O81">
-        <v>3.88</v>
+        <v>3.94</v>
       </c>
       <c r="P81">
-        <v>3.8</v>
+        <v>2.16</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13557,10 +13557,10 @@
         <v>0</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="O82">
-        <v>3.94</v>
+        <v>5.2</v>
       </c>
       <c r="P82">
-        <v>2.16</v>
+        <v>5.97</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -13720,10 +13720,10 @@
         <v>0</v>
       </c>
       <c r="AC82">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD82">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.4</v>
+        <v>2.46</v>
       </c>
       <c r="O83">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="P83">
-        <v>5.97</v>
+        <v>2.4</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -13883,10 +13883,10 @@
         <v>0</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.46</v>
+        <v>5.58</v>
       </c>
       <c r="O84">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="P84">
-        <v>2.4</v>
+        <v>1.45</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14046,10 +14046,10 @@
         <v>0</v>
       </c>
       <c r="AC84">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AD84">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AE84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>5.58</v>
+        <v>1.31</v>
       </c>
       <c r="O85">
-        <v>4.9</v>
+        <v>5.65</v>
       </c>
       <c r="P85">
-        <v>1.45</v>
+        <v>7.49</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -14209,10 +14209,10 @@
         <v>0</v>
       </c>
       <c r="AC85">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD85">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AE85">
         <v>0</v>
@@ -14336,55 +14336,55 @@
         <v>0</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK86">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14499,55 +14499,55 @@
         <v>0</v>
       </c>
       <c r="Q87">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R87">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S87">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T87">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U87">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V87">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W87">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X87">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y87">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z87">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AA87">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB87">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC87">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD87">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE87">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF87">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG87">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK87">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14662,55 +14662,55 @@
         <v>4.86</v>
       </c>
       <c r="Q88">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R88">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S88">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T88">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U88">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V88">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W88">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X88">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y88">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z88">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA88">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC88">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD88">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF88">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG88">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK88">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -16292,55 +16292,55 @@
         <v>0</v>
       </c>
       <c r="Q98">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R98">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S98">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T98">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U98">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V98">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W98">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X98">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y98">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z98">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA98">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB98">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC98">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD98">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE98">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF98">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG98">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK98">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O99">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="O100">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P100">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q100">
         <v>0</v>
@@ -17270,34 +17270,34 @@
         <v>1.7</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S104">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T104">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U104">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="V104">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W104">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X104">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y104">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z104">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA104">
         <v>1.81</v>
@@ -17306,19 +17306,19 @@
         <v>1.91</v>
       </c>
       <c r="AC104">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD104">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE104">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF104">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG104">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK104">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17433,55 +17433,55 @@
         <v>1.99</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S105">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T105">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U105">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V105">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W105">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X105">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y105">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z105">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA105">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB105">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC105">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD105">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE105">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF105">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG105">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK105">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -21173,13 +21173,13 @@
         </is>
       </c>
       <c r="N128">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O128">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P128">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q128">
         <v>0</v>
@@ -21336,13 +21336,13 @@
         </is>
       </c>
       <c r="N129">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O129">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="P129">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="Q129">
         <v>0</v>
@@ -21499,13 +21499,13 @@
         </is>
       </c>
       <c r="N130">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O130">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P130">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q130">
         <v>0</v>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -2763,55 +2763,55 @@
         <v>0</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,65 +3406,65 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="O19">
-        <v>3.75</v>
+        <v>3.66</v>
       </c>
       <c r="P19">
-        <v>3.84</v>
+        <v>2.17</v>
       </c>
       <c r="Q19">
-        <v>2.54</v>
+        <v>3.58</v>
       </c>
       <c r="R19">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="S19">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T19">
-        <v>3.22</v>
+        <v>3.8</v>
       </c>
       <c r="U19">
+        <v>2.25</v>
+      </c>
+      <c r="V19">
+        <v>1.55</v>
+      </c>
+      <c r="W19">
+        <v>1.11</v>
+      </c>
+      <c r="X19">
+        <v>1.03</v>
+      </c>
+      <c r="Y19">
+        <v>1.17</v>
+      </c>
+      <c r="Z19">
+        <v>4.8</v>
+      </c>
+      <c r="AA19">
+        <v>1.53</v>
+      </c>
+      <c r="AB19">
+        <v>2.4</v>
+      </c>
+      <c r="AC19">
+        <v>2.15</v>
+      </c>
+      <c r="AD19">
+        <v>1.62</v>
+      </c>
+      <c r="AE19">
+        <v>1.17</v>
+      </c>
+      <c r="AF19">
+        <v>1.48</v>
+      </c>
+      <c r="AG19">
         <v>2.45</v>
       </c>
-      <c r="V19">
-        <v>1.54</v>
-      </c>
-      <c r="W19">
-        <v>1.1</v>
-      </c>
-      <c r="X19">
-        <v>1.04</v>
-      </c>
-      <c r="Y19">
-        <v>1.2</v>
-      </c>
-      <c r="Z19">
-        <v>4.4</v>
-      </c>
-      <c r="AA19">
-        <v>1.63</v>
-      </c>
-      <c r="AB19">
-        <v>2.1</v>
-      </c>
-      <c r="AC19">
-        <v>2.47</v>
-      </c>
-      <c r="AD19">
-        <v>1.44</v>
-      </c>
-      <c r="AE19">
-        <v>1.15</v>
-      </c>
-      <c r="AF19">
-        <v>1.53</v>
-      </c>
-      <c r="AG19">
-        <v>2.38</v>
-      </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
+        <v>1.25</v>
+      </c>
+      <c r="AK19">
         <v>1.33</v>
-      </c>
-      <c r="AK19">
-        <v>1.65</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>3</v>
+        <v>1.85</v>
       </c>
       <c r="O20">
-        <v>3.66</v>
+        <v>3.75</v>
       </c>
       <c r="P20">
-        <v>2.17</v>
+        <v>3.84</v>
       </c>
       <c r="Q20">
-        <v>3.58</v>
+        <v>2.54</v>
       </c>
       <c r="R20">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="S20">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T20">
-        <v>3.8</v>
+        <v>3.22</v>
       </c>
       <c r="U20">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="V20">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W20">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X20">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y20">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z20">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AA20">
+        <v>1.63</v>
+      </c>
+      <c r="AB20">
+        <v>2.1</v>
+      </c>
+      <c r="AC20">
+        <v>2.47</v>
+      </c>
+      <c r="AD20">
+        <v>1.44</v>
+      </c>
+      <c r="AE20">
+        <v>1.15</v>
+      </c>
+      <c r="AF20">
         <v>1.53</v>
       </c>
-      <c r="AB20">
-        <v>2.4</v>
-      </c>
-      <c r="AC20">
-        <v>2.15</v>
-      </c>
-      <c r="AD20">
-        <v>1.62</v>
-      </c>
-      <c r="AE20">
-        <v>1.17</v>
-      </c>
-      <c r="AF20">
-        <v>1.48</v>
-      </c>
       <c r="AG20">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK20">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4230,34 +4230,34 @@
         <v>2.13</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA24">
         <v>1.77</v>
@@ -4266,19 +4266,19 @@
         <v>1.94</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4393,55 +4393,55 @@
         <v>4.38</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4719,10 +4719,10 @@
         <v>1.33</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -4731,10 +4731,10 @@
         <v>0</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W27">
         <v>0</v>
@@ -4743,31 +4743,31 @@
         <v>0</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="O28">
-        <v>4.25</v>
+        <v>4.7</v>
       </c>
       <c r="P28">
-        <v>5.34</v>
+        <v>5</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="O29">
-        <v>4.7</v>
+        <v>4.25</v>
       </c>
       <c r="P29">
-        <v>5</v>
+        <v>5.34</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5371,55 +5371,55 @@
         <v>3.52</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G36">
@@ -6173,68 +6173,68 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N36">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O36">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P36">
-        <v>5.09</v>
+        <v>0</v>
       </c>
       <c r="Q36">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="R36">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S36">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T36">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="U36">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="V36">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W36">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X36">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y36">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z36">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA36">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB36">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC36">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD36">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE36">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF36">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG36">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK36">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G37">
@@ -6336,68 +6336,68 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>5.09</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -7001,55 +7001,55 @@
         <v>4.03</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7164,55 +7164,55 @@
         <v>2.02</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7327,55 +7327,55 @@
         <v>1.87</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8305,55 +8305,55 @@
         <v>1.63</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -9274,19 +9274,19 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S55">
         <v>0</v>
@@ -9295,10 +9295,10 @@
         <v>0</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W55">
         <v>0</v>
@@ -9313,25 +9313,25 @@
         <v>0</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,31 +10415,31 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="O62">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P62">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="Q62">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="R62">
-        <v>2.42</v>
+        <v>2.27</v>
       </c>
       <c r="S62">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T62">
         <v>4</v>
       </c>
       <c r="U62">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="V62">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W62">
         <v>1.17</v>
@@ -10448,31 +10448,31 @@
         <v>1.02</v>
       </c>
       <c r="Y62">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z62">
-        <v>5.4</v>
+        <v>5.75</v>
       </c>
       <c r="AA62">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AB62">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="AC62">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AD62">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AE62">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF62">
         <v>1.4</v>
       </c>
       <c r="AG62">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK62">
-        <v>1.87</v>
+        <v>1.69</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,31 +10578,31 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="O63">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P63">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q63">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="R63">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="S63">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T63">
         <v>4</v>
       </c>
       <c r="U63">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="V63">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="W63">
         <v>1.17</v>
@@ -10611,31 +10611,31 @@
         <v>1.02</v>
       </c>
       <c r="Y63">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z63">
-        <v>5.75</v>
+        <v>5.4</v>
       </c>
       <c r="AA63">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AB63">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="AC63">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AD63">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AE63">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF63">
         <v>1.4</v>
       </c>
       <c r="AG63">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK63">
-        <v>1.69</v>
+        <v>1.87</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -11076,55 +11076,55 @@
         <v>1.74</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T66">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W66">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X66">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z66">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AK66">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11239,55 +11239,55 @@
         <v>3.03</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T67">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W67">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z67">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF67">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK67">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -12543,55 +12543,55 @@
         <v>3.28</v>
       </c>
       <c r="Q75">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R75">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S75">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T75">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U75">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V75">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W75">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X75">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y75">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z75">
-        <v>0</v>
+        <v>5.31</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC75">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD75">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF75">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG75">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK75">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12706,55 +12706,55 @@
         <v>0</v>
       </c>
       <c r="Q76">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S76">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T76">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U76">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V76">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="W76">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X76">
         <v>0</v>
       </c>
       <c r="Y76">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z76">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA76">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD76">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG76">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK76">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
+        <v>2.8</v>
+      </c>
+      <c r="O77">
+        <v>3.32</v>
+      </c>
+      <c r="P77">
+        <v>2.42</v>
+      </c>
+      <c r="Q77">
         <v>3.3</v>
       </c>
-      <c r="O77">
-        <v>3.68</v>
-      </c>
-      <c r="P77">
-        <v>2.03</v>
-      </c>
-      <c r="Q77">
-        <v>4.16</v>
-      </c>
       <c r="R77">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S77">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T77">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="U77">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="V77">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="W77">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X77">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y77">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="Z77">
-        <v>4.33</v>
+        <v>3.25</v>
       </c>
       <c r="AA77">
-        <v>1.62</v>
+        <v>1.98</v>
       </c>
       <c r="AB77">
-        <v>2.29</v>
+        <v>1.75</v>
       </c>
       <c r="AC77">
-        <v>2.5</v>
+        <v>3.51</v>
       </c>
       <c r="AD77">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AE77">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF77">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AG77">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="AK77">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="O78">
-        <v>3.32</v>
+        <v>3.68</v>
       </c>
       <c r="P78">
-        <v>2.42</v>
+        <v>2.03</v>
       </c>
       <c r="Q78">
-        <v>3.3</v>
+        <v>4.16</v>
       </c>
       <c r="R78">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S78">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T78">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="U78">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="V78">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="W78">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X78">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y78">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="Z78">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="AA78">
-        <v>1.98</v>
+        <v>1.62</v>
       </c>
       <c r="AB78">
-        <v>1.75</v>
+        <v>2.29</v>
       </c>
       <c r="AC78">
-        <v>3.51</v>
+        <v>2.5</v>
       </c>
       <c r="AD78">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AE78">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF78">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AG78">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="AK78">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
+        <v>2.46</v>
+      </c>
+      <c r="O80">
+        <v>3.9</v>
+      </c>
+      <c r="P80">
+        <v>2.4</v>
+      </c>
+      <c r="Q80">
+        <v>2.98</v>
+      </c>
+      <c r="R80">
+        <v>2.42</v>
+      </c>
+      <c r="S80">
+        <v>1.2</v>
+      </c>
+      <c r="T80">
+        <v>3.9</v>
+      </c>
+      <c r="U80">
+        <v>1.98</v>
+      </c>
+      <c r="V80">
+        <v>1.76</v>
+      </c>
+      <c r="W80">
+        <v>1.2</v>
+      </c>
+      <c r="X80">
+        <v>1.01</v>
+      </c>
+      <c r="Y80">
+        <v>1.08</v>
+      </c>
+      <c r="Z80">
+        <v>6</v>
+      </c>
+      <c r="AA80">
+        <v>1.35</v>
+      </c>
+      <c r="AB80">
+        <v>2.85</v>
+      </c>
+      <c r="AC80">
         <v>1.81</v>
       </c>
-      <c r="O80">
-        <v>3.88</v>
-      </c>
-      <c r="P80">
-        <v>3.8</v>
-      </c>
-      <c r="Q80">
-        <v>0</v>
-      </c>
-      <c r="R80">
-        <v>0</v>
-      </c>
-      <c r="S80">
-        <v>0</v>
-      </c>
-      <c r="T80">
-        <v>0</v>
-      </c>
-      <c r="U80">
-        <v>0</v>
-      </c>
-      <c r="V80">
-        <v>0</v>
-      </c>
-      <c r="W80">
-        <v>0</v>
-      </c>
-      <c r="X80">
-        <v>0</v>
-      </c>
-      <c r="Y80">
-        <v>0</v>
-      </c>
-      <c r="Z80">
-        <v>0</v>
-      </c>
-      <c r="AA80">
-        <v>0</v>
-      </c>
-      <c r="AB80">
-        <v>0</v>
-      </c>
-      <c r="AC80">
-        <v>0</v>
-      </c>
       <c r="AD80">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG80">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK80">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.8</v>
+        <v>1.81</v>
       </c>
       <c r="O81">
-        <v>3.94</v>
+        <v>3.88</v>
       </c>
       <c r="P81">
-        <v>2.16</v>
+        <v>3.8</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W81">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y81">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z81">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC81">
-        <v>1.9</v>
+        <v>2.28</v>
       </c>
       <c r="AD81">
-        <v>1.9</v>
+        <v>1.54</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG81">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK81">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.4</v>
+        <v>5.58</v>
       </c>
       <c r="O82">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="P82">
-        <v>5.97</v>
+        <v>1.45</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S82">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T82">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V82">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W82">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z82">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD82">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AG82">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK82">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="O83">
-        <v>3.9</v>
+        <v>3.94</v>
       </c>
       <c r="P83">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AC83">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AD83">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>5.58</v>
+        <v>1.31</v>
       </c>
       <c r="O84">
+        <v>5.65</v>
+      </c>
+      <c r="P84">
+        <v>7.49</v>
+      </c>
+      <c r="Q84">
+        <v>1.65</v>
+      </c>
+      <c r="R84">
+        <v>2.99</v>
+      </c>
+      <c r="S84">
+        <v>1.12</v>
+      </c>
+      <c r="T84">
         <v>4.9</v>
       </c>
-      <c r="P84">
-        <v>1.45</v>
-      </c>
-      <c r="Q84">
-        <v>0</v>
-      </c>
-      <c r="R84">
-        <v>0</v>
-      </c>
-      <c r="S84">
-        <v>0</v>
-      </c>
-      <c r="T84">
-        <v>0</v>
-      </c>
       <c r="U84">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V84">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="W84">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X84">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z84">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AC84">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AD84">
-        <v>1.94</v>
+        <v>2.21</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG84">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK84">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="O85">
-        <v>5.65</v>
+        <v>5.2</v>
       </c>
       <c r="P85">
-        <v>7.49</v>
+        <v>5.97</v>
       </c>
       <c r="Q85">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="R85">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S85">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T85">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="U85">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V85">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="W85">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X85">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z85">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA85">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB85">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC85">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD85">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AE85">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF85">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG85">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK85">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -16129,34 +16129,34 @@
         <v>2.29</v>
       </c>
       <c r="Q97">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R97">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S97">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T97">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U97">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V97">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W97">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X97">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y97">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z97">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA97">
         <v>1.94</v>
@@ -16165,19 +16165,19 @@
         <v>1.78</v>
       </c>
       <c r="AC97">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="AD97">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE97">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF97">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG97">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AK97">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16781,55 +16781,55 @@
         <v>20</v>
       </c>
       <c r="Q101">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R101">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S101">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T101">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="U101">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V101">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="W101">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X101">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y101">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z101">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA101">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AB101">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AC101">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD101">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AE101">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF101">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG101">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK101">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O108">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="Q108">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="R108">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S108">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T108">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U108">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V108">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W108">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X108">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y108">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z108">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA108">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB108">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC108">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD108">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE108">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF108">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG108">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK108">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -19226,55 +19226,55 @@
         <v>1.75</v>
       </c>
       <c r="Q116">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R116">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S116">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T116">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U116">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V116">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W116">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X116">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y116">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z116">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA116">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB116">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AC116">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD116">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE116">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF116">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG116">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK116">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL116">
         <v>0</v>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,49 +8948,49 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="O53">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="P53">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="Q53">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="R53">
         <v>2.4</v>
       </c>
       <c r="S53">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T53">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U53">
-        <v>2.59</v>
+        <v>2.38</v>
       </c>
       <c r="V53">
         <v>1.48</v>
       </c>
       <c r="W53">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X53">
         <v>1.04</v>
       </c>
       <c r="Y53">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z53">
         <v>4.1</v>
       </c>
       <c r="AA53">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB53">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AC53">
         <v>2.8</v>
@@ -8999,13 +8999,13 @@
         <v>1.4</v>
       </c>
       <c r="AE53">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF53">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AG53">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK53">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,49 +9111,49 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="O54">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="P54">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q54">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="R54">
         <v>2.4</v>
       </c>
       <c r="S54">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T54">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U54">
-        <v>2.38</v>
+        <v>2.59</v>
       </c>
       <c r="V54">
         <v>1.48</v>
       </c>
       <c r="W54">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X54">
         <v>1.04</v>
       </c>
       <c r="Y54">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z54">
         <v>4.1</v>
       </c>
       <c r="AA54">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB54">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AC54">
         <v>2.8</v>
@@ -9162,13 +9162,13 @@
         <v>1.4</v>
       </c>
       <c r="AE54">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF54">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AG54">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK54">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,19 +10252,19 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.5</v>
+        <v>2.09</v>
       </c>
       <c r="O61">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="P61">
-        <v>5.61</v>
+        <v>3.1</v>
       </c>
       <c r="Q61">
-        <v>1.88</v>
+        <v>2.36</v>
       </c>
       <c r="R61">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="S61">
         <v>1.2</v>
@@ -10273,43 +10273,43 @@
         <v>4</v>
       </c>
       <c r="U61">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="V61">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="W61">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X61">
         <v>1.02</v>
       </c>
       <c r="Y61">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z61">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA61">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AB61">
-        <v>2.6</v>
+        <v>2.81</v>
       </c>
       <c r="AC61">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AD61">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AE61">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AF61">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AG61">
-        <v>2.18</v>
+        <v>2.7</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AK61">
-        <v>2.88</v>
+        <v>1.87</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,19 +10578,19 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.09</v>
+        <v>1.5</v>
       </c>
       <c r="O63">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="P63">
-        <v>3.1</v>
+        <v>5.61</v>
       </c>
       <c r="Q63">
-        <v>2.36</v>
+        <v>1.88</v>
       </c>
       <c r="R63">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="S63">
         <v>1.2</v>
@@ -10599,43 +10599,43 @@
         <v>4</v>
       </c>
       <c r="U63">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="V63">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="W63">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X63">
         <v>1.02</v>
       </c>
       <c r="Y63">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z63">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AA63">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AB63">
-        <v>2.81</v>
+        <v>2.6</v>
       </c>
       <c r="AC63">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AD63">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AE63">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AF63">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AG63">
-        <v>2.7</v>
+        <v>2.18</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AK63">
-        <v>1.87</v>
+        <v>2.88</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="O99">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P99">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O100">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q100">
         <v>0</v>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -807,10 +807,10 @@
         <v>1.67</v>
       </c>
       <c r="Q3">
-        <v>4.86</v>
+        <v>4.25</v>
       </c>
       <c r="R3">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="S3">
         <v>1.31</v>
@@ -834,10 +834,10 @@
         <v>1.2</v>
       </c>
       <c r="Z3">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="AA3">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AB3">
         <v>1.97</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK3">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -4873,31 +4873,31 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="O28">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="P28">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Q28">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="R28">
-        <v>2.66</v>
+        <v>2.85</v>
       </c>
       <c r="S28">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T28">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="U28">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V28">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="W28">
         <v>1.22</v>
@@ -4909,28 +4909,28 @@
         <v>1.1</v>
       </c>
       <c r="Z28">
-        <v>6.05</v>
+        <v>5.95</v>
       </c>
       <c r="AA28">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AB28">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AC28">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AD28">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AE28">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AF28">
         <v>1.44</v>
       </c>
       <c r="AG28">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK28">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,16 +5036,16 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="O29">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="P29">
-        <v>5.34</v>
+        <v>5.5</v>
       </c>
       <c r="Q29">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R29">
         <v>2.38</v>
@@ -5066,34 +5066,34 @@
         <v>1.12</v>
       </c>
       <c r="X29">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z29">
         <v>4.2</v>
       </c>
       <c r="AA29">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AB29">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="AC29">
-        <v>2.54</v>
+        <v>2.65</v>
       </c>
       <c r="AD29">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AE29">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF29">
         <v>1.73</v>
       </c>
       <c r="AG29">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5362,19 +5362,19 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.01</v>
+        <v>2.28</v>
       </c>
       <c r="O31">
-        <v>3.77</v>
+        <v>3.3</v>
       </c>
       <c r="P31">
-        <v>3.52</v>
+        <v>2.78</v>
       </c>
       <c r="Q31">
-        <v>2.9</v>
+        <v>2.61</v>
       </c>
       <c r="R31">
-        <v>2.46</v>
+        <v>2.27</v>
       </c>
       <c r="S31">
         <v>1.29</v>
@@ -5383,13 +5383,13 @@
         <v>3.28</v>
       </c>
       <c r="U31">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="V31">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W31">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X31">
         <v>1.01</v>
@@ -5398,13 +5398,13 @@
         <v>1.18</v>
       </c>
       <c r="Z31">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AA31">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AB31">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AC31">
         <v>2.38</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AK31">
         <v>1.54</v>
@@ -6992,16 +6992,16 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="O41">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="P41">
-        <v>4.03</v>
+        <v>3.65</v>
       </c>
       <c r="Q41">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="R41">
         <v>2.28</v>
@@ -7025,16 +7025,16 @@
         <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z41">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA41">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AB41">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AC41">
         <v>2.47</v>
@@ -7046,7 +7046,7 @@
         <v>1.19</v>
       </c>
       <c r="AF41">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG41">
         <v>2.25</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="O42">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P42">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q42">
         <v>3.58</v>
@@ -7176,10 +7176,10 @@
         <v>3.25</v>
       </c>
       <c r="U42">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="V42">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W42">
         <v>1.11</v>
@@ -7188,22 +7188,22 @@
         <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z42">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="AA42">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AB42">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AC42">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AD42">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE42">
         <v>1.14</v>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AK42">
         <v>1.3</v>
@@ -7330,7 +7330,7 @@
         <v>4.15</v>
       </c>
       <c r="R43">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S43">
         <v>1.29</v>
@@ -7345,7 +7345,7 @@
         <v>1.5</v>
       </c>
       <c r="W43">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X43">
         <v>1.02</v>
@@ -7369,7 +7369,7 @@
         <v>1.44</v>
       </c>
       <c r="AE43">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF43">
         <v>1.57</v>
@@ -8009,10 +8009,10 @@
         <v>0</v>
       </c>
       <c r="AA47">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AB47">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC47">
         <v>0</v>
@@ -8133,34 +8133,34 @@
         </is>
       </c>
       <c r="N48">
-        <v>4.98</v>
+        <v>4.78</v>
       </c>
       <c r="O48">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="P48">
-        <v>1.63</v>
+        <v>1.86</v>
       </c>
       <c r="Q48">
-        <v>4.25</v>
+        <v>4.31</v>
       </c>
       <c r="R48">
+        <v>2.46</v>
+      </c>
+      <c r="S48">
+        <v>1.28</v>
+      </c>
+      <c r="T48">
+        <v>3.3</v>
+      </c>
+      <c r="U48">
         <v>2.45</v>
       </c>
-      <c r="S48">
-        <v>1.29</v>
-      </c>
-      <c r="T48">
-        <v>3.5</v>
-      </c>
-      <c r="U48">
-        <v>2.36</v>
-      </c>
       <c r="V48">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="W48">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X48">
         <v>1.03</v>
@@ -8172,25 +8172,25 @@
         <v>4.5</v>
       </c>
       <c r="AA48">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB48">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AC48">
         <v>2.44</v>
       </c>
       <c r="AD48">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE48">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF48">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG48">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK48">
         <v>1.25</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.03</v>
+        <v>1.44</v>
       </c>
       <c r="O61">
-        <v>3.85</v>
+        <v>4.33</v>
       </c>
       <c r="P61">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="Q61">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="R61">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="S61">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T61">
-        <v>4.5</v>
+        <v>3.64</v>
       </c>
       <c r="U61">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="V61">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="W61">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="X61">
         <v>1.02</v>
       </c>
       <c r="Y61">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z61">
-        <v>5.5</v>
+        <v>5.05</v>
       </c>
       <c r="AA61">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AB61">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="AC61">
-        <v>1.98</v>
+        <v>2.19</v>
       </c>
       <c r="AD61">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="AE61">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AF61">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="AG61">
-        <v>2.8</v>
+        <v>2.18</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AK61">
-        <v>1.76</v>
+        <v>2.88</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.44</v>
+        <v>2.03</v>
       </c>
       <c r="O62">
-        <v>4.33</v>
+        <v>3.85</v>
       </c>
       <c r="P62">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="Q62">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="R62">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="S62">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T62">
-        <v>3.64</v>
+        <v>4.5</v>
       </c>
       <c r="U62">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="V62">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W62">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="X62">
         <v>1.02</v>
       </c>
       <c r="Y62">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z62">
-        <v>5.05</v>
+        <v>5.5</v>
       </c>
       <c r="AA62">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AB62">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AC62">
-        <v>2.19</v>
+        <v>1.98</v>
       </c>
       <c r="AD62">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AE62">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AF62">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
       <c r="AG62">
-        <v>2.18</v>
+        <v>2.8</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AK62">
-        <v>2.88</v>
+        <v>1.76</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10904,31 +10904,31 @@
         </is>
       </c>
       <c r="N65">
-        <v>4.36</v>
+        <v>4.93</v>
       </c>
       <c r="O65">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="P65">
-        <v>1.74</v>
+        <v>1.59</v>
       </c>
       <c r="Q65">
-        <v>4.8</v>
+        <v>4.42</v>
       </c>
       <c r="R65">
         <v>2.3</v>
       </c>
       <c r="S65">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T65">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="U65">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="V65">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W65">
         <v>1.12</v>
@@ -10937,22 +10937,22 @@
         <v>1.05</v>
       </c>
       <c r="Y65">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z65">
-        <v>3.94</v>
+        <v>3.84</v>
       </c>
       <c r="AA65">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB65">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AC65">
-        <v>2.8</v>
+        <v>2.61</v>
       </c>
       <c r="AD65">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AE65">
         <v>1.13</v>
@@ -10977,7 +10977,7 @@
         <v>2.14</v>
       </c>
       <c r="AK65">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,16 +11067,16 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
       <c r="O66">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="P66">
-        <v>3.03</v>
+        <v>2.76</v>
       </c>
       <c r="Q66">
-        <v>2.87</v>
+        <v>2.65</v>
       </c>
       <c r="R66">
         <v>2.37</v>
@@ -11085,7 +11085,7 @@
         <v>1.25</v>
       </c>
       <c r="T66">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U66">
         <v>2.4</v>
@@ -11097,7 +11097,7 @@
         <v>1.08</v>
       </c>
       <c r="X66">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y66">
         <v>1.17</v>
@@ -11106,16 +11106,16 @@
         <v>4.05</v>
       </c>
       <c r="AA66">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AB66">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AC66">
         <v>2.75</v>
       </c>
       <c r="AD66">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE66">
         <v>1.11</v>
@@ -11124,7 +11124,7 @@
         <v>1.55</v>
       </c>
       <c r="AG66">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>1.36</v>
       </c>
       <c r="AK66">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -12371,19 +12371,19 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="O74">
-        <v>3.81</v>
+        <v>3.7</v>
       </c>
       <c r="P74">
-        <v>3.28</v>
+        <v>3.05</v>
       </c>
       <c r="Q74">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="R74">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="S74">
         <v>1.25</v>
@@ -12398,16 +12398,16 @@
         <v>1.6</v>
       </c>
       <c r="W74">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X74">
         <v>1.01</v>
       </c>
       <c r="Y74">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z74">
-        <v>5.31</v>
+        <v>4.3</v>
       </c>
       <c r="AA74">
         <v>1.45</v>
@@ -12416,7 +12416,7 @@
         <v>2.55</v>
       </c>
       <c r="AC74">
-        <v>2.21</v>
+        <v>2.34</v>
       </c>
       <c r="AD74">
         <v>1.49</v>
@@ -12444,7 +12444,7 @@
         <v>1.22</v>
       </c>
       <c r="AK74">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q75">
         <v>1.34</v>
@@ -12549,7 +12549,7 @@
         <v>3.6</v>
       </c>
       <c r="S75">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="T75">
         <v>5.5</v>
@@ -12573,16 +12573,16 @@
         <v>8.5</v>
       </c>
       <c r="AA75">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AB75">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AC75">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AD75">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AE75">
         <v>1.48</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.31</v>
+        <v>4.7</v>
       </c>
       <c r="O82">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="P82">
-        <v>6.1</v>
+        <v>1.45</v>
       </c>
       <c r="Q82">
-        <v>1.68</v>
+        <v>4.13</v>
       </c>
       <c r="R82">
-        <v>3.22</v>
+        <v>2.6</v>
       </c>
       <c r="S82">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="T82">
-        <v>5</v>
+        <v>4.55</v>
       </c>
       <c r="U82">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="V82">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="W82">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="X82">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Z82">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="AA82">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AB82">
-        <v>3.9</v>
+        <v>3.28</v>
       </c>
       <c r="AC82">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="AD82">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="AE82">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AF82">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG82">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.08</v>
+        <v>2.5</v>
       </c>
       <c r="AK82">
-        <v>3.18</v>
+        <v>1.15</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="O83">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="P83">
-        <v>5.35</v>
+        <v>6.1</v>
       </c>
       <c r="Q83">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="R83">
-        <v>2.77</v>
+        <v>3.22</v>
       </c>
       <c r="S83">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="T83">
-        <v>4.65</v>
+        <v>5</v>
       </c>
       <c r="U83">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="V83">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="W83">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X83">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y83">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Z83">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AA83">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AB83">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="AC83">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AD83">
-        <v>2.04</v>
+        <v>2.21</v>
       </c>
       <c r="AE83">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AF83">
         <v>1.4</v>
       </c>
       <c r="AG83">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AK83">
-        <v>2.56</v>
+        <v>3.18</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,31 +14001,31 @@
         </is>
       </c>
       <c r="N84">
-        <v>4.7</v>
+        <v>1.45</v>
       </c>
       <c r="O84">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="P84">
-        <v>1.45</v>
+        <v>5.35</v>
       </c>
       <c r="Q84">
-        <v>4.13</v>
+        <v>1.88</v>
       </c>
       <c r="R84">
-        <v>2.6</v>
+        <v>2.77</v>
       </c>
       <c r="S84">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="T84">
-        <v>4.55</v>
+        <v>4.65</v>
       </c>
       <c r="U84">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="V84">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="W84">
         <v>1.25</v>
@@ -14034,31 +14034,31 @@
         <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z84">
-        <v>8.5</v>
+        <v>7.2</v>
       </c>
       <c r="AA84">
         <v>1.25</v>
       </c>
       <c r="AB84">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AC84">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AD84">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AE84">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AF84">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG84">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>2.5</v>
+        <v>1.12</v>
       </c>
       <c r="AK84">
-        <v>1.15</v>
+        <v>2.56</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -18894,13 +18894,13 @@
         <v>2</v>
       </c>
       <c r="O114">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="P114">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q114">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="R114">
         <v>1.85</v>
@@ -18909,7 +18909,7 @@
         <v>1.62</v>
       </c>
       <c r="T114">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="U114">
         <v>3.7</v>
@@ -18924,19 +18924,19 @@
         <v>1.08</v>
       </c>
       <c r="Y114">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="Z114">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="AA114">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="AB114">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC114">
-        <v>5.67</v>
+        <v>5.15</v>
       </c>
       <c r="AD114">
         <v>1.12</v>
@@ -18945,10 +18945,10 @@
         <v>1.03</v>
       </c>
       <c r="AF114">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="AG114">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AK114">
         <v>1.67</v>
@@ -19869,13 +19869,13 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="O120">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="P120">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="Q120">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G123">
@@ -20367,55 +20367,55 @@
         <v>0</v>
       </c>
       <c r="Q123">
-        <v>4.2</v>
+        <v>1.78</v>
       </c>
       <c r="R123">
-        <v>2.07</v>
+        <v>2.33</v>
       </c>
       <c r="S123">
+        <v>1.29</v>
+      </c>
+      <c r="T123">
+        <v>2.96</v>
+      </c>
+      <c r="U123">
+        <v>2.44</v>
+      </c>
+      <c r="V123">
+        <v>1.46</v>
+      </c>
+      <c r="W123">
+        <v>1.08</v>
+      </c>
+      <c r="X123">
+        <v>1.04</v>
+      </c>
+      <c r="Y123">
+        <v>1.17</v>
+      </c>
+      <c r="Z123">
+        <v>3.94</v>
+      </c>
+      <c r="AA123">
+        <v>1.66</v>
+      </c>
+      <c r="AB123">
+        <v>2.09</v>
+      </c>
+      <c r="AC123">
+        <v>2.9</v>
+      </c>
+      <c r="AD123">
         <v>1.38</v>
       </c>
-      <c r="T123">
-        <v>2.7</v>
-      </c>
-      <c r="U123">
-        <v>2.78</v>
-      </c>
-      <c r="V123">
-        <v>1.33</v>
-      </c>
-      <c r="W123">
-        <v>1.04</v>
-      </c>
-      <c r="X123">
-        <v>1.01</v>
-      </c>
-      <c r="Y123">
-        <v>1.26</v>
-      </c>
-      <c r="Z123">
-        <v>3.2</v>
-      </c>
-      <c r="AA123">
-        <v>2.05</v>
-      </c>
-      <c r="AB123">
-        <v>1.75</v>
-      </c>
-      <c r="AC123">
-        <v>3.2</v>
-      </c>
-      <c r="AD123">
-        <v>1.26</v>
-      </c>
       <c r="AE123">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF123">
-        <v>1.81</v>
+        <v>2.01</v>
       </c>
       <c r="AG123">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="AK123">
-        <v>1.15</v>
+        <v>3.05</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G124">
@@ -20530,55 +20530,55 @@
         <v>0</v>
       </c>
       <c r="Q124">
-        <v>1.78</v>
+        <v>4.2</v>
       </c>
       <c r="R124">
-        <v>2.33</v>
+        <v>2.07</v>
       </c>
       <c r="S124">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T124">
-        <v>2.96</v>
+        <v>2.7</v>
       </c>
       <c r="U124">
-        <v>2.44</v>
+        <v>2.78</v>
       </c>
       <c r="V124">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="W124">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X124">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y124">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="Z124">
-        <v>3.94</v>
+        <v>3.2</v>
       </c>
       <c r="AA124">
-        <v>1.66</v>
+        <v>2.05</v>
       </c>
       <c r="AB124">
-        <v>2.09</v>
+        <v>1.75</v>
       </c>
       <c r="AC124">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AD124">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AE124">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AF124">
-        <v>2.01</v>
+        <v>1.81</v>
       </c>
       <c r="AG124">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="AK124">
-        <v>3.05</v>
+        <v>1.15</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="O125">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="P125">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="Q125">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R125">
+        <v>1.7</v>
+      </c>
+      <c r="S125">
         <v>1.73</v>
       </c>
-      <c r="S125">
-        <v>1.69</v>
-      </c>
       <c r="T125">
-        <v>2.12</v>
+        <v>1.99</v>
       </c>
       <c r="U125">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="V125">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="W125">
         <v>1.03</v>
       </c>
       <c r="X125">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Y125">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="Z125">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="AA125">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="AB125">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AC125">
-        <v>6.5</v>
+        <v>5.1</v>
       </c>
       <c r="AD125">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AE125">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF125">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AG125">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AK125">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="O126">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="P126">
-        <v>8.15</v>
+        <v>6.9</v>
       </c>
       <c r="Q126">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="R126">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="S126">
+        <v>1.56</v>
+      </c>
+      <c r="T126">
+        <v>2.26</v>
+      </c>
+      <c r="U126">
+        <v>3.58</v>
+      </c>
+      <c r="V126">
+        <v>1.21</v>
+      </c>
+      <c r="W126">
+        <v>1.01</v>
+      </c>
+      <c r="X126">
+        <v>1.07</v>
+      </c>
+      <c r="Y126">
         <v>1.5</v>
       </c>
-      <c r="T126">
-        <v>2.5</v>
-      </c>
-      <c r="U126">
-        <v>3.46</v>
-      </c>
-      <c r="V126">
-        <v>1.24</v>
-      </c>
-      <c r="W126">
-        <v>1.02</v>
-      </c>
-      <c r="X126">
-        <v>1.1</v>
-      </c>
-      <c r="Y126">
+      <c r="Z126">
+        <v>2.35</v>
+      </c>
+      <c r="AA126">
+        <v>2.57</v>
+      </c>
+      <c r="AB126">
         <v>1.44</v>
       </c>
-      <c r="Z126">
-        <v>2.5</v>
-      </c>
-      <c r="AA126">
-        <v>2.4</v>
-      </c>
-      <c r="AB126">
-        <v>1.5</v>
-      </c>
       <c r="AC126">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AD126">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE126">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AF126">
-        <v>2.51</v>
+        <v>2.6</v>
       </c>
       <c r="AG126">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK126">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,64 +21173,64 @@
         </is>
       </c>
       <c r="N128">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="O128">
-        <v>6.15</v>
+        <v>4.95</v>
       </c>
       <c r="P128">
-        <v>9</v>
+        <v>5.45</v>
       </c>
       <c r="Q128">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="R128">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="S128">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="T128">
-        <v>4.15</v>
+        <v>4.6</v>
       </c>
       <c r="U128">
         <v>1.83</v>
       </c>
       <c r="V128">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="W128">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X128">
         <v>1.01</v>
       </c>
       <c r="Y128">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="Z128">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="AA128">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AB128">
-        <v>3.11</v>
+        <v>3.28</v>
       </c>
       <c r="AC128">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="AD128">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="AE128">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AF128">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AG128">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AK128">
-        <v>3</v>
+        <v>2.61</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,64 +21336,64 @@
         </is>
       </c>
       <c r="N129">
-        <v>1.48</v>
+        <v>2</v>
       </c>
       <c r="O129">
-        <v>4.65</v>
+        <v>4.15</v>
       </c>
       <c r="P129">
-        <v>5.48</v>
+        <v>2.85</v>
       </c>
       <c r="Q129">
-        <v>1.83</v>
+        <v>2.27</v>
       </c>
       <c r="R129">
         <v>2.75</v>
       </c>
       <c r="S129">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="T129">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="U129">
-        <v>1.97</v>
+        <v>1.74</v>
       </c>
       <c r="V129">
-        <v>1.8</v>
+        <v>2.01</v>
       </c>
       <c r="W129">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="X129">
+        <v>1</v>
+      </c>
+      <c r="Y129">
         <v>1.01</v>
       </c>
-      <c r="Y129">
-        <v>1.05</v>
-      </c>
       <c r="Z129">
-        <v>6.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA129">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AB129">
-        <v>3.4</v>
+        <v>3.76</v>
       </c>
       <c r="AC129">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AD129">
-        <v>1.87</v>
+        <v>2.23</v>
       </c>
       <c r="AE129">
         <v>1.41</v>
       </c>
       <c r="AF129">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AG129">
-        <v>2.6</v>
+        <v>3.65</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK129">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,64 +21499,64 @@
         </is>
       </c>
       <c r="N130">
-        <v>2.15</v>
+        <v>1.28</v>
       </c>
       <c r="O130">
-        <v>3.86</v>
+        <v>5.6</v>
       </c>
       <c r="P130">
-        <v>2.86</v>
+        <v>7.2</v>
       </c>
       <c r="Q130">
-        <v>2.54</v>
+        <v>1.65</v>
       </c>
       <c r="R130">
-        <v>2.48</v>
+        <v>2.85</v>
       </c>
       <c r="S130">
         <v>1.18</v>
       </c>
       <c r="T130">
-        <v>3.96</v>
+        <v>4.2</v>
       </c>
       <c r="U130">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="V130">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="W130">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X130">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y130">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z130">
-        <v>5.65</v>
+        <v>6.35</v>
       </c>
       <c r="AA130">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AB130">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="AC130">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AD130">
-        <v>1.78</v>
+        <v>1.96</v>
       </c>
       <c r="AE130">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AF130">
-        <v>1.36</v>
+        <v>1.59</v>
       </c>
       <c r="AG130">
-        <v>2.9</v>
+        <v>2.18</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.38</v>
+        <v>1.11</v>
       </c>
       <c r="AK130">
-        <v>1.62</v>
+        <v>3.6</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,80 +21662,80 @@
         </is>
       </c>
       <c r="N131">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="O131">
-        <v>4.2</v>
+        <v>3.86</v>
       </c>
       <c r="P131">
-        <v>3.01</v>
+        <v>2.86</v>
       </c>
       <c r="Q131">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="R131">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="S131">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="T131">
-        <v>4.95</v>
+        <v>4</v>
       </c>
       <c r="U131">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="V131">
-        <v>1.99</v>
+        <v>1.73</v>
       </c>
       <c r="W131">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="X131">
         <v>1</v>
       </c>
       <c r="Y131">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Z131">
-        <v>8.5</v>
+        <v>5.65</v>
       </c>
       <c r="AA131">
+        <v>1.36</v>
+      </c>
+      <c r="AB131">
+        <v>2.7</v>
+      </c>
+      <c r="AC131">
+        <v>2</v>
+      </c>
+      <c r="AD131">
+        <v>1.77</v>
+      </c>
+      <c r="AE131">
+        <v>1.28</v>
+      </c>
+      <c r="AF131">
+        <v>1.36</v>
+      </c>
+      <c r="AG131">
+        <v>2.84</v>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ131">
         <v>1.2</v>
       </c>
-      <c r="AB131">
-        <v>3.75</v>
-      </c>
-      <c r="AC131">
-        <v>1.64</v>
-      </c>
-      <c r="AD131">
-        <v>2.19</v>
-      </c>
-      <c r="AE131">
-        <v>1.47</v>
-      </c>
-      <c r="AF131">
-        <v>1.24</v>
-      </c>
-      <c r="AG131">
-        <v>3.65</v>
-      </c>
-      <c r="AH131" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI131" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ131">
-        <v>1.19</v>
-      </c>
       <c r="AK131">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -23138,34 +23138,34 @@
         <v>0</v>
       </c>
       <c r="Q140">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R140">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S140">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T140">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U140">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="V140">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W140">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X140">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y140">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z140">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA140">
         <v>2.4</v>
@@ -23174,19 +23174,19 @@
         <v>1.53</v>
       </c>
       <c r="AC140">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD140">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE140">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF140">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG140">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK140">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="O146">
-        <v>3.91</v>
+        <v>3.67</v>
       </c>
       <c r="P146">
-        <v>6.63</v>
+        <v>4.48</v>
       </c>
       <c r="Q146">
-        <v>2.13</v>
+        <v>2.4</v>
       </c>
       <c r="R146">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="S146">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="T146">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="U146">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="V146">
+        <v>1.43</v>
+      </c>
+      <c r="W146">
+        <v>1.06</v>
+      </c>
+      <c r="X146">
+        <v>1</v>
+      </c>
+      <c r="Y146">
+        <v>1.28</v>
+      </c>
+      <c r="Z146">
+        <v>3.6</v>
+      </c>
+      <c r="AA146">
+        <v>1.81</v>
+      </c>
+      <c r="AB146">
+        <v>1.94</v>
+      </c>
+      <c r="AC146">
+        <v>3.1</v>
+      </c>
+      <c r="AD146">
         <v>1.36</v>
       </c>
-      <c r="W146">
-        <v>1.05</v>
-      </c>
-      <c r="X146">
-        <v>1.03</v>
-      </c>
-      <c r="Y146">
-        <v>1.3</v>
-      </c>
-      <c r="Z146">
-        <v>3.46</v>
-      </c>
-      <c r="AA146">
-        <v>1.96</v>
-      </c>
-      <c r="AB146">
-        <v>1.79</v>
-      </c>
-      <c r="AC146">
-        <v>3.4</v>
-      </c>
-      <c r="AD146">
-        <v>1.3</v>
-      </c>
       <c r="AE146">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF146">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AG146">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK146">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,64 +24270,64 @@
         </is>
       </c>
       <c r="N147">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="O147">
-        <v>3.67</v>
+        <v>3.91</v>
       </c>
       <c r="P147">
-        <v>4.48</v>
+        <v>6.63</v>
       </c>
       <c r="Q147">
-        <v>2.4</v>
+        <v>2.13</v>
       </c>
       <c r="R147">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="S147">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="T147">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="U147">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="V147">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="W147">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X147">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y147">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z147">
-        <v>3.6</v>
+        <v>3.46</v>
       </c>
       <c r="AA147">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="AB147">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AC147">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AD147">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE147">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF147">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AG147">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK147">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G152">
@@ -25094,55 +25094,55 @@
         <v>0</v>
       </c>
       <c r="Q152">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="R152">
-        <v>2.06</v>
+        <v>2.29</v>
       </c>
       <c r="S152">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="T152">
-        <v>2.77</v>
+        <v>4</v>
       </c>
       <c r="U152">
-        <v>2.78</v>
+        <v>2.2</v>
       </c>
       <c r="V152">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="W152">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="X152">
         <v>1</v>
       </c>
       <c r="Y152">
+        <v>1.1</v>
+      </c>
+      <c r="Z152">
+        <v>5.1</v>
+      </c>
+      <c r="AA152">
+        <v>1.53</v>
+      </c>
+      <c r="AB152">
+        <v>2.37</v>
+      </c>
+      <c r="AC152">
+        <v>2.08</v>
+      </c>
+      <c r="AD152">
+        <v>1.67</v>
+      </c>
+      <c r="AE152">
         <v>1.25</v>
       </c>
-      <c r="Z152">
-        <v>3.28</v>
-      </c>
-      <c r="AA152">
-        <v>1.89</v>
-      </c>
-      <c r="AB152">
-        <v>1.81</v>
-      </c>
-      <c r="AC152">
-        <v>3.14</v>
-      </c>
-      <c r="AD152">
-        <v>1.27</v>
-      </c>
-      <c r="AE152">
-        <v>1.06</v>
-      </c>
       <c r="AF152">
-        <v>1.8</v>
+        <v>1.38</v>
       </c>
       <c r="AG152">
-        <v>1.98</v>
+        <v>2.77</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK152">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G153">
@@ -25257,55 +25257,55 @@
         <v>0</v>
       </c>
       <c r="Q153">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="R153">
-        <v>2.29</v>
+        <v>2.06</v>
       </c>
       <c r="S153">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="T153">
-        <v>4</v>
+        <v>2.77</v>
       </c>
       <c r="U153">
-        <v>2.2</v>
+        <v>2.78</v>
       </c>
       <c r="V153">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="W153">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="X153">
         <v>1</v>
       </c>
       <c r="Y153">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="Z153">
-        <v>5.1</v>
+        <v>3.28</v>
       </c>
       <c r="AA153">
-        <v>1.53</v>
+        <v>1.89</v>
       </c>
       <c r="AB153">
-        <v>2.37</v>
+        <v>1.81</v>
       </c>
       <c r="AC153">
-        <v>2.08</v>
+        <v>3.14</v>
       </c>
       <c r="AD153">
-        <v>1.67</v>
+        <v>1.27</v>
       </c>
       <c r="AE153">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AF153">
-        <v>1.38</v>
+        <v>1.8</v>
       </c>
       <c r="AG153">
-        <v>2.77</v>
+        <v>1.98</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK153">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25414,7 +25414,7 @@
         <v>2.05</v>
       </c>
       <c r="O154">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="P154">
         <v>4</v>
@@ -25574,13 +25574,13 @@
         </is>
       </c>
       <c r="N155">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="O155">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="P155">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="Q155">
         <v>0</v>
@@ -26887,34 +26887,34 @@
         <v>6</v>
       </c>
       <c r="Q163">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R163">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S163">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T163">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="U163">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="V163">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W163">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X163">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y163">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z163">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA163">
         <v>2.6</v>
@@ -26923,19 +26923,19 @@
         <v>1.47</v>
       </c>
       <c r="AC163">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD163">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE163">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF163">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG163">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -26948,10 +26948,10 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK163">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27702,34 +27702,34 @@
         <v>0</v>
       </c>
       <c r="Q168">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R168">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S168">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="T168">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U168">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="V168">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W168">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X168">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y168">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z168">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA168">
         <v>2.87</v>
@@ -27738,19 +27738,19 @@
         <v>1.4</v>
       </c>
       <c r="AC168">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AD168">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE168">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF168">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG168">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
@@ -27763,10 +27763,10 @@
         </is>
       </c>
       <c r="AJ168">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK168">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,64 +28345,64 @@
         </is>
       </c>
       <c r="N172">
-        <v>2.45</v>
+        <v>2.17</v>
       </c>
       <c r="O172">
-        <v>3.21</v>
+        <v>3.3</v>
       </c>
       <c r="P172">
-        <v>3.11</v>
+        <v>3.6</v>
       </c>
       <c r="Q172">
+        <v>2.7</v>
+      </c>
+      <c r="R172">
+        <v>1.96</v>
+      </c>
+      <c r="S172">
+        <v>1.46</v>
+      </c>
+      <c r="T172">
         <v>2.62</v>
       </c>
-      <c r="R172">
-        <v>2.1</v>
-      </c>
-      <c r="S172">
-        <v>1.43</v>
-      </c>
-      <c r="T172">
-        <v>2.7</v>
-      </c>
       <c r="U172">
-        <v>3.05</v>
+        <v>2.91</v>
       </c>
       <c r="V172">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W172">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X172">
         <v>1.06</v>
       </c>
       <c r="Y172">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="Z172">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AA172">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB172">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AC172">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AD172">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE172">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF172">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AG172">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28415,10 +28415,10 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AK172">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,64 +28508,64 @@
         </is>
       </c>
       <c r="N173">
-        <v>2.17</v>
+        <v>2.45</v>
       </c>
       <c r="O173">
-        <v>3.3</v>
+        <v>3.21</v>
       </c>
       <c r="P173">
-        <v>3.6</v>
+        <v>3.11</v>
       </c>
       <c r="Q173">
+        <v>2.62</v>
+      </c>
+      <c r="R173">
+        <v>2.1</v>
+      </c>
+      <c r="S173">
+        <v>1.43</v>
+      </c>
+      <c r="T173">
         <v>2.7</v>
       </c>
-      <c r="R173">
-        <v>1.96</v>
-      </c>
-      <c r="S173">
-        <v>1.46</v>
-      </c>
-      <c r="T173">
-        <v>2.62</v>
-      </c>
       <c r="U173">
-        <v>2.91</v>
+        <v>3.05</v>
       </c>
       <c r="V173">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W173">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X173">
         <v>1.06</v>
       </c>
       <c r="Y173">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="Z173">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="AA173">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB173">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AC173">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AD173">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE173">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF173">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AG173">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28578,10 +28578,10 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AK173">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AL173">
         <v>0</v>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,80 +8785,80 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="O52">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="P52">
-        <v>4.83</v>
+        <v>4.2</v>
       </c>
       <c r="Q52">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="R52">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="S52">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T52">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="U52">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V52">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W52">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X52">
         <v>1.04</v>
       </c>
       <c r="Y52">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AA52">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AB52">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AC52">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AD52">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE52">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF52">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AG52">
+        <v>2.1</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ52">
+        <v>1.2</v>
+      </c>
+      <c r="AK52">
         <v>2</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ52">
-        <v>1.22</v>
-      </c>
-      <c r="AK52">
-        <v>2.26</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,80 +8948,80 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="O53">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P53">
-        <v>4.2</v>
+        <v>4.83</v>
       </c>
       <c r="Q53">
+        <v>2.15</v>
+      </c>
+      <c r="R53">
         <v>2.3</v>
       </c>
-      <c r="R53">
-        <v>2.41</v>
-      </c>
       <c r="S53">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T53">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="U53">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V53">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W53">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X53">
         <v>1.04</v>
       </c>
       <c r="Y53">
+        <v>1.19</v>
+      </c>
+      <c r="Z53">
+        <v>3.9</v>
+      </c>
+      <c r="AA53">
+        <v>1.72</v>
+      </c>
+      <c r="AB53">
+        <v>2.05</v>
+      </c>
+      <c r="AC53">
+        <v>2.8</v>
+      </c>
+      <c r="AD53">
+        <v>1.4</v>
+      </c>
+      <c r="AE53">
+        <v>1.15</v>
+      </c>
+      <c r="AF53">
+        <v>1.72</v>
+      </c>
+      <c r="AG53">
+        <v>2</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ53">
         <v>1.22</v>
       </c>
-      <c r="Z53">
-        <v>4.2</v>
-      </c>
-      <c r="AA53">
-        <v>1.71</v>
-      </c>
-      <c r="AB53">
-        <v>2.12</v>
-      </c>
-      <c r="AC53">
-        <v>2.83</v>
-      </c>
-      <c r="AD53">
-        <v>1.43</v>
-      </c>
-      <c r="AE53">
-        <v>1.14</v>
-      </c>
-      <c r="AF53">
-        <v>1.67</v>
-      </c>
-      <c r="AG53">
-        <v>2.1</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ53">
-        <v>1.2</v>
-      </c>
       <c r="AK53">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="O83">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="P83">
-        <v>6.1</v>
+        <v>5.35</v>
       </c>
       <c r="Q83">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="R83">
-        <v>3.22</v>
+        <v>2.77</v>
       </c>
       <c r="S83">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="T83">
-        <v>5</v>
+        <v>4.65</v>
       </c>
       <c r="U83">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="V83">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="W83">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="X83">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Z83">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AA83">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AB83">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="AC83">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AD83">
-        <v>2.21</v>
+        <v>2.04</v>
       </c>
       <c r="AE83">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AF83">
         <v>1.4</v>
       </c>
       <c r="AG83">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AK83">
-        <v>3.18</v>
+        <v>2.56</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="O84">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="P84">
-        <v>5.35</v>
+        <v>6.1</v>
       </c>
       <c r="Q84">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="R84">
-        <v>2.77</v>
+        <v>3.22</v>
       </c>
       <c r="S84">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="T84">
-        <v>4.65</v>
+        <v>5</v>
       </c>
       <c r="U84">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="V84">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="W84">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X84">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y84">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Z84">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AA84">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AB84">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="AC84">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AD84">
-        <v>2.04</v>
+        <v>2.21</v>
       </c>
       <c r="AE84">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AF84">
         <v>1.4</v>
       </c>
       <c r="AG84">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AK84">
-        <v>2.56</v>
+        <v>3.18</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,64 +21499,64 @@
         </is>
       </c>
       <c r="N130">
+        <v>2.15</v>
+      </c>
+      <c r="O130">
+        <v>3.86</v>
+      </c>
+      <c r="P130">
+        <v>2.86</v>
+      </c>
+      <c r="Q130">
+        <v>2.54</v>
+      </c>
+      <c r="R130">
+        <v>2.48</v>
+      </c>
+      <c r="S130">
+        <v>1.2</v>
+      </c>
+      <c r="T130">
+        <v>4</v>
+      </c>
+      <c r="U130">
+        <v>2</v>
+      </c>
+      <c r="V130">
+        <v>1.73</v>
+      </c>
+      <c r="W130">
+        <v>1.18</v>
+      </c>
+      <c r="X130">
+        <v>1</v>
+      </c>
+      <c r="Y130">
+        <v>1.08</v>
+      </c>
+      <c r="Z130">
+        <v>5.65</v>
+      </c>
+      <c r="AA130">
+        <v>1.36</v>
+      </c>
+      <c r="AB130">
+        <v>2.7</v>
+      </c>
+      <c r="AC130">
+        <v>2</v>
+      </c>
+      <c r="AD130">
+        <v>1.77</v>
+      </c>
+      <c r="AE130">
         <v>1.28</v>
       </c>
-      <c r="O130">
-        <v>5.6</v>
-      </c>
-      <c r="P130">
-        <v>7.2</v>
-      </c>
-      <c r="Q130">
-        <v>1.65</v>
-      </c>
-      <c r="R130">
-        <v>2.85</v>
-      </c>
-      <c r="S130">
-        <v>1.18</v>
-      </c>
-      <c r="T130">
-        <v>4.2</v>
-      </c>
-      <c r="U130">
-        <v>1.83</v>
-      </c>
-      <c r="V130">
-        <v>1.83</v>
-      </c>
-      <c r="W130">
-        <v>1.22</v>
-      </c>
-      <c r="X130">
-        <v>1.01</v>
-      </c>
-      <c r="Y130">
-        <v>1.06</v>
-      </c>
-      <c r="Z130">
-        <v>6.35</v>
-      </c>
-      <c r="AA130">
-        <v>1.31</v>
-      </c>
-      <c r="AB130">
-        <v>3.4</v>
-      </c>
-      <c r="AC130">
-        <v>1.85</v>
-      </c>
-      <c r="AD130">
-        <v>1.96</v>
-      </c>
-      <c r="AE130">
+      <c r="AF130">
         <v>1.36</v>
       </c>
-      <c r="AF130">
-        <v>1.59</v>
-      </c>
       <c r="AG130">
-        <v>2.18</v>
+        <v>2.84</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AK130">
-        <v>3.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,64 +21662,64 @@
         </is>
       </c>
       <c r="N131">
-        <v>2.15</v>
+        <v>1.28</v>
       </c>
       <c r="O131">
-        <v>3.86</v>
+        <v>5.6</v>
       </c>
       <c r="P131">
-        <v>2.86</v>
+        <v>7.2</v>
       </c>
       <c r="Q131">
-        <v>2.54</v>
+        <v>1.65</v>
       </c>
       <c r="R131">
-        <v>2.48</v>
+        <v>2.85</v>
       </c>
       <c r="S131">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T131">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="U131">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="V131">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="W131">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X131">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y131">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z131">
-        <v>5.65</v>
+        <v>6.35</v>
       </c>
       <c r="AA131">
+        <v>1.31</v>
+      </c>
+      <c r="AB131">
+        <v>3.4</v>
+      </c>
+      <c r="AC131">
+        <v>1.85</v>
+      </c>
+      <c r="AD131">
+        <v>1.96</v>
+      </c>
+      <c r="AE131">
         <v>1.36</v>
       </c>
-      <c r="AB131">
-        <v>2.7</v>
-      </c>
-      <c r="AC131">
-        <v>2</v>
-      </c>
-      <c r="AD131">
-        <v>1.77</v>
-      </c>
-      <c r="AE131">
-        <v>1.28</v>
-      </c>
       <c r="AF131">
-        <v>1.36</v>
+        <v>1.59</v>
       </c>
       <c r="AG131">
-        <v>2.84</v>
+        <v>2.18</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AK131">
-        <v>1.62</v>
+        <v>3.6</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,64 +26552,64 @@
         </is>
       </c>
       <c r="N161">
-        <v>1.12</v>
+        <v>4.55</v>
       </c>
       <c r="O161">
-        <v>8.199999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="P161">
-        <v>15</v>
+        <v>1.74</v>
       </c>
       <c r="Q161">
-        <v>1.44</v>
+        <v>5</v>
       </c>
       <c r="R161">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="S161">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="T161">
-        <v>3.88</v>
+        <v>2.66</v>
       </c>
       <c r="U161">
-        <v>2.05</v>
+        <v>2.81</v>
       </c>
       <c r="V161">
-        <v>1.77</v>
+        <v>1.42</v>
       </c>
       <c r="W161">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="X161">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y161">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="Z161">
-        <v>5.45</v>
+        <v>3.4</v>
       </c>
       <c r="AA161">
-        <v>1.4</v>
+        <v>1.96</v>
       </c>
       <c r="AB161">
-        <v>2.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC161">
-        <v>2.1</v>
+        <v>3.37</v>
       </c>
       <c r="AD161">
-        <v>1.67</v>
+        <v>1.27</v>
       </c>
       <c r="AE161">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AF161">
-        <v>2.46</v>
+        <v>1.85</v>
       </c>
       <c r="AG161">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>1.06</v>
+        <v>2.11</v>
       </c>
       <c r="AK161">
-        <v>6.5</v>
+        <v>1.13</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G162">
@@ -26715,80 +26715,80 @@
         </is>
       </c>
       <c r="N162">
-        <v>4.55</v>
+        <v>1.12</v>
       </c>
       <c r="O162">
-        <v>3.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="P162">
-        <v>1.74</v>
+        <v>15</v>
       </c>
       <c r="Q162">
-        <v>5</v>
+        <v>1.44</v>
       </c>
       <c r="R162">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="S162">
+        <v>1.18</v>
+      </c>
+      <c r="T162">
+        <v>3.88</v>
+      </c>
+      <c r="U162">
+        <v>2.05</v>
+      </c>
+      <c r="V162">
+        <v>1.77</v>
+      </c>
+      <c r="W162">
+        <v>1.2</v>
+      </c>
+      <c r="X162">
+        <v>1.01</v>
+      </c>
+      <c r="Y162">
+        <v>1.08</v>
+      </c>
+      <c r="Z162">
+        <v>5.45</v>
+      </c>
+      <c r="AA162">
         <v>1.4</v>
       </c>
-      <c r="T162">
-        <v>2.66</v>
-      </c>
-      <c r="U162">
-        <v>2.81</v>
-      </c>
-      <c r="V162">
-        <v>1.42</v>
-      </c>
-      <c r="W162">
-        <v>1.08</v>
-      </c>
-      <c r="X162">
-        <v>1.05</v>
-      </c>
-      <c r="Y162">
-        <v>1.3</v>
-      </c>
-      <c r="Z162">
-        <v>3.4</v>
-      </c>
-      <c r="AA162">
-        <v>1.96</v>
-      </c>
       <c r="AB162">
-        <v>1.85</v>
+        <v>2.7</v>
       </c>
       <c r="AC162">
-        <v>3.37</v>
+        <v>2.1</v>
       </c>
       <c r="AD162">
-        <v>1.27</v>
+        <v>1.67</v>
       </c>
       <c r="AE162">
+        <v>1.25</v>
+      </c>
+      <c r="AF162">
+        <v>2.46</v>
+      </c>
+      <c r="AG162">
+        <v>1.5</v>
+      </c>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ162">
         <v>1.06</v>
       </c>
-      <c r="AF162">
-        <v>1.85</v>
-      </c>
-      <c r="AG162">
-        <v>1.85</v>
-      </c>
-      <c r="AH162" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI162" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ162">
-        <v>2.11</v>
-      </c>
       <c r="AK162">
-        <v>1.13</v>
+        <v>6.5</v>
       </c>
       <c r="AL162">
         <v>0</v>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -19872,10 +19872,10 @@
         <v>2.62</v>
       </c>
       <c r="O120">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="P120">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="Q120">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G123">
@@ -20367,55 +20367,55 @@
         <v>0</v>
       </c>
       <c r="Q123">
-        <v>1.78</v>
+        <v>4.2</v>
       </c>
       <c r="R123">
-        <v>2.33</v>
+        <v>2.07</v>
       </c>
       <c r="S123">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T123">
-        <v>2.96</v>
+        <v>2.7</v>
       </c>
       <c r="U123">
-        <v>2.44</v>
+        <v>2.78</v>
       </c>
       <c r="V123">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="W123">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X123">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y123">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="Z123">
-        <v>3.94</v>
+        <v>3.2</v>
       </c>
       <c r="AA123">
-        <v>1.66</v>
+        <v>2.05</v>
       </c>
       <c r="AB123">
-        <v>2.09</v>
+        <v>1.75</v>
       </c>
       <c r="AC123">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AD123">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AE123">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AF123">
-        <v>2.01</v>
+        <v>1.81</v>
       </c>
       <c r="AG123">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="AK123">
-        <v>3.05</v>
+        <v>1.15</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G124">
@@ -20530,55 +20530,55 @@
         <v>0</v>
       </c>
       <c r="Q124">
-        <v>4.2</v>
+        <v>1.78</v>
       </c>
       <c r="R124">
-        <v>2.07</v>
+        <v>2.33</v>
       </c>
       <c r="S124">
+        <v>1.29</v>
+      </c>
+      <c r="T124">
+        <v>2.96</v>
+      </c>
+      <c r="U124">
+        <v>2.44</v>
+      </c>
+      <c r="V124">
+        <v>1.46</v>
+      </c>
+      <c r="W124">
+        <v>1.08</v>
+      </c>
+      <c r="X124">
+        <v>1.04</v>
+      </c>
+      <c r="Y124">
+        <v>1.17</v>
+      </c>
+      <c r="Z124">
+        <v>3.94</v>
+      </c>
+      <c r="AA124">
+        <v>1.66</v>
+      </c>
+      <c r="AB124">
+        <v>2.09</v>
+      </c>
+      <c r="AC124">
+        <v>2.9</v>
+      </c>
+      <c r="AD124">
         <v>1.38</v>
       </c>
-      <c r="T124">
-        <v>2.7</v>
-      </c>
-      <c r="U124">
-        <v>2.78</v>
-      </c>
-      <c r="V124">
-        <v>1.33</v>
-      </c>
-      <c r="W124">
-        <v>1.04</v>
-      </c>
-      <c r="X124">
-        <v>1.01</v>
-      </c>
-      <c r="Y124">
-        <v>1.26</v>
-      </c>
-      <c r="Z124">
-        <v>3.2</v>
-      </c>
-      <c r="AA124">
-        <v>2.05</v>
-      </c>
-      <c r="AB124">
-        <v>1.75</v>
-      </c>
-      <c r="AC124">
-        <v>3.2</v>
-      </c>
-      <c r="AD124">
-        <v>1.26</v>
-      </c>
       <c r="AE124">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF124">
-        <v>1.81</v>
+        <v>2.01</v>
       </c>
       <c r="AG124">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="AK124">
-        <v>1.15</v>
+        <v>3.05</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20699,7 +20699,7 @@
         <v>1.7</v>
       </c>
       <c r="S125">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="T125">
         <v>1.99</v>
@@ -20856,16 +20856,16 @@
         <v>6.9</v>
       </c>
       <c r="Q126">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="R126">
         <v>1.91</v>
       </c>
       <c r="S126">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="T126">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U126">
         <v>3.58</v>
@@ -20874,10 +20874,10 @@
         <v>1.21</v>
       </c>
       <c r="W126">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X126">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y126">
         <v>1.5</v>
@@ -20886,13 +20886,13 @@
         <v>2.35</v>
       </c>
       <c r="AA126">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="AB126">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AC126">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AD126">
         <v>1.15</v>
@@ -20904,7 +20904,7 @@
         <v>2.6</v>
       </c>
       <c r="AG126">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AK126">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -23144,16 +23144,16 @@
         <v>1.96</v>
       </c>
       <c r="S140">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="T140">
-        <v>2.33</v>
+        <v>2.7</v>
       </c>
       <c r="U140">
-        <v>3.46</v>
+        <v>2.88</v>
       </c>
       <c r="V140">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="W140">
         <v>1.03</v>
@@ -23162,7 +23162,7 @@
         <v>1.04</v>
       </c>
       <c r="Y140">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="Z140">
         <v>2.55</v>
@@ -23180,13 +23180,13 @@
         <v>1.13</v>
       </c>
       <c r="AE140">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF140">
         <v>2.4</v>
       </c>
       <c r="AG140">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,7 +23199,7 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.21</v>
+        <v>1.03</v>
       </c>
       <c r="AK140">
         <v>2.45</v>
@@ -26229,25 +26229,25 @@
         <v>1.58</v>
       </c>
       <c r="O159">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="P159">
-        <v>5.96</v>
+        <v>5.95</v>
       </c>
       <c r="Q159">
         <v>2.2</v>
       </c>
       <c r="R159">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="S159">
         <v>1.53</v>
       </c>
       <c r="T159">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="U159">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="V159">
         <v>1.22</v>
@@ -26256,34 +26256,34 @@
         <v>1.02</v>
       </c>
       <c r="X159">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y159">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="Z159">
         <v>2.5</v>
       </c>
       <c r="AA159">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AB159">
         <v>1.5</v>
       </c>
       <c r="AC159">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AD159">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AE159">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF159">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AG159">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26296,10 +26296,10 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK159">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26878,25 +26878,25 @@
         </is>
       </c>
       <c r="N163">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="O163">
         <v>3.1</v>
       </c>
       <c r="P163">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Q163">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="R163">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="S163">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="T163">
-        <v>2.24</v>
+        <v>2.45</v>
       </c>
       <c r="U163">
         <v>3.35</v>
@@ -26917,10 +26917,10 @@
         <v>2.4</v>
       </c>
       <c r="AA163">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AB163">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AC163">
         <v>5</v>
@@ -26932,10 +26932,10 @@
         <v>1.04</v>
       </c>
       <c r="AF163">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AG163">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -27367,55 +27367,55 @@
         </is>
       </c>
       <c r="N166">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="O166">
         <v>2.8</v>
       </c>
       <c r="P166">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Q166">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="R166">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="S166">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="T166">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="U166">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="V166">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="W166">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X166">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="Y166">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="Z166">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AA166">
         <v>3.1</v>
       </c>
       <c r="AB166">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AC166">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="AD166">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AE166">
         <v>1.03</v>
@@ -27424,7 +27424,7 @@
         <v>2.3</v>
       </c>
       <c r="AG166">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AH166" t="inlineStr">
         <is>
@@ -27440,7 +27440,7 @@
         <v>1.36</v>
       </c>
       <c r="AK166">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27702,19 +27702,19 @@
         <v>0</v>
       </c>
       <c r="Q168">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="R168">
         <v>1.85</v>
       </c>
       <c r="S168">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="T168">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="U168">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="V168">
         <v>1.17</v>
@@ -27726,22 +27726,22 @@
         <v>1.14</v>
       </c>
       <c r="Y168">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Z168">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AA168">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="AB168">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AC168">
         <v>5.7</v>
       </c>
       <c r="AD168">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AE168">
         <v>1.03</v>
@@ -27766,7 +27766,7 @@
         <v>1.4</v>
       </c>
       <c r="AK168">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AL168">
         <v>0</v>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q2">
         <v>4.8</v>
@@ -671,7 +671,7 @@
         <v>1.33</v>
       </c>
       <c r="Z2">
-        <v>2.99</v>
+        <v>2.83</v>
       </c>
       <c r="AA2">
         <v>2.16</v>
@@ -680,7 +680,7 @@
         <v>1.66</v>
       </c>
       <c r="AC2">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AD2">
         <v>1.19</v>
@@ -970,25 +970,25 @@
         <v>2.65</v>
       </c>
       <c r="Q4">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="R4">
         <v>2.25</v>
       </c>
       <c r="S4">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T4">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="U4">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="V4">
         <v>1.44</v>
       </c>
       <c r="W4">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X4">
         <v>1.03</v>
@@ -1012,13 +1012,13 @@
         <v>1.34</v>
       </c>
       <c r="AE4">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF4">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG4">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AK4">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1287,25 +1287,25 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="O6">
-        <v>3.26</v>
+        <v>3.15</v>
       </c>
       <c r="P6">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="Q6">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="R6">
-        <v>1.96</v>
+        <v>2.11</v>
       </c>
       <c r="S6">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T6">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="U6">
         <v>3</v>
@@ -1314,16 +1314,16 @@
         <v>1.32</v>
       </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X6">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y6">
         <v>1.36</v>
       </c>
       <c r="Z6">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="AA6">
         <v>2.21</v>
@@ -1613,16 +1613,16 @@
         </is>
       </c>
       <c r="N8">
+        <v>2.7</v>
+      </c>
+      <c r="O8">
         <v>3</v>
       </c>
-      <c r="O8">
-        <v>2.95</v>
-      </c>
       <c r="P8">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="Q8">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="R8">
         <v>1.95</v>
@@ -1631,7 +1631,7 @@
         <v>1.48</v>
       </c>
       <c r="T8">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="U8">
         <v>3.2</v>
@@ -1652,7 +1652,7 @@
         <v>2.74</v>
       </c>
       <c r="AA8">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AB8">
         <v>1.6</v>
@@ -1664,7 +1664,7 @@
         <v>1.17</v>
       </c>
       <c r="AE8">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF8">
         <v>1.87</v>
@@ -1788,22 +1788,22 @@
         <v>3.2</v>
       </c>
       <c r="R9">
-        <v>1.96</v>
+        <v>1.84</v>
       </c>
       <c r="S9">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T9">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="U9">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="V9">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W9">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X9">
         <v>1.09</v>
@@ -2102,31 +2102,31 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.91</v>
+        <v>2.99</v>
       </c>
       <c r="O11">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="P11">
-        <v>2.48</v>
+        <v>2.35</v>
       </c>
       <c r="Q11">
-        <v>3.55</v>
+        <v>3.64</v>
       </c>
       <c r="R11">
         <v>2</v>
       </c>
       <c r="S11">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T11">
         <v>2.88</v>
       </c>
       <c r="U11">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="V11">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W11">
         <v>1.05</v>
@@ -2138,7 +2138,7 @@
         <v>1.36</v>
       </c>
       <c r="Z11">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="AA11">
         <v>2.08</v>
@@ -2159,7 +2159,7 @@
         <v>1.8</v>
       </c>
       <c r="AG11">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK11">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2428,16 +2428,16 @@
         </is>
       </c>
       <c r="N13">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="O13">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P13">
         <v>1.7</v>
       </c>
       <c r="Q13">
-        <v>4.53</v>
+        <v>4.5</v>
       </c>
       <c r="R13">
         <v>2.45</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.47</v>
+        <v>2.78</v>
       </c>
       <c r="O14">
         <v>3</v>
       </c>
       <c r="P14">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="Q14">
         <v>3.5</v>
@@ -2606,7 +2606,7 @@
         <v>2.04</v>
       </c>
       <c r="S14">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="T14">
         <v>3.4</v>
@@ -2618,7 +2618,7 @@
         <v>1.57</v>
       </c>
       <c r="W14">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X14">
         <v>1.03</v>
@@ -2636,7 +2636,7 @@
         <v>2.15</v>
       </c>
       <c r="AC14">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AD14">
         <v>1.56</v>
@@ -2648,7 +2648,7 @@
         <v>1.49</v>
       </c>
       <c r="AG14">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2763,13 +2763,13 @@
         <v>0</v>
       </c>
       <c r="Q15">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="R15">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="S15">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T15">
         <v>3.4</v>
@@ -2778,7 +2778,7 @@
         <v>2.35</v>
       </c>
       <c r="V15">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W15">
         <v>1.08</v>
@@ -2811,7 +2811,7 @@
         <v>1.7</v>
       </c>
       <c r="AG15">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AK15">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="O17">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="P17">
         <v>1.67</v>
@@ -3095,10 +3095,10 @@
         <v>2.6</v>
       </c>
       <c r="S17">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="T17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U17">
         <v>1.8</v>
@@ -3107,7 +3107,7 @@
         <v>1.68</v>
       </c>
       <c r="W17">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X17">
         <v>1.02</v>
@@ -3116,10 +3116,10 @@
         <v>1.08</v>
       </c>
       <c r="Z17">
-        <v>3.75</v>
+        <v>5.65</v>
       </c>
       <c r="AA17">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB17">
         <v>2.81</v>
@@ -3131,7 +3131,7 @@
         <v>1.7</v>
       </c>
       <c r="AE17">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF17">
         <v>1.42</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,58 +3243,58 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="O18">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="P18">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="Q18">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="R18">
+        <v>2.18</v>
+      </c>
+      <c r="S18">
+        <v>1.3</v>
+      </c>
+      <c r="T18">
+        <v>3.3</v>
+      </c>
+      <c r="U18">
         <v>2.4</v>
       </c>
-      <c r="S18">
-        <v>1.25</v>
-      </c>
-      <c r="T18">
-        <v>3.6</v>
-      </c>
-      <c r="U18">
-        <v>2.36</v>
-      </c>
       <c r="V18">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="W18">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y18">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="Z18">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA18">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AB18">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AC18">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AD18">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE18">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AF18">
         <v>1.55</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK18">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,16 +3406,16 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.1</v>
+        <v>1.88</v>
       </c>
       <c r="O19">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P19">
-        <v>2.15</v>
+        <v>3.95</v>
       </c>
       <c r="Q19">
-        <v>3.62</v>
+        <v>2.25</v>
       </c>
       <c r="R19">
         <v>2.4</v>
@@ -3424,46 +3424,46 @@
         <v>1.25</v>
       </c>
       <c r="T19">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="U19">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="V19">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="W19">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X19">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="Z19">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA19">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AB19">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="AC19">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AD19">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AE19">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF19">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AG19">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>1.33</v>
+        <v>1.85</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.04</v>
+        <v>3.1</v>
       </c>
       <c r="O20">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P20">
-        <v>3.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q20">
-        <v>2.5</v>
+        <v>3.62</v>
       </c>
       <c r="R20">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="S20">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T20">
-        <v>3.15</v>
+        <v>3.34</v>
       </c>
       <c r="U20">
+        <v>2.25</v>
+      </c>
+      <c r="V20">
+        <v>1.58</v>
+      </c>
+      <c r="W20">
+        <v>1.15</v>
+      </c>
+      <c r="X20">
+        <v>1.03</v>
+      </c>
+      <c r="Y20">
+        <v>1.12</v>
+      </c>
+      <c r="Z20">
+        <v>4.8</v>
+      </c>
+      <c r="AA20">
+        <v>1.54</v>
+      </c>
+      <c r="AB20">
         <v>2.4</v>
       </c>
-      <c r="V20">
+      <c r="AC20">
+        <v>2.35</v>
+      </c>
+      <c r="AD20">
+        <v>1.57</v>
+      </c>
+      <c r="AE20">
+        <v>1.23</v>
+      </c>
+      <c r="AF20">
         <v>1.5</v>
       </c>
-      <c r="W20">
-        <v>1.12</v>
-      </c>
-      <c r="X20">
-        <v>1.04</v>
-      </c>
-      <c r="Y20">
-        <v>1.2</v>
-      </c>
-      <c r="Z20">
-        <v>4.33</v>
-      </c>
-      <c r="AA20">
-        <v>1.62</v>
-      </c>
-      <c r="AB20">
-        <v>2.2</v>
-      </c>
-      <c r="AC20">
-        <v>2.47</v>
-      </c>
-      <c r="AD20">
-        <v>1.44</v>
-      </c>
-      <c r="AE20">
-        <v>1.15</v>
-      </c>
-      <c r="AF20">
-        <v>1.55</v>
-      </c>
       <c r="AG20">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
+        <v>1.22</v>
+      </c>
+      <c r="AK20">
         <v>1.33</v>
-      </c>
-      <c r="AK20">
-        <v>1.73</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="O21">
-        <v>3.66</v>
+        <v>3.51</v>
       </c>
       <c r="P21">
         <v>5.25</v>
@@ -3765,10 +3765,10 @@
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z21">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="AA21">
         <v>2.12</v>
@@ -4221,16 +4221,16 @@
         </is>
       </c>
       <c r="N24">
-        <v>3.25</v>
+        <v>2.72</v>
       </c>
       <c r="O24">
-        <v>3.55</v>
+        <v>3.23</v>
       </c>
       <c r="P24">
         <v>2</v>
       </c>
       <c r="Q24">
-        <v>3.78</v>
+        <v>3.85</v>
       </c>
       <c r="R24">
         <v>2.25</v>
@@ -4239,13 +4239,13 @@
         <v>1.31</v>
       </c>
       <c r="T24">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U24">
         <v>2.53</v>
       </c>
       <c r="V24">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="W24">
         <v>1.06</v>
@@ -4254,16 +4254,16 @@
         <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z24">
         <v>4.13</v>
       </c>
       <c r="AA24">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AB24">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="AC24">
         <v>2.75</v>
@@ -4275,10 +4275,10 @@
         <v>1.13</v>
       </c>
       <c r="AF24">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AG24">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="O25">
         <v>3.6</v>
@@ -4402,7 +4402,7 @@
         <v>1.25</v>
       </c>
       <c r="T25">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U25">
         <v>2.25</v>
@@ -4414,19 +4414,19 @@
         <v>1.15</v>
       </c>
       <c r="X25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z25">
-        <v>4.64</v>
+        <v>4.63</v>
       </c>
       <c r="AA25">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AB25">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC25">
         <v>2.45</v>
@@ -4435,13 +4435,13 @@
         <v>1.49</v>
       </c>
       <c r="AE25">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AF25">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG25">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK25">
         <v>2</v>
@@ -4547,34 +4547,34 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="O26">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="P26">
-        <v>5.25</v>
+        <v>5.35</v>
       </c>
       <c r="Q26">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="R26">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="S26">
         <v>1.25</v>
       </c>
       <c r="T26">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="U26">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="V26">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W26">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X26">
         <v>1.02</v>
@@ -4595,7 +4595,7 @@
         <v>2.33</v>
       </c>
       <c r="AD26">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AE26">
         <v>1.23</v>
@@ -4604,7 +4604,7 @@
         <v>1.6</v>
       </c>
       <c r="AG26">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.84</v>
+        <v>1.64</v>
       </c>
       <c r="O30">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P30">
-        <v>3.91</v>
+        <v>4.35</v>
       </c>
       <c r="Q30">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="R30">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="S30">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T30">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="U30">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V30">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W30">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z30">
-        <v>3.14</v>
+        <v>3.51</v>
       </c>
       <c r="AA30">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AB30">
         <v>1.78</v>
       </c>
       <c r="AC30">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="AD30">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE30">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF30">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG30">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK30">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5525,7 +5525,7 @@
         </is>
       </c>
       <c r="N32">
-        <v>6.55</v>
+        <v>6.5</v>
       </c>
       <c r="O32">
         <v>5.25</v>
@@ -5540,40 +5540,40 @@
         <v>2.43</v>
       </c>
       <c r="S32">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T32">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U32">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="V32">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W32">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X32">
         <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Z32">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="AA32">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AB32">
-        <v>2.64</v>
+        <v>2.82</v>
       </c>
       <c r="AC32">
         <v>2.1</v>
       </c>
       <c r="AD32">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AE32">
         <v>1.3</v>
@@ -5582,7 +5582,7 @@
         <v>1.65</v>
       </c>
       <c r="AG32">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5854,10 +5854,10 @@
         <v>5.4</v>
       </c>
       <c r="O34">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="P34">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="Q34">
         <v>5.2</v>
@@ -5869,7 +5869,7 @@
         <v>1.2</v>
       </c>
       <c r="T34">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="U34">
         <v>2.05</v>
@@ -5924,7 +5924,7 @@
         <v>1.2</v>
       </c>
       <c r="AK34">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="O35">
         <v>3.5</v>
       </c>
       <c r="P35">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="Q35">
         <v>2.8</v>
@@ -6050,19 +6050,19 @@
         <v>1.2</v>
       </c>
       <c r="Z35">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="AA35">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB35">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AC35">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="AD35">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE35">
         <v>1.14</v>
@@ -6071,7 +6071,7 @@
         <v>1.62</v>
       </c>
       <c r="AG35">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>3.3</v>
       </c>
       <c r="P36">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6385,7 +6385,7 @@
         <v>1.88</v>
       </c>
       <c r="AC37">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AD37">
         <v>1.33</v>
@@ -6397,7 +6397,7 @@
         <v>1.9</v>
       </c>
       <c r="AG37">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O39">
         <v>3.2</v>
       </c>
       <c r="P39">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="Q39">
         <v>2.88</v>
@@ -6693,7 +6693,7 @@
         <v>1.42</v>
       </c>
       <c r="W39">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X39">
         <v>1.01</v>
@@ -6711,16 +6711,16 @@
         <v>1.86</v>
       </c>
       <c r="AC39">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="AD39">
         <v>1.29</v>
       </c>
       <c r="AE39">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF39">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG39">
         <v>2.05</v>
@@ -6829,10 +6829,10 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="O40">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="P40">
         <v>11.6</v>
@@ -6850,10 +6850,10 @@
         <v>3.6</v>
       </c>
       <c r="U40">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="V40">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="W40">
         <v>1.17</v>
@@ -6862,16 +6862,16 @@
         <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="Z40">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="AA40">
         <v>1.43</v>
       </c>
       <c r="AB40">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AC40">
         <v>2.33</v>
@@ -7158,7 +7158,7 @@
         <v>3.1</v>
       </c>
       <c r="O42">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P42">
         <v>2</v>
@@ -7179,7 +7179,7 @@
         <v>2.3</v>
       </c>
       <c r="V42">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W42">
         <v>1.11</v>
@@ -7188,7 +7188,7 @@
         <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z42">
         <v>3.9</v>
@@ -7200,7 +7200,7 @@
         <v>2.05</v>
       </c>
       <c r="AC42">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="AD42">
         <v>1.41</v>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AK42">
         <v>1.3</v>
@@ -7327,7 +7327,7 @@
         <v>1.87</v>
       </c>
       <c r="Q43">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="R43">
         <v>2.35</v>
@@ -7369,7 +7369,7 @@
         <v>1.44</v>
       </c>
       <c r="AE43">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF43">
         <v>1.57</v>
@@ -7391,7 +7391,7 @@
         <v>1.22</v>
       </c>
       <c r="AK43">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7490,7 +7490,7 @@
         <v>0</v>
       </c>
       <c r="Q44">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="R44">
         <v>2.2</v>
@@ -7511,31 +7511,31 @@
         <v>1.08</v>
       </c>
       <c r="X44">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y44">
         <v>1.22</v>
       </c>
       <c r="Z44">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AA44">
-        <v>2.04</v>
+        <v>1.73</v>
       </c>
       <c r="AB44">
-        <v>1.74</v>
+        <v>1.98</v>
       </c>
       <c r="AC44">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AD44">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE44">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF44">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AG44">
         <v>1.9</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK44">
         <v>1.88</v>
@@ -7653,10 +7653,10 @@
         <v>0</v>
       </c>
       <c r="Q45">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="R45">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="S45">
         <v>1.3</v>
@@ -7665,7 +7665,7 @@
         <v>3.2</v>
       </c>
       <c r="U45">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="V45">
         <v>1.45</v>
@@ -7677,16 +7677,16 @@
         <v>1.03</v>
       </c>
       <c r="Y45">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z45">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="AA45">
-        <v>1.81</v>
+        <v>1.63</v>
       </c>
       <c r="AB45">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="AC45">
         <v>2.55</v>
@@ -7698,10 +7698,10 @@
         <v>1.13</v>
       </c>
       <c r="AF45">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AG45">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -8296,16 +8296,16 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="O49">
         <v>3.1</v>
       </c>
       <c r="P49">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="Q49">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="R49">
         <v>1.92</v>
@@ -8317,10 +8317,10 @@
         <v>2.69</v>
       </c>
       <c r="U49">
-        <v>3.23</v>
+        <v>3.16</v>
       </c>
       <c r="V49">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W49">
         <v>1.01</v>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK49">
         <v>1.52</v>
@@ -8622,7 +8622,7 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="O51">
         <v>7</v>
@@ -8670,7 +8670,7 @@
         <v>2.22</v>
       </c>
       <c r="AD51">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AE51">
         <v>1.24</v>
@@ -8679,7 +8679,7 @@
         <v>2.21</v>
       </c>
       <c r="AG51">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         <v>2.3</v>
       </c>
       <c r="R52">
-        <v>2.41</v>
+        <v>2.16</v>
       </c>
       <c r="S52">
         <v>1.3</v>
@@ -8812,7 +8812,7 @@
         <v>1.5</v>
       </c>
       <c r="W52">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X52">
         <v>1.04</v>
@@ -8827,7 +8827,7 @@
         <v>1.71</v>
       </c>
       <c r="AB52">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AC52">
         <v>2.83</v>
@@ -8839,7 +8839,7 @@
         <v>1.14</v>
       </c>
       <c r="AF52">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG52">
         <v>2.1</v>
@@ -8948,25 +8948,25 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="O53">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="P53">
-        <v>4.83</v>
+        <v>5.25</v>
       </c>
       <c r="Q53">
         <v>2.15</v>
       </c>
       <c r="R53">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="S53">
         <v>1.32</v>
       </c>
       <c r="T53">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U53">
         <v>2.5</v>
@@ -8999,13 +8999,13 @@
         <v>1.4</v>
       </c>
       <c r="AE53">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF53">
         <v>1.72</v>
       </c>
       <c r="AG53">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>1.22</v>
       </c>
       <c r="AK53">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="O55">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="P55">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q55">
         <v>2.6</v>
@@ -9289,7 +9289,7 @@
         <v>2.33</v>
       </c>
       <c r="S55">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T55">
         <v>3.3</v>
@@ -9313,7 +9313,7 @@
         <v>3.94</v>
       </c>
       <c r="AA55">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB55">
         <v>2.05</v>
@@ -9347,7 +9347,7 @@
         <v>1.31</v>
       </c>
       <c r="AK55">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9446,7 +9446,7 @@
         <v>0</v>
       </c>
       <c r="Q56">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="R56">
         <v>2.07</v>
@@ -9455,46 +9455,46 @@
         <v>1.4</v>
       </c>
       <c r="T56">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="U56">
         <v>2.8</v>
       </c>
       <c r="V56">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W56">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X56">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z56">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AA56">
         <v>1.78</v>
       </c>
       <c r="AB56">
-        <v>1.74</v>
+        <v>1.92</v>
       </c>
       <c r="AC56">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="AD56">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AE56">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF56">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AG56">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9645,19 +9645,19 @@
         <v>1.4</v>
       </c>
       <c r="AC57">
-        <v>5.5</v>
+        <v>4.95</v>
       </c>
       <c r="AD57">
         <v>1.13</v>
       </c>
       <c r="AE57">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF57">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="AG57">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>1.4</v>
       </c>
       <c r="AK57">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9769,7 +9769,7 @@
         <v>3.6</v>
       </c>
       <c r="P58">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="O59">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P59">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -10089,22 +10089,22 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="O60">
-        <v>3.85</v>
+        <v>3.88</v>
       </c>
       <c r="P60">
-        <v>3.05</v>
+        <v>3.56</v>
       </c>
       <c r="Q60">
         <v>2.3</v>
       </c>
       <c r="R60">
-        <v>2.37</v>
+        <v>2.42</v>
       </c>
       <c r="S60">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T60">
         <v>4</v>
@@ -10134,13 +10134,13 @@
         <v>2.7</v>
       </c>
       <c r="AC60">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AD60">
         <v>1.75</v>
       </c>
       <c r="AE60">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AF60">
         <v>1.4</v>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="O61">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="P61">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Q61">
         <v>1.9</v>
@@ -10276,10 +10276,10 @@
         <v>2.1</v>
       </c>
       <c r="V61">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W61">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X61">
         <v>1.02</v>
@@ -10294,7 +10294,7 @@
         <v>1.43</v>
       </c>
       <c r="AB61">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AC61">
         <v>2.19</v>
@@ -10306,7 +10306,7 @@
         <v>1.24</v>
       </c>
       <c r="AF61">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AG61">
         <v>2.18</v>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AK61">
         <v>2.88</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="O62">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="P62">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="Q62">
         <v>2.5</v>
@@ -10451,16 +10451,16 @@
         <v>1.12</v>
       </c>
       <c r="Z62">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA62">
         <v>1.38</v>
       </c>
       <c r="AB62">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="AC62">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="AD62">
         <v>1.76</v>
@@ -10469,7 +10469,7 @@
         <v>1.29</v>
       </c>
       <c r="AF62">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AG62">
         <v>2.8</v>
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="O63">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="P63">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10617,10 +10617,10 @@
         <v>0</v>
       </c>
       <c r="AA63">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB63">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC63">
         <v>0</v>
@@ -10747,13 +10747,13 @@
         <v>3.6</v>
       </c>
       <c r="P64">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q64">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="R64">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="S64">
         <v>1.18</v>
@@ -10762,16 +10762,16 @@
         <v>2.8</v>
       </c>
       <c r="U64">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="V64">
-        <v>1.49</v>
+        <v>1.63</v>
       </c>
       <c r="W64">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X64">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y64">
         <v>1.11</v>
@@ -10780,25 +10780,25 @@
         <v>4.95</v>
       </c>
       <c r="AA64">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AB64">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AC64">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="AD64">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AE64">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AF64">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AG64">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AK64">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11233,7 +11233,7 @@
         <v>3</v>
       </c>
       <c r="O67">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="P67">
         <v>2.15</v>
@@ -11242,13 +11242,13 @@
         <v>3.5</v>
       </c>
       <c r="R67">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="S67">
         <v>1.22</v>
       </c>
       <c r="T67">
-        <v>3.66</v>
+        <v>3.8</v>
       </c>
       <c r="U67">
         <v>2.05</v>
@@ -11260,25 +11260,25 @@
         <v>1.14</v>
       </c>
       <c r="X67">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y67">
         <v>1.15</v>
       </c>
       <c r="Z67">
-        <v>5.25</v>
+        <v>5.4</v>
       </c>
       <c r="AA67">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AB67">
-        <v>2.51</v>
+        <v>2.65</v>
       </c>
       <c r="AC67">
         <v>2.15</v>
       </c>
       <c r="AD67">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AE67">
         <v>1.25</v>
@@ -11287,7 +11287,7 @@
         <v>1.4</v>
       </c>
       <c r="AG67">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11396,10 +11396,10 @@
         <v>2.38</v>
       </c>
       <c r="O68">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P68">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="Q68">
         <v>2.91</v>
@@ -11426,7 +11426,7 @@
         <v>1.03</v>
       </c>
       <c r="Y68">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Z68">
         <v>4.65</v>
@@ -11444,7 +11444,7 @@
         <v>1.5</v>
       </c>
       <c r="AE68">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AF68">
         <v>1.45</v>
@@ -11466,7 +11466,7 @@
         <v>1.44</v>
       </c>
       <c r="AK68">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="O69">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P69">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="Q69">
+        <v>2.38</v>
+      </c>
+      <c r="R69">
+        <v>2.18</v>
+      </c>
+      <c r="S69">
+        <v>1.32</v>
+      </c>
+      <c r="T69">
+        <v>2.86</v>
+      </c>
+      <c r="U69">
         <v>2.5</v>
       </c>
-      <c r="R69">
-        <v>2.25</v>
-      </c>
-      <c r="S69">
-        <v>1.3</v>
-      </c>
-      <c r="T69">
-        <v>3.2</v>
-      </c>
-      <c r="U69">
-        <v>2.41</v>
-      </c>
       <c r="V69">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W69">
         <v>1.08</v>
       </c>
       <c r="X69">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y69">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z69">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AA69">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AB69">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AC69">
-        <v>2.62</v>
+        <v>2.91</v>
       </c>
       <c r="AD69">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE69">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF69">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AG69">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK69">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -12211,7 +12211,7 @@
         <v>1.57</v>
       </c>
       <c r="O73">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P73">
         <v>4.6</v>
@@ -12235,7 +12235,7 @@
         <v>1.44</v>
       </c>
       <c r="W73">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X73">
         <v>1.04</v>
@@ -12259,13 +12259,13 @@
         <v>1.35</v>
       </c>
       <c r="AE73">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF73">
         <v>1.8</v>
       </c>
       <c r="AG73">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>1.09</v>
       </c>
       <c r="AK73">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12534,22 +12534,22 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="O75">
         <v>7</v>
       </c>
       <c r="P75">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q75">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="R75">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="S75">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="T75">
         <v>5.5</v>
@@ -12582,16 +12582,16 @@
         <v>1.62</v>
       </c>
       <c r="AD75">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AE75">
         <v>1.48</v>
       </c>
       <c r="AF75">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="AG75">
-        <v>1.67</v>
+        <v>2.24</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AK75">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="O76">
         <v>3.2</v>
       </c>
       <c r="P76">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="Q76">
         <v>3.3</v>
@@ -12715,7 +12715,7 @@
         <v>1.42</v>
       </c>
       <c r="T76">
-        <v>2.9</v>
+        <v>2.69</v>
       </c>
       <c r="U76">
         <v>2.97</v>
@@ -12730,7 +12730,7 @@
         <v>1.04</v>
       </c>
       <c r="Y76">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z76">
         <v>3.25</v>
@@ -12742,13 +12742,13 @@
         <v>1.78</v>
       </c>
       <c r="AC76">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AD76">
         <v>1.25</v>
       </c>
       <c r="AE76">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF76">
         <v>1.75</v>
@@ -12860,19 +12860,19 @@
         </is>
       </c>
       <c r="N77">
-        <v>3.3</v>
+        <v>3.67</v>
       </c>
       <c r="O77">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="P77">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q77">
         <v>4.16</v>
       </c>
       <c r="R77">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S77">
         <v>1.25</v>
@@ -12881,13 +12881,13 @@
         <v>3.45</v>
       </c>
       <c r="U77">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V77">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W77">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X77">
         <v>1.03</v>
@@ -12896,16 +12896,16 @@
         <v>1.19</v>
       </c>
       <c r="Z77">
-        <v>4.33</v>
+        <v>4.64</v>
       </c>
       <c r="AA77">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AB77">
         <v>2.29</v>
       </c>
       <c r="AC77">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AD77">
         <v>1.44</v>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK77">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="O78">
-        <v>4.35</v>
+        <v>4.3</v>
       </c>
       <c r="P78">
-        <v>5.25</v>
+        <v>5.39</v>
       </c>
       <c r="Q78">
         <v>0</v>
@@ -13186,10 +13186,10 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="O79">
-        <v>3.5</v>
+        <v>3.73</v>
       </c>
       <c r="P79">
         <v>2.35</v>
@@ -13204,10 +13204,10 @@
         <v>1.2</v>
       </c>
       <c r="T79">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="U79">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="V79">
         <v>1.76</v>
@@ -13225,7 +13225,7 @@
         <v>7</v>
       </c>
       <c r="AA79">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AB79">
         <v>2.85</v>
@@ -13234,7 +13234,7 @@
         <v>1.96</v>
       </c>
       <c r="AD79">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AE79">
         <v>1.3</v>
@@ -13243,7 +13243,7 @@
         <v>1.3</v>
       </c>
       <c r="AG79">
-        <v>2.9</v>
+        <v>2.99</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="O80">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P80">
-        <v>3.03</v>
+        <v>3.25</v>
       </c>
       <c r="Q80">
         <v>2.33</v>
@@ -13367,7 +13367,7 @@
         <v>1.25</v>
       </c>
       <c r="T80">
-        <v>3.36</v>
+        <v>3.6</v>
       </c>
       <c r="U80">
         <v>2.25</v>
@@ -13379,7 +13379,7 @@
         <v>1.12</v>
       </c>
       <c r="X80">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y80">
         <v>1.13</v>
@@ -13419,7 +13419,7 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK80">
         <v>1.85</v>
@@ -13518,19 +13518,19 @@
         <v>3.95</v>
       </c>
       <c r="P81">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="Q81">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="R81">
         <v>2.7</v>
       </c>
       <c r="S81">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T81">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="U81">
         <v>1.85</v>
@@ -13554,13 +13554,13 @@
         <v>1.3</v>
       </c>
       <c r="AB81">
-        <v>3.36</v>
+        <v>3.39</v>
       </c>
       <c r="AC81">
         <v>1.75</v>
       </c>
       <c r="AD81">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AE81">
         <v>1.38</v>
@@ -13693,13 +13693,13 @@
         <v>1.14</v>
       </c>
       <c r="T82">
-        <v>4.55</v>
+        <v>4.8</v>
       </c>
       <c r="U82">
         <v>1.83</v>
       </c>
       <c r="V82">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="W82">
         <v>1.25</v>
@@ -13708,31 +13708,31 @@
         <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Z82">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="AA82">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AB82">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="AC82">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AD82">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AE82">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AF82">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AG82">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="AK82">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="O83">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="P83">
-        <v>5.35</v>
+        <v>5.6</v>
       </c>
       <c r="Q83">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="R83">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="S83">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="T83">
-        <v>4.65</v>
+        <v>5.25</v>
       </c>
       <c r="U83">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="V83">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="W83">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X83">
         <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z83">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="AA83">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AB83">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="AC83">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AD83">
-        <v>2.04</v>
+        <v>2.21</v>
       </c>
       <c r="AE83">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="AF83">
         <v>1.4</v>
       </c>
       <c r="AG83">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AK83">
-        <v>2.56</v>
+        <v>3.18</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="O84">
-        <v>5.3</v>
+        <v>4.55</v>
       </c>
       <c r="P84">
-        <v>6.1</v>
+        <v>5.35</v>
       </c>
       <c r="Q84">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="R84">
-        <v>3.22</v>
+        <v>2.77</v>
       </c>
       <c r="S84">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="T84">
-        <v>5</v>
+        <v>4.65</v>
       </c>
       <c r="U84">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="V84">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="W84">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="X84">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Z84">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="AA84">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AB84">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AC84">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AD84">
-        <v>2.21</v>
+        <v>2.04</v>
       </c>
       <c r="AE84">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AF84">
         <v>1.4</v>
       </c>
       <c r="AG84">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AK84">
-        <v>3.18</v>
+        <v>2.56</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14176,7 +14176,7 @@
         <v>2.4</v>
       </c>
       <c r="R85">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="S85">
         <v>1.41</v>
@@ -14194,25 +14194,25 @@
         <v>1.04</v>
       </c>
       <c r="X85">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y85">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z85">
         <v>2.8</v>
       </c>
       <c r="AA85">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AB85">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AC85">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AD85">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AE85">
         <v>1.06</v>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK85">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14327,28 +14327,28 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="O86">
         <v>3.4</v>
       </c>
       <c r="P86">
-        <v>4.05</v>
+        <v>5</v>
       </c>
       <c r="Q86">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="R86">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="S86">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="T86">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="U86">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="V86">
         <v>1.28</v>
@@ -14360,31 +14360,31 @@
         <v>1.03</v>
       </c>
       <c r="Y86">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z86">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AA86">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AB86">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="AC86">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="AD86">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AE86">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF86">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AG86">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK86">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14490,10 +14490,10 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="O87">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P87">
         <v>2.6</v>
@@ -14502,7 +14502,7 @@
         <v>2.95</v>
       </c>
       <c r="R87">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S87">
         <v>1.3</v>
@@ -14517,10 +14517,10 @@
         <v>1.44</v>
       </c>
       <c r="W87">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X87">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y87">
         <v>1.19</v>
@@ -14532,16 +14532,16 @@
         <v>1.71</v>
       </c>
       <c r="AB87">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AC87">
         <v>2.79</v>
       </c>
       <c r="AD87">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE87">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF87">
         <v>1.6</v>
@@ -14563,7 +14563,7 @@
         <v>1.38</v>
       </c>
       <c r="AK87">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G88">
@@ -14649,68 +14649,68 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N88">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="O88">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="P88">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="Q88">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="R88">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S88">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T88">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="U88">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V88">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W88">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X88">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y88">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z88">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA88">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB88">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC88">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD88">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AE88">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF88">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG88">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK88">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G89">
@@ -14812,68 +14812,68 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S89">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T89">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U89">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V89">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W89">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X89">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y89">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z89">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA89">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB89">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC89">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD89">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG89">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK89">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S90">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T90">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U90">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V90">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W90">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X90">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y90">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z90">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA90">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB90">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC90">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD90">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG90">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK90">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15142,61 +15142,61 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.55</v>
+        <v>2.74</v>
       </c>
       <c r="O91">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="P91">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="Q91">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="R91">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="S91">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="T91">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="U91">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="V91">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="W91">
         <v>1.03</v>
       </c>
       <c r="X91">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y91">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="Z91">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AA91">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AB91">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AC91">
-        <v>4.6</v>
+        <v>4.09</v>
       </c>
       <c r="AD91">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AE91">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF91">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AG91">
         <v>1.8</v>
@@ -15215,7 +15215,7 @@
         <v>1.28</v>
       </c>
       <c r="AK91">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -16488,7 +16488,7 @@
         <v>2.25</v>
       </c>
       <c r="AB99">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AC99">
         <v>4.05</v>
@@ -16516,7 +16516,7 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AK99">
         <v>1.67</v>
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="O101">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="P101">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="Q101">
         <v>3.3</v>
@@ -16787,25 +16787,25 @@
         <v>1.91</v>
       </c>
       <c r="S101">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="T101">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="U101">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="V101">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W101">
         <v>1.04</v>
       </c>
       <c r="X101">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y101">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="Z101">
         <v>2.41</v>
@@ -16829,7 +16829,7 @@
         <v>2.01</v>
       </c>
       <c r="AG101">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -17424,58 +17424,58 @@
         </is>
       </c>
       <c r="N105">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O105">
-        <v>3.84</v>
+        <v>3.75</v>
       </c>
       <c r="P105">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q105">
-        <v>5</v>
+        <v>4.84</v>
       </c>
       <c r="R105">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S105">
         <v>1.3</v>
       </c>
       <c r="T105">
-        <v>3.16</v>
+        <v>2.82</v>
       </c>
       <c r="U105">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="V105">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="W105">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X105">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y105">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z105">
         <v>3.7</v>
       </c>
       <c r="AA105">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AB105">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AC105">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AD105">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AE105">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF105">
         <v>1.73</v>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.2</v>
+        <v>2.09</v>
       </c>
       <c r="AK105">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17587,31 +17587,31 @@
         </is>
       </c>
       <c r="N106">
-        <v>3.79</v>
+        <v>4.2</v>
       </c>
       <c r="O106">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P106">
         <v>1.99</v>
       </c>
       <c r="Q106">
-        <v>4.8</v>
+        <v>5.24</v>
       </c>
       <c r="R106">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="S106">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T106">
         <v>2.88</v>
       </c>
       <c r="U106">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="V106">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W106">
         <v>1.05</v>
@@ -17620,16 +17620,16 @@
         <v>1.03</v>
       </c>
       <c r="Y106">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z106">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="AA106">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AB106">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AC106">
         <v>3.6</v>
@@ -17641,10 +17641,10 @@
         <v>1.06</v>
       </c>
       <c r="AF106">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG106">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.25</v>
+        <v>1.95</v>
       </c>
       <c r="AK106">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -18565,7 +18565,7 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="O112">
         <v>3.1</v>
@@ -18583,31 +18583,31 @@
         <v>1.38</v>
       </c>
       <c r="T112">
-        <v>2.73</v>
+        <v>2.95</v>
       </c>
       <c r="U112">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="V112">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W112">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X112">
         <v>1.05</v>
       </c>
       <c r="Y112">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z112">
-        <v>3.66</v>
+        <v>3.5</v>
       </c>
       <c r="AA112">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AB112">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AC112">
         <v>3.2</v>
@@ -18619,10 +18619,10 @@
         <v>1.11</v>
       </c>
       <c r="AF112">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG112">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>2</v>
       </c>
       <c r="O114">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="P114">
         <v>3.9</v>
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>3.57</v>
+        <v>3.49</v>
       </c>
       <c r="O115">
-        <v>3.58</v>
+        <v>3.35</v>
       </c>
       <c r="P115">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="Q115">
         <v>4.16</v>
@@ -19069,7 +19069,7 @@
         <v>2.17</v>
       </c>
       <c r="S115">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T115">
         <v>2.9</v>
@@ -19084,34 +19084,34 @@
         <v>1.06</v>
       </c>
       <c r="X115">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y115">
         <v>1.28</v>
       </c>
       <c r="Z115">
-        <v>3.55</v>
+        <v>3.62</v>
       </c>
       <c r="AA115">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AB115">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AC115">
         <v>3.2</v>
       </c>
       <c r="AD115">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE115">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF115">
         <v>1.67</v>
       </c>
       <c r="AG115">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.7</v>
+        <v>1.22</v>
       </c>
       <c r="AK115">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19217,28 +19217,28 @@
         </is>
       </c>
       <c r="N116">
-        <v>2.28</v>
+        <v>2.03</v>
       </c>
       <c r="O116">
-        <v>3.81</v>
+        <v>3.55</v>
       </c>
       <c r="P116">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="Q116">
-        <v>2.47</v>
+        <v>2.67</v>
       </c>
       <c r="R116">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="S116">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T116">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="U116">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="V116">
         <v>1.49</v>
@@ -19250,31 +19250,31 @@
         <v>1.01</v>
       </c>
       <c r="Y116">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z116">
-        <v>4.21</v>
+        <v>4.1</v>
       </c>
       <c r="AA116">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AB116">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="AC116">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="AD116">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE116">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF116">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AG116">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AK116">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="O117">
-        <v>7.35</v>
+        <v>6.75</v>
       </c>
       <c r="P117">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Q117">
         <v>1.55</v>
@@ -19395,16 +19395,16 @@
         <v>2.75</v>
       </c>
       <c r="S117">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T117">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="U117">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="V117">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W117">
         <v>1.11</v>
@@ -19419,13 +19419,13 @@
         <v>4.8</v>
       </c>
       <c r="AA117">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AB117">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="AC117">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="AD117">
         <v>1.53</v>
@@ -19450,7 +19450,7 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK117">
         <v>4.5</v>
@@ -19869,13 +19869,13 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="O120">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="P120">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q120">
         <v>0</v>
@@ -20032,52 +20032,52 @@
         </is>
       </c>
       <c r="N121">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="O121">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P121">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="Q121">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="R121">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="S121">
         <v>1.2</v>
       </c>
       <c r="T121">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U121">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V121">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="W121">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X121">
         <v>1.02</v>
       </c>
       <c r="Y121">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z121">
-        <v>5.25</v>
+        <v>3.6</v>
       </c>
       <c r="AA121">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB121">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="AC121">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AD121">
         <v>1.71</v>
@@ -20086,10 +20086,10 @@
         <v>1.25</v>
       </c>
       <c r="AF121">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AG121">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>1.33</v>
       </c>
       <c r="AK121">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20195,31 +20195,31 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="O122">
-        <v>3.89</v>
+        <v>3.35</v>
       </c>
       <c r="P122">
-        <v>4.99</v>
+        <v>3.48</v>
       </c>
       <c r="Q122">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="R122">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="S122">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="T122">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="U122">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="V122">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W122">
         <v>1.04</v>
@@ -20231,19 +20231,19 @@
         <v>1.35</v>
       </c>
       <c r="Z122">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="AA122">
         <v>2.26</v>
       </c>
       <c r="AB122">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AC122">
-        <v>3.98</v>
+        <v>3.68</v>
       </c>
       <c r="AD122">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE122">
         <v>1.04</v>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AK122">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="O123">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P123">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q123">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R123">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S123">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T123">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U123">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="V123">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W123">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X123">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y123">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z123">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA123">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB123">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC123">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD123">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE123">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF123">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG123">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK123">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O124">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P124">
-        <v>0</v>
+        <v>6.11</v>
       </c>
       <c r="Q124">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="R124">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S124">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T124">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="U124">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="V124">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W124">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X124">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y124">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z124">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="AA124">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="AB124">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="AC124">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AD124">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE124">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF124">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AG124">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK124">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20684,10 +20684,10 @@
         </is>
       </c>
       <c r="N125">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="O125">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P125">
         <v>4</v>
@@ -20856,46 +20856,46 @@
         <v>6.9</v>
       </c>
       <c r="Q126">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="R126">
         <v>1.91</v>
       </c>
       <c r="S126">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="T126">
         <v>2.28</v>
       </c>
       <c r="U126">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="V126">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="W126">
+        <v>1.02</v>
+      </c>
+      <c r="X126">
         <v>1.05</v>
-      </c>
-      <c r="X126">
-        <v>1.11</v>
       </c>
       <c r="Y126">
         <v>1.5</v>
       </c>
       <c r="Z126">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="AA126">
         <v>2.55</v>
       </c>
       <c r="AB126">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AC126">
         <v>5</v>
       </c>
       <c r="AD126">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AE126">
         <v>1.01</v>
@@ -20904,7 +20904,7 @@
         <v>2.6</v>
       </c>
       <c r="AG126">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -21019,16 +21019,16 @@
         <v>0</v>
       </c>
       <c r="Q127">
-        <v>5.07</v>
+        <v>4.86</v>
       </c>
       <c r="R127">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S127">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T127">
-        <v>2.99</v>
+        <v>3.08</v>
       </c>
       <c r="U127">
         <v>2.59</v>
@@ -21037,34 +21037,34 @@
         <v>1.43</v>
       </c>
       <c r="W127">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X127">
         <v>1</v>
       </c>
       <c r="Y127">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z127">
-        <v>3.58</v>
+        <v>3.71</v>
       </c>
       <c r="AA127">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AB127">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AC127">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="AD127">
         <v>1.33</v>
       </c>
       <c r="AE127">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF127">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AG127">
         <v>1.93</v>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AK127">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -22477,16 +22477,16 @@
         </is>
       </c>
       <c r="N136">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="O136">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P136">
-        <v>4.05</v>
+        <v>3.75</v>
       </c>
       <c r="Q136">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="R136">
         <v>2.25</v>
@@ -22519,7 +22519,7 @@
         <v>1.82</v>
       </c>
       <c r="AB136">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AC136">
         <v>3.1</v>
@@ -22640,40 +22640,40 @@
         </is>
       </c>
       <c r="N137">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="O137">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="P137">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="Q137">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="R137">
-        <v>2.24</v>
+        <v>2.48</v>
       </c>
       <c r="S137">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T137">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U137">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="V137">
         <v>1.53</v>
       </c>
       <c r="W137">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X137">
         <v>1.03</v>
       </c>
       <c r="Y137">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z137">
         <v>4.5</v>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK137">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22803,22 +22803,22 @@
         </is>
       </c>
       <c r="N138">
-        <v>2.33</v>
+        <v>2.12</v>
       </c>
       <c r="O138">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="P138">
-        <v>3.06</v>
+        <v>2.8</v>
       </c>
       <c r="Q138">
-        <v>2.8</v>
+        <v>2.97</v>
       </c>
       <c r="R138">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S138">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T138">
         <v>2.8</v>
@@ -22827,40 +22827,40 @@
         <v>2.8</v>
       </c>
       <c r="V138">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W138">
         <v>1.08</v>
       </c>
       <c r="X138">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y138">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z138">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AA138">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB138">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AC138">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AD138">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE138">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF138">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG138">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AK138">
         <v>1.53</v>
@@ -22966,64 +22966,64 @@
         </is>
       </c>
       <c r="N139">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="O139">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="P139">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="Q139">
-        <v>5.65</v>
+        <v>5.5</v>
       </c>
       <c r="R139">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="S139">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T139">
-        <v>2.85</v>
+        <v>2.99</v>
       </c>
       <c r="U139">
-        <v>2.94</v>
+        <v>2.75</v>
       </c>
       <c r="V139">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W139">
         <v>1.08</v>
       </c>
       <c r="X139">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y139">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z139">
-        <v>3.41</v>
+        <v>3.65</v>
       </c>
       <c r="AA139">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="AB139">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AC139">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AD139">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE139">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF139">
         <v>1.91</v>
       </c>
       <c r="AG139">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AK139">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23138,55 +23138,55 @@
         <v>0</v>
       </c>
       <c r="Q140">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R140">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S140">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T140">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U140">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V140">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W140">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X140">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y140">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z140">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA140">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB140">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC140">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AD140">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE140">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF140">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AG140">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK140">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -23621,61 +23621,61 @@
         <v>1.64</v>
       </c>
       <c r="O143">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P143">
         <v>5.01</v>
       </c>
       <c r="Q143">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="R143">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="S143">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T143">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="U143">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="V143">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W143">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X143">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y143">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z143">
         <v>3</v>
       </c>
       <c r="AA143">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AB143">
         <v>1.74</v>
       </c>
       <c r="AC143">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AD143">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE143">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF143">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG143">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23691,7 +23691,7 @@
         <v>1.22</v>
       </c>
       <c r="AK143">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -25085,64 +25085,64 @@
         </is>
       </c>
       <c r="N152">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O152">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P152">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q152">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R152">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S152">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="T152">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U152">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V152">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W152">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X152">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y152">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z152">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AA152">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB152">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC152">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD152">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE152">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF152">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AG152">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK152">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25248,64 +25248,64 @@
         </is>
       </c>
       <c r="N153">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O153">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P153">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q153">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="R153">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S153">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T153">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U153">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="V153">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W153">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X153">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y153">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z153">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA153">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB153">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC153">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AD153">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE153">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF153">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG153">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK153">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25450,10 +25450,10 @@
         <v>0</v>
       </c>
       <c r="AA154">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AB154">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC154">
         <v>0</v>
@@ -25764,31 +25764,31 @@
         <v>1.5</v>
       </c>
       <c r="W156">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X156">
         <v>1.03</v>
       </c>
       <c r="Y156">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z156">
-        <v>4.07</v>
+        <v>4.33</v>
       </c>
       <c r="AA156">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AB156">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AC156">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="AD156">
         <v>1.44</v>
       </c>
       <c r="AE156">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF156">
         <v>1.85</v>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AK156">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25909,40 +25909,40 @@
         <v>3.16</v>
       </c>
       <c r="Q157">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R157">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S157">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T157">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U157">
-        <v>2.73</v>
+        <v>2.99</v>
       </c>
       <c r="V157">
         <v>1.36</v>
       </c>
       <c r="W157">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X157">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y157">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z157">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA157">
-        <v>2.25</v>
+        <v>2.01</v>
       </c>
       <c r="AB157">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="AC157">
         <v>3.34</v>
@@ -25951,13 +25951,13 @@
         <v>1.24</v>
       </c>
       <c r="AE157">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF157">
         <v>1.73</v>
       </c>
       <c r="AG157">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK157">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26072,22 +26072,22 @@
         <v>3.8</v>
       </c>
       <c r="Q158">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R158">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="S158">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="T158">
         <v>2.55</v>
       </c>
       <c r="U158">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="V158">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W158">
         <v>1.03</v>
@@ -26096,31 +26096,31 @@
         <v>1.06</v>
       </c>
       <c r="Y158">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Z158">
-        <v>2.64</v>
+        <v>2.59</v>
       </c>
       <c r="AA158">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AB158">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AC158">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="AD158">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE158">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF158">
         <v>2.1</v>
       </c>
       <c r="AG158">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26277,13 +26277,13 @@
         <v>1.12</v>
       </c>
       <c r="AE159">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF159">
         <v>2.1</v>
       </c>
       <c r="AG159">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26296,7 +26296,7 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AK159">
         <v>2.04</v>
@@ -26389,22 +26389,22 @@
         </is>
       </c>
       <c r="N160">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="O160">
-        <v>3.89</v>
+        <v>3.4</v>
       </c>
       <c r="P160">
-        <v>4.89</v>
+        <v>3.7</v>
       </c>
       <c r="Q160">
         <v>2.38</v>
       </c>
       <c r="R160">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="S160">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T160">
         <v>2.73</v>
@@ -26416,7 +26416,7 @@
         <v>1.37</v>
       </c>
       <c r="W160">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X160">
         <v>1.03</v>
@@ -26431,22 +26431,22 @@
         <v>1.89</v>
       </c>
       <c r="AB160">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AC160">
         <v>3.4</v>
       </c>
       <c r="AD160">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE160">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF160">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG160">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26462,7 +26462,7 @@
         <v>1.32</v>
       </c>
       <c r="AK160">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -26552,22 +26552,22 @@
         </is>
       </c>
       <c r="N161">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="O161">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P161">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="Q161">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="R161">
         <v>2.2</v>
       </c>
       <c r="S161">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T161">
         <v>2.66</v>
@@ -26576,40 +26576,40 @@
         <v>2.81</v>
       </c>
       <c r="V161">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W161">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X161">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y161">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z161">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AA161">
         <v>1.96</v>
       </c>
       <c r="AB161">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AC161">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="AD161">
         <v>1.27</v>
       </c>
       <c r="AE161">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF161">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG161">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="AK161">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -26718,7 +26718,7 @@
         <v>1.12</v>
       </c>
       <c r="O162">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="P162">
         <v>15</v>
@@ -26730,19 +26730,19 @@
         <v>3</v>
       </c>
       <c r="S162">
+        <v>1.22</v>
+      </c>
+      <c r="T162">
+        <v>3.9</v>
+      </c>
+      <c r="U162">
+        <v>2.11</v>
+      </c>
+      <c r="V162">
+        <v>1.69</v>
+      </c>
+      <c r="W162">
         <v>1.18</v>
-      </c>
-      <c r="T162">
-        <v>3.88</v>
-      </c>
-      <c r="U162">
-        <v>2.05</v>
-      </c>
-      <c r="V162">
-        <v>1.77</v>
-      </c>
-      <c r="W162">
-        <v>1.2</v>
       </c>
       <c r="X162">
         <v>1.01</v>
@@ -26754,22 +26754,22 @@
         <v>5.45</v>
       </c>
       <c r="AA162">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AB162">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AC162">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AD162">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AE162">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF162">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="AG162">
         <v>1.5</v>
@@ -26788,7 +26788,7 @@
         <v>1.06</v>
       </c>
       <c r="AK162">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -26878,7 +26878,7 @@
         </is>
       </c>
       <c r="N163">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="O163">
         <v>3.1</v>
@@ -26887,16 +26887,16 @@
         <v>6.5</v>
       </c>
       <c r="Q163">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="R163">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="S163">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="T163">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="U163">
         <v>3.35</v>
@@ -26905,53 +26905,53 @@
         <v>1.26</v>
       </c>
       <c r="W163">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X163">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y163">
         <v>1.5</v>
       </c>
       <c r="Z163">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AA163">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AB163">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AC163">
         <v>5</v>
       </c>
       <c r="AD163">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE163">
         <v>1.04</v>
       </c>
       <c r="AF163">
+        <v>2.5</v>
+      </c>
+      <c r="AG163">
+        <v>1.5</v>
+      </c>
+      <c r="AH163" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ163">
+        <v>1.3</v>
+      </c>
+      <c r="AK163">
         <v>2.3</v>
-      </c>
-      <c r="AG163">
-        <v>1.52</v>
-      </c>
-      <c r="AH163" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI163" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ163">
-        <v>1.33</v>
-      </c>
-      <c r="AK163">
-        <v>2.15</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27367,7 +27367,7 @@
         </is>
       </c>
       <c r="N166">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="O166">
         <v>2.8</v>
@@ -27376,7 +27376,7 @@
         <v>3.7</v>
       </c>
       <c r="Q166">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="R166">
         <v>1.85</v>
@@ -27385,7 +27385,7 @@
         <v>1.63</v>
       </c>
       <c r="T166">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="U166">
         <v>3.7</v>
@@ -27403,7 +27403,7 @@
         <v>1.62</v>
       </c>
       <c r="Z166">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AA166">
         <v>3.1</v>
@@ -27415,7 +27415,7 @@
         <v>5</v>
       </c>
       <c r="AD166">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AE166">
         <v>1.03</v>
@@ -27440,7 +27440,7 @@
         <v>1.36</v>
       </c>
       <c r="AK166">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27530,10 +27530,10 @@
         </is>
       </c>
       <c r="N167">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="O167">
-        <v>3.78</v>
+        <v>3.65</v>
       </c>
       <c r="P167">
         <v>3.7</v>
@@ -27545,10 +27545,10 @@
         <v>2.26</v>
       </c>
       <c r="S167">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T167">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="U167">
         <v>2.4</v>
@@ -27557,25 +27557,25 @@
         <v>1.5</v>
       </c>
       <c r="W167">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X167">
         <v>1.03</v>
       </c>
       <c r="Y167">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z167">
-        <v>3.97</v>
+        <v>3.78</v>
       </c>
       <c r="AA167">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AB167">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AC167">
-        <v>2.96</v>
+        <v>2.65</v>
       </c>
       <c r="AD167">
         <v>1.37</v>
@@ -27584,10 +27584,10 @@
         <v>1.12</v>
       </c>
       <c r="AF167">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG167">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27603,7 +27603,7 @@
         <v>1.22</v>
       </c>
       <c r="AK167">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -27702,55 +27702,55 @@
         <v>0</v>
       </c>
       <c r="Q168">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="R168">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S168">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="T168">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U168">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="V168">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W168">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X168">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y168">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z168">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AA168">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AB168">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC168">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AD168">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE168">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF168">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AG168">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
@@ -27763,10 +27763,10 @@
         </is>
       </c>
       <c r="AJ168">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK168">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -28019,13 +28019,13 @@
         </is>
       </c>
       <c r="N170">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="O170">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="P170">
-        <v>3.06</v>
+        <v>2.75</v>
       </c>
       <c r="Q170">
         <v>0</v>
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,64 +28345,64 @@
         </is>
       </c>
       <c r="N172">
-        <v>2.17</v>
+        <v>2.45</v>
       </c>
       <c r="O172">
-        <v>3.3</v>
+        <v>3.21</v>
       </c>
       <c r="P172">
-        <v>3.6</v>
+        <v>3.11</v>
       </c>
       <c r="Q172">
+        <v>2.62</v>
+      </c>
+      <c r="R172">
+        <v>2.1</v>
+      </c>
+      <c r="S172">
+        <v>1.43</v>
+      </c>
+      <c r="T172">
         <v>2.7</v>
       </c>
-      <c r="R172">
-        <v>1.96</v>
-      </c>
-      <c r="S172">
-        <v>1.46</v>
-      </c>
-      <c r="T172">
-        <v>2.62</v>
-      </c>
       <c r="U172">
-        <v>2.91</v>
+        <v>3.05</v>
       </c>
       <c r="V172">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W172">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X172">
         <v>1.06</v>
       </c>
       <c r="Y172">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="Z172">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="AA172">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB172">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AC172">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AD172">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE172">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF172">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AG172">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28415,10 +28415,10 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AK172">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,64 +28508,64 @@
         </is>
       </c>
       <c r="N173">
-        <v>2.45</v>
+        <v>2.17</v>
       </c>
       <c r="O173">
-        <v>3.21</v>
+        <v>3.3</v>
       </c>
       <c r="P173">
-        <v>3.11</v>
+        <v>3.6</v>
       </c>
       <c r="Q173">
+        <v>2.7</v>
+      </c>
+      <c r="R173">
+        <v>1.96</v>
+      </c>
+      <c r="S173">
+        <v>1.46</v>
+      </c>
+      <c r="T173">
         <v>2.62</v>
       </c>
-      <c r="R173">
-        <v>2.1</v>
-      </c>
-      <c r="S173">
-        <v>1.43</v>
-      </c>
-      <c r="T173">
-        <v>2.7</v>
-      </c>
       <c r="U173">
-        <v>3.05</v>
+        <v>2.91</v>
       </c>
       <c r="V173">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W173">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X173">
         <v>1.06</v>
       </c>
       <c r="Y173">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="Z173">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AA173">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB173">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AC173">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AD173">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE173">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF173">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AG173">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28578,10 +28578,10 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AK173">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -29332,22 +29332,22 @@
         <v>1.6</v>
       </c>
       <c r="Q178">
-        <v>4.42</v>
+        <v>4.25</v>
       </c>
       <c r="R178">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="S178">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T178">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="U178">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="V178">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W178">
         <v>1.11</v>
@@ -29356,31 +29356,31 @@
         <v>1.03</v>
       </c>
       <c r="Y178">
+        <v>1.16</v>
+      </c>
+      <c r="Z178">
+        <v>4.1</v>
+      </c>
+      <c r="AA178">
+        <v>1.63</v>
+      </c>
+      <c r="AB178">
+        <v>2.12</v>
+      </c>
+      <c r="AC178">
+        <v>2.5</v>
+      </c>
+      <c r="AD178">
+        <v>1.41</v>
+      </c>
+      <c r="AE178">
         <v>1.17</v>
       </c>
-      <c r="Z178">
-        <v>4</v>
-      </c>
-      <c r="AA178">
-        <v>1.67</v>
-      </c>
-      <c r="AB178">
-        <v>2.05</v>
-      </c>
-      <c r="AC178">
-        <v>2.59</v>
-      </c>
-      <c r="AD178">
-        <v>1.39</v>
-      </c>
-      <c r="AE178">
-        <v>1.14</v>
-      </c>
       <c r="AF178">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AG178">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
@@ -29393,10 +29393,10 @@
         </is>
       </c>
       <c r="AJ178">
-        <v>1.25</v>
+        <v>1.91</v>
       </c>
       <c r="AK178">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29984,55 +29984,55 @@
         <v>2.58</v>
       </c>
       <c r="Q182">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="R182">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="S182">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="T182">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="U182">
-        <v>2.39</v>
+        <v>2.52</v>
       </c>
       <c r="V182">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="W182">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X182">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y182">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z182">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="AA182">
-        <v>1.94</v>
+        <v>1.73</v>
       </c>
       <c r="AB182">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AC182">
-        <v>2.69</v>
+        <v>3.04</v>
       </c>
       <c r="AD182">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AE182">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF182">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AG182">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AH182" t="inlineStr">
         <is>
@@ -30045,10 +30045,10 @@
         </is>
       </c>
       <c r="AJ182">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AK182">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AL182">
         <v>0</v>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="O144">
-        <v>3.67</v>
+        <v>3.91</v>
       </c>
       <c r="P144">
-        <v>4.48</v>
+        <v>6.63</v>
       </c>
       <c r="Q144">
-        <v>2.39</v>
+        <v>2.17</v>
       </c>
       <c r="R144">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="S144">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T144">
-        <v>3.13</v>
+        <v>2.9</v>
       </c>
       <c r="U144">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="V144">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="W144">
+        <v>1.08</v>
+      </c>
+      <c r="X144">
+        <v>1.03</v>
+      </c>
+      <c r="Y144">
+        <v>1.28</v>
+      </c>
+      <c r="Z144">
+        <v>3.42</v>
+      </c>
+      <c r="AA144">
+        <v>2.02</v>
+      </c>
+      <c r="AB144">
+        <v>1.84</v>
+      </c>
+      <c r="AC144">
+        <v>3.45</v>
+      </c>
+      <c r="AD144">
+        <v>1.3</v>
+      </c>
+      <c r="AE144">
         <v>1.06</v>
       </c>
-      <c r="X144">
-        <v>1</v>
-      </c>
-      <c r="Y144">
-        <v>1.24</v>
-      </c>
-      <c r="Z144">
-        <v>3.38</v>
-      </c>
-      <c r="AA144">
-        <v>1.88</v>
-      </c>
-      <c r="AB144">
-        <v>1.96</v>
-      </c>
-      <c r="AC144">
-        <v>2.94</v>
-      </c>
-      <c r="AD144">
-        <v>1.37</v>
-      </c>
-      <c r="AE144">
-        <v>1.13</v>
-      </c>
       <c r="AF144">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AG144">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK144">
-        <v>1.85</v>
+        <v>2.22</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="O145">
-        <v>3.91</v>
+        <v>3.67</v>
       </c>
       <c r="P145">
-        <v>6.63</v>
+        <v>4.48</v>
       </c>
       <c r="Q145">
-        <v>2.17</v>
+        <v>2.39</v>
       </c>
       <c r="R145">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="S145">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T145">
-        <v>2.9</v>
+        <v>3.13</v>
       </c>
       <c r="U145">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="V145">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="W145">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X145">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y145">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Z145">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="AA145">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="AB145">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="AC145">
-        <v>3.45</v>
+        <v>2.94</v>
       </c>
       <c r="AD145">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AE145">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF145">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AG145">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK145">
-        <v>2.22</v>
+        <v>1.85</v>
       </c>
       <c r="AL145">
         <v>0</v>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,16 +3243,16 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.1</v>
+        <v>1.88</v>
       </c>
       <c r="O18">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P18">
-        <v>2.15</v>
+        <v>3.95</v>
       </c>
       <c r="Q18">
-        <v>3.62</v>
+        <v>2.25</v>
       </c>
       <c r="R18">
         <v>2.4</v>
@@ -3261,46 +3261,46 @@
         <v>1.25</v>
       </c>
       <c r="T18">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="U18">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="V18">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="W18">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X18">
         <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="Z18">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AA18">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AB18">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="AC18">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AD18">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AE18">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AF18">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AG18">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK18">
-        <v>1.33</v>
+        <v>1.85</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,16 +3406,16 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.88</v>
+        <v>3.1</v>
       </c>
       <c r="O19">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P19">
-        <v>3.95</v>
+        <v>2.15</v>
       </c>
       <c r="Q19">
-        <v>2.25</v>
+        <v>3.62</v>
       </c>
       <c r="R19">
         <v>2.4</v>
@@ -3424,46 +3424,46 @@
         <v>1.25</v>
       </c>
       <c r="T19">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="U19">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="V19">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="W19">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X19">
         <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="Z19">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA19">
+        <v>1.54</v>
+      </c>
+      <c r="AB19">
+        <v>2.4</v>
+      </c>
+      <c r="AC19">
+        <v>2.35</v>
+      </c>
+      <c r="AD19">
         <v>1.57</v>
       </c>
-      <c r="AB19">
-        <v>2.14</v>
-      </c>
-      <c r="AC19">
-        <v>2.5</v>
-      </c>
-      <c r="AD19">
-        <v>1.44</v>
-      </c>
       <c r="AE19">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AF19">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AG19">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK19">
-        <v>1.85</v>
+        <v>1.33</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G170">
@@ -28019,64 +28019,64 @@
         </is>
       </c>
       <c r="N170">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="O170">
         <v>3.3</v>
       </c>
       <c r="P170">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="Q170">
+        <v>2.62</v>
+      </c>
+      <c r="R170">
+        <v>2.1</v>
+      </c>
+      <c r="S170">
+        <v>1.43</v>
+      </c>
+      <c r="T170">
         <v>2.7</v>
       </c>
-      <c r="R170">
-        <v>1.96</v>
-      </c>
-      <c r="S170">
-        <v>1.44</v>
-      </c>
-      <c r="T170">
-        <v>2.48</v>
-      </c>
       <c r="U170">
-        <v>2.89</v>
+        <v>3.05</v>
       </c>
       <c r="V170">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W170">
         <v>1.04</v>
       </c>
       <c r="X170">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y170">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="Z170">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="AA170">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AB170">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AC170">
-        <v>3.92</v>
+        <v>3.75</v>
       </c>
       <c r="AD170">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE170">
         <v>1.04</v>
       </c>
       <c r="AF170">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG170">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH170" t="inlineStr">
         <is>
@@ -28089,10 +28089,10 @@
         </is>
       </c>
       <c r="AJ170">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AK170">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,64 +28182,64 @@
         </is>
       </c>
       <c r="N171">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="O171">
         <v>3.3</v>
       </c>
       <c r="P171">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="Q171">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="R171">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="S171">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T171">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="U171">
-        <v>3.05</v>
+        <v>2.89</v>
       </c>
       <c r="V171">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W171">
         <v>1.04</v>
       </c>
       <c r="X171">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y171">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="Z171">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AA171">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AB171">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AC171">
-        <v>3.75</v>
+        <v>3.92</v>
       </c>
       <c r="AD171">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE171">
         <v>1.04</v>
       </c>
       <c r="AF171">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG171">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH171" t="inlineStr">
         <is>
@@ -28252,10 +28252,10 @@
         </is>
       </c>
       <c r="AJ171">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AK171">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AL171">
         <v>0</v>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -671,19 +671,19 @@
         <v>1.33</v>
       </c>
       <c r="Z2">
-        <v>2.83</v>
+        <v>2.99</v>
       </c>
       <c r="AA2">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AB2">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AC2">
         <v>3.9</v>
       </c>
       <c r="AD2">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AE2">
         <v>1.02</v>
@@ -708,7 +708,7 @@
         <v>1.34</v>
       </c>
       <c r="AK2">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,80 +798,80 @@
         </is>
       </c>
       <c r="N3">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="O3">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="P3">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Q3">
-        <v>5.01</v>
+        <v>4.5</v>
       </c>
       <c r="R3">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="S3">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T3">
+        <v>2.92</v>
+      </c>
+      <c r="U3">
+        <v>2.67</v>
+      </c>
+      <c r="V3">
+        <v>1.38</v>
+      </c>
+      <c r="W3">
+        <v>1.1</v>
+      </c>
+      <c r="X3">
+        <v>1</v>
+      </c>
+      <c r="Y3">
+        <v>1.24</v>
+      </c>
+      <c r="Z3">
+        <v>3.34</v>
+      </c>
+      <c r="AA3">
+        <v>1.95</v>
+      </c>
+      <c r="AB3">
+        <v>1.88</v>
+      </c>
+      <c r="AC3">
         <v>3.08</v>
       </c>
-      <c r="U3">
-        <v>2.53</v>
-      </c>
-      <c r="V3">
-        <v>1.42</v>
-      </c>
-      <c r="W3">
-        <v>1.06</v>
-      </c>
-      <c r="X3">
-        <v>1.01</v>
-      </c>
-      <c r="Y3">
-        <v>1.19</v>
-      </c>
-      <c r="Z3">
-        <v>3.74</v>
-      </c>
-      <c r="AA3">
-        <v>1.8</v>
-      </c>
-      <c r="AB3">
+      <c r="AD3">
+        <v>1.28</v>
+      </c>
+      <c r="AE3">
+        <v>1.07</v>
+      </c>
+      <c r="AF3">
+        <v>1.78</v>
+      </c>
+      <c r="AG3">
+        <v>1.86</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3">
         <v>2</v>
       </c>
-      <c r="AC3">
-        <v>2.81</v>
-      </c>
-      <c r="AD3">
-        <v>1.33</v>
-      </c>
-      <c r="AE3">
-        <v>1.09</v>
-      </c>
-      <c r="AF3">
-        <v>1.64</v>
-      </c>
-      <c r="AG3">
-        <v>1.95</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3">
-        <v>2.11</v>
-      </c>
       <c r="AK3">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -970,10 +970,10 @@
         <v>2.65</v>
       </c>
       <c r="Q4">
-        <v>2.78</v>
+        <v>2.59</v>
       </c>
       <c r="R4">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S4">
         <v>1.32</v>
@@ -982,10 +982,10 @@
         <v>3.2</v>
       </c>
       <c r="U4">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="V4">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W4">
         <v>1.07</v>
@@ -994,7 +994,7 @@
         <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z4">
         <v>3.8</v>
@@ -1006,16 +1006,16 @@
         <v>2.05</v>
       </c>
       <c r="AC4">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AD4">
         <v>1.34</v>
       </c>
       <c r="AE4">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF4">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG4">
         <v>2.15</v>
@@ -1034,7 +1034,7 @@
         <v>1.23</v>
       </c>
       <c r="AK4">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="O6">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="P6">
         <v>2.34</v>
@@ -1302,16 +1302,16 @@
         <v>2.11</v>
       </c>
       <c r="S6">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T6">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="U6">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="V6">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W6">
         <v>1.03</v>
@@ -1338,7 +1338,7 @@
         <v>1.19</v>
       </c>
       <c r="AE6">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF6">
         <v>1.85</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="O8">
         <v>3</v>
       </c>
       <c r="P8">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="Q8">
         <v>3.75</v>
@@ -1631,7 +1631,7 @@
         <v>1.48</v>
       </c>
       <c r="T8">
-        <v>2.44</v>
+        <v>2.64</v>
       </c>
       <c r="U8">
         <v>3.2</v>
@@ -1652,7 +1652,7 @@
         <v>2.74</v>
       </c>
       <c r="AA8">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB8">
         <v>1.6</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK8">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1942,7 +1942,7 @@
         <v>2.99</v>
       </c>
       <c r="O10">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="P10">
         <v>2.35</v>
@@ -1996,7 +1996,7 @@
         <v>1.8</v>
       </c>
       <c r="AG10">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="N12">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="O12">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P12">
         <v>1.7</v>
@@ -2280,7 +2280,7 @@
         <v>2.45</v>
       </c>
       <c r="S12">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T12">
         <v>3.55</v>
@@ -2295,25 +2295,25 @@
         <v>1.17</v>
       </c>
       <c r="X12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
         <v>1.15</v>
       </c>
       <c r="Z12">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="AA12">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AB12">
         <v>2.4</v>
       </c>
       <c r="AC12">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="AD12">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AE12">
         <v>1.2</v>
@@ -2322,7 +2322,7 @@
         <v>1.5</v>
       </c>
       <c r="AG12">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.24</v>
       </c>
       <c r="AK12">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="O13">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="P13">
         <v>2.05</v>
@@ -2449,7 +2449,7 @@
         <v>3.4</v>
       </c>
       <c r="U13">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="V13">
         <v>1.57</v>
@@ -2461,10 +2461,10 @@
         <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z13">
-        <v>4.85</v>
+        <v>4.79</v>
       </c>
       <c r="AA13">
         <v>1.57</v>
@@ -2482,7 +2482,7 @@
         <v>1.2</v>
       </c>
       <c r="AF13">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AG13">
         <v>2.44</v>
@@ -2600,22 +2600,22 @@
         <v>0</v>
       </c>
       <c r="Q14">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="R14">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="S14">
         <v>1.33</v>
       </c>
       <c r="T14">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U14">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="V14">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W14">
         <v>1.08</v>
@@ -2627,16 +2627,16 @@
         <v>1.21</v>
       </c>
       <c r="Z14">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AA14">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AB14">
         <v>2.12</v>
       </c>
       <c r="AC14">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="AD14">
         <v>1.44</v>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK14">
         <v>2.32</v>
@@ -2920,10 +2920,10 @@
         <v>3.7</v>
       </c>
       <c r="O16">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="P16">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Q16">
         <v>4.18</v>
@@ -2944,7 +2944,7 @@
         <v>1.68</v>
       </c>
       <c r="W16">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X16">
         <v>1.02</v>
@@ -2956,7 +2956,7 @@
         <v>5.65</v>
       </c>
       <c r="AA16">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB16">
         <v>2.81</v>
@@ -2965,13 +2965,13 @@
         <v>2.02</v>
       </c>
       <c r="AD16">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AE16">
         <v>1.26</v>
       </c>
       <c r="AF16">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AG16">
         <v>2.6</v>
@@ -3092,25 +3092,25 @@
         <v>2.7</v>
       </c>
       <c r="R17">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="S17">
         <v>1.3</v>
       </c>
       <c r="T17">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="U17">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="V17">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W17">
         <v>1.11</v>
       </c>
       <c r="X17">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
         <v>1.22</v>
@@ -3125,16 +3125,16 @@
         <v>2.2</v>
       </c>
       <c r="AC17">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="AD17">
         <v>1.4</v>
       </c>
       <c r="AE17">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF17">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG17">
         <v>2.3</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK17">
         <v>1.65</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.88</v>
+        <v>3.1</v>
       </c>
       <c r="O18">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P18">
-        <v>3.95</v>
+        <v>2.15</v>
       </c>
       <c r="Q18">
-        <v>2.25</v>
+        <v>3.62</v>
       </c>
       <c r="R18">
         <v>2.4</v>
       </c>
       <c r="S18">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T18">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="U18">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="V18">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="W18">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X18">
         <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="Z18">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AA18">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AB18">
-        <v>2.14</v>
+        <v>2.55</v>
       </c>
       <c r="AC18">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AD18">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AE18">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AF18">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AG18">
-        <v>2.3</v>
+        <v>2.53</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK18">
-        <v>1.85</v>
+        <v>1.33</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,16 +3406,16 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.1</v>
+        <v>1.83</v>
       </c>
       <c r="O19">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="P19">
-        <v>2.15</v>
+        <v>3.75</v>
       </c>
       <c r="Q19">
-        <v>3.62</v>
+        <v>2.25</v>
       </c>
       <c r="R19">
         <v>2.4</v>
@@ -3424,46 +3424,46 @@
         <v>1.25</v>
       </c>
       <c r="T19">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="U19">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="V19">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="W19">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X19">
         <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Z19">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AA19">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AB19">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="AC19">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AD19">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AE19">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AF19">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AG19">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>1.33</v>
+        <v>1.86</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3581,7 +3581,7 @@
         <v>2.28</v>
       </c>
       <c r="R20">
-        <v>2.09</v>
+        <v>2.24</v>
       </c>
       <c r="S20">
         <v>1.44</v>
@@ -3602,13 +3602,13 @@
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z20">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="AA20">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AB20">
         <v>1.73</v>
@@ -3934,10 +3934,10 @@
         <v>0</v>
       </c>
       <c r="AA22">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB22">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC22">
         <v>0</v>
@@ -4058,49 +4058,49 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.72</v>
+        <v>2.95</v>
       </c>
       <c r="O23">
-        <v>3.23</v>
+        <v>3.4</v>
       </c>
       <c r="P23">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="Q23">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="R23">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="S23">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T23">
         <v>3</v>
       </c>
       <c r="U23">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="V23">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="W23">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X23">
         <v>1.04</v>
       </c>
       <c r="Y23">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z23">
         <v>4.13</v>
       </c>
       <c r="AA23">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AB23">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC23">
         <v>2.75</v>
@@ -4112,7 +4112,7 @@
         <v>1.13</v>
       </c>
       <c r="AF23">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG23">
         <v>2.02</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="O24">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P24">
-        <v>3.75</v>
+        <v>3.27</v>
       </c>
       <c r="Q24">
         <v>2.24</v>
@@ -4239,7 +4239,7 @@
         <v>1.25</v>
       </c>
       <c r="T24">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="U24">
         <v>2.25</v>
@@ -4251,31 +4251,31 @@
         <v>1.15</v>
       </c>
       <c r="X24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z24">
-        <v>4.63</v>
+        <v>4.4</v>
       </c>
       <c r="AA24">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AB24">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="AC24">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AD24">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AE24">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF24">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG24">
         <v>2.3</v>
@@ -4384,16 +4384,16 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="O25">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="P25">
-        <v>5.35</v>
+        <v>5.1</v>
       </c>
       <c r="Q25">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="R25">
         <v>2.5</v>
@@ -4402,7 +4402,7 @@
         <v>1.25</v>
       </c>
       <c r="T25">
-        <v>3.28</v>
+        <v>3.55</v>
       </c>
       <c r="U25">
         <v>2.29</v>
@@ -4411,10 +4411,10 @@
         <v>1.6</v>
       </c>
       <c r="W25">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X25">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
         <v>1.13</v>
@@ -4429,7 +4429,7 @@
         <v>2.29</v>
       </c>
       <c r="AC25">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AD25">
         <v>1.58</v>
@@ -4438,10 +4438,10 @@
         <v>1.23</v>
       </c>
       <c r="AF25">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG25">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="O27">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="P27">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="Q27">
         <v>1.96</v>
@@ -4725,10 +4725,10 @@
         <v>2.7</v>
       </c>
       <c r="S27">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T27">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="U27">
         <v>1.98</v>
@@ -4767,7 +4767,7 @@
         <v>1.44</v>
       </c>
       <c r="AG27">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK27">
         <v>2.45</v>
@@ -4876,22 +4876,22 @@
         <v>1.48</v>
       </c>
       <c r="O28">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P28">
         <v>5.6</v>
       </c>
       <c r="Q28">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="R28">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="S28">
         <v>1.28</v>
       </c>
       <c r="T28">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="U28">
         <v>2.4</v>
@@ -4903,25 +4903,25 @@
         <v>1.12</v>
       </c>
       <c r="X28">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
         <v>1.15</v>
       </c>
       <c r="Z28">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="AA28">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AB28">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AC28">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="AD28">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AE28">
         <v>1.17</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK28">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,19 +5036,19 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="O29">
         <v>3.75</v>
       </c>
       <c r="P29">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="Q29">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="R29">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S29">
         <v>1.36</v>
@@ -5057,10 +5057,10 @@
         <v>2.97</v>
       </c>
       <c r="U29">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="V29">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W29">
         <v>1.07</v>
@@ -5069,16 +5069,16 @@
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z29">
-        <v>3.51</v>
+        <v>3.3</v>
       </c>
       <c r="AA29">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AB29">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AC29">
         <v>3.08</v>
@@ -5087,13 +5087,13 @@
         <v>1.28</v>
       </c>
       <c r="AE29">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF29">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG29">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5199,40 +5199,40 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O30">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="P30">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="Q30">
         <v>2.61</v>
       </c>
       <c r="R30">
-        <v>2.22</v>
+        <v>2.46</v>
       </c>
       <c r="S30">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T30">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="U30">
         <v>2.35</v>
       </c>
       <c r="V30">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W30">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z30">
         <v>4</v>
@@ -5241,7 +5241,7 @@
         <v>1.64</v>
       </c>
       <c r="AB30">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="AC30">
         <v>2.38</v>
@@ -5250,7 +5250,7 @@
         <v>1.47</v>
       </c>
       <c r="AE30">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF30">
         <v>1.55</v>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="N31">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="O31">
         <v>5.25</v>
@@ -5371,10 +5371,10 @@
         <v>1.37</v>
       </c>
       <c r="Q31">
-        <v>4.73</v>
+        <v>6.5</v>
       </c>
       <c r="R31">
-        <v>2.43</v>
+        <v>2.57</v>
       </c>
       <c r="S31">
         <v>1.21</v>
@@ -5383,13 +5383,13 @@
         <v>3.75</v>
       </c>
       <c r="U31">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="V31">
         <v>1.7</v>
       </c>
       <c r="W31">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X31">
         <v>1.02</v>
@@ -5398,19 +5398,19 @@
         <v>1.08</v>
       </c>
       <c r="Z31">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="AA31">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AB31">
-        <v>2.82</v>
+        <v>2.63</v>
       </c>
       <c r="AC31">
         <v>2.1</v>
       </c>
       <c r="AD31">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AE31">
         <v>1.3</v>
@@ -5419,7 +5419,7 @@
         <v>1.65</v>
       </c>
       <c r="AG31">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.13</v>
+        <v>2.74</v>
       </c>
       <c r="AK31">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="O33">
-        <v>4.5</v>
+        <v>4.58</v>
       </c>
       <c r="P33">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="Q33">
         <v>5.2</v>
@@ -5730,13 +5730,13 @@
         <v>1.41</v>
       </c>
       <c r="AB33">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AC33">
         <v>2.16</v>
       </c>
       <c r="AD33">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AE33">
         <v>1.28</v>
@@ -5745,7 +5745,7 @@
         <v>1.53</v>
       </c>
       <c r="AG33">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5851,25 +5851,25 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="O34">
         <v>3.5</v>
       </c>
       <c r="P34">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="Q34">
         <v>2.8</v>
       </c>
       <c r="R34">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="S34">
         <v>1.35</v>
       </c>
       <c r="T34">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="U34">
         <v>2.45</v>
@@ -5887,7 +5887,7 @@
         <v>1.2</v>
       </c>
       <c r="Z34">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AA34">
         <v>1.73</v>
@@ -5896,10 +5896,10 @@
         <v>2</v>
       </c>
       <c r="AC34">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="AD34">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE34">
         <v>1.14</v>
@@ -5908,7 +5908,7 @@
         <v>1.62</v>
       </c>
       <c r="AG34">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>3.3</v>
       </c>
       <c r="P35">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6047,25 +6047,25 @@
         <v>0</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF35">
         <v>0</v>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="O36">
         <v>3.8</v>
@@ -6192,10 +6192,10 @@
         <v>2.34</v>
       </c>
       <c r="S36">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T36">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="U36">
         <v>2.65</v>
@@ -6222,7 +6222,7 @@
         <v>1.88</v>
       </c>
       <c r="AC36">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="AD36">
         <v>1.33</v>
@@ -6503,16 +6503,16 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="O38">
         <v>3.2</v>
       </c>
       <c r="P38">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="Q38">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="R38">
         <v>2.03</v>
@@ -6527,13 +6527,13 @@
         <v>2.84</v>
       </c>
       <c r="V38">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="W38">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y38">
         <v>1.24</v>
@@ -6548,16 +6548,16 @@
         <v>1.86</v>
       </c>
       <c r="AC38">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="AD38">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AE38">
         <v>1.06</v>
       </c>
       <c r="AF38">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AG38">
         <v>2.05</v>
@@ -6669,61 +6669,61 @@
         <v>1.22</v>
       </c>
       <c r="O39">
-        <v>6.2</v>
+        <v>5.75</v>
       </c>
       <c r="P39">
-        <v>11.6</v>
+        <v>8</v>
       </c>
       <c r="Q39">
         <v>1.57</v>
       </c>
       <c r="R39">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="S39">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T39">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="U39">
         <v>2.1</v>
       </c>
       <c r="V39">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="W39">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X39">
         <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z39">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AA39">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AB39">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AC39">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="AD39">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AE39">
         <v>1.25</v>
       </c>
       <c r="AF39">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AG39">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AK39">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6835,13 +6835,13 @@
         <v>3.58</v>
       </c>
       <c r="P40">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="Q40">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="R40">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="S40">
         <v>1.25</v>
@@ -6859,7 +6859,7 @@
         <v>1.12</v>
       </c>
       <c r="X40">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y40">
         <v>1.18</v>
@@ -6874,10 +6874,10 @@
         <v>2.21</v>
       </c>
       <c r="AC40">
-        <v>2.47</v>
+        <v>2.33</v>
       </c>
       <c r="AD40">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AE40">
         <v>1.19</v>
@@ -6902,7 +6902,7 @@
         <v>1.25</v>
       </c>
       <c r="AK40">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7001,10 +7001,10 @@
         <v>2</v>
       </c>
       <c r="Q41">
-        <v>3.58</v>
+        <v>3.35</v>
       </c>
       <c r="R41">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S41">
         <v>1.29</v>
@@ -7016,10 +7016,10 @@
         <v>2.3</v>
       </c>
       <c r="V41">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W41">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X41">
         <v>1.02</v>
@@ -7028,28 +7028,28 @@
         <v>1.17</v>
       </c>
       <c r="Z41">
-        <v>3.9</v>
+        <v>3.98</v>
       </c>
       <c r="AA41">
         <v>1.63</v>
       </c>
       <c r="AB41">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC41">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="AD41">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AE41">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF41">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG41">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>1.22</v>
       </c>
       <c r="AK41">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,19 +7155,19 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.64</v>
+        <v>3.1</v>
       </c>
       <c r="O42">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P42">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="Q42">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="R42">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="S42">
         <v>1.29</v>
@@ -7176,13 +7176,13 @@
         <v>3.25</v>
       </c>
       <c r="U42">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="V42">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W42">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X42">
         <v>1.02</v>
@@ -7191,28 +7191,28 @@
         <v>1.17</v>
       </c>
       <c r="Z42">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AA42">
         <v>1.62</v>
       </c>
       <c r="AB42">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC42">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="AD42">
         <v>1.44</v>
       </c>
       <c r="AE42">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF42">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG42">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7339,10 +7339,10 @@
         <v>3</v>
       </c>
       <c r="U43">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="V43">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W43">
         <v>1.08</v>
@@ -7351,16 +7351,16 @@
         <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z43">
         <v>3.1</v>
       </c>
       <c r="AA43">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AB43">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="AC43">
         <v>3.3</v>
@@ -7372,10 +7372,10 @@
         <v>1.06</v>
       </c>
       <c r="AF43">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="AG43">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7481,19 +7481,19 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="Q44">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="R44">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S44">
         <v>1.3</v>
@@ -7502,10 +7502,10 @@
         <v>3.2</v>
       </c>
       <c r="U44">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="V44">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W44">
         <v>1.1</v>
@@ -7517,28 +7517,28 @@
         <v>1.23</v>
       </c>
       <c r="Z44">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="AA44">
-        <v>1.63</v>
+        <v>1.81</v>
       </c>
       <c r="AB44">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="AC44">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="AD44">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AE44">
         <v>1.13</v>
       </c>
       <c r="AF44">
-        <v>1.76</v>
+        <v>1.54</v>
       </c>
       <c r="AG44">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -8145,13 +8145,13 @@
         <v>3.16</v>
       </c>
       <c r="R48">
-        <v>1.92</v>
+        <v>2.09</v>
       </c>
       <c r="S48">
         <v>1.44</v>
       </c>
       <c r="T48">
-        <v>2.69</v>
+        <v>2.47</v>
       </c>
       <c r="U48">
         <v>3.16</v>
@@ -8166,19 +8166,19 @@
         <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="Z48">
         <v>2.83</v>
       </c>
       <c r="AA48">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AB48">
         <v>1.65</v>
       </c>
       <c r="AC48">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="AD48">
         <v>1.18</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="O50">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="P50">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="Q50">
         <v>1.57</v>
@@ -8507,7 +8507,7 @@
         <v>2.22</v>
       </c>
       <c r="AD50">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AE50">
         <v>1.24</v>
@@ -8625,10 +8625,10 @@
         <v>1.74</v>
       </c>
       <c r="O51">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P51">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="Q51">
         <v>2.3</v>
@@ -8640,28 +8640,28 @@
         <v>1.3</v>
       </c>
       <c r="T51">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="U51">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V51">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W51">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X51">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z51">
         <v>4.2</v>
       </c>
       <c r="AA51">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AB51">
         <v>2.1</v>
@@ -8676,7 +8676,7 @@
         <v>1.14</v>
       </c>
       <c r="AF51">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG51">
         <v>2.1</v>
@@ -8785,19 +8785,19 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="O52">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="P52">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q52">
         <v>2.15</v>
       </c>
       <c r="R52">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="S52">
         <v>1.32</v>
@@ -8806,7 +8806,7 @@
         <v>3.25</v>
       </c>
       <c r="U52">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="V52">
         <v>1.48</v>
@@ -8821,7 +8821,7 @@
         <v>1.19</v>
       </c>
       <c r="Z52">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AA52">
         <v>1.72</v>
@@ -8836,13 +8836,13 @@
         <v>1.4</v>
       </c>
       <c r="AE52">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF52">
         <v>1.72</v>
       </c>
       <c r="AG52">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK52">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9111,16 +9111,16 @@
         </is>
       </c>
       <c r="N54">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O54">
         <v>3.3</v>
       </c>
       <c r="P54">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="Q54">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="R54">
         <v>2.33</v>
@@ -9150,7 +9150,7 @@
         <v>3.94</v>
       </c>
       <c r="AA54">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB54">
         <v>2.05</v>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AK54">
         <v>1.67</v>
@@ -9283,7 +9283,7 @@
         <v>0</v>
       </c>
       <c r="Q55">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="R55">
         <v>2.07</v>
@@ -9298,31 +9298,31 @@
         <v>2.8</v>
       </c>
       <c r="V55">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="W55">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X55">
         <v>1.02</v>
       </c>
       <c r="Y55">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="Z55">
         <v>3</v>
       </c>
       <c r="AA55">
-        <v>1.78</v>
+        <v>2.06</v>
       </c>
       <c r="AB55">
-        <v>1.92</v>
+        <v>1.73</v>
       </c>
       <c r="AC55">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="AD55">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AE55">
         <v>1.05</v>
@@ -9344,7 +9344,7 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AK55">
         <v>1.88</v>
@@ -9452,7 +9452,7 @@
         <v>1.83</v>
       </c>
       <c r="S56">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="T56">
         <v>2.4</v>
@@ -9461,7 +9461,7 @@
         <v>3.6</v>
       </c>
       <c r="V56">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W56">
         <v>1.04</v>
@@ -9470,31 +9470,31 @@
         <v>1.13</v>
       </c>
       <c r="Y56">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="Z56">
-        <v>2.7</v>
+        <v>2.42</v>
       </c>
       <c r="AA56">
-        <v>2.73</v>
+        <v>2.52</v>
       </c>
       <c r="AB56">
         <v>1.4</v>
       </c>
       <c r="AC56">
-        <v>4.95</v>
+        <v>5.2</v>
       </c>
       <c r="AD56">
         <v>1.13</v>
       </c>
       <c r="AE56">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF56">
         <v>2.2</v>
       </c>
       <c r="AG56">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O57">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P57">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="O58">
         <v>3.6</v>
       </c>
       <c r="P58">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -9802,10 +9802,10 @@
         <v>0</v>
       </c>
       <c r="AA58">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB58">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC58">
         <v>0</v>
@@ -9929,10 +9929,10 @@
         <v>1.88</v>
       </c>
       <c r="O59">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="P59">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="Q59">
         <v>2.3</v>
@@ -9941,16 +9941,16 @@
         <v>2.42</v>
       </c>
       <c r="S59">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T59">
         <v>4</v>
       </c>
       <c r="U59">
-        <v>2.13</v>
+        <v>1.95</v>
       </c>
       <c r="V59">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="W59">
         <v>1.17</v>
@@ -9965,10 +9965,10 @@
         <v>5.4</v>
       </c>
       <c r="AA59">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB59">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AC59">
         <v>2.09</v>
@@ -9977,7 +9977,7 @@
         <v>1.75</v>
       </c>
       <c r="AE59">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AF59">
         <v>1.4</v>
@@ -9999,7 +9999,7 @@
         <v>1.3</v>
       </c>
       <c r="AK59">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="O60">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="P60">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Q60">
         <v>1.9</v>
@@ -10104,10 +10104,10 @@
         <v>2.54</v>
       </c>
       <c r="S60">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T60">
-        <v>3.64</v>
+        <v>4</v>
       </c>
       <c r="U60">
         <v>2.1</v>
@@ -10125,13 +10125,13 @@
         <v>1.1</v>
       </c>
       <c r="Z60">
-        <v>5.05</v>
+        <v>5.5</v>
       </c>
       <c r="AA60">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AB60">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="AC60">
         <v>2.19</v>
@@ -10143,7 +10143,7 @@
         <v>1.24</v>
       </c>
       <c r="AF60">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG60">
         <v>2.18</v>
@@ -10276,10 +10276,10 @@
         <v>2.07</v>
       </c>
       <c r="V61">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W61">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="X61">
         <v>1.02</v>
@@ -10288,22 +10288,22 @@
         <v>1.12</v>
       </c>
       <c r="Z61">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA61">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AB61">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AC61">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AD61">
         <v>1.76</v>
       </c>
       <c r="AE61">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF61">
         <v>1.37</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="O62">
-        <v>3.44</v>
+        <v>3.07</v>
       </c>
       <c r="P62">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10593,10 +10593,10 @@
         <v>1.84</v>
       </c>
       <c r="S63">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="T63">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="U63">
         <v>3.25</v>
@@ -10629,13 +10629,13 @@
         <v>1.17</v>
       </c>
       <c r="AE63">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF63">
         <v>2.05</v>
       </c>
       <c r="AG63">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AK63">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10747,7 +10747,7 @@
         <v>3.6</v>
       </c>
       <c r="P64">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q64">
         <v>3.1</v>
@@ -10762,16 +10762,16 @@
         <v>2.8</v>
       </c>
       <c r="U64">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="V64">
         <v>1.63</v>
       </c>
       <c r="W64">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X64">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y64">
         <v>1.11</v>
@@ -10780,13 +10780,13 @@
         <v>4.95</v>
       </c>
       <c r="AA64">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AB64">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AC64">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AD64">
         <v>1.47</v>
@@ -10795,10 +10795,10 @@
         <v>1.25</v>
       </c>
       <c r="AF64">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AG64">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.5</v>
+        <v>1.23</v>
       </c>
       <c r="AK64">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10904,16 +10904,16 @@
         </is>
       </c>
       <c r="N65">
-        <v>4.5</v>
+        <v>4.97</v>
       </c>
       <c r="O65">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P65">
         <v>1.59</v>
       </c>
       <c r="Q65">
-        <v>5.15</v>
+        <v>5.47</v>
       </c>
       <c r="R65">
         <v>2.3</v>
@@ -10922,7 +10922,7 @@
         <v>1.33</v>
       </c>
       <c r="T65">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="U65">
         <v>2.47</v>
@@ -10934,7 +10934,7 @@
         <v>1.12</v>
       </c>
       <c r="X65">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y65">
         <v>1.22</v>
@@ -10949,13 +10949,13 @@
         <v>2.1</v>
       </c>
       <c r="AC65">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="AD65">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE65">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF65">
         <v>1.73</v>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="AK65">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="O66">
         <v>3.51</v>
       </c>
       <c r="P66">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="Q66">
         <v>2.9</v>
@@ -11088,7 +11088,7 @@
         <v>3.6</v>
       </c>
       <c r="U66">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V66">
         <v>1.47</v>
@@ -11106,7 +11106,7 @@
         <v>4.05</v>
       </c>
       <c r="AA66">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AB66">
         <v>2.15</v>
@@ -11115,7 +11115,7 @@
         <v>2.75</v>
       </c>
       <c r="AD66">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AE66">
         <v>1.13</v>
@@ -11233,13 +11233,13 @@
         <v>3</v>
       </c>
       <c r="O67">
-        <v>3.78</v>
+        <v>3.65</v>
       </c>
       <c r="P67">
         <v>2.15</v>
       </c>
       <c r="Q67">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R67">
         <v>2.5</v>
@@ -11248,7 +11248,7 @@
         <v>1.22</v>
       </c>
       <c r="T67">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="U67">
         <v>2.05</v>
@@ -11257,28 +11257,28 @@
         <v>1.7</v>
       </c>
       <c r="W67">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X67">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y67">
         <v>1.15</v>
       </c>
       <c r="Z67">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AA67">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB67">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="AC67">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AD67">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AE67">
         <v>1.25</v>
@@ -11287,7 +11287,7 @@
         <v>1.4</v>
       </c>
       <c r="AG67">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11396,7 +11396,7 @@
         <v>2.38</v>
       </c>
       <c r="O68">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="P68">
         <v>2.55</v>
@@ -11426,7 +11426,7 @@
         <v>1.03</v>
       </c>
       <c r="Y68">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Z68">
         <v>4.65</v>
@@ -11444,7 +11444,7 @@
         <v>1.5</v>
       </c>
       <c r="AE68">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF68">
         <v>1.45</v>
@@ -12045,16 +12045,16 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="O72">
         <v>3.7</v>
       </c>
       <c r="P72">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="Q72">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="R72">
         <v>2.3</v>
@@ -12063,19 +12063,19 @@
         <v>1.3</v>
       </c>
       <c r="T72">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="U72">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="V72">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W72">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X72">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y72">
         <v>1.26</v>
@@ -12084,19 +12084,19 @@
         <v>3.68</v>
       </c>
       <c r="AA72">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AB72">
         <v>1.93</v>
       </c>
       <c r="AC72">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="AD72">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE72">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF72">
         <v>1.8</v>
@@ -12208,7 +12208,7 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="O73">
         <v>3.62</v>
@@ -12220,13 +12220,13 @@
         <v>2.58</v>
       </c>
       <c r="R73">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="S73">
         <v>1.25</v>
       </c>
       <c r="T73">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="U73">
         <v>2.25</v>
@@ -12235,16 +12235,16 @@
         <v>1.6</v>
       </c>
       <c r="W73">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X73">
         <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z73">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="AA73">
         <v>1.45</v>
@@ -12259,13 +12259,13 @@
         <v>1.49</v>
       </c>
       <c r="AE73">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF73">
         <v>1.44</v>
       </c>
       <c r="AG73">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="O74">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="P74">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="Q74">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="R74">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="S74">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="T74">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="U74">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="V74">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="W74">
+        <v>1.25</v>
+      </c>
+      <c r="X74">
+        <v>0</v>
+      </c>
+      <c r="Y74">
+        <v>1.06</v>
+      </c>
+      <c r="Z74">
+        <v>7.5</v>
+      </c>
+      <c r="AA74">
         <v>1.29</v>
       </c>
-      <c r="X74">
-        <v>0</v>
-      </c>
-      <c r="Y74">
-        <v>1.05</v>
-      </c>
-      <c r="Z74">
-        <v>8.5</v>
-      </c>
-      <c r="AA74">
-        <v>1.22</v>
-      </c>
       <c r="AB74">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="AC74">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AD74">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AE74">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AF74">
         <v>1.64</v>
       </c>
       <c r="AG74">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AK74">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
       <c r="O75">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P75">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="Q75">
         <v>3.3</v>
@@ -12567,7 +12567,7 @@
         <v>1.04</v>
       </c>
       <c r="Y75">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z75">
         <v>3.25</v>
@@ -12579,13 +12579,13 @@
         <v>1.78</v>
       </c>
       <c r="AC75">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD75">
         <v>1.25</v>
       </c>
       <c r="AE75">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF75">
         <v>1.75</v>
@@ -12607,7 +12607,7 @@
         <v>1.53</v>
       </c>
       <c r="AK75">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12697,19 +12697,19 @@
         </is>
       </c>
       <c r="N76">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="O76">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="P76">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q76">
         <v>4.16</v>
       </c>
       <c r="R76">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S76">
         <v>1.25</v>
@@ -12718,25 +12718,25 @@
         <v>3.45</v>
       </c>
       <c r="U76">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="V76">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="W76">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X76">
         <v>1.03</v>
       </c>
       <c r="Y76">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z76">
-        <v>4.64</v>
+        <v>4.5</v>
       </c>
       <c r="AA76">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB76">
         <v>2.29</v>
@@ -12748,7 +12748,7 @@
         <v>1.44</v>
       </c>
       <c r="AE76">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF76">
         <v>1.53</v>
@@ -12860,10 +12860,10 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="O77">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="P77">
         <v>5.39</v>
@@ -13032,7 +13032,7 @@
         <v>2.35</v>
       </c>
       <c r="Q78">
-        <v>2.98</v>
+        <v>2.63</v>
       </c>
       <c r="R78">
         <v>2.5</v>
@@ -13041,10 +13041,10 @@
         <v>1.2</v>
       </c>
       <c r="T78">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="U78">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="V78">
         <v>1.76</v>
@@ -13059,10 +13059,10 @@
         <v>1.08</v>
       </c>
       <c r="Z78">
-        <v>7</v>
+        <v>5.3</v>
       </c>
       <c r="AA78">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AB78">
         <v>2.85</v>
@@ -13071,7 +13071,7 @@
         <v>1.96</v>
       </c>
       <c r="AD78">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AE78">
         <v>1.3</v>
@@ -13080,7 +13080,7 @@
         <v>1.3</v>
       </c>
       <c r="AG78">
-        <v>2.99</v>
+        <v>2.75</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.2</v>
+        <v>1.47</v>
       </c>
       <c r="AK78">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13186,16 +13186,16 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="O79">
-        <v>3.55</v>
+        <v>3.48</v>
       </c>
       <c r="P79">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q79">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="R79">
         <v>2.5</v>
@@ -13204,13 +13204,13 @@
         <v>1.25</v>
       </c>
       <c r="T79">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="U79">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="V79">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W79">
         <v>1.12</v>
@@ -13219,31 +13219,31 @@
         <v>1.03</v>
       </c>
       <c r="Y79">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z79">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AA79">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB79">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AC79">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AD79">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AE79">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF79">
         <v>1.51</v>
       </c>
       <c r="AG79">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK79">
         <v>1.85</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,31 +13349,31 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.3</v>
+        <v>4.45</v>
       </c>
       <c r="O80">
-        <v>3.95</v>
+        <v>4.85</v>
       </c>
       <c r="P80">
-        <v>2.25</v>
+        <v>1.45</v>
       </c>
       <c r="Q80">
-        <v>2.63</v>
+        <v>5.25</v>
       </c>
       <c r="R80">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="S80">
         <v>1.14</v>
       </c>
       <c r="T80">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="U80">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="V80">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="W80">
         <v>1.25</v>
@@ -13382,31 +13382,31 @@
         <v>1.01</v>
       </c>
       <c r="Y80">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z80">
-        <v>6.39</v>
+        <v>7</v>
       </c>
       <c r="AA80">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AB80">
-        <v>3.39</v>
+        <v>3.28</v>
       </c>
       <c r="AC80">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AD80">
         <v>2.06</v>
       </c>
       <c r="AE80">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AF80">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AG80">
-        <v>3.42</v>
+        <v>2.8</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.17</v>
+        <v>2.52</v>
       </c>
       <c r="AK80">
-        <v>1.5</v>
+        <v>1.13</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>4.7</v>
+        <v>1.25</v>
       </c>
       <c r="O81">
-        <v>4.7</v>
+        <v>5.05</v>
       </c>
       <c r="P81">
-        <v>1.45</v>
+        <v>5.6</v>
       </c>
       <c r="Q81">
-        <v>4.13</v>
+        <v>1.68</v>
       </c>
       <c r="R81">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="S81">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="T81">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="U81">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="V81">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="W81">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X81">
         <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Z81">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AA81">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AB81">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AC81">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AD81">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="AE81">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="AF81">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AG81">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>2.52</v>
+        <v>1.08</v>
       </c>
       <c r="AK81">
-        <v>1.13</v>
+        <v>3.18</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="O82">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="P82">
-        <v>5.6</v>
+        <v>5.35</v>
       </c>
       <c r="Q82">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="R82">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="S82">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="T82">
-        <v>5.25</v>
+        <v>4.65</v>
       </c>
       <c r="U82">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="V82">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="W82">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="X82">
         <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z82">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="AA82">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AB82">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AC82">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AD82">
-        <v>2.21</v>
+        <v>2.02</v>
       </c>
       <c r="AE82">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AF82">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG82">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AK82">
-        <v>3.18</v>
+        <v>2.56</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,31 +13838,31 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.42</v>
+        <v>2.13</v>
       </c>
       <c r="O83">
-        <v>4.55</v>
+        <v>3.75</v>
       </c>
       <c r="P83">
-        <v>5.35</v>
+        <v>2.41</v>
       </c>
       <c r="Q83">
+        <v>2.76</v>
+      </c>
+      <c r="R83">
+        <v>2.7</v>
+      </c>
+      <c r="S83">
+        <v>1.17</v>
+      </c>
+      <c r="T83">
+        <v>4.4</v>
+      </c>
+      <c r="U83">
         <v>1.85</v>
       </c>
-      <c r="R83">
-        <v>2.77</v>
-      </c>
-      <c r="S83">
-        <v>1.15</v>
-      </c>
-      <c r="T83">
-        <v>4.65</v>
-      </c>
-      <c r="U83">
-        <v>1.79</v>
-      </c>
       <c r="V83">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="W83">
         <v>1.25</v>
@@ -13871,31 +13871,31 @@
         <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Z83">
-        <v>7.3</v>
+        <v>6.39</v>
       </c>
       <c r="AA83">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AB83">
-        <v>3.6</v>
+        <v>3.39</v>
       </c>
       <c r="AC83">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AD83">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="AE83">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AF83">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AG83">
-        <v>2.77</v>
+        <v>3.42</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AK83">
-        <v>2.56</v>
+        <v>1.5</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14037,7 +14037,7 @@
         <v>1.37</v>
       </c>
       <c r="Z84">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AA84">
         <v>2.11</v>
@@ -14049,13 +14049,13 @@
         <v>3.6</v>
       </c>
       <c r="AD84">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AE84">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF84">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AG84">
         <v>1.67</v>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.29</v>
+        <v>1.69</v>
       </c>
       <c r="AK84">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14164,25 +14164,25 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="O85">
         <v>3.35</v>
       </c>
       <c r="P85">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="Q85">
         <v>2.38</v>
       </c>
       <c r="R85">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="S85">
         <v>1.32</v>
       </c>
       <c r="T85">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="U85">
         <v>2.5</v>
@@ -14206,7 +14206,7 @@
         <v>1.77</v>
       </c>
       <c r="AB85">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC85">
         <v>2.91</v>
@@ -14234,7 +14234,7 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK85">
         <v>1.8</v>
@@ -14330,7 +14330,7 @@
         <v>1.71</v>
       </c>
       <c r="O86">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P86">
         <v>5</v>
@@ -14339,7 +14339,7 @@
         <v>2.3</v>
       </c>
       <c r="R86">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="S86">
         <v>1.46</v>
@@ -14375,7 +14375,7 @@
         <v>4.05</v>
       </c>
       <c r="AD86">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AE86">
         <v>1.02</v>
@@ -14384,7 +14384,7 @@
         <v>2.1</v>
       </c>
       <c r="AG86">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>1.27</v>
       </c>
       <c r="AK86">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14493,16 +14493,16 @@
         <v>2.29</v>
       </c>
       <c r="O87">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P87">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="Q87">
         <v>2.95</v>
       </c>
       <c r="R87">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="S87">
         <v>1.3</v>
@@ -14514,7 +14514,7 @@
         <v>2.5</v>
       </c>
       <c r="V87">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W87">
         <v>1.09</v>
@@ -14535,7 +14535,7 @@
         <v>2.02</v>
       </c>
       <c r="AC87">
-        <v>2.79</v>
+        <v>2.69</v>
       </c>
       <c r="AD87">
         <v>1.36</v>
@@ -14563,7 +14563,7 @@
         <v>1.38</v>
       </c>
       <c r="AK87">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14816,7 +14816,7 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="O89">
         <v>4.2</v>
@@ -14828,43 +14828,43 @@
         <v>2.05</v>
       </c>
       <c r="R89">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="S89">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T89">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U89">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="V89">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="W89">
         <v>1.13</v>
       </c>
       <c r="X89">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y89">
         <v>1.2</v>
       </c>
       <c r="Z89">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA89">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB89">
         <v>2.15</v>
       </c>
       <c r="AC89">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AD89">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AE89">
         <v>1.14</v>
@@ -14889,7 +14889,7 @@
         <v>1.17</v>
       </c>
       <c r="AK89">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14985,28 +14985,28 @@
         <v>3.35</v>
       </c>
       <c r="P90">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="Q90">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="R90">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S90">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T90">
-        <v>2.96</v>
+        <v>3.19</v>
       </c>
       <c r="U90">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="V90">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="W90">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X90">
         <v>1.05</v>
@@ -15033,10 +15033,10 @@
         <v>1.13</v>
       </c>
       <c r="AF90">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG90">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK90">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15145,10 +15145,10 @@
         <v>2.74</v>
       </c>
       <c r="O91">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="P91">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="Q91">
         <v>3.3</v>
@@ -15178,16 +15178,16 @@
         <v>1.39</v>
       </c>
       <c r="Z91">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AA91">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AB91">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AC91">
-        <v>4.09</v>
+        <v>4.2</v>
       </c>
       <c r="AD91">
         <v>1.16</v>
@@ -15196,7 +15196,7 @@
         <v>1.03</v>
       </c>
       <c r="AF91">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AG91">
         <v>1.8</v>
@@ -15215,7 +15215,7 @@
         <v>1.28</v>
       </c>
       <c r="AK91">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK96">
         <v>1.52</v>
@@ -16488,7 +16488,7 @@
         <v>2.25</v>
       </c>
       <c r="AB99">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AC99">
         <v>4.05</v>
@@ -16516,7 +16516,7 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AK99">
         <v>1.67</v>
@@ -16772,7 +16772,7 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.55</v>
+        <v>2.39</v>
       </c>
       <c r="O101">
         <v>2.85</v>
@@ -16811,13 +16811,13 @@
         <v>2.41</v>
       </c>
       <c r="AA101">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="AB101">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AC101">
-        <v>4.55</v>
+        <v>4.84</v>
       </c>
       <c r="AD101">
         <v>1.16</v>
@@ -16935,61 +16935,61 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="O102">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="P102">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Q102">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="R102">
-        <v>2.79</v>
+        <v>3.33</v>
       </c>
       <c r="S102">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="T102">
-        <v>3.98</v>
+        <v>5.5</v>
       </c>
       <c r="U102">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="V102">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="W102">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="X102">
         <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Z102">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="AA102">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AB102">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AC102">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="AD102">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="AE102">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AF102">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AG102">
         <v>2.1</v>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK102">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17442,19 +17442,19 @@
         <v>1.3</v>
       </c>
       <c r="T105">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="U105">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="V105">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W105">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X105">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y105">
         <v>1.2</v>
@@ -17463,19 +17463,19 @@
         <v>3.7</v>
       </c>
       <c r="AA105">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AB105">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AC105">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AD105">
         <v>1.34</v>
       </c>
       <c r="AE105">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF105">
         <v>1.73</v>
@@ -17587,25 +17587,25 @@
         </is>
       </c>
       <c r="N106">
-        <v>4.2</v>
+        <v>3.79</v>
       </c>
       <c r="O106">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P106">
-        <v>1.99</v>
+        <v>1.7</v>
       </c>
       <c r="Q106">
-        <v>5.24</v>
+        <v>5.07</v>
       </c>
       <c r="R106">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="S106">
         <v>1.4</v>
       </c>
       <c r="T106">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="U106">
         <v>2.73</v>
@@ -17638,7 +17638,7 @@
         <v>1.25</v>
       </c>
       <c r="AE106">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF106">
         <v>1.85</v>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.95</v>
+        <v>1.21</v>
       </c>
       <c r="AK106">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -18091,10 +18091,10 @@
         <v>2.15</v>
       </c>
       <c r="S109">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T109">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="U109">
         <v>2.8</v>
@@ -18118,7 +18118,7 @@
         <v>1.95</v>
       </c>
       <c r="AB109">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC109">
         <v>3.64</v>
@@ -18127,13 +18127,13 @@
         <v>1.27</v>
       </c>
       <c r="AE109">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF109">
         <v>1.8</v>
       </c>
       <c r="AG109">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>1.22</v>
       </c>
       <c r="AK109">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18402,7 +18402,7 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="O111">
         <v>3.1</v>
@@ -18417,22 +18417,22 @@
         <v>2.1</v>
       </c>
       <c r="S111">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T111">
-        <v>2.95</v>
+        <v>2.73</v>
       </c>
       <c r="U111">
         <v>2.7</v>
       </c>
       <c r="V111">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W111">
         <v>1.1</v>
       </c>
       <c r="X111">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y111">
         <v>1.28</v>
@@ -18444,7 +18444,7 @@
         <v>1.82</v>
       </c>
       <c r="AB111">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AC111">
         <v>3.2</v>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AK111">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18731,10 +18731,10 @@
         <v>3.49</v>
       </c>
       <c r="O113">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P113">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q113">
         <v>4.16</v>
@@ -18743,7 +18743,7 @@
         <v>2.17</v>
       </c>
       <c r="S113">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T113">
         <v>2.9</v>
@@ -18782,10 +18782,10 @@
         <v>1.11</v>
       </c>
       <c r="AF113">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG113">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18930,10 +18930,10 @@
         <v>4.1</v>
       </c>
       <c r="AA114">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AB114">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AC114">
         <v>2.65</v>
@@ -18948,7 +18948,7 @@
         <v>1.58</v>
       </c>
       <c r="AG114">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="O115">
-        <v>6.75</v>
+        <v>6</v>
       </c>
       <c r="P115">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="Q115">
         <v>1.55</v>
@@ -19072,7 +19072,7 @@
         <v>1.23</v>
       </c>
       <c r="T115">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="U115">
         <v>2.29</v>
@@ -19093,7 +19093,7 @@
         <v>4.8</v>
       </c>
       <c r="AA115">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AB115">
         <v>2.35</v>
@@ -19108,7 +19108,7 @@
         <v>1.18</v>
       </c>
       <c r="AF115">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="AG115">
         <v>1.57</v>
@@ -19127,7 +19127,7 @@
         <v>1.02</v>
       </c>
       <c r="AK115">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>4.78</v>
+        <v>4.84</v>
       </c>
       <c r="O116">
-        <v>3.64</v>
+        <v>3.95</v>
       </c>
       <c r="P116">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="Q116">
         <v>4.2</v>
@@ -19232,7 +19232,7 @@
         <v>2.4</v>
       </c>
       <c r="S116">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T116">
         <v>3.55</v>
@@ -19247,16 +19247,16 @@
         <v>1.11</v>
       </c>
       <c r="X116">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y116">
         <v>1.12</v>
       </c>
       <c r="Z116">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AA116">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AB116">
         <v>2.18</v>
@@ -19268,7 +19268,7 @@
         <v>1.53</v>
       </c>
       <c r="AE116">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AF116">
         <v>1.55</v>
@@ -19290,7 +19290,7 @@
         <v>1.25</v>
       </c>
       <c r="AK116">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19543,37 +19543,37 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="O118">
+        <v>2.64</v>
+      </c>
+      <c r="P118">
         <v>2.8</v>
       </c>
-      <c r="P118">
-        <v>2.9</v>
-      </c>
       <c r="Q118">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="R118">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="S118">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="T118">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="U118">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="V118">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="W118">
         <v>1.02</v>
       </c>
       <c r="X118">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Y118">
         <v>1.74</v>
@@ -19582,25 +19582,25 @@
         <v>2.02</v>
       </c>
       <c r="AA118">
-        <v>3.28</v>
+        <v>3.41</v>
       </c>
       <c r="AB118">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AC118">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="AD118">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AE118">
         <v>1.02</v>
       </c>
       <c r="AF118">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="AG118">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19709,7 +19709,7 @@
         <v>2</v>
       </c>
       <c r="O119">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P119">
         <v>2.87</v>
@@ -19739,31 +19739,31 @@
         <v>1.02</v>
       </c>
       <c r="Y119">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z119">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="AA119">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AB119">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AC119">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="AD119">
         <v>1.71</v>
       </c>
       <c r="AE119">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF119">
         <v>1.39</v>
       </c>
       <c r="AG119">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19869,19 +19869,19 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="O120">
         <v>3.35</v>
       </c>
       <c r="P120">
-        <v>3.48</v>
+        <v>3.8</v>
       </c>
       <c r="Q120">
         <v>2.55</v>
       </c>
       <c r="R120">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="S120">
         <v>1.47</v>
@@ -19911,7 +19911,7 @@
         <v>2.26</v>
       </c>
       <c r="AB120">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AC120">
         <v>3.68</v>
@@ -20041,55 +20041,55 @@
         <v>1.83</v>
       </c>
       <c r="Q121">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="R121">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S121">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T121">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U121">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="V121">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W121">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X121">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y121">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z121">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA121">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB121">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC121">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD121">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE121">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF121">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG121">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AK121">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="O122">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="P122">
-        <v>6.11</v>
+        <v>5.75</v>
       </c>
       <c r="Q122">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="R122">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S122">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T122">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U122">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V122">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W122">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X122">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y122">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z122">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA122">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AB122">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AC122">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD122">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE122">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF122">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG122">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK122">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20367,49 +20367,49 @@
         <v>6.9</v>
       </c>
       <c r="Q123">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="R123">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S123">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="T123">
         <v>2.28</v>
       </c>
       <c r="U123">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="V123">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="W123">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X123">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Y123">
         <v>1.5</v>
       </c>
       <c r="Z123">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AA123">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AB123">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AC123">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AD123">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AE123">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF123">
         <v>2.6</v>
@@ -20428,7 +20428,7 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AK123">
         <v>2.31</v>
@@ -20542,43 +20542,43 @@
         <v>1.99</v>
       </c>
       <c r="U124">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="V124">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="W124">
         <v>1.03</v>
       </c>
       <c r="X124">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Y124">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="Z124">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AA124">
         <v>3.08</v>
       </c>
       <c r="AB124">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC124">
-        <v>5.1</v>
+        <v>5.75</v>
       </c>
       <c r="AD124">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AE124">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF124">
-        <v>2.2</v>
+        <v>2.57</v>
       </c>
       <c r="AG124">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20594,7 +20594,7 @@
         <v>1.2</v>
       </c>
       <c r="AK124">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20693,71 +20693,71 @@
         <v>0</v>
       </c>
       <c r="Q125">
-        <v>4.86</v>
+        <v>4.6</v>
       </c>
       <c r="R125">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S125">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T125">
-        <v>3.08</v>
+        <v>3.21</v>
       </c>
       <c r="U125">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="V125">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W125">
         <v>1.07</v>
       </c>
       <c r="X125">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y125">
+        <v>1.17</v>
+      </c>
+      <c r="Z125">
+        <v>3.94</v>
+      </c>
+      <c r="AA125">
+        <v>1.73</v>
+      </c>
+      <c r="AB125">
+        <v>1.96</v>
+      </c>
+      <c r="AC125">
+        <v>2.62</v>
+      </c>
+      <c r="AD125">
+        <v>1.38</v>
+      </c>
+      <c r="AE125">
+        <v>1.14</v>
+      </c>
+      <c r="AF125">
+        <v>1.64</v>
+      </c>
+      <c r="AG125">
+        <v>2.13</v>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ125">
+        <v>1.25</v>
+      </c>
+      <c r="AK125">
         <v>1.2</v>
-      </c>
-      <c r="Z125">
-        <v>3.71</v>
-      </c>
-      <c r="AA125">
-        <v>1.77</v>
-      </c>
-      <c r="AB125">
-        <v>1.9</v>
-      </c>
-      <c r="AC125">
-        <v>2.81</v>
-      </c>
-      <c r="AD125">
-        <v>1.33</v>
-      </c>
-      <c r="AE125">
-        <v>1.12</v>
-      </c>
-      <c r="AF125">
-        <v>1.7</v>
-      </c>
-      <c r="AG125">
-        <v>1.93</v>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ125">
-        <v>2.05</v>
-      </c>
-      <c r="AK125">
-        <v>1.18</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20856,13 +20856,13 @@
         <v>5.45</v>
       </c>
       <c r="Q126">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R126">
-        <v>2.97</v>
+        <v>2.75</v>
       </c>
       <c r="S126">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T126">
         <v>4.6</v>
@@ -20880,7 +20880,7 @@
         <v>1.01</v>
       </c>
       <c r="Y126">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Z126">
         <v>7.2</v>
@@ -20892,10 +20892,10 @@
         <v>3.28</v>
       </c>
       <c r="AC126">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="AD126">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AE126">
         <v>1.4</v>
@@ -20917,7 +20917,7 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AK126">
         <v>2.61</v>
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="O127">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="P127">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="Q127">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="R127">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="S127">
         <v>1.12</v>
       </c>
       <c r="T127">
-        <v>4.95</v>
+        <v>4.8</v>
       </c>
       <c r="U127">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="V127">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="W127">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X127">
         <v>1.01</v>
       </c>
       <c r="Y127">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Z127">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="AA127">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AB127">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="AC127">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AD127">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AE127">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AF127">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AG127">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK127">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21173,31 +21173,31 @@
         </is>
       </c>
       <c r="N128">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="O128">
-        <v>3.86</v>
+        <v>3.65</v>
       </c>
       <c r="P128">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="Q128">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="R128">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S128">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T128">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="U128">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="V128">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="W128">
         <v>1.22</v>
@@ -21206,31 +21206,31 @@
         <v>1.01</v>
       </c>
       <c r="Y128">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z128">
-        <v>6.5</v>
+        <v>6.15</v>
       </c>
       <c r="AA128">
+        <v>1.34</v>
+      </c>
+      <c r="AB128">
+        <v>2.92</v>
+      </c>
+      <c r="AC128">
+        <v>1.88</v>
+      </c>
+      <c r="AD128">
+        <v>1.88</v>
+      </c>
+      <c r="AE128">
+        <v>1.34</v>
+      </c>
+      <c r="AF128">
         <v>1.32</v>
       </c>
-      <c r="AB128">
-        <v>2.75</v>
-      </c>
-      <c r="AC128">
-        <v>1.89</v>
-      </c>
-      <c r="AD128">
-        <v>1.86</v>
-      </c>
-      <c r="AE128">
-        <v>1.36</v>
-      </c>
-      <c r="AF128">
-        <v>1.33</v>
-      </c>
       <c r="AG128">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK128">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21336,19 +21336,19 @@
         </is>
       </c>
       <c r="N129">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O129">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="P129">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="Q129">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="R129">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="S129">
         <v>1.18</v>
@@ -21369,31 +21369,31 @@
         <v>1.01</v>
       </c>
       <c r="Y129">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z129">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="AA129">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AB129">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="AC129">
         <v>1.83</v>
       </c>
       <c r="AD129">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AE129">
         <v>1.36</v>
       </c>
       <c r="AF129">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AG129">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AK129">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -22151,22 +22151,22 @@
         </is>
       </c>
       <c r="N134">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="O134">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P134">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="Q134">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="R134">
         <v>2.25</v>
       </c>
       <c r="S134">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T134">
         <v>2.88</v>
@@ -22178,7 +22178,7 @@
         <v>1.4</v>
       </c>
       <c r="W134">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X134">
         <v>1.05</v>
@@ -22202,7 +22202,7 @@
         <v>1.33</v>
       </c>
       <c r="AE134">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF134">
         <v>1.73</v>
@@ -22323,13 +22323,13 @@
         <v>3.25</v>
       </c>
       <c r="Q135">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="R135">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="S135">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T135">
         <v>3.25</v>
@@ -22359,7 +22359,7 @@
         <v>2.2</v>
       </c>
       <c r="AC135">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="AD135">
         <v>1.5</v>
@@ -22371,7 +22371,7 @@
         <v>1.5</v>
       </c>
       <c r="AG135">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22477,7 +22477,7 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
       <c r="O136">
         <v>3.08</v>
@@ -22486,7 +22486,7 @@
         <v>2.8</v>
       </c>
       <c r="Q136">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="R136">
         <v>2.1</v>
@@ -22507,10 +22507,10 @@
         <v>1.08</v>
       </c>
       <c r="X136">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y136">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z136">
         <v>3.2</v>
@@ -22534,7 +22534,7 @@
         <v>1.75</v>
       </c>
       <c r="AG136">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>1.31</v>
       </c>
       <c r="AK136">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22640,43 +22640,43 @@
         </is>
       </c>
       <c r="N137">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="O137">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="P137">
         <v>1.51</v>
       </c>
       <c r="Q137">
-        <v>5.5</v>
+        <v>6.45</v>
       </c>
       <c r="R137">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S137">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T137">
         <v>2.99</v>
       </c>
       <c r="U137">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="V137">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W137">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X137">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y137">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z137">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AA137">
         <v>1.87</v>
@@ -22710,7 +22710,7 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AK137">
         <v>1.13</v>
@@ -22815,28 +22815,28 @@
         <v>2.1</v>
       </c>
       <c r="R138">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="S138">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="T138">
-        <v>2.7</v>
+        <v>2.31</v>
       </c>
       <c r="U138">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="V138">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="W138">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X138">
         <v>1.1</v>
       </c>
       <c r="Y138">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Z138">
         <v>2.55</v>
@@ -22860,7 +22860,7 @@
         <v>2.4</v>
       </c>
       <c r="AG138">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AK138">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -23295,7 +23295,7 @@
         <v>1.64</v>
       </c>
       <c r="O141">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P141">
         <v>5.01</v>
@@ -23325,10 +23325,10 @@
         <v>1.06</v>
       </c>
       <c r="Y141">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Z141">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="AA141">
         <v>2.06</v>
@@ -23343,10 +23343,10 @@
         <v>1.22</v>
       </c>
       <c r="AE141">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF141">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG141">
         <v>1.65</v>
@@ -24433,13 +24433,13 @@
         </is>
       </c>
       <c r="N148">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="O148">
         <v>3.4</v>
       </c>
       <c r="P148">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q148">
         <v>2.5</v>
@@ -24454,7 +24454,7 @@
         <v>3.27</v>
       </c>
       <c r="U148">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V148">
         <v>1.5</v>
@@ -24463,7 +24463,7 @@
         <v>1.11</v>
       </c>
       <c r="X148">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y148">
         <v>1.18</v>
@@ -24475,7 +24475,7 @@
         <v>1.7</v>
       </c>
       <c r="AB148">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AC148">
         <v>2.75</v>
@@ -24484,7 +24484,7 @@
         <v>1.4</v>
       </c>
       <c r="AE148">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF148">
         <v>1.57</v>
@@ -24506,7 +24506,7 @@
         <v>1.25</v>
       </c>
       <c r="AK148">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G150">
@@ -24759,64 +24759,64 @@
         </is>
       </c>
       <c r="N150">
-        <v>2.28</v>
+        <v>2.65</v>
       </c>
       <c r="O150">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="P150">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="Q150">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R150">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S150">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T150">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U150">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V150">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W150">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X150">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y150">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z150">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA150">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB150">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC150">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD150">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE150">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF150">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG150">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH150" t="inlineStr">
         <is>
@@ -24829,10 +24829,10 @@
         </is>
       </c>
       <c r="AJ150">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK150">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL150">
         <v>0</v>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,64 +24922,64 @@
         </is>
       </c>
       <c r="N151">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="O151">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="P151">
-        <v>3.03</v>
+        <v>2.88</v>
       </c>
       <c r="Q151">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R151">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S151">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T151">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U151">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V151">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W151">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X151">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y151">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z151">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA151">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB151">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC151">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD151">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE151">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF151">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG151">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -24992,10 +24992,10 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK151">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25411,10 +25411,10 @@
         </is>
       </c>
       <c r="N154">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="O154">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="P154">
         <v>6.5</v>
@@ -25423,7 +25423,7 @@
         <v>1.85</v>
       </c>
       <c r="R154">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="S154">
         <v>1.26</v>
@@ -25444,28 +25444,28 @@
         <v>1.03</v>
       </c>
       <c r="Y154">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z154">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AA154">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AB154">
         <v>2.25</v>
       </c>
       <c r="AC154">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AD154">
         <v>1.44</v>
       </c>
       <c r="AE154">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF154">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG154">
         <v>1.85</v>
@@ -25595,7 +25595,7 @@
         <v>2.75</v>
       </c>
       <c r="U155">
-        <v>2.99</v>
+        <v>2.85</v>
       </c>
       <c r="V155">
         <v>1.36</v>
@@ -25647,7 +25647,7 @@
         <v>1.29</v>
       </c>
       <c r="AK155">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25752,10 +25752,10 @@
         <v>1.95</v>
       </c>
       <c r="S156">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="T156">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="U156">
         <v>3.6</v>
@@ -25764,7 +25764,7 @@
         <v>1.25</v>
       </c>
       <c r="W156">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X156">
         <v>1.06</v>
@@ -25782,7 +25782,7 @@
         <v>1.49</v>
       </c>
       <c r="AC156">
-        <v>4.3</v>
+        <v>4.84</v>
       </c>
       <c r="AD156">
         <v>1.15</v>
@@ -25900,28 +25900,28 @@
         </is>
       </c>
       <c r="N157">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="O157">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P157">
-        <v>4.7</v>
+        <v>5.95</v>
       </c>
       <c r="Q157">
         <v>2.2</v>
       </c>
       <c r="R157">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="S157">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="T157">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="U157">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="V157">
         <v>1.22</v>
@@ -25936,28 +25936,28 @@
         <v>1.53</v>
       </c>
       <c r="Z157">
+        <v>2.45</v>
+      </c>
+      <c r="AA157">
         <v>2.5</v>
       </c>
-      <c r="AA157">
-        <v>2.4</v>
-      </c>
       <c r="AB157">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AC157">
-        <v>4.8</v>
+        <v>5.04</v>
       </c>
       <c r="AD157">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE157">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF157">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AG157">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25973,7 +25973,7 @@
         <v>1.1</v>
       </c>
       <c r="AK157">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26063,19 +26063,19 @@
         </is>
       </c>
       <c r="N158">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="O158">
         <v>3.4</v>
       </c>
       <c r="P158">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Q158">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R158">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="S158">
         <v>1.36</v>
@@ -26108,7 +26108,7 @@
         <v>1.8</v>
       </c>
       <c r="AC158">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="AD158">
         <v>1.31</v>
@@ -26117,7 +26117,7 @@
         <v>1.08</v>
       </c>
       <c r="AF158">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG158">
         <v>1.93</v>
@@ -26136,7 +26136,7 @@
         <v>1.32</v>
       </c>
       <c r="AK158">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26259,25 +26259,25 @@
         <v>1.01</v>
       </c>
       <c r="Y159">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z159">
-        <v>5.45</v>
+        <v>5.75</v>
       </c>
       <c r="AA159">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AB159">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AC159">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AD159">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AE159">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AF159">
         <v>2.45</v>
@@ -26389,13 +26389,13 @@
         </is>
       </c>
       <c r="N160">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O160">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P160">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q160">
         <v>4.8</v>
@@ -26561,13 +26561,13 @@
         <v>6</v>
       </c>
       <c r="Q161">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R161">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="S161">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="T161">
         <v>2.38</v>
@@ -26576,25 +26576,25 @@
         <v>3.42</v>
       </c>
       <c r="V161">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="W161">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X161">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y161">
         <v>1.45</v>
       </c>
       <c r="Z161">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="AA161">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="AB161">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AC161">
         <v>4.6</v>
@@ -26606,10 +26606,10 @@
         <v>1.01</v>
       </c>
       <c r="AF161">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AG161">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26625,7 +26625,7 @@
         <v>1.3</v>
       </c>
       <c r="AK161">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -26887,10 +26887,10 @@
         <v>4.2</v>
       </c>
       <c r="Q163">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="R163">
-        <v>2.9</v>
+        <v>2.66</v>
       </c>
       <c r="S163">
         <v>1.15</v>
@@ -26899,10 +26899,10 @@
         <v>4.8</v>
       </c>
       <c r="U163">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="V163">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="W163">
         <v>1.29</v>
@@ -26920,13 +26920,13 @@
         <v>1.25</v>
       </c>
       <c r="AB163">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AC163">
         <v>1.67</v>
       </c>
       <c r="AD163">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AE163">
         <v>1.44</v>
@@ -26951,7 +26951,7 @@
         <v>1.2</v>
       </c>
       <c r="AK163">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27056,10 +27056,10 @@
         <v>1.85</v>
       </c>
       <c r="S164">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="T164">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="U164">
         <v>3.7</v>
@@ -27071,19 +27071,19 @@
         <v>1.04</v>
       </c>
       <c r="X164">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y164">
         <v>1.62</v>
       </c>
       <c r="Z164">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AA164">
         <v>3.1</v>
       </c>
       <c r="AB164">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AC164">
         <v>5.75</v>
@@ -27376,16 +27376,16 @@
         <v>0</v>
       </c>
       <c r="Q166">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="R166">
         <v>1.85</v>
       </c>
       <c r="S166">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="T166">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="U166">
         <v>3.98</v>
@@ -27403,13 +27403,13 @@
         <v>1.65</v>
       </c>
       <c r="Z166">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AA166">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AB166">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AC166">
         <v>5.75</v>
@@ -27424,7 +27424,7 @@
         <v>2.42</v>
       </c>
       <c r="AG166">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="AH166" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         </is>
       </c>
       <c r="AJ166">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AK166">
         <v>1.73</v>
@@ -27530,25 +27530,25 @@
         </is>
       </c>
       <c r="N167">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="O167">
         <v>2.95</v>
       </c>
       <c r="P167">
-        <v>3.03</v>
+        <v>2.9</v>
       </c>
       <c r="Q167">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R167">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="S167">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="T167">
-        <v>2.29</v>
+        <v>2.46</v>
       </c>
       <c r="U167">
         <v>3.38</v>
@@ -27563,22 +27563,22 @@
         <v>1.06</v>
       </c>
       <c r="Y167">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="Z167">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="AA167">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="AB167">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AC167">
-        <v>4.72</v>
+        <v>4.1</v>
       </c>
       <c r="AD167">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AE167">
         <v>1.05</v>
@@ -27603,7 +27603,7 @@
         <v>1.33</v>
       </c>
       <c r="AK167">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -27693,13 +27693,13 @@
         </is>
       </c>
       <c r="N168">
-        <v>2.45</v>
+        <v>2.22</v>
       </c>
       <c r="O168">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="P168">
-        <v>2.75</v>
+        <v>3.54</v>
       </c>
       <c r="Q168">
         <v>0</v>
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G170">
@@ -28019,64 +28019,64 @@
         </is>
       </c>
       <c r="N170">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="O170">
         <v>3.3</v>
       </c>
       <c r="P170">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="Q170">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="R170">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="S170">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T170">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="U170">
-        <v>3.05</v>
+        <v>2.89</v>
       </c>
       <c r="V170">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W170">
         <v>1.04</v>
       </c>
       <c r="X170">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y170">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="Z170">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AA170">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AB170">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AC170">
-        <v>3.75</v>
+        <v>3.92</v>
       </c>
       <c r="AD170">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE170">
         <v>1.04</v>
       </c>
       <c r="AF170">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG170">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH170" t="inlineStr">
         <is>
@@ -28089,10 +28089,10 @@
         </is>
       </c>
       <c r="AJ170">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AK170">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,64 +28182,64 @@
         </is>
       </c>
       <c r="N171">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="O171">
         <v>3.3</v>
       </c>
       <c r="P171">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="Q171">
+        <v>2.62</v>
+      </c>
+      <c r="R171">
+        <v>2.1</v>
+      </c>
+      <c r="S171">
+        <v>1.43</v>
+      </c>
+      <c r="T171">
         <v>2.7</v>
       </c>
-      <c r="R171">
-        <v>1.96</v>
-      </c>
-      <c r="S171">
-        <v>1.44</v>
-      </c>
-      <c r="T171">
-        <v>2.48</v>
-      </c>
       <c r="U171">
-        <v>2.89</v>
+        <v>3.05</v>
       </c>
       <c r="V171">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W171">
         <v>1.04</v>
       </c>
       <c r="X171">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y171">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="Z171">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="AA171">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AB171">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AC171">
-        <v>3.92</v>
+        <v>3.75</v>
       </c>
       <c r="AD171">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE171">
         <v>1.04</v>
       </c>
       <c r="AF171">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG171">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH171" t="inlineStr">
         <is>
@@ -28252,10 +28252,10 @@
         </is>
       </c>
       <c r="AJ171">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AK171">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AL171">
         <v>0</v>
@@ -28671,10 +28671,10 @@
         </is>
       </c>
       <c r="N174">
-        <v>4.35</v>
+        <v>3.8</v>
       </c>
       <c r="O174">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P174">
         <v>1.83</v>
@@ -28683,22 +28683,22 @@
         <v>4.4</v>
       </c>
       <c r="R174">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="S174">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T174">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U174">
         <v>2.72</v>
       </c>
       <c r="V174">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W174">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X174">
         <v>1.05</v>
@@ -28713,10 +28713,10 @@
         <v>1.95</v>
       </c>
       <c r="AB174">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC174">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="AD174">
         <v>1.3</v>
@@ -29018,13 +29018,13 @@
         <v>3.2</v>
       </c>
       <c r="U176">
-        <v>2.34</v>
+        <v>2.17</v>
       </c>
       <c r="V176">
         <v>1.52</v>
       </c>
       <c r="W176">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X176">
         <v>1.03</v>
@@ -29036,7 +29036,7 @@
         <v>4.1</v>
       </c>
       <c r="AA176">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="AB176">
         <v>2.12</v>
@@ -29048,13 +29048,13 @@
         <v>1.41</v>
       </c>
       <c r="AE176">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF176">
-        <v>1.59</v>
+        <v>1.49</v>
       </c>
       <c r="AG176">
-        <v>2.13</v>
+        <v>2.38</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29070,7 +29070,7 @@
         <v>1.91</v>
       </c>
       <c r="AK176">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29326,16 +29326,16 @@
         <v>1.77</v>
       </c>
       <c r="O178">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P178">
-        <v>3.7</v>
+        <v>4.17</v>
       </c>
       <c r="Q178">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="R178">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="S178">
         <v>1.36</v>
@@ -29347,7 +29347,7 @@
         <v>2.85</v>
       </c>
       <c r="V178">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W178">
         <v>1.07</v>
@@ -29362,10 +29362,10 @@
         <v>3.2</v>
       </c>
       <c r="AA178">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AB178">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC178">
         <v>3.3</v>
@@ -29374,7 +29374,7 @@
         <v>1.26</v>
       </c>
       <c r="AE178">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF178">
         <v>1.75</v>
@@ -29393,10 +29393,10 @@
         </is>
       </c>
       <c r="AJ178">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK178">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29486,16 +29486,16 @@
         </is>
       </c>
       <c r="N179">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="O179">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="P179">
-        <v>2.68</v>
+        <v>2.3</v>
       </c>
       <c r="Q179">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="R179">
         <v>1.88</v>
@@ -29507,10 +29507,10 @@
         <v>2.31</v>
       </c>
       <c r="U179">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="V179">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="W179">
         <v>1.01</v>
@@ -29519,10 +29519,10 @@
         <v>1.08</v>
       </c>
       <c r="Y179">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="Z179">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="AA179">
         <v>2.49</v>
@@ -29531,10 +29531,10 @@
         <v>1.49</v>
       </c>
       <c r="AC179">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AD179">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE179">
         <v>1.04</v>
@@ -29658,7 +29658,7 @@
         <v>2.58</v>
       </c>
       <c r="Q180">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="R180">
         <v>2.11</v>
@@ -29670,10 +29670,10 @@
         <v>2.92</v>
       </c>
       <c r="U180">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="V180">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="W180">
         <v>1.08</v>
@@ -29688,19 +29688,19 @@
         <v>3.75</v>
       </c>
       <c r="AA180">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AB180">
         <v>1.95</v>
       </c>
       <c r="AC180">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="AD180">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AE180">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF180">
         <v>1.6</v>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="O46">
-        <v>3.6</v>
+        <v>3.77</v>
       </c>
       <c r="P46">
-        <v>4.55</v>
+        <v>5</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -7970,34 +7970,34 @@
         </is>
       </c>
       <c r="N47">
-        <v>3.7</v>
+        <v>4.78</v>
       </c>
       <c r="O47">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="P47">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="Q47">
         <v>4.31</v>
       </c>
       <c r="R47">
-        <v>2.46</v>
+        <v>2.28</v>
       </c>
       <c r="S47">
         <v>1.28</v>
       </c>
       <c r="T47">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U47">
         <v>2.36</v>
       </c>
       <c r="V47">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W47">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X47">
         <v>1.03</v>
@@ -8006,7 +8006,7 @@
         <v>1.22</v>
       </c>
       <c r="Z47">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA47">
         <v>1.62</v>
@@ -8021,13 +8021,13 @@
         <v>1.5</v>
       </c>
       <c r="AE47">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AF47">
         <v>1.6</v>
       </c>
       <c r="AG47">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.85</v>
+        <v>1.25</v>
       </c>
       <c r="AK47">
         <v>1.25</v>
@@ -16283,58 +16283,58 @@
         </is>
       </c>
       <c r="N98">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="O98">
         <v>3.25</v>
       </c>
       <c r="P98">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q98">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="R98">
         <v>2.15</v>
       </c>
       <c r="S98">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T98">
-        <v>2.79</v>
+        <v>2.62</v>
       </c>
       <c r="U98">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="V98">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W98">
         <v>1.07</v>
       </c>
       <c r="X98">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y98">
         <v>1.35</v>
       </c>
       <c r="Z98">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="AA98">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB98">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC98">
-        <v>3.75</v>
+        <v>3.54</v>
       </c>
       <c r="AD98">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE98">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF98">
         <v>1.83</v>
@@ -16356,7 +16356,7 @@
         <v>1.64</v>
       </c>
       <c r="AK98">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -17759,55 +17759,55 @@
         <v>0</v>
       </c>
       <c r="Q107">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R107">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S107">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T107">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U107">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V107">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W107">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X107">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y107">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z107">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA107">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB107">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC107">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD107">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE107">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF107">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG107">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK107">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>3.93</v>
+        <v>1.46</v>
       </c>
       <c r="O121">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="P121">
-        <v>1.83</v>
+        <v>5.75</v>
       </c>
       <c r="Q121">
-        <v>4.69</v>
+        <v>2.01</v>
       </c>
       <c r="R121">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="S121">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="T121">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="U121">
-        <v>3.01</v>
+        <v>2.56</v>
       </c>
       <c r="V121">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="W121">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X121">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y121">
+        <v>1.21</v>
+      </c>
+      <c r="Z121">
+        <v>3.58</v>
+      </c>
+      <c r="AA121">
+        <v>1.87</v>
+      </c>
+      <c r="AB121">
+        <v>1.92</v>
+      </c>
+      <c r="AC121">
+        <v>2.81</v>
+      </c>
+      <c r="AD121">
         <v>1.33</v>
       </c>
-      <c r="Z121">
-        <v>3.08</v>
-      </c>
-      <c r="AA121">
-        <v>2.1</v>
-      </c>
-      <c r="AB121">
-        <v>1.75</v>
-      </c>
-      <c r="AC121">
-        <v>3.6</v>
-      </c>
-      <c r="AD121">
-        <v>1.24</v>
-      </c>
       <c r="AE121">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF121">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AG121">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.85</v>
+        <v>1.17</v>
       </c>
       <c r="AK121">
-        <v>1.18</v>
+        <v>2.5</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.46</v>
+        <v>3.93</v>
       </c>
       <c r="O122">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="P122">
-        <v>5.75</v>
+        <v>1.83</v>
       </c>
       <c r="Q122">
-        <v>2.01</v>
+        <v>4.69</v>
       </c>
       <c r="R122">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="S122">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="T122">
-        <v>2.9</v>
+        <v>2.66</v>
       </c>
       <c r="U122">
-        <v>2.56</v>
+        <v>3.01</v>
       </c>
       <c r="V122">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="W122">
+        <v>1.03</v>
+      </c>
+      <c r="X122">
         <v>1.06</v>
       </c>
-      <c r="X122">
-        <v>1.01</v>
-      </c>
       <c r="Y122">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="Z122">
-        <v>3.58</v>
+        <v>3.08</v>
       </c>
       <c r="AA122">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AB122">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AC122">
-        <v>2.81</v>
+        <v>3.6</v>
       </c>
       <c r="AD122">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AE122">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF122">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AG122">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.17</v>
+        <v>1.85</v>
       </c>
       <c r="AK122">
-        <v>2.5</v>
+        <v>1.18</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -23790,7 +23790,7 @@
         <v>6.63</v>
       </c>
       <c r="Q144">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="R144">
         <v>2.2</v>
@@ -23799,7 +23799,7 @@
         <v>1.38</v>
       </c>
       <c r="T144">
-        <v>2.9</v>
+        <v>2.67</v>
       </c>
       <c r="U144">
         <v>2.88</v>
@@ -23820,7 +23820,7 @@
         <v>3.42</v>
       </c>
       <c r="AA144">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AB144">
         <v>1.84</v>
@@ -23835,7 +23835,7 @@
         <v>1.06</v>
       </c>
       <c r="AF144">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG144">
         <v>1.78</v>
@@ -23953,7 +23953,7 @@
         <v>4.48</v>
       </c>
       <c r="Q145">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="R145">
         <v>2.32</v>
@@ -23977,25 +23977,25 @@
         <v>1</v>
       </c>
       <c r="Y145">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z145">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="AA145">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AB145">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="AC145">
         <v>2.94</v>
       </c>
       <c r="AD145">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE145">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF145">
         <v>1.7</v>
@@ -28037,16 +28037,16 @@
         <v>1.44</v>
       </c>
       <c r="T170">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="U170">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="V170">
         <v>1.33</v>
       </c>
       <c r="W170">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X170">
         <v>1.06</v>
@@ -28055,16 +28055,16 @@
         <v>1.38</v>
       </c>
       <c r="Z170">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="AA170">
         <v>2.19</v>
       </c>
       <c r="AB170">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AC170">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="AD170">
         <v>1.23</v>
@@ -28182,13 +28182,13 @@
         </is>
       </c>
       <c r="N171">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="O171">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="P171">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="Q171">
         <v>2.62</v>
@@ -28212,13 +28212,13 @@
         <v>1.04</v>
       </c>
       <c r="X171">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y171">
         <v>1.31</v>
       </c>
       <c r="Z171">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="AA171">
         <v>2.1</v>
@@ -28227,10 +28227,10 @@
         <v>1.71</v>
       </c>
       <c r="AC171">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AD171">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE171">
         <v>1.04</v>
@@ -28252,7 +28252,7 @@
         </is>
       </c>
       <c r="AJ171">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AK171">
         <v>1.68</v>
@@ -28849,10 +28849,10 @@
         <v>2.63</v>
       </c>
       <c r="S175">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T175">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U175">
         <v>2.38</v>
@@ -28891,7 +28891,7 @@
         <v>2.1</v>
       </c>
       <c r="AG175">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.1</v>
+        <v>1.83</v>
       </c>
       <c r="O18">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="P18">
-        <v>2.15</v>
+        <v>3.75</v>
       </c>
       <c r="Q18">
-        <v>3.62</v>
+        <v>2.25</v>
       </c>
       <c r="R18">
         <v>2.4</v>
       </c>
       <c r="S18">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T18">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="U18">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="V18">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="W18">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X18">
         <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Z18">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA18">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AB18">
-        <v>2.55</v>
+        <v>2.14</v>
       </c>
       <c r="AC18">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AD18">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AE18">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AF18">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AG18">
-        <v>2.53</v>
+        <v>2.28</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK18">
-        <v>1.33</v>
+        <v>1.86</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.83</v>
+        <v>3.1</v>
       </c>
       <c r="O19">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="P19">
-        <v>3.75</v>
+        <v>2.15</v>
       </c>
       <c r="Q19">
-        <v>2.25</v>
+        <v>3.62</v>
       </c>
       <c r="R19">
         <v>2.4</v>
       </c>
       <c r="S19">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T19">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="U19">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="V19">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="W19">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X19">
         <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z19">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AA19">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AB19">
-        <v>2.14</v>
+        <v>2.55</v>
       </c>
       <c r="AC19">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AD19">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AE19">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AF19">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AG19">
-        <v>2.28</v>
+        <v>2.53</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK19">
-        <v>1.86</v>
+        <v>1.33</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>1.46</v>
+        <v>3.93</v>
       </c>
       <c r="O121">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="P121">
-        <v>5.75</v>
+        <v>1.83</v>
       </c>
       <c r="Q121">
-        <v>2.01</v>
+        <v>4.69</v>
       </c>
       <c r="R121">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="S121">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="T121">
-        <v>2.9</v>
+        <v>2.66</v>
       </c>
       <c r="U121">
-        <v>2.56</v>
+        <v>3.01</v>
       </c>
       <c r="V121">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="W121">
+        <v>1.03</v>
+      </c>
+      <c r="X121">
         <v>1.06</v>
       </c>
-      <c r="X121">
-        <v>1.01</v>
-      </c>
       <c r="Y121">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="Z121">
-        <v>3.58</v>
+        <v>3.08</v>
       </c>
       <c r="AA121">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AB121">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AC121">
-        <v>2.81</v>
+        <v>3.6</v>
       </c>
       <c r="AD121">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AE121">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF121">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AG121">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.17</v>
+        <v>1.85</v>
       </c>
       <c r="AK121">
-        <v>2.5</v>
+        <v>1.18</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>3.93</v>
+        <v>1.46</v>
       </c>
       <c r="O122">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="P122">
-        <v>1.83</v>
+        <v>5.75</v>
       </c>
       <c r="Q122">
-        <v>4.69</v>
+        <v>2.01</v>
       </c>
       <c r="R122">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="S122">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="T122">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="U122">
-        <v>3.01</v>
+        <v>2.56</v>
       </c>
       <c r="V122">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="W122">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X122">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y122">
+        <v>1.21</v>
+      </c>
+      <c r="Z122">
+        <v>3.58</v>
+      </c>
+      <c r="AA122">
+        <v>1.87</v>
+      </c>
+      <c r="AB122">
+        <v>1.92</v>
+      </c>
+      <c r="AC122">
+        <v>2.81</v>
+      </c>
+      <c r="AD122">
         <v>1.33</v>
       </c>
-      <c r="Z122">
-        <v>3.08</v>
-      </c>
-      <c r="AA122">
-        <v>2.1</v>
-      </c>
-      <c r="AB122">
-        <v>1.75</v>
-      </c>
-      <c r="AC122">
-        <v>3.6</v>
-      </c>
-      <c r="AD122">
-        <v>1.24</v>
-      </c>
       <c r="AE122">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF122">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AG122">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.85</v>
+        <v>1.17</v>
       </c>
       <c r="AK122">
-        <v>1.18</v>
+        <v>2.5</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -27210,19 +27210,19 @@
         <v>3.65</v>
       </c>
       <c r="P165">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="Q165">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R165">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="S165">
         <v>1.32</v>
       </c>
       <c r="T165">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="U165">
         <v>2.4</v>
@@ -27231,22 +27231,22 @@
         <v>1.5</v>
       </c>
       <c r="W165">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X165">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y165">
         <v>1.19</v>
       </c>
       <c r="Z165">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="AA165">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AB165">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AC165">
         <v>2.65</v>
@@ -27255,13 +27255,13 @@
         <v>1.37</v>
       </c>
       <c r="AE165">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF165">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG165">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
@@ -27274,10 +27274,10 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK165">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G170">
@@ -28019,64 +28019,64 @@
         </is>
       </c>
       <c r="N170">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="O170">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="P170">
-        <v>3.6</v>
+        <v>3.08</v>
       </c>
       <c r="Q170">
+        <v>2.62</v>
+      </c>
+      <c r="R170">
+        <v>2.1</v>
+      </c>
+      <c r="S170">
+        <v>1.43</v>
+      </c>
+      <c r="T170">
         <v>2.7</v>
       </c>
-      <c r="R170">
-        <v>1.96</v>
-      </c>
-      <c r="S170">
-        <v>1.44</v>
-      </c>
-      <c r="T170">
-        <v>2.6</v>
-      </c>
       <c r="U170">
-        <v>2.91</v>
+        <v>3.05</v>
       </c>
       <c r="V170">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W170">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X170">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y170">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="Z170">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="AA170">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AB170">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AC170">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AD170">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE170">
         <v>1.04</v>
       </c>
       <c r="AF170">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG170">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH170" t="inlineStr">
         <is>
@@ -28089,10 +28089,10 @@
         </is>
       </c>
       <c r="AJ170">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AK170">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,64 +28182,64 @@
         </is>
       </c>
       <c r="N171">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="O171">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="P171">
-        <v>3.08</v>
+        <v>3.6</v>
       </c>
       <c r="Q171">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="R171">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="S171">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T171">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="U171">
-        <v>3.05</v>
+        <v>2.91</v>
       </c>
       <c r="V171">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W171">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X171">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y171">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="Z171">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="AA171">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AB171">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AC171">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AD171">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE171">
         <v>1.04</v>
       </c>
       <c r="AF171">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG171">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH171" t="inlineStr">
         <is>
@@ -28252,10 +28252,10 @@
         </is>
       </c>
       <c r="AJ171">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AK171">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AL171">
         <v>0</v>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -647,16 +647,16 @@
         <v>4.8</v>
       </c>
       <c r="R2">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="S2">
         <v>1.47</v>
       </c>
       <c r="T2">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="U2">
-        <v>3.22</v>
+        <v>3.16</v>
       </c>
       <c r="V2">
         <v>1.3</v>
@@ -671,13 +671,13 @@
         <v>1.33</v>
       </c>
       <c r="Z2">
-        <v>2.99</v>
+        <v>2.83</v>
       </c>
       <c r="AA2">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AB2">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AC2">
         <v>3.9</v>
@@ -708,7 +708,7 @@
         <v>1.34</v>
       </c>
       <c r="AK2">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -801,40 +801,40 @@
         <v>3.7</v>
       </c>
       <c r="O3">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P3">
         <v>1.69</v>
       </c>
       <c r="Q3">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="R3">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="S3">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T3">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="U3">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="V3">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W3">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z3">
-        <v>3.34</v>
+        <v>3.45</v>
       </c>
       <c r="AA3">
         <v>1.95</v>
@@ -843,19 +843,19 @@
         <v>1.88</v>
       </c>
       <c r="AC3">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AD3">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE3">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF3">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG3">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AK3">
         <v>1.14</v>
@@ -970,28 +970,28 @@
         <v>2.65</v>
       </c>
       <c r="Q4">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="R4">
         <v>2.3</v>
       </c>
       <c r="S4">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T4">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="U4">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="V4">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W4">
         <v>1.07</v>
       </c>
       <c r="X4">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y4">
         <v>1.19</v>
@@ -1006,16 +1006,16 @@
         <v>2.05</v>
       </c>
       <c r="AC4">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="AD4">
         <v>1.34</v>
       </c>
       <c r="AE4">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF4">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG4">
         <v>2.15</v>
@@ -1034,7 +1034,7 @@
         <v>1.23</v>
       </c>
       <c r="AK4">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC5">
         <v>0</v>
@@ -1287,25 +1287,25 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="O6">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="P6">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="Q6">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R6">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="S6">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="T6">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="U6">
         <v>3.15</v>
@@ -1320,31 +1320,31 @@
         <v>1.05</v>
       </c>
       <c r="Y6">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z6">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AA6">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="AB6">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AC6">
         <v>4</v>
       </c>
       <c r="AD6">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE6">
         <v>1.03</v>
       </c>
       <c r="AF6">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG6">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>1.48</v>
       </c>
       <c r="T8">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="U8">
         <v>3.2</v>
@@ -1652,10 +1652,10 @@
         <v>2.74</v>
       </c>
       <c r="AA8">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AB8">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC8">
         <v>3.98</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="O10">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="P10">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="Q10">
         <v>3.64</v>
@@ -1954,16 +1954,16 @@
         <v>2</v>
       </c>
       <c r="S10">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T10">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="U10">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="V10">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W10">
         <v>1.05</v>
@@ -1972,7 +1972,7 @@
         <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z10">
         <v>2.82</v>
@@ -1984,7 +1984,7 @@
         <v>1.72</v>
       </c>
       <c r="AC10">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AD10">
         <v>1.21</v>
@@ -1996,7 +1996,7 @@
         <v>1.8</v>
       </c>
       <c r="AG10">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O12">
-        <v>4</v>
+        <v>3.97</v>
       </c>
       <c r="P12">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="Q12">
         <v>4.5</v>
@@ -2310,7 +2310,7 @@
         <v>2.4</v>
       </c>
       <c r="AC12">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="AD12">
         <v>1.62</v>
@@ -2338,7 +2338,7 @@
         <v>1.24</v>
       </c>
       <c r="AK12">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,22 +2428,22 @@
         </is>
       </c>
       <c r="N13">
+        <v>3.4</v>
+      </c>
+      <c r="O13">
         <v>3</v>
       </c>
-      <c r="O13">
-        <v>3.35</v>
-      </c>
       <c r="P13">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="Q13">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R13">
         <v>2.04</v>
       </c>
       <c r="S13">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T13">
         <v>3.4</v>
@@ -2452,19 +2452,19 @@
         <v>2.23</v>
       </c>
       <c r="V13">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W13">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
         <v>1.16</v>
       </c>
       <c r="Z13">
-        <v>4.79</v>
+        <v>4.8</v>
       </c>
       <c r="AA13">
         <v>1.57</v>
@@ -2482,10 +2482,10 @@
         <v>1.2</v>
       </c>
       <c r="AF13">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AG13">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2600,49 +2600,49 @@
         <v>0</v>
       </c>
       <c r="Q14">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="R14">
-        <v>2.37</v>
+        <v>2.29</v>
       </c>
       <c r="S14">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T14">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U14">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V14">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W14">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X14">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y14">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z14">
-        <v>4.33</v>
+        <v>4.9</v>
       </c>
       <c r="AA14">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB14">
         <v>2.12</v>
       </c>
       <c r="AC14">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="AD14">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE14">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF14">
         <v>1.7</v>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="AK14">
         <v>2.32</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="O16">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="P16">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="Q16">
         <v>4.18</v>
@@ -2935,7 +2935,7 @@
         <v>1.15</v>
       </c>
       <c r="T16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U16">
         <v>1.8</v>
@@ -2950,28 +2950,28 @@
         <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z16">
-        <v>5.65</v>
+        <v>5.75</v>
       </c>
       <c r="AA16">
         <v>1.4</v>
       </c>
       <c r="AB16">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="AC16">
         <v>2.02</v>
       </c>
       <c r="AD16">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AE16">
         <v>1.26</v>
       </c>
       <c r="AF16">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AG16">
         <v>2.6</v>
@@ -3083,10 +3083,10 @@
         <v>2.15</v>
       </c>
       <c r="O17">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P17">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="Q17">
         <v>2.7</v>
@@ -3095,16 +3095,16 @@
         <v>2.17</v>
       </c>
       <c r="S17">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T17">
         <v>3.04</v>
       </c>
       <c r="U17">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="V17">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W17">
         <v>1.11</v>
@@ -3116,7 +3116,7 @@
         <v>1.22</v>
       </c>
       <c r="Z17">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AA17">
         <v>1.65</v>
@@ -3137,7 +3137,7 @@
         <v>1.53</v>
       </c>
       <c r="AG17">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="O18">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="P18">
-        <v>3.75</v>
+        <v>3.46</v>
       </c>
       <c r="Q18">
         <v>2.25</v>
@@ -3276,13 +3276,13 @@
         <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z18">
         <v>4.5</v>
       </c>
       <c r="AA18">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AB18">
         <v>2.14</v>
@@ -3316,7 +3316,7 @@
         <v>1.25</v>
       </c>
       <c r="AK18">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O19">
         <v>3.7</v>
       </c>
       <c r="P19">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q19">
         <v>3.62</v>
@@ -3421,7 +3421,7 @@
         <v>2.4</v>
       </c>
       <c r="S19">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T19">
         <v>3.34</v>
@@ -3436,34 +3436,34 @@
         <v>1.11</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
         <v>1.12</v>
       </c>
       <c r="Z19">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AA19">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AB19">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AC19">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AD19">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AE19">
         <v>1.23</v>
       </c>
       <c r="AF19">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AG19">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="O20">
-        <v>3.51</v>
+        <v>3.66</v>
       </c>
       <c r="P20">
         <v>5.25</v>
@@ -3581,7 +3581,7 @@
         <v>2.28</v>
       </c>
       <c r="R20">
-        <v>2.24</v>
+        <v>2.09</v>
       </c>
       <c r="S20">
         <v>1.44</v>
@@ -3590,7 +3590,7 @@
         <v>2.68</v>
       </c>
       <c r="U20">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="V20">
         <v>1.35</v>
@@ -3602,7 +3602,7 @@
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z20">
         <v>3</v>
@@ -3934,10 +3934,10 @@
         <v>0</v>
       </c>
       <c r="AA22">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB22">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC22">
         <v>0</v>
@@ -4058,49 +4058,49 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.95</v>
+        <v>2.72</v>
       </c>
       <c r="O23">
-        <v>3.4</v>
+        <v>3.23</v>
       </c>
       <c r="P23">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="Q23">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="R23">
         <v>2.09</v>
       </c>
       <c r="S23">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T23">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U23">
         <v>2.5</v>
       </c>
       <c r="V23">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W23">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X23">
         <v>1.04</v>
       </c>
       <c r="Y23">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z23">
         <v>4.13</v>
       </c>
       <c r="AA23">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AB23">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AC23">
         <v>2.75</v>
@@ -4109,7 +4109,7 @@
         <v>1.43</v>
       </c>
       <c r="AE23">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF23">
         <v>1.6</v>
@@ -4221,25 +4221,25 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="O24">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P24">
-        <v>3.27</v>
+        <v>3.7</v>
       </c>
       <c r="Q24">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="R24">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="S24">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T24">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U24">
         <v>2.25</v>
@@ -4254,28 +4254,28 @@
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z24">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA24">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AB24">
-        <v>2.12</v>
+        <v>2.45</v>
       </c>
       <c r="AC24">
         <v>2.5</v>
       </c>
       <c r="AD24">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AE24">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AF24">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG24">
         <v>2.3</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK24">
         <v>2</v>
@@ -4384,16 +4384,16 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="O25">
-        <v>4.45</v>
+        <v>4.3</v>
       </c>
       <c r="P25">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Q25">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="R25">
         <v>2.5</v>
@@ -4411,34 +4411,34 @@
         <v>1.6</v>
       </c>
       <c r="W25">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X25">
         <v>1.03</v>
       </c>
       <c r="Y25">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z25">
-        <v>4.55</v>
+        <v>4.4</v>
       </c>
       <c r="AA25">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB25">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="AC25">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AD25">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AE25">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AF25">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG25">
         <v>2.1</v>
@@ -4457,7 +4457,7 @@
         <v>1.2</v>
       </c>
       <c r="AK25">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4710,25 +4710,25 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="O27">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="P27">
         <v>4.8</v>
       </c>
       <c r="Q27">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="R27">
         <v>2.7</v>
       </c>
       <c r="S27">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="T27">
-        <v>4.05</v>
+        <v>4.33</v>
       </c>
       <c r="U27">
         <v>1.98</v>
@@ -4746,19 +4746,19 @@
         <v>1.1</v>
       </c>
       <c r="Z27">
-        <v>5.95</v>
+        <v>5.9</v>
       </c>
       <c r="AA27">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB27">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="AC27">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AD27">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AE27">
         <v>1.32</v>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK27">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,25 +4873,25 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="O28">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="P28">
-        <v>5.6</v>
+        <v>5.75</v>
       </c>
       <c r="Q28">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="R28">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="S28">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T28">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="U28">
         <v>2.4</v>
@@ -4906,22 +4906,22 @@
         <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z28">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="AA28">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AB28">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AC28">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="AD28">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AE28">
         <v>1.17</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AK28">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5042,7 +5042,7 @@
         <v>3.75</v>
       </c>
       <c r="P29">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="Q29">
         <v>2.2</v>
@@ -5057,7 +5057,7 @@
         <v>2.97</v>
       </c>
       <c r="U29">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="V29">
         <v>1.39</v>
@@ -5069,19 +5069,19 @@
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z29">
         <v>3.3</v>
       </c>
       <c r="AA29">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AB29">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AC29">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="AD29">
         <v>1.28</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AK29">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5202,37 +5202,37 @@
         <v>2.2</v>
       </c>
       <c r="O30">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P30">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="Q30">
         <v>2.61</v>
       </c>
       <c r="R30">
-        <v>2.46</v>
+        <v>2.33</v>
       </c>
       <c r="S30">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T30">
         <v>3.8</v>
       </c>
       <c r="U30">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="V30">
         <v>1.57</v>
       </c>
       <c r="W30">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="Z30">
         <v>4</v>
@@ -5250,7 +5250,7 @@
         <v>1.47</v>
       </c>
       <c r="AE30">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF30">
         <v>1.55</v>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="N31">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="O31">
         <v>5.25</v>
@@ -5371,10 +5371,10 @@
         <v>1.37</v>
       </c>
       <c r="Q31">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="R31">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="S31">
         <v>1.21</v>
@@ -5383,22 +5383,22 @@
         <v>3.75</v>
       </c>
       <c r="U31">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V31">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="W31">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X31">
         <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z31">
-        <v>5.75</v>
+        <v>5.96</v>
       </c>
       <c r="AA31">
         <v>1.4</v>
@@ -5410,7 +5410,7 @@
         <v>2.1</v>
       </c>
       <c r="AD31">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AE31">
         <v>1.3</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AK31">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5688,16 +5688,16 @@
         </is>
       </c>
       <c r="N33">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="O33">
-        <v>4.58</v>
+        <v>4.45</v>
       </c>
       <c r="P33">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="Q33">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="R33">
         <v>2.5</v>
@@ -5706,7 +5706,7 @@
         <v>1.2</v>
       </c>
       <c r="T33">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U33">
         <v>2.05</v>
@@ -5721,31 +5721,31 @@
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z33">
-        <v>5.61</v>
+        <v>5.68</v>
       </c>
       <c r="AA33">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AB33">
         <v>2.6</v>
       </c>
       <c r="AC33">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AD33">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AE33">
         <v>1.28</v>
       </c>
       <c r="AF33">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG33">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>1.2</v>
       </c>
       <c r="AK33">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,7 +5851,7 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O34">
         <v>3.5</v>
@@ -5866,10 +5866,10 @@
         <v>2.3</v>
       </c>
       <c r="S34">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T34">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="U34">
         <v>2.45</v>
@@ -5878,10 +5878,10 @@
         <v>1.48</v>
       </c>
       <c r="W34">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X34">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y34">
         <v>1.2</v>
@@ -5890,10 +5890,10 @@
         <v>3.7</v>
       </c>
       <c r="AA34">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AB34">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AC34">
         <v>2.85</v>
@@ -5902,7 +5902,7 @@
         <v>1.33</v>
       </c>
       <c r="AE34">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF34">
         <v>1.62</v>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="O35">
         <v>3.3</v>
@@ -6023,40 +6023,40 @@
         <v>2.81</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y35">
         <v>1.33</v>
       </c>
       <c r="Z35">
-        <v>3.07</v>
+        <v>3.36</v>
       </c>
       <c r="AA35">
         <v>2.07</v>
       </c>
       <c r="AB35">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AC35">
         <v>3.5</v>
@@ -6065,13 +6065,13 @@
         <v>1.25</v>
       </c>
       <c r="AE35">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6180,7 +6180,7 @@
         <v>1.59</v>
       </c>
       <c r="O36">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="P36">
         <v>5.14</v>
@@ -6195,7 +6195,7 @@
         <v>1.35</v>
       </c>
       <c r="T36">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="U36">
         <v>2.65</v>
@@ -6216,13 +6216,13 @@
         <v>3.42</v>
       </c>
       <c r="AA36">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AB36">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC36">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AD36">
         <v>1.33</v>
@@ -6231,7 +6231,7 @@
         <v>1.11</v>
       </c>
       <c r="AF36">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AG36">
         <v>1.85</v>
@@ -6509,7 +6509,7 @@
         <v>3.2</v>
       </c>
       <c r="P38">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="Q38">
         <v>2.78</v>
@@ -6530,10 +6530,10 @@
         <v>1.37</v>
       </c>
       <c r="W38">
+        <v>1.07</v>
+      </c>
+      <c r="X38">
         <v>1.03</v>
-      </c>
-      <c r="X38">
-        <v>1.05</v>
       </c>
       <c r="Y38">
         <v>1.24</v>
@@ -6551,13 +6551,13 @@
         <v>3.14</v>
       </c>
       <c r="AD38">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE38">
         <v>1.06</v>
       </c>
       <c r="AF38">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG38">
         <v>2.05</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK38">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6669,7 +6669,7 @@
         <v>1.22</v>
       </c>
       <c r="O39">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="P39">
         <v>8</v>
@@ -6678,19 +6678,19 @@
         <v>1.57</v>
       </c>
       <c r="R39">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="S39">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T39">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="U39">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="V39">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="W39">
         <v>1.14</v>
@@ -6699,10 +6699,10 @@
         <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z39">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AA39">
         <v>1.42</v>
@@ -6711,13 +6711,13 @@
         <v>2.55</v>
       </c>
       <c r="AC39">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AD39">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AE39">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF39">
         <v>1.99</v>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AK39">
         <v>4</v>
@@ -6829,16 +6829,16 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="O40">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="P40">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="Q40">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="R40">
         <v>2.38</v>
@@ -6847,7 +6847,7 @@
         <v>1.25</v>
       </c>
       <c r="T40">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U40">
         <v>2.32</v>
@@ -6856,10 +6856,10 @@
         <v>1.53</v>
       </c>
       <c r="W40">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X40">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
         <v>1.18</v>
@@ -6868,13 +6868,13 @@
         <v>4.5</v>
       </c>
       <c r="AA40">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AB40">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AC40">
-        <v>2.33</v>
+        <v>2.47</v>
       </c>
       <c r="AD40">
         <v>1.5</v>
@@ -6883,7 +6883,7 @@
         <v>1.19</v>
       </c>
       <c r="AF40">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AG40">
         <v>2.25</v>
@@ -6902,7 +6902,7 @@
         <v>1.25</v>
       </c>
       <c r="AK40">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7001,10 +7001,10 @@
         <v>2</v>
       </c>
       <c r="Q41">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="R41">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="S41">
         <v>1.29</v>
@@ -7013,10 +7013,10 @@
         <v>3.25</v>
       </c>
       <c r="U41">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="V41">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W41">
         <v>1.08</v>
@@ -7031,16 +7031,16 @@
         <v>3.98</v>
       </c>
       <c r="AA41">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AB41">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AC41">
         <v>2.59</v>
       </c>
       <c r="AD41">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AE41">
         <v>1.12</v>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AK41">
         <v>1.28</v>
@@ -7170,19 +7170,19 @@
         <v>2.18</v>
       </c>
       <c r="S42">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T42">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="U42">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="V42">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="W42">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X42">
         <v>1.02</v>
@@ -7200,19 +7200,19 @@
         <v>2.1</v>
       </c>
       <c r="AC42">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="AD42">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AE42">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AF42">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG42">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>1.22</v>
       </c>
       <c r="AK42">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="Q43">
-        <v>2.48</v>
+        <v>2.12</v>
       </c>
       <c r="R43">
         <v>2.2</v>
@@ -7336,7 +7336,7 @@
         <v>1.33</v>
       </c>
       <c r="T43">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="U43">
         <v>2.8</v>
@@ -7357,25 +7357,25 @@
         <v>3.1</v>
       </c>
       <c r="AA43">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AB43">
-        <v>1.77</v>
+        <v>1.98</v>
       </c>
       <c r="AC43">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="AD43">
         <v>1.27</v>
       </c>
       <c r="AE43">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF43">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="AG43">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AK43">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7493,7 +7493,7 @@
         <v>2.28</v>
       </c>
       <c r="R44">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S44">
         <v>1.3</v>
@@ -7505,7 +7505,7 @@
         <v>2.63</v>
       </c>
       <c r="V44">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W44">
         <v>1.1</v>
@@ -7523,7 +7523,7 @@
         <v>1.81</v>
       </c>
       <c r="AB44">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AC44">
         <v>2.8</v>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK44">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="O46">
-        <v>3.77</v>
+        <v>3.5</v>
       </c>
       <c r="P46">
-        <v>5</v>
+        <v>5.14</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -7970,19 +7970,19 @@
         </is>
       </c>
       <c r="N47">
-        <v>4.78</v>
+        <v>3.25</v>
       </c>
       <c r="O47">
-        <v>3.92</v>
+        <v>3.7</v>
       </c>
       <c r="P47">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="Q47">
         <v>4.31</v>
       </c>
       <c r="R47">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="S47">
         <v>1.28</v>
@@ -7991,16 +7991,16 @@
         <v>3.3</v>
       </c>
       <c r="U47">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="V47">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="W47">
         <v>1.09</v>
       </c>
       <c r="X47">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
         <v>1.22</v>
@@ -8027,7 +8027,7 @@
         <v>1.6</v>
       </c>
       <c r="AG47">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK47">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,19 +8133,19 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="O48">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P48">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="Q48">
-        <v>3.16</v>
+        <v>2.88</v>
       </c>
       <c r="R48">
-        <v>2.09</v>
+        <v>1.91</v>
       </c>
       <c r="S48">
         <v>1.44</v>
@@ -8166,22 +8166,22 @@
         <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="Z48">
         <v>2.83</v>
       </c>
       <c r="AA48">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AB48">
         <v>1.65</v>
       </c>
       <c r="AC48">
-        <v>3.86</v>
+        <v>3.91</v>
       </c>
       <c r="AD48">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AE48">
         <v>1.02</v>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK48">
         <v>1.52</v>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="N49">
-        <v>3.19</v>
+        <v>3.15</v>
       </c>
       <c r="O49">
         <v>3.35</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="O50">
         <v>6.9</v>
@@ -8468,55 +8468,55 @@
         <v>12</v>
       </c>
       <c r="Q50">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="R50">
-        <v>2.72</v>
+        <v>3.12</v>
       </c>
       <c r="S50">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="T50">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="U50">
         <v>2.06</v>
       </c>
       <c r="V50">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="W50">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X50">
         <v>0</v>
       </c>
       <c r="Y50">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z50">
-        <v>5.1</v>
+        <v>5.95</v>
       </c>
       <c r="AA50">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="AB50">
-        <v>2.49</v>
+        <v>2.77</v>
       </c>
       <c r="AC50">
-        <v>2.22</v>
+        <v>2.05</v>
       </c>
       <c r="AD50">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AE50">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AF50">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AG50">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AK50">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,25 +8622,25 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="O51">
         <v>3.6</v>
       </c>
       <c r="P51">
-        <v>4.05</v>
+        <v>3.61</v>
       </c>
       <c r="Q51">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R51">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="S51">
         <v>1.3</v>
       </c>
       <c r="T51">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U51">
         <v>2.45</v>
@@ -8649,28 +8649,28 @@
         <v>1.48</v>
       </c>
       <c r="W51">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y51">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z51">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA51">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB51">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="AC51">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="AD51">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE51">
         <v>1.14</v>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK51">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="O52">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P52">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="Q52">
         <v>2.15</v>
@@ -8806,7 +8806,7 @@
         <v>3.25</v>
       </c>
       <c r="U52">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="V52">
         <v>1.48</v>
@@ -8818,31 +8818,31 @@
         <v>1.04</v>
       </c>
       <c r="Y52">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z52">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA52">
         <v>1.72</v>
       </c>
       <c r="AB52">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC52">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AD52">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE52">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF52">
         <v>1.72</v>
       </c>
       <c r="AG52">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK52">
         <v>2.2</v>
@@ -9114,19 +9114,19 @@
         <v>2.05</v>
       </c>
       <c r="O54">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P54">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="Q54">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="R54">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="S54">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T54">
         <v>3.3</v>
@@ -9147,10 +9147,10 @@
         <v>1.18</v>
       </c>
       <c r="Z54">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="AA54">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB54">
         <v>2.05</v>
@@ -9184,7 +9184,7 @@
         <v>1.29</v>
       </c>
       <c r="AK54">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9283,16 +9283,16 @@
         <v>0</v>
       </c>
       <c r="Q55">
-        <v>2.55</v>
+        <v>2.18</v>
       </c>
       <c r="R55">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="S55">
         <v>1.4</v>
       </c>
       <c r="T55">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="U55">
         <v>2.8</v>
@@ -9301,7 +9301,7 @@
         <v>1.38</v>
       </c>
       <c r="W55">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X55">
         <v>1.02</v>
@@ -9313,16 +9313,16 @@
         <v>3</v>
       </c>
       <c r="AA55">
-        <v>2.06</v>
+        <v>1.78</v>
       </c>
       <c r="AB55">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="AC55">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="AD55">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="AE55">
         <v>1.05</v>
@@ -9461,37 +9461,37 @@
         <v>3.6</v>
       </c>
       <c r="V56">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="W56">
         <v>1.04</v>
       </c>
       <c r="X56">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Y56">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Z56">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AA56">
-        <v>2.52</v>
+        <v>2.73</v>
       </c>
       <c r="AB56">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC56">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AD56">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE56">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF56">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AG56">
         <v>1.64</v>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AK56">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="O57">
         <v>3.5</v>
       </c>
       <c r="P57">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="O58">
-        <v>3.6</v>
+        <v>3.23</v>
       </c>
       <c r="P58">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -9802,10 +9802,10 @@
         <v>0</v>
       </c>
       <c r="AA58">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB58">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC58">
         <v>0</v>
@@ -9926,28 +9926,28 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="O59">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="P59">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="Q59">
         <v>2.3</v>
       </c>
       <c r="R59">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="S59">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T59">
         <v>4</v>
       </c>
       <c r="U59">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="V59">
         <v>1.73</v>
@@ -9959,31 +9959,31 @@
         <v>1.02</v>
       </c>
       <c r="Y59">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z59">
-        <v>5.4</v>
+        <v>5.75</v>
       </c>
       <c r="AA59">
         <v>1.4</v>
       </c>
       <c r="AB59">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AC59">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AD59">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AE59">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AF59">
         <v>1.4</v>
       </c>
       <c r="AG59">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>1.3</v>
       </c>
       <c r="AK59">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,10 +10089,10 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="O60">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="P60">
         <v>5.5</v>
@@ -10101,22 +10101,22 @@
         <v>1.9</v>
       </c>
       <c r="R60">
-        <v>2.54</v>
+        <v>2.63</v>
       </c>
       <c r="S60">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T60">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U60">
         <v>2.1</v>
       </c>
       <c r="V60">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W60">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X60">
         <v>1.02</v>
@@ -10125,13 +10125,13 @@
         <v>1.1</v>
       </c>
       <c r="Z60">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA60">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AB60">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="AC60">
         <v>2.19</v>
@@ -10143,7 +10143,7 @@
         <v>1.24</v>
       </c>
       <c r="AF60">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AG60">
         <v>2.18</v>
@@ -10162,7 +10162,7 @@
         <v>1.14</v>
       </c>
       <c r="AK60">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10255,7 +10255,7 @@
         <v>1.95</v>
       </c>
       <c r="O61">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="P61">
         <v>3.5</v>
@@ -10288,25 +10288,25 @@
         <v>1.12</v>
       </c>
       <c r="Z61">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA61">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AB61">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AC61">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AD61">
         <v>1.76</v>
       </c>
       <c r="AE61">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AF61">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AG61">
         <v>2.8</v>
@@ -10325,7 +10325,7 @@
         <v>1.25</v>
       </c>
       <c r="AK61">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="O62">
-        <v>3.07</v>
+        <v>3.44</v>
       </c>
       <c r="P62">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10590,19 +10590,19 @@
         <v>3.2</v>
       </c>
       <c r="R63">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="S63">
         <v>1.57</v>
       </c>
       <c r="T63">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="U63">
         <v>3.25</v>
       </c>
       <c r="V63">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="W63">
         <v>1.01</v>
@@ -10614,7 +10614,7 @@
         <v>1.44</v>
       </c>
       <c r="Z63">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="AA63">
         <v>2.53</v>
@@ -10629,13 +10629,13 @@
         <v>1.17</v>
       </c>
       <c r="AE63">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF63">
         <v>2.05</v>
       </c>
       <c r="AG63">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK63">
         <v>1.42</v>
@@ -10744,13 +10744,13 @@
         <v>2.45</v>
       </c>
       <c r="O64">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P64">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q64">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="R64">
         <v>2.3</v>
@@ -10762,13 +10762,13 @@
         <v>2.8</v>
       </c>
       <c r="U64">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="V64">
         <v>1.63</v>
       </c>
       <c r="W64">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X64">
         <v>1.02</v>
@@ -10786,7 +10786,7 @@
         <v>2.4</v>
       </c>
       <c r="AC64">
-        <v>2.27</v>
+        <v>2.7</v>
       </c>
       <c r="AD64">
         <v>1.47</v>
@@ -10798,7 +10798,7 @@
         <v>1.53</v>
       </c>
       <c r="AG64">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK64">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10904,16 +10904,16 @@
         </is>
       </c>
       <c r="N65">
-        <v>4.97</v>
+        <v>4.5</v>
       </c>
       <c r="O65">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="P65">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="Q65">
-        <v>5.47</v>
+        <v>4.8</v>
       </c>
       <c r="R65">
         <v>2.3</v>
@@ -10922,7 +10922,7 @@
         <v>1.33</v>
       </c>
       <c r="T65">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="U65">
         <v>2.47</v>
@@ -10931,7 +10931,7 @@
         <v>1.48</v>
       </c>
       <c r="W65">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X65">
         <v>1.04</v>
@@ -10943,10 +10943,10 @@
         <v>3.84</v>
       </c>
       <c r="AA65">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AB65">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AC65">
         <v>2.7</v>
@@ -10977,7 +10977,7 @@
         <v>2.28</v>
       </c>
       <c r="AK65">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,16 +11067,16 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O66">
-        <v>3.51</v>
+        <v>3.4</v>
       </c>
       <c r="P66">
         <v>2.7</v>
       </c>
       <c r="Q66">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="R66">
         <v>2.37</v>
@@ -11106,7 +11106,7 @@
         <v>4.05</v>
       </c>
       <c r="AA66">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AB66">
         <v>2.15</v>
@@ -11115,16 +11115,16 @@
         <v>2.75</v>
       </c>
       <c r="AD66">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AE66">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF66">
         <v>1.55</v>
       </c>
       <c r="AG66">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11236,7 +11236,7 @@
         <v>3.65</v>
       </c>
       <c r="P67">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="Q67">
         <v>3.4</v>
@@ -11245,10 +11245,10 @@
         <v>2.5</v>
       </c>
       <c r="S67">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T67">
-        <v>3.75</v>
+        <v>3.66</v>
       </c>
       <c r="U67">
         <v>2.05</v>
@@ -11260,25 +11260,25 @@
         <v>1.18</v>
       </c>
       <c r="X67">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z67">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="AA67">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AB67">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="AC67">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AD67">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AE67">
         <v>1.25</v>
@@ -11287,7 +11287,7 @@
         <v>1.4</v>
       </c>
       <c r="AG67">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11393,19 +11393,19 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="O68">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P68">
-        <v>2.55</v>
+        <v>2.36</v>
       </c>
       <c r="Q68">
         <v>2.91</v>
       </c>
       <c r="R68">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="S68">
         <v>1.25</v>
@@ -11447,7 +11447,7 @@
         <v>1.18</v>
       </c>
       <c r="AF68">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG68">
         <v>2.5</v>
@@ -12048,34 +12048,34 @@
         <v>1.62</v>
       </c>
       <c r="O72">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P72">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="Q72">
         <v>2.16</v>
       </c>
       <c r="R72">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S72">
         <v>1.3</v>
       </c>
       <c r="T72">
-        <v>2.8</v>
+        <v>2.99</v>
       </c>
       <c r="U72">
         <v>2.73</v>
       </c>
       <c r="V72">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W72">
         <v>1.06</v>
       </c>
       <c r="X72">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y72">
         <v>1.26</v>
@@ -12096,13 +12096,13 @@
         <v>1.33</v>
       </c>
       <c r="AE72">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF72">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AG72">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>1.09</v>
       </c>
       <c r="AK72">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12211,7 +12211,7 @@
         <v>2.13</v>
       </c>
       <c r="O73">
-        <v>3.62</v>
+        <v>3.74</v>
       </c>
       <c r="P73">
         <v>2.76</v>
@@ -12226,7 +12226,7 @@
         <v>1.25</v>
       </c>
       <c r="T73">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="U73">
         <v>2.25</v>
@@ -12235,25 +12235,25 @@
         <v>1.6</v>
       </c>
       <c r="W73">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X73">
         <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z73">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AA73">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AB73">
         <v>2.55</v>
       </c>
       <c r="AC73">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AD73">
         <v>1.49</v>
@@ -12265,7 +12265,7 @@
         <v>1.44</v>
       </c>
       <c r="AG73">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12416,7 +12416,7 @@
         <v>3.25</v>
       </c>
       <c r="AC74">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AD74">
         <v>2</v>
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.94</v>
+        <v>2.87</v>
       </c>
       <c r="O75">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P75">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="Q75">
         <v>3.3</v>
@@ -12564,10 +12564,10 @@
         <v>1.05</v>
       </c>
       <c r="X75">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y75">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z75">
         <v>3.25</v>
@@ -12579,7 +12579,7 @@
         <v>1.78</v>
       </c>
       <c r="AC75">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AD75">
         <v>1.25</v>
@@ -12591,7 +12591,7 @@
         <v>1.75</v>
       </c>
       <c r="AG75">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>1.53</v>
       </c>
       <c r="AK75">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12697,10 +12697,10 @@
         </is>
       </c>
       <c r="N76">
+        <v>3.55</v>
+      </c>
+      <c r="O76">
         <v>3.5</v>
-      </c>
-      <c r="O76">
-        <v>3.75</v>
       </c>
       <c r="P76">
         <v>1.91</v>
@@ -12709,7 +12709,7 @@
         <v>4.16</v>
       </c>
       <c r="R76">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="S76">
         <v>1.25</v>
@@ -12718,22 +12718,22 @@
         <v>3.45</v>
       </c>
       <c r="U76">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="V76">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W76">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X76">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y76">
         <v>1.18</v>
       </c>
       <c r="Z76">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA76">
         <v>1.62</v>
@@ -12742,10 +12742,10 @@
         <v>2.29</v>
       </c>
       <c r="AC76">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AD76">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE76">
         <v>1.18</v>
@@ -12767,7 +12767,7 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK76">
         <v>1.29</v>
@@ -12860,10 +12860,10 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="O77">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="P77">
         <v>5.39</v>
@@ -13023,16 +13023,16 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="O78">
         <v>3.73</v>
       </c>
       <c r="P78">
-        <v>2.35</v>
+        <v>2.17</v>
       </c>
       <c r="Q78">
-        <v>2.63</v>
+        <v>2.92</v>
       </c>
       <c r="R78">
         <v>2.5</v>
@@ -13041,7 +13041,7 @@
         <v>1.2</v>
       </c>
       <c r="T78">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="U78">
         <v>1.95</v>
@@ -13056,10 +13056,10 @@
         <v>1.01</v>
       </c>
       <c r="Y78">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z78">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AA78">
         <v>1.4</v>
@@ -13071,7 +13071,7 @@
         <v>1.96</v>
       </c>
       <c r="AD78">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AE78">
         <v>1.3</v>
@@ -13080,7 +13080,7 @@
         <v>1.3</v>
       </c>
       <c r="AG78">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.47</v>
+        <v>1.23</v>
       </c>
       <c r="AK78">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.96</v>
+        <v>1.79</v>
       </c>
       <c r="O79">
-        <v>3.48</v>
+        <v>3.45</v>
       </c>
       <c r="P79">
         <v>3.1</v>
       </c>
       <c r="Q79">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R79">
         <v>2.5</v>
       </c>
       <c r="S79">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T79">
-        <v>3.36</v>
+        <v>3.75</v>
       </c>
       <c r="U79">
         <v>2.27</v>
       </c>
       <c r="V79">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W79">
         <v>1.12</v>
       </c>
       <c r="X79">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z79">
         <v>4.8</v>
       </c>
       <c r="AA79">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AB79">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="AC79">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AD79">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AE79">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF79">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG79">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK79">
         <v>1.85</v>
@@ -13349,16 +13349,16 @@
         </is>
       </c>
       <c r="N80">
-        <v>4.45</v>
+        <v>4.7</v>
       </c>
       <c r="O80">
-        <v>4.85</v>
+        <v>4.55</v>
       </c>
       <c r="P80">
         <v>1.45</v>
       </c>
       <c r="Q80">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="R80">
         <v>2.88</v>
@@ -13373,7 +13373,7 @@
         <v>1.83</v>
       </c>
       <c r="V80">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="W80">
         <v>1.25</v>
@@ -13385,19 +13385,19 @@
         <v>1.04</v>
       </c>
       <c r="Z80">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="AA80">
         <v>1.25</v>
       </c>
       <c r="AB80">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AC80">
         <v>1.67</v>
       </c>
       <c r="AD80">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AE80">
         <v>1.43</v>
@@ -13512,19 +13512,19 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="O81">
-        <v>5.05</v>
+        <v>5.9</v>
       </c>
       <c r="P81">
         <v>5.6</v>
       </c>
       <c r="Q81">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="R81">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="S81">
         <v>1.13</v>
@@ -13539,7 +13539,7 @@
         <v>1.97</v>
       </c>
       <c r="W81">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X81">
         <v>1.01</v>
@@ -13548,7 +13548,7 @@
         <v>1.02</v>
       </c>
       <c r="Z81">
-        <v>6.5</v>
+        <v>7.7</v>
       </c>
       <c r="AA81">
         <v>1.27</v>
@@ -13675,31 +13675,31 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="O82">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="P82">
-        <v>5.35</v>
+        <v>4.65</v>
       </c>
       <c r="Q82">
         <v>1.85</v>
       </c>
       <c r="R82">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="S82">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T82">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="U82">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V82">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="W82">
         <v>1.25</v>
@@ -13714,16 +13714,16 @@
         <v>7.5</v>
       </c>
       <c r="AA82">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AB82">
         <v>3.6</v>
       </c>
       <c r="AC82">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AD82">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AE82">
         <v>1.44</v>
@@ -13732,7 +13732,7 @@
         <v>1.36</v>
       </c>
       <c r="AG82">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>1.12</v>
       </c>
       <c r="AK82">
-        <v>2.56</v>
+        <v>2.51</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13838,28 +13838,28 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.13</v>
+        <v>2.24</v>
       </c>
       <c r="O83">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="P83">
         <v>2.41</v>
       </c>
       <c r="Q83">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="R83">
         <v>2.7</v>
       </c>
       <c r="S83">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T83">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="U83">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="V83">
         <v>1.93</v>
@@ -13886,7 +13886,7 @@
         <v>1.75</v>
       </c>
       <c r="AD83">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AE83">
         <v>1.38</v>
@@ -13895,7 +13895,7 @@
         <v>1.3</v>
       </c>
       <c r="AG83">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -14025,7 +14025,7 @@
         <v>3</v>
       </c>
       <c r="V84">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W84">
         <v>1.04</v>
@@ -14034,7 +14034,7 @@
         <v>1.03</v>
       </c>
       <c r="Y84">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="Z84">
         <v>2.9</v>
@@ -14043,7 +14043,7 @@
         <v>2.11</v>
       </c>
       <c r="AB84">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC84">
         <v>3.6</v>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.69</v>
+        <v>1.26</v>
       </c>
       <c r="AK84">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14167,22 +14167,22 @@
         <v>1.9</v>
       </c>
       <c r="O85">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P85">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="Q85">
         <v>2.38</v>
       </c>
       <c r="R85">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S85">
         <v>1.32</v>
       </c>
       <c r="T85">
-        <v>2.87</v>
+        <v>3.21</v>
       </c>
       <c r="U85">
         <v>2.5</v>
@@ -14197,10 +14197,10 @@
         <v>1</v>
       </c>
       <c r="Y85">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z85">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AA85">
         <v>1.77</v>
@@ -14215,13 +14215,13 @@
         <v>1.36</v>
       </c>
       <c r="AE85">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF85">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AG85">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="O86">
-        <v>3.45</v>
+        <v>3.23</v>
       </c>
       <c r="P86">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="Q86">
         <v>2.3</v>
@@ -14360,22 +14360,22 @@
         <v>1.03</v>
       </c>
       <c r="Y86">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z86">
         <v>2.7</v>
       </c>
       <c r="AA86">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AB86">
         <v>1.64</v>
       </c>
       <c r="AC86">
-        <v>4.05</v>
+        <v>4.18</v>
       </c>
       <c r="AD86">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AE86">
         <v>1.02</v>
@@ -14397,7 +14397,7 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK86">
         <v>2.09</v>
@@ -14490,7 +14490,7 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="O87">
         <v>3.4</v>
@@ -14502,7 +14502,7 @@
         <v>2.95</v>
       </c>
       <c r="R87">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="S87">
         <v>1.3</v>
@@ -14514,10 +14514,10 @@
         <v>2.5</v>
       </c>
       <c r="V87">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W87">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X87">
         <v>1</v>
@@ -14529,19 +14529,19 @@
         <v>4</v>
       </c>
       <c r="AA87">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AB87">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AC87">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AD87">
         <v>1.36</v>
       </c>
       <c r="AE87">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF87">
         <v>1.6</v>
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="O89">
-        <v>4.2</v>
+        <v>3.72</v>
       </c>
       <c r="P89">
-        <v>5.27</v>
+        <v>4.25</v>
       </c>
       <c r="Q89">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="R89">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="S89">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T89">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="U89">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="V89">
         <v>1.51</v>
       </c>
       <c r="W89">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X89">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z89">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA89">
         <v>1.61</v>
       </c>
       <c r="AB89">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC89">
-        <v>2.55</v>
+        <v>2.41</v>
       </c>
       <c r="AD89">
         <v>1.48</v>
       </c>
       <c r="AE89">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF89">
         <v>1.7</v>
       </c>
       <c r="AG89">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14979,25 +14979,25 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O90">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P90">
-        <v>2.91</v>
+        <v>2.8</v>
       </c>
       <c r="Q90">
         <v>2.85</v>
       </c>
       <c r="R90">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="S90">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T90">
-        <v>3.19</v>
+        <v>2.91</v>
       </c>
       <c r="U90">
         <v>2.59</v>
@@ -15006,37 +15006,37 @@
         <v>1.41</v>
       </c>
       <c r="W90">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X90">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y90">
         <v>1.2</v>
       </c>
       <c r="Z90">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AA90">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AB90">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC90">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="AD90">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE90">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF90">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG90">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15145,22 +15145,22 @@
         <v>2.74</v>
       </c>
       <c r="O91">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="P91">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="Q91">
         <v>3.3</v>
       </c>
       <c r="R91">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="S91">
         <v>1.49</v>
       </c>
       <c r="T91">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="U91">
         <v>3.28</v>
@@ -15169,7 +15169,7 @@
         <v>1.29</v>
       </c>
       <c r="W91">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X91">
         <v>1.05</v>
@@ -15178,19 +15178,19 @@
         <v>1.39</v>
       </c>
       <c r="Z91">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="AA91">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="AB91">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AC91">
         <v>4.2</v>
       </c>
       <c r="AD91">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE91">
         <v>1.03</v>
@@ -15199,7 +15199,7 @@
         <v>1.95</v>
       </c>
       <c r="AG91">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="O96">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P96">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="Q96">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R96">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S96">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T96">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U96">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V96">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W96">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X96">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y96">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z96">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AA96">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AB96">
         <v>1.67</v>
       </c>
       <c r="AC96">
-        <v>3.45</v>
+        <v>3.72</v>
       </c>
       <c r="AD96">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AE96">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF96">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG96">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK96">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16289,58 +16289,58 @@
         <v>3.25</v>
       </c>
       <c r="P98">
+        <v>2.05</v>
+      </c>
+      <c r="Q98">
+        <v>4.1</v>
+      </c>
+      <c r="R98">
         <v>2.1</v>
       </c>
-      <c r="Q98">
-        <v>3.98</v>
-      </c>
-      <c r="R98">
-        <v>2.15</v>
-      </c>
       <c r="S98">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T98">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="U98">
         <v>3</v>
       </c>
       <c r="V98">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W98">
         <v>1.07</v>
       </c>
       <c r="X98">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y98">
         <v>1.35</v>
       </c>
       <c r="Z98">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="AA98">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AB98">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AC98">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="AD98">
         <v>1.24</v>
       </c>
       <c r="AE98">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF98">
         <v>1.83</v>
       </c>
       <c r="AG98">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AK98">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16446,80 +16446,80 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.21</v>
+        <v>2.03</v>
       </c>
       <c r="O99">
-        <v>3.18</v>
+        <v>2.7</v>
       </c>
       <c r="P99">
-        <v>3.59</v>
+        <v>4.45</v>
       </c>
       <c r="Q99">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="R99">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="S99">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="T99">
-        <v>2.41</v>
+        <v>2.27</v>
       </c>
       <c r="U99">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="V99">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W99">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X99">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="Y99">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z99">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="AA99">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AB99">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AC99">
-        <v>4.05</v>
+        <v>3.92</v>
       </c>
       <c r="AD99">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE99">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF99">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="AG99">
+        <v>1.73</v>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ99">
+        <v>1.4</v>
+      </c>
+      <c r="AK99">
         <v>1.77</v>
-      </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ99">
-        <v>1.36</v>
-      </c>
-      <c r="AK99">
-        <v>1.67</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16775,7 +16775,7 @@
         <v>2.39</v>
       </c>
       <c r="O101">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="P101">
         <v>2.85</v>
@@ -16790,7 +16790,7 @@
         <v>1.56</v>
       </c>
       <c r="T101">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="U101">
         <v>3.5</v>
@@ -16829,7 +16829,7 @@
         <v>2.01</v>
       </c>
       <c r="AG101">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16935,49 +16935,49 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="O102">
-        <v>6.75</v>
+        <v>7.2</v>
       </c>
       <c r="P102">
-        <v>9.5</v>
+        <v>9.75</v>
       </c>
       <c r="Q102">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="R102">
-        <v>3.33</v>
+        <v>2.98</v>
       </c>
       <c r="S102">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="T102">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="U102">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="V102">
         <v>1.89</v>
       </c>
       <c r="W102">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X102">
         <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Z102">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="AA102">
         <v>1.22</v>
       </c>
       <c r="AB102">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AC102">
         <v>1.54</v>
@@ -16989,7 +16989,7 @@
         <v>1.44</v>
       </c>
       <c r="AF102">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG102">
         <v>2.1</v>
@@ -17424,16 +17424,16 @@
         </is>
       </c>
       <c r="N105">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="O105">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="P105">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q105">
-        <v>4.84</v>
+        <v>4.83</v>
       </c>
       <c r="R105">
         <v>2.25</v>
@@ -17442,7 +17442,7 @@
         <v>1.3</v>
       </c>
       <c r="T105">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="U105">
         <v>2.6</v>
@@ -17451,34 +17451,34 @@
         <v>1.44</v>
       </c>
       <c r="W105">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X105">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y105">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z105">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="AA105">
         <v>1.78</v>
       </c>
       <c r="AB105">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AC105">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="AD105">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE105">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF105">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG105">
         <v>2</v>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="AK105">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17587,55 +17587,55 @@
         </is>
       </c>
       <c r="N106">
-        <v>3.79</v>
+        <v>4.5</v>
       </c>
       <c r="O106">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="P106">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="Q106">
-        <v>5.07</v>
+        <v>5.23</v>
       </c>
       <c r="R106">
         <v>2.15</v>
       </c>
       <c r="S106">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T106">
-        <v>2.85</v>
+        <v>2.77</v>
       </c>
       <c r="U106">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="V106">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W106">
         <v>1.05</v>
       </c>
       <c r="X106">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y106">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z106">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AA106">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB106">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AC106">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD106">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE106">
         <v>1.1</v>
@@ -17644,7 +17644,7 @@
         <v>1.85</v>
       </c>
       <c r="AG106">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK106">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17750,77 +17750,77 @@
         </is>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O107">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P107">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q107">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="R107">
         <v>2.1</v>
       </c>
       <c r="S107">
+        <v>1.43</v>
+      </c>
+      <c r="T107">
+        <v>2.53</v>
+      </c>
+      <c r="U107">
+        <v>3.02</v>
+      </c>
+      <c r="V107">
+        <v>1.34</v>
+      </c>
+      <c r="W107">
+        <v>1.07</v>
+      </c>
+      <c r="X107">
+        <v>1.06</v>
+      </c>
+      <c r="Y107">
         <v>1.36</v>
       </c>
-      <c r="T107">
-        <v>2.88</v>
-      </c>
-      <c r="U107">
-        <v>2.88</v>
-      </c>
-      <c r="V107">
+      <c r="Z107">
+        <v>2.9</v>
+      </c>
+      <c r="AA107">
+        <v>2.13</v>
+      </c>
+      <c r="AB107">
+        <v>1.7</v>
+      </c>
+      <c r="AC107">
+        <v>3.9</v>
+      </c>
+      <c r="AD107">
+        <v>1.27</v>
+      </c>
+      <c r="AE107">
+        <v>1.06</v>
+      </c>
+      <c r="AF107">
+        <v>1.83</v>
+      </c>
+      <c r="AG107">
+        <v>1.85</v>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ107">
         <v>1.36</v>
-      </c>
-      <c r="W107">
-        <v>1.06</v>
-      </c>
-      <c r="X107">
-        <v>1.03</v>
-      </c>
-      <c r="Y107">
-        <v>1.3</v>
-      </c>
-      <c r="Z107">
-        <v>3.2</v>
-      </c>
-      <c r="AA107">
-        <v>2</v>
-      </c>
-      <c r="AB107">
-        <v>1.73</v>
-      </c>
-      <c r="AC107">
-        <v>3.5</v>
-      </c>
-      <c r="AD107">
-        <v>1.25</v>
-      </c>
-      <c r="AE107">
-        <v>1.08</v>
-      </c>
-      <c r="AF107">
-        <v>1.75</v>
-      </c>
-      <c r="AG107">
-        <v>2.03</v>
-      </c>
-      <c r="AH107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ107">
-        <v>1.29</v>
       </c>
       <c r="AK107">
         <v>1.6</v>
@@ -18082,25 +18082,25 @@
         <v>3.45</v>
       </c>
       <c r="P109">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Q109">
-        <v>2.37</v>
+        <v>2.42</v>
       </c>
       <c r="R109">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="S109">
         <v>1.36</v>
       </c>
       <c r="T109">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="U109">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="V109">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W109">
         <v>1.06</v>
@@ -18112,25 +18112,25 @@
         <v>1.3</v>
       </c>
       <c r="Z109">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA109">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB109">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC109">
         <v>3.64</v>
       </c>
       <c r="AD109">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE109">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF109">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AG109">
         <v>1.91</v>
@@ -18149,7 +18149,7 @@
         <v>1.22</v>
       </c>
       <c r="AK109">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18408,7 +18408,7 @@
         <v>3.1</v>
       </c>
       <c r="P111">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="Q111">
         <v>3.1</v>
@@ -18420,43 +18420,43 @@
         <v>1.35</v>
       </c>
       <c r="T111">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="U111">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="V111">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W111">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X111">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="Z111">
-        <v>3.5</v>
+        <v>3.66</v>
       </c>
       <c r="AA111">
         <v>1.82</v>
       </c>
       <c r="AB111">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AC111">
         <v>3.2</v>
       </c>
       <c r="AD111">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE111">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF111">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG111">
         <v>2.1</v>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK111">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18728,22 +18728,22 @@
         </is>
       </c>
       <c r="N113">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="O113">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P113">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q113">
-        <v>4.16</v>
+        <v>4.09</v>
       </c>
       <c r="R113">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="S113">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T113">
         <v>2.9</v>
@@ -18758,34 +18758,34 @@
         <v>1.06</v>
       </c>
       <c r="X113">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y113">
         <v>1.28</v>
       </c>
       <c r="Z113">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="AA113">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB113">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AC113">
         <v>3.2</v>
       </c>
       <c r="AD113">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE113">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF113">
         <v>1.6</v>
       </c>
       <c r="AG113">
-        <v>2.12</v>
+        <v>2.01</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18891,28 +18891,28 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="O114">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="P114">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="Q114">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="R114">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="S114">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T114">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U114">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="V114">
         <v>1.49</v>
@@ -18924,16 +18924,16 @@
         <v>1.01</v>
       </c>
       <c r="Y114">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z114">
-        <v>4.1</v>
+        <v>4.32</v>
       </c>
       <c r="AA114">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AB114">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AC114">
         <v>2.65</v>
@@ -18961,7 +18961,7 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AK114">
         <v>1.75</v>
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="O115">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="P115">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q115">
         <v>1.55</v>
@@ -19069,16 +19069,16 @@
         <v>2.75</v>
       </c>
       <c r="S115">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="T115">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U115">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="V115">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W115">
         <v>1.11</v>
@@ -19093,7 +19093,7 @@
         <v>4.8</v>
       </c>
       <c r="AA115">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB115">
         <v>2.35</v>
@@ -19108,7 +19108,7 @@
         <v>1.18</v>
       </c>
       <c r="AF115">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="AG115">
         <v>1.57</v>
@@ -19127,7 +19127,7 @@
         <v>1.02</v>
       </c>
       <c r="AK115">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>4.84</v>
+        <v>4.82</v>
       </c>
       <c r="O116">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="P116">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q116">
         <v>4.2</v>
@@ -19235,25 +19235,25 @@
         <v>1.3</v>
       </c>
       <c r="T116">
-        <v>3.55</v>
+        <v>3.22</v>
       </c>
       <c r="U116">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="V116">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W116">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X116">
         <v>1.03</v>
       </c>
       <c r="Y116">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z116">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="AA116">
         <v>1.53</v>
@@ -19543,31 +19543,31 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="O118">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="P118">
         <v>2.8</v>
       </c>
       <c r="Q118">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R118">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="S118">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="T118">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="U118">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="V118">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="W118">
         <v>1.02</v>
@@ -19576,16 +19576,16 @@
         <v>1.15</v>
       </c>
       <c r="Y118">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="Z118">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AA118">
-        <v>3.41</v>
+        <v>3.5</v>
       </c>
       <c r="AB118">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AC118">
         <v>6</v>
@@ -19597,10 +19597,10 @@
         <v>1.02</v>
       </c>
       <c r="AF118">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="AG118">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK118">
         <v>1.44</v>
@@ -19706,13 +19706,13 @@
         </is>
       </c>
       <c r="N119">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="O119">
         <v>3.8</v>
       </c>
       <c r="P119">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="Q119">
         <v>2.38</v>
@@ -19739,16 +19739,16 @@
         <v>1.02</v>
       </c>
       <c r="Y119">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z119">
-        <v>5.5</v>
+        <v>5.77</v>
       </c>
       <c r="AA119">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AB119">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AC119">
         <v>2.06</v>
@@ -19757,7 +19757,7 @@
         <v>1.71</v>
       </c>
       <c r="AE119">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF119">
         <v>1.39</v>
@@ -19869,19 +19869,19 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="O120">
-        <v>3.35</v>
+        <v>3.21</v>
       </c>
       <c r="P120">
-        <v>3.8</v>
+        <v>4.24</v>
       </c>
       <c r="Q120">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="R120">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="S120">
         <v>1.47</v>
@@ -19908,7 +19908,7 @@
         <v>3.04</v>
       </c>
       <c r="AA120">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="AB120">
         <v>1.75</v>
@@ -20041,28 +20041,28 @@
         <v>1.83</v>
       </c>
       <c r="Q121">
-        <v>4.69</v>
+        <v>4.2</v>
       </c>
       <c r="R121">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S121">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="T121">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="U121">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="V121">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="W121">
         <v>1.03</v>
       </c>
       <c r="X121">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y121">
         <v>1.33</v>
@@ -20074,13 +20074,13 @@
         <v>2.1</v>
       </c>
       <c r="AB121">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC121">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="AD121">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE121">
         <v>1.05</v>
@@ -20089,7 +20089,7 @@
         <v>1.81</v>
       </c>
       <c r="AG121">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AK121">
         <v>1.18</v>
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="O122">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P122">
-        <v>5.75</v>
+        <v>6.05</v>
       </c>
       <c r="Q122">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="R122">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="S122">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T122">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="U122">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="V122">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W122">
         <v>1.06</v>
       </c>
       <c r="X122">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y122">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z122">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="AA122">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AB122">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AC122">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="AD122">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE122">
         <v>1.1</v>
       </c>
       <c r="AF122">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG122">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK122">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20358,13 +20358,13 @@
         </is>
       </c>
       <c r="N123">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="O123">
         <v>3.45</v>
       </c>
       <c r="P123">
-        <v>6.9</v>
+        <v>5.5</v>
       </c>
       <c r="Q123">
         <v>2.05</v>
@@ -20376,7 +20376,7 @@
         <v>1.55</v>
       </c>
       <c r="T123">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="U123">
         <v>3.5</v>
@@ -20385,34 +20385,34 @@
         <v>1.25</v>
       </c>
       <c r="W123">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X123">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y123">
         <v>1.5</v>
       </c>
       <c r="Z123">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AA123">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="AB123">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AC123">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AD123">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AE123">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF123">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AG123">
         <v>1.44</v>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="AK123">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20521,13 +20521,13 @@
         </is>
       </c>
       <c r="N124">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="O124">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="P124">
-        <v>4</v>
+        <v>4.55</v>
       </c>
       <c r="Q124">
         <v>2.8</v>
@@ -20536,34 +20536,34 @@
         <v>1.7</v>
       </c>
       <c r="S124">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="T124">
         <v>1.99</v>
       </c>
       <c r="U124">
-        <v>4.33</v>
+        <v>3.95</v>
       </c>
       <c r="V124">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="W124">
         <v>1.03</v>
       </c>
       <c r="X124">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="Y124">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="Z124">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AA124">
         <v>3.08</v>
       </c>
       <c r="AB124">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AC124">
         <v>5.75</v>
@@ -20575,7 +20575,7 @@
         <v>1.02</v>
       </c>
       <c r="AF124">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AG124">
         <v>1.5</v>
@@ -20693,22 +20693,22 @@
         <v>0</v>
       </c>
       <c r="Q125">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="R125">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S125">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T125">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="U125">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="V125">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W125">
         <v>1.07</v>
@@ -20720,28 +20720,28 @@
         <v>1.17</v>
       </c>
       <c r="Z125">
-        <v>3.94</v>
+        <v>3.9</v>
       </c>
       <c r="AA125">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AB125">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AC125">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AD125">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE125">
         <v>1.14</v>
       </c>
       <c r="AF125">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AG125">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.25</v>
+        <v>2.01</v>
       </c>
       <c r="AK125">
         <v>1.2</v>
@@ -20847,7 +20847,7 @@
         </is>
       </c>
       <c r="N126">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="O126">
         <v>4.95</v>
@@ -20859,22 +20859,22 @@
         <v>1.83</v>
       </c>
       <c r="R126">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="S126">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T126">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="U126">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V126">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="W126">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X126">
         <v>1.01</v>
@@ -20895,16 +20895,16 @@
         <v>1.74</v>
       </c>
       <c r="AD126">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="AE126">
         <v>1.4</v>
       </c>
       <c r="AF126">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AG126">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -21010,10 +21010,10 @@
         </is>
       </c>
       <c r="N127">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="O127">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="P127">
         <v>3.25</v>
@@ -21022,16 +21022,16 @@
         <v>2.3</v>
       </c>
       <c r="R127">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="S127">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="T127">
         <v>4.8</v>
       </c>
       <c r="U127">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="V127">
         <v>1.95</v>
@@ -21043,16 +21043,16 @@
         <v>1.01</v>
       </c>
       <c r="Y127">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Z127">
         <v>8.5</v>
       </c>
       <c r="AA127">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AB127">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AC127">
         <v>1.68</v>
@@ -21064,10 +21064,10 @@
         <v>1.44</v>
       </c>
       <c r="AF127">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AG127">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AK127">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21173,7 +21173,7 @@
         </is>
       </c>
       <c r="N128">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="O128">
         <v>3.65</v>
@@ -21182,13 +21182,13 @@
         <v>2.85</v>
       </c>
       <c r="Q128">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="R128">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="S128">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T128">
         <v>4.4</v>
@@ -21197,7 +21197,7 @@
         <v>1.91</v>
       </c>
       <c r="V128">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="W128">
         <v>1.22</v>
@@ -21206,7 +21206,7 @@
         <v>1.01</v>
       </c>
       <c r="Y128">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="Z128">
         <v>6.15</v>
@@ -21224,10 +21224,10 @@
         <v>1.88</v>
       </c>
       <c r="AE128">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AF128">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AG128">
         <v>3.1</v>
@@ -21246,7 +21246,7 @@
         <v>1.25</v>
       </c>
       <c r="AK128">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21336,25 +21336,25 @@
         </is>
       </c>
       <c r="N129">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="O129">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="P129">
-        <v>6.8</v>
+        <v>6.55</v>
       </c>
       <c r="Q129">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="R129">
-        <v>2.82</v>
+        <v>2.69</v>
       </c>
       <c r="S129">
         <v>1.18</v>
       </c>
       <c r="T129">
-        <v>4.2</v>
+        <v>3.92</v>
       </c>
       <c r="U129">
         <v>1.83</v>
@@ -21372,28 +21372,28 @@
         <v>1.06</v>
       </c>
       <c r="Z129">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="AA129">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB129">
-        <v>3.04</v>
+        <v>3.12</v>
       </c>
       <c r="AC129">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AD129">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AE129">
         <v>1.36</v>
       </c>
       <c r="AF129">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AG129">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AK129">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -22151,22 +22151,22 @@
         </is>
       </c>
       <c r="N134">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="O134">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P134">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="Q134">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="R134">
         <v>2.25</v>
       </c>
       <c r="S134">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="T134">
         <v>2.88</v>
@@ -22184,7 +22184,7 @@
         <v>1.05</v>
       </c>
       <c r="Y134">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z134">
         <v>3.5</v>
@@ -22317,22 +22317,22 @@
         <v>1.92</v>
       </c>
       <c r="O135">
+        <v>3.65</v>
+      </c>
+      <c r="P135">
         <v>3.4</v>
       </c>
-      <c r="P135">
-        <v>3.25</v>
-      </c>
       <c r="Q135">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="R135">
         <v>2.38</v>
       </c>
       <c r="S135">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T135">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U135">
         <v>2.25</v>
@@ -22347,7 +22347,7 @@
         <v>1.03</v>
       </c>
       <c r="Y135">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z135">
         <v>4.5</v>
@@ -22359,7 +22359,7 @@
         <v>2.2</v>
       </c>
       <c r="AC135">
-        <v>2.35</v>
+        <v>2.47</v>
       </c>
       <c r="AD135">
         <v>1.5</v>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK135">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22477,16 +22477,16 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.34</v>
+        <v>2.12</v>
       </c>
       <c r="O136">
         <v>3.08</v>
       </c>
       <c r="P136">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="Q136">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="R136">
         <v>2.1</v>
@@ -22510,7 +22510,7 @@
         <v>1</v>
       </c>
       <c r="Y136">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="Z136">
         <v>3.2</v>
@@ -22522,16 +22522,16 @@
         <v>1.75</v>
       </c>
       <c r="AC136">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD136">
         <v>1.25</v>
       </c>
       <c r="AE136">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF136">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG136">
         <v>2</v>
@@ -22547,7 +22547,7 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK136">
         <v>1.55</v>
@@ -22640,28 +22640,28 @@
         </is>
       </c>
       <c r="N137">
-        <v>5.5</v>
+        <v>5.65</v>
       </c>
       <c r="O137">
         <v>3.9</v>
       </c>
       <c r="P137">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="Q137">
-        <v>6.45</v>
+        <v>6</v>
       </c>
       <c r="R137">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="S137">
         <v>1.37</v>
       </c>
       <c r="T137">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="U137">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="V137">
         <v>1.41</v>
@@ -22673,22 +22673,22 @@
         <v>1.01</v>
       </c>
       <c r="Y137">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z137">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="AA137">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AB137">
         <v>1.88</v>
       </c>
       <c r="AC137">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="AD137">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE137">
         <v>1.11</v>
@@ -22697,7 +22697,7 @@
         <v>1.91</v>
       </c>
       <c r="AG137">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,7 +22710,7 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.22</v>
+        <v>2.27</v>
       </c>
       <c r="AK137">
         <v>1.13</v>
@@ -22824,16 +22824,16 @@
         <v>2.31</v>
       </c>
       <c r="U138">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="V138">
         <v>1.24</v>
       </c>
       <c r="W138">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X138">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Y138">
         <v>1.42</v>
@@ -22842,16 +22842,16 @@
         <v>2.55</v>
       </c>
       <c r="AA138">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AB138">
         <v>1.5</v>
       </c>
       <c r="AC138">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AD138">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AE138">
         <v>1.05</v>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="AK138">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -23295,37 +23295,37 @@
         <v>1.64</v>
       </c>
       <c r="O141">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="P141">
         <v>5.01</v>
       </c>
       <c r="Q141">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="R141">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S141">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="T141">
         <v>2.88</v>
       </c>
       <c r="U141">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="V141">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W141">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X141">
         <v>1.06</v>
       </c>
       <c r="Y141">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z141">
         <v>3</v>
@@ -23337,35 +23337,35 @@
         <v>1.74</v>
       </c>
       <c r="AC141">
-        <v>3.58</v>
+        <v>3.76</v>
       </c>
       <c r="AD141">
         <v>1.22</v>
       </c>
       <c r="AE141">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF141">
+        <v>2.05</v>
+      </c>
+      <c r="AG141">
+        <v>1.7</v>
+      </c>
+      <c r="AH141" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ141">
+        <v>1.25</v>
+      </c>
+      <c r="AK141">
         <v>2.1</v>
-      </c>
-      <c r="AG141">
-        <v>1.65</v>
-      </c>
-      <c r="AH141" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI141" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ141">
-        <v>1.22</v>
-      </c>
-      <c r="AK141">
-        <v>2.25</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23455,13 +23455,13 @@
         </is>
       </c>
       <c r="N142">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O142">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P142">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q142">
         <v>0</v>
@@ -23494,10 +23494,10 @@
         <v>0</v>
       </c>
       <c r="AA142">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB142">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC142">
         <v>0</v>
@@ -23790,16 +23790,16 @@
         <v>6.63</v>
       </c>
       <c r="Q144">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="R144">
         <v>2.2</v>
       </c>
       <c r="S144">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T144">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="U144">
         <v>2.88</v>
@@ -23817,10 +23817,10 @@
         <v>1.28</v>
       </c>
       <c r="Z144">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="AA144">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AB144">
         <v>1.84</v>
@@ -23832,13 +23832,13 @@
         <v>1.3</v>
       </c>
       <c r="AE144">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF144">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG144">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23854,7 +23854,7 @@
         <v>1.25</v>
       </c>
       <c r="AK144">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23953,49 +23953,49 @@
         <v>4.48</v>
       </c>
       <c r="Q145">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="R145">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="S145">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T145">
-        <v>3.13</v>
+        <v>3.08</v>
       </c>
       <c r="U145">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="V145">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W145">
         <v>1.06</v>
       </c>
       <c r="X145">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y145">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z145">
-        <v>3.44</v>
+        <v>3.38</v>
       </c>
       <c r="AA145">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AB145">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AC145">
         <v>2.94</v>
       </c>
       <c r="AD145">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE145">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF145">
         <v>1.7</v>
@@ -24017,7 +24017,7 @@
         <v>1.29</v>
       </c>
       <c r="AK145">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O146">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P146">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q146">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R146">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S146">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T146">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U146">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V146">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W146">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X146">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y146">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z146">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA146">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB146">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC146">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD146">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE146">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF146">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG146">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK146">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G147">
@@ -24279,55 +24279,55 @@
         <v>0</v>
       </c>
       <c r="Q147">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R147">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S147">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T147">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U147">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V147">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W147">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X147">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y147">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z147">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AA147">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB147">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC147">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD147">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE147">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF147">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG147">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK147">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24439,7 +24439,7 @@
         <v>3.4</v>
       </c>
       <c r="P148">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q148">
         <v>2.5</v>
@@ -24451,10 +24451,10 @@
         <v>1.3</v>
       </c>
       <c r="T148">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="U148">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V148">
         <v>1.5</v>
@@ -24466,10 +24466,10 @@
         <v>1.04</v>
       </c>
       <c r="Y148">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z148">
-        <v>3.92</v>
+        <v>3.95</v>
       </c>
       <c r="AA148">
         <v>1.7</v>
@@ -24478,13 +24478,13 @@
         <v>2.1</v>
       </c>
       <c r="AC148">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AD148">
         <v>1.4</v>
       </c>
       <c r="AE148">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF148">
         <v>1.57</v>
@@ -24506,7 +24506,7 @@
         <v>1.25</v>
       </c>
       <c r="AK148">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -24768,7 +24768,7 @@
         <v>2.85</v>
       </c>
       <c r="Q150">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R150">
         <v>1.81</v>
@@ -24789,25 +24789,25 @@
         <v>1.02</v>
       </c>
       <c r="X150">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y150">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="Z150">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="AA150">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AB150">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC150">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="AD150">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE150">
         <v>1.04</v>
@@ -24934,52 +24934,52 @@
         <v>3</v>
       </c>
       <c r="R151">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="S151">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T151">
         <v>3.3</v>
       </c>
       <c r="U151">
-        <v>2.56</v>
+        <v>2.36</v>
       </c>
       <c r="V151">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W151">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X151">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y151">
         <v>1.22</v>
       </c>
       <c r="Z151">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="AA151">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AB151">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AC151">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AD151">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AE151">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF151">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG151">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -24992,10 +24992,10 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK151">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25254,7 +25254,7 @@
         <v>2.65</v>
       </c>
       <c r="P153">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -25411,7 +25411,7 @@
         </is>
       </c>
       <c r="N154">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="O154">
         <v>4.8</v>
@@ -25423,13 +25423,13 @@
         <v>1.85</v>
       </c>
       <c r="R154">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S154">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="T154">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="U154">
         <v>2.52</v>
@@ -25447,10 +25447,10 @@
         <v>1.18</v>
       </c>
       <c r="Z154">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AA154">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB154">
         <v>2.25</v>
@@ -25462,13 +25462,13 @@
         <v>1.44</v>
       </c>
       <c r="AE154">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF154">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG154">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25589,10 +25589,10 @@
         <v>2.05</v>
       </c>
       <c r="S155">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T155">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U155">
         <v>2.85</v>
@@ -25601,22 +25601,22 @@
         <v>1.36</v>
       </c>
       <c r="W155">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X155">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y155">
         <v>1.3</v>
       </c>
       <c r="Z155">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA155">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AB155">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AC155">
         <v>3.34</v>
@@ -25631,7 +25631,7 @@
         <v>1.73</v>
       </c>
       <c r="AG155">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,7 +25644,7 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK155">
         <v>1.59</v>
@@ -25746,16 +25746,16 @@
         <v>3.8</v>
       </c>
       <c r="Q156">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="R156">
         <v>1.95</v>
       </c>
       <c r="S156">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="T156">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="U156">
         <v>3.6</v>
@@ -25767,7 +25767,7 @@
         <v>1.05</v>
       </c>
       <c r="X156">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y156">
         <v>1.47</v>
@@ -25776,7 +25776,7 @@
         <v>2.59</v>
       </c>
       <c r="AA156">
-        <v>2.2</v>
+        <v>2.51</v>
       </c>
       <c r="AB156">
         <v>1.49</v>
@@ -25785,7 +25785,7 @@
         <v>4.84</v>
       </c>
       <c r="AD156">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE156">
         <v>1.04</v>
@@ -25807,7 +25807,7 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK156">
         <v>1.73</v>
@@ -25900,7 +25900,7 @@
         </is>
       </c>
       <c r="N157">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="O157">
         <v>3.35</v>
@@ -25915,13 +25915,13 @@
         <v>1.92</v>
       </c>
       <c r="S157">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="T157">
         <v>2.4</v>
       </c>
       <c r="U157">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="V157">
         <v>1.22</v>
@@ -25948,7 +25948,7 @@
         <v>5.04</v>
       </c>
       <c r="AD157">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE157">
         <v>1.01</v>
@@ -25957,7 +25957,7 @@
         <v>2.18</v>
       </c>
       <c r="AG157">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AK157">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26063,13 +26063,13 @@
         </is>
       </c>
       <c r="N158">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="O158">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="P158">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="Q158">
         <v>2.3</v>
@@ -26120,7 +26120,7 @@
         <v>1.75</v>
       </c>
       <c r="AG158">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,80 +26226,80 @@
         </is>
       </c>
       <c r="N159">
-        <v>1.12</v>
+        <v>4.75</v>
       </c>
       <c r="O159">
-        <v>8.300000000000001</v>
+        <v>3.6</v>
       </c>
       <c r="P159">
-        <v>15</v>
+        <v>1.69</v>
       </c>
       <c r="Q159">
-        <v>1.44</v>
+        <v>4.8</v>
       </c>
       <c r="R159">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="S159">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="T159">
-        <v>3.9</v>
+        <v>2.66</v>
       </c>
       <c r="U159">
-        <v>2.11</v>
+        <v>2.81</v>
       </c>
       <c r="V159">
-        <v>1.69</v>
+        <v>1.38</v>
       </c>
       <c r="W159">
+        <v>1.04</v>
+      </c>
+      <c r="X159">
+        <v>1.05</v>
+      </c>
+      <c r="Y159">
+        <v>1.29</v>
+      </c>
+      <c r="Z159">
+        <v>3.35</v>
+      </c>
+      <c r="AA159">
+        <v>1.96</v>
+      </c>
+      <c r="AB159">
+        <v>1.85</v>
+      </c>
+      <c r="AC159">
+        <v>3.3</v>
+      </c>
+      <c r="AD159">
+        <v>1.27</v>
+      </c>
+      <c r="AE159">
+        <v>1.06</v>
+      </c>
+      <c r="AF159">
+        <v>1.84</v>
+      </c>
+      <c r="AG159">
+        <v>1.84</v>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ159">
+        <v>2.14</v>
+      </c>
+      <c r="AK159">
         <v>1.18</v>
-      </c>
-      <c r="X159">
-        <v>1.01</v>
-      </c>
-      <c r="Y159">
-        <v>1.13</v>
-      </c>
-      <c r="Z159">
-        <v>5.75</v>
-      </c>
-      <c r="AA159">
-        <v>1.42</v>
-      </c>
-      <c r="AB159">
-        <v>2.6</v>
-      </c>
-      <c r="AC159">
-        <v>2.1</v>
-      </c>
-      <c r="AD159">
-        <v>1.65</v>
-      </c>
-      <c r="AE159">
-        <v>1.27</v>
-      </c>
-      <c r="AF159">
-        <v>2.45</v>
-      </c>
-      <c r="AG159">
-        <v>1.5</v>
-      </c>
-      <c r="AH159" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI159" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ159">
-        <v>1.06</v>
-      </c>
-      <c r="AK159">
-        <v>5.75</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,64 +26389,64 @@
         </is>
       </c>
       <c r="N160">
-        <v>4.8</v>
+        <v>1.11</v>
       </c>
       <c r="O160">
-        <v>3.7</v>
+        <v>8.6</v>
       </c>
       <c r="P160">
-        <v>1.73</v>
+        <v>16</v>
       </c>
       <c r="Q160">
-        <v>4.8</v>
+        <v>1.44</v>
       </c>
       <c r="R160">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="S160">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="T160">
-        <v>2.66</v>
+        <v>3.94</v>
       </c>
       <c r="U160">
-        <v>2.81</v>
+        <v>2.1</v>
       </c>
       <c r="V160">
-        <v>1.38</v>
+        <v>1.68</v>
       </c>
       <c r="W160">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="X160">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y160">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="Z160">
-        <v>3.35</v>
+        <v>5.41</v>
       </c>
       <c r="AA160">
-        <v>1.96</v>
+        <v>1.41</v>
       </c>
       <c r="AB160">
-        <v>1.86</v>
+        <v>2.63</v>
       </c>
       <c r="AC160">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="AD160">
-        <v>1.27</v>
+        <v>1.65</v>
       </c>
       <c r="AE160">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AF160">
-        <v>1.84</v>
+        <v>2.45</v>
       </c>
       <c r="AG160">
-        <v>1.84</v>
+        <v>1.5</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26459,10 +26459,10 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>2.14</v>
+        <v>1.06</v>
       </c>
       <c r="AK160">
-        <v>1.18</v>
+        <v>6.25</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -26564,25 +26564,25 @@
         <v>2.16</v>
       </c>
       <c r="R161">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="S161">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="T161">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="U161">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="V161">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="W161">
         <v>1.05</v>
       </c>
       <c r="X161">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y161">
         <v>1.45</v>
@@ -26591,25 +26591,25 @@
         <v>2.48</v>
       </c>
       <c r="AA161">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="AB161">
         <v>1.47</v>
       </c>
       <c r="AC161">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AD161">
         <v>1.15</v>
       </c>
       <c r="AE161">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF161">
         <v>2.5</v>
       </c>
       <c r="AG161">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AK161">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -26887,10 +26887,10 @@
         <v>4.2</v>
       </c>
       <c r="Q163">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="R163">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="S163">
         <v>1.15</v>
@@ -26899,10 +26899,10 @@
         <v>4.8</v>
       </c>
       <c r="U163">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="V163">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="W163">
         <v>1.29</v>
@@ -26914,28 +26914,28 @@
         <v>1.06</v>
       </c>
       <c r="Z163">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AA163">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AB163">
         <v>3.5</v>
       </c>
       <c r="AC163">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AD163">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AE163">
         <v>1.44</v>
       </c>
       <c r="AF163">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AG163">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -26951,7 +26951,7 @@
         <v>1.2</v>
       </c>
       <c r="AK163">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27041,43 +27041,43 @@
         </is>
       </c>
       <c r="N164">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="O164">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="P164">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="Q164">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="R164">
         <v>1.85</v>
       </c>
       <c r="S164">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="T164">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="U164">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="V164">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W164">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X164">
         <v>1.08</v>
       </c>
       <c r="Y164">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Z164">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AA164">
         <v>3.1</v>
@@ -27086,10 +27086,10 @@
         <v>1.34</v>
       </c>
       <c r="AC164">
-        <v>5.75</v>
+        <v>6.05</v>
       </c>
       <c r="AD164">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AE164">
         <v>1.03</v>
@@ -27213,16 +27213,16 @@
         <v>3.5</v>
       </c>
       <c r="Q165">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R165">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="S165">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T165">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="U165">
         <v>2.4</v>
@@ -27231,7 +27231,7 @@
         <v>1.5</v>
       </c>
       <c r="W165">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X165">
         <v>1</v>
@@ -27243,10 +27243,10 @@
         <v>3.8</v>
       </c>
       <c r="AA165">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AB165">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="AC165">
         <v>2.65</v>
@@ -27255,7 +27255,7 @@
         <v>1.37</v>
       </c>
       <c r="AE165">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF165">
         <v>1.61</v>
@@ -27376,7 +27376,7 @@
         <v>0</v>
       </c>
       <c r="Q166">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="R166">
         <v>1.85</v>
@@ -27403,7 +27403,7 @@
         <v>1.65</v>
       </c>
       <c r="Z166">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="AA166">
         <v>2.7</v>
@@ -27412,19 +27412,19 @@
         <v>1.32</v>
       </c>
       <c r="AC166">
-        <v>5.75</v>
+        <v>5.2</v>
       </c>
       <c r="AD166">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE166">
         <v>1.03</v>
       </c>
       <c r="AF166">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AG166">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AH166" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         </is>
       </c>
       <c r="AJ166">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AK166">
         <v>1.73</v>
@@ -27539,13 +27539,13 @@
         <v>2.9</v>
       </c>
       <c r="Q167">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R167">
         <v>1.86</v>
       </c>
       <c r="S167">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="T167">
         <v>2.46</v>
@@ -27563,22 +27563,22 @@
         <v>1.06</v>
       </c>
       <c r="Y167">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="Z167">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="AA167">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="AB167">
         <v>1.53</v>
       </c>
       <c r="AC167">
-        <v>4.1</v>
+        <v>4.72</v>
       </c>
       <c r="AD167">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AE167">
         <v>1.05</v>
@@ -27587,7 +27587,7 @@
         <v>2</v>
       </c>
       <c r="AG167">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27603,7 +27603,7 @@
         <v>1.33</v>
       </c>
       <c r="AK167">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -27693,13 +27693,13 @@
         </is>
       </c>
       <c r="N168">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="O168">
         <v>2.9</v>
       </c>
       <c r="P168">
-        <v>3.54</v>
+        <v>3.37</v>
       </c>
       <c r="Q168">
         <v>0</v>
@@ -27732,10 +27732,10 @@
         <v>2.37</v>
       </c>
       <c r="AA168">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AB168">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC168">
         <v>0</v>
@@ -28019,13 +28019,13 @@
         </is>
       </c>
       <c r="N170">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="O170">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="P170">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="Q170">
         <v>2.62</v>
@@ -28034,7 +28034,7 @@
         <v>2.1</v>
       </c>
       <c r="S170">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T170">
         <v>2.7</v>
@@ -28043,31 +28043,31 @@
         <v>3.05</v>
       </c>
       <c r="V170">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W170">
         <v>1.04</v>
       </c>
       <c r="X170">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y170">
         <v>1.31</v>
       </c>
       <c r="Z170">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="AA170">
         <v>2.1</v>
       </c>
       <c r="AB170">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC170">
-        <v>3.85</v>
+        <v>3.54</v>
       </c>
       <c r="AD170">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE170">
         <v>1.04</v>
@@ -28197,10 +28197,10 @@
         <v>1.96</v>
       </c>
       <c r="S171">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T171">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="U171">
         <v>2.91</v>
@@ -28209,7 +28209,7 @@
         <v>1.33</v>
       </c>
       <c r="W171">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X171">
         <v>1.06</v>
@@ -28218,25 +28218,25 @@
         <v>1.38</v>
       </c>
       <c r="Z171">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="AA171">
         <v>2.19</v>
       </c>
       <c r="AB171">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AC171">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AD171">
         <v>1.23</v>
       </c>
       <c r="AE171">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF171">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG171">
         <v>1.85</v>
@@ -28345,64 +28345,64 @@
         </is>
       </c>
       <c r="N172">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O172">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P172">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q172">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R172">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S172">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T172">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U172">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="V172">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W172">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X172">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y172">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z172">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AA172">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AB172">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC172">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AD172">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE172">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF172">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG172">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28415,10 +28415,10 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK172">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28508,64 +28508,64 @@
         </is>
       </c>
       <c r="N173">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O173">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P173">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q173">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R173">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S173">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T173">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U173">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V173">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W173">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X173">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y173">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z173">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA173">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB173">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC173">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AD173">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE173">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF173">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG173">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28578,10 +28578,10 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK173">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -28671,10 +28671,10 @@
         </is>
       </c>
       <c r="N174">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="O174">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P174">
         <v>1.83</v>
@@ -28683,19 +28683,19 @@
         <v>4.4</v>
       </c>
       <c r="R174">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="S174">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T174">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="U174">
         <v>2.72</v>
       </c>
       <c r="V174">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W174">
         <v>1.07</v>
@@ -28704,7 +28704,7 @@
         <v>1.05</v>
       </c>
       <c r="Y174">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z174">
         <v>3.4</v>
@@ -28713,16 +28713,16 @@
         <v>1.95</v>
       </c>
       <c r="AB174">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC174">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AD174">
         <v>1.3</v>
       </c>
       <c r="AE174">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF174">
         <v>1.76</v>
@@ -28744,7 +28744,7 @@
         <v>1.91</v>
       </c>
       <c r="AK174">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -28837,28 +28837,28 @@
         <v>1.25</v>
       </c>
       <c r="O175">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="P175">
         <v>11</v>
       </c>
       <c r="Q175">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R175">
         <v>2.63</v>
       </c>
       <c r="S175">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T175">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U175">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="V175">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W175">
         <v>1.11</v>
@@ -28870,28 +28870,28 @@
         <v>1.15</v>
       </c>
       <c r="Z175">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="AA175">
         <v>1.63</v>
       </c>
       <c r="AB175">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC175">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="AD175">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AE175">
         <v>1.16</v>
       </c>
       <c r="AF175">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG175">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -29006,10 +29006,10 @@
         <v>1.6</v>
       </c>
       <c r="Q176">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="R176">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="S176">
         <v>1.27</v>
@@ -29018,43 +29018,43 @@
         <v>3.2</v>
       </c>
       <c r="U176">
-        <v>2.17</v>
+        <v>2.47</v>
       </c>
       <c r="V176">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W176">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X176">
         <v>1.03</v>
       </c>
       <c r="Y176">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z176">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="AA176">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="AB176">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AC176">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="AD176">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AE176">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF176">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="AG176">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,7 +29067,7 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.91</v>
+        <v>1.19</v>
       </c>
       <c r="AK176">
         <v>1.17</v>
@@ -29323,19 +29323,19 @@
         </is>
       </c>
       <c r="N178">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="O178">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P178">
-        <v>4.17</v>
+        <v>3.48</v>
       </c>
       <c r="Q178">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="R178">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="S178">
         <v>1.36</v>
@@ -29347,37 +29347,37 @@
         <v>2.85</v>
       </c>
       <c r="V178">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W178">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X178">
         <v>1.05</v>
       </c>
       <c r="Y178">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z178">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA178">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AB178">
         <v>1.8</v>
       </c>
       <c r="AC178">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AD178">
         <v>1.26</v>
       </c>
       <c r="AE178">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF178">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AG178">
         <v>1.95</v>
@@ -29393,10 +29393,10 @@
         </is>
       </c>
       <c r="AJ178">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK178">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29486,10 +29486,10 @@
         </is>
       </c>
       <c r="N179">
+        <v>2.95</v>
+      </c>
+      <c r="O179">
         <v>3</v>
-      </c>
-      <c r="O179">
-        <v>3.1</v>
       </c>
       <c r="P179">
         <v>2.3</v>
@@ -29507,22 +29507,22 @@
         <v>2.31</v>
       </c>
       <c r="U179">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="V179">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="W179">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X179">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y179">
         <v>1.5</v>
       </c>
       <c r="Z179">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="AA179">
         <v>2.49</v>
@@ -29531,10 +29531,10 @@
         <v>1.49</v>
       </c>
       <c r="AC179">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="AD179">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE179">
         <v>1.04</v>
@@ -29543,7 +29543,7 @@
         <v>2</v>
       </c>
       <c r="AG179">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -29661,46 +29661,46 @@
         <v>3</v>
       </c>
       <c r="R180">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="S180">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T180">
-        <v>2.92</v>
+        <v>3.04</v>
       </c>
       <c r="U180">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="V180">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W180">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X180">
         <v>1.04</v>
       </c>
       <c r="Y180">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z180">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="AA180">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AB180">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AC180">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="AD180">
         <v>1.36</v>
       </c>
       <c r="AE180">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF180">
         <v>1.6</v>
@@ -29719,10 +29719,10 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AK180">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AL180">
         <v>0</v>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU180"/>
+  <dimension ref="A1:AU181"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18686,22 +18686,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>3.47</v>
+        <v>2.02</v>
       </c>
       <c r="O113">
-        <v>3.35</v>
+        <v>2.89</v>
       </c>
       <c r="P113">
-        <v>2.02</v>
+        <v>3.6</v>
       </c>
       <c r="Q113">
-        <v>4.09</v>
+        <v>2.7</v>
       </c>
       <c r="R113">
-        <v>2.18</v>
+        <v>1.84</v>
       </c>
       <c r="S113">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="T113">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="U113">
-        <v>2.65</v>
+        <v>3.7</v>
       </c>
       <c r="V113">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="W113">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X113">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="Y113">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="Z113">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="AA113">
-        <v>1.85</v>
+        <v>2.59</v>
       </c>
       <c r="AB113">
-        <v>1.91</v>
+        <v>1.39</v>
       </c>
       <c r="AC113">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="AD113">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AE113">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF113">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="AG113">
-        <v>2.01</v>
+        <v>1.54</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AK113">
-        <v>1.28</v>
+        <v>1.73</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18849,7 +18849,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.12</v>
+        <v>3.47</v>
       </c>
       <c r="O114">
-        <v>3.58</v>
+        <v>3.35</v>
       </c>
       <c r="P114">
-        <v>3.3</v>
+        <v>2.02</v>
       </c>
       <c r="Q114">
-        <v>2.68</v>
+        <v>4.09</v>
       </c>
       <c r="R114">
         <v>2.18</v>
       </c>
       <c r="S114">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="T114">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="U114">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="V114">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="W114">
+        <v>1.06</v>
+      </c>
+      <c r="X114">
+        <v>1.05</v>
+      </c>
+      <c r="Y114">
+        <v>1.28</v>
+      </c>
+      <c r="Z114">
+        <v>3.5</v>
+      </c>
+      <c r="AA114">
+        <v>1.85</v>
+      </c>
+      <c r="AB114">
+        <v>1.91</v>
+      </c>
+      <c r="AC114">
+        <v>3.2</v>
+      </c>
+      <c r="AD114">
+        <v>1.3</v>
+      </c>
+      <c r="AE114">
         <v>1.08</v>
       </c>
-      <c r="X114">
-        <v>1.01</v>
-      </c>
-      <c r="Y114">
-        <v>1.21</v>
-      </c>
-      <c r="Z114">
-        <v>4.32</v>
-      </c>
-      <c r="AA114">
-        <v>1.71</v>
-      </c>
-      <c r="AB114">
-        <v>2.13</v>
-      </c>
-      <c r="AC114">
-        <v>2.65</v>
-      </c>
-      <c r="AD114">
-        <v>1.4</v>
-      </c>
-      <c r="AE114">
-        <v>1.11</v>
-      </c>
       <c r="AF114">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AG114">
-        <v>2.23</v>
+        <v>2.01</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK114">
-        <v>1.75</v>
+        <v>1.28</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19012,7 +19012,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.15</v>
+        <v>2.12</v>
       </c>
       <c r="O115">
-        <v>7.5</v>
+        <v>3.58</v>
       </c>
       <c r="P115">
-        <v>12</v>
+        <v>3.3</v>
       </c>
       <c r="Q115">
-        <v>1.55</v>
+        <v>2.68</v>
       </c>
       <c r="R115">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="S115">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="T115">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="U115">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="V115">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="W115">
+        <v>1.08</v>
+      </c>
+      <c r="X115">
+        <v>1.01</v>
+      </c>
+      <c r="Y115">
+        <v>1.21</v>
+      </c>
+      <c r="Z115">
+        <v>4.32</v>
+      </c>
+      <c r="AA115">
+        <v>1.71</v>
+      </c>
+      <c r="AB115">
+        <v>2.13</v>
+      </c>
+      <c r="AC115">
+        <v>2.65</v>
+      </c>
+      <c r="AD115">
+        <v>1.4</v>
+      </c>
+      <c r="AE115">
         <v>1.11</v>
       </c>
-      <c r="X115">
-        <v>1.03</v>
-      </c>
-      <c r="Y115">
-        <v>1.12</v>
-      </c>
-      <c r="Z115">
-        <v>4.8</v>
-      </c>
-      <c r="AA115">
-        <v>1.55</v>
-      </c>
-      <c r="AB115">
-        <v>2.35</v>
-      </c>
-      <c r="AC115">
-        <v>2.39</v>
-      </c>
-      <c r="AD115">
-        <v>1.53</v>
-      </c>
-      <c r="AE115">
-        <v>1.18</v>
-      </c>
       <c r="AF115">
-        <v>2.14</v>
+        <v>1.58</v>
       </c>
       <c r="AG115">
-        <v>1.57</v>
+        <v>2.23</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.02</v>
+        <v>1.23</v>
       </c>
       <c r="AK115">
-        <v>4.5</v>
+        <v>1.75</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19170,27 +19170,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>4.82</v>
+        <v>1.15</v>
       </c>
       <c r="O116">
-        <v>3.7</v>
+        <v>7.5</v>
       </c>
       <c r="P116">
-        <v>1.67</v>
+        <v>12</v>
       </c>
       <c r="Q116">
-        <v>4.2</v>
+        <v>1.55</v>
       </c>
       <c r="R116">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="S116">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="T116">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="U116">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="V116">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W116">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X116">
         <v>1.03</v>
       </c>
       <c r="Y116">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Z116">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AA116">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AB116">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="AC116">
-        <v>2.43</v>
+        <v>2.39</v>
       </c>
       <c r="AD116">
         <v>1.53</v>
       </c>
       <c r="AE116">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF116">
-        <v>1.55</v>
+        <v>2.14</v>
       </c>
       <c r="AG116">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="AK116">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19321,7 +19321,7 @@
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>2026-08-09 14:15:00</t>
+          <t>2026-08-09 14:00:00</t>
         </is>
       </c>
     </row>
@@ -19338,22 +19338,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q117">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R117">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S117">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T117">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U117">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V117">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W117">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X117">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y117">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z117">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA117">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB117">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AC117">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD117">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE117">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF117">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG117">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK117">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19496,27 +19496,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="O118">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="P118">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q118">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R118">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S118">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="T118">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U118">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="V118">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W118">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X118">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Y118">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z118">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA118">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB118">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC118">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AD118">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE118">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF118">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG118">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK118">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19647,7 +19647,7 @@
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>2026-08-09 14:30:00</t>
+          <t>2026-08-09 14:15:00</t>
         </is>
       </c>
     </row>
@@ -19664,22 +19664,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,64 +19706,64 @@
         </is>
       </c>
       <c r="N119">
-        <v>1.93</v>
+        <v>2.55</v>
       </c>
       <c r="O119">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="P119">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="Q119">
-        <v>2.38</v>
+        <v>3.5</v>
       </c>
       <c r="R119">
-        <v>2.39</v>
+        <v>1.73</v>
       </c>
       <c r="S119">
-        <v>1.2</v>
+        <v>1.74</v>
       </c>
       <c r="T119">
-        <v>4</v>
+        <v>2.05</v>
       </c>
       <c r="U119">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="V119">
-        <v>1.67</v>
+        <v>1.13</v>
       </c>
       <c r="W119">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="X119">
+        <v>1.15</v>
+      </c>
+      <c r="Y119">
+        <v>1.66</v>
+      </c>
+      <c r="Z119">
+        <v>1.98</v>
+      </c>
+      <c r="AA119">
+        <v>3.5</v>
+      </c>
+      <c r="AB119">
+        <v>1.32</v>
+      </c>
+      <c r="AC119">
+        <v>6</v>
+      </c>
+      <c r="AD119">
+        <v>1.09</v>
+      </c>
+      <c r="AE119">
         <v>1.02</v>
       </c>
-      <c r="Y119">
-        <v>1.08</v>
-      </c>
-      <c r="Z119">
-        <v>5.77</v>
-      </c>
-      <c r="AA119">
-        <v>1.4</v>
-      </c>
-      <c r="AB119">
-        <v>2.63</v>
-      </c>
-      <c r="AC119">
-        <v>2.06</v>
-      </c>
-      <c r="AD119">
-        <v>1.71</v>
-      </c>
-      <c r="AE119">
-        <v>1.25</v>
-      </c>
       <c r="AF119">
-        <v>1.39</v>
+        <v>2.51</v>
       </c>
       <c r="AG119">
-        <v>2.65</v>
+        <v>1.44</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK119">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19827,7 +19827,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="O120">
-        <v>3.21</v>
+        <v>3.8</v>
       </c>
       <c r="P120">
-        <v>4.24</v>
+        <v>3.1</v>
       </c>
       <c r="Q120">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="R120">
+        <v>2.39</v>
+      </c>
+      <c r="S120">
+        <v>1.2</v>
+      </c>
+      <c r="T120">
+        <v>4</v>
+      </c>
+      <c r="U120">
+        <v>2.1</v>
+      </c>
+      <c r="V120">
+        <v>1.67</v>
+      </c>
+      <c r="W120">
+        <v>1.13</v>
+      </c>
+      <c r="X120">
+        <v>1.02</v>
+      </c>
+      <c r="Y120">
+        <v>1.08</v>
+      </c>
+      <c r="Z120">
+        <v>5.77</v>
+      </c>
+      <c r="AA120">
+        <v>1.4</v>
+      </c>
+      <c r="AB120">
+        <v>2.63</v>
+      </c>
+      <c r="AC120">
         <v>2.06</v>
       </c>
-      <c r="S120">
-        <v>1.47</v>
-      </c>
-      <c r="T120">
-        <v>2.6</v>
-      </c>
-      <c r="U120">
-        <v>3.14</v>
-      </c>
-      <c r="V120">
-        <v>1.34</v>
-      </c>
-      <c r="W120">
-        <v>1.04</v>
-      </c>
-      <c r="X120">
-        <v>1.03</v>
-      </c>
-      <c r="Y120">
-        <v>1.35</v>
-      </c>
-      <c r="Z120">
-        <v>3.04</v>
-      </c>
-      <c r="AA120">
-        <v>2.18</v>
-      </c>
-      <c r="AB120">
-        <v>1.75</v>
-      </c>
-      <c r="AC120">
-        <v>3.68</v>
-      </c>
       <c r="AD120">
-        <v>1.22</v>
+        <v>1.71</v>
       </c>
       <c r="AE120">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="AF120">
-        <v>1.94</v>
+        <v>1.39</v>
       </c>
       <c r="AG120">
-        <v>1.79</v>
+        <v>2.65</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AK120">
-        <v>1.86</v>
+        <v>1.69</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -19985,12 +19985,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>3.93</v>
+        <v>1.89</v>
       </c>
       <c r="O121">
-        <v>3.35</v>
+        <v>3.21</v>
       </c>
       <c r="P121">
-        <v>1.83</v>
+        <v>4.24</v>
       </c>
       <c r="Q121">
-        <v>4.2</v>
+        <v>2.52</v>
       </c>
       <c r="R121">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S121">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="T121">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="U121">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="V121">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="W121">
+        <v>1.04</v>
+      </c>
+      <c r="X121">
         <v>1.03</v>
       </c>
-      <c r="X121">
-        <v>1.01</v>
-      </c>
       <c r="Y121">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z121">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="AA121">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AB121">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC121">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="AD121">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE121">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF121">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="AG121">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.76</v>
+        <v>1.24</v>
       </c>
       <c r="AK121">
-        <v>1.18</v>
+        <v>1.86</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20136,7 +20136,7 @@
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>2026-08-09 15:00:00</t>
+          <t>2026-08-09 14:30:00</t>
         </is>
       </c>
     </row>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,65 +20195,65 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.44</v>
+        <v>3.93</v>
       </c>
       <c r="O122">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="P122">
-        <v>6.05</v>
+        <v>1.83</v>
       </c>
       <c r="Q122">
-        <v>1.91</v>
+        <v>4.2</v>
       </c>
       <c r="R122">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="S122">
+        <v>1.39</v>
+      </c>
+      <c r="T122">
+        <v>2.75</v>
+      </c>
+      <c r="U122">
+        <v>3</v>
+      </c>
+      <c r="V122">
+        <v>1.38</v>
+      </c>
+      <c r="W122">
+        <v>1.03</v>
+      </c>
+      <c r="X122">
+        <v>1.01</v>
+      </c>
+      <c r="Y122">
         <v>1.33</v>
       </c>
-      <c r="T122">
-        <v>2.91</v>
-      </c>
-      <c r="U122">
-        <v>2.6</v>
-      </c>
-      <c r="V122">
-        <v>1.44</v>
-      </c>
-      <c r="W122">
-        <v>1.06</v>
-      </c>
-      <c r="X122">
+      <c r="Z122">
+        <v>3.08</v>
+      </c>
+      <c r="AA122">
+        <v>2.1</v>
+      </c>
+      <c r="AB122">
+        <v>1.7</v>
+      </c>
+      <c r="AC122">
+        <v>3.34</v>
+      </c>
+      <c r="AD122">
+        <v>1.25</v>
+      </c>
+      <c r="AE122">
         <v>1.05</v>
       </c>
-      <c r="Y122">
-        <v>1.2</v>
-      </c>
-      <c r="Z122">
-        <v>3.68</v>
-      </c>
-      <c r="AA122">
-        <v>1.75</v>
-      </c>
-      <c r="AB122">
-        <v>1.96</v>
-      </c>
-      <c r="AC122">
-        <v>2.78</v>
-      </c>
-      <c r="AD122">
-        <v>1.36</v>
-      </c>
-      <c r="AE122">
-        <v>1.1</v>
-      </c>
       <c r="AF122">
+        <v>1.81</v>
+      </c>
+      <c r="AG122">
         <v>1.85</v>
       </c>
-      <c r="AG122">
-        <v>1.77</v>
-      </c>
       <c r="AH122" t="inlineStr">
         <is>
           <t>[]</t>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.16</v>
+        <v>1.76</v>
       </c>
       <c r="AK122">
-        <v>2.45</v>
+        <v>1.18</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20316,22 +20316,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="O123">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="P123">
-        <v>5.5</v>
+        <v>6.05</v>
       </c>
       <c r="Q123">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="R123">
-        <v>2.05</v>
+        <v>2.24</v>
       </c>
       <c r="S123">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="T123">
-        <v>2.26</v>
+        <v>2.91</v>
       </c>
       <c r="U123">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="V123">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="W123">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X123">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y123">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="Z123">
-        <v>2.35</v>
+        <v>3.68</v>
       </c>
       <c r="AA123">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB123">
-        <v>1.44</v>
+        <v>1.96</v>
       </c>
       <c r="AC123">
-        <v>5.5</v>
+        <v>2.78</v>
       </c>
       <c r="AD123">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AE123">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AF123">
-        <v>2.63</v>
+        <v>1.85</v>
       </c>
       <c r="AG123">
-        <v>1.44</v>
+        <v>1.77</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AK123">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
-        <v>1.99</v>
+        <v>1.53</v>
       </c>
       <c r="O124">
+        <v>3.45</v>
+      </c>
+      <c r="P124">
+        <v>5.5</v>
+      </c>
+      <c r="Q124">
+        <v>2.05</v>
+      </c>
+      <c r="R124">
+        <v>2.05</v>
+      </c>
+      <c r="S124">
+        <v>1.55</v>
+      </c>
+      <c r="T124">
+        <v>2.24</v>
+      </c>
+      <c r="U124">
+        <v>3.5</v>
+      </c>
+      <c r="V124">
+        <v>1.25</v>
+      </c>
+      <c r="W124">
+        <v>1.04</v>
+      </c>
+      <c r="X124">
+        <v>1.08</v>
+      </c>
+      <c r="Y124">
+        <v>1.53</v>
+      </c>
+      <c r="Z124">
+        <v>2.35</v>
+      </c>
+      <c r="AA124">
         <v>2.7</v>
       </c>
-      <c r="P124">
-        <v>4.55</v>
-      </c>
-      <c r="Q124">
-        <v>2.8</v>
-      </c>
-      <c r="R124">
-        <v>1.7</v>
-      </c>
-      <c r="S124">
-        <v>1.65</v>
-      </c>
-      <c r="T124">
-        <v>1.99</v>
-      </c>
-      <c r="U124">
-        <v>3.95</v>
-      </c>
-      <c r="V124">
+      <c r="AB124">
+        <v>1.44</v>
+      </c>
+      <c r="AC124">
+        <v>5.5</v>
+      </c>
+      <c r="AD124">
         <v>1.14</v>
       </c>
-      <c r="W124">
+      <c r="AE124">
         <v>1.03</v>
       </c>
-      <c r="X124">
-        <v>1.12</v>
-      </c>
-      <c r="Y124">
-        <v>1.63</v>
-      </c>
-      <c r="Z124">
-        <v>2.1</v>
-      </c>
-      <c r="AA124">
-        <v>3.08</v>
-      </c>
-      <c r="AB124">
-        <v>1.33</v>
-      </c>
-      <c r="AC124">
-        <v>5.75</v>
-      </c>
-      <c r="AD124">
-        <v>1.05</v>
-      </c>
-      <c r="AE124">
-        <v>1.02</v>
-      </c>
       <c r="AF124">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AG124">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK124">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20642,22 +20642,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O125">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P125">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q125">
-        <v>4.75</v>
+        <v>2.8</v>
       </c>
       <c r="R125">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="S125">
-        <v>1.31</v>
+        <v>1.65</v>
       </c>
       <c r="T125">
-        <v>3.1</v>
+        <v>1.98</v>
       </c>
       <c r="U125">
-        <v>2.45</v>
+        <v>3.95</v>
       </c>
       <c r="V125">
-        <v>1.47</v>
+        <v>1.14</v>
       </c>
       <c r="W125">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X125">
+        <v>1.12</v>
+      </c>
+      <c r="Y125">
+        <v>1.63</v>
+      </c>
+      <c r="Z125">
+        <v>2</v>
+      </c>
+      <c r="AA125">
+        <v>3.14</v>
+      </c>
+      <c r="AB125">
+        <v>1.3</v>
+      </c>
+      <c r="AC125">
+        <v>5.75</v>
+      </c>
+      <c r="AD125">
+        <v>1.05</v>
+      </c>
+      <c r="AE125">
         <v>1.02</v>
       </c>
-      <c r="Y125">
-        <v>1.17</v>
-      </c>
-      <c r="Z125">
-        <v>3.9</v>
-      </c>
-      <c r="AA125">
-        <v>1.76</v>
-      </c>
-      <c r="AB125">
-        <v>2.05</v>
-      </c>
-      <c r="AC125">
-        <v>2.8</v>
-      </c>
-      <c r="AD125">
-        <v>1.36</v>
-      </c>
-      <c r="AE125">
-        <v>1.14</v>
-      </c>
       <c r="AF125">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="AG125">
-        <v>2</v>
+        <v>1.44</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>2.01</v>
+        <v>1.2</v>
       </c>
       <c r="AK125">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20805,22 +20805,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O126">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="P126">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="Q126">
-        <v>1.83</v>
+        <v>4.75</v>
       </c>
       <c r="R126">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="S126">
+        <v>1.31</v>
+      </c>
+      <c r="T126">
+        <v>3.1</v>
+      </c>
+      <c r="U126">
+        <v>2.45</v>
+      </c>
+      <c r="V126">
+        <v>1.47</v>
+      </c>
+      <c r="W126">
+        <v>1.07</v>
+      </c>
+      <c r="X126">
+        <v>1.02</v>
+      </c>
+      <c r="Y126">
+        <v>1.17</v>
+      </c>
+      <c r="Z126">
+        <v>3.9</v>
+      </c>
+      <c r="AA126">
+        <v>1.76</v>
+      </c>
+      <c r="AB126">
+        <v>2.05</v>
+      </c>
+      <c r="AC126">
+        <v>2.8</v>
+      </c>
+      <c r="AD126">
+        <v>1.36</v>
+      </c>
+      <c r="AE126">
         <v>1.14</v>
       </c>
-      <c r="T126">
-        <v>5</v>
-      </c>
-      <c r="U126">
-        <v>1.86</v>
-      </c>
-      <c r="V126">
-        <v>1.91</v>
-      </c>
-      <c r="W126">
-        <v>1.24</v>
-      </c>
-      <c r="X126">
-        <v>1.01</v>
-      </c>
-      <c r="Y126">
-        <v>1.03</v>
-      </c>
-      <c r="Z126">
-        <v>7.2</v>
-      </c>
-      <c r="AA126">
-        <v>1.25</v>
-      </c>
-      <c r="AB126">
-        <v>3.28</v>
-      </c>
-      <c r="AC126">
-        <v>1.74</v>
-      </c>
-      <c r="AD126">
-        <v>1.98</v>
-      </c>
-      <c r="AE126">
-        <v>1.4</v>
-      </c>
       <c r="AF126">
-        <v>1.39</v>
+        <v>1.65</v>
       </c>
       <c r="AG126">
-        <v>2.72</v>
+        <v>2</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.14</v>
+        <v>2.01</v>
       </c>
       <c r="AK126">
-        <v>2.61</v>
+        <v>1.2</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>1.82</v>
+        <v>1.4</v>
       </c>
       <c r="O127">
-        <v>3.8</v>
+        <v>4.95</v>
       </c>
       <c r="P127">
-        <v>3.25</v>
+        <v>5.45</v>
       </c>
       <c r="Q127">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="R127">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="S127">
         <v>1.14</v>
       </c>
       <c r="T127">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="U127">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="V127">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="W127">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X127">
         <v>1.01</v>
       </c>
       <c r="Y127">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Z127">
-        <v>8.5</v>
+        <v>7.2</v>
       </c>
       <c r="AA127">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AB127">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="AC127">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="AD127">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AE127">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AF127">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="AG127">
-        <v>3.48</v>
+        <v>2.72</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AK127">
-        <v>1.87</v>
+        <v>2.61</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,34 +21173,34 @@
         </is>
       </c>
       <c r="N128">
-        <v>2.04</v>
+        <v>1.82</v>
       </c>
       <c r="O128">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="P128">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="Q128">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="R128">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="S128">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T128">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="U128">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="V128">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="W128">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X128">
         <v>1.01</v>
@@ -21209,28 +21209,28 @@
         <v>1.06</v>
       </c>
       <c r="Z128">
-        <v>6.15</v>
+        <v>8.5</v>
       </c>
       <c r="AA128">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AB128">
-        <v>2.92</v>
+        <v>3.8</v>
       </c>
       <c r="AC128">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="AD128">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AE128">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AF128">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AG128">
-        <v>3.1</v>
+        <v>3.48</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK128">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,31 +21336,31 @@
         </is>
       </c>
       <c r="N129">
-        <v>1.31</v>
+        <v>2.04</v>
       </c>
       <c r="O129">
-        <v>5</v>
+        <v>3.65</v>
       </c>
       <c r="P129">
-        <v>6.55</v>
+        <v>2.85</v>
       </c>
       <c r="Q129">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="R129">
-        <v>2.69</v>
+        <v>2.49</v>
       </c>
       <c r="S129">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T129">
-        <v>3.92</v>
+        <v>4.4</v>
       </c>
       <c r="U129">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="V129">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="W129">
         <v>1.22</v>
@@ -21372,28 +21372,28 @@
         <v>1.06</v>
       </c>
       <c r="Z129">
-        <v>6.5</v>
+        <v>6.15</v>
       </c>
       <c r="AA129">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AB129">
-        <v>3.12</v>
+        <v>2.92</v>
       </c>
       <c r="AC129">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AD129">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AE129">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AF129">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="AG129">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AK129">
-        <v>3.6</v>
+        <v>1.57</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21457,22 +21457,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,64 +21499,64 @@
         </is>
       </c>
       <c r="N130">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O130">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P130">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="Q130">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="R130">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="S130">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T130">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="U130">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V130">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W130">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X130">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y130">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z130">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA130">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB130">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AC130">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD130">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE130">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF130">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG130">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK130">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G133">
@@ -22104,12 +22104,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O134">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P134">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="Q134">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R134">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S134">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="T134">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U134">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V134">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W134">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X134">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y134">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z134">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA134">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB134">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC134">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD134">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE134">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF134">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG134">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK134">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22255,7 +22255,7 @@
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>2026-08-09 15:15:00</t>
+          <t>2026-08-09 15:00:00</t>
         </is>
       </c>
     </row>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="O135">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="P135">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="Q135">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="R135">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S135">
+        <v>1.34</v>
+      </c>
+      <c r="T135">
+        <v>2.88</v>
+      </c>
+      <c r="U135">
+        <v>2.75</v>
+      </c>
+      <c r="V135">
+        <v>1.4</v>
+      </c>
+      <c r="W135">
+        <v>1.1</v>
+      </c>
+      <c r="X135">
+        <v>1.05</v>
+      </c>
+      <c r="Y135">
         <v>1.25</v>
       </c>
-      <c r="T135">
+      <c r="Z135">
         <v>3.5</v>
       </c>
-      <c r="U135">
-        <v>2.25</v>
-      </c>
-      <c r="V135">
-        <v>1.53</v>
-      </c>
-      <c r="W135">
-        <v>1.14</v>
-      </c>
-      <c r="X135">
-        <v>1.03</v>
-      </c>
-      <c r="Y135">
-        <v>1.18</v>
-      </c>
-      <c r="Z135">
-        <v>4.5</v>
-      </c>
       <c r="AA135">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="AB135">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AC135">
-        <v>2.47</v>
+        <v>3.1</v>
       </c>
       <c r="AD135">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AE135">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AF135">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AG135">
-        <v>2.36</v>
+        <v>2</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK135">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22435,7 +22435,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,80 +22477,80 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="O136">
-        <v>3.08</v>
+        <v>3.65</v>
       </c>
       <c r="P136">
-        <v>2.62</v>
+        <v>3.4</v>
       </c>
       <c r="Q136">
-        <v>2.96</v>
+        <v>2.45</v>
       </c>
       <c r="R136">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="S136">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="T136">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="U136">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="V136">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="W136">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X136">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y136">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z136">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA136">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="AB136">
+        <v>2.2</v>
+      </c>
+      <c r="AC136">
+        <v>2.47</v>
+      </c>
+      <c r="AD136">
+        <v>1.5</v>
+      </c>
+      <c r="AE136">
+        <v>1.18</v>
+      </c>
+      <c r="AF136">
+        <v>1.5</v>
+      </c>
+      <c r="AG136">
+        <v>2.36</v>
+      </c>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ136">
+        <v>1.21</v>
+      </c>
+      <c r="AK136">
         <v>1.75</v>
-      </c>
-      <c r="AC136">
-        <v>3.5</v>
-      </c>
-      <c r="AD136">
-        <v>1.25</v>
-      </c>
-      <c r="AE136">
-        <v>1.1</v>
-      </c>
-      <c r="AF136">
-        <v>1.73</v>
-      </c>
-      <c r="AG136">
-        <v>2</v>
-      </c>
-      <c r="AH136" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI136" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ136">
-        <v>1.25</v>
-      </c>
-      <c r="AK136">
-        <v>1.55</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22598,7 +22598,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,64 +22640,64 @@
         </is>
       </c>
       <c r="N137">
-        <v>5.65</v>
+        <v>2.12</v>
       </c>
       <c r="O137">
-        <v>3.9</v>
+        <v>3.08</v>
       </c>
       <c r="P137">
-        <v>1.48</v>
+        <v>2.62</v>
       </c>
       <c r="Q137">
-        <v>6</v>
+        <v>2.96</v>
       </c>
       <c r="R137">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="S137">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T137">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U137">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="V137">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W137">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X137">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y137">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z137">
-        <v>3.66</v>
+        <v>3.2</v>
       </c>
       <c r="AA137">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AB137">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AC137">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="AD137">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AE137">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF137">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AG137">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>2.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK137">
-        <v>1.13</v>
+        <v>1.55</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22756,27 +22756,27 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G138">
@@ -22803,81 +22803,81 @@
         </is>
       </c>
       <c r="N138">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="O138">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P138">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q138">
-        <v>2.1</v>
+        <v>6</v>
       </c>
       <c r="R138">
-        <v>1.94</v>
+        <v>2.36</v>
       </c>
       <c r="S138">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="T138">
-        <v>2.31</v>
+        <v>3</v>
       </c>
       <c r="U138">
-        <v>3.46</v>
+        <v>2.79</v>
       </c>
       <c r="V138">
+        <v>1.41</v>
+      </c>
+      <c r="W138">
+        <v>1.06</v>
+      </c>
+      <c r="X138">
+        <v>1.01</v>
+      </c>
+      <c r="Y138">
         <v>1.24</v>
       </c>
-      <c r="W138">
-        <v>1.04</v>
-      </c>
-      <c r="X138">
-        <v>1.04</v>
-      </c>
-      <c r="Y138">
-        <v>1.42</v>
-      </c>
       <c r="Z138">
-        <v>2.55</v>
+        <v>3.66</v>
       </c>
       <c r="AA138">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="AB138">
-        <v>1.5</v>
+        <v>1.88</v>
       </c>
       <c r="AC138">
-        <v>4.6</v>
+        <v>3.18</v>
       </c>
       <c r="AD138">
+        <v>1.33</v>
+      </c>
+      <c r="AE138">
+        <v>1.11</v>
+      </c>
+      <c r="AF138">
+        <v>1.91</v>
+      </c>
+      <c r="AG138">
+        <v>1.77</v>
+      </c>
+      <c r="AH138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ138">
+        <v>2.27</v>
+      </c>
+      <c r="AK138">
         <v>1.13</v>
       </c>
-      <c r="AE138">
-        <v>1.05</v>
-      </c>
-      <c r="AF138">
-        <v>2.4</v>
-      </c>
-      <c r="AG138">
-        <v>1.5</v>
-      </c>
-      <c r="AH138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ138">
-        <v>1.08</v>
-      </c>
-      <c r="AK138">
-        <v>2.45</v>
-      </c>
       <c r="AL138">
         <v>0</v>
       </c>
@@ -22907,7 +22907,7 @@
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>2026-08-09 15:30:00</t>
+          <t>2026-08-09 15:15:00</t>
         </is>
       </c>
     </row>
@@ -22924,22 +22924,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G139">
@@ -22975,55 +22975,55 @@
         <v>0</v>
       </c>
       <c r="Q139">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R139">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S139">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T139">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U139">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="V139">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W139">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X139">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y139">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z139">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA139">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB139">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC139">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD139">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE139">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF139">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG139">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK139">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="G140">
@@ -23250,7 +23250,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G141">
@@ -23292,64 +23292,64 @@
         </is>
       </c>
       <c r="N141">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="O141">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P141">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="Q141">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R141">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S141">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T141">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U141">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V141">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W141">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X141">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y141">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z141">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA141">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB141">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC141">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD141">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE141">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF141">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG141">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK141">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23408,27 +23408,27 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G142">
@@ -23455,64 +23455,64 @@
         </is>
       </c>
       <c r="N142">
-        <v>2.52</v>
+        <v>1.64</v>
       </c>
       <c r="O142">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="P142">
-        <v>2.55</v>
+        <v>5.01</v>
       </c>
       <c r="Q142">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R142">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S142">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T142">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U142">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V142">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W142">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X142">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y142">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z142">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA142">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="AB142">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="AC142">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD142">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE142">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF142">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG142">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23525,10 +23525,10 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK142">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23559,7 +23559,7 @@
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>2026-08-09 16:00:00</t>
+          <t>2026-08-09 15:30:00</t>
         </is>
       </c>
     </row>
@@ -23576,22 +23576,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,13 +23618,13 @@
         </is>
       </c>
       <c r="N143">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O143">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P143">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -23657,10 +23657,10 @@
         <v>0</v>
       </c>
       <c r="AA143">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB143">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC143">
         <v>0</v>
@@ -23739,22 +23739,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O144">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="P144">
-        <v>6.63</v>
+        <v>0</v>
       </c>
       <c r="Q144">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="R144">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S144">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="T144">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U144">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V144">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W144">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X144">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y144">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z144">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AA144">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB144">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC144">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AD144">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE144">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF144">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG144">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK144">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="O145">
-        <v>3.67</v>
+        <v>3.91</v>
       </c>
       <c r="P145">
-        <v>4.48</v>
+        <v>6.63</v>
       </c>
       <c r="Q145">
-        <v>2.46</v>
+        <v>2.12</v>
       </c>
       <c r="R145">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="S145">
+        <v>1.37</v>
+      </c>
+      <c r="T145">
+        <v>2.8</v>
+      </c>
+      <c r="U145">
+        <v>2.88</v>
+      </c>
+      <c r="V145">
         <v>1.36</v>
       </c>
-      <c r="T145">
-        <v>3.08</v>
-      </c>
-      <c r="U145">
-        <v>2.79</v>
-      </c>
-      <c r="V145">
-        <v>1.42</v>
-      </c>
       <c r="W145">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X145">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y145">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z145">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="AA145">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AB145">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="AC145">
-        <v>2.94</v>
+        <v>3.45</v>
       </c>
       <c r="AD145">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE145">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF145">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AG145">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK145">
-        <v>1.75</v>
+        <v>2.28</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24065,7 +24065,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
-        <v>1.54</v>
+        <v>1.83</v>
       </c>
       <c r="O146">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="P146">
-        <v>5.2</v>
+        <v>4.48</v>
       </c>
       <c r="Q146">
-        <v>2.05</v>
+        <v>2.48</v>
       </c>
       <c r="R146">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="S146">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T146">
-        <v>2.75</v>
+        <v>3.08</v>
       </c>
       <c r="U146">
-        <v>2.71</v>
+        <v>2.79</v>
       </c>
       <c r="V146">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="W146">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X146">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y146">
         <v>1.24</v>
       </c>
       <c r="Z146">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="AA146">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AB146">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AC146">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="AD146">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AE146">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF146">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AG146">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AK146">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,64 +24270,64 @@
         </is>
       </c>
       <c r="N147">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O147">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P147">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q147">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="R147">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="S147">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="T147">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U147">
-        <v>3.4</v>
+        <v>2.71</v>
       </c>
       <c r="V147">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="W147">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X147">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y147">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
       <c r="Z147">
-        <v>2.44</v>
+        <v>3.34</v>
       </c>
       <c r="AA147">
-        <v>2.55</v>
+        <v>1.91</v>
       </c>
       <c r="AB147">
-        <v>1.5</v>
+        <v>1.88</v>
       </c>
       <c r="AC147">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD147">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="AE147">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF147">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AG147">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK147">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24391,7 +24391,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,64 +24433,64 @@
         </is>
       </c>
       <c r="N148">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="O148">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P148">
-        <v>3.3</v>
+        <v>3.87</v>
       </c>
       <c r="Q148">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R148">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S148">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T148">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U148">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V148">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W148">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X148">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y148">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z148">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA148">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB148">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC148">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD148">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE148">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF148">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG148">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -24503,10 +24503,10 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK148">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -24554,7 +24554,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G149">
@@ -24596,64 +24596,64 @@
         </is>
       </c>
       <c r="N149">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O149">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P149">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q149">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R149">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S149">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T149">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U149">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V149">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W149">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X149">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y149">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z149">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA149">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB149">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC149">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD149">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE149">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF149">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG149">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
@@ -24666,10 +24666,10 @@
         </is>
       </c>
       <c r="AJ149">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK149">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -24717,22 +24717,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G150">
@@ -24759,64 +24759,64 @@
         </is>
       </c>
       <c r="N150">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O150">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P150">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q150">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R150">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="S150">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="T150">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U150">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="V150">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W150">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X150">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y150">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z150">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA150">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB150">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC150">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AD150">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE150">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF150">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG150">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AH150" t="inlineStr">
         <is>
@@ -24829,10 +24829,10 @@
         </is>
       </c>
       <c r="AJ150">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK150">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AL150">
         <v>0</v>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,64 +24922,64 @@
         </is>
       </c>
       <c r="N151">
-        <v>2.28</v>
+        <v>2.65</v>
       </c>
       <c r="O151">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="P151">
+        <v>2.85</v>
+      </c>
+      <c r="Q151">
+        <v>3.1</v>
+      </c>
+      <c r="R151">
+        <v>1.81</v>
+      </c>
+      <c r="S151">
+        <v>1.51</v>
+      </c>
+      <c r="T151">
+        <v>2.31</v>
+      </c>
+      <c r="U151">
+        <v>3.02</v>
+      </c>
+      <c r="V151">
+        <v>1.31</v>
+      </c>
+      <c r="W151">
+        <v>1.02</v>
+      </c>
+      <c r="X151">
+        <v>1.06</v>
+      </c>
+      <c r="Y151">
+        <v>1.32</v>
+      </c>
+      <c r="Z151">
         <v>2.88</v>
       </c>
-      <c r="Q151">
-        <v>3</v>
-      </c>
-      <c r="R151">
-        <v>2.15</v>
-      </c>
-      <c r="S151">
-        <v>1.33</v>
-      </c>
-      <c r="T151">
-        <v>3.3</v>
-      </c>
-      <c r="U151">
-        <v>2.36</v>
-      </c>
-      <c r="V151">
-        <v>1.5</v>
-      </c>
-      <c r="W151">
-        <v>1.09</v>
-      </c>
-      <c r="X151">
-        <v>1</v>
-      </c>
-      <c r="Y151">
+      <c r="AA151">
+        <v>2.2</v>
+      </c>
+      <c r="AB151">
+        <v>1.65</v>
+      </c>
+      <c r="AC151">
+        <v>3.48</v>
+      </c>
+      <c r="AD151">
         <v>1.22</v>
       </c>
-      <c r="Z151">
-        <v>4</v>
-      </c>
-      <c r="AA151">
-        <v>1.73</v>
-      </c>
-      <c r="AB151">
-        <v>2</v>
-      </c>
-      <c r="AC151">
-        <v>2.75</v>
-      </c>
-      <c r="AD151">
-        <v>1.42</v>
-      </c>
       <c r="AE151">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AF151">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AG151">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -24992,10 +24992,10 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AK151">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25043,22 +25043,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,64 +25085,64 @@
         </is>
       </c>
       <c r="N152">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="O152">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="P152">
+        <v>2.88</v>
+      </c>
+      <c r="Q152">
+        <v>3</v>
+      </c>
+      <c r="R152">
+        <v>2.15</v>
+      </c>
+      <c r="S152">
+        <v>1.33</v>
+      </c>
+      <c r="T152">
+        <v>3.3</v>
+      </c>
+      <c r="U152">
+        <v>2.36</v>
+      </c>
+      <c r="V152">
+        <v>1.5</v>
+      </c>
+      <c r="W152">
+        <v>1.09</v>
+      </c>
+      <c r="X152">
+        <v>1</v>
+      </c>
+      <c r="Y152">
+        <v>1.22</v>
+      </c>
+      <c r="Z152">
         <v>4</v>
       </c>
-      <c r="Q152">
-        <v>0</v>
-      </c>
-      <c r="R152">
-        <v>0</v>
-      </c>
-      <c r="S152">
-        <v>0</v>
-      </c>
-      <c r="T152">
-        <v>0</v>
-      </c>
-      <c r="U152">
-        <v>0</v>
-      </c>
-      <c r="V152">
-        <v>0</v>
-      </c>
-      <c r="W152">
-        <v>0</v>
-      </c>
-      <c r="X152">
-        <v>0</v>
-      </c>
-      <c r="Y152">
-        <v>0</v>
-      </c>
-      <c r="Z152">
-        <v>0</v>
-      </c>
       <c r="AA152">
-        <v>3.4</v>
+        <v>1.73</v>
       </c>
       <c r="AB152">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AC152">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD152">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE152">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF152">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG152">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK152">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,49 +25248,49 @@
         </is>
       </c>
       <c r="N153">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="O153">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="P153">
+        <v>3.9</v>
+      </c>
+      <c r="Q153">
+        <v>0</v>
+      </c>
+      <c r="R153">
+        <v>0</v>
+      </c>
+      <c r="S153">
+        <v>0</v>
+      </c>
+      <c r="T153">
+        <v>0</v>
+      </c>
+      <c r="U153">
+        <v>0</v>
+      </c>
+      <c r="V153">
+        <v>0</v>
+      </c>
+      <c r="W153">
+        <v>0</v>
+      </c>
+      <c r="X153">
+        <v>0</v>
+      </c>
+      <c r="Y153">
+        <v>0</v>
+      </c>
+      <c r="Z153">
+        <v>0</v>
+      </c>
+      <c r="AA153">
         <v>3.4</v>
       </c>
-      <c r="Q153">
-        <v>0</v>
-      </c>
-      <c r="R153">
-        <v>0</v>
-      </c>
-      <c r="S153">
-        <v>0</v>
-      </c>
-      <c r="T153">
-        <v>0</v>
-      </c>
-      <c r="U153">
-        <v>0</v>
-      </c>
-      <c r="V153">
-        <v>0</v>
-      </c>
-      <c r="W153">
-        <v>0</v>
-      </c>
-      <c r="X153">
-        <v>0</v>
-      </c>
-      <c r="Y153">
-        <v>0</v>
-      </c>
-      <c r="Z153">
-        <v>0</v>
-      </c>
-      <c r="AA153">
-        <v>2.87</v>
-      </c>
       <c r="AB153">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AC153">
         <v>0</v>
@@ -25369,22 +25369,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
-        <v>1.36</v>
+        <v>2.4</v>
       </c>
       <c r="O154">
-        <v>4.8</v>
+        <v>2.65</v>
       </c>
       <c r="P154">
-        <v>6.5</v>
+        <v>3.2</v>
       </c>
       <c r="Q154">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R154">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S154">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T154">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U154">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="V154">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W154">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X154">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y154">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z154">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AA154">
-        <v>1.62</v>
+        <v>2.87</v>
       </c>
       <c r="AB154">
-        <v>2.25</v>
+        <v>1.4</v>
       </c>
       <c r="AC154">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD154">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE154">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF154">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG154">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK154">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25532,22 +25532,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,80 +25574,80 @@
         </is>
       </c>
       <c r="N155">
-        <v>2.28</v>
+        <v>1.36</v>
       </c>
       <c r="O155">
-        <v>3.15</v>
+        <v>4.8</v>
       </c>
       <c r="P155">
-        <v>3.16</v>
+        <v>6.5</v>
       </c>
       <c r="Q155">
-        <v>3</v>
+        <v>1.85</v>
       </c>
       <c r="R155">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="S155">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="T155">
+        <v>3.25</v>
+      </c>
+      <c r="U155">
+        <v>2.52</v>
+      </c>
+      <c r="V155">
+        <v>1.5</v>
+      </c>
+      <c r="W155">
+        <v>1.11</v>
+      </c>
+      <c r="X155">
+        <v>1.03</v>
+      </c>
+      <c r="Y155">
+        <v>1.18</v>
+      </c>
+      <c r="Z155">
+        <v>4.33</v>
+      </c>
+      <c r="AA155">
+        <v>1.62</v>
+      </c>
+      <c r="AB155">
+        <v>2.25</v>
+      </c>
+      <c r="AC155">
+        <v>2.6</v>
+      </c>
+      <c r="AD155">
+        <v>1.44</v>
+      </c>
+      <c r="AE155">
+        <v>1.15</v>
+      </c>
+      <c r="AF155">
+        <v>1.85</v>
+      </c>
+      <c r="AG155">
+        <v>1.88</v>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ155">
+        <v>1.18</v>
+      </c>
+      <c r="AK155">
         <v>2.88</v>
-      </c>
-      <c r="U155">
-        <v>2.85</v>
-      </c>
-      <c r="V155">
-        <v>1.36</v>
-      </c>
-      <c r="W155">
-        <v>1.08</v>
-      </c>
-      <c r="X155">
-        <v>1</v>
-      </c>
-      <c r="Y155">
-        <v>1.3</v>
-      </c>
-      <c r="Z155">
-        <v>3.3</v>
-      </c>
-      <c r="AA155">
-        <v>2</v>
-      </c>
-      <c r="AB155">
-        <v>1.76</v>
-      </c>
-      <c r="AC155">
-        <v>3.34</v>
-      </c>
-      <c r="AD155">
-        <v>1.24</v>
-      </c>
-      <c r="AE155">
-        <v>1.07</v>
-      </c>
-      <c r="AF155">
-        <v>1.73</v>
-      </c>
-      <c r="AG155">
-        <v>2</v>
-      </c>
-      <c r="AH155" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI155" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ155">
-        <v>1.3</v>
-      </c>
-      <c r="AK155">
-        <v>1.59</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
+        <v>2.28</v>
+      </c>
+      <c r="O156">
+        <v>3.15</v>
+      </c>
+      <c r="P156">
+        <v>3.16</v>
+      </c>
+      <c r="Q156">
+        <v>3</v>
+      </c>
+      <c r="R156">
         <v>2.05</v>
       </c>
-      <c r="O156">
-        <v>3.1</v>
-      </c>
-      <c r="P156">
-        <v>3.8</v>
-      </c>
-      <c r="Q156">
-        <v>2.5</v>
-      </c>
-      <c r="R156">
-        <v>1.95</v>
-      </c>
       <c r="S156">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="T156">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="U156">
-        <v>3.6</v>
+        <v>2.85</v>
       </c>
       <c r="V156">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="W156">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X156">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y156">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="Z156">
-        <v>2.59</v>
+        <v>3.3</v>
       </c>
       <c r="AA156">
-        <v>2.51</v>
+        <v>2</v>
       </c>
       <c r="AB156">
-        <v>1.49</v>
+        <v>1.76</v>
       </c>
       <c r="AC156">
-        <v>4.84</v>
+        <v>3.34</v>
       </c>
       <c r="AD156">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AE156">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF156">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AG156">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>1.3</v>
       </c>
       <c r="AK156">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25853,12 +25853,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
-        <v>1.63</v>
+        <v>2.05</v>
       </c>
       <c r="O157">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="P157">
-        <v>5.95</v>
+        <v>3.8</v>
       </c>
       <c r="Q157">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="R157">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="S157">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="T157">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="U157">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="V157">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W157">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X157">
         <v>1.05</v>
       </c>
       <c r="Y157">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="Z157">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="AA157">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="AB157">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AC157">
-        <v>5.04</v>
+        <v>4.84</v>
       </c>
       <c r="AD157">
         <v>1.17</v>
       </c>
       <c r="AE157">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF157">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AG157">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25973,7 +25973,7 @@
         <v>1.3</v>
       </c>
       <c r="AK157">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26004,7 +26004,7 @@
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>2026-08-09 16:30:00</t>
+          <t>2026-08-09 16:00:00</t>
         </is>
       </c>
     </row>
@@ -26021,22 +26021,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,80 +26063,80 @@
         </is>
       </c>
       <c r="N158">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="O158">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="P158">
-        <v>3.28</v>
+        <v>5.95</v>
       </c>
       <c r="Q158">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="R158">
-        <v>2.16</v>
+        <v>1.92</v>
       </c>
       <c r="S158">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="T158">
-        <v>2.73</v>
+        <v>2.4</v>
       </c>
       <c r="U158">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="V158">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="W158">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X158">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y158">
+        <v>1.53</v>
+      </c>
+      <c r="Z158">
+        <v>2.45</v>
+      </c>
+      <c r="AA158">
+        <v>2.5</v>
+      </c>
+      <c r="AB158">
+        <v>1.44</v>
+      </c>
+      <c r="AC158">
+        <v>5.04</v>
+      </c>
+      <c r="AD158">
+        <v>1.17</v>
+      </c>
+      <c r="AE158">
+        <v>1.01</v>
+      </c>
+      <c r="AF158">
+        <v>2.18</v>
+      </c>
+      <c r="AG158">
+        <v>1.57</v>
+      </c>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ158">
         <v>1.3</v>
       </c>
-      <c r="Z158">
-        <v>3.3</v>
-      </c>
-      <c r="AA158">
-        <v>1.89</v>
-      </c>
-      <c r="AB158">
-        <v>1.8</v>
-      </c>
-      <c r="AC158">
-        <v>3.24</v>
-      </c>
-      <c r="AD158">
-        <v>1.31</v>
-      </c>
-      <c r="AE158">
-        <v>1.08</v>
-      </c>
-      <c r="AF158">
-        <v>1.75</v>
-      </c>
-      <c r="AG158">
-        <v>1.9</v>
-      </c>
-      <c r="AH158" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI158" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ158">
-        <v>1.32</v>
-      </c>
       <c r="AK158">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,64 +26226,64 @@
         </is>
       </c>
       <c r="N159">
-        <v>4.75</v>
+        <v>1.95</v>
       </c>
       <c r="O159">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="P159">
-        <v>1.69</v>
+        <v>3.28</v>
       </c>
       <c r="Q159">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="R159">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="S159">
         <v>1.36</v>
       </c>
       <c r="T159">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="U159">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="V159">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W159">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X159">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y159">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z159">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AA159">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="AB159">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC159">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="AD159">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AE159">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF159">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AG159">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26296,10 +26296,10 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>2.14</v>
+        <v>1.32</v>
       </c>
       <c r="AK159">
-        <v>1.18</v>
+        <v>1.78</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,80 +26389,80 @@
         </is>
       </c>
       <c r="N160">
-        <v>1.11</v>
+        <v>4.75</v>
       </c>
       <c r="O160">
-        <v>8.6</v>
+        <v>3.6</v>
       </c>
       <c r="P160">
-        <v>16</v>
+        <v>1.69</v>
       </c>
       <c r="Q160">
-        <v>1.44</v>
+        <v>4.8</v>
       </c>
       <c r="R160">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="S160">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="T160">
-        <v>3.94</v>
+        <v>2.66</v>
       </c>
       <c r="U160">
-        <v>2.1</v>
+        <v>2.81</v>
       </c>
       <c r="V160">
-        <v>1.68</v>
+        <v>1.38</v>
       </c>
       <c r="W160">
+        <v>1.04</v>
+      </c>
+      <c r="X160">
+        <v>1.05</v>
+      </c>
+      <c r="Y160">
+        <v>1.29</v>
+      </c>
+      <c r="Z160">
+        <v>3.35</v>
+      </c>
+      <c r="AA160">
+        <v>1.96</v>
+      </c>
+      <c r="AB160">
+        <v>1.85</v>
+      </c>
+      <c r="AC160">
+        <v>3.3</v>
+      </c>
+      <c r="AD160">
+        <v>1.27</v>
+      </c>
+      <c r="AE160">
+        <v>1.06</v>
+      </c>
+      <c r="AF160">
+        <v>1.84</v>
+      </c>
+      <c r="AG160">
+        <v>1.84</v>
+      </c>
+      <c r="AH160" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI160" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ160">
+        <v>2.14</v>
+      </c>
+      <c r="AK160">
         <v>1.18</v>
-      </c>
-      <c r="X160">
-        <v>1.01</v>
-      </c>
-      <c r="Y160">
-        <v>1.08</v>
-      </c>
-      <c r="Z160">
-        <v>5.41</v>
-      </c>
-      <c r="AA160">
-        <v>1.41</v>
-      </c>
-      <c r="AB160">
-        <v>2.63</v>
-      </c>
-      <c r="AC160">
-        <v>2.1</v>
-      </c>
-      <c r="AD160">
-        <v>1.65</v>
-      </c>
-      <c r="AE160">
-        <v>1.26</v>
-      </c>
-      <c r="AF160">
-        <v>2.45</v>
-      </c>
-      <c r="AG160">
-        <v>1.5</v>
-      </c>
-      <c r="AH160" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI160" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ160">
-        <v>1.06</v>
-      </c>
-      <c r="AK160">
-        <v>6.25</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -26505,27 +26505,27 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,61 +26552,61 @@
         </is>
       </c>
       <c r="N161">
-        <v>1.53</v>
+        <v>1.11</v>
       </c>
       <c r="O161">
-        <v>3.35</v>
+        <v>8.6</v>
       </c>
       <c r="P161">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="Q161">
-        <v>2.16</v>
+        <v>1.44</v>
       </c>
       <c r="R161">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="S161">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="T161">
+        <v>3.94</v>
+      </c>
+      <c r="U161">
+        <v>2.1</v>
+      </c>
+      <c r="V161">
+        <v>1.68</v>
+      </c>
+      <c r="W161">
+        <v>1.18</v>
+      </c>
+      <c r="X161">
+        <v>1.01</v>
+      </c>
+      <c r="Y161">
+        <v>1.08</v>
+      </c>
+      <c r="Z161">
+        <v>5.41</v>
+      </c>
+      <c r="AA161">
+        <v>1.41</v>
+      </c>
+      <c r="AB161">
+        <v>2.63</v>
+      </c>
+      <c r="AC161">
+        <v>2.1</v>
+      </c>
+      <c r="AD161">
+        <v>1.65</v>
+      </c>
+      <c r="AE161">
+        <v>1.26</v>
+      </c>
+      <c r="AF161">
         <v>2.45</v>
-      </c>
-      <c r="U161">
-        <v>3.3</v>
-      </c>
-      <c r="V161">
-        <v>1.29</v>
-      </c>
-      <c r="W161">
-        <v>1.05</v>
-      </c>
-      <c r="X161">
-        <v>1.08</v>
-      </c>
-      <c r="Y161">
-        <v>1.45</v>
-      </c>
-      <c r="Z161">
-        <v>2.48</v>
-      </c>
-      <c r="AA161">
-        <v>2.43</v>
-      </c>
-      <c r="AB161">
-        <v>1.47</v>
-      </c>
-      <c r="AC161">
-        <v>5.5</v>
-      </c>
-      <c r="AD161">
-        <v>1.15</v>
-      </c>
-      <c r="AE161">
-        <v>1.04</v>
-      </c>
-      <c r="AF161">
-        <v>2.5</v>
       </c>
       <c r="AG161">
         <v>1.5</v>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>1.23</v>
+        <v>1.06</v>
       </c>
       <c r="AK161">
-        <v>2.3</v>
+        <v>6.25</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -26656,7 +26656,7 @@
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>2026-08-09 17:00:00</t>
+          <t>2026-08-09 16:30:00</t>
         </is>
       </c>
     </row>
@@ -26673,7 +26673,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G162">
@@ -26715,64 +26715,64 @@
         </is>
       </c>
       <c r="N162">
-        <v>2.41</v>
+        <v>1.53</v>
       </c>
       <c r="O162">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P162">
+        <v>6</v>
+      </c>
+      <c r="Q162">
+        <v>2.16</v>
+      </c>
+      <c r="R162">
+        <v>2.05</v>
+      </c>
+      <c r="S162">
+        <v>1.44</v>
+      </c>
+      <c r="T162">
+        <v>2.45</v>
+      </c>
+      <c r="U162">
+        <v>3.3</v>
+      </c>
+      <c r="V162">
+        <v>1.29</v>
+      </c>
+      <c r="W162">
+        <v>1.05</v>
+      </c>
+      <c r="X162">
+        <v>1.08</v>
+      </c>
+      <c r="Y162">
+        <v>1.45</v>
+      </c>
+      <c r="Z162">
+        <v>2.48</v>
+      </c>
+      <c r="AA162">
         <v>2.43</v>
       </c>
-      <c r="Q162">
-        <v>0</v>
-      </c>
-      <c r="R162">
-        <v>0</v>
-      </c>
-      <c r="S162">
-        <v>0</v>
-      </c>
-      <c r="T162">
-        <v>0</v>
-      </c>
-      <c r="U162">
-        <v>0</v>
-      </c>
-      <c r="V162">
-        <v>0</v>
-      </c>
-      <c r="W162">
-        <v>0</v>
-      </c>
-      <c r="X162">
-        <v>0</v>
-      </c>
-      <c r="Y162">
-        <v>0</v>
-      </c>
-      <c r="Z162">
-        <v>0</v>
-      </c>
-      <c r="AA162">
-        <v>0</v>
-      </c>
       <c r="AB162">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC162">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD162">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE162">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF162">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG162">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26785,10 +26785,10 @@
         </is>
       </c>
       <c r="AJ162">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK162">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -26831,12 +26831,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G163">
@@ -26878,64 +26878,64 @@
         </is>
       </c>
       <c r="N163">
-        <v>1.57</v>
+        <v>2.41</v>
       </c>
       <c r="O163">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="P163">
-        <v>4.2</v>
+        <v>2.43</v>
       </c>
       <c r="Q163">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="R163">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S163">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="T163">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="U163">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V163">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W163">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X163">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y163">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z163">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA163">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB163">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AC163">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD163">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AE163">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF163">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AG163">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -26948,10 +26948,10 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK163">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -26982,7 +26982,7 @@
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>2026-08-09 17:15:00</t>
+          <t>2026-08-09 17:00:00</t>
         </is>
       </c>
     </row>
@@ -26994,12 +26994,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,65 +27041,65 @@
         </is>
       </c>
       <c r="N164">
-        <v>1.94</v>
+        <v>1.57</v>
       </c>
       <c r="O164">
-        <v>2.91</v>
+        <v>4.2</v>
       </c>
       <c r="P164">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="Q164">
-        <v>2.5</v>
+        <v>2.04</v>
       </c>
       <c r="R164">
-        <v>1.85</v>
+        <v>2.9</v>
       </c>
       <c r="S164">
-        <v>1.57</v>
+        <v>1.15</v>
       </c>
       <c r="T164">
-        <v>2.21</v>
+        <v>4.8</v>
       </c>
       <c r="U164">
-        <v>3.9</v>
+        <v>1.8</v>
       </c>
       <c r="V164">
-        <v>1.22</v>
+        <v>2</v>
       </c>
       <c r="W164">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
       <c r="X164">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y164">
-        <v>1.6</v>
+        <v>1.06</v>
       </c>
       <c r="Z164">
-        <v>2.15</v>
+        <v>8</v>
       </c>
       <c r="AA164">
+        <v>1.28</v>
+      </c>
+      <c r="AB164">
+        <v>3.5</v>
+      </c>
+      <c r="AC164">
+        <v>1.71</v>
+      </c>
+      <c r="AD164">
+        <v>2.11</v>
+      </c>
+      <c r="AE164">
+        <v>1.44</v>
+      </c>
+      <c r="AF164">
+        <v>1.33</v>
+      </c>
+      <c r="AG164">
         <v>3.1</v>
       </c>
-      <c r="AB164">
-        <v>1.34</v>
-      </c>
-      <c r="AC164">
-        <v>6.05</v>
-      </c>
-      <c r="AD164">
-        <v>1.11</v>
-      </c>
-      <c r="AE164">
-        <v>1.03</v>
-      </c>
-      <c r="AF164">
-        <v>2.3</v>
-      </c>
-      <c r="AG164">
-        <v>1.55</v>
-      </c>
       <c r="AH164" t="inlineStr">
         <is>
           <t>[]</t>
@@ -27111,10 +27111,10 @@
         </is>
       </c>
       <c r="AJ164">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AK164">
-        <v>1.8</v>
+        <v>2.14</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -27145,7 +27145,7 @@
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>2026-08-09 17:30:00</t>
+          <t>2026-08-09 17:15:00</t>
         </is>
       </c>
     </row>
@@ -27157,12 +27157,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G165">
@@ -27204,64 +27204,64 @@
         </is>
       </c>
       <c r="N165">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="O165">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="P165">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="Q165">
+        <v>2.5</v>
+      </c>
+      <c r="R165">
+        <v>1.85</v>
+      </c>
+      <c r="S165">
+        <v>1.57</v>
+      </c>
+      <c r="T165">
+        <v>2.21</v>
+      </c>
+      <c r="U165">
+        <v>3.9</v>
+      </c>
+      <c r="V165">
+        <v>1.22</v>
+      </c>
+      <c r="W165">
+        <v>1.03</v>
+      </c>
+      <c r="X165">
+        <v>1.08</v>
+      </c>
+      <c r="Y165">
+        <v>1.6</v>
+      </c>
+      <c r="Z165">
+        <v>2.15</v>
+      </c>
+      <c r="AA165">
+        <v>3.1</v>
+      </c>
+      <c r="AB165">
+        <v>1.34</v>
+      </c>
+      <c r="AC165">
+        <v>6.05</v>
+      </c>
+      <c r="AD165">
+        <v>1.11</v>
+      </c>
+      <c r="AE165">
+        <v>1.03</v>
+      </c>
+      <c r="AF165">
         <v>2.3</v>
       </c>
-      <c r="R165">
-        <v>2.32</v>
-      </c>
-      <c r="S165">
-        <v>1.3</v>
-      </c>
-      <c r="T165">
-        <v>3.2</v>
-      </c>
-      <c r="U165">
-        <v>2.4</v>
-      </c>
-      <c r="V165">
-        <v>1.5</v>
-      </c>
-      <c r="W165">
-        <v>1.11</v>
-      </c>
-      <c r="X165">
-        <v>1</v>
-      </c>
-      <c r="Y165">
-        <v>1.19</v>
-      </c>
-      <c r="Z165">
-        <v>3.8</v>
-      </c>
-      <c r="AA165">
-        <v>1.75</v>
-      </c>
-      <c r="AB165">
-        <v>2.09</v>
-      </c>
-      <c r="AC165">
-        <v>2.65</v>
-      </c>
-      <c r="AD165">
-        <v>1.37</v>
-      </c>
-      <c r="AE165">
-        <v>1.12</v>
-      </c>
-      <c r="AF165">
-        <v>1.61</v>
-      </c>
       <c r="AG165">
-        <v>2.16</v>
+        <v>1.55</v>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
@@ -27274,10 +27274,10 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AK165">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27308,7 +27308,7 @@
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>2026-08-09 18:00:00</t>
+          <t>2026-08-09 17:30:00</t>
         </is>
       </c>
     </row>
@@ -27325,7 +27325,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G166">
@@ -27367,64 +27367,64 @@
         </is>
       </c>
       <c r="N166">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O166">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P166">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q166">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="R166">
-        <v>1.85</v>
+        <v>2.32</v>
       </c>
       <c r="S166">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="T166">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="U166">
-        <v>3.98</v>
+        <v>2.4</v>
       </c>
       <c r="V166">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="W166">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X166">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="Y166">
-        <v>1.65</v>
+        <v>1.19</v>
       </c>
       <c r="Z166">
-        <v>2.12</v>
+        <v>3.8</v>
       </c>
       <c r="AA166">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB166">
-        <v>1.32</v>
+        <v>2.09</v>
       </c>
       <c r="AC166">
-        <v>5.2</v>
+        <v>2.65</v>
       </c>
       <c r="AD166">
-        <v>1.11</v>
+        <v>1.37</v>
       </c>
       <c r="AE166">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AF166">
-        <v>2.4</v>
+        <v>1.61</v>
       </c>
       <c r="AG166">
-        <v>1.49</v>
+        <v>2.16</v>
       </c>
       <c r="AH166" t="inlineStr">
         <is>
@@ -27437,10 +27437,10 @@
         </is>
       </c>
       <c r="AJ166">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AK166">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27488,7 +27488,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G167">
@@ -27530,64 +27530,64 @@
         </is>
       </c>
       <c r="N167">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O167">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P167">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q167">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="R167">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="S167">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="T167">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="U167">
-        <v>3.38</v>
+        <v>3.98</v>
       </c>
       <c r="V167">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W167">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X167">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="Y167">
-        <v>1.46</v>
+        <v>1.65</v>
       </c>
       <c r="Z167">
-        <v>2.52</v>
+        <v>2.12</v>
       </c>
       <c r="AA167">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AB167">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="AC167">
-        <v>4.72</v>
+        <v>5.2</v>
       </c>
       <c r="AD167">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AE167">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF167">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AG167">
-        <v>1.69</v>
+        <v>1.49</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27600,10 +27600,10 @@
         </is>
       </c>
       <c r="AJ167">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AK167">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -27651,7 +27651,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G168">
@@ -27693,80 +27693,80 @@
         </is>
       </c>
       <c r="N168">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="O168">
+        <v>2.95</v>
+      </c>
+      <c r="P168">
         <v>2.9</v>
       </c>
-      <c r="P168">
-        <v>3.37</v>
-      </c>
       <c r="Q168">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R168">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S168">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T168">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="U168">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="V168">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W168">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X168">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y168">
+        <v>1.46</v>
+      </c>
+      <c r="Z168">
+        <v>2.52</v>
+      </c>
+      <c r="AA168">
+        <v>2.5</v>
+      </c>
+      <c r="AB168">
+        <v>1.53</v>
+      </c>
+      <c r="AC168">
+        <v>4.72</v>
+      </c>
+      <c r="AD168">
+        <v>1.15</v>
+      </c>
+      <c r="AE168">
+        <v>1.05</v>
+      </c>
+      <c r="AF168">
+        <v>2</v>
+      </c>
+      <c r="AG168">
+        <v>1.69</v>
+      </c>
+      <c r="AH168" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI168" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ168">
+        <v>1.33</v>
+      </c>
+      <c r="AK168">
         <v>1.51</v>
-      </c>
-      <c r="Z168">
-        <v>2.37</v>
-      </c>
-      <c r="AA168">
-        <v>2.7</v>
-      </c>
-      <c r="AB168">
-        <v>1.44</v>
-      </c>
-      <c r="AC168">
-        <v>0</v>
-      </c>
-      <c r="AD168">
-        <v>0</v>
-      </c>
-      <c r="AE168">
-        <v>0</v>
-      </c>
-      <c r="AF168">
-        <v>0</v>
-      </c>
-      <c r="AG168">
-        <v>0</v>
-      </c>
-      <c r="AH168" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI168" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ168">
-        <v>0</v>
-      </c>
-      <c r="AK168">
-        <v>0</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -27809,12 +27809,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G169">
@@ -27856,13 +27856,13 @@
         </is>
       </c>
       <c r="N169">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O169">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P169">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q169">
         <v>0</v>
@@ -27889,16 +27889,16 @@
         <v>0</v>
       </c>
       <c r="Y169">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z169">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA169">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB169">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC169">
         <v>0</v>
@@ -27960,7 +27960,7 @@
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>2026-08-09 18:15:00</t>
+          <t>2026-08-09 18:00:00</t>
         </is>
       </c>
     </row>
@@ -27972,12 +27972,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G170">
@@ -28019,64 +28019,64 @@
         </is>
       </c>
       <c r="N170">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O170">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P170">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q170">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="R170">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S170">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T170">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U170">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="V170">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W170">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X170">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y170">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z170">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA170">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB170">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC170">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AD170">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE170">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF170">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG170">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AH170" t="inlineStr">
         <is>
@@ -28089,10 +28089,10 @@
         </is>
       </c>
       <c r="AJ170">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AK170">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -28123,7 +28123,7 @@
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>2026-08-09 18:30:00</t>
+          <t>2026-08-09 18:15:00</t>
         </is>
       </c>
     </row>
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,64 +28182,64 @@
         </is>
       </c>
       <c r="N171">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="O171">
         <v>3.3</v>
       </c>
       <c r="P171">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q171">
+        <v>2.62</v>
+      </c>
+      <c r="R171">
+        <v>2.1</v>
+      </c>
+      <c r="S171">
+        <v>1.44</v>
+      </c>
+      <c r="T171">
         <v>2.7</v>
       </c>
-      <c r="R171">
-        <v>1.96</v>
-      </c>
-      <c r="S171">
-        <v>1.4</v>
-      </c>
-      <c r="T171">
-        <v>2.62</v>
-      </c>
       <c r="U171">
-        <v>2.91</v>
+        <v>3.05</v>
       </c>
       <c r="V171">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W171">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X171">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y171">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="Z171">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="AA171">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AB171">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AC171">
-        <v>4.2</v>
+        <v>3.54</v>
       </c>
       <c r="AD171">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE171">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF171">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG171">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH171" t="inlineStr">
         <is>
@@ -28252,10 +28252,10 @@
         </is>
       </c>
       <c r="AJ171">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AK171">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AL171">
         <v>0</v>
@@ -28303,7 +28303,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,64 +28345,64 @@
         </is>
       </c>
       <c r="N172">
-        <v>2.55</v>
+        <v>2.17</v>
       </c>
       <c r="O172">
+        <v>3.3</v>
+      </c>
+      <c r="P172">
+        <v>3.6</v>
+      </c>
+      <c r="Q172">
         <v>2.7</v>
       </c>
-      <c r="P172">
-        <v>2.8</v>
-      </c>
-      <c r="Q172">
-        <v>3.2</v>
-      </c>
       <c r="R172">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="S172">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="T172">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="U172">
-        <v>3.7</v>
+        <v>2.91</v>
       </c>
       <c r="V172">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="W172">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X172">
         <v>1.06</v>
       </c>
       <c r="Y172">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="Z172">
-        <v>2.41</v>
+        <v>2.9</v>
       </c>
       <c r="AA172">
-        <v>2.52</v>
+        <v>2.19</v>
       </c>
       <c r="AB172">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="AC172">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="AD172">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="AE172">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF172">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="AG172">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28415,10 +28415,10 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AK172">
-        <v>1.35</v>
+        <v>1.65</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28629,7 +28629,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,64 +28671,64 @@
         </is>
       </c>
       <c r="N174">
-        <v>3.55</v>
+        <v>2.55</v>
       </c>
       <c r="O174">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="P174">
-        <v>1.83</v>
+        <v>2.8</v>
       </c>
       <c r="Q174">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="R174">
+        <v>1.91</v>
+      </c>
+      <c r="S174">
+        <v>1.5</v>
+      </c>
+      <c r="T174">
         <v>2.2</v>
       </c>
-      <c r="S174">
-        <v>1.34</v>
-      </c>
-      <c r="T174">
-        <v>2.95</v>
-      </c>
       <c r="U174">
-        <v>2.72</v>
+        <v>3.7</v>
       </c>
       <c r="V174">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="W174">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X174">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y174">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="Z174">
-        <v>3.4</v>
+        <v>2.41</v>
       </c>
       <c r="AA174">
-        <v>1.95</v>
+        <v>2.52</v>
       </c>
       <c r="AB174">
-        <v>1.78</v>
+        <v>1.41</v>
       </c>
       <c r="AC174">
-        <v>3.08</v>
+        <v>5.1</v>
       </c>
       <c r="AD174">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AE174">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="AF174">
-        <v>1.76</v>
+        <v>2.08</v>
       </c>
       <c r="AG174">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AH174" t="inlineStr">
         <is>
@@ -28741,10 +28741,10 @@
         </is>
       </c>
       <c r="AJ174">
-        <v>1.91</v>
+        <v>1.33</v>
       </c>
       <c r="AK174">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -28787,12 +28787,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>1.25</v>
+        <v>3.55</v>
       </c>
       <c r="O175">
-        <v>6.25</v>
+        <v>3.4</v>
       </c>
       <c r="P175">
-        <v>11</v>
+        <v>1.83</v>
       </c>
       <c r="Q175">
-        <v>1.61</v>
+        <v>4.4</v>
       </c>
       <c r="R175">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="S175">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="T175">
-        <v>3.6</v>
+        <v>2.95</v>
       </c>
       <c r="U175">
-        <v>2.37</v>
+        <v>2.72</v>
       </c>
       <c r="V175">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="W175">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X175">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y175">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="Z175">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="AA175">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="AB175">
-        <v>2.3</v>
+        <v>1.78</v>
       </c>
       <c r="AC175">
-        <v>2.5</v>
+        <v>3.08</v>
       </c>
       <c r="AD175">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AE175">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AF175">
-        <v>2.15</v>
+        <v>1.76</v>
       </c>
       <c r="AG175">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.04</v>
+        <v>1.91</v>
       </c>
       <c r="AK175">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -28938,7 +28938,7 @@
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>2026-08-09 19:30:00</t>
+          <t>2026-08-09 18:30:00</t>
         </is>
       </c>
     </row>
@@ -28950,12 +28950,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>4.52</v>
+        <v>1.25</v>
       </c>
       <c r="O176">
-        <v>3.92</v>
+        <v>6.2</v>
       </c>
       <c r="P176">
-        <v>1.6</v>
+        <v>10</v>
       </c>
       <c r="Q176">
-        <v>4.2</v>
+        <v>1.61</v>
       </c>
       <c r="R176">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="S176">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T176">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="U176">
-        <v>2.47</v>
+        <v>2.37</v>
       </c>
       <c r="V176">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="W176">
         <v>1.11</v>
       </c>
       <c r="X176">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y176">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z176">
-        <v>4.05</v>
+        <v>4.33</v>
       </c>
       <c r="AA176">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AB176">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AC176">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="AD176">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AE176">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AF176">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="AG176">
-        <v>2.11</v>
+        <v>1.62</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.19</v>
+        <v>1.04</v>
       </c>
       <c r="AK176">
-        <v>1.17</v>
+        <v>3.6</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29101,7 +29101,7 @@
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>2026-08-09 20:00:00</t>
+          <t>2026-08-09 19:30:00</t>
         </is>
       </c>
     </row>
@@ -29113,12 +29113,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,64 +29160,64 @@
         </is>
       </c>
       <c r="N177">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="O177">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P177">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q177">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R177">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S177">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T177">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U177">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V177">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W177">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X177">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y177">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z177">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA177">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB177">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC177">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD177">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE177">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF177">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG177">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK177">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29264,7 +29264,7 @@
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>2026-08-09 20:30:00</t>
+          <t>2026-08-09 20:00:00</t>
         </is>
       </c>
     </row>
@@ -29276,12 +29276,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,64 +29323,64 @@
         </is>
       </c>
       <c r="N178">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O178">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P178">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Q178">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R178">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S178">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T178">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U178">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="V178">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W178">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X178">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y178">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z178">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA178">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB178">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC178">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD178">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE178">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF178">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG178">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
@@ -29393,10 +29393,10 @@
         </is>
       </c>
       <c r="AJ178">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK178">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29427,7 +29427,7 @@
       </c>
       <c r="AU178" t="inlineStr">
         <is>
-          <t>2026-08-09 21:00:00</t>
+          <t>2026-08-09 20:30:00</t>
         </is>
       </c>
     </row>
@@ -29444,7 +29444,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,80 +29486,80 @@
         </is>
       </c>
       <c r="N179">
-        <v>2.95</v>
+        <v>1.84</v>
       </c>
       <c r="O179">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="P179">
-        <v>2.3</v>
+        <v>3.48</v>
       </c>
       <c r="Q179">
-        <v>3.65</v>
+        <v>2.38</v>
       </c>
       <c r="R179">
+        <v>2.15</v>
+      </c>
+      <c r="S179">
+        <v>1.36</v>
+      </c>
+      <c r="T179">
+        <v>2.9</v>
+      </c>
+      <c r="U179">
+        <v>2.85</v>
+      </c>
+      <c r="V179">
+        <v>1.37</v>
+      </c>
+      <c r="W179">
+        <v>1.06</v>
+      </c>
+      <c r="X179">
+        <v>1.05</v>
+      </c>
+      <c r="Y179">
+        <v>1.3</v>
+      </c>
+      <c r="Z179">
+        <v>3.3</v>
+      </c>
+      <c r="AA179">
+        <v>1.91</v>
+      </c>
+      <c r="AB179">
+        <v>1.8</v>
+      </c>
+      <c r="AC179">
+        <v>3.4</v>
+      </c>
+      <c r="AD179">
+        <v>1.26</v>
+      </c>
+      <c r="AE179">
+        <v>1.11</v>
+      </c>
+      <c r="AF179">
+        <v>1.79</v>
+      </c>
+      <c r="AG179">
+        <v>1.95</v>
+      </c>
+      <c r="AH179" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI179" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ179">
+        <v>1.2</v>
+      </c>
+      <c r="AK179">
         <v>1.88</v>
-      </c>
-      <c r="S179">
-        <v>1.51</v>
-      </c>
-      <c r="T179">
-        <v>2.31</v>
-      </c>
-      <c r="U179">
-        <v>3.46</v>
-      </c>
-      <c r="V179">
-        <v>1.28</v>
-      </c>
-      <c r="W179">
-        <v>1.04</v>
-      </c>
-      <c r="X179">
-        <v>1.07</v>
-      </c>
-      <c r="Y179">
-        <v>1.5</v>
-      </c>
-      <c r="Z179">
-        <v>2.46</v>
-      </c>
-      <c r="AA179">
-        <v>2.49</v>
-      </c>
-      <c r="AB179">
-        <v>1.49</v>
-      </c>
-      <c r="AC179">
-        <v>4.1</v>
-      </c>
-      <c r="AD179">
-        <v>1.13</v>
-      </c>
-      <c r="AE179">
-        <v>1.04</v>
-      </c>
-      <c r="AF179">
-        <v>2</v>
-      </c>
-      <c r="AG179">
-        <v>1.67</v>
-      </c>
-      <c r="AH179" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI179" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ179">
-        <v>1.53</v>
-      </c>
-      <c r="AK179">
-        <v>1.33</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29602,156 +29602,319 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Guayaquil City FC</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="G180">
+        <v>0</v>
+      </c>
+      <c r="H180">
+        <v>0</v>
+      </c>
+      <c r="I180">
+        <v>0</v>
+      </c>
+      <c r="J180">
+        <v>0</v>
+      </c>
+      <c r="K180">
+        <v>0</v>
+      </c>
+      <c r="L180">
+        <v>0</v>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N180">
+        <v>2.95</v>
+      </c>
+      <c r="O180">
+        <v>3</v>
+      </c>
+      <c r="P180">
+        <v>2.3</v>
+      </c>
+      <c r="Q180">
+        <v>3.65</v>
+      </c>
+      <c r="R180">
+        <v>1.88</v>
+      </c>
+      <c r="S180">
+        <v>1.51</v>
+      </c>
+      <c r="T180">
+        <v>2.31</v>
+      </c>
+      <c r="U180">
+        <v>3.46</v>
+      </c>
+      <c r="V180">
+        <v>1.28</v>
+      </c>
+      <c r="W180">
+        <v>1.04</v>
+      </c>
+      <c r="X180">
+        <v>1.07</v>
+      </c>
+      <c r="Y180">
+        <v>1.5</v>
+      </c>
+      <c r="Z180">
+        <v>2.46</v>
+      </c>
+      <c r="AA180">
+        <v>2.49</v>
+      </c>
+      <c r="AB180">
+        <v>1.49</v>
+      </c>
+      <c r="AC180">
+        <v>4.1</v>
+      </c>
+      <c r="AD180">
+        <v>1.13</v>
+      </c>
+      <c r="AE180">
+        <v>1.04</v>
+      </c>
+      <c r="AF180">
+        <v>2</v>
+      </c>
+      <c r="AG180">
+        <v>1.67</v>
+      </c>
+      <c r="AH180" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI180" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ180">
+        <v>1.53</v>
+      </c>
+      <c r="AK180">
+        <v>1.33</v>
+      </c>
+      <c r="AL180">
+        <v>0</v>
+      </c>
+      <c r="AM180">
+        <v>-1</v>
+      </c>
+      <c r="AN180">
+        <v>-1</v>
+      </c>
+      <c r="AO180">
+        <v>-1</v>
+      </c>
+      <c r="AP180">
+        <v>-1</v>
+      </c>
+      <c r="AQ180">
+        <v>0</v>
+      </c>
+      <c r="AR180">
+        <v>0</v>
+      </c>
+      <c r="AS180">
+        <v>0</v>
+      </c>
+      <c r="AT180">
+        <v>0</v>
+      </c>
+      <c r="AU180" t="inlineStr">
+        <is>
+          <t>2026-08-09 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr">
+      <c r="C181" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr">
+      <c r="D181" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr">
+      <c r="E181" t="inlineStr">
         <is>
           <t>Seattle Reign</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr">
+      <c r="F181" t="inlineStr">
         <is>
           <t>Angel City</t>
         </is>
       </c>
-      <c r="G180">
-        <v>0</v>
-      </c>
-      <c r="H180">
-        <v>0</v>
-      </c>
-      <c r="I180">
-        <v>0</v>
-      </c>
-      <c r="J180">
-        <v>0</v>
-      </c>
-      <c r="K180">
-        <v>0</v>
-      </c>
-      <c r="L180">
-        <v>0</v>
-      </c>
-      <c r="M180" t="inlineStr">
+      <c r="G181">
+        <v>0</v>
+      </c>
+      <c r="H181">
+        <v>0</v>
+      </c>
+      <c r="I181">
+        <v>0</v>
+      </c>
+      <c r="J181">
+        <v>0</v>
+      </c>
+      <c r="K181">
+        <v>0</v>
+      </c>
+      <c r="L181">
+        <v>0</v>
+      </c>
+      <c r="M181" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N180">
+      <c r="N181">
         <v>2.42</v>
       </c>
-      <c r="O180">
+      <c r="O181">
         <v>3.2</v>
       </c>
-      <c r="P180">
+      <c r="P181">
         <v>2.58</v>
       </c>
-      <c r="Q180">
+      <c r="Q181">
         <v>3</v>
       </c>
-      <c r="R180">
+      <c r="R181">
         <v>2.3</v>
       </c>
-      <c r="S180">
+      <c r="S181">
         <v>1.3</v>
       </c>
-      <c r="T180">
+      <c r="T181">
         <v>3.04</v>
       </c>
-      <c r="U180">
+      <c r="U181">
         <v>2.53</v>
       </c>
-      <c r="V180">
+      <c r="V181">
         <v>1.42</v>
       </c>
-      <c r="W180">
+      <c r="W181">
         <v>1.07</v>
       </c>
-      <c r="X180">
+      <c r="X181">
         <v>1.04</v>
       </c>
-      <c r="Y180">
+      <c r="Y181">
         <v>1.19</v>
       </c>
-      <c r="Z180">
+      <c r="Z181">
         <v>3.05</v>
       </c>
-      <c r="AA180">
+      <c r="AA181">
         <v>1.93</v>
       </c>
-      <c r="AB180">
+      <c r="AB181">
         <v>1.72</v>
       </c>
-      <c r="AC180">
+      <c r="AC181">
         <v>3.3</v>
       </c>
-      <c r="AD180">
+      <c r="AD181">
         <v>1.36</v>
       </c>
-      <c r="AE180">
+      <c r="AE181">
         <v>1.08</v>
       </c>
-      <c r="AF180">
+      <c r="AF181">
         <v>1.6</v>
       </c>
-      <c r="AG180">
+      <c r="AG181">
         <v>2.15</v>
       </c>
-      <c r="AH180" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI180" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ180">
+      <c r="AH181" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI181" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ181">
         <v>1.44</v>
       </c>
-      <c r="AK180">
+      <c r="AK181">
         <v>1.44</v>
       </c>
-      <c r="AL180">
-        <v>0</v>
-      </c>
-      <c r="AM180">
-        <v>-1</v>
-      </c>
-      <c r="AN180">
-        <v>-1</v>
-      </c>
-      <c r="AO180">
-        <v>-1</v>
-      </c>
-      <c r="AP180">
-        <v>-1</v>
-      </c>
-      <c r="AQ180">
-        <v>0</v>
-      </c>
-      <c r="AR180">
-        <v>0</v>
-      </c>
-      <c r="AS180">
-        <v>0</v>
-      </c>
-      <c r="AT180">
-        <v>0</v>
-      </c>
-      <c r="AU180" t="inlineStr">
+      <c r="AL181">
+        <v>0</v>
+      </c>
+      <c r="AM181">
+        <v>-1</v>
+      </c>
+      <c r="AN181">
+        <v>-1</v>
+      </c>
+      <c r="AO181">
+        <v>-1</v>
+      </c>
+      <c r="AP181">
+        <v>-1</v>
+      </c>
+      <c r="AQ181">
+        <v>0</v>
+      </c>
+      <c r="AR181">
+        <v>0</v>
+      </c>
+      <c r="AS181">
+        <v>0</v>
+      </c>
+      <c r="AT181">
+        <v>0</v>
+      </c>
+      <c r="AU181" t="inlineStr">
         <is>
           <t>2026-08-09 22:00:00</t>
         </is>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>3.93</v>
+        <v>1.44</v>
       </c>
       <c r="O122">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="P122">
-        <v>1.83</v>
+        <v>6.05</v>
       </c>
       <c r="Q122">
-        <v>4.2</v>
+        <v>1.91</v>
       </c>
       <c r="R122">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="S122">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="T122">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="U122">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="V122">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W122">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X122">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y122">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="Z122">
-        <v>3.08</v>
+        <v>3.68</v>
       </c>
       <c r="AA122">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AB122">
-        <v>1.7</v>
+        <v>1.96</v>
       </c>
       <c r="AC122">
-        <v>3.34</v>
+        <v>2.78</v>
       </c>
       <c r="AD122">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AE122">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF122">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AG122">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.76</v>
+        <v>1.16</v>
       </c>
       <c r="AK122">
-        <v>1.18</v>
+        <v>2.45</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,65 +20358,65 @@
         </is>
       </c>
       <c r="N123">
-        <v>1.44</v>
+        <v>3.93</v>
       </c>
       <c r="O123">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="P123">
-        <v>6.05</v>
+        <v>1.83</v>
       </c>
       <c r="Q123">
-        <v>1.91</v>
+        <v>4.2</v>
       </c>
       <c r="R123">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="S123">
+        <v>1.39</v>
+      </c>
+      <c r="T123">
+        <v>2.75</v>
+      </c>
+      <c r="U123">
+        <v>3</v>
+      </c>
+      <c r="V123">
+        <v>1.38</v>
+      </c>
+      <c r="W123">
+        <v>1.03</v>
+      </c>
+      <c r="X123">
+        <v>1.01</v>
+      </c>
+      <c r="Y123">
         <v>1.33</v>
       </c>
-      <c r="T123">
-        <v>2.91</v>
-      </c>
-      <c r="U123">
-        <v>2.6</v>
-      </c>
-      <c r="V123">
-        <v>1.44</v>
-      </c>
-      <c r="W123">
-        <v>1.06</v>
-      </c>
-      <c r="X123">
+      <c r="Z123">
+        <v>3.08</v>
+      </c>
+      <c r="AA123">
+        <v>2.1</v>
+      </c>
+      <c r="AB123">
+        <v>1.7</v>
+      </c>
+      <c r="AC123">
+        <v>3.34</v>
+      </c>
+      <c r="AD123">
+        <v>1.25</v>
+      </c>
+      <c r="AE123">
         <v>1.05</v>
       </c>
-      <c r="Y123">
-        <v>1.2</v>
-      </c>
-      <c r="Z123">
-        <v>3.68</v>
-      </c>
-      <c r="AA123">
-        <v>1.75</v>
-      </c>
-      <c r="AB123">
-        <v>1.96</v>
-      </c>
-      <c r="AC123">
-        <v>2.78</v>
-      </c>
-      <c r="AD123">
-        <v>1.36</v>
-      </c>
-      <c r="AE123">
-        <v>1.1</v>
-      </c>
       <c r="AF123">
+        <v>1.81</v>
+      </c>
+      <c r="AG123">
         <v>1.85</v>
       </c>
-      <c r="AG123">
-        <v>1.77</v>
-      </c>
       <c r="AH123" t="inlineStr">
         <is>
           <t>[]</t>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.16</v>
+        <v>1.76</v>
       </c>
       <c r="AK123">
-        <v>2.45</v>
+        <v>1.18</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="O156">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P156">
-        <v>3.16</v>
+        <v>3.8</v>
       </c>
       <c r="Q156">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="R156">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="S156">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="T156">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="U156">
-        <v>2.85</v>
+        <v>3.6</v>
       </c>
       <c r="V156">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="W156">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X156">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y156">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="Z156">
-        <v>3.3</v>
+        <v>2.59</v>
       </c>
       <c r="AA156">
-        <v>2</v>
+        <v>2.51</v>
       </c>
       <c r="AB156">
-        <v>1.76</v>
+        <v>1.49</v>
       </c>
       <c r="AC156">
-        <v>3.34</v>
+        <v>4.84</v>
       </c>
       <c r="AD156">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AE156">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF156">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AG156">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>1.3</v>
       </c>
       <c r="AK156">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
+        <v>2.28</v>
+      </c>
+      <c r="O157">
+        <v>3.15</v>
+      </c>
+      <c r="P157">
+        <v>3.16</v>
+      </c>
+      <c r="Q157">
+        <v>3</v>
+      </c>
+      <c r="R157">
         <v>2.05</v>
       </c>
-      <c r="O157">
-        <v>3.1</v>
-      </c>
-      <c r="P157">
-        <v>3.8</v>
-      </c>
-      <c r="Q157">
-        <v>2.5</v>
-      </c>
-      <c r="R157">
-        <v>1.95</v>
-      </c>
       <c r="S157">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="T157">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="U157">
-        <v>3.6</v>
+        <v>2.85</v>
       </c>
       <c r="V157">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="W157">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X157">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y157">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="Z157">
-        <v>2.59</v>
+        <v>3.3</v>
       </c>
       <c r="AA157">
-        <v>2.51</v>
+        <v>2</v>
       </c>
       <c r="AB157">
-        <v>1.49</v>
+        <v>1.76</v>
       </c>
       <c r="AC157">
-        <v>4.84</v>
+        <v>3.34</v>
       </c>
       <c r="AD157">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AE157">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF157">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AG157">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25973,7 +25973,7 @@
         <v>1.3</v>
       </c>
       <c r="AK157">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="AL157">
         <v>0</v>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -1290,7 +1290,7 @@
         <v>2.9</v>
       </c>
       <c r="O6">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P6">
         <v>2.38</v>
@@ -1299,19 +1299,19 @@
         <v>3.5</v>
       </c>
       <c r="R6">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S6">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="T6">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="U6">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="V6">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W6">
         <v>1.03</v>
@@ -1341,10 +1341,10 @@
         <v>1.03</v>
       </c>
       <c r="AF6">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG6">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1942,10 +1942,10 @@
         <v>2.8</v>
       </c>
       <c r="O10">
-        <v>3.24</v>
+        <v>3.15</v>
       </c>
       <c r="P10">
-        <v>2.42</v>
+        <v>2.37</v>
       </c>
       <c r="Q10">
         <v>3.64</v>
@@ -1954,7 +1954,7 @@
         <v>2</v>
       </c>
       <c r="S10">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T10">
         <v>2.62</v>
@@ -1972,7 +1972,7 @@
         <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z10">
         <v>2.82</v>
@@ -1984,7 +1984,7 @@
         <v>1.72</v>
       </c>
       <c r="AC10">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AD10">
         <v>1.21</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q14">
         <v>1.9</v>
@@ -2627,13 +2627,13 @@
         <v>1.2</v>
       </c>
       <c r="Z14">
-        <v>4.9</v>
+        <v>4.92</v>
       </c>
       <c r="AA14">
         <v>1.67</v>
       </c>
       <c r="AB14">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="AC14">
         <v>2.62</v>
@@ -2645,10 +2645,10 @@
         <v>1.18</v>
       </c>
       <c r="AF14">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG14">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.72</v>
+        <v>3.25</v>
       </c>
       <c r="O23">
-        <v>3.23</v>
+        <v>3.55</v>
       </c>
       <c r="P23">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q23">
         <v>3.78</v>
@@ -4221,16 +4221,16 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="O24">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="P24">
-        <v>3.7</v>
+        <v>4.05</v>
       </c>
       <c r="Q24">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="R24">
         <v>2.38</v>
@@ -4242,7 +4242,7 @@
         <v>3.6</v>
       </c>
       <c r="U24">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="V24">
         <v>1.6</v>
@@ -4257,7 +4257,7 @@
         <v>1.15</v>
       </c>
       <c r="Z24">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="AA24">
         <v>1.53</v>
@@ -4272,7 +4272,7 @@
         <v>1.53</v>
       </c>
       <c r="AE24">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AF24">
         <v>1.53</v>
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="O46">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P46">
-        <v>5.14</v>
+        <v>5</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA46">
         <v>1.95</v>
       </c>
       <c r="AB46">
+        <v>1.83</v>
+      </c>
+      <c r="AC46">
+        <v>3.3</v>
+      </c>
+      <c r="AD46">
+        <v>1.3</v>
+      </c>
+      <c r="AE46">
+        <v>1.1</v>
+      </c>
+      <c r="AF46">
         <v>1.85</v>
       </c>
-      <c r="AC46">
-        <v>0</v>
-      </c>
-      <c r="AD46">
-        <v>0</v>
-      </c>
-      <c r="AE46">
-        <v>0</v>
-      </c>
-      <c r="AF46">
-        <v>0</v>
-      </c>
       <c r="AG46">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,31 +13675,31 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.41</v>
+        <v>2.24</v>
       </c>
       <c r="O82">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="P82">
-        <v>4.65</v>
+        <v>2.41</v>
       </c>
       <c r="Q82">
-        <v>1.85</v>
+        <v>2.88</v>
       </c>
       <c r="R82">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="S82">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="T82">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="U82">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="V82">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="W82">
         <v>1.25</v>
@@ -13711,28 +13711,28 @@
         <v>1.05</v>
       </c>
       <c r="Z82">
-        <v>7.5</v>
+        <v>6.39</v>
       </c>
       <c r="AA82">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AB82">
-        <v>3.6</v>
+        <v>3.39</v>
       </c>
       <c r="AC82">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AD82">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AE82">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AF82">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AG82">
-        <v>2.8</v>
+        <v>3.48</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AK82">
-        <v>2.51</v>
+        <v>1.5</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,31 +13838,31 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.24</v>
+        <v>1.41</v>
       </c>
       <c r="O83">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="P83">
-        <v>2.41</v>
+        <v>4.65</v>
       </c>
       <c r="Q83">
-        <v>2.88</v>
+        <v>1.85</v>
       </c>
       <c r="R83">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="S83">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T83">
-        <v>4.45</v>
+        <v>4.6</v>
       </c>
       <c r="U83">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="V83">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="W83">
         <v>1.25</v>
@@ -13874,28 +13874,28 @@
         <v>1.05</v>
       </c>
       <c r="Z83">
-        <v>6.39</v>
+        <v>7.5</v>
       </c>
       <c r="AA83">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AB83">
-        <v>3.39</v>
+        <v>3.6</v>
       </c>
       <c r="AC83">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AD83">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AE83">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AF83">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AG83">
-        <v>3.48</v>
+        <v>2.8</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AK83">
-        <v>1.5</v>
+        <v>2.51</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="O91">
         <v>2.98</v>
       </c>
       <c r="P91">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q91">
         <v>3.3</v>
@@ -15163,13 +15163,13 @@
         <v>2.39</v>
       </c>
       <c r="U91">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="V91">
         <v>1.29</v>
       </c>
       <c r="W91">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X91">
         <v>1.05</v>
@@ -15178,10 +15178,10 @@
         <v>1.39</v>
       </c>
       <c r="Z91">
-        <v>2.74</v>
+        <v>2.91</v>
       </c>
       <c r="AA91">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AB91">
         <v>1.6</v>
@@ -15190,7 +15190,7 @@
         <v>4.2</v>
       </c>
       <c r="AD91">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE91">
         <v>1.03</v>
@@ -15199,7 +15199,7 @@
         <v>1.95</v>
       </c>
       <c r="AG91">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         <v>1.28</v>
       </c>
       <c r="AK91">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -23458,7 +23458,7 @@
         <v>1.64</v>
       </c>
       <c r="O142">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P142">
         <v>5.01</v>
@@ -23491,13 +23491,13 @@
         <v>1.33</v>
       </c>
       <c r="Z142">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AA142">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AB142">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AC142">
         <v>3.76</v>
@@ -23509,7 +23509,7 @@
         <v>1.02</v>
       </c>
       <c r="AF142">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG142">
         <v>1.7</v>
@@ -23944,13 +23944,13 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="O145">
-        <v>3.91</v>
+        <v>4</v>
       </c>
       <c r="P145">
-        <v>6.63</v>
+        <v>5.5</v>
       </c>
       <c r="Q145">
         <v>2.12</v>
@@ -24001,7 +24001,7 @@
         <v>1.93</v>
       </c>
       <c r="AG145">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24107,16 +24107,16 @@
         </is>
       </c>
       <c r="N146">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="O146">
-        <v>3.67</v>
+        <v>3.42</v>
       </c>
       <c r="P146">
-        <v>4.48</v>
+        <v>3.65</v>
       </c>
       <c r="Q146">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="R146">
         <v>2.29</v>
@@ -24128,7 +24128,7 @@
         <v>3.08</v>
       </c>
       <c r="U146">
-        <v>2.79</v>
+        <v>2.65</v>
       </c>
       <c r="V146">
         <v>1.42</v>
@@ -24155,7 +24155,7 @@
         <v>2.94</v>
       </c>
       <c r="AD146">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE146">
         <v>1.13</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
+        <v>2.28</v>
+      </c>
+      <c r="O156">
+        <v>3.15</v>
+      </c>
+      <c r="P156">
+        <v>3.16</v>
+      </c>
+      <c r="Q156">
+        <v>3</v>
+      </c>
+      <c r="R156">
         <v>2.05</v>
       </c>
-      <c r="O156">
-        <v>3.1</v>
-      </c>
-      <c r="P156">
-        <v>3.8</v>
-      </c>
-      <c r="Q156">
-        <v>2.5</v>
-      </c>
-      <c r="R156">
-        <v>1.95</v>
-      </c>
       <c r="S156">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="T156">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="U156">
-        <v>3.6</v>
+        <v>2.85</v>
       </c>
       <c r="V156">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="W156">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X156">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y156">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="Z156">
-        <v>2.59</v>
+        <v>3.3</v>
       </c>
       <c r="AA156">
-        <v>2.51</v>
+        <v>2</v>
       </c>
       <c r="AB156">
-        <v>1.49</v>
+        <v>1.76</v>
       </c>
       <c r="AC156">
-        <v>4.84</v>
+        <v>3.34</v>
       </c>
       <c r="AD156">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AE156">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF156">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AG156">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>1.3</v>
       </c>
       <c r="AK156">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="O157">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P157">
-        <v>3.16</v>
+        <v>3.8</v>
       </c>
       <c r="Q157">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="R157">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="S157">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="T157">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="U157">
-        <v>2.85</v>
+        <v>3.6</v>
       </c>
       <c r="V157">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="W157">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X157">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y157">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="Z157">
-        <v>3.3</v>
+        <v>2.59</v>
       </c>
       <c r="AA157">
-        <v>2</v>
+        <v>2.51</v>
       </c>
       <c r="AB157">
-        <v>1.76</v>
+        <v>1.49</v>
       </c>
       <c r="AC157">
-        <v>3.34</v>
+        <v>4.84</v>
       </c>
       <c r="AD157">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AE157">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF157">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AG157">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25973,7 +25973,7 @@
         <v>1.3</v>
       </c>
       <c r="AK157">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -28182,13 +28182,13 @@
         </is>
       </c>
       <c r="N171">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="O171">
         <v>3.3</v>
       </c>
       <c r="P171">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q171">
         <v>2.62</v>
@@ -28221,7 +28221,7 @@
         <v>3.1</v>
       </c>
       <c r="AA171">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB171">
         <v>1.72</v>
@@ -28236,7 +28236,7 @@
         <v>1.04</v>
       </c>
       <c r="AF171">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG171">
         <v>1.87</v>
@@ -28345,13 +28345,13 @@
         </is>
       </c>
       <c r="N172">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="O172">
         <v>3.3</v>
       </c>
       <c r="P172">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="Q172">
         <v>2.7</v>
@@ -28366,10 +28366,10 @@
         <v>2.62</v>
       </c>
       <c r="U172">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="V172">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W172">
         <v>1.05</v>
@@ -28381,13 +28381,13 @@
         <v>1.38</v>
       </c>
       <c r="Z172">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="AA172">
         <v>2.19</v>
       </c>
       <c r="AB172">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AC172">
         <v>4.2</v>
@@ -29027,13 +29027,13 @@
         <v>1.11</v>
       </c>
       <c r="X176">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y176">
         <v>1.15</v>
       </c>
       <c r="Z176">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AA176">
         <v>1.63</v>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -641,19 +641,19 @@
         <v>3.1</v>
       </c>
       <c r="P2">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="Q2">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="R2">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="S2">
         <v>1.47</v>
       </c>
       <c r="T2">
-        <v>2.7</v>
+        <v>2.47</v>
       </c>
       <c r="U2">
         <v>3.16</v>
@@ -668,22 +668,22 @@
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="Z2">
-        <v>2.83</v>
+        <v>2.97</v>
       </c>
       <c r="AA2">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AB2">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC2">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="AD2">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AE2">
         <v>1.02</v>
@@ -708,7 +708,7 @@
         <v>1.34</v>
       </c>
       <c r="AK2">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -801,10 +801,10 @@
         <v>3.7</v>
       </c>
       <c r="O3">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="P3">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q3">
         <v>4.75</v>
@@ -831,19 +831,19 @@
         <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z3">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="AA3">
         <v>1.95</v>
       </c>
       <c r="AB3">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AC3">
-        <v>3.14</v>
+        <v>2.85</v>
       </c>
       <c r="AD3">
         <v>1.27</v>
@@ -855,7 +855,7 @@
         <v>1.8</v>
       </c>
       <c r="AG3">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="O4">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
-        <v>2.65</v>
+        <v>2.94</v>
       </c>
       <c r="Q4">
         <v>2.63</v>
@@ -982,7 +982,7 @@
         <v>3.24</v>
       </c>
       <c r="U4">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="V4">
         <v>1.44</v>
@@ -1006,16 +1006,16 @@
         <v>2.05</v>
       </c>
       <c r="AC4">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AD4">
         <v>1.34</v>
       </c>
       <c r="AE4">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF4">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG4">
         <v>2.15</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="O5">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="P5">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB5">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AC5">
         <v>0</v>
@@ -1290,7 +1290,7 @@
         <v>2.9</v>
       </c>
       <c r="O6">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P6">
         <v>2.38</v>
@@ -1308,19 +1308,19 @@
         <v>2.47</v>
       </c>
       <c r="U6">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="V6">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W6">
         <v>1.03</v>
       </c>
       <c r="X6">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y6">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z6">
         <v>2.8</v>
@@ -1341,10 +1341,10 @@
         <v>1.03</v>
       </c>
       <c r="AF6">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG6">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1489,10 +1489,10 @@
         <v>0</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC7">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="O8">
         <v>3</v>
       </c>
       <c r="P8">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="Q8">
         <v>3.75</v>
@@ -1649,7 +1649,7 @@
         <v>1.37</v>
       </c>
       <c r="Z8">
-        <v>2.74</v>
+        <v>2.85</v>
       </c>
       <c r="AA8">
         <v>2.23</v>
@@ -1686,7 +1686,7 @@
         <v>1.36</v>
       </c>
       <c r="AK8">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1942,10 +1942,10 @@
         <v>2.8</v>
       </c>
       <c r="O10">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="P10">
-        <v>2.37</v>
+        <v>2.42</v>
       </c>
       <c r="Q10">
         <v>3.64</v>
@@ -1960,10 +1960,10 @@
         <v>2.62</v>
       </c>
       <c r="U10">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="V10">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W10">
         <v>1.05</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.16</v>
+        <v>2.35</v>
       </c>
       <c r="O11">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="P11">
+        <v>2.9</v>
+      </c>
+      <c r="Q11">
+        <v>2.8</v>
+      </c>
+      <c r="R11">
+        <v>2.1</v>
+      </c>
+      <c r="S11">
+        <v>1.41</v>
+      </c>
+      <c r="T11">
+        <v>2.73</v>
+      </c>
+      <c r="U11">
+        <v>2.88</v>
+      </c>
+      <c r="V11">
+        <v>1.33</v>
+      </c>
+      <c r="W11">
+        <v>1.06</v>
+      </c>
+      <c r="X11">
+        <v>1.06</v>
+      </c>
+      <c r="Y11">
+        <v>1.33</v>
+      </c>
+      <c r="Z11">
         <v>3</v>
       </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>0</v>
-      </c>
-      <c r="V11">
-        <v>0</v>
-      </c>
-      <c r="W11">
-        <v>0</v>
-      </c>
-      <c r="X11">
-        <v>0</v>
-      </c>
-      <c r="Y11">
-        <v>0</v>
-      </c>
-      <c r="Z11">
-        <v>0</v>
-      </c>
       <c r="AA11">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2268,7 +2268,7 @@
         <v>4.4</v>
       </c>
       <c r="O12">
-        <v>3.97</v>
+        <v>4.05</v>
       </c>
       <c r="P12">
         <v>1.6</v>
@@ -2280,10 +2280,10 @@
         <v>2.45</v>
       </c>
       <c r="S12">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T12">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="U12">
         <v>2.28</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="O13">
         <v>3</v>
       </c>
       <c r="P13">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="Q13">
         <v>3.3</v>
@@ -2443,16 +2443,16 @@
         <v>2.04</v>
       </c>
       <c r="S13">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T13">
         <v>3.4</v>
       </c>
       <c r="U13">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="V13">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W13">
         <v>1.11</v>
@@ -2473,16 +2473,16 @@
         <v>2.15</v>
       </c>
       <c r="AC13">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="AD13">
         <v>1.56</v>
       </c>
       <c r="AE13">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF13">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AG13">
         <v>2.4</v>
@@ -2594,10 +2594,10 @@
         <v>1.55</v>
       </c>
       <c r="O14">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P14">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="Q14">
         <v>1.9</v>
@@ -2627,7 +2627,7 @@
         <v>1.2</v>
       </c>
       <c r="Z14">
-        <v>4.92</v>
+        <v>4.2</v>
       </c>
       <c r="AA14">
         <v>1.67</v>
@@ -2763,55 +2763,55 @@
         <v>0</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
+        <v>3.7</v>
+      </c>
+      <c r="O16">
         <v>3.9</v>
       </c>
-      <c r="O16">
-        <v>4.2</v>
-      </c>
       <c r="P16">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="Q16">
         <v>4.18</v>
@@ -2932,7 +2932,7 @@
         <v>2.6</v>
       </c>
       <c r="S16">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="T16">
         <v>4</v>
@@ -2950,7 +2950,7 @@
         <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z16">
         <v>5.75</v>
@@ -2959,7 +2959,7 @@
         <v>1.4</v>
       </c>
       <c r="AB16">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="AC16">
         <v>2.02</v>
@@ -2971,7 +2971,7 @@
         <v>1.26</v>
       </c>
       <c r="AF16">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AG16">
         <v>2.6</v>
@@ -3083,7 +3083,7 @@
         <v>2.15</v>
       </c>
       <c r="O17">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P17">
         <v>2.8</v>
@@ -3095,7 +3095,7 @@
         <v>2.17</v>
       </c>
       <c r="S17">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T17">
         <v>3.04</v>
@@ -3104,7 +3104,7 @@
         <v>2.4</v>
       </c>
       <c r="V17">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W17">
         <v>1.11</v>
@@ -3131,13 +3131,13 @@
         <v>1.4</v>
       </c>
       <c r="AE17">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF17">
         <v>1.53</v>
       </c>
       <c r="AG17">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="O18">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P18">
         <v>3.46</v>
@@ -3270,19 +3270,19 @@
         <v>1.52</v>
       </c>
       <c r="W18">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X18">
         <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z18">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AA18">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AB18">
         <v>2.14</v>
@@ -3300,7 +3300,7 @@
         <v>1.55</v>
       </c>
       <c r="AG18">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>1.25</v>
       </c>
       <c r="AK18">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O19">
         <v>3.7</v>
       </c>
       <c r="P19">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q19">
         <v>3.62</v>
@@ -3430,19 +3430,19 @@
         <v>2.25</v>
       </c>
       <c r="V19">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="W19">
         <v>1.11</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y19">
         <v>1.12</v>
       </c>
       <c r="Z19">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AA19">
         <v>1.55</v>
@@ -3454,10 +3454,10 @@
         <v>2.4</v>
       </c>
       <c r="AD19">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AE19">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AF19">
         <v>1.48</v>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="O20">
-        <v>3.66</v>
+        <v>3.51</v>
       </c>
       <c r="P20">
         <v>5.25</v>
@@ -3590,7 +3590,7 @@
         <v>2.68</v>
       </c>
       <c r="U20">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="V20">
         <v>1.35</v>
@@ -3617,7 +3617,7 @@
         <v>3.68</v>
       </c>
       <c r="AD20">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE20">
         <v>1.03</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="O21">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P21">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="O22">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="P22">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -4064,28 +4064,28 @@
         <v>3.55</v>
       </c>
       <c r="P23">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q23">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="R23">
         <v>2.09</v>
       </c>
       <c r="S23">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T23">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U23">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="V23">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="W23">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X23">
         <v>1.04</v>
@@ -4112,7 +4112,7 @@
         <v>1.11</v>
       </c>
       <c r="AF23">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG23">
         <v>2.02</v>
@@ -4230,7 +4230,7 @@
         <v>4.05</v>
       </c>
       <c r="Q24">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="R24">
         <v>2.38</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK24">
         <v>2</v>
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="O25">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="P25">
         <v>5</v>
@@ -4405,7 +4405,7 @@
         <v>3.55</v>
       </c>
       <c r="U25">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="V25">
         <v>1.6</v>
@@ -4429,7 +4429,7 @@
         <v>2.23</v>
       </c>
       <c r="AC25">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="AD25">
         <v>1.53</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK25">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="O27">
         <v>4.6</v>
       </c>
       <c r="P27">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="Q27">
         <v>1.85</v>
@@ -4725,19 +4725,19 @@
         <v>2.7</v>
       </c>
       <c r="S27">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T27">
         <v>4.33</v>
       </c>
       <c r="U27">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="V27">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="W27">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X27">
         <v>1.01</v>
@@ -4746,25 +4746,25 @@
         <v>1.1</v>
       </c>
       <c r="Z27">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="AA27">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AB27">
-        <v>3.05</v>
+        <v>3.21</v>
       </c>
       <c r="AC27">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AD27">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AE27">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AF27">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AG27">
         <v>2.5</v>
@@ -4783,7 +4783,7 @@
         <v>1.15</v>
       </c>
       <c r="AK27">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,25 +4873,25 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="O28">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="P28">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="Q28">
         <v>1.91</v>
       </c>
       <c r="R28">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="S28">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T28">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="U28">
         <v>2.4</v>
@@ -4906,22 +4906,22 @@
         <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z28">
         <v>4.25</v>
       </c>
       <c r="AA28">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AB28">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AC28">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="AD28">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AE28">
         <v>1.17</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AK28">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5039,16 +5039,16 @@
         <v>1.62</v>
       </c>
       <c r="O29">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P29">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="Q29">
         <v>2.2</v>
       </c>
       <c r="R29">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="S29">
         <v>1.36</v>
@@ -5057,7 +5057,7 @@
         <v>2.97</v>
       </c>
       <c r="U29">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V29">
         <v>1.39</v>
@@ -5078,7 +5078,7 @@
         <v>1.94</v>
       </c>
       <c r="AB29">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AC29">
         <v>3.3</v>
@@ -5087,13 +5087,13 @@
         <v>1.28</v>
       </c>
       <c r="AE29">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF29">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AG29">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK29">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5202,16 +5202,16 @@
         <v>2.2</v>
       </c>
       <c r="O30">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P30">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="Q30">
         <v>2.61</v>
       </c>
       <c r="R30">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="S30">
         <v>1.22</v>
@@ -5232,7 +5232,7 @@
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z30">
         <v>4</v>
@@ -5241,7 +5241,7 @@
         <v>1.64</v>
       </c>
       <c r="AB30">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AC30">
         <v>2.38</v>
@@ -5250,13 +5250,13 @@
         <v>1.47</v>
       </c>
       <c r="AE30">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF30">
         <v>1.55</v>
       </c>
       <c r="AG30">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5362,19 +5362,19 @@
         </is>
       </c>
       <c r="N31">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="O31">
         <v>5.25</v>
       </c>
       <c r="P31">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="Q31">
         <v>6</v>
       </c>
       <c r="R31">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="S31">
         <v>1.21</v>
@@ -5383,10 +5383,10 @@
         <v>3.75</v>
       </c>
       <c r="U31">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="V31">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="W31">
         <v>1.15</v>
@@ -5398,7 +5398,7 @@
         <v>1.13</v>
       </c>
       <c r="Z31">
-        <v>5.96</v>
+        <v>6</v>
       </c>
       <c r="AA31">
         <v>1.4</v>
@@ -5410,7 +5410,7 @@
         <v>2.1</v>
       </c>
       <c r="AD31">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AE31">
         <v>1.3</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>2.78</v>
+        <v>1.18</v>
       </c>
       <c r="AK31">
         <v>1.07</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5688,25 +5688,25 @@
         </is>
       </c>
       <c r="N33">
-        <v>5.75</v>
+        <v>6.15</v>
       </c>
       <c r="O33">
         <v>4.45</v>
       </c>
       <c r="P33">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="Q33">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="R33">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="S33">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T33">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="U33">
         <v>2.05</v>
@@ -5724,7 +5724,7 @@
         <v>1.13</v>
       </c>
       <c r="Z33">
-        <v>5.68</v>
+        <v>5.7</v>
       </c>
       <c r="AA33">
         <v>1.4</v>
@@ -5733,13 +5733,13 @@
         <v>2.6</v>
       </c>
       <c r="AC33">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AD33">
         <v>1.69</v>
       </c>
       <c r="AE33">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AF33">
         <v>1.55</v>
@@ -5863,13 +5863,13 @@
         <v>2.8</v>
       </c>
       <c r="R34">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="S34">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T34">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="U34">
         <v>2.45</v>
@@ -5881,22 +5881,22 @@
         <v>1.06</v>
       </c>
       <c r="X34">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
         <v>1.2</v>
       </c>
       <c r="Z34">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="AA34">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB34">
         <v>1.94</v>
       </c>
       <c r="AC34">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="AD34">
         <v>1.33</v>
@@ -6014,34 +6014,34 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="O35">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P35">
-        <v>2.81</v>
+        <v>2.87</v>
       </c>
       <c r="Q35">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="R35">
         <v>2.1</v>
       </c>
       <c r="S35">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="T35">
-        <v>2.9</v>
+        <v>2.58</v>
       </c>
       <c r="U35">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="V35">
         <v>1.35</v>
       </c>
       <c r="W35">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X35">
         <v>1.06</v>
@@ -6050,28 +6050,28 @@
         <v>1.33</v>
       </c>
       <c r="Z35">
-        <v>3.36</v>
+        <v>3.32</v>
       </c>
       <c r="AA35">
         <v>2.07</v>
       </c>
       <c r="AB35">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AC35">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="AD35">
         <v>1.25</v>
       </c>
       <c r="AE35">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF35">
         <v>1.8</v>
       </c>
       <c r="AG35">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK35">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6210,13 +6210,13 @@
         <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z36">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AA36">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AB36">
         <v>1.9</v>
@@ -6231,7 +6231,7 @@
         <v>1.11</v>
       </c>
       <c r="AF36">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AG36">
         <v>1.85</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O38">
         <v>3.2</v>
       </c>
       <c r="P38">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="Q38">
         <v>2.78</v>
@@ -6533,7 +6533,7 @@
         <v>1.07</v>
       </c>
       <c r="X38">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y38">
         <v>1.24</v>
@@ -6548,7 +6548,7 @@
         <v>1.86</v>
       </c>
       <c r="AC38">
-        <v>3.14</v>
+        <v>3.35</v>
       </c>
       <c r="AD38">
         <v>1.3</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK38">
         <v>1.54</v>
@@ -6666,25 +6666,25 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="O39">
-        <v>6.25</v>
+        <v>6.3</v>
       </c>
       <c r="P39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q39">
         <v>1.57</v>
       </c>
       <c r="R39">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="S39">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T39">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="U39">
         <v>2.25</v>
@@ -6696,13 +6696,13 @@
         <v>1.14</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
         <v>1.1</v>
       </c>
       <c r="Z39">
-        <v>5.2</v>
+        <v>5.15</v>
       </c>
       <c r="AA39">
         <v>1.42</v>
@@ -6714,7 +6714,7 @@
         <v>2.25</v>
       </c>
       <c r="AD39">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AE39">
         <v>1.22</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="O40">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P40">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="Q40">
         <v>2.25</v>
@@ -6844,10 +6844,10 @@
         <v>2.38</v>
       </c>
       <c r="S40">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T40">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U40">
         <v>2.32</v>
@@ -6856,7 +6856,7 @@
         <v>1.53</v>
       </c>
       <c r="W40">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X40">
         <v>1.01</v>
@@ -6995,13 +6995,13 @@
         <v>3.1</v>
       </c>
       <c r="O41">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P41">
         <v>2</v>
       </c>
       <c r="Q41">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="R41">
         <v>2.3</v>
@@ -7010,10 +7010,10 @@
         <v>1.29</v>
       </c>
       <c r="T41">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U41">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="V41">
         <v>1.5</v>
@@ -7022,10 +7022,10 @@
         <v>1.08</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z41">
         <v>3.98</v>
@@ -7034,13 +7034,13 @@
         <v>1.66</v>
       </c>
       <c r="AB41">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC41">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AD41">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE41">
         <v>1.12</v>
@@ -7049,7 +7049,7 @@
         <v>1.55</v>
       </c>
       <c r="AG41">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AK41">
         <v>1.28</v>
@@ -7176,28 +7176,28 @@
         <v>3.14</v>
       </c>
       <c r="U42">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="V42">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="W42">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X42">
         <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z42">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AA42">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB42">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AC42">
         <v>2.52</v>
@@ -7206,13 +7206,13 @@
         <v>1.41</v>
       </c>
       <c r="AE42">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF42">
         <v>1.52</v>
       </c>
       <c r="AG42">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="Q43">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="R43">
         <v>2.2</v>
       </c>
       <c r="S43">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T43">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="U43">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="V43">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W43">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X43">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="Z43">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="AA43">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AB43">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC43">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AD43">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AE43">
         <v>1.13</v>
       </c>
       <c r="AF43">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG43">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK43">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="O44">
-        <v>3.81</v>
+        <v>3.61</v>
       </c>
       <c r="P44">
-        <v>4.51</v>
+        <v>4.01</v>
       </c>
       <c r="Q44">
         <v>2.28</v>
       </c>
       <c r="R44">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S44">
+        <v>1.36</v>
+      </c>
+      <c r="T44">
+        <v>2.65</v>
+      </c>
+      <c r="U44">
+        <v>2.8</v>
+      </c>
+      <c r="V44">
+        <v>1.36</v>
+      </c>
+      <c r="W44">
+        <v>1.07</v>
+      </c>
+      <c r="X44">
+        <v>1.02</v>
+      </c>
+      <c r="Y44">
         <v>1.3</v>
       </c>
-      <c r="T44">
-        <v>3.2</v>
-      </c>
-      <c r="U44">
-        <v>2.63</v>
-      </c>
-      <c r="V44">
-        <v>1.45</v>
-      </c>
-      <c r="W44">
+      <c r="Z44">
+        <v>3.1</v>
+      </c>
+      <c r="AA44">
+        <v>1.93</v>
+      </c>
+      <c r="AB44">
+        <v>1.8</v>
+      </c>
+      <c r="AC44">
+        <v>3.35</v>
+      </c>
+      <c r="AD44">
+        <v>1.27</v>
+      </c>
+      <c r="AE44">
         <v>1.1</v>
       </c>
-      <c r="X44">
-        <v>1.03</v>
-      </c>
-      <c r="Y44">
-        <v>1.23</v>
-      </c>
-      <c r="Z44">
-        <v>3.75</v>
-      </c>
-      <c r="AA44">
-        <v>1.81</v>
-      </c>
-      <c r="AB44">
-        <v>2</v>
-      </c>
-      <c r="AC44">
-        <v>2.8</v>
-      </c>
-      <c r="AD44">
-        <v>1.38</v>
-      </c>
-      <c r="AE44">
-        <v>1.13</v>
-      </c>
       <c r="AF44">
-        <v>1.54</v>
+        <v>1.82</v>
       </c>
       <c r="AG44">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AK44">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -8136,7 +8136,7 @@
         <v>2.45</v>
       </c>
       <c r="O48">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P48">
         <v>2.73</v>
@@ -8157,7 +8157,7 @@
         <v>3.16</v>
       </c>
       <c r="V48">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W48">
         <v>1.01</v>
@@ -8172,16 +8172,16 @@
         <v>2.83</v>
       </c>
       <c r="AA48">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="AB48">
         <v>1.65</v>
       </c>
       <c r="AC48">
-        <v>3.91</v>
+        <v>3.86</v>
       </c>
       <c r="AD48">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AE48">
         <v>1.02</v>
@@ -8206,7 +8206,7 @@
         <v>1.33</v>
       </c>
       <c r="AK48">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O49">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P49">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8468,7 +8468,7 @@
         <v>12</v>
       </c>
       <c r="Q50">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R50">
         <v>3.12</v>
@@ -8483,7 +8483,7 @@
         <v>2.06</v>
       </c>
       <c r="V50">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="W50">
         <v>1.17</v>
@@ -8492,7 +8492,7 @@
         <v>0</v>
       </c>
       <c r="Y50">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z50">
         <v>5.95</v>
@@ -8507,16 +8507,16 @@
         <v>2.05</v>
       </c>
       <c r="AD50">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AE50">
         <v>1.28</v>
       </c>
       <c r="AF50">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="AG50">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AK50">
-        <v>6.5</v>
+        <v>6.15</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,19 +8622,19 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="O51">
         <v>3.6</v>
       </c>
       <c r="P51">
-        <v>3.61</v>
+        <v>3.75</v>
       </c>
       <c r="Q51">
         <v>2.4</v>
       </c>
       <c r="R51">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S51">
         <v>1.3</v>
@@ -8652,10 +8652,10 @@
         <v>1.09</v>
       </c>
       <c r="X51">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y51">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z51">
         <v>4.1</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="O52">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="P52">
-        <v>4.95</v>
+        <v>4.78</v>
       </c>
       <c r="Q52">
         <v>2.15</v>
@@ -8806,7 +8806,7 @@
         <v>3.25</v>
       </c>
       <c r="U52">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V52">
         <v>1.48</v>
@@ -8818,10 +8818,10 @@
         <v>1.04</v>
       </c>
       <c r="Y52">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z52">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA52">
         <v>1.72</v>
@@ -8836,7 +8836,7 @@
         <v>1.36</v>
       </c>
       <c r="AE52">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF52">
         <v>1.72</v>
@@ -8858,7 +8858,7 @@
         <v>1.24</v>
       </c>
       <c r="AK52">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9117,10 +9117,10 @@
         <v>3.5</v>
       </c>
       <c r="P54">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="Q54">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="R54">
         <v>2.3</v>
@@ -9132,7 +9132,7 @@
         <v>3.3</v>
       </c>
       <c r="U54">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="V54">
         <v>1.48</v>
@@ -9150,7 +9150,7 @@
         <v>3.92</v>
       </c>
       <c r="AA54">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AB54">
         <v>2.05</v>
@@ -9168,7 +9168,7 @@
         <v>1.59</v>
       </c>
       <c r="AG54">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9274,25 +9274,25 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q55">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="R55">
         <v>2.3</v>
       </c>
       <c r="S55">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T55">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="U55">
         <v>2.8</v>
@@ -9307,19 +9307,19 @@
         <v>1.02</v>
       </c>
       <c r="Y55">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="Z55">
         <v>3</v>
       </c>
       <c r="AA55">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="AB55">
-        <v>1.92</v>
+        <v>1.73</v>
       </c>
       <c r="AC55">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="AD55">
         <v>1.35</v>
@@ -9331,7 +9331,7 @@
         <v>1.9</v>
       </c>
       <c r="AG55">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="O56">
-        <v>2.86</v>
+        <v>2.73</v>
       </c>
       <c r="P56">
-        <v>2.61</v>
+        <v>2.23</v>
       </c>
       <c r="Q56">
         <v>3.8</v>
@@ -9470,13 +9470,13 @@
         <v>1.11</v>
       </c>
       <c r="Y56">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="Z56">
         <v>2.38</v>
       </c>
       <c r="AA56">
-        <v>2.73</v>
+        <v>2.55</v>
       </c>
       <c r="AB56">
         <v>1.44</v>
@@ -9488,13 +9488,13 @@
         <v>1.14</v>
       </c>
       <c r="AE56">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF56">
         <v>2.1</v>
       </c>
       <c r="AG56">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>3.13</v>
+        <v>2.86</v>
       </c>
       <c r="O57">
-        <v>3.5</v>
+        <v>3.37</v>
       </c>
       <c r="P57">
-        <v>2.21</v>
+        <v>2.11</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="O58">
-        <v>3.23</v>
+        <v>3.55</v>
       </c>
       <c r="P58">
-        <v>4</v>
+        <v>4.48</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="O59">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="P59">
-        <v>3.05</v>
+        <v>3.78</v>
       </c>
       <c r="Q59">
         <v>2.3</v>
@@ -9944,7 +9944,7 @@
         <v>1.17</v>
       </c>
       <c r="T59">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U59">
         <v>2.13</v>
@@ -9971,7 +9971,7 @@
         <v>2.7</v>
       </c>
       <c r="AC59">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AD59">
         <v>1.76</v>
@@ -10089,10 +10089,10 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="O60">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="P60">
         <v>5.5</v>
@@ -10107,7 +10107,7 @@
         <v>1.22</v>
       </c>
       <c r="T60">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="U60">
         <v>2.1</v>
@@ -10143,7 +10143,7 @@
         <v>1.24</v>
       </c>
       <c r="AF60">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AG60">
         <v>2.18</v>
@@ -10252,16 +10252,16 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="O61">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="P61">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q61">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R61">
         <v>2.5</v>
@@ -10273,10 +10273,10 @@
         <v>4.5</v>
       </c>
       <c r="U61">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="V61">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W61">
         <v>1.16</v>
@@ -10288,25 +10288,25 @@
         <v>1.12</v>
       </c>
       <c r="Z61">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="AA61">
         <v>1.43</v>
       </c>
       <c r="AB61">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AC61">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="AD61">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AE61">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AF61">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AG61">
         <v>2.8</v>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK61">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="O62">
-        <v>3.44</v>
+        <v>3.25</v>
       </c>
       <c r="P62">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA62">
         <v>2.05</v>
       </c>
       <c r="AB62">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="O63">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="P63">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="Q63">
         <v>3.2</v>
@@ -10596,7 +10596,7 @@
         <v>1.57</v>
       </c>
       <c r="T63">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="U63">
         <v>3.25</v>
@@ -10635,7 +10635,7 @@
         <v>2.05</v>
       </c>
       <c r="AG63">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O64">
         <v>3.4</v>
@@ -10780,10 +10780,10 @@
         <v>4.95</v>
       </c>
       <c r="AA64">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AB64">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AC64">
         <v>2.7</v>
@@ -10795,7 +10795,7 @@
         <v>1.25</v>
       </c>
       <c r="AF64">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AG64">
         <v>2.3</v>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK64">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10904,25 +10904,25 @@
         </is>
       </c>
       <c r="N65">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="O65">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="P65">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="Q65">
-        <v>4.8</v>
+        <v>4.42</v>
       </c>
       <c r="R65">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S65">
         <v>1.33</v>
       </c>
       <c r="T65">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="U65">
         <v>2.47</v>
@@ -10943,16 +10943,16 @@
         <v>3.84</v>
       </c>
       <c r="AA65">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AB65">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="AC65">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="AD65">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE65">
         <v>1.14</v>
@@ -10977,7 +10977,7 @@
         <v>2.28</v>
       </c>
       <c r="AK65">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11076,16 +11076,16 @@
         <v>2.7</v>
       </c>
       <c r="Q66">
-        <v>2.91</v>
+        <v>2.85</v>
       </c>
       <c r="R66">
         <v>2.37</v>
       </c>
       <c r="S66">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T66">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U66">
         <v>2.5</v>
@@ -11106,7 +11106,7 @@
         <v>4.05</v>
       </c>
       <c r="AA66">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AB66">
         <v>2.15</v>
@@ -11118,7 +11118,7 @@
         <v>1.38</v>
       </c>
       <c r="AE66">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF66">
         <v>1.55</v>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK66">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11233,16 +11233,16 @@
         <v>3</v>
       </c>
       <c r="O67">
-        <v>3.65</v>
+        <v>3.78</v>
       </c>
       <c r="P67">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="Q67">
         <v>3.4</v>
       </c>
       <c r="R67">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S67">
         <v>1.23</v>
@@ -11260,7 +11260,7 @@
         <v>1.18</v>
       </c>
       <c r="X67">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y67">
         <v>1.14</v>
@@ -11272,7 +11272,7 @@
         <v>1.49</v>
       </c>
       <c r="AB67">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="AC67">
         <v>2.15</v>
@@ -11396,10 +11396,10 @@
         <v>2.34</v>
       </c>
       <c r="O68">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="P68">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="Q68">
         <v>2.91</v>
@@ -11447,10 +11447,10 @@
         <v>1.18</v>
       </c>
       <c r="AF68">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG68">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q71">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S71">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T71">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U71">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V71">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W71">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y71">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z71">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA71">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AB71">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AC71">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD71">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE71">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF71">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG71">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK71">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,80 +12045,80 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.62</v>
+        <v>2.11</v>
       </c>
       <c r="O72">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="P72">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="Q72">
-        <v>2.16</v>
+        <v>2.46</v>
       </c>
       <c r="R72">
+        <v>2.06</v>
+      </c>
+      <c r="S72">
+        <v>1.39</v>
+      </c>
+      <c r="T72">
+        <v>3</v>
+      </c>
+      <c r="U72">
+        <v>2.69</v>
+      </c>
+      <c r="V72">
+        <v>1.4</v>
+      </c>
+      <c r="W72">
+        <v>1.07</v>
+      </c>
+      <c r="X72">
+        <v>1.01</v>
+      </c>
+      <c r="Y72">
+        <v>1.3</v>
+      </c>
+      <c r="Z72">
+        <v>3.42</v>
+      </c>
+      <c r="AA72">
+        <v>1.94</v>
+      </c>
+      <c r="AB72">
+        <v>1.85</v>
+      </c>
+      <c r="AC72">
+        <v>2.92</v>
+      </c>
+      <c r="AD72">
+        <v>1.31</v>
+      </c>
+      <c r="AE72">
+        <v>1.07</v>
+      </c>
+      <c r="AF72">
+        <v>1.67</v>
+      </c>
+      <c r="AG72">
         <v>2.15</v>
       </c>
-      <c r="S72">
-        <v>1.3</v>
-      </c>
-      <c r="T72">
-        <v>2.99</v>
-      </c>
-      <c r="U72">
-        <v>2.73</v>
-      </c>
-      <c r="V72">
-        <v>1.42</v>
-      </c>
-      <c r="W72">
-        <v>1.06</v>
-      </c>
-      <c r="X72">
-        <v>1</v>
-      </c>
-      <c r="Y72">
-        <v>1.26</v>
-      </c>
-      <c r="Z72">
-        <v>3.68</v>
-      </c>
-      <c r="AA72">
-        <v>1.78</v>
-      </c>
-      <c r="AB72">
-        <v>1.93</v>
-      </c>
-      <c r="AC72">
-        <v>3.1</v>
-      </c>
-      <c r="AD72">
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ72">
         <v>1.33</v>
       </c>
-      <c r="AE72">
-        <v>1.1</v>
-      </c>
-      <c r="AF72">
-        <v>1.76</v>
-      </c>
-      <c r="AG72">
-        <v>1.96</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ72">
-        <v>1.09</v>
-      </c>
       <c r="AK72">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12208,16 +12208,16 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="O73">
-        <v>3.74</v>
+        <v>3.62</v>
       </c>
       <c r="P73">
         <v>2.76</v>
       </c>
       <c r="Q73">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="R73">
         <v>2.4</v>
@@ -12235,7 +12235,7 @@
         <v>1.6</v>
       </c>
       <c r="W73">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X73">
         <v>1.01</v>
@@ -12253,7 +12253,7 @@
         <v>2.55</v>
       </c>
       <c r="AC73">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AD73">
         <v>1.49</v>
@@ -12265,7 +12265,7 @@
         <v>1.44</v>
       </c>
       <c r="AG73">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12380,16 +12380,16 @@
         <v>8.5</v>
       </c>
       <c r="Q74">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="R74">
         <v>3</v>
       </c>
       <c r="S74">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="T74">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="U74">
         <v>1.8</v>
@@ -12404,31 +12404,31 @@
         <v>0</v>
       </c>
       <c r="Y74">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z74">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AA74">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AB74">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AC74">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AD74">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AE74">
         <v>1.3</v>
       </c>
       <c r="AF74">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AG74">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AK74">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12534,25 +12534,25 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="O75">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P75">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="Q75">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="R75">
         <v>2.2</v>
       </c>
       <c r="S75">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T75">
-        <v>2.69</v>
+        <v>2.91</v>
       </c>
       <c r="U75">
         <v>2.97</v>
@@ -12579,19 +12579,19 @@
         <v>1.78</v>
       </c>
       <c r="AC75">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="AD75">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE75">
         <v>1.11</v>
       </c>
       <c r="AF75">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG75">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12697,19 +12697,19 @@
         </is>
       </c>
       <c r="N76">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O76">
         <v>3.5</v>
       </c>
       <c r="P76">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="Q76">
-        <v>4.16</v>
+        <v>4.2</v>
       </c>
       <c r="R76">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="S76">
         <v>1.25</v>
@@ -12733,13 +12733,13 @@
         <v>1.18</v>
       </c>
       <c r="Z76">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AA76">
         <v>1.62</v>
       </c>
       <c r="AB76">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AC76">
         <v>2.5</v>
@@ -12748,7 +12748,7 @@
         <v>1.5</v>
       </c>
       <c r="AE76">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF76">
         <v>1.53</v>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AK76">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="O77">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="P77">
-        <v>5.39</v>
+        <v>5.3</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S77">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T77">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U77">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V77">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W77">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X77">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y77">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z77">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA77">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB77">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AC77">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD77">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK77">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="O78">
         <v>3.73</v>
       </c>
       <c r="P78">
-        <v>2.17</v>
+        <v>2.35</v>
       </c>
       <c r="Q78">
         <v>2.92</v>
@@ -13044,13 +13044,13 @@
         <v>3.9</v>
       </c>
       <c r="U78">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="V78">
         <v>1.76</v>
       </c>
       <c r="W78">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X78">
         <v>1.01</v>
@@ -13062,7 +13062,7 @@
         <v>6</v>
       </c>
       <c r="AA78">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AB78">
         <v>2.85</v>
@@ -13071,7 +13071,7 @@
         <v>1.96</v>
       </c>
       <c r="AD78">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AE78">
         <v>1.3</v>
@@ -13186,7 +13186,7 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.79</v>
+        <v>1.96</v>
       </c>
       <c r="O79">
         <v>3.45</v>
@@ -13204,7 +13204,7 @@
         <v>1.26</v>
       </c>
       <c r="T79">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="U79">
         <v>2.27</v>
@@ -13219,16 +13219,16 @@
         <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z79">
         <v>4.8</v>
       </c>
       <c r="AA79">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AB79">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="AC79">
         <v>2.28</v>
@@ -13240,7 +13240,7 @@
         <v>1.18</v>
       </c>
       <c r="AF79">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG79">
         <v>2.38</v>
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
+        <v>5</v>
+      </c>
+      <c r="O80">
         <v>4.7</v>
       </c>
-      <c r="O80">
-        <v>4.55</v>
-      </c>
       <c r="P80">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="Q80">
         <v>4</v>
@@ -13364,16 +13364,16 @@
         <v>2.88</v>
       </c>
       <c r="S80">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="T80">
-        <v>4.8</v>
+        <v>4.55</v>
       </c>
       <c r="U80">
         <v>1.83</v>
       </c>
       <c r="V80">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="W80">
         <v>1.25</v>
@@ -13397,10 +13397,10 @@
         <v>1.67</v>
       </c>
       <c r="AD80">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AE80">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AF80">
         <v>1.37</v>
@@ -13515,13 +13515,13 @@
         <v>1.31</v>
       </c>
       <c r="O81">
-        <v>5.9</v>
+        <v>5.05</v>
       </c>
       <c r="P81">
         <v>5.6</v>
       </c>
       <c r="Q81">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="R81">
         <v>3</v>
@@ -13548,19 +13548,19 @@
         <v>1.02</v>
       </c>
       <c r="Z81">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="AA81">
         <v>1.27</v>
       </c>
       <c r="AB81">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AC81">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AD81">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AE81">
         <v>1.54</v>
@@ -13678,22 +13678,22 @@
         <v>2.24</v>
       </c>
       <c r="O82">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="P82">
         <v>2.41</v>
       </c>
       <c r="Q82">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="R82">
         <v>2.7</v>
       </c>
       <c r="S82">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T82">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="U82">
         <v>1.84</v>
@@ -13720,10 +13720,10 @@
         <v>3.39</v>
       </c>
       <c r="AC82">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AD82">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AE82">
         <v>1.38</v>
@@ -14001,7 +14001,7 @@
         </is>
       </c>
       <c r="N84">
-        <v>3.51</v>
+        <v>3</v>
       </c>
       <c r="O84">
         <v>3.31</v>
@@ -14164,58 +14164,58 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="O85">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P85">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="Q85">
         <v>2.38</v>
       </c>
       <c r="R85">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S85">
         <v>1.32</v>
       </c>
       <c r="T85">
-        <v>3.21</v>
+        <v>2.9</v>
       </c>
       <c r="U85">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V85">
         <v>1.44</v>
       </c>
       <c r="W85">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X85">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y85">
         <v>1.22</v>
       </c>
       <c r="Z85">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="AA85">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AB85">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AC85">
-        <v>2.91</v>
+        <v>2.85</v>
       </c>
       <c r="AD85">
         <v>1.36</v>
       </c>
       <c r="AE85">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF85">
         <v>1.67</v>
@@ -14237,7 +14237,7 @@
         <v>1.22</v>
       </c>
       <c r="AK85">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14327,28 +14327,28 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="O86">
-        <v>3.23</v>
+        <v>3.3</v>
       </c>
       <c r="P86">
-        <v>4.3</v>
+        <v>4.65</v>
       </c>
       <c r="Q86">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="R86">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="S86">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="T86">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="U86">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="V86">
         <v>1.28</v>
@@ -14360,31 +14360,31 @@
         <v>1.03</v>
       </c>
       <c r="Y86">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z86">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AA86">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="AB86">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AC86">
-        <v>4.18</v>
+        <v>4.3</v>
       </c>
       <c r="AD86">
         <v>1.16</v>
       </c>
       <c r="AE86">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF86">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AG86">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK86">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14517,7 +14517,7 @@
         <v>1.44</v>
       </c>
       <c r="W87">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X87">
         <v>1</v>
@@ -14563,7 +14563,7 @@
         <v>1.38</v>
       </c>
       <c r="AK87">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14816,31 +14816,31 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="O89">
-        <v>3.72</v>
+        <v>4</v>
       </c>
       <c r="P89">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="Q89">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="R89">
         <v>2.26</v>
       </c>
       <c r="S89">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T89">
-        <v>3.55</v>
+        <v>3.28</v>
       </c>
       <c r="U89">
         <v>2.25</v>
       </c>
       <c r="V89">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="W89">
         <v>1.08</v>
@@ -14855,16 +14855,16 @@
         <v>4.4</v>
       </c>
       <c r="AA89">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB89">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC89">
-        <v>2.41</v>
+        <v>2.55</v>
       </c>
       <c r="AD89">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AE89">
         <v>1.18</v>
@@ -14873,7 +14873,7 @@
         <v>1.7</v>
       </c>
       <c r="AG89">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,7 +14886,7 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK89">
         <v>2.3</v>
@@ -14988,7 +14988,7 @@
         <v>2.8</v>
       </c>
       <c r="Q90">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="R90">
         <v>2.28</v>
@@ -15003,7 +15003,7 @@
         <v>2.59</v>
       </c>
       <c r="V90">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W90">
         <v>1.05</v>
@@ -15015,13 +15015,13 @@
         <v>1.2</v>
       </c>
       <c r="Z90">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AA90">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AB90">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AC90">
         <v>2.95</v>
@@ -15036,7 +15036,7 @@
         <v>1.6</v>
       </c>
       <c r="AG90">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15969,19 +15969,19 @@
         <v>2.86</v>
       </c>
       <c r="R96">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S96">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T96">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="U96">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="V96">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W96">
         <v>1.05</v>
@@ -15996,13 +15996,13 @@
         <v>2.92</v>
       </c>
       <c r="AA96">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AB96">
         <v>1.67</v>
       </c>
       <c r="AC96">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="AD96">
         <v>1.2</v>
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.03</v>
+        <v>2.16</v>
       </c>
       <c r="O99">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="P99">
-        <v>4.45</v>
+        <v>4.1</v>
       </c>
       <c r="Q99">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="R99">
-        <v>2.08</v>
+        <v>1.77</v>
       </c>
       <c r="S99">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="T99">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="U99">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="V99">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W99">
         <v>1</v>
       </c>
       <c r="X99">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y99">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z99">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="AA99">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="AB99">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC99">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="AD99">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AE99">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF99">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AG99">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AK99">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16772,10 +16772,10 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="O101">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="P101">
         <v>2.85</v>
@@ -16787,34 +16787,34 @@
         <v>1.91</v>
       </c>
       <c r="S101">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="T101">
-        <v>2.43</v>
+        <v>2.24</v>
       </c>
       <c r="U101">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="V101">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W101">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X101">
         <v>1.08</v>
       </c>
       <c r="Y101">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="Z101">
         <v>2.41</v>
       </c>
       <c r="AA101">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="AB101">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AC101">
         <v>4.84</v>
@@ -16842,7 +16842,7 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK101">
         <v>1.41</v>
@@ -16935,25 +16935,25 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="O102">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="P102">
-        <v>9.75</v>
+        <v>9.5</v>
       </c>
       <c r="Q102">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="R102">
         <v>2.98</v>
       </c>
       <c r="S102">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="T102">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="U102">
         <v>1.81</v>
@@ -16962,19 +16962,19 @@
         <v>1.89</v>
       </c>
       <c r="W102">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X102">
         <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Z102">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="AA102">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AB102">
         <v>3.8</v>
@@ -17424,25 +17424,25 @@
         </is>
       </c>
       <c r="N105">
-        <v>4.3</v>
+        <v>4.26</v>
       </c>
       <c r="O105">
-        <v>3.65</v>
+        <v>3.61</v>
       </c>
       <c r="P105">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Q105">
-        <v>4.83</v>
+        <v>4.88</v>
       </c>
       <c r="R105">
         <v>2.25</v>
       </c>
       <c r="S105">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T105">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="U105">
         <v>2.6</v>
@@ -17451,34 +17451,34 @@
         <v>1.44</v>
       </c>
       <c r="W105">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X105">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z105">
-        <v>3.62</v>
+        <v>3.44</v>
       </c>
       <c r="AA105">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AB105">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AC105">
-        <v>2.83</v>
+        <v>2.99</v>
       </c>
       <c r="AD105">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE105">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF105">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG105">
         <v>2</v>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>2.03</v>
+        <v>1.22</v>
       </c>
       <c r="AK105">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17602,7 +17602,7 @@
         <v>2.15</v>
       </c>
       <c r="S106">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="T106">
         <v>2.77</v>
@@ -17614,7 +17614,7 @@
         <v>1.39</v>
       </c>
       <c r="W106">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X106">
         <v>1.05</v>
@@ -17629,16 +17629,16 @@
         <v>2</v>
       </c>
       <c r="AB106">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AC106">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="AD106">
         <v>1.27</v>
       </c>
       <c r="AE106">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF106">
         <v>1.85</v>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.25</v>
+        <v>1.92</v>
       </c>
       <c r="AK106">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17762,7 +17762,7 @@
         <v>2.8</v>
       </c>
       <c r="R107">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S107">
         <v>1.43</v>
@@ -17777,7 +17777,7 @@
         <v>1.34</v>
       </c>
       <c r="W107">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X107">
         <v>1.06</v>
@@ -17789,16 +17789,16 @@
         <v>2.9</v>
       </c>
       <c r="AA107">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AB107">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC107">
         <v>3.9</v>
       </c>
       <c r="AD107">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AE107">
         <v>1.06</v>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK107">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O108">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q108">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="R108">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S108">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T108">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U108">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V108">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W108">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X108">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y108">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z108">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA108">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB108">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC108">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD108">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE108">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF108">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG108">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK108">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18133,7 +18133,7 @@
         <v>1.84</v>
       </c>
       <c r="AG109">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18402,10 +18402,10 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="O111">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P111">
         <v>2.61</v>
@@ -18417,46 +18417,46 @@
         <v>2.1</v>
       </c>
       <c r="S111">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T111">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="U111">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="V111">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W111">
         <v>1.06</v>
       </c>
       <c r="X111">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y111">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="Z111">
         <v>3.66</v>
       </c>
       <c r="AA111">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AB111">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AC111">
         <v>3.2</v>
       </c>
       <c r="AD111">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE111">
         <v>1.09</v>
       </c>
       <c r="AF111">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG111">
         <v>2.1</v>
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="O112">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="P112">
-        <v>4.6</v>
+        <v>4.72</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18604,10 +18604,10 @@
         <v>0</v>
       </c>
       <c r="AA112">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AB112">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AC112">
         <v>0</v>
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="O113">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="P113">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="Q113">
         <v>2.7</v>
@@ -18746,25 +18746,25 @@
         <v>1.6</v>
       </c>
       <c r="T113">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="U113">
         <v>3.7</v>
       </c>
       <c r="V113">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W113">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X113">
         <v>1.14</v>
       </c>
       <c r="Y113">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="Z113">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AA113">
         <v>2.59</v>
@@ -18776,7 +18776,7 @@
         <v>6</v>
       </c>
       <c r="AD113">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AE113">
         <v>1.03</v>
@@ -18785,7 +18785,7 @@
         <v>2.25</v>
       </c>
       <c r="AG113">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18891,31 +18891,31 @@
         </is>
       </c>
       <c r="N114">
-        <v>3.47</v>
+        <v>3.07</v>
       </c>
       <c r="O114">
         <v>3.35</v>
       </c>
       <c r="P114">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q114">
-        <v>4.09</v>
+        <v>4.16</v>
       </c>
       <c r="R114">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="S114">
         <v>1.35</v>
       </c>
       <c r="T114">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U114">
         <v>2.65</v>
       </c>
       <c r="V114">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W114">
         <v>1.06</v>
@@ -18936,7 +18936,7 @@
         <v>1.91</v>
       </c>
       <c r="AC114">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="AD114">
         <v>1.3</v>
@@ -18945,10 +18945,10 @@
         <v>1.08</v>
       </c>
       <c r="AF114">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG114">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK114">
         <v>1.28</v>
@@ -19054,16 +19054,16 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="O115">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="P115">
-        <v>3.3</v>
+        <v>2.83</v>
       </c>
       <c r="Q115">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="R115">
         <v>2.18</v>
@@ -19084,19 +19084,19 @@
         <v>1.08</v>
       </c>
       <c r="X115">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y115">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z115">
         <v>4.32</v>
       </c>
       <c r="AA115">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AB115">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="AC115">
         <v>2.65</v>
@@ -19127,7 +19127,7 @@
         <v>1.23</v>
       </c>
       <c r="AK115">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19220,10 +19220,10 @@
         <v>1.15</v>
       </c>
       <c r="O116">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="P116">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Q116">
         <v>1.55</v>
@@ -19232,16 +19232,16 @@
         <v>2.75</v>
       </c>
       <c r="S116">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T116">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U116">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="V116">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W116">
         <v>1.11</v>
@@ -19250,10 +19250,10 @@
         <v>1.03</v>
       </c>
       <c r="Y116">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Z116">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AA116">
         <v>1.55</v>
@@ -19271,10 +19271,10 @@
         <v>1.18</v>
       </c>
       <c r="AF116">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="AG116">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19290,7 +19290,7 @@
         <v>1.02</v>
       </c>
       <c r="AK116">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19380,19 +19380,19 @@
         </is>
       </c>
       <c r="N117">
-        <v>4.82</v>
+        <v>3.84</v>
       </c>
       <c r="O117">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="P117">
         <v>1.67</v>
       </c>
       <c r="Q117">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="R117">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="S117">
         <v>1.3</v>
@@ -19419,7 +19419,7 @@
         <v>4.3</v>
       </c>
       <c r="AA117">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AB117">
         <v>2.18</v>
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O118">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q118">
         <v>0</v>
@@ -19582,10 +19582,10 @@
         <v>0</v>
       </c>
       <c r="AA118">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB118">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC118">
         <v>0</v>
@@ -19706,10 +19706,10 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="O119">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="P119">
         <v>2.8</v>
@@ -19721,10 +19721,10 @@
         <v>1.73</v>
       </c>
       <c r="S119">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="T119">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="U119">
         <v>4.6</v>
@@ -19739,13 +19739,13 @@
         <v>1.15</v>
       </c>
       <c r="Y119">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="Z119">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="AA119">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AB119">
         <v>1.32</v>
@@ -19760,7 +19760,7 @@
         <v>1.02</v>
       </c>
       <c r="AF119">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="AG119">
         <v>1.44</v>
@@ -19872,13 +19872,13 @@
         <v>1.93</v>
       </c>
       <c r="O120">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P120">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="Q120">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R120">
         <v>2.39</v>
@@ -19939,7 +19939,7 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK120">
         <v>1.69</v>
@@ -20038,7 +20038,7 @@
         <v>3.21</v>
       </c>
       <c r="P121">
-        <v>4.24</v>
+        <v>3.48</v>
       </c>
       <c r="Q121">
         <v>2.52</v>
@@ -20050,7 +20050,7 @@
         <v>1.47</v>
       </c>
       <c r="T121">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="U121">
         <v>3.14</v>
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="O122">
-        <v>4</v>
+        <v>4.45</v>
       </c>
       <c r="P122">
-        <v>6.05</v>
+        <v>7.55</v>
       </c>
       <c r="Q122">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="R122">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="S122">
         <v>1.33</v>
       </c>
       <c r="T122">
-        <v>2.91</v>
+        <v>3.02</v>
       </c>
       <c r="U122">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="V122">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W122">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X122">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y122">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z122">
-        <v>3.68</v>
+        <v>3.94</v>
       </c>
       <c r="AA122">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AB122">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="AC122">
-        <v>2.78</v>
+        <v>2.59</v>
       </c>
       <c r="AD122">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE122">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF122">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AG122">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AK122">
-        <v>2.45</v>
+        <v>2.89</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20358,13 +20358,13 @@
         </is>
       </c>
       <c r="N123">
-        <v>3.93</v>
+        <v>3.55</v>
       </c>
       <c r="O123">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P123">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="Q123">
         <v>4.2</v>
@@ -20373,49 +20373,49 @@
         <v>2.1</v>
       </c>
       <c r="S123">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="T123">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="U123">
         <v>3</v>
       </c>
       <c r="V123">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W123">
         <v>1.03</v>
       </c>
       <c r="X123">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y123">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z123">
-        <v>3.08</v>
+        <v>2.93</v>
       </c>
       <c r="AA123">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AB123">
         <v>1.7</v>
       </c>
       <c r="AC123">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AD123">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE123">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF123">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AG123">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AK123">
         <v>1.18</v>
@@ -20533,46 +20533,46 @@
         <v>2.05</v>
       </c>
       <c r="R124">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="S124">
         <v>1.55</v>
       </c>
       <c r="T124">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U124">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="V124">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="W124">
         <v>1.04</v>
       </c>
       <c r="X124">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y124">
         <v>1.53</v>
       </c>
       <c r="Z124">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="AA124">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AB124">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AC124">
         <v>5.5</v>
       </c>
       <c r="AD124">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE124">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF124">
         <v>2.63</v>
@@ -20696,13 +20696,13 @@
         <v>2.8</v>
       </c>
       <c r="R125">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="S125">
         <v>1.65</v>
       </c>
       <c r="T125">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="U125">
         <v>3.95</v>
@@ -20717,7 +20717,7 @@
         <v>1.12</v>
       </c>
       <c r="Y125">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="Z125">
         <v>2</v>
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O126">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P126">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q126">
         <v>4.75</v>
@@ -20862,13 +20862,13 @@
         <v>2.25</v>
       </c>
       <c r="S126">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="T126">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="U126">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="V126">
         <v>1.47</v>
@@ -20883,19 +20883,19 @@
         <v>1.17</v>
       </c>
       <c r="Z126">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AA126">
         <v>1.76</v>
       </c>
       <c r="AB126">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AC126">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AD126">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE126">
         <v>1.14</v>
@@ -20904,7 +20904,7 @@
         <v>1.65</v>
       </c>
       <c r="AG126">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AK126">
         <v>1.2</v>
@@ -21016,7 +21016,7 @@
         <v>4.95</v>
       </c>
       <c r="P127">
-        <v>5.45</v>
+        <v>4.9</v>
       </c>
       <c r="Q127">
         <v>1.83</v>
@@ -21031,10 +21031,10 @@
         <v>5</v>
       </c>
       <c r="U127">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="V127">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="W127">
         <v>1.24</v>
@@ -21046,7 +21046,7 @@
         <v>1.03</v>
       </c>
       <c r="Z127">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="AA127">
         <v>1.25</v>
@@ -21055,10 +21055,10 @@
         <v>3.28</v>
       </c>
       <c r="AC127">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AD127">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="AE127">
         <v>1.4</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,34 +21173,34 @@
         </is>
       </c>
       <c r="N128">
-        <v>1.82</v>
+        <v>2.04</v>
       </c>
       <c r="O128">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="P128">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="Q128">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="R128">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="S128">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T128">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="U128">
+        <v>1.91</v>
+      </c>
+      <c r="V128">
         <v>1.8</v>
       </c>
-      <c r="V128">
-        <v>1.95</v>
-      </c>
       <c r="W128">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X128">
         <v>1.01</v>
@@ -21209,28 +21209,28 @@
         <v>1.06</v>
       </c>
       <c r="Z128">
-        <v>8.5</v>
+        <v>6.15</v>
       </c>
       <c r="AA128">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AB128">
-        <v>3.8</v>
+        <v>2.92</v>
       </c>
       <c r="AC128">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AD128">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AE128">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AF128">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AG128">
-        <v>3.48</v>
+        <v>3.1</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK128">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,31 +21336,31 @@
         </is>
       </c>
       <c r="N129">
-        <v>2.04</v>
+        <v>1.3</v>
       </c>
       <c r="O129">
-        <v>3.65</v>
+        <v>5.35</v>
       </c>
       <c r="P129">
-        <v>2.85</v>
+        <v>6.6</v>
       </c>
       <c r="Q129">
-        <v>2.4</v>
+        <v>1.71</v>
       </c>
       <c r="R129">
-        <v>2.49</v>
+        <v>2.72</v>
       </c>
       <c r="S129">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T129">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="U129">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="V129">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="W129">
         <v>1.22</v>
@@ -21369,47 +21369,47 @@
         <v>1.01</v>
       </c>
       <c r="Y129">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z129">
-        <v>6.15</v>
+        <v>6.5</v>
       </c>
       <c r="AA129">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AB129">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AC129">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AD129">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AE129">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AF129">
-        <v>1.33</v>
+        <v>1.58</v>
       </c>
       <c r="AG129">
+        <v>2.2</v>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ129">
+        <v>1.08</v>
+      </c>
+      <c r="AK129">
         <v>3.1</v>
-      </c>
-      <c r="AH129" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI129" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ129">
-        <v>1.25</v>
-      </c>
-      <c r="AK129">
-        <v>1.57</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,34 +21499,34 @@
         </is>
       </c>
       <c r="N130">
-        <v>1.31</v>
+        <v>1.91</v>
       </c>
       <c r="O130">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="P130">
-        <v>6.55</v>
+        <v>3.25</v>
       </c>
       <c r="Q130">
-        <v>1.72</v>
+        <v>2.3</v>
       </c>
       <c r="R130">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="S130">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="T130">
-        <v>3.92</v>
+        <v>4.8</v>
       </c>
       <c r="U130">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="V130">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="W130">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X130">
         <v>1.01</v>
@@ -21535,28 +21535,28 @@
         <v>1.06</v>
       </c>
       <c r="Z130">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA130">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AB130">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="AC130">
-        <v>1.86</v>
+        <v>1.68</v>
       </c>
       <c r="AD130">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AE130">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AF130">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="AG130">
-        <v>2.2</v>
+        <v>3.48</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AK130">
-        <v>3.6</v>
+        <v>1.75</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -22314,13 +22314,13 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="O135">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P135">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="Q135">
         <v>2.38</v>
@@ -22365,7 +22365,7 @@
         <v>1.33</v>
       </c>
       <c r="AE135">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF135">
         <v>1.73</v>
@@ -22477,19 +22477,19 @@
         </is>
       </c>
       <c r="N136">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="O136">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="P136">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="Q136">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="R136">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="S136">
         <v>1.25</v>
@@ -22498,34 +22498,34 @@
         <v>3.5</v>
       </c>
       <c r="U136">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="V136">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W136">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X136">
         <v>1.03</v>
       </c>
       <c r="Y136">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z136">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA136">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="AB136">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC136">
-        <v>2.47</v>
+        <v>2.59</v>
       </c>
       <c r="AD136">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE136">
         <v>1.18</v>
@@ -22534,7 +22534,7 @@
         <v>1.5</v>
       </c>
       <c r="AG136">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK136">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22640,16 +22640,16 @@
         </is>
       </c>
       <c r="N137">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="O137">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="P137">
-        <v>2.62</v>
+        <v>2.95</v>
       </c>
       <c r="Q137">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="R137">
         <v>2.1</v>
@@ -22673,19 +22673,19 @@
         <v>1</v>
       </c>
       <c r="Y137">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z137">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA137">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB137">
         <v>1.75</v>
       </c>
       <c r="AC137">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD137">
         <v>1.25</v>
@@ -22694,7 +22694,7 @@
         <v>1.1</v>
       </c>
       <c r="AF137">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG137">
         <v>2</v>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK137">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="N138">
-        <v>5.65</v>
+        <v>6</v>
       </c>
       <c r="O138">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P138">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="Q138">
         <v>6</v>
@@ -22821,7 +22821,7 @@
         <v>1.37</v>
       </c>
       <c r="T138">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="U138">
         <v>2.79</v>
@@ -22854,7 +22854,7 @@
         <v>1.33</v>
       </c>
       <c r="AE138">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF138">
         <v>1.91</v>
@@ -22966,13 +22966,13 @@
         </is>
       </c>
       <c r="N139">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O139">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P139">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q139">
         <v>2.1</v>
@@ -22987,7 +22987,7 @@
         <v>2.31</v>
       </c>
       <c r="U139">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="V139">
         <v>1.24</v>
@@ -22996,7 +22996,7 @@
         <v>1.04</v>
       </c>
       <c r="X139">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Y139">
         <v>1.42</v>
@@ -23008,10 +23008,10 @@
         <v>2.2</v>
       </c>
       <c r="AB139">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AC139">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="AD139">
         <v>1.13</v>
@@ -23039,7 +23039,7 @@
         <v>1.08</v>
       </c>
       <c r="AK139">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23618,13 +23618,13 @@
         </is>
       </c>
       <c r="N143">
-        <v>2.52</v>
+        <v>2.25</v>
       </c>
       <c r="O143">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="P143">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -23657,10 +23657,10 @@
         <v>0</v>
       </c>
       <c r="AA143">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AB143">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AC143">
         <v>0</v>
@@ -23790,55 +23790,55 @@
         <v>0</v>
       </c>
       <c r="Q144">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="R144">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S144">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T144">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U144">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V144">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W144">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X144">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y144">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z144">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA144">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB144">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC144">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD144">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE144">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF144">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AG144">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK144">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -24285,10 +24285,10 @@
         <v>2.2</v>
       </c>
       <c r="S147">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="T147">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="U147">
         <v>2.71</v>
@@ -24297,7 +24297,7 @@
         <v>1.37</v>
       </c>
       <c r="W147">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X147">
         <v>1.03</v>
@@ -24309,25 +24309,25 @@
         <v>3.34</v>
       </c>
       <c r="AA147">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AB147">
         <v>1.88</v>
       </c>
       <c r="AC147">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AD147">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AE147">
         <v>1.07</v>
       </c>
       <c r="AF147">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG147">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK147">
         <v>2.25</v>
@@ -24433,64 +24433,64 @@
         </is>
       </c>
       <c r="N148">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="O148">
         <v>3</v>
       </c>
       <c r="P148">
-        <v>3.87</v>
+        <v>4</v>
       </c>
       <c r="Q148">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="R148">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S148">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T148">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U148">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V148">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W148">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X148">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y148">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z148">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AA148">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB148">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC148">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD148">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE148">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF148">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG148">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -24503,10 +24503,10 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK148">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -24596,13 +24596,13 @@
         </is>
       </c>
       <c r="N149">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="O149">
         <v>3.4</v>
       </c>
       <c r="P149">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="Q149">
         <v>2.5</v>
@@ -24669,7 +24669,7 @@
         <v>1.25</v>
       </c>
       <c r="AK149">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -24937,7 +24937,7 @@
         <v>1.81</v>
       </c>
       <c r="S151">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="T151">
         <v>2.31</v>
@@ -24964,19 +24964,19 @@
         <v>2.2</v>
       </c>
       <c r="AB151">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC151">
         <v>3.48</v>
       </c>
       <c r="AD151">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE151">
         <v>1.04</v>
       </c>
       <c r="AF151">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="AG151">
         <v>1.89</v>
@@ -24995,7 +24995,7 @@
         <v>1.4</v>
       </c>
       <c r="AK151">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25085,19 +25085,19 @@
         </is>
       </c>
       <c r="N152">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="O152">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P152">
+        <v>2.68</v>
+      </c>
+      <c r="Q152">
         <v>2.88</v>
       </c>
-      <c r="Q152">
-        <v>3</v>
-      </c>
       <c r="R152">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="S152">
         <v>1.33</v>
@@ -25115,28 +25115,28 @@
         <v>1.09</v>
       </c>
       <c r="X152">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y152">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z152">
         <v>4</v>
       </c>
       <c r="AA152">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AB152">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC152">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AD152">
         <v>1.42</v>
       </c>
       <c r="AE152">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF152">
         <v>1.53</v>
@@ -25158,7 +25158,7 @@
         <v>1.44</v>
       </c>
       <c r="AK152">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25417,74 +25417,74 @@
         <v>2.65</v>
       </c>
       <c r="P154">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q154">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R154">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S154">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="T154">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U154">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="V154">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W154">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X154">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y154">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z154">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA154">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="AB154">
+        <v>1.34</v>
+      </c>
+      <c r="AC154">
+        <v>6.45</v>
+      </c>
+      <c r="AD154">
+        <v>1.1</v>
+      </c>
+      <c r="AE154">
+        <v>1.03</v>
+      </c>
+      <c r="AF154">
+        <v>2.3</v>
+      </c>
+      <c r="AG154">
+        <v>1.57</v>
+      </c>
+      <c r="AH154" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI154" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ154">
         <v>1.4</v>
       </c>
-      <c r="AC154">
-        <v>0</v>
-      </c>
-      <c r="AD154">
-        <v>0</v>
-      </c>
-      <c r="AE154">
-        <v>0</v>
-      </c>
-      <c r="AF154">
-        <v>0</v>
-      </c>
-      <c r="AG154">
-        <v>0</v>
-      </c>
-      <c r="AH154" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI154" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ154">
-        <v>0</v>
-      </c>
       <c r="AK154">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25577,28 +25577,28 @@
         <v>1.36</v>
       </c>
       <c r="O155">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="P155">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="Q155">
         <v>1.85</v>
       </c>
       <c r="R155">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="S155">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T155">
         <v>3.25</v>
       </c>
       <c r="U155">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="V155">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W155">
         <v>1.11</v>
@@ -25607,7 +25607,7 @@
         <v>1.03</v>
       </c>
       <c r="Y155">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z155">
         <v>4.33</v>
@@ -25616,22 +25616,22 @@
         <v>1.62</v>
       </c>
       <c r="AB155">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC155">
         <v>2.6</v>
       </c>
       <c r="AD155">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AE155">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF155">
         <v>1.85</v>
       </c>
       <c r="AG155">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25737,13 +25737,13 @@
         </is>
       </c>
       <c r="N156">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="O156">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="P156">
-        <v>3.16</v>
+        <v>2.61</v>
       </c>
       <c r="Q156">
         <v>3</v>
@@ -25752,7 +25752,7 @@
         <v>2.05</v>
       </c>
       <c r="S156">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T156">
         <v>2.88</v>
@@ -25794,7 +25794,7 @@
         <v>1.73</v>
       </c>
       <c r="AG156">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25900,13 +25900,13 @@
         </is>
       </c>
       <c r="N157">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="O157">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="P157">
-        <v>3.8</v>
+        <v>3.18</v>
       </c>
       <c r="Q157">
         <v>2.5</v>
@@ -25951,7 +25951,7 @@
         <v>1.17</v>
       </c>
       <c r="AE157">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF157">
         <v>2.1</v>
@@ -25970,7 +25970,7 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK157">
         <v>1.73</v>
@@ -26066,10 +26066,10 @@
         <v>1.63</v>
       </c>
       <c r="O158">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P158">
-        <v>5.95</v>
+        <v>5.25</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -26084,7 +26084,7 @@
         <v>2.4</v>
       </c>
       <c r="U158">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="V158">
         <v>1.22</v>
@@ -26111,16 +26111,16 @@
         <v>5.04</v>
       </c>
       <c r="AD158">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE158">
         <v>1.01</v>
       </c>
       <c r="AF158">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AG158">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>1.3</v>
       </c>
       <c r="AK158">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26392,10 +26392,10 @@
         <v>4.75</v>
       </c>
       <c r="O160">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P160">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q160">
         <v>4.8</v>
@@ -26552,10 +26552,10 @@
         </is>
       </c>
       <c r="N161">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="O161">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="P161">
         <v>16</v>
@@ -26570,7 +26570,7 @@
         <v>1.22</v>
       </c>
       <c r="T161">
-        <v>3.94</v>
+        <v>3.8</v>
       </c>
       <c r="U161">
         <v>2.1</v>
@@ -26579,7 +26579,7 @@
         <v>1.68</v>
       </c>
       <c r="W161">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X161">
         <v>1.01</v>
@@ -26591,25 +26591,25 @@
         <v>5.41</v>
       </c>
       <c r="AA161">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AB161">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AC161">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AD161">
         <v>1.65</v>
       </c>
       <c r="AE161">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AF161">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AG161">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26715,25 +26715,25 @@
         </is>
       </c>
       <c r="N162">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="O162">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P162">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Q162">
         <v>2.16</v>
       </c>
       <c r="R162">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="S162">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="T162">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="U162">
         <v>3.3</v>
@@ -26757,7 +26757,7 @@
         <v>2.43</v>
       </c>
       <c r="AB162">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AC162">
         <v>5.5</v>
@@ -26878,13 +26878,13 @@
         </is>
       </c>
       <c r="N163">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="O163">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="P163">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="Q163">
         <v>0</v>
@@ -27050,7 +27050,7 @@
         <v>4.2</v>
       </c>
       <c r="Q164">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="R164">
         <v>2.9</v>
@@ -27062,37 +27062,37 @@
         <v>4.8</v>
       </c>
       <c r="U164">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V164">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="W164">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X164">
         <v>1.01</v>
       </c>
       <c r="Y164">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Z164">
-        <v>8</v>
+        <v>4.33</v>
       </c>
       <c r="AA164">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AB164">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AC164">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AD164">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="AE164">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AF164">
         <v>1.33</v>
@@ -27114,7 +27114,7 @@
         <v>1.2</v>
       </c>
       <c r="AK164">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -27204,25 +27204,25 @@
         </is>
       </c>
       <c r="N165">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="O165">
         <v>3</v>
       </c>
       <c r="P165">
-        <v>4.1</v>
+        <v>4.45</v>
       </c>
       <c r="Q165">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="R165">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="S165">
         <v>1.57</v>
       </c>
       <c r="T165">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="U165">
         <v>3.9</v>
@@ -27530,13 +27530,13 @@
         </is>
       </c>
       <c r="N167">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O167">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="P167">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q167">
         <v>2.75</v>
@@ -27551,7 +27551,7 @@
         <v>2.2</v>
       </c>
       <c r="U167">
-        <v>3.98</v>
+        <v>3.7</v>
       </c>
       <c r="V167">
         <v>1.22</v>
@@ -27572,7 +27572,7 @@
         <v>2.7</v>
       </c>
       <c r="AB167">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AC167">
         <v>5.2</v>
@@ -27600,7 +27600,7 @@
         </is>
       </c>
       <c r="AJ167">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="AK167">
         <v>1.73</v>
@@ -27699,19 +27699,19 @@
         <v>2.95</v>
       </c>
       <c r="P168">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="Q168">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="R168">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="S168">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="T168">
-        <v>2.46</v>
+        <v>2.29</v>
       </c>
       <c r="U168">
         <v>3.38</v>
@@ -27726,10 +27726,10 @@
         <v>1.06</v>
       </c>
       <c r="Y168">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="Z168">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="AA168">
         <v>2.5</v>
@@ -27738,16 +27738,16 @@
         <v>1.53</v>
       </c>
       <c r="AC168">
-        <v>4.72</v>
+        <v>4.44</v>
       </c>
       <c r="AD168">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AE168">
         <v>1.05</v>
       </c>
       <c r="AF168">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG168">
         <v>1.69</v>
@@ -27766,7 +27766,7 @@
         <v>1.33</v>
       </c>
       <c r="AK168">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -27856,10 +27856,10 @@
         </is>
       </c>
       <c r="N169">
-        <v>2.21</v>
+        <v>2.31</v>
       </c>
       <c r="O169">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="P169">
         <v>3.37</v>
@@ -28511,28 +28511,28 @@
         <v>2.65</v>
       </c>
       <c r="O173">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="P173">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="Q173">
-        <v>3.32</v>
+        <v>3.15</v>
       </c>
       <c r="R173">
         <v>2</v>
       </c>
       <c r="S173">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="T173">
-        <v>2.6</v>
+        <v>2.18</v>
       </c>
       <c r="U173">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="V173">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="W173">
         <v>1.06</v>
@@ -28541,31 +28541,31 @@
         <v>1.08</v>
       </c>
       <c r="Y173">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z173">
         <v>2.85</v>
       </c>
       <c r="AA173">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="AB173">
         <v>1.53</v>
       </c>
       <c r="AC173">
-        <v>3.94</v>
+        <v>3.9</v>
       </c>
       <c r="AD173">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE173">
         <v>1.03</v>
       </c>
       <c r="AF173">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AG173">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28578,10 +28578,10 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AK173">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -28671,7 +28671,7 @@
         </is>
       </c>
       <c r="N174">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O174">
         <v>2.7</v>
@@ -28680,10 +28680,10 @@
         <v>2.8</v>
       </c>
       <c r="Q174">
-        <v>3.2</v>
+        <v>3.46</v>
       </c>
       <c r="R174">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="S174">
         <v>1.5</v>
@@ -28704,19 +28704,19 @@
         <v>1.06</v>
       </c>
       <c r="Y174">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Z174">
         <v>2.41</v>
       </c>
       <c r="AA174">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="AB174">
         <v>1.41</v>
       </c>
       <c r="AC174">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AD174">
         <v>1.1</v>
@@ -28741,10 +28741,10 @@
         </is>
       </c>
       <c r="AJ174">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AK174">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -28834,28 +28834,28 @@
         </is>
       </c>
       <c r="N175">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="O175">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P175">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="Q175">
         <v>4.4</v>
       </c>
       <c r="R175">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="S175">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T175">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="U175">
-        <v>2.72</v>
+        <v>2.77</v>
       </c>
       <c r="V175">
         <v>1.36</v>
@@ -28867,28 +28867,28 @@
         <v>1.05</v>
       </c>
       <c r="Y175">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z175">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA175">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB175">
         <v>1.78</v>
       </c>
       <c r="AC175">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AD175">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE175">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF175">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AG175">
         <v>1.91</v>
@@ -29160,13 +29160,13 @@
         </is>
       </c>
       <c r="N177">
-        <v>4.52</v>
+        <v>3.28</v>
       </c>
       <c r="O177">
-        <v>3.92</v>
+        <v>3.31</v>
       </c>
       <c r="P177">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="Q177">
         <v>4.2</v>
@@ -29181,10 +29181,10 @@
         <v>3.2</v>
       </c>
       <c r="U177">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="V177">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W177">
         <v>1.11</v>
@@ -29202,16 +29202,16 @@
         <v>1.65</v>
       </c>
       <c r="AB177">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AC177">
         <v>2.59</v>
       </c>
       <c r="AD177">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AE177">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF177">
         <v>1.6</v>
@@ -29233,7 +29233,7 @@
         <v>1.19</v>
       </c>
       <c r="AK177">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29486,58 +29486,58 @@
         </is>
       </c>
       <c r="N179">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="O179">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P179">
-        <v>3.48</v>
+        <v>3.8</v>
       </c>
       <c r="Q179">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R179">
         <v>2.15</v>
       </c>
       <c r="S179">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T179">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="U179">
-        <v>2.85</v>
+        <v>2.73</v>
       </c>
       <c r="V179">
         <v>1.37</v>
       </c>
       <c r="W179">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X179">
         <v>1.05</v>
       </c>
       <c r="Y179">
+        <v>1.25</v>
+      </c>
+      <c r="Z179">
+        <v>3.5</v>
+      </c>
+      <c r="AA179">
+        <v>1.85</v>
+      </c>
+      <c r="AB179">
+        <v>1.85</v>
+      </c>
+      <c r="AC179">
+        <v>3.1</v>
+      </c>
+      <c r="AD179">
         <v>1.3</v>
       </c>
-      <c r="Z179">
-        <v>3.3</v>
-      </c>
-      <c r="AA179">
-        <v>1.91</v>
-      </c>
-      <c r="AB179">
-        <v>1.8</v>
-      </c>
-      <c r="AC179">
-        <v>3.4</v>
-      </c>
-      <c r="AD179">
-        <v>1.26</v>
-      </c>
       <c r="AE179">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF179">
         <v>1.79</v>
@@ -29559,7 +29559,7 @@
         <v>1.2</v>
       </c>
       <c r="AK179">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29649,13 +29649,13 @@
         </is>
       </c>
       <c r="N180">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="O180">
         <v>3</v>
       </c>
       <c r="P180">
-        <v>2.3</v>
+        <v>2.68</v>
       </c>
       <c r="Q180">
         <v>3.65</v>
@@ -29664,13 +29664,13 @@
         <v>1.88</v>
       </c>
       <c r="S180">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="T180">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="U180">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="V180">
         <v>1.28</v>
@@ -29682,10 +29682,10 @@
         <v>1.07</v>
       </c>
       <c r="Y180">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="Z180">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="AA180">
         <v>2.49</v>
@@ -29706,7 +29706,7 @@
         <v>2</v>
       </c>
       <c r="AG180">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AH180" t="inlineStr">
         <is>
@@ -29719,10 +29719,10 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AK180">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AL180">
         <v>0</v>
@@ -29860,7 +29860,7 @@
         <v>3.3</v>
       </c>
       <c r="AD181">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE181">
         <v>1.08</v>
@@ -29869,7 +29869,7 @@
         <v>1.6</v>
       </c>
       <c r="AG181">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AH181" t="inlineStr">
         <is>
@@ -29882,7 +29882,7 @@
         </is>
       </c>
       <c r="AJ181">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AK181">
         <v>1.44</v>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O4">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P4">
-        <v>2.94</v>
+        <v>2.87</v>
       </c>
       <c r="Q4">
         <v>2.63</v>
@@ -976,13 +976,13 @@
         <v>2.3</v>
       </c>
       <c r="S4">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T4">
         <v>3.24</v>
       </c>
       <c r="U4">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="V4">
         <v>1.44</v>
@@ -2271,7 +2271,7 @@
         <v>4.05</v>
       </c>
       <c r="P12">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="Q12">
         <v>4.5</v>
@@ -2283,7 +2283,7 @@
         <v>1.26</v>
       </c>
       <c r="T12">
-        <v>3.75</v>
+        <v>3.42</v>
       </c>
       <c r="U12">
         <v>2.28</v>
@@ -2310,7 +2310,7 @@
         <v>2.4</v>
       </c>
       <c r="AC12">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AD12">
         <v>1.62</v>
@@ -2338,7 +2338,7 @@
         <v>1.24</v>
       </c>
       <c r="AK12">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2434,7 +2434,7 @@
         <v>3</v>
       </c>
       <c r="P13">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="Q13">
         <v>3.3</v>
@@ -2449,16 +2449,16 @@
         <v>3.4</v>
       </c>
       <c r="U13">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="V13">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W13">
         <v>1.11</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y13">
         <v>1.16</v>
@@ -2473,7 +2473,7 @@
         <v>2.15</v>
       </c>
       <c r="AC13">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="AD13">
         <v>1.56</v>
@@ -2482,7 +2482,7 @@
         <v>1.18</v>
       </c>
       <c r="AF13">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG13">
         <v>2.4</v>
@@ -3083,7 +3083,7 @@
         <v>2.15</v>
       </c>
       <c r="O17">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="P17">
         <v>2.8</v>
@@ -3104,7 +3104,7 @@
         <v>2.4</v>
       </c>
       <c r="V17">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W17">
         <v>1.11</v>
@@ -3137,7 +3137,7 @@
         <v>1.53</v>
       </c>
       <c r="AG17">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>1.81</v>
       </c>
       <c r="O18">
-        <v>3.75</v>
+        <v>3.54</v>
       </c>
       <c r="P18">
         <v>3.46</v>
@@ -3270,28 +3270,28 @@
         <v>1.52</v>
       </c>
       <c r="W18">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
         <v>1.2</v>
       </c>
       <c r="Z18">
-        <v>4.3</v>
+        <v>4.35</v>
       </c>
       <c r="AA18">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AB18">
         <v>2.14</v>
       </c>
       <c r="AC18">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AD18">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AE18">
         <v>1.2</v>
@@ -3300,7 +3300,7 @@
         <v>1.55</v>
       </c>
       <c r="AG18">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>1.25</v>
       </c>
       <c r="AK18">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3457,10 +3457,10 @@
         <v>1.55</v>
       </c>
       <c r="AE19">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF19">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AG19">
         <v>2.5</v>
@@ -3901,7 +3901,7 @@
         <v>3.4</v>
       </c>
       <c r="P22">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>2.97</v>
       </c>
       <c r="U29">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="V29">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W29">
         <v>1.07</v>
@@ -5072,13 +5072,13 @@
         <v>1.26</v>
       </c>
       <c r="Z29">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA29">
         <v>1.94</v>
       </c>
       <c r="AB29">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AC29">
         <v>3.3</v>
@@ -5090,10 +5090,10 @@
         <v>1.1</v>
       </c>
       <c r="AF29">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG29">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>1.29</v>
       </c>
       <c r="AF33">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG33">
         <v>2.3</v>
@@ -5761,7 +5761,7 @@
         <v>1.2</v>
       </c>
       <c r="AK33">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5896,7 +5896,7 @@
         <v>1.94</v>
       </c>
       <c r="AC34">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AD34">
         <v>1.33</v>
@@ -6023,19 +6023,19 @@
         <v>2.87</v>
       </c>
       <c r="Q35">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="R35">
         <v>2.1</v>
       </c>
       <c r="S35">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T35">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="U35">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="V35">
         <v>1.35</v>
@@ -6047,13 +6047,13 @@
         <v>1.06</v>
       </c>
       <c r="Y35">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z35">
-        <v>3.32</v>
+        <v>3.08</v>
       </c>
       <c r="AA35">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AB35">
         <v>1.81</v>
@@ -6068,7 +6068,7 @@
         <v>1.05</v>
       </c>
       <c r="AF35">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG35">
         <v>2</v>
@@ -6192,7 +6192,7 @@
         <v>2.34</v>
       </c>
       <c r="S36">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T36">
         <v>3.02</v>
@@ -6216,7 +6216,7 @@
         <v>3.34</v>
       </c>
       <c r="AA36">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AB36">
         <v>1.9</v>
@@ -6234,7 +6234,7 @@
         <v>1.9</v>
       </c>
       <c r="AG36">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -7810,22 +7810,22 @@
         <v>1.67</v>
       </c>
       <c r="O46">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P46">
         <v>5</v>
       </c>
       <c r="Q46">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R46">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="S46">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T46">
-        <v>3.01</v>
+        <v>2.8</v>
       </c>
       <c r="U46">
         <v>2.73</v>
@@ -7840,10 +7840,10 @@
         <v>1.05</v>
       </c>
       <c r="Y46">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z46">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="AA46">
         <v>1.95</v>
@@ -7970,34 +7970,34 @@
         </is>
       </c>
       <c r="N47">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O47">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P47">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Q47">
-        <v>4.31</v>
+        <v>4.23</v>
       </c>
       <c r="R47">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="S47">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T47">
         <v>3.3</v>
       </c>
       <c r="U47">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="V47">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W47">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X47">
         <v>1.02</v>
@@ -8006,7 +8006,7 @@
         <v>1.22</v>
       </c>
       <c r="Z47">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AA47">
         <v>1.62</v>
@@ -8018,16 +8018,16 @@
         <v>2.44</v>
       </c>
       <c r="AD47">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE47">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF47">
         <v>1.6</v>
       </c>
       <c r="AG47">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.86</v>
+        <v>3.12</v>
       </c>
       <c r="O57">
-        <v>3.37</v>
+        <v>3.66</v>
       </c>
       <c r="P57">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -11233,7 +11233,7 @@
         <v>3</v>
       </c>
       <c r="O67">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="P67">
         <v>2.25</v>
@@ -11245,7 +11245,7 @@
         <v>2.4</v>
       </c>
       <c r="S67">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T67">
         <v>3.66</v>
@@ -11260,13 +11260,13 @@
         <v>1.18</v>
       </c>
       <c r="X67">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y67">
         <v>1.14</v>
       </c>
       <c r="Z67">
-        <v>5.4</v>
+        <v>5.48</v>
       </c>
       <c r="AA67">
         <v>1.49</v>
@@ -11278,7 +11278,7 @@
         <v>2.15</v>
       </c>
       <c r="AD67">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AE67">
         <v>1.25</v>
@@ -11396,7 +11396,7 @@
         <v>2.34</v>
       </c>
       <c r="O68">
-        <v>3.62</v>
+        <v>3.35</v>
       </c>
       <c r="P68">
         <v>2.45</v>
@@ -11426,7 +11426,7 @@
         <v>1.03</v>
       </c>
       <c r="Y68">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z68">
         <v>4.65</v>
@@ -11444,10 +11444,10 @@
         <v>1.5</v>
       </c>
       <c r="AE68">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF68">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AG68">
         <v>2.46</v>
@@ -14170,7 +14170,7 @@
         <v>3.5</v>
       </c>
       <c r="P85">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="Q85">
         <v>2.38</v>
@@ -14182,13 +14182,13 @@
         <v>1.32</v>
       </c>
       <c r="T85">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="U85">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="V85">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W85">
         <v>1.09</v>
@@ -14237,7 +14237,7 @@
         <v>1.22</v>
       </c>
       <c r="AK85">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14828,7 +14828,7 @@
         <v>2.05</v>
       </c>
       <c r="R89">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="S89">
         <v>1.28</v>
@@ -14840,7 +14840,7 @@
         <v>2.25</v>
       </c>
       <c r="V89">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="W89">
         <v>1.08</v>
@@ -14852,7 +14852,7 @@
         <v>1.18</v>
       </c>
       <c r="Z89">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA89">
         <v>1.62</v>
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="O91">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="P91">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q91">
         <v>3.3</v>
@@ -15169,7 +15169,7 @@
         <v>1.29</v>
       </c>
       <c r="W91">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X91">
         <v>1.05</v>
@@ -15199,7 +15199,7 @@
         <v>1.95</v>
       </c>
       <c r="AG91">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -16283,31 +16283,31 @@
         </is>
       </c>
       <c r="N98">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O98">
         <v>3.25</v>
       </c>
       <c r="P98">
-        <v>2.05</v>
+        <v>2.27</v>
       </c>
       <c r="Q98">
-        <v>4.1</v>
+        <v>4.17</v>
       </c>
       <c r="R98">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="S98">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T98">
-        <v>2.79</v>
+        <v>2.57</v>
       </c>
       <c r="U98">
         <v>3</v>
       </c>
       <c r="V98">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W98">
         <v>1.07</v>
@@ -16316,22 +16316,22 @@
         <v>1.06</v>
       </c>
       <c r="Y98">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z98">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AA98">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AB98">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AC98">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AD98">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE98">
         <v>1.07</v>
@@ -16340,7 +16340,7 @@
         <v>1.83</v>
       </c>
       <c r="AG98">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>1.65</v>
       </c>
       <c r="AK98">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16778,7 +16778,7 @@
         <v>2.85</v>
       </c>
       <c r="P101">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="Q101">
         <v>3.3</v>
@@ -16811,10 +16811,10 @@
         <v>2.41</v>
       </c>
       <c r="AA101">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="AB101">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AC101">
         <v>4.84</v>
@@ -17587,7 +17587,7 @@
         </is>
       </c>
       <c r="N106">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="O106">
         <v>3.27</v>
@@ -17596,13 +17596,13 @@
         <v>1.62</v>
       </c>
       <c r="Q106">
-        <v>5.23</v>
+        <v>5.05</v>
       </c>
       <c r="R106">
         <v>2.15</v>
       </c>
       <c r="S106">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T106">
         <v>2.77</v>
@@ -17629,7 +17629,7 @@
         <v>2</v>
       </c>
       <c r="AB106">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AC106">
         <v>3.14</v>
@@ -17644,7 +17644,7 @@
         <v>1.85</v>
       </c>
       <c r="AG106">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AK106">
         <v>1.18</v>
@@ -17913,13 +17913,13 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="O108">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="P108">
-        <v>7.5</v>
+        <v>7.25</v>
       </c>
       <c r="Q108">
         <v>1.93</v>
@@ -17937,34 +17937,34 @@
         <v>2.66</v>
       </c>
       <c r="V108">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W108">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X108">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y108">
         <v>1.25</v>
       </c>
       <c r="Z108">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AA108">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AB108">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AC108">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="AD108">
         <v>1.31</v>
       </c>
       <c r="AE108">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF108">
         <v>2.1</v>
@@ -17983,7 +17983,7 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="AK108">
         <v>2.68</v>
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="O112">
-        <v>3.82</v>
+        <v>3.38</v>
       </c>
       <c r="P112">
-        <v>4.72</v>
+        <v>4.2</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="O116">
         <v>6.5</v>
       </c>
       <c r="P116">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="Q116">
         <v>1.55</v>
@@ -19235,7 +19235,7 @@
         <v>1.23</v>
       </c>
       <c r="T116">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="U116">
         <v>2.29</v>
@@ -19250,13 +19250,13 @@
         <v>1.03</v>
       </c>
       <c r="Y116">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z116">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AA116">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AB116">
         <v>2.35</v>
@@ -19271,10 +19271,10 @@
         <v>1.18</v>
       </c>
       <c r="AF116">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="AG116">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19290,7 +19290,7 @@
         <v>1.02</v>
       </c>
       <c r="AK116">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
+        <v>3.55</v>
+      </c>
+      <c r="O122">
+        <v>3.2</v>
+      </c>
+      <c r="P122">
+        <v>1.91</v>
+      </c>
+      <c r="Q122">
+        <v>4.2</v>
+      </c>
+      <c r="R122">
+        <v>2.1</v>
+      </c>
+      <c r="S122">
+        <v>1.41</v>
+      </c>
+      <c r="T122">
+        <v>2.65</v>
+      </c>
+      <c r="U122">
+        <v>3</v>
+      </c>
+      <c r="V122">
         <v>1.35</v>
       </c>
-      <c r="O122">
-        <v>4.45</v>
-      </c>
-      <c r="P122">
-        <v>7.55</v>
-      </c>
-      <c r="Q122">
-        <v>1.83</v>
-      </c>
-      <c r="R122">
-        <v>2.34</v>
-      </c>
-      <c r="S122">
-        <v>1.33</v>
-      </c>
-      <c r="T122">
-        <v>3.02</v>
-      </c>
-      <c r="U122">
-        <v>2.54</v>
-      </c>
-      <c r="V122">
-        <v>1.46</v>
-      </c>
       <c r="W122">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X122">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y122">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="Z122">
-        <v>3.94</v>
+        <v>2.93</v>
       </c>
       <c r="AA122">
-        <v>1.67</v>
+        <v>2.03</v>
       </c>
       <c r="AB122">
-        <v>2.08</v>
+        <v>1.7</v>
       </c>
       <c r="AC122">
-        <v>2.59</v>
+        <v>3.5</v>
       </c>
       <c r="AD122">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AE122">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AF122">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="AG122">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.13</v>
+        <v>1.75</v>
       </c>
       <c r="AK122">
-        <v>2.89</v>
+        <v>1.18</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>3.55</v>
+        <v>1.35</v>
       </c>
       <c r="O123">
-        <v>3.2</v>
+        <v>4.45</v>
       </c>
       <c r="P123">
-        <v>1.91</v>
+        <v>7.55</v>
       </c>
       <c r="Q123">
-        <v>4.2</v>
+        <v>1.83</v>
       </c>
       <c r="R123">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="S123">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="T123">
-        <v>2.65</v>
+        <v>3.02</v>
       </c>
       <c r="U123">
-        <v>3</v>
+        <v>2.54</v>
       </c>
       <c r="V123">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="W123">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X123">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y123">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="Z123">
-        <v>2.93</v>
+        <v>3.94</v>
       </c>
       <c r="AA123">
-        <v>2.03</v>
+        <v>1.67</v>
       </c>
       <c r="AB123">
-        <v>1.7</v>
+        <v>2.08</v>
       </c>
       <c r="AC123">
-        <v>3.5</v>
+        <v>2.59</v>
       </c>
       <c r="AD123">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AE123">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AF123">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AG123">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.75</v>
+        <v>1.13</v>
       </c>
       <c r="AK123">
-        <v>1.18</v>
+        <v>2.89</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -22640,7 +22640,7 @@
         </is>
       </c>
       <c r="N137">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O137">
         <v>3.1</v>
@@ -22694,7 +22694,7 @@
         <v>1.1</v>
       </c>
       <c r="AF137">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG137">
         <v>2</v>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK137">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22809,22 +22809,22 @@
         <v>4</v>
       </c>
       <c r="P138">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="Q138">
         <v>6</v>
       </c>
       <c r="R138">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="S138">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T138">
-        <v>2.77</v>
+        <v>2.99</v>
       </c>
       <c r="U138">
-        <v>2.79</v>
+        <v>2.62</v>
       </c>
       <c r="V138">
         <v>1.41</v>
@@ -22833,7 +22833,7 @@
         <v>1.06</v>
       </c>
       <c r="X138">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y138">
         <v>1.24</v>
@@ -23129,13 +23129,13 @@
         </is>
       </c>
       <c r="N140">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O140">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P140">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q140">
         <v>0</v>
@@ -23491,13 +23491,13 @@
         <v>1.33</v>
       </c>
       <c r="Z142">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AA142">
         <v>2.05</v>
       </c>
       <c r="AB142">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AC142">
         <v>3.76</v>
@@ -23512,7 +23512,7 @@
         <v>1.95</v>
       </c>
       <c r="AG142">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23525,7 +23525,7 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK142">
         <v>2.1</v>
@@ -23790,22 +23790,22 @@
         <v>0</v>
       </c>
       <c r="Q144">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="R144">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="S144">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="T144">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="U144">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="V144">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W144">
         <v>1.06</v>
@@ -23814,31 +23814,31 @@
         <v>1.02</v>
       </c>
       <c r="Y144">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z144">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AA144">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AB144">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AC144">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="AD144">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AE144">
         <v>1.06</v>
       </c>
       <c r="AF144">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="AG144">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AK144">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23944,16 +23944,16 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="O145">
-        <v>4</v>
+        <v>3.78</v>
       </c>
       <c r="P145">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="Q145">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="R145">
         <v>2.2</v>
@@ -23962,7 +23962,7 @@
         <v>1.37</v>
       </c>
       <c r="T145">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="U145">
         <v>2.88</v>
@@ -23971,37 +23971,37 @@
         <v>1.36</v>
       </c>
       <c r="W145">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X145">
         <v>1.03</v>
       </c>
       <c r="Y145">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z145">
-        <v>3.45</v>
+        <v>3.48</v>
       </c>
       <c r="AA145">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB145">
         <v>1.84</v>
       </c>
       <c r="AC145">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AD145">
         <v>1.3</v>
       </c>
       <c r="AE145">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF145">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG145">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24017,7 +24017,7 @@
         <v>1.25</v>
       </c>
       <c r="AK145">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24110,10 +24110,10 @@
         <v>1.9</v>
       </c>
       <c r="O146">
-        <v>3.42</v>
+        <v>3.54</v>
       </c>
       <c r="P146">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="Q146">
         <v>2.49</v>
@@ -24146,7 +24146,7 @@
         <v>3.38</v>
       </c>
       <c r="AA146">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AB146">
         <v>1.94</v>
@@ -24155,10 +24155,10 @@
         <v>2.94</v>
       </c>
       <c r="AD146">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AE146">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF146">
         <v>1.7</v>
@@ -26226,13 +26226,13 @@
         </is>
       </c>
       <c r="N159">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="O159">
-        <v>3.28</v>
+        <v>3.52</v>
       </c>
       <c r="P159">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="Q159">
         <v>2.3</v>
@@ -26280,10 +26280,10 @@
         <v>1.08</v>
       </c>
       <c r="AF159">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG159">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26428,13 +26428,13 @@
         <v>3.35</v>
       </c>
       <c r="AA160">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AB160">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AC160">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="AD160">
         <v>1.27</v>
@@ -26443,10 +26443,10 @@
         <v>1.06</v>
       </c>
       <c r="AF160">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG160">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26459,7 +26459,7 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AK160">
         <v>1.18</v>
@@ -26552,10 +26552,10 @@
         </is>
       </c>
       <c r="N161">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="O161">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="P161">
         <v>16</v>
@@ -26585,7 +26585,7 @@
         <v>1.01</v>
       </c>
       <c r="Y161">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z161">
         <v>5.41</v>
@@ -26609,7 +26609,7 @@
         <v>2.55</v>
       </c>
       <c r="AG161">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -27373,7 +27373,7 @@
         <v>3.65</v>
       </c>
       <c r="P166">
-        <v>3.5</v>
+        <v>3.17</v>
       </c>
       <c r="Q166">
         <v>2.3</v>
@@ -27394,7 +27394,7 @@
         <v>1.5</v>
       </c>
       <c r="W166">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X166">
         <v>1</v>
@@ -27409,7 +27409,7 @@
         <v>1.75</v>
       </c>
       <c r="AB166">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="AC166">
         <v>2.65</v>
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,64 +28182,64 @@
         </is>
       </c>
       <c r="N171">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="O171">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="P171">
-        <v>3.4</v>
+        <v>3.02</v>
       </c>
       <c r="Q171">
+        <v>2.75</v>
+      </c>
+      <c r="R171">
+        <v>1.96</v>
+      </c>
+      <c r="S171">
+        <v>1.4</v>
+      </c>
+      <c r="T171">
         <v>2.62</v>
       </c>
-      <c r="R171">
-        <v>2.1</v>
-      </c>
-      <c r="S171">
-        <v>1.44</v>
-      </c>
-      <c r="T171">
-        <v>2.7</v>
-      </c>
       <c r="U171">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="V171">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W171">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X171">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y171">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="Z171">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AA171">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AB171">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AC171">
-        <v>3.54</v>
+        <v>4.2</v>
       </c>
       <c r="AD171">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE171">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF171">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AG171">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH171" t="inlineStr">
         <is>
@@ -28252,10 +28252,10 @@
         </is>
       </c>
       <c r="AJ171">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AK171">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AL171">
         <v>0</v>
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,64 +28345,64 @@
         </is>
       </c>
       <c r="N172">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="O172">
         <v>3.3</v>
       </c>
       <c r="P172">
-        <v>3.35</v>
+        <v>3.54</v>
       </c>
       <c r="Q172">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="R172">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="S172">
         <v>1.4</v>
       </c>
       <c r="T172">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="U172">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="V172">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W172">
         <v>1.05</v>
       </c>
       <c r="X172">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y172">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="Z172">
-        <v>2.95</v>
+        <v>3.22</v>
       </c>
       <c r="AA172">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="AB172">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AC172">
-        <v>4.2</v>
+        <v>3.54</v>
       </c>
       <c r="AD172">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE172">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF172">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AG172">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28415,10 +28415,10 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AK172">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28997,10 +28997,10 @@
         </is>
       </c>
       <c r="N176">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="O176">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="P176">
         <v>10</v>
@@ -29012,10 +29012,10 @@
         <v>2.63</v>
       </c>
       <c r="S176">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T176">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U176">
         <v>2.37</v>
@@ -29033,7 +29033,7 @@
         <v>1.15</v>
       </c>
       <c r="Z176">
-        <v>4.5</v>
+        <v>4.67</v>
       </c>
       <c r="AA176">
         <v>1.63</v>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="O56">
-        <v>2.73</v>
+        <v>2.86</v>
       </c>
       <c r="P56">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="Q56">
         <v>3.8</v>
@@ -9458,7 +9458,7 @@
         <v>2.4</v>
       </c>
       <c r="U56">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="V56">
         <v>1.22</v>
@@ -9473,7 +9473,7 @@
         <v>1.5</v>
       </c>
       <c r="Z56">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="AA56">
         <v>2.55</v>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AK56">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -14985,7 +14985,7 @@
         <v>3.4</v>
       </c>
       <c r="P90">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="Q90">
         <v>2.87</v>
@@ -14997,13 +14997,13 @@
         <v>1.33</v>
       </c>
       <c r="T90">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="U90">
         <v>2.59</v>
       </c>
       <c r="V90">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W90">
         <v>1.05</v>
@@ -15018,19 +15018,19 @@
         <v>3.8</v>
       </c>
       <c r="AA90">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AB90">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AC90">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="AD90">
         <v>1.35</v>
       </c>
       <c r="AE90">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF90">
         <v>1.6</v>
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AK90">
         <v>1.52</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G94">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="G95">
@@ -17753,16 +17753,16 @@
         <v>2.2</v>
       </c>
       <c r="O107">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P107">
         <v>2.95</v>
       </c>
       <c r="Q107">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="R107">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="S107">
         <v>1.43</v>
@@ -17771,10 +17771,10 @@
         <v>2.53</v>
       </c>
       <c r="U107">
-        <v>3.02</v>
+        <v>2.95</v>
       </c>
       <c r="V107">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W107">
         <v>1.05</v>
@@ -17798,7 +17798,7 @@
         <v>3.9</v>
       </c>
       <c r="AD107">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE107">
         <v>1.06</v>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK107">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -18402,10 +18402,10 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="O111">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P111">
         <v>2.61</v>
@@ -18417,34 +18417,34 @@
         <v>2.1</v>
       </c>
       <c r="S111">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T111">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="U111">
         <v>2.56</v>
       </c>
       <c r="V111">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W111">
         <v>1.06</v>
       </c>
       <c r="X111">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z111">
-        <v>3.66</v>
+        <v>3.5</v>
       </c>
       <c r="AA111">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AB111">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AC111">
         <v>3.2</v>
@@ -18453,7 +18453,7 @@
         <v>1.3</v>
       </c>
       <c r="AE111">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF111">
         <v>1.67</v>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AK111">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18734,58 +18734,58 @@
         <v>2.87</v>
       </c>
       <c r="P113">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q113">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="R113">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="S113">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="T113">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="U113">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="V113">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W113">
         <v>1.01</v>
       </c>
       <c r="X113">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Y113">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="Z113">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AA113">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AB113">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AC113">
-        <v>6</v>
+        <v>5.15</v>
       </c>
       <c r="AD113">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AE113">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF113">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AG113">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>1.4</v>
       </c>
       <c r="AK113">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -19706,25 +19706,25 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="O119">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="P119">
         <v>2.8</v>
       </c>
       <c r="Q119">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="R119">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="S119">
         <v>1.69</v>
       </c>
       <c r="T119">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="U119">
         <v>4.6</v>
@@ -19736,16 +19736,16 @@
         <v>1.02</v>
       </c>
       <c r="X119">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Y119">
         <v>1.78</v>
       </c>
       <c r="Z119">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AA119">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AB119">
         <v>1.32</v>
@@ -19754,7 +19754,7 @@
         <v>6</v>
       </c>
       <c r="AD119">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AE119">
         <v>1.02</v>
@@ -19763,7 +19763,7 @@
         <v>2.5</v>
       </c>
       <c r="AG119">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK119">
         <v>1.44</v>
@@ -20204,7 +20204,7 @@
         <v>1.91</v>
       </c>
       <c r="Q122">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="R122">
         <v>2.1</v>
@@ -20367,19 +20367,19 @@
         <v>7.55</v>
       </c>
       <c r="Q123">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R123">
         <v>2.34</v>
       </c>
       <c r="S123">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T123">
         <v>3.02</v>
       </c>
       <c r="U123">
-        <v>2.54</v>
+        <v>2.09</v>
       </c>
       <c r="V123">
         <v>1.46</v>
@@ -20388,34 +20388,34 @@
         <v>1.08</v>
       </c>
       <c r="X123">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y123">
         <v>1.17</v>
       </c>
       <c r="Z123">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="AA123">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AB123">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AC123">
         <v>2.59</v>
       </c>
       <c r="AD123">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE123">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF123">
         <v>1.95</v>
       </c>
       <c r="AG123">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>1.13</v>
       </c>
       <c r="AK123">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20521,34 +20521,34 @@
         </is>
       </c>
       <c r="N124">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="O124">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P124">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Q124">
         <v>2.05</v>
       </c>
       <c r="R124">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="S124">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="T124">
         <v>2.26</v>
       </c>
       <c r="U124">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="V124">
         <v>1.21</v>
       </c>
       <c r="W124">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X124">
         <v>1.05</v>
@@ -20557,16 +20557,16 @@
         <v>1.53</v>
       </c>
       <c r="Z124">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="AA124">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="AB124">
         <v>1.52</v>
       </c>
       <c r="AC124">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="AD124">
         <v>1.17</v>
@@ -20575,7 +20575,7 @@
         <v>1.04</v>
       </c>
       <c r="AF124">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AG124">
         <v>1.44</v>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK124">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20684,10 +20684,10 @@
         </is>
       </c>
       <c r="N125">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="O125">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="P125">
         <v>3.9</v>
@@ -20699,7 +20699,7 @@
         <v>1.69</v>
       </c>
       <c r="S125">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="T125">
         <v>1.97</v>
@@ -20714,25 +20714,25 @@
         <v>1.03</v>
       </c>
       <c r="X125">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Y125">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="Z125">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AA125">
         <v>3.14</v>
       </c>
       <c r="AB125">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AC125">
         <v>5.75</v>
       </c>
       <c r="AD125">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AE125">
         <v>1.02</v>
@@ -20741,7 +20741,7 @@
         <v>2.5</v>
       </c>
       <c r="AG125">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -22966,13 +22966,13 @@
         </is>
       </c>
       <c r="N139">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="O139">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P139">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="Q139">
         <v>2.1</v>
@@ -22984,19 +22984,19 @@
         <v>1.51</v>
       </c>
       <c r="T139">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="U139">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
       <c r="V139">
         <v>1.24</v>
       </c>
       <c r="W139">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X139">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Y139">
         <v>1.42</v>
@@ -23005,13 +23005,13 @@
         <v>2.55</v>
       </c>
       <c r="AA139">
-        <v>2.2</v>
+        <v>2.41</v>
       </c>
       <c r="AB139">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AC139">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="AD139">
         <v>1.13</v>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AK139">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23618,13 +23618,13 @@
         </is>
       </c>
       <c r="N143">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O143">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P143">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -23657,10 +23657,10 @@
         <v>0</v>
       </c>
       <c r="AA143">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AB143">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AC143">
         <v>0</v>
@@ -24922,7 +24922,7 @@
         </is>
       </c>
       <c r="N151">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="O151">
         <v>2.55</v>
@@ -24931,13 +24931,13 @@
         <v>2.85</v>
       </c>
       <c r="Q151">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R151">
         <v>1.81</v>
       </c>
       <c r="S151">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T151">
         <v>2.31</v>
@@ -24964,16 +24964,16 @@
         <v>2.2</v>
       </c>
       <c r="AB151">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AC151">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="AD151">
         <v>1.2</v>
       </c>
       <c r="AE151">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF151">
         <v>1.91</v>
@@ -25094,7 +25094,7 @@
         <v>2.68</v>
       </c>
       <c r="Q152">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="R152">
         <v>2.16</v>
@@ -25112,7 +25112,7 @@
         <v>1.5</v>
       </c>
       <c r="W152">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X152">
         <v>1.04</v>
@@ -25133,13 +25133,13 @@
         <v>2.78</v>
       </c>
       <c r="AD152">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE152">
         <v>1.15</v>
       </c>
       <c r="AF152">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG152">
         <v>2.25</v>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AK152">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25251,7 +25251,7 @@
         <v>2.05</v>
       </c>
       <c r="O153">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="P153">
         <v>3.9</v>
@@ -25411,31 +25411,31 @@
         </is>
       </c>
       <c r="N154">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="O154">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="P154">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q154">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="R154">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="S154">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="T154">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="U154">
-        <v>3.85</v>
+        <v>3.98</v>
       </c>
       <c r="V154">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="W154">
         <v>1.03</v>
@@ -25447,13 +25447,13 @@
         <v>1.64</v>
       </c>
       <c r="Z154">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AA154">
         <v>2.88</v>
       </c>
       <c r="AB154">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AC154">
         <v>6.45</v>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AK154">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25586,13 +25586,13 @@
         <v>1.85</v>
       </c>
       <c r="R155">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="S155">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T155">
-        <v>3.25</v>
+        <v>3.36</v>
       </c>
       <c r="U155">
         <v>2.44</v>
@@ -25601,22 +25601,22 @@
         <v>1.53</v>
       </c>
       <c r="W155">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X155">
         <v>1.03</v>
       </c>
       <c r="Y155">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z155">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="AA155">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB155">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AC155">
         <v>2.6</v>
@@ -25625,13 +25625,13 @@
         <v>1.48</v>
       </c>
       <c r="AE155">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AF155">
         <v>1.85</v>
       </c>
       <c r="AG155">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25737,13 +25737,13 @@
         </is>
       </c>
       <c r="N156">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="O156">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="P156">
-        <v>2.61</v>
+        <v>2.8</v>
       </c>
       <c r="Q156">
         <v>3</v>
@@ -25752,19 +25752,19 @@
         <v>2.05</v>
       </c>
       <c r="S156">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T156">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U156">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="V156">
         <v>1.36</v>
       </c>
       <c r="W156">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X156">
         <v>1</v>
@@ -25782,10 +25782,10 @@
         <v>1.76</v>
       </c>
       <c r="AC156">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AD156">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE156">
         <v>1.07</v>
@@ -25794,7 +25794,7 @@
         <v>1.73</v>
       </c>
       <c r="AG156">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25903,22 +25903,22 @@
         <v>1.97</v>
       </c>
       <c r="O157">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="P157">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="Q157">
         <v>2.5</v>
       </c>
       <c r="R157">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="S157">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="T157">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="U157">
         <v>3.6</v>
@@ -25927,19 +25927,19 @@
         <v>1.25</v>
       </c>
       <c r="W157">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X157">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y157">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Z157">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="AA157">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="AB157">
         <v>1.49</v>
@@ -25951,10 +25951,10 @@
         <v>1.17</v>
       </c>
       <c r="AE157">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF157">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AG157">
         <v>1.67</v>
@@ -25970,7 +25970,7 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK157">
         <v>1.73</v>
@@ -26069,7 +26069,7 @@
         <v>3.25</v>
       </c>
       <c r="P158">
-        <v>5.25</v>
+        <v>5.95</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -26078,7 +26078,7 @@
         <v>1.92</v>
       </c>
       <c r="S158">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="T158">
         <v>2.4</v>
@@ -26093,7 +26093,7 @@
         <v>1.02</v>
       </c>
       <c r="X158">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y158">
         <v>1.53</v>
@@ -26108,10 +26108,10 @@
         <v>1.44</v>
       </c>
       <c r="AC158">
-        <v>5.04</v>
+        <v>5</v>
       </c>
       <c r="AD158">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AE158">
         <v>1.01</v>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AK158">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26715,13 +26715,13 @@
         </is>
       </c>
       <c r="N162">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="O162">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P162">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="Q162">
         <v>2.16</v>
@@ -26745,34 +26745,34 @@
         <v>1.05</v>
       </c>
       <c r="X162">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y162">
+        <v>1.49</v>
+      </c>
+      <c r="Z162">
+        <v>2.45</v>
+      </c>
+      <c r="AA162">
+        <v>2.41</v>
+      </c>
+      <c r="AB162">
         <v>1.45</v>
       </c>
-      <c r="Z162">
-        <v>2.48</v>
-      </c>
-      <c r="AA162">
-        <v>2.43</v>
-      </c>
-      <c r="AB162">
-        <v>1.44</v>
-      </c>
       <c r="AC162">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="AD162">
         <v>1.15</v>
       </c>
       <c r="AE162">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF162">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AG162">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26785,10 +26785,10 @@
         </is>
       </c>
       <c r="AJ162">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK162">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -26878,13 +26878,13 @@
         </is>
       </c>
       <c r="N163">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O163">
         <v>3.33</v>
       </c>
       <c r="P163">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q163">
         <v>0</v>
@@ -27207,22 +27207,22 @@
         <v>1.91</v>
       </c>
       <c r="O165">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="P165">
         <v>4.45</v>
       </c>
       <c r="Q165">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="R165">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="S165">
         <v>1.57</v>
       </c>
       <c r="T165">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="U165">
         <v>3.9</v>
@@ -27240,7 +27240,7 @@
         <v>1.6</v>
       </c>
       <c r="Z165">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AA165">
         <v>3.1</v>
@@ -27530,28 +27530,28 @@
         </is>
       </c>
       <c r="N167">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="O167">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="P167">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q167">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R167">
         <v>1.85</v>
       </c>
       <c r="S167">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="T167">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="U167">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="V167">
         <v>1.22</v>
@@ -27569,7 +27569,7 @@
         <v>2.12</v>
       </c>
       <c r="AA167">
-        <v>2.7</v>
+        <v>3.08</v>
       </c>
       <c r="AB167">
         <v>1.36</v>
@@ -27600,7 +27600,7 @@
         </is>
       </c>
       <c r="AJ167">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AK167">
         <v>1.73</v>
@@ -27702,10 +27702,10 @@
         <v>2.87</v>
       </c>
       <c r="Q168">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="R168">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="S168">
         <v>1.52</v>
@@ -27726,31 +27726,31 @@
         <v>1.06</v>
       </c>
       <c r="Y168">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="Z168">
-        <v>2.49</v>
+        <v>2.63</v>
       </c>
       <c r="AA168">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AB168">
         <v>1.53</v>
       </c>
       <c r="AC168">
-        <v>4.44</v>
+        <v>4.1</v>
       </c>
       <c r="AD168">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AE168">
         <v>1.05</v>
       </c>
       <c r="AF168">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG168">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
@@ -27766,7 +27766,7 @@
         <v>1.33</v>
       </c>
       <c r="AK168">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -27859,10 +27859,10 @@
         <v>2.31</v>
       </c>
       <c r="O169">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="P169">
-        <v>3.37</v>
+        <v>3.27</v>
       </c>
       <c r="Q169">
         <v>0</v>
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,64 +28182,64 @@
         </is>
       </c>
       <c r="N171">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="O171">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="P171">
-        <v>3.02</v>
+        <v>3.54</v>
       </c>
       <c r="Q171">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="R171">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="S171">
         <v>1.4</v>
       </c>
       <c r="T171">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="U171">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="V171">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W171">
         <v>1.05</v>
       </c>
       <c r="X171">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y171">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="Z171">
-        <v>2.8</v>
+        <v>3.22</v>
       </c>
       <c r="AA171">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AB171">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AC171">
-        <v>4.2</v>
+        <v>3.54</v>
       </c>
       <c r="AD171">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE171">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF171">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AG171">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH171" t="inlineStr">
         <is>
@@ -28252,10 +28252,10 @@
         </is>
       </c>
       <c r="AJ171">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AK171">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AL171">
         <v>0</v>
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,64 +28345,64 @@
         </is>
       </c>
       <c r="N172">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="O172">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="P172">
-        <v>3.54</v>
+        <v>3.02</v>
       </c>
       <c r="Q172">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="R172">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="S172">
         <v>1.4</v>
       </c>
       <c r="T172">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="U172">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="V172">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W172">
         <v>1.05</v>
       </c>
       <c r="X172">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y172">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="Z172">
-        <v>3.22</v>
+        <v>2.8</v>
       </c>
       <c r="AA172">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AB172">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AC172">
-        <v>3.54</v>
+        <v>4.2</v>
       </c>
       <c r="AD172">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE172">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF172">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AG172">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28415,10 +28415,10 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AK172">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -29160,19 +29160,19 @@
         </is>
       </c>
       <c r="N177">
-        <v>3.28</v>
+        <v>3.75</v>
       </c>
       <c r="O177">
-        <v>3.31</v>
+        <v>3.65</v>
       </c>
       <c r="P177">
         <v>1.76</v>
       </c>
       <c r="Q177">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="R177">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="S177">
         <v>1.27</v>
@@ -29181,10 +29181,10 @@
         <v>3.2</v>
       </c>
       <c r="U177">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="V177">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="W177">
         <v>1.11</v>
@@ -29196,28 +29196,28 @@
         <v>1.17</v>
       </c>
       <c r="Z177">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="AA177">
         <v>1.65</v>
       </c>
       <c r="AB177">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AC177">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="AD177">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AE177">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF177">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="AG177">
-        <v>2.11</v>
+        <v>2.38</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29233,7 +29233,7 @@
         <v>1.19</v>
       </c>
       <c r="AK177">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29649,19 +29649,19 @@
         </is>
       </c>
       <c r="N180">
-        <v>2.91</v>
+        <v>2.7</v>
       </c>
       <c r="O180">
         <v>3</v>
       </c>
       <c r="P180">
-        <v>2.68</v>
+        <v>2.2</v>
       </c>
       <c r="Q180">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="R180">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="S180">
         <v>1.53</v>
@@ -29673,7 +29673,7 @@
         <v>3.5</v>
       </c>
       <c r="V180">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="W180">
         <v>1.04</v>
@@ -29682,22 +29682,22 @@
         <v>1.07</v>
       </c>
       <c r="Y180">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="Z180">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="AA180">
         <v>2.49</v>
       </c>
       <c r="AB180">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AC180">
         <v>4.1</v>
       </c>
       <c r="AD180">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE180">
         <v>1.04</v>
@@ -29706,7 +29706,7 @@
         <v>2</v>
       </c>
       <c r="AG180">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AH180" t="inlineStr">
         <is>
@@ -29719,10 +29719,10 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AK180">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AL180">
         <v>0</v>
@@ -29824,13 +29824,13 @@
         <v>3</v>
       </c>
       <c r="R181">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S181">
         <v>1.3</v>
       </c>
       <c r="T181">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="U181">
         <v>2.53</v>
@@ -29839,7 +29839,7 @@
         <v>1.42</v>
       </c>
       <c r="W181">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X181">
         <v>1.04</v>
@@ -29860,16 +29860,16 @@
         <v>3.3</v>
       </c>
       <c r="AD181">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE181">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF181">
         <v>1.6</v>
       </c>
       <c r="AG181">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AH181" t="inlineStr">
         <is>
@@ -29882,10 +29882,10 @@
         </is>
       </c>
       <c r="AJ181">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AK181">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AL181">
         <v>0</v>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -641,13 +641,13 @@
         <v>3.1</v>
       </c>
       <c r="P2">
+        <v>1.96</v>
+      </c>
+      <c r="Q2">
+        <v>4.65</v>
+      </c>
+      <c r="R2">
         <v>1.97</v>
-      </c>
-      <c r="Q2">
-        <v>4.7</v>
-      </c>
-      <c r="R2">
-        <v>1.92</v>
       </c>
       <c r="S2">
         <v>1.47</v>
@@ -671,10 +671,10 @@
         <v>1.37</v>
       </c>
       <c r="Z2">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="AA2">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="AB2">
         <v>1.65</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.34</v>
+        <v>1.79</v>
       </c>
       <c r="AK2">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -961,25 +961,25 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="O4">
         <v>3.5</v>
       </c>
       <c r="P4">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="Q4">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="R4">
         <v>2.3</v>
       </c>
       <c r="S4">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T4">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="U4">
         <v>2.63</v>
@@ -997,7 +997,7 @@
         <v>1.19</v>
       </c>
       <c r="Z4">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="AA4">
         <v>1.73</v>
@@ -1006,7 +1006,7 @@
         <v>2.05</v>
       </c>
       <c r="AC4">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AD4">
         <v>1.34</v>
@@ -1015,7 +1015,7 @@
         <v>1.14</v>
       </c>
       <c r="AF4">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG4">
         <v>2.15</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="O5">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="P5">
-        <v>3.25</v>
+        <v>3.37</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="O6">
         <v>3.15</v>
       </c>
       <c r="P6">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="Q6">
         <v>3.5</v>
       </c>
       <c r="R6">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S6">
         <v>1.48</v>
@@ -1308,7 +1308,7 @@
         <v>2.47</v>
       </c>
       <c r="U6">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="V6">
         <v>1.31</v>
@@ -1317,13 +1317,13 @@
         <v>1.03</v>
       </c>
       <c r="X6">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y6">
         <v>1.36</v>
       </c>
       <c r="Z6">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AA6">
         <v>2.22</v>
@@ -1341,7 +1341,7 @@
         <v>1.03</v>
       </c>
       <c r="AF6">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AG6">
         <v>1.83</v>
@@ -1456,7 +1456,7 @@
         <v>3.2</v>
       </c>
       <c r="P7">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1613,31 +1613,31 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="O8">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="P8">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="Q8">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="R8">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S8">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="T8">
-        <v>2.65</v>
+        <v>2.47</v>
       </c>
       <c r="U8">
         <v>3.2</v>
       </c>
       <c r="V8">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W8">
         <v>1.01</v>
@@ -1649,22 +1649,22 @@
         <v>1.37</v>
       </c>
       <c r="Z8">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="AA8">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AB8">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC8">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="AD8">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE8">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF8">
         <v>1.87</v>
@@ -1686,7 +1686,7 @@
         <v>1.36</v>
       </c>
       <c r="AK8">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1942,10 +1942,10 @@
         <v>2.8</v>
       </c>
       <c r="O10">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P10">
-        <v>2.42</v>
+        <v>2.37</v>
       </c>
       <c r="Q10">
         <v>3.64</v>
@@ -1963,7 +1963,7 @@
         <v>2.83</v>
       </c>
       <c r="V10">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W10">
         <v>1.05</v>
@@ -1972,10 +1972,10 @@
         <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z10">
-        <v>2.82</v>
+        <v>3.23</v>
       </c>
       <c r="AA10">
         <v>2.08</v>
@@ -1993,10 +1993,10 @@
         <v>1.05</v>
       </c>
       <c r="AF10">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AG10">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2271,46 +2271,46 @@
         <v>4.05</v>
       </c>
       <c r="P12">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="Q12">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="R12">
         <v>2.45</v>
       </c>
       <c r="S12">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T12">
         <v>3.42</v>
       </c>
       <c r="U12">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="V12">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W12">
         <v>1.17</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
         <v>1.15</v>
       </c>
       <c r="Z12">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AA12">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AB12">
         <v>2.4</v>
       </c>
       <c r="AC12">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AD12">
         <v>1.62</v>
@@ -2319,10 +2319,10 @@
         <v>1.2</v>
       </c>
       <c r="AF12">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG12">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.24</v>
       </c>
       <c r="AK12">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="O13">
         <v>3</v>
       </c>
       <c r="P13">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="Q13">
         <v>3.3</v>
@@ -2449,10 +2449,10 @@
         <v>3.4</v>
       </c>
       <c r="U13">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="V13">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="W13">
         <v>1.11</v>
@@ -2461,28 +2461,28 @@
         <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z13">
-        <v>4.8</v>
+        <v>4.85</v>
       </c>
       <c r="AA13">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB13">
         <v>2.15</v>
       </c>
       <c r="AC13">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="AD13">
         <v>1.56</v>
       </c>
       <c r="AE13">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AF13">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG13">
         <v>2.4</v>
@@ -2920,10 +2920,10 @@
         <v>3.7</v>
       </c>
       <c r="O16">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="P16">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q16">
         <v>4.18</v>
@@ -2932,10 +2932,10 @@
         <v>2.6</v>
       </c>
       <c r="S16">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T16">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U16">
         <v>1.8</v>
@@ -2944,22 +2944,22 @@
         <v>1.68</v>
       </c>
       <c r="W16">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z16">
-        <v>5.75</v>
+        <v>6.02</v>
       </c>
       <c r="AA16">
         <v>1.4</v>
       </c>
       <c r="AB16">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="AC16">
         <v>2.02</v>
@@ -2971,7 +2971,7 @@
         <v>1.26</v>
       </c>
       <c r="AF16">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AG16">
         <v>2.6</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="O17">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="P17">
-        <v>2.8</v>
+        <v>3.02</v>
       </c>
       <c r="Q17">
         <v>2.7</v>
@@ -3095,7 +3095,7 @@
         <v>2.17</v>
       </c>
       <c r="S17">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T17">
         <v>3.04</v>
@@ -3104,13 +3104,13 @@
         <v>2.4</v>
       </c>
       <c r="V17">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W17">
         <v>1.11</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y17">
         <v>1.22</v>
@@ -3119,19 +3119,19 @@
         <v>4.2</v>
       </c>
       <c r="AA17">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB17">
         <v>2.2</v>
       </c>
       <c r="AC17">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="AD17">
         <v>1.4</v>
       </c>
       <c r="AE17">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF17">
         <v>1.53</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK17">
         <v>1.65</v>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="O18">
         <v>3.54</v>
@@ -3273,25 +3273,25 @@
         <v>1.09</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y18">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z18">
         <v>4.35</v>
       </c>
       <c r="AA18">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AB18">
         <v>2.14</v>
       </c>
       <c r="AC18">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AD18">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AE18">
         <v>1.2</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK18">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O19">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P19">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q19">
         <v>3.62</v>
@@ -3430,19 +3430,19 @@
         <v>2.25</v>
       </c>
       <c r="V19">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W19">
         <v>1.11</v>
       </c>
       <c r="X19">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
         <v>1.12</v>
       </c>
       <c r="Z19">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="AA19">
         <v>1.55</v>
@@ -3454,7 +3454,7 @@
         <v>2.4</v>
       </c>
       <c r="AD19">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AE19">
         <v>1.18</v>
@@ -3463,7 +3463,7 @@
         <v>1.5</v>
       </c>
       <c r="AG19">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="O20">
         <v>3.51</v>
@@ -3590,7 +3590,7 @@
         <v>2.68</v>
       </c>
       <c r="U20">
-        <v>3.08</v>
+        <v>3.13</v>
       </c>
       <c r="V20">
         <v>1.35</v>
@@ -3611,7 +3611,7 @@
         <v>2.17</v>
       </c>
       <c r="AB20">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AC20">
         <v>3.68</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="AK20">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3898,10 +3898,10 @@
         <v>1.95</v>
       </c>
       <c r="O22">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P22">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="O25">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="P25">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="Q25">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="R25">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="S25">
         <v>1.25</v>
       </c>
       <c r="T25">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="U25">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="V25">
         <v>1.6</v>
       </c>
       <c r="W25">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X25">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z25">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
       <c r="AA25">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB25">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AC25">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="AD25">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AE25">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AF25">
         <v>1.65</v>
       </c>
       <c r="AG25">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>1.19</v>
       </c>
       <c r="AK25">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="O29">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P29">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="Q29">
         <v>2.2</v>
@@ -5054,13 +5054,13 @@
         <v>1.36</v>
       </c>
       <c r="T29">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="U29">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="V29">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="W29">
         <v>1.07</v>
@@ -5075,10 +5075,10 @@
         <v>3.2</v>
       </c>
       <c r="AA29">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AB29">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AC29">
         <v>3.3</v>
@@ -5093,7 +5093,7 @@
         <v>1.85</v>
       </c>
       <c r="AG29">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK29">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="O31">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="P31">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="Q31">
         <v>6</v>
@@ -5395,16 +5395,16 @@
         <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z31">
-        <v>6</v>
+        <v>6.05</v>
       </c>
       <c r="AA31">
         <v>1.4</v>
       </c>
       <c r="AB31">
-        <v>2.63</v>
+        <v>2.83</v>
       </c>
       <c r="AC31">
         <v>2.1</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AK31">
         <v>1.07</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O32">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P32">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5688,7 +5688,7 @@
         </is>
       </c>
       <c r="N33">
-        <v>6.15</v>
+        <v>5.5</v>
       </c>
       <c r="O33">
         <v>4.45</v>
@@ -5697,7 +5697,7 @@
         <v>1.5</v>
       </c>
       <c r="Q33">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="R33">
         <v>2.55</v>
@@ -5706,7 +5706,7 @@
         <v>1.17</v>
       </c>
       <c r="T33">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="U33">
         <v>2.05</v>
@@ -5721,19 +5721,19 @@
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z33">
-        <v>5.7</v>
+        <v>5.72</v>
       </c>
       <c r="AA33">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AB33">
         <v>2.6</v>
       </c>
       <c r="AC33">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="AD33">
         <v>1.69</v>
@@ -5742,10 +5742,10 @@
         <v>1.29</v>
       </c>
       <c r="AF33">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG33">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>1.2</v>
       </c>
       <c r="AK33">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5893,10 +5893,10 @@
         <v>1.79</v>
       </c>
       <c r="AB34">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="AC34">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="AD34">
         <v>1.33</v>
@@ -5905,7 +5905,7 @@
         <v>1.13</v>
       </c>
       <c r="AF34">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG34">
         <v>2.2</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G35">
@@ -6010,68 +6010,68 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N35">
-        <v>2.37</v>
+        <v>1.59</v>
       </c>
       <c r="O35">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="P35">
-        <v>2.87</v>
+        <v>5.14</v>
       </c>
       <c r="Q35">
-        <v>3.05</v>
+        <v>2.17</v>
       </c>
       <c r="R35">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="S35">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T35">
+        <v>3.02</v>
+      </c>
+      <c r="U35">
         <v>2.65</v>
       </c>
-      <c r="U35">
-        <v>2.9</v>
-      </c>
       <c r="V35">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="W35">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X35">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Z35">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="AA35">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AB35">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AC35">
-        <v>3.53</v>
+        <v>3.25</v>
       </c>
       <c r="AD35">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AE35">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF35">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG35">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AK35">
-        <v>1.53</v>
+        <v>2.21</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G36">
@@ -6173,68 +6173,68 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N36">
-        <v>1.59</v>
+        <v>2.37</v>
       </c>
       <c r="O36">
-        <v>3.82</v>
+        <v>3.1</v>
       </c>
       <c r="P36">
-        <v>5.14</v>
+        <v>2.87</v>
       </c>
       <c r="Q36">
-        <v>2.17</v>
+        <v>3.04</v>
       </c>
       <c r="R36">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="S36">
         <v>1.36</v>
       </c>
       <c r="T36">
-        <v>3.02</v>
+        <v>2.88</v>
       </c>
       <c r="U36">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="V36">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W36">
         <v>1.08</v>
       </c>
       <c r="X36">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y36">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="Z36">
         <v>3.34</v>
       </c>
       <c r="AA36">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="AB36">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AC36">
-        <v>3.25</v>
+        <v>3.56</v>
       </c>
       <c r="AD36">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AE36">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF36">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AG36">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="AK36">
-        <v>2.21</v>
+        <v>1.5</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>3.2</v>
       </c>
       <c r="P38">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="Q38">
         <v>2.78</v>
@@ -6518,7 +6518,7 @@
         <v>2.03</v>
       </c>
       <c r="S38">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T38">
         <v>2.88</v>
@@ -6533,7 +6533,7 @@
         <v>1.07</v>
       </c>
       <c r="X38">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y38">
         <v>1.24</v>
@@ -6545,22 +6545,22 @@
         <v>1.93</v>
       </c>
       <c r="AB38">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AC38">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AD38">
         <v>1.3</v>
       </c>
       <c r="AE38">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF38">
         <v>1.7</v>
       </c>
       <c r="AG38">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK38">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,7 +6666,7 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="O39">
         <v>6.3</v>
@@ -6678,16 +6678,16 @@
         <v>1.57</v>
       </c>
       <c r="R39">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="S39">
         <v>1.22</v>
       </c>
       <c r="T39">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="U39">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="V39">
         <v>1.64</v>
@@ -6699,7 +6699,7 @@
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z39">
         <v>5.15</v>
@@ -6708,22 +6708,22 @@
         <v>1.42</v>
       </c>
       <c r="AB39">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="AC39">
         <v>2.25</v>
       </c>
       <c r="AD39">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AE39">
         <v>1.22</v>
       </c>
       <c r="AF39">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="AG39">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AK39">
         <v>4</v>
@@ -7327,10 +7327,10 @@
         <v>4.51</v>
       </c>
       <c r="Q43">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="R43">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="S43">
         <v>1.3</v>
@@ -7357,13 +7357,13 @@
         <v>4.1</v>
       </c>
       <c r="AA43">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="AB43">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AC43">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="AD43">
         <v>1.36</v>
@@ -7372,7 +7372,7 @@
         <v>1.13</v>
       </c>
       <c r="AF43">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG43">
         <v>2.1</v>
@@ -7391,7 +7391,7 @@
         <v>1.2</v>
       </c>
       <c r="AK43">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,16 +7481,16 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="O44">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="P44">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="Q44">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="R44">
         <v>2.1</v>
@@ -7499,7 +7499,7 @@
         <v>1.36</v>
       </c>
       <c r="T44">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="U44">
         <v>2.8</v>
@@ -7517,7 +7517,7 @@
         <v>1.3</v>
       </c>
       <c r="Z44">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="AA44">
         <v>1.93</v>
@@ -7535,10 +7535,10 @@
         <v>1.1</v>
       </c>
       <c r="AF44">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AG44">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK44">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="O48">
         <v>3.1</v>
@@ -8145,10 +8145,10 @@
         <v>2.88</v>
       </c>
       <c r="R48">
-        <v>1.91</v>
+        <v>2.09</v>
       </c>
       <c r="S48">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="T48">
         <v>2.47</v>
@@ -8157,7 +8157,7 @@
         <v>3.16</v>
       </c>
       <c r="V48">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W48">
         <v>1.01</v>
@@ -8175,7 +8175,7 @@
         <v>2.21</v>
       </c>
       <c r="AB48">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC48">
         <v>3.86</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AK48">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8459,16 +8459,16 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="O50">
-        <v>6.9</v>
+        <v>8.1</v>
       </c>
       <c r="P50">
         <v>12</v>
       </c>
       <c r="Q50">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="R50">
         <v>3.12</v>
@@ -8477,46 +8477,46 @@
         <v>1.2</v>
       </c>
       <c r="T50">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="U50">
         <v>2.06</v>
       </c>
       <c r="V50">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="W50">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X50">
         <v>0</v>
       </c>
       <c r="Y50">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="Z50">
-        <v>5.95</v>
+        <v>6.07</v>
       </c>
       <c r="AA50">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AB50">
-        <v>2.77</v>
+        <v>3.01</v>
       </c>
       <c r="AC50">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AD50">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AE50">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AF50">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AG50">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AK50">
         <v>6.15</v>
@@ -8622,25 +8622,25 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="O51">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P51">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="Q51">
         <v>2.4</v>
       </c>
       <c r="R51">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="S51">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T51">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U51">
         <v>2.45</v>
@@ -8649,28 +8649,28 @@
         <v>1.48</v>
       </c>
       <c r="W51">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X51">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z51">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA51">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB51">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="AC51">
-        <v>2.86</v>
+        <v>2.68</v>
       </c>
       <c r="AD51">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AE51">
         <v>1.14</v>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK51">
         <v>1.91</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="O52">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="P52">
-        <v>4.78</v>
+        <v>5</v>
       </c>
       <c r="Q52">
         <v>2.15</v>
@@ -8818,10 +8818,10 @@
         <v>1.04</v>
       </c>
       <c r="Y52">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z52">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA52">
         <v>1.72</v>
@@ -8836,10 +8836,10 @@
         <v>1.36</v>
       </c>
       <c r="AE52">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF52">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AG52">
         <v>2</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="O54">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="P54">
-        <v>2.97</v>
+        <v>3.18</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -9138,7 +9138,7 @@
         <v>1.48</v>
       </c>
       <c r="W54">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X54">
         <v>1.04</v>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK54">
         <v>1.65</v>
@@ -9274,31 +9274,31 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="O55">
-        <v>3.7</v>
+        <v>3.81</v>
       </c>
       <c r="P55">
-        <v>4</v>
+        <v>3.81</v>
       </c>
       <c r="Q55">
         <v>2.3</v>
       </c>
       <c r="R55">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S55">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T55">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="U55">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="V55">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W55">
         <v>1.07</v>
@@ -9307,16 +9307,16 @@
         <v>1.02</v>
       </c>
       <c r="Y55">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="Z55">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AA55">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="AB55">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="AC55">
         <v>3.6</v>
@@ -9325,7 +9325,7 @@
         <v>1.35</v>
       </c>
       <c r="AE55">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF55">
         <v>1.9</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="O57">
-        <v>3.66</v>
+        <v>3.5</v>
       </c>
       <c r="P57">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="O58">
         <v>3.55</v>
       </c>
       <c r="P58">
-        <v>4.48</v>
+        <v>4.5</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -9926,16 +9926,16 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="O59">
-        <v>3.75</v>
+        <v>3.92</v>
       </c>
       <c r="P59">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="Q59">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="R59">
         <v>2.44</v>
@@ -9947,10 +9947,10 @@
         <v>4.5</v>
       </c>
       <c r="U59">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="V59">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="W59">
         <v>1.17</v>
@@ -9977,7 +9977,7 @@
         <v>1.76</v>
       </c>
       <c r="AE59">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF59">
         <v>1.4</v>
@@ -10089,25 +10089,25 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="O60">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="P60">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="Q60">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="R60">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="S60">
         <v>1.22</v>
       </c>
       <c r="T60">
-        <v>3.64</v>
+        <v>3.9</v>
       </c>
       <c r="U60">
         <v>2.1</v>
@@ -10128,22 +10128,22 @@
         <v>5</v>
       </c>
       <c r="AA60">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AB60">
         <v>2.5</v>
       </c>
       <c r="AC60">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AD60">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AE60">
         <v>1.24</v>
       </c>
       <c r="AF60">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AG60">
         <v>2.18</v>
@@ -10162,7 +10162,7 @@
         <v>1.14</v>
       </c>
       <c r="AK60">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="O61">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P61">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="Q61">
         <v>2.4</v>
@@ -10279,34 +10279,34 @@
         <v>1.72</v>
       </c>
       <c r="W61">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X61">
         <v>1.02</v>
       </c>
       <c r="Y61">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z61">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="AA61">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AB61">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="AC61">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="AD61">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AE61">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AF61">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AG61">
         <v>2.8</v>
@@ -10325,7 +10325,7 @@
         <v>1.22</v>
       </c>
       <c r="AK61">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="O62">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="P62">
         <v>3.5</v>
       </c>
       <c r="Q62">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="R62">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S62">
         <v>1.41</v>
       </c>
       <c r="T62">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="U62">
         <v>2.99</v>
       </c>
       <c r="V62">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W62">
         <v>1.03</v>
       </c>
       <c r="X62">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y62">
         <v>1.3</v>
       </c>
       <c r="Z62">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AA62">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB62">
         <v>1.7</v>
       </c>
       <c r="AC62">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AD62">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE62">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF62">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG62">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AK62">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10584,37 +10584,37 @@
         <v>2.9</v>
       </c>
       <c r="P63">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="Q63">
         <v>3.2</v>
       </c>
       <c r="R63">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="S63">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="T63">
         <v>2.42</v>
       </c>
       <c r="U63">
-        <v>3.25</v>
+        <v>3.52</v>
       </c>
       <c r="V63">
         <v>1.23</v>
       </c>
       <c r="W63">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X63">
         <v>1.09</v>
       </c>
       <c r="Y63">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="Z63">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AA63">
         <v>2.53</v>
@@ -10629,7 +10629,7 @@
         <v>1.17</v>
       </c>
       <c r="AE63">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF63">
         <v>2.05</v>
@@ -10741,7 +10741,7 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O64">
         <v>3.4</v>
@@ -10780,13 +10780,13 @@
         <v>4.95</v>
       </c>
       <c r="AA64">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AB64">
         <v>2.38</v>
       </c>
       <c r="AC64">
-        <v>2.7</v>
+        <v>2.21</v>
       </c>
       <c r="AD64">
         <v>1.47</v>
@@ -10795,10 +10795,10 @@
         <v>1.25</v>
       </c>
       <c r="AF64">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AG64">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AK64">
         <v>1.5</v>
@@ -11236,7 +11236,7 @@
         <v>3.8</v>
       </c>
       <c r="P67">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q67">
         <v>3.4</v>
@@ -11260,25 +11260,25 @@
         <v>1.18</v>
       </c>
       <c r="X67">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y67">
         <v>1.14</v>
       </c>
       <c r="Z67">
-        <v>5.48</v>
+        <v>5</v>
       </c>
       <c r="AA67">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AB67">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AC67">
         <v>2.15</v>
       </c>
       <c r="AD67">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AE67">
         <v>1.25</v>
@@ -11287,7 +11287,7 @@
         <v>1.4</v>
       </c>
       <c r="AG67">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="O68">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P68">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="Q68">
         <v>2.91</v>
@@ -11426,7 +11426,7 @@
         <v>1.03</v>
       </c>
       <c r="Y68">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="Z68">
         <v>4.65</v>
@@ -11444,13 +11444,13 @@
         <v>1.5</v>
       </c>
       <c r="AE68">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF68">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AG68">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11882,31 +11882,31 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="O71">
         <v>3.7</v>
       </c>
       <c r="P71">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="Q71">
         <v>2.16</v>
       </c>
       <c r="R71">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S71">
         <v>1.3</v>
       </c>
       <c r="T71">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="U71">
         <v>2.73</v>
       </c>
       <c r="V71">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W71">
         <v>1.06</v>
@@ -11921,7 +11921,7 @@
         <v>3.68</v>
       </c>
       <c r="AA71">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AB71">
         <v>1.93</v>
@@ -11933,10 +11933,10 @@
         <v>1.33</v>
       </c>
       <c r="AE71">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF71">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AG71">
         <v>1.9</v>
@@ -11955,7 +11955,7 @@
         <v>1.09</v>
       </c>
       <c r="AK71">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12045,31 +12045,31 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="O72">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="P72">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="Q72">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="R72">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="S72">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T72">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="U72">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="V72">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W72">
         <v>1.07</v>
@@ -12081,10 +12081,10 @@
         <v>1.3</v>
       </c>
       <c r="Z72">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="AA72">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AB72">
         <v>1.85</v>
@@ -12096,13 +12096,13 @@
         <v>1.31</v>
       </c>
       <c r="AE72">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF72">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG72">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AK72">
         <v>1.6</v>
@@ -12534,7 +12534,7 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="O75">
         <v>3.3</v>
@@ -12552,7 +12552,7 @@
         <v>1.41</v>
       </c>
       <c r="T75">
-        <v>2.91</v>
+        <v>2.69</v>
       </c>
       <c r="U75">
         <v>2.97</v>
@@ -12588,7 +12588,7 @@
         <v>1.11</v>
       </c>
       <c r="AF75">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AG75">
         <v>1.95</v>
@@ -12607,7 +12607,7 @@
         <v>1.53</v>
       </c>
       <c r="AK75">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12697,10 +12697,10 @@
         </is>
       </c>
       <c r="N76">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="O76">
-        <v>3.5</v>
+        <v>3.61</v>
       </c>
       <c r="P76">
         <v>1.85</v>
@@ -12712,10 +12712,10 @@
         <v>2.28</v>
       </c>
       <c r="S76">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T76">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="U76">
         <v>2.34</v>
@@ -12727,25 +12727,25 @@
         <v>1.11</v>
       </c>
       <c r="X76">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y76">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z76">
         <v>4.45</v>
       </c>
       <c r="AA76">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AB76">
         <v>2.3</v>
       </c>
       <c r="AC76">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AD76">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE76">
         <v>1.2</v>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.23</v>
+        <v>1.85</v>
       </c>
       <c r="AK76">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12863,16 +12863,16 @@
         <v>1.55</v>
       </c>
       <c r="O77">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="P77">
         <v>5.3</v>
       </c>
       <c r="Q77">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="R77">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="S77">
         <v>1.26</v>
@@ -12881,10 +12881,10 @@
         <v>3.34</v>
       </c>
       <c r="U77">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="V77">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W77">
         <v>1.12</v>
@@ -12893,31 +12893,31 @@
         <v>1.03</v>
       </c>
       <c r="Y77">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z77">
-        <v>4.65</v>
+        <v>5.01</v>
       </c>
       <c r="AA77">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AB77">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AC77">
+        <v>2.35</v>
+      </c>
+      <c r="AD77">
+        <v>1.57</v>
+      </c>
+      <c r="AE77">
+        <v>1.18</v>
+      </c>
+      <c r="AF77">
+        <v>1.57</v>
+      </c>
+      <c r="AG77">
         <v>2.38</v>
-      </c>
-      <c r="AD77">
-        <v>1.53</v>
-      </c>
-      <c r="AE77">
-        <v>1.22</v>
-      </c>
-      <c r="AF77">
-        <v>1.6</v>
-      </c>
-      <c r="AG77">
-        <v>2.25</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>1.22</v>
       </c>
       <c r="AK77">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -14007,10 +14007,10 @@
         <v>3.31</v>
       </c>
       <c r="P84">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="Q84">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="R84">
         <v>2</v>
@@ -14055,7 +14055,7 @@
         <v>1.04</v>
       </c>
       <c r="AF84">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AG84">
         <v>1.67</v>
@@ -14164,31 +14164,31 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="O85">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P85">
         <v>3.75</v>
       </c>
       <c r="Q85">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="R85">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S85">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T85">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="U85">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="V85">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W85">
         <v>1.09</v>
@@ -14197,19 +14197,19 @@
         <v>1.03</v>
       </c>
       <c r="Y85">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z85">
         <v>3.78</v>
       </c>
       <c r="AA85">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AB85">
         <v>1.97</v>
       </c>
       <c r="AC85">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="AD85">
         <v>1.36</v>
@@ -14221,7 +14221,7 @@
         <v>1.67</v>
       </c>
       <c r="AG85">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="O86">
         <v>3.3</v>
       </c>
       <c r="P86">
-        <v>4.65</v>
+        <v>3.9</v>
       </c>
       <c r="Q86">
         <v>2.39</v>
@@ -14345,7 +14345,7 @@
         <v>1.47</v>
       </c>
       <c r="T86">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="U86">
         <v>3.28</v>
@@ -14366,16 +14366,16 @@
         <v>2.62</v>
       </c>
       <c r="AA86">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="AB86">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AC86">
         <v>4.3</v>
       </c>
       <c r="AD86">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AE86">
         <v>1.01</v>
@@ -14400,7 +14400,7 @@
         <v>1.28</v>
       </c>
       <c r="AK86">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14490,7 +14490,7 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O87">
         <v>3.4</v>
@@ -14505,7 +14505,7 @@
         <v>2.3</v>
       </c>
       <c r="S87">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T87">
         <v>2.96</v>
@@ -14517,16 +14517,16 @@
         <v>1.44</v>
       </c>
       <c r="W87">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X87">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y87">
         <v>1.19</v>
       </c>
       <c r="Z87">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="AA87">
         <v>1.73</v>
@@ -14535,7 +14535,7 @@
         <v>2</v>
       </c>
       <c r="AC87">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AD87">
         <v>1.36</v>
@@ -14816,7 +14816,7 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="O89">
         <v>4</v>
@@ -14831,28 +14831,28 @@
         <v>2.38</v>
       </c>
       <c r="S89">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T89">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="U89">
         <v>2.25</v>
       </c>
       <c r="V89">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W89">
         <v>1.08</v>
       </c>
       <c r="X89">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y89">
         <v>1.18</v>
       </c>
       <c r="Z89">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA89">
         <v>1.62</v>
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="O90">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P90">
-        <v>2.91</v>
+        <v>2.8</v>
       </c>
       <c r="Q90">
         <v>2.87</v>
@@ -14994,10 +14994,10 @@
         <v>2.28</v>
       </c>
       <c r="S90">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T90">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U90">
         <v>2.59</v>
@@ -15006,16 +15006,16 @@
         <v>1.45</v>
       </c>
       <c r="W90">
+        <v>1.1</v>
+      </c>
+      <c r="X90">
         <v>1.05</v>
-      </c>
-      <c r="X90">
-        <v>1.03</v>
       </c>
       <c r="Y90">
         <v>1.2</v>
       </c>
       <c r="Z90">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AA90">
         <v>1.76</v>
@@ -15027,10 +15027,10 @@
         <v>3.1</v>
       </c>
       <c r="AD90">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE90">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF90">
         <v>1.6</v>
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK90">
         <v>1.52</v>
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O91">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P91">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q91">
         <v>3.3</v>
@@ -15181,13 +15181,13 @@
         <v>2.91</v>
       </c>
       <c r="AA91">
-        <v>2.17</v>
+        <v>2.24</v>
       </c>
       <c r="AB91">
         <v>1.6</v>
       </c>
       <c r="AC91">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AD91">
         <v>1.16</v>
@@ -15199,7 +15199,7 @@
         <v>1.95</v>
       </c>
       <c r="AG91">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK91">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -16455,7 +16455,7 @@
         <v>4.1</v>
       </c>
       <c r="Q99">
-        <v>2.89</v>
+        <v>2.76</v>
       </c>
       <c r="R99">
         <v>1.77</v>
@@ -16464,7 +16464,7 @@
         <v>1.59</v>
       </c>
       <c r="T99">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="U99">
         <v>3.3</v>
@@ -16482,7 +16482,7 @@
         <v>1.38</v>
       </c>
       <c r="Z99">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="AA99">
         <v>2.35</v>
@@ -16516,7 +16516,7 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AK99">
         <v>1.69</v>
@@ -16778,7 +16778,7 @@
         <v>2.85</v>
       </c>
       <c r="P101">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="Q101">
         <v>3.3</v>
@@ -16790,13 +16790,13 @@
         <v>1.5</v>
       </c>
       <c r="T101">
-        <v>2.24</v>
+        <v>2.43</v>
       </c>
       <c r="U101">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="V101">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W101">
         <v>1.05</v>
@@ -16829,7 +16829,7 @@
         <v>2.01</v>
       </c>
       <c r="AG101">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK101">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -17424,16 +17424,16 @@
         </is>
       </c>
       <c r="N105">
-        <v>4.26</v>
+        <v>4.36</v>
       </c>
       <c r="O105">
-        <v>3.61</v>
+        <v>3.7</v>
       </c>
       <c r="P105">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="Q105">
-        <v>4.88</v>
+        <v>4.94</v>
       </c>
       <c r="R105">
         <v>2.25</v>
@@ -17442,7 +17442,7 @@
         <v>1.33</v>
       </c>
       <c r="T105">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="U105">
         <v>2.6</v>
@@ -17451,31 +17451,31 @@
         <v>1.44</v>
       </c>
       <c r="W105">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X105">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y105">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z105">
-        <v>3.44</v>
+        <v>3.52</v>
       </c>
       <c r="AA105">
         <v>1.85</v>
       </c>
       <c r="AB105">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AC105">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="AD105">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AE105">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF105">
         <v>1.75</v>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK105">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17590,22 +17590,22 @@
         <v>4.55</v>
       </c>
       <c r="O106">
-        <v>3.27</v>
+        <v>3.6</v>
       </c>
       <c r="P106">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="Q106">
         <v>5.05</v>
       </c>
       <c r="R106">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="S106">
         <v>1.36</v>
       </c>
       <c r="T106">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="U106">
         <v>2.7</v>
@@ -17632,13 +17632,13 @@
         <v>1.82</v>
       </c>
       <c r="AC106">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="AD106">
         <v>1.27</v>
       </c>
       <c r="AE106">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF106">
         <v>1.85</v>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AK106">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17925,7 +17925,7 @@
         <v>1.93</v>
       </c>
       <c r="R108">
-        <v>2.19</v>
+        <v>2.38</v>
       </c>
       <c r="S108">
         <v>1.38</v>
@@ -17937,13 +17937,13 @@
         <v>2.66</v>
       </c>
       <c r="V108">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W108">
         <v>1.1</v>
       </c>
       <c r="X108">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y108">
         <v>1.25</v>
@@ -17952,7 +17952,7 @@
         <v>3.5</v>
       </c>
       <c r="AA108">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AB108">
         <v>1.9</v>
@@ -17961,10 +17961,10 @@
         <v>3.25</v>
       </c>
       <c r="AD108">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE108">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF108">
         <v>2.1</v>
@@ -18082,7 +18082,7 @@
         <v>3.45</v>
       </c>
       <c r="P109">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="Q109">
         <v>2.42</v>
@@ -18091,10 +18091,10 @@
         <v>2.06</v>
       </c>
       <c r="S109">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T109">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="U109">
         <v>2.75</v>
@@ -18103,22 +18103,22 @@
         <v>1.4</v>
       </c>
       <c r="W109">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X109">
         <v>1.06</v>
       </c>
       <c r="Y109">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z109">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="AA109">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AB109">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC109">
         <v>3.64</v>
@@ -18133,7 +18133,7 @@
         <v>1.84</v>
       </c>
       <c r="AG109">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="O112">
-        <v>3.38</v>
+        <v>3.55</v>
       </c>
       <c r="P112">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18891,10 +18891,10 @@
         </is>
       </c>
       <c r="N114">
-        <v>3.07</v>
+        <v>3.4</v>
       </c>
       <c r="O114">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P114">
         <v>2</v>
@@ -18921,34 +18921,34 @@
         <v>1.06</v>
       </c>
       <c r="X114">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y114">
         <v>1.28</v>
       </c>
       <c r="Z114">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA114">
         <v>1.85</v>
       </c>
       <c r="AB114">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AC114">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="AD114">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AE114">
         <v>1.08</v>
       </c>
       <c r="AF114">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG114">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -19054,28 +19054,28 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="O115">
         <v>3.55</v>
       </c>
       <c r="P115">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="Q115">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="R115">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="S115">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T115">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U115">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="V115">
         <v>1.49</v>
@@ -19087,13 +19087,13 @@
         <v>1.02</v>
       </c>
       <c r="Y115">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z115">
         <v>4.32</v>
       </c>
       <c r="AA115">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AB115">
         <v>2.14</v>
@@ -19124,7 +19124,7 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AK115">
         <v>1.77</v>
@@ -19220,7 +19220,7 @@
         <v>1.14</v>
       </c>
       <c r="O116">
-        <v>6.5</v>
+        <v>7.05</v>
       </c>
       <c r="P116">
         <v>12</v>
@@ -19250,13 +19250,13 @@
         <v>1.03</v>
       </c>
       <c r="Y116">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z116">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AA116">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AB116">
         <v>2.35</v>
@@ -19271,10 +19271,10 @@
         <v>1.18</v>
       </c>
       <c r="AF116">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="AG116">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="O118">
         <v>3.65</v>
       </c>
       <c r="P118">
-        <v>4.8</v>
+        <v>4.69</v>
       </c>
       <c r="Q118">
         <v>0</v>
@@ -19869,13 +19869,13 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="O120">
         <v>3.6</v>
       </c>
       <c r="P120">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -19905,13 +19905,13 @@
         <v>1.08</v>
       </c>
       <c r="Z120">
-        <v>5.77</v>
+        <v>5.3</v>
       </c>
       <c r="AA120">
         <v>1.4</v>
       </c>
       <c r="AB120">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="AC120">
         <v>2.06</v>
@@ -19920,7 +19920,7 @@
         <v>1.71</v>
       </c>
       <c r="AE120">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF120">
         <v>1.39</v>
@@ -20038,7 +20038,7 @@
         <v>3.21</v>
       </c>
       <c r="P121">
-        <v>3.48</v>
+        <v>4.1</v>
       </c>
       <c r="Q121">
         <v>2.52</v>
@@ -20047,16 +20047,16 @@
         <v>2.06</v>
       </c>
       <c r="S121">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="T121">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="U121">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="V121">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W121">
         <v>1.04</v>
@@ -20204,25 +20204,25 @@
         <v>1.91</v>
       </c>
       <c r="Q122">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="R122">
         <v>2.1</v>
       </c>
       <c r="S122">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T122">
         <v>2.65</v>
       </c>
       <c r="U122">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="V122">
         <v>1.35</v>
       </c>
       <c r="W122">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X122">
         <v>1.02</v>
@@ -20240,19 +20240,19 @@
         <v>1.7</v>
       </c>
       <c r="AC122">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AD122">
         <v>1.2</v>
       </c>
       <c r="AE122">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF122">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AG122">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.75</v>
+        <v>1.22</v>
       </c>
       <c r="AK122">
         <v>1.18</v>
@@ -20358,7 +20358,7 @@
         </is>
       </c>
       <c r="N123">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="O123">
         <v>4.45</v>
@@ -20367,19 +20367,19 @@
         <v>7.55</v>
       </c>
       <c r="Q123">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="R123">
         <v>2.34</v>
       </c>
       <c r="S123">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T123">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="U123">
-        <v>2.09</v>
+        <v>2.6</v>
       </c>
       <c r="V123">
         <v>1.46</v>
@@ -20403,7 +20403,7 @@
         <v>2</v>
       </c>
       <c r="AC123">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="AD123">
         <v>1.36</v>
@@ -20415,7 +20415,7 @@
         <v>1.95</v>
       </c>
       <c r="AG123">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>1.13</v>
       </c>
       <c r="AK123">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20847,25 +20847,25 @@
         </is>
       </c>
       <c r="N126">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="O126">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P126">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="Q126">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="R126">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S126">
         <v>1.35</v>
       </c>
       <c r="T126">
-        <v>3.22</v>
+        <v>2.87</v>
       </c>
       <c r="U126">
         <v>2.47</v>
@@ -20877,25 +20877,25 @@
         <v>1.07</v>
       </c>
       <c r="X126">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y126">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z126">
         <v>4.1</v>
       </c>
       <c r="AA126">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB126">
         <v>2.01</v>
       </c>
       <c r="AC126">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AD126">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE126">
         <v>1.14</v>
@@ -22314,7 +22314,7 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="O135">
         <v>3.4</v>
@@ -22347,7 +22347,7 @@
         <v>1.05</v>
       </c>
       <c r="Y135">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z135">
         <v>3.5</v>
@@ -22371,7 +22371,7 @@
         <v>1.73</v>
       </c>
       <c r="AG135">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22480,28 +22480,28 @@
         <v>1.91</v>
       </c>
       <c r="O136">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P136">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="Q136">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="R136">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S136">
         <v>1.25</v>
       </c>
       <c r="T136">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="U136">
         <v>2.29</v>
       </c>
       <c r="V136">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W136">
         <v>1.12</v>
@@ -22510,7 +22510,7 @@
         <v>1.03</v>
       </c>
       <c r="Y136">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z136">
         <v>4.4</v>
@@ -22522,7 +22522,7 @@
         <v>2.15</v>
       </c>
       <c r="AC136">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="AD136">
         <v>1.44</v>
@@ -22531,10 +22531,10 @@
         <v>1.18</v>
       </c>
       <c r="AF136">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG136">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>1.18</v>
       </c>
       <c r="AK136">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22640,16 +22640,16 @@
         </is>
       </c>
       <c r="N137">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="O137">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P137">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="Q137">
-        <v>2.8</v>
+        <v>3.13</v>
       </c>
       <c r="R137">
         <v>2.1</v>
@@ -22673,7 +22673,7 @@
         <v>1</v>
       </c>
       <c r="Y137">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z137">
         <v>3.25</v>
@@ -22688,7 +22688,7 @@
         <v>3.6</v>
       </c>
       <c r="AD137">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE137">
         <v>1.1</v>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK137">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22803,19 +22803,19 @@
         </is>
       </c>
       <c r="N138">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="O138">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P138">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="Q138">
         <v>6</v>
       </c>
       <c r="R138">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="S138">
         <v>1.33</v>
@@ -22824,10 +22824,10 @@
         <v>2.99</v>
       </c>
       <c r="U138">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V138">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W138">
         <v>1.06</v>
@@ -22851,16 +22851,16 @@
         <v>3.18</v>
       </c>
       <c r="AD138">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE138">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF138">
         <v>1.91</v>
       </c>
       <c r="AG138">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="AK138">
         <v>1.13</v>
@@ -23458,7 +23458,7 @@
         <v>1.64</v>
       </c>
       <c r="O142">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P142">
         <v>5.01</v>
@@ -23488,19 +23488,19 @@
         <v>1.06</v>
       </c>
       <c r="Y142">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z142">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AA142">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB142">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AC142">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="AD142">
         <v>1.22</v>
@@ -23512,7 +23512,7 @@
         <v>1.95</v>
       </c>
       <c r="AG142">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23525,10 +23525,10 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK142">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23781,13 +23781,13 @@
         </is>
       </c>
       <c r="N144">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O144">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P144">
-        <v>0</v>
+        <v>10.23</v>
       </c>
       <c r="Q144">
         <v>1.67</v>
@@ -23796,16 +23796,16 @@
         <v>2.45</v>
       </c>
       <c r="S144">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="T144">
-        <v>3</v>
+        <v>2.59</v>
       </c>
       <c r="U144">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="V144">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W144">
         <v>1.06</v>
@@ -23814,31 +23814,31 @@
         <v>1.02</v>
       </c>
       <c r="Y144">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z144">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AA144">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AB144">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AC144">
         <v>2.9</v>
       </c>
       <c r="AD144">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AE144">
         <v>1.06</v>
       </c>
       <c r="AF144">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AG144">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AK144">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -24270,13 +24270,13 @@
         </is>
       </c>
       <c r="N147">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="O147">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P147">
-        <v>5.2</v>
+        <v>4.75</v>
       </c>
       <c r="Q147">
         <v>2.05</v>
@@ -24300,19 +24300,19 @@
         <v>1.06</v>
       </c>
       <c r="X147">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y147">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z147">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="AA147">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AB147">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC147">
         <v>3</v>
@@ -24321,13 +24321,13 @@
         <v>1.32</v>
       </c>
       <c r="AE147">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF147">
         <v>1.85</v>
       </c>
       <c r="AG147">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AK147">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24433,19 +24433,19 @@
         </is>
       </c>
       <c r="N148">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="O148">
         <v>3</v>
       </c>
       <c r="P148">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q148">
         <v>2.57</v>
       </c>
       <c r="R148">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="S148">
         <v>1.5</v>
@@ -24457,40 +24457,40 @@
         <v>3.5</v>
       </c>
       <c r="V148">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W148">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X148">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Y148">
+        <v>1.47</v>
+      </c>
+      <c r="Z148">
+        <v>2.44</v>
+      </c>
+      <c r="AA148">
+        <v>2.5</v>
+      </c>
+      <c r="AB148">
         <v>1.49</v>
       </c>
-      <c r="Z148">
-        <v>2.48</v>
-      </c>
-      <c r="AA148">
-        <v>2.46</v>
-      </c>
-      <c r="AB148">
-        <v>1.43</v>
-      </c>
       <c r="AC148">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AD148">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AE148">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AF148">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AG148">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -24503,10 +24503,10 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AK148">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -24596,7 +24596,7 @@
         </is>
       </c>
       <c r="N149">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="O149">
         <v>3.4</v>
@@ -24623,13 +24623,13 @@
         <v>1.5</v>
       </c>
       <c r="W149">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X149">
         <v>1.04</v>
       </c>
       <c r="Y149">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z149">
         <v>3.95</v>
@@ -24638,7 +24638,7 @@
         <v>1.7</v>
       </c>
       <c r="AB149">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AC149">
         <v>2.7</v>
@@ -24647,7 +24647,7 @@
         <v>1.4</v>
       </c>
       <c r="AE149">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF149">
         <v>1.57</v>
@@ -24669,7 +24669,7 @@
         <v>1.25</v>
       </c>
       <c r="AK149">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -24925,19 +24925,19 @@
         <v>2.4</v>
       </c>
       <c r="O151">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="P151">
         <v>2.85</v>
       </c>
       <c r="Q151">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R151">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="S151">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T151">
         <v>2.31</v>
@@ -24958,25 +24958,25 @@
         <v>1.32</v>
       </c>
       <c r="Z151">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AA151">
         <v>2.2</v>
       </c>
       <c r="AB151">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AC151">
         <v>3.42</v>
       </c>
       <c r="AD151">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AE151">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF151">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AG151">
         <v>1.89</v>
@@ -24995,7 +24995,7 @@
         <v>1.4</v>
       </c>
       <c r="AK151">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25094,13 +25094,13 @@
         <v>2.68</v>
       </c>
       <c r="Q152">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="R152">
         <v>2.16</v>
       </c>
       <c r="S152">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T152">
         <v>3.3</v>
@@ -25118,31 +25118,31 @@
         <v>1.04</v>
       </c>
       <c r="Y152">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z152">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA152">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AB152">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="AC152">
         <v>2.78</v>
       </c>
       <c r="AD152">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE152">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AF152">
         <v>1.57</v>
       </c>
       <c r="AG152">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25628,7 +25628,7 @@
         <v>1.12</v>
       </c>
       <c r="AF155">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG155">
         <v>1.8</v>
@@ -25746,7 +25746,7 @@
         <v>2.8</v>
       </c>
       <c r="Q156">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R156">
         <v>2.05</v>
@@ -25755,10 +25755,10 @@
         <v>1.38</v>
       </c>
       <c r="T156">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="U156">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="V156">
         <v>1.36</v>
@@ -25773,7 +25773,7 @@
         <v>1.3</v>
       </c>
       <c r="Z156">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AA156">
         <v>2</v>
@@ -25782,10 +25782,10 @@
         <v>1.76</v>
       </c>
       <c r="AC156">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AD156">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE156">
         <v>1.07</v>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK156">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25909,16 +25909,16 @@
         <v>3.4</v>
       </c>
       <c r="Q157">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="R157">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="S157">
         <v>1.57</v>
       </c>
       <c r="T157">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="U157">
         <v>3.6</v>
@@ -25933,7 +25933,7 @@
         <v>1.06</v>
       </c>
       <c r="Y157">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="Z157">
         <v>2.5</v>
@@ -25942,10 +25942,10 @@
         <v>2.55</v>
       </c>
       <c r="AB157">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AC157">
-        <v>4.84</v>
+        <v>5.1</v>
       </c>
       <c r="AD157">
         <v>1.17</v>
@@ -25954,7 +25954,7 @@
         <v>1.04</v>
       </c>
       <c r="AF157">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AG157">
         <v>1.67</v>
@@ -26226,13 +26226,13 @@
         </is>
       </c>
       <c r="N159">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="O159">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="P159">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q159">
         <v>2.3</v>
@@ -26241,7 +26241,7 @@
         <v>2.16</v>
       </c>
       <c r="S159">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T159">
         <v>2.73</v>
@@ -26253,7 +26253,7 @@
         <v>1.37</v>
       </c>
       <c r="W159">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X159">
         <v>1.03</v>
@@ -26268,7 +26268,7 @@
         <v>1.89</v>
       </c>
       <c r="AB159">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC159">
         <v>3.24</v>
@@ -26280,10 +26280,10 @@
         <v>1.08</v>
       </c>
       <c r="AF159">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG159">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26389,13 +26389,13 @@
         </is>
       </c>
       <c r="N160">
-        <v>4.75</v>
+        <v>4.98</v>
       </c>
       <c r="O160">
         <v>3.7</v>
       </c>
       <c r="P160">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="Q160">
         <v>4.8</v>
@@ -26419,7 +26419,7 @@
         <v>1.04</v>
       </c>
       <c r="X160">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y160">
         <v>1.29</v>
@@ -26431,10 +26431,10 @@
         <v>1.94</v>
       </c>
       <c r="AB160">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AC160">
-        <v>3.31</v>
+        <v>3.4</v>
       </c>
       <c r="AD160">
         <v>1.27</v>
@@ -26459,7 +26459,7 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="AK160">
         <v>1.18</v>
@@ -26558,7 +26558,7 @@
         <v>8.6</v>
       </c>
       <c r="P161">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q161">
         <v>1.44</v>
@@ -26567,28 +26567,28 @@
         <v>3</v>
       </c>
       <c r="S161">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="T161">
-        <v>3.8</v>
+        <v>3.96</v>
       </c>
       <c r="U161">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V161">
         <v>1.68</v>
       </c>
       <c r="W161">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X161">
         <v>1.01</v>
       </c>
       <c r="Y161">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z161">
-        <v>5.41</v>
+        <v>5.75</v>
       </c>
       <c r="AA161">
         <v>1.42</v>
@@ -26597,19 +26597,19 @@
         <v>2.6</v>
       </c>
       <c r="AC161">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AD161">
         <v>1.65</v>
       </c>
       <c r="AE161">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AF161">
         <v>2.55</v>
       </c>
       <c r="AG161">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26625,7 +26625,7 @@
         <v>1.06</v>
       </c>
       <c r="AK161">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -27862,7 +27862,7 @@
         <v>3</v>
       </c>
       <c r="P169">
-        <v>3.27</v>
+        <v>3.37</v>
       </c>
       <c r="Q169">
         <v>0</v>
@@ -27895,10 +27895,10 @@
         <v>2.37</v>
       </c>
       <c r="AA169">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AB169">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC169">
         <v>0</v>
@@ -28508,64 +28508,64 @@
         </is>
       </c>
       <c r="N173">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="O173">
-        <v>2.35</v>
+        <v>2.95</v>
       </c>
       <c r="P173">
-        <v>3.15</v>
+        <v>2.87</v>
       </c>
       <c r="Q173">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="R173">
         <v>2</v>
       </c>
       <c r="S173">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="T173">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="U173">
         <v>3.4</v>
       </c>
       <c r="V173">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="W173">
         <v>1.06</v>
       </c>
       <c r="X173">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y173">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z173">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AA173">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="AB173">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AC173">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AD173">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE173">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF173">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AG173">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28578,10 +28578,10 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AK173">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -28674,13 +28674,13 @@
         <v>2.5</v>
       </c>
       <c r="O174">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="P174">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="Q174">
-        <v>3.46</v>
+        <v>3.25</v>
       </c>
       <c r="R174">
         <v>1.9</v>
@@ -28689,46 +28689,46 @@
         <v>1.5</v>
       </c>
       <c r="T174">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="U174">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="V174">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="W174">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X174">
         <v>1.06</v>
       </c>
       <c r="Y174">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="Z174">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="AA174">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AB174">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AC174">
         <v>5.4</v>
       </c>
       <c r="AD174">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE174">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF174">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="AG174">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AH174" t="inlineStr">
         <is>
@@ -28741,10 +28741,10 @@
         </is>
       </c>
       <c r="AJ174">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AK174">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -28834,61 +28834,61 @@
         </is>
       </c>
       <c r="N175">
-        <v>3.9</v>
+        <v>4.28</v>
       </c>
       <c r="O175">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P175">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q175">
         <v>4.4</v>
       </c>
       <c r="R175">
-        <v>2.31</v>
+        <v>2.17</v>
       </c>
       <c r="S175">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="T175">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U175">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="V175">
         <v>1.36</v>
       </c>
       <c r="W175">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X175">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y175">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z175">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA175">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB175">
         <v>1.78</v>
       </c>
       <c r="AC175">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="AD175">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE175">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF175">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AG175">
         <v>1.91</v>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AK175">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -29495,25 +29495,25 @@
         <v>3.8</v>
       </c>
       <c r="Q179">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R179">
         <v>2.15</v>
       </c>
       <c r="S179">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T179">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="U179">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="V179">
         <v>1.37</v>
       </c>
       <c r="W179">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X179">
         <v>1.05</v>
@@ -29522,22 +29522,22 @@
         <v>1.25</v>
       </c>
       <c r="Z179">
-        <v>3.5</v>
+        <v>3.81</v>
       </c>
       <c r="AA179">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AB179">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC179">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AD179">
         <v>1.3</v>
       </c>
       <c r="AE179">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF179">
         <v>1.79</v>
@@ -29559,7 +29559,7 @@
         <v>1.2</v>
       </c>
       <c r="AK179">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AL179">
         <v>0</v>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -798,65 +798,65 @@
         </is>
       </c>
       <c r="N3">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O3">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="P3">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q3">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="R3">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="S3">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T3">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U3">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="V3">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="W3">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
         <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z3">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AA3">
         <v>1.95</v>
       </c>
       <c r="AB3">
+        <v>1.9</v>
+      </c>
+      <c r="AC3">
+        <v>3.08</v>
+      </c>
+      <c r="AD3">
+        <v>1.28</v>
+      </c>
+      <c r="AE3">
+        <v>1.07</v>
+      </c>
+      <c r="AF3">
+        <v>1.79</v>
+      </c>
+      <c r="AG3">
         <v>1.85</v>
       </c>
-      <c r="AC3">
-        <v>2.85</v>
-      </c>
-      <c r="AD3">
-        <v>1.27</v>
-      </c>
-      <c r="AE3">
-        <v>1.06</v>
-      </c>
-      <c r="AF3">
-        <v>1.8</v>
-      </c>
-      <c r="AG3">
-        <v>1.87</v>
-      </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>[]</t>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AK3">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="O5">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="P5">
         <v>3.37</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="O7">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P7">
-        <v>2.76</v>
+        <v>2.55</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -2102,55 +2102,55 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="O11">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="P11">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="Q11">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="R11">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="S11">
         <v>1.41</v>
       </c>
       <c r="T11">
-        <v>2.73</v>
+        <v>2.47</v>
       </c>
       <c r="U11">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="V11">
         <v>1.33</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X11">
         <v>1.06</v>
       </c>
       <c r="Y11">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z11">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AA11">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AB11">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AC11">
         <v>3.6</v>
       </c>
       <c r="AD11">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AE11">
         <v>1.06</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK11">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2597,7 +2597,7 @@
         <v>3.9</v>
       </c>
       <c r="P14">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="Q14">
         <v>1.9</v>
@@ -2606,37 +2606,37 @@
         <v>2.29</v>
       </c>
       <c r="S14">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T14">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U14">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V14">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W14">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X14">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
         <v>1.2</v>
       </c>
       <c r="Z14">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA14">
         <v>1.67</v>
       </c>
       <c r="AB14">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AC14">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="AD14">
         <v>1.46</v>
@@ -2648,7 +2648,7 @@
         <v>1.67</v>
       </c>
       <c r="AG14">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AK14">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2763,7 +2763,7 @@
         <v>0</v>
       </c>
       <c r="Q15">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="R15">
         <v>2.1</v>
@@ -2784,28 +2784,28 @@
         <v>1.04</v>
       </c>
       <c r="X15">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y15">
         <v>1.3</v>
       </c>
       <c r="Z15">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AA15">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB15">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC15">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AD15">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE15">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF15">
         <v>1.73</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK15">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3732,34 +3732,34 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="O21">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P21">
-        <v>3.2</v>
+        <v>3.39</v>
       </c>
       <c r="Q21">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="R21">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="S21">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T21">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="U21">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="V21">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W21">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X21">
         <v>1.01</v>
@@ -3771,7 +3771,7 @@
         <v>3.5</v>
       </c>
       <c r="AA21">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB21">
         <v>1.9</v>
@@ -3780,7 +3780,7 @@
         <v>2.92</v>
       </c>
       <c r="AD21">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AE21">
         <v>1.08</v>
@@ -3789,7 +3789,7 @@
         <v>1.67</v>
       </c>
       <c r="AG21">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK21">
         <v>1.73</v>
@@ -4058,58 +4058,58 @@
         </is>
       </c>
       <c r="N23">
-        <v>3.25</v>
+        <v>2.72</v>
       </c>
       <c r="O23">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P23">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="Q23">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="R23">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="S23">
         <v>1.3</v>
       </c>
       <c r="T23">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U23">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="V23">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W23">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X23">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z23">
-        <v>4.13</v>
+        <v>4.17</v>
       </c>
       <c r="AA23">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AB23">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AC23">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AD23">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE23">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF23">
         <v>1.67</v>
@@ -4221,28 +4221,28 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="O24">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="P24">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="Q24">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="R24">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="S24">
         <v>1.22</v>
       </c>
       <c r="T24">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="U24">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="V24">
         <v>1.6</v>
@@ -4254,10 +4254,10 @@
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z24">
-        <v>4.45</v>
+        <v>5</v>
       </c>
       <c r="AA24">
         <v>1.53</v>
@@ -4269,10 +4269,10 @@
         <v>2.5</v>
       </c>
       <c r="AD24">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AE24">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AF24">
         <v>1.53</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK24">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.12</v>
+        <v>2.75</v>
       </c>
       <c r="AK26">
         <v>1.05</v>
@@ -4710,34 +4710,34 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="O27">
         <v>4.6</v>
       </c>
       <c r="P27">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="Q27">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="R27">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="S27">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T27">
         <v>4.33</v>
       </c>
       <c r="U27">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V27">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W27">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X27">
         <v>1.01</v>
@@ -4746,22 +4746,22 @@
         <v>1.1</v>
       </c>
       <c r="Z27">
-        <v>6.1</v>
+        <v>6.15</v>
       </c>
       <c r="AA27">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AB27">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="AC27">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AD27">
         <v>1.89</v>
       </c>
       <c r="AE27">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AF27">
         <v>1.43</v>
@@ -4783,7 +4783,7 @@
         <v>1.15</v>
       </c>
       <c r="AK27">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,19 +4873,19 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="O28">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P28">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q28">
         <v>1.91</v>
       </c>
       <c r="R28">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="S28">
         <v>1.3</v>
@@ -4903,25 +4903,25 @@
         <v>1.12</v>
       </c>
       <c r="X28">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y28">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z28">
-        <v>4.25</v>
+        <v>4.1</v>
       </c>
       <c r="AA28">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB28">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AC28">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="AD28">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AE28">
         <v>1.17</v>
@@ -4930,7 +4930,7 @@
         <v>1.73</v>
       </c>
       <c r="AG28">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AK28">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5202,10 +5202,10 @@
         <v>2.2</v>
       </c>
       <c r="O30">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="P30">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="Q30">
         <v>2.61</v>
@@ -5214,13 +5214,13 @@
         <v>2.22</v>
       </c>
       <c r="S30">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T30">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="U30">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="V30">
         <v>1.57</v>
@@ -5229,10 +5229,10 @@
         <v>1.15</v>
       </c>
       <c r="X30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y30">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z30">
         <v>4</v>
@@ -5241,7 +5241,7 @@
         <v>1.64</v>
       </c>
       <c r="AB30">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AC30">
         <v>2.38</v>
@@ -5256,7 +5256,7 @@
         <v>1.55</v>
       </c>
       <c r="AG30">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="O40">
         <v>3.75</v>
@@ -6844,7 +6844,7 @@
         <v>2.38</v>
       </c>
       <c r="S40">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T40">
         <v>3.4</v>
@@ -6859,7 +6859,7 @@
         <v>1.12</v>
       </c>
       <c r="X40">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y40">
         <v>1.18</v>
@@ -6868,22 +6868,22 @@
         <v>4.5</v>
       </c>
       <c r="AA40">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AB40">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AC40">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="AD40">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AE40">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF40">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG40">
         <v>2.25</v>
@@ -7001,22 +7001,22 @@
         <v>2</v>
       </c>
       <c r="Q41">
-        <v>3.74</v>
+        <v>3.55</v>
       </c>
       <c r="R41">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S41">
         <v>1.29</v>
       </c>
       <c r="T41">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U41">
         <v>2.41</v>
       </c>
       <c r="V41">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W41">
         <v>1.08</v>
@@ -7031,25 +7031,25 @@
         <v>3.98</v>
       </c>
       <c r="AA41">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AB41">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AC41">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AD41">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE41">
         <v>1.12</v>
       </c>
       <c r="AF41">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AG41">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK41">
         <v>1.28</v>
@@ -7155,16 +7155,16 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="O42">
         <v>3.5</v>
       </c>
       <c r="P42">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q42">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="R42">
         <v>2.18</v>
@@ -7176,43 +7176,43 @@
         <v>3.14</v>
       </c>
       <c r="U42">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="V42">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="W42">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X42">
         <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z42">
         <v>4.2</v>
       </c>
       <c r="AA42">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB42">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AC42">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="AD42">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE42">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF42">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG42">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>1.22</v>
       </c>
       <c r="AK42">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7807,28 +7807,28 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="O46">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P46">
         <v>5</v>
       </c>
       <c r="Q46">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R46">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="S46">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T46">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="U46">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="V46">
         <v>1.4</v>
@@ -7837,34 +7837,34 @@
         <v>1.05</v>
       </c>
       <c r="X46">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z46">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="AA46">
         <v>1.95</v>
       </c>
       <c r="AB46">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AC46">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="AD46">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE46">
         <v>1.1</v>
       </c>
       <c r="AF46">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG46">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AK46">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7985,7 +7985,7 @@
         <v>2.45</v>
       </c>
       <c r="S47">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T47">
         <v>3.3</v>
@@ -7994,19 +7994,19 @@
         <v>2.36</v>
       </c>
       <c r="V47">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W47">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X47">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y47">
         <v>1.22</v>
       </c>
       <c r="Z47">
-        <v>4.4</v>
+        <v>4.67</v>
       </c>
       <c r="AA47">
         <v>1.62</v>
@@ -8021,13 +8021,13 @@
         <v>1.44</v>
       </c>
       <c r="AE47">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF47">
         <v>1.6</v>
       </c>
       <c r="AG47">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8296,10 +8296,10 @@
         </is>
       </c>
       <c r="N49">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="O49">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P49">
         <v>2.05</v>
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="O53">
-        <v>5.4</v>
+        <v>5.25</v>
       </c>
       <c r="P53">
-        <v>8.75</v>
+        <v>7.72</v>
       </c>
       <c r="Q53">
         <v>1.65</v>
@@ -8963,10 +8963,10 @@
         <v>2.8</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U53">
         <v>1.95</v>
@@ -8975,16 +8975,16 @@
         <v>1.67</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA53">
         <v>1.38</v>
@@ -10904,16 +10904,16 @@
         </is>
       </c>
       <c r="N65">
-        <v>4.3</v>
+        <v>5.02</v>
       </c>
       <c r="O65">
         <v>3.8</v>
       </c>
       <c r="P65">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="Q65">
-        <v>4.42</v>
+        <v>5.25</v>
       </c>
       <c r="R65">
         <v>2.38</v>
@@ -10922,7 +10922,7 @@
         <v>1.33</v>
       </c>
       <c r="T65">
-        <v>3.15</v>
+        <v>3.04</v>
       </c>
       <c r="U65">
         <v>2.47</v>
@@ -10946,10 +10946,10 @@
         <v>1.73</v>
       </c>
       <c r="AB65">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AC65">
-        <v>2.61</v>
+        <v>2.75</v>
       </c>
       <c r="AD65">
         <v>1.4</v>
@@ -10977,7 +10977,7 @@
         <v>2.28</v>
       </c>
       <c r="AK65">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,7 +11067,7 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="O66">
         <v>3.4</v>
@@ -11076,7 +11076,7 @@
         <v>2.7</v>
       </c>
       <c r="Q66">
-        <v>2.85</v>
+        <v>2.69</v>
       </c>
       <c r="R66">
         <v>2.37</v>
@@ -11088,7 +11088,7 @@
         <v>3.3</v>
       </c>
       <c r="U66">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="V66">
         <v>1.47</v>
@@ -11097,7 +11097,7 @@
         <v>1.08</v>
       </c>
       <c r="X66">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y66">
         <v>1.17</v>
@@ -11112,7 +11112,7 @@
         <v>2.15</v>
       </c>
       <c r="AC66">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AD66">
         <v>1.38</v>
@@ -11121,7 +11121,7 @@
         <v>1.13</v>
       </c>
       <c r="AF66">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG66">
         <v>2.3</v>
@@ -11140,7 +11140,7 @@
         <v>1.4</v>
       </c>
       <c r="AK66">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="O71">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="P71">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="Q71">
-        <v>2.16</v>
+        <v>2.7</v>
       </c>
       <c r="R71">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="S71">
+        <v>1.36</v>
+      </c>
+      <c r="T71">
+        <v>2.85</v>
+      </c>
+      <c r="U71">
+        <v>2.65</v>
+      </c>
+      <c r="V71">
+        <v>1.42</v>
+      </c>
+      <c r="W71">
+        <v>1.07</v>
+      </c>
+      <c r="X71">
+        <v>1.01</v>
+      </c>
+      <c r="Y71">
         <v>1.3</v>
       </c>
-      <c r="T71">
-        <v>3.2</v>
-      </c>
-      <c r="U71">
-        <v>2.73</v>
-      </c>
-      <c r="V71">
-        <v>1.44</v>
-      </c>
-      <c r="W71">
-        <v>1.06</v>
-      </c>
-      <c r="X71">
-        <v>1</v>
-      </c>
-      <c r="Y71">
-        <v>1.26</v>
-      </c>
       <c r="Z71">
-        <v>3.68</v>
+        <v>3.35</v>
       </c>
       <c r="AA71">
+        <v>1.9</v>
+      </c>
+      <c r="AB71">
         <v>1.85</v>
       </c>
-      <c r="AB71">
-        <v>1.93</v>
-      </c>
       <c r="AC71">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AD71">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE71">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF71">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AG71">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.09</v>
+        <v>1.31</v>
       </c>
       <c r="AK71">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,65 +12045,65 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="O72">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="P72">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="Q72">
-        <v>2.7</v>
+        <v>2.16</v>
       </c>
       <c r="R72">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="S72">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T72">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="U72">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="V72">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W72">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X72">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y72">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z72">
-        <v>3.35</v>
+        <v>3.68</v>
       </c>
       <c r="AA72">
+        <v>1.85</v>
+      </c>
+      <c r="AB72">
+        <v>1.93</v>
+      </c>
+      <c r="AC72">
+        <v>3.1</v>
+      </c>
+      <c r="AD72">
+        <v>1.33</v>
+      </c>
+      <c r="AE72">
+        <v>1.13</v>
+      </c>
+      <c r="AF72">
+        <v>1.77</v>
+      </c>
+      <c r="AG72">
         <v>1.9</v>
       </c>
-      <c r="AB72">
-        <v>1.85</v>
-      </c>
-      <c r="AC72">
-        <v>2.92</v>
-      </c>
-      <c r="AD72">
-        <v>1.31</v>
-      </c>
-      <c r="AE72">
-        <v>1.08</v>
-      </c>
-      <c r="AF72">
-        <v>1.7</v>
-      </c>
-      <c r="AG72">
-        <v>2</v>
-      </c>
       <c r="AH72" t="inlineStr">
         <is>
           <t>[]</t>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.31</v>
+        <v>1.09</v>
       </c>
       <c r="AK72">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12208,25 +12208,25 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="O73">
-        <v>3.62</v>
+        <v>3.76</v>
       </c>
       <c r="P73">
         <v>2.76</v>
       </c>
       <c r="Q73">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="R73">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="S73">
         <v>1.25</v>
       </c>
       <c r="T73">
-        <v>3.42</v>
+        <v>4</v>
       </c>
       <c r="U73">
         <v>2.25</v>
@@ -12241,7 +12241,7 @@
         <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z73">
         <v>5</v>
@@ -12253,19 +12253,19 @@
         <v>2.55</v>
       </c>
       <c r="AC73">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="AD73">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="AE73">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AF73">
         <v>1.44</v>
       </c>
       <c r="AG73">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>1.22</v>
       </c>
       <c r="AK73">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="O74">
         <v>5.75</v>
       </c>
       <c r="P74">
-        <v>8.5</v>
+        <v>6.95</v>
       </c>
       <c r="Q74">
         <v>1.57</v>
@@ -12392,10 +12392,10 @@
         <v>4.5</v>
       </c>
       <c r="U74">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="V74">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="W74">
         <v>1.25</v>
@@ -12413,7 +12413,7 @@
         <v>1.3</v>
       </c>
       <c r="AB74">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="AC74">
         <v>1.77</v>
@@ -12428,7 +12428,7 @@
         <v>1.55</v>
       </c>
       <c r="AG74">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AK74">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -13023,16 +13023,16 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="O78">
         <v>3.73</v>
       </c>
       <c r="P78">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="Q78">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="R78">
         <v>2.5</v>
@@ -13041,13 +13041,13 @@
         <v>1.2</v>
       </c>
       <c r="T78">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="U78">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="V78">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="W78">
         <v>1.18</v>
@@ -13056,13 +13056,13 @@
         <v>1.01</v>
       </c>
       <c r="Y78">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z78">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AA78">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AB78">
         <v>2.85</v>
@@ -13080,7 +13080,7 @@
         <v>1.3</v>
       </c>
       <c r="AG78">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13186,25 +13186,25 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="O79">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P79">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q79">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="R79">
         <v>2.5</v>
       </c>
       <c r="S79">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T79">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U79">
         <v>2.27</v>
@@ -13216,7 +13216,7 @@
         <v>1.12</v>
       </c>
       <c r="X79">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y79">
         <v>1.17</v>
@@ -13225,10 +13225,10 @@
         <v>4.8</v>
       </c>
       <c r="AA79">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB79">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="AC79">
         <v>2.28</v>
@@ -13243,7 +13243,7 @@
         <v>1.51</v>
       </c>
       <c r="AG79">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="O80">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="P80">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="Q80">
         <v>4</v>
@@ -13364,16 +13364,16 @@
         <v>2.88</v>
       </c>
       <c r="S80">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T80">
         <v>4.55</v>
       </c>
       <c r="U80">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="V80">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="W80">
         <v>1.25</v>
@@ -13382,7 +13382,7 @@
         <v>1.01</v>
       </c>
       <c r="Y80">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Z80">
         <v>7.1</v>
@@ -13391,7 +13391,7 @@
         <v>1.25</v>
       </c>
       <c r="AB80">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AC80">
         <v>1.67</v>
@@ -13400,13 +13400,13 @@
         <v>2.1</v>
       </c>
       <c r="AE80">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AF80">
         <v>1.37</v>
       </c>
       <c r="AG80">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="AK80">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13512,7 +13512,7 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="O81">
         <v>5.05</v>
@@ -13533,13 +13533,13 @@
         <v>5.25</v>
       </c>
       <c r="U81">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V81">
         <v>1.97</v>
       </c>
       <c r="W81">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X81">
         <v>1.01</v>
@@ -13569,7 +13569,7 @@
         <v>1.4</v>
       </c>
       <c r="AG81">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13675,25 +13675,25 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="O82">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P82">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="Q82">
-        <v>2.76</v>
+        <v>2.63</v>
       </c>
       <c r="R82">
         <v>2.7</v>
       </c>
       <c r="S82">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T82">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="U82">
         <v>1.84</v>
@@ -13702,7 +13702,7 @@
         <v>1.93</v>
       </c>
       <c r="W82">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X82">
         <v>1.01</v>
@@ -13726,7 +13726,7 @@
         <v>2</v>
       </c>
       <c r="AE82">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AF82">
         <v>1.3</v>
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="O83">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="P83">
-        <v>4.65</v>
+        <v>5</v>
       </c>
       <c r="Q83">
         <v>1.85</v>
@@ -13853,28 +13853,28 @@
         <v>2.76</v>
       </c>
       <c r="S83">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="T83">
         <v>4.6</v>
       </c>
       <c r="U83">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="V83">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="W83">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X83">
         <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z83">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AA83">
         <v>1.28</v>
@@ -13895,7 +13895,7 @@
         <v>1.36</v>
       </c>
       <c r="AG83">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>2.9</v>
       </c>
       <c r="Q96">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="R96">
         <v>2</v>
@@ -15978,10 +15978,10 @@
         <v>2.63</v>
       </c>
       <c r="U96">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="V96">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W96">
         <v>1.05</v>
@@ -15996,7 +15996,7 @@
         <v>2.92</v>
       </c>
       <c r="AA96">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AB96">
         <v>1.67</v>
@@ -16014,7 +16014,7 @@
         <v>1.8</v>
       </c>
       <c r="AG96">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16289,25 +16289,25 @@
         <v>3.25</v>
       </c>
       <c r="P98">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="Q98">
-        <v>4.17</v>
+        <v>3.7</v>
       </c>
       <c r="R98">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="S98">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T98">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="U98">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="V98">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W98">
         <v>1.07</v>
@@ -16316,31 +16316,31 @@
         <v>1.06</v>
       </c>
       <c r="Y98">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z98">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AA98">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB98">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AC98">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AD98">
         <v>1.25</v>
       </c>
       <c r="AE98">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF98">
         <v>1.83</v>
       </c>
       <c r="AG98">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AK98">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16935,31 +16935,31 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="O102">
-        <v>6.5</v>
+        <v>6.85</v>
       </c>
       <c r="P102">
-        <v>9.5</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="Q102">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="R102">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="S102">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="T102">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="U102">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V102">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="W102">
         <v>1.22</v>
@@ -16971,13 +16971,13 @@
         <v>1.02</v>
       </c>
       <c r="Z102">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="AA102">
         <v>1.28</v>
       </c>
       <c r="AB102">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AC102">
         <v>1.54</v>
@@ -16986,13 +16986,13 @@
         <v>2.23</v>
       </c>
       <c r="AE102">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AF102">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AG102">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17008,7 +17008,7 @@
         <v>1.03</v>
       </c>
       <c r="AK102">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -18082,7 +18082,7 @@
         <v>3.45</v>
       </c>
       <c r="P109">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="Q109">
         <v>2.42</v>
@@ -18731,7 +18731,7 @@
         <v>2</v>
       </c>
       <c r="O113">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="P113">
         <v>3.8</v>
@@ -18752,13 +18752,13 @@
         <v>3.75</v>
       </c>
       <c r="V113">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W113">
         <v>1.01</v>
       </c>
       <c r="X113">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Y113">
         <v>1.62</v>
@@ -18785,7 +18785,7 @@
         <v>2.38</v>
       </c>
       <c r="AG113">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -19380,58 +19380,58 @@
         </is>
       </c>
       <c r="N117">
-        <v>3.84</v>
+        <v>4.33</v>
       </c>
       <c r="O117">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P117">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Q117">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="R117">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="S117">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T117">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="U117">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="V117">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="W117">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X117">
         <v>1.03</v>
       </c>
       <c r="Y117">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z117">
-        <v>4.3</v>
+        <v>5.51</v>
       </c>
       <c r="AA117">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="AB117">
-        <v>2.18</v>
+        <v>2.55</v>
       </c>
       <c r="AC117">
-        <v>2.43</v>
+        <v>2.1</v>
       </c>
       <c r="AD117">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AE117">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF117">
         <v>1.55</v>
@@ -19450,7 +19450,7 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK117">
         <v>1.2</v>
@@ -19706,10 +19706,10 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.52</v>
+        <v>2.57</v>
       </c>
       <c r="O119">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="P119">
         <v>2.8</v>
@@ -19730,16 +19730,16 @@
         <v>4.6</v>
       </c>
       <c r="V119">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="W119">
         <v>1.02</v>
       </c>
       <c r="X119">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="Y119">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Z119">
         <v>1.98</v>
@@ -19754,7 +19754,7 @@
         <v>6</v>
       </c>
       <c r="AD119">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AE119">
         <v>1.02</v>
@@ -20524,49 +20524,49 @@
         <v>1.48</v>
       </c>
       <c r="O124">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P124">
-        <v>5.6</v>
+        <v>6.9</v>
       </c>
       <c r="Q124">
         <v>2.05</v>
       </c>
       <c r="R124">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S124">
         <v>1.51</v>
       </c>
       <c r="T124">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="U124">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="V124">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W124">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X124">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y124">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="Z124">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AA124">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AB124">
         <v>1.52</v>
       </c>
       <c r="AC124">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="AD124">
         <v>1.17</v>
@@ -20575,7 +20575,7 @@
         <v>1.04</v>
       </c>
       <c r="AF124">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AG124">
         <v>1.44</v>
@@ -20684,10 +20684,10 @@
         </is>
       </c>
       <c r="N125">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="O125">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="P125">
         <v>3.9</v>
@@ -20696,13 +20696,13 @@
         <v>2.8</v>
       </c>
       <c r="R125">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="S125">
         <v>1.7</v>
       </c>
       <c r="T125">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="U125">
         <v>3.95</v>
@@ -20723,7 +20723,7 @@
         <v>2.1</v>
       </c>
       <c r="AA125">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AB125">
         <v>1.33</v>
@@ -21010,19 +21010,19 @@
         </is>
       </c>
       <c r="N127">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="O127">
-        <v>4.95</v>
+        <v>4.85</v>
       </c>
       <c r="P127">
         <v>4.9</v>
       </c>
       <c r="Q127">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="R127">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="S127">
         <v>1.14</v>
@@ -21037,7 +21037,7 @@
         <v>1.92</v>
       </c>
       <c r="W127">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X127">
         <v>1.01</v>
@@ -21046,13 +21046,13 @@
         <v>1.03</v>
       </c>
       <c r="Z127">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AA127">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AB127">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="AC127">
         <v>1.68</v>
@@ -21067,7 +21067,7 @@
         <v>1.39</v>
       </c>
       <c r="AG127">
-        <v>2.72</v>
+        <v>2.3</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,7 +21080,7 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AK127">
         <v>2.61</v>
@@ -21173,19 +21173,19 @@
         </is>
       </c>
       <c r="N128">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="O128">
         <v>3.65</v>
       </c>
       <c r="P128">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="Q128">
         <v>2.45</v>
       </c>
       <c r="R128">
-        <v>2.49</v>
+        <v>2.69</v>
       </c>
       <c r="S128">
         <v>1.17</v>
@@ -21197,10 +21197,10 @@
         <v>1.91</v>
       </c>
       <c r="V128">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="W128">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X128">
         <v>1.01</v>
@@ -21218,10 +21218,10 @@
         <v>2.92</v>
       </c>
       <c r="AC128">
+        <v>1.9</v>
+      </c>
+      <c r="AD128">
         <v>1.85</v>
-      </c>
-      <c r="AD128">
-        <v>1.83</v>
       </c>
       <c r="AE128">
         <v>1.39</v>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK128">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21336,13 +21336,13 @@
         </is>
       </c>
       <c r="N129">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="O129">
-        <v>5.35</v>
+        <v>5</v>
       </c>
       <c r="P129">
-        <v>6.6</v>
+        <v>6.23</v>
       </c>
       <c r="Q129">
         <v>1.71</v>
@@ -21369,25 +21369,25 @@
         <v>1.01</v>
       </c>
       <c r="Y129">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z129">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="AA129">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AB129">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AC129">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AD129">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="AE129">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AF129">
         <v>1.58</v>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AK129">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21502,7 +21502,7 @@
         <v>1.91</v>
       </c>
       <c r="O130">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="P130">
         <v>3.25</v>
@@ -21514,10 +21514,10 @@
         <v>2.7</v>
       </c>
       <c r="S130">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="T130">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="U130">
         <v>1.8</v>
@@ -21538,7 +21538,7 @@
         <v>8.5</v>
       </c>
       <c r="AA130">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AB130">
         <v>3.5</v>
@@ -21547,16 +21547,16 @@
         <v>1.68</v>
       </c>
       <c r="AD130">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AE130">
         <v>1.44</v>
       </c>
       <c r="AF130">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AG130">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK130">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -22966,13 +22966,13 @@
         </is>
       </c>
       <c r="N139">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="O139">
         <v>3.6</v>
       </c>
       <c r="P139">
-        <v>6.25</v>
+        <v>6.95</v>
       </c>
       <c r="Q139">
         <v>2.1</v>
@@ -22984,7 +22984,7 @@
         <v>1.51</v>
       </c>
       <c r="T139">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="U139">
         <v>3.46</v>
@@ -23008,7 +23008,7 @@
         <v>2.41</v>
       </c>
       <c r="AB139">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AC139">
         <v>4.6</v>
@@ -23017,7 +23017,7 @@
         <v>1.13</v>
       </c>
       <c r="AE139">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AF139">
         <v>2.4</v>
@@ -23944,13 +23944,13 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="O145">
-        <v>3.78</v>
+        <v>3.85</v>
       </c>
       <c r="P145">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="Q145">
         <v>2.09</v>
@@ -23971,7 +23971,7 @@
         <v>1.36</v>
       </c>
       <c r="W145">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X145">
         <v>1.03</v>
@@ -23983,7 +23983,7 @@
         <v>3.48</v>
       </c>
       <c r="AA145">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="AB145">
         <v>1.84</v>
@@ -23995,7 +23995,7 @@
         <v>1.3</v>
       </c>
       <c r="AE145">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF145">
         <v>1.95</v>
@@ -24110,22 +24110,22 @@
         <v>1.9</v>
       </c>
       <c r="O146">
-        <v>3.54</v>
+        <v>3.42</v>
       </c>
       <c r="P146">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="Q146">
         <v>2.49</v>
       </c>
       <c r="R146">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="S146">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T146">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="U146">
         <v>2.65</v>
@@ -24149,22 +24149,22 @@
         <v>1.9</v>
       </c>
       <c r="AB146">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AC146">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="AD146">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE146">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF146">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG146">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -25251,10 +25251,10 @@
         <v>2.05</v>
       </c>
       <c r="O153">
-        <v>2.66</v>
+        <v>2.71</v>
       </c>
       <c r="P153">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -25411,16 +25411,16 @@
         </is>
       </c>
       <c r="N154">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="O154">
         <v>2.75</v>
       </c>
       <c r="P154">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q154">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R154">
         <v>1.85</v>
@@ -26063,7 +26063,7 @@
         </is>
       </c>
       <c r="N158">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="O158">
         <v>3.25</v>
@@ -26715,13 +26715,13 @@
         </is>
       </c>
       <c r="N162">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="O162">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P162">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Q162">
         <v>2.16</v>
@@ -26748,7 +26748,7 @@
         <v>1.06</v>
       </c>
       <c r="Y162">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Z162">
         <v>2.45</v>
@@ -26763,7 +26763,7 @@
         <v>4.6</v>
       </c>
       <c r="AD162">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AE162">
         <v>1.01</v>
@@ -27041,58 +27041,58 @@
         </is>
       </c>
       <c r="N164">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="O164">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="P164">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="Q164">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="R164">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="S164">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T164">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="U164">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="V164">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="W164">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X164">
         <v>1.01</v>
       </c>
       <c r="Y164">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Z164">
-        <v>4.33</v>
+        <v>8.5</v>
       </c>
       <c r="AA164">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AB164">
-        <v>3.34</v>
+        <v>3.55</v>
       </c>
       <c r="AC164">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AD164">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AE164">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AF164">
         <v>1.33</v>
@@ -27204,13 +27204,13 @@
         </is>
       </c>
       <c r="N165">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="O165">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="P165">
-        <v>4.45</v>
+        <v>4.2</v>
       </c>
       <c r="Q165">
         <v>2.8</v>
@@ -27222,7 +27222,7 @@
         <v>1.57</v>
       </c>
       <c r="T165">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="U165">
         <v>3.9</v>
@@ -27249,7 +27249,7 @@
         <v>1.34</v>
       </c>
       <c r="AC165">
-        <v>6.05</v>
+        <v>6.03</v>
       </c>
       <c r="AD165">
         <v>1.11</v>
@@ -27367,10 +27367,10 @@
         </is>
       </c>
       <c r="N166">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="O166">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="P166">
         <v>3.17</v>
@@ -27394,7 +27394,7 @@
         <v>1.5</v>
       </c>
       <c r="W166">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X166">
         <v>1</v>
@@ -27412,7 +27412,7 @@
         <v>2.04</v>
       </c>
       <c r="AC166">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="AD166">
         <v>1.37</v>
@@ -27440,7 +27440,7 @@
         <v>1.21</v>
       </c>
       <c r="AK166">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27530,16 +27530,16 @@
         </is>
       </c>
       <c r="N167">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O167">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="P167">
         <v>3.75</v>
       </c>
       <c r="Q167">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="R167">
         <v>1.85</v>
@@ -28182,13 +28182,13 @@
         </is>
       </c>
       <c r="N171">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O171">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="P171">
-        <v>3.54</v>
+        <v>3.2</v>
       </c>
       <c r="Q171">
         <v>2.62</v>
@@ -28206,19 +28206,19 @@
         <v>3.05</v>
       </c>
       <c r="V171">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W171">
         <v>1.05</v>
       </c>
       <c r="X171">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y171">
         <v>1.31</v>
       </c>
       <c r="Z171">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="AA171">
         <v>2.05</v>
@@ -28227,7 +28227,7 @@
         <v>1.7</v>
       </c>
       <c r="AC171">
-        <v>3.54</v>
+        <v>3.8</v>
       </c>
       <c r="AD171">
         <v>1.25</v>
@@ -28345,19 +28345,19 @@
         </is>
       </c>
       <c r="N172">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="O172">
         <v>3.18</v>
       </c>
       <c r="P172">
-        <v>3.02</v>
+        <v>3.5</v>
       </c>
       <c r="Q172">
         <v>2.75</v>
       </c>
       <c r="R172">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="S172">
         <v>1.4</v>
@@ -28372,7 +28372,7 @@
         <v>1.3</v>
       </c>
       <c r="W172">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X172">
         <v>1.06</v>
@@ -28381,13 +28381,13 @@
         <v>1.38</v>
       </c>
       <c r="Z172">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AA172">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AB172">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC172">
         <v>4.2</v>
@@ -28396,10 +28396,10 @@
         <v>1.23</v>
       </c>
       <c r="AE172">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF172">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG172">
         <v>1.85</v>
@@ -28418,7 +28418,7 @@
         <v>1.35</v>
       </c>
       <c r="AK172">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28834,13 +28834,13 @@
         </is>
       </c>
       <c r="N175">
-        <v>4.28</v>
+        <v>3.58</v>
       </c>
       <c r="O175">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P175">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="Q175">
         <v>4.4</v>
@@ -28997,13 +28997,13 @@
         </is>
       </c>
       <c r="N176">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="O176">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="P176">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q176">
         <v>1.61</v>
@@ -29027,13 +29027,13 @@
         <v>1.11</v>
       </c>
       <c r="X176">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y176">
         <v>1.15</v>
       </c>
       <c r="Z176">
-        <v>4.67</v>
+        <v>4.6</v>
       </c>
       <c r="AA176">
         <v>1.63</v>
@@ -29051,7 +29051,7 @@
         <v>1.16</v>
       </c>
       <c r="AF176">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG176">
         <v>1.62</v>
@@ -29160,10 +29160,10 @@
         </is>
       </c>
       <c r="N177">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O177">
-        <v>3.65</v>
+        <v>3.31</v>
       </c>
       <c r="P177">
         <v>1.76</v>
@@ -29175,7 +29175,7 @@
         <v>2.26</v>
       </c>
       <c r="S177">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T177">
         <v>3.2</v>
@@ -29202,16 +29202,16 @@
         <v>1.65</v>
       </c>
       <c r="AB177">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AC177">
         <v>2.63</v>
       </c>
       <c r="AD177">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AE177">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF177">
         <v>1.49</v>
@@ -29233,7 +29233,7 @@
         <v>1.19</v>
       </c>
       <c r="AK177">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29486,10 +29486,10 @@
         </is>
       </c>
       <c r="N179">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="O179">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P179">
         <v>3.8</v>
@@ -29513,7 +29513,7 @@
         <v>1.37</v>
       </c>
       <c r="W179">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X179">
         <v>1.05</v>
@@ -29688,7 +29688,7 @@
         <v>2.49</v>
       </c>
       <c r="AA180">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="AB180">
         <v>1.48</v>
@@ -29700,7 +29700,7 @@
         <v>1.12</v>
       </c>
       <c r="AE180">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF180">
         <v>2</v>
@@ -29833,7 +29833,7 @@
         <v>3.2</v>
       </c>
       <c r="U181">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="V181">
         <v>1.42</v>
@@ -29863,13 +29863,13 @@
         <v>1.33</v>
       </c>
       <c r="AE181">
-        <v>1.13</v>
+        <v>1.5</v>
       </c>
       <c r="AF181">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="AG181">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AH181" t="inlineStr">
         <is>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -638,13 +638,13 @@
         <v>3.83</v>
       </c>
       <c r="O2">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P2">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="Q2">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="R2">
         <v>1.97</v>
@@ -671,7 +671,7 @@
         <v>1.37</v>
       </c>
       <c r="Z2">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="AA2">
         <v>2.21</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AK2">
         <v>1.16</v>
@@ -1290,13 +1290,13 @@
         <v>3</v>
       </c>
       <c r="O6">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="P6">
-        <v>2.22</v>
+        <v>2.37</v>
       </c>
       <c r="Q6">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="R6">
         <v>2.05</v>
@@ -1323,7 +1323,7 @@
         <v>1.36</v>
       </c>
       <c r="Z6">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AA6">
         <v>2.22</v>
@@ -1975,7 +1975,7 @@
         <v>1.34</v>
       </c>
       <c r="Z10">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="AA10">
         <v>2.08</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="O20">
         <v>3.51</v>
       </c>
       <c r="P20">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="Q20">
         <v>2.28</v>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK20">
         <v>2.23</v>
@@ -8133,16 +8133,16 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="O48">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P48">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="Q48">
-        <v>2.88</v>
+        <v>3.16</v>
       </c>
       <c r="R48">
         <v>2.09</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,65 +11882,65 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="O71">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="P71">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="Q71">
-        <v>2.7</v>
+        <v>2.16</v>
       </c>
       <c r="R71">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="S71">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T71">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="U71">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="V71">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W71">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X71">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y71">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z71">
-        <v>3.35</v>
+        <v>3.68</v>
       </c>
       <c r="AA71">
+        <v>1.85</v>
+      </c>
+      <c r="AB71">
+        <v>1.93</v>
+      </c>
+      <c r="AC71">
+        <v>3.1</v>
+      </c>
+      <c r="AD71">
+        <v>1.33</v>
+      </c>
+      <c r="AE71">
+        <v>1.13</v>
+      </c>
+      <c r="AF71">
+        <v>1.77</v>
+      </c>
+      <c r="AG71">
         <v>1.9</v>
       </c>
-      <c r="AB71">
-        <v>1.85</v>
-      </c>
-      <c r="AC71">
-        <v>2.92</v>
-      </c>
-      <c r="AD71">
-        <v>1.31</v>
-      </c>
-      <c r="AE71">
-        <v>1.08</v>
-      </c>
-      <c r="AF71">
-        <v>1.7</v>
-      </c>
-      <c r="AG71">
-        <v>2</v>
-      </c>
       <c r="AH71" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.31</v>
+        <v>1.09</v>
       </c>
       <c r="AK71">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="O72">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="P72">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="Q72">
-        <v>2.16</v>
+        <v>2.7</v>
       </c>
       <c r="R72">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="S72">
+        <v>1.36</v>
+      </c>
+      <c r="T72">
+        <v>2.85</v>
+      </c>
+      <c r="U72">
+        <v>2.65</v>
+      </c>
+      <c r="V72">
+        <v>1.42</v>
+      </c>
+      <c r="W72">
+        <v>1.07</v>
+      </c>
+      <c r="X72">
+        <v>1.01</v>
+      </c>
+      <c r="Y72">
         <v>1.3</v>
       </c>
-      <c r="T72">
-        <v>3.2</v>
-      </c>
-      <c r="U72">
-        <v>2.73</v>
-      </c>
-      <c r="V72">
-        <v>1.44</v>
-      </c>
-      <c r="W72">
-        <v>1.06</v>
-      </c>
-      <c r="X72">
-        <v>1</v>
-      </c>
-      <c r="Y72">
-        <v>1.26</v>
-      </c>
       <c r="Z72">
-        <v>3.68</v>
+        <v>3.35</v>
       </c>
       <c r="AA72">
+        <v>1.9</v>
+      </c>
+      <c r="AB72">
         <v>1.85</v>
       </c>
-      <c r="AB72">
-        <v>1.93</v>
-      </c>
       <c r="AC72">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AD72">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE72">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF72">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AG72">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.09</v>
+        <v>1.31</v>
       </c>
       <c r="AK72">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12537,7 +12537,7 @@
         <v>2.65</v>
       </c>
       <c r="O75">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P75">
         <v>2.27</v>
@@ -12555,7 +12555,7 @@
         <v>2.69</v>
       </c>
       <c r="U75">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="V75">
         <v>1.38</v>
@@ -12573,7 +12573,7 @@
         <v>3.25</v>
       </c>
       <c r="AA75">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AB75">
         <v>1.78</v>
@@ -12703,10 +12703,10 @@
         <v>3.61</v>
       </c>
       <c r="P76">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="Q76">
-        <v>4.2</v>
+        <v>4.26</v>
       </c>
       <c r="R76">
         <v>2.28</v>
@@ -12739,7 +12739,7 @@
         <v>1.61</v>
       </c>
       <c r="AB76">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AC76">
         <v>2.43</v>
@@ -12748,7 +12748,7 @@
         <v>1.44</v>
       </c>
       <c r="AE76">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF76">
         <v>1.53</v>
@@ -14330,10 +14330,10 @@
         <v>1.68</v>
       </c>
       <c r="O86">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P86">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="Q86">
         <v>2.39</v>
@@ -14342,10 +14342,10 @@
         <v>1.99</v>
       </c>
       <c r="S86">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="T86">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="U86">
         <v>3.28</v>
@@ -14366,13 +14366,13 @@
         <v>2.62</v>
       </c>
       <c r="AA86">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AB86">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AC86">
-        <v>4.3</v>
+        <v>4.35</v>
       </c>
       <c r="AD86">
         <v>1.2</v>
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="O90">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P90">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="Q90">
         <v>2.87</v>
@@ -14997,7 +14997,7 @@
         <v>1.3</v>
       </c>
       <c r="T90">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="U90">
         <v>2.59</v>
@@ -15009,7 +15009,7 @@
         <v>1.1</v>
       </c>
       <c r="X90">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y90">
         <v>1.2</v>
@@ -15018,10 +15018,10 @@
         <v>4.1</v>
       </c>
       <c r="AA90">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AB90">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AC90">
         <v>3.1</v>
@@ -16455,7 +16455,7 @@
         <v>4.1</v>
       </c>
       <c r="Q99">
-        <v>2.76</v>
+        <v>2.89</v>
       </c>
       <c r="R99">
         <v>1.77</v>
@@ -16464,7 +16464,7 @@
         <v>1.59</v>
       </c>
       <c r="T99">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="U99">
         <v>3.3</v>
@@ -16482,7 +16482,7 @@
         <v>1.38</v>
       </c>
       <c r="Z99">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="AA99">
         <v>2.35</v>
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="O111">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P111">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="Q111">
         <v>3.1</v>
@@ -18426,7 +18426,7 @@
         <v>2.56</v>
       </c>
       <c r="V111">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W111">
         <v>1.06</v>
@@ -18453,7 +18453,7 @@
         <v>1.3</v>
       </c>
       <c r="AE111">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF111">
         <v>1.67</v>
@@ -18891,46 +18891,46 @@
         </is>
       </c>
       <c r="N114">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O114">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P114">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="Q114">
-        <v>4.16</v>
+        <v>4.09</v>
       </c>
       <c r="R114">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="S114">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T114">
         <v>2.88</v>
       </c>
       <c r="U114">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="V114">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W114">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X114">
         <v>1</v>
       </c>
       <c r="Y114">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z114">
         <v>3.7</v>
       </c>
       <c r="AA114">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB114">
         <v>1.95</v>
@@ -18942,13 +18942,13 @@
         <v>1.35</v>
       </c>
       <c r="AE114">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF114">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG114">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK114">
         <v>1.28</v>
@@ -19057,7 +19057,7 @@
         <v>2.12</v>
       </c>
       <c r="O115">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P115">
         <v>3.05</v>
@@ -19069,10 +19069,10 @@
         <v>2.22</v>
       </c>
       <c r="S115">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T115">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U115">
         <v>2.54</v>
@@ -19090,13 +19090,13 @@
         <v>1.21</v>
       </c>
       <c r="Z115">
-        <v>4.32</v>
+        <v>4.37</v>
       </c>
       <c r="AA115">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AB115">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AC115">
         <v>2.65</v>
@@ -20038,7 +20038,7 @@
         <v>3.21</v>
       </c>
       <c r="P121">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q121">
         <v>2.52</v>
@@ -20047,13 +20047,13 @@
         <v>2.06</v>
       </c>
       <c r="S121">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T121">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="U121">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="V121">
         <v>1.33</v>
@@ -20068,7 +20068,7 @@
         <v>1.35</v>
       </c>
       <c r="Z121">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="AA121">
         <v>2.18</v>
@@ -20102,7 +20102,7 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK121">
         <v>1.86</v>
@@ -25589,7 +25589,7 @@
         <v>2.5</v>
       </c>
       <c r="S155">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T155">
         <v>3.36</v>
@@ -25607,16 +25607,16 @@
         <v>1.03</v>
       </c>
       <c r="Y155">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z155">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AA155">
         <v>1.65</v>
       </c>
       <c r="AB155">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AC155">
         <v>2.6</v>
@@ -25625,13 +25625,13 @@
         <v>1.48</v>
       </c>
       <c r="AE155">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AF155">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG155">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O5">
         <v>3.1</v>
       </c>
       <c r="P5">
-        <v>3.37</v>
+        <v>2.97</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="N6">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O6">
         <v>3</v>
@@ -1308,7 +1308,7 @@
         <v>2.47</v>
       </c>
       <c r="U6">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="V6">
         <v>1.31</v>
@@ -1453,10 +1453,10 @@
         <v>2.55</v>
       </c>
       <c r="O7">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P7">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1613,16 +1613,16 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="O8">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="P8">
         <v>2.15</v>
       </c>
       <c r="Q8">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="R8">
         <v>2</v>
@@ -1649,7 +1649,7 @@
         <v>1.37</v>
       </c>
       <c r="Z8">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="AA8">
         <v>2.19</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="O10">
         <v>3.2</v>
       </c>
       <c r="P10">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="Q10">
         <v>3.64</v>
@@ -1993,10 +1993,10 @@
         <v>1.05</v>
       </c>
       <c r="AF10">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AG10">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2102,19 +2102,19 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O11">
         <v>2.9</v>
       </c>
       <c r="P11">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
       </c>
       <c r="R11">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="S11">
         <v>1.41</v>
@@ -2138,7 +2138,7 @@
         <v>1.3</v>
       </c>
       <c r="Z11">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="AA11">
         <v>2.05</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK11">
         <v>1.43</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="O14">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="P14">
         <v>5</v>
@@ -2621,13 +2621,13 @@
         <v>1.09</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y14">
         <v>1.2</v>
       </c>
       <c r="Z14">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA14">
         <v>1.67</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AK14">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="O16">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="P16">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q16">
         <v>4.18</v>
@@ -2947,7 +2947,7 @@
         <v>1.17</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
         <v>1.1</v>
@@ -2959,7 +2959,7 @@
         <v>1.4</v>
       </c>
       <c r="AB16">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="AC16">
         <v>2.02</v>
@@ -3080,16 +3080,16 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="O17">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="P17">
-        <v>3.02</v>
+        <v>2.95</v>
       </c>
       <c r="Q17">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="R17">
         <v>2.17</v>
@@ -3104,7 +3104,7 @@
         <v>2.4</v>
       </c>
       <c r="V17">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="W17">
         <v>1.11</v>
@@ -3122,7 +3122,7 @@
         <v>1.67</v>
       </c>
       <c r="AB17">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC17">
         <v>2.57</v>
@@ -3131,13 +3131,13 @@
         <v>1.4</v>
       </c>
       <c r="AE17">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF17">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG17">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="O18">
         <v>3.54</v>
@@ -3273,13 +3273,13 @@
         <v>1.09</v>
       </c>
       <c r="X18">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y18">
         <v>1.17</v>
       </c>
       <c r="Z18">
-        <v>4.35</v>
+        <v>4.58</v>
       </c>
       <c r="AA18">
         <v>1.63</v>
@@ -3288,10 +3288,10 @@
         <v>2.14</v>
       </c>
       <c r="AC18">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AD18">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AE18">
         <v>1.2</v>
@@ -3300,7 +3300,7 @@
         <v>1.55</v>
       </c>
       <c r="AG18">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>2.25</v>
       </c>
       <c r="V19">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="W19">
         <v>1.11</v>
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="O20">
         <v>3.51</v>
@@ -3602,7 +3602,7 @@
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z20">
         <v>3</v>
@@ -3623,10 +3623,10 @@
         <v>1.03</v>
       </c>
       <c r="AF20">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AG20">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK20">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3765,22 +3765,22 @@
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z21">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AA21">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB21">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AC21">
         <v>2.92</v>
       </c>
       <c r="AD21">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AE21">
         <v>1.08</v>
@@ -4058,19 +4058,19 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="O23">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P23">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
       <c r="Q23">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="R23">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S23">
         <v>1.3</v>
@@ -4079,7 +4079,7 @@
         <v>3.1</v>
       </c>
       <c r="U23">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V23">
         <v>1.45</v>
@@ -4091,28 +4091,28 @@
         <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z23">
-        <v>4.17</v>
+        <v>4.07</v>
       </c>
       <c r="AA23">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AB23">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC23">
-        <v>2.77</v>
+        <v>2.83</v>
       </c>
       <c r="AD23">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE23">
         <v>1.14</v>
       </c>
       <c r="AF23">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG23">
         <v>2.02</v>
@@ -4131,7 +4131,7 @@
         <v>1.3</v>
       </c>
       <c r="AK23">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="O24">
-        <v>3.7</v>
+        <v>3.52</v>
       </c>
       <c r="P24">
-        <v>4.2</v>
+        <v>3.27</v>
       </c>
       <c r="Q24">
         <v>2.19</v>
@@ -4269,7 +4269,7 @@
         <v>2.5</v>
       </c>
       <c r="AD24">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AE24">
         <v>1.19</v>
@@ -4278,7 +4278,7 @@
         <v>1.53</v>
       </c>
       <c r="AG24">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4547,49 +4547,49 @@
         </is>
       </c>
       <c r="N26">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O26">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="P26">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="Q26">
-        <v>6.5</v>
+        <v>6.73</v>
       </c>
       <c r="R26">
         <v>2.55</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U26">
         <v>2.25</v>
       </c>
       <c r="V26">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z26">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AA26">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AB26">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AC26">
         <v>2.45</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>2.75</v>
+        <v>1.12</v>
       </c>
       <c r="AK26">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="O27">
         <v>4.6</v>
@@ -4749,25 +4749,25 @@
         <v>6.15</v>
       </c>
       <c r="AA27">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AB27">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AC27">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AD27">
         <v>1.89</v>
       </c>
       <c r="AE27">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AF27">
         <v>1.43</v>
       </c>
       <c r="AG27">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>1.15</v>
       </c>
       <c r="AK27">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="O28">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P28">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="Q28">
         <v>1.91</v>
@@ -4903,25 +4903,25 @@
         <v>1.12</v>
       </c>
       <c r="X28">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z28">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="AA28">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AB28">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AC28">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="AD28">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE28">
         <v>1.17</v>
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="O30">
         <v>3.3</v>
@@ -5226,13 +5226,13 @@
         <v>1.57</v>
       </c>
       <c r="W30">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z30">
         <v>4</v>
@@ -5241,7 +5241,7 @@
         <v>1.64</v>
       </c>
       <c r="AB30">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="AC30">
         <v>2.38</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.35</v>
+        <v>2.65</v>
       </c>
       <c r="O32">
         <v>3.1</v>
       </c>
       <c r="P32">
-        <v>2.84</v>
+        <v>2.5</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -6201,7 +6201,7 @@
         <v>2.8</v>
       </c>
       <c r="V36">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W36">
         <v>1.08</v>
@@ -6210,19 +6210,19 @@
         <v>1.06</v>
       </c>
       <c r="Y36">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z36">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="AA36">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AB36">
         <v>1.81</v>
       </c>
       <c r="AC36">
-        <v>3.56</v>
+        <v>3.59</v>
       </c>
       <c r="AD36">
         <v>1.25</v>
@@ -6250,7 +6250,7 @@
         <v>1.4</v>
       </c>
       <c r="AK36">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6560,7 +6560,7 @@
         <v>1.7</v>
       </c>
       <c r="AG38">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6829,22 +6829,22 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="O40">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="P40">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="Q40">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="R40">
         <v>2.38</v>
       </c>
       <c r="S40">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T40">
         <v>3.4</v>
@@ -6859,7 +6859,7 @@
         <v>1.12</v>
       </c>
       <c r="X40">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
         <v>1.18</v>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="N41">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O41">
         <v>3.4</v>
@@ -7004,43 +7004,43 @@
         <v>3.55</v>
       </c>
       <c r="R41">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="S41">
         <v>1.29</v>
       </c>
       <c r="T41">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U41">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="V41">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W41">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X41">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
         <v>1.2</v>
       </c>
       <c r="Z41">
-        <v>3.98</v>
+        <v>4.5</v>
       </c>
       <c r="AA41">
         <v>1.63</v>
       </c>
       <c r="AB41">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AC41">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AD41">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE41">
         <v>1.12</v>
@@ -7167,52 +7167,52 @@
         <v>3.35</v>
       </c>
       <c r="R42">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="S42">
         <v>1.28</v>
       </c>
       <c r="T42">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="U42">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="V42">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W42">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X42">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y42">
+        <v>1.16</v>
+      </c>
+      <c r="Z42">
+        <v>4</v>
+      </c>
+      <c r="AA42">
+        <v>1.7</v>
+      </c>
+      <c r="AB42">
+        <v>2.05</v>
+      </c>
+      <c r="AC42">
+        <v>2.7</v>
+      </c>
+      <c r="AD42">
+        <v>1.4</v>
+      </c>
+      <c r="AE42">
         <v>1.15</v>
       </c>
-      <c r="Z42">
-        <v>4.2</v>
-      </c>
-      <c r="AA42">
-        <v>1.62</v>
-      </c>
-      <c r="AB42">
-        <v>2.15</v>
-      </c>
-      <c r="AC42">
-        <v>2.6</v>
-      </c>
-      <c r="AD42">
-        <v>1.44</v>
-      </c>
-      <c r="AE42">
-        <v>1.12</v>
-      </c>
       <c r="AF42">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG42">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK42">
         <v>1.28</v>
@@ -7318,19 +7318,19 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="O43">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="P43">
-        <v>4.51</v>
+        <v>4.37</v>
       </c>
       <c r="Q43">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="R43">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="S43">
         <v>1.3</v>
@@ -7354,16 +7354,16 @@
         <v>1.23</v>
       </c>
       <c r="Z43">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="AA43">
-        <v>1.63</v>
+        <v>1.81</v>
       </c>
       <c r="AB43">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="AC43">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="AD43">
         <v>1.36</v>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK43">
         <v>2.1</v>
@@ -7481,16 +7481,16 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="O44">
-        <v>3.5</v>
+        <v>3.61</v>
       </c>
       <c r="P44">
-        <v>4</v>
+        <v>4.01</v>
       </c>
       <c r="Q44">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="R44">
         <v>2.1</v>
@@ -7499,16 +7499,16 @@
         <v>1.36</v>
       </c>
       <c r="T44">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="U44">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="V44">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W44">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X44">
         <v>1.02</v>
@@ -7526,16 +7526,16 @@
         <v>1.8</v>
       </c>
       <c r="AC44">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AD44">
         <v>1.27</v>
       </c>
       <c r="AE44">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF44">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AG44">
         <v>2</v>
@@ -7554,7 +7554,7 @@
         <v>1.22</v>
       </c>
       <c r="AK44">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -8459,19 +8459,19 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="O50">
-        <v>8.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="P50">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q50">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="R50">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="S50">
         <v>1.2</v>
@@ -8495,7 +8495,7 @@
         <v>1.06</v>
       </c>
       <c r="Z50">
-        <v>6.07</v>
+        <v>6.05</v>
       </c>
       <c r="AA50">
         <v>1.38</v>
@@ -8507,16 +8507,16 @@
         <v>2.02</v>
       </c>
       <c r="AD50">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AE50">
         <v>1.32</v>
       </c>
       <c r="AF50">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AG50">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>1.08</v>
       </c>
       <c r="AK50">
-        <v>6.15</v>
+        <v>6.25</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="O55">
-        <v>3.81</v>
+        <v>3.3</v>
       </c>
       <c r="P55">
-        <v>3.81</v>
+        <v>4</v>
       </c>
       <c r="Q55">
         <v>2.3</v>
@@ -9289,7 +9289,7 @@
         <v>2.2</v>
       </c>
       <c r="S55">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T55">
         <v>2.95</v>
@@ -9298,10 +9298,10 @@
         <v>2.75</v>
       </c>
       <c r="V55">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W55">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X55">
         <v>1.02</v>
@@ -9310,10 +9310,10 @@
         <v>1.24</v>
       </c>
       <c r="Z55">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AA55">
-        <v>2.06</v>
+        <v>1.87</v>
       </c>
       <c r="AB55">
         <v>1.92</v>
@@ -10415,40 +10415,40 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="O62">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="P62">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q62">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="R62">
         <v>2.1</v>
       </c>
       <c r="S62">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="T62">
         <v>2.8</v>
       </c>
       <c r="U62">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="V62">
         <v>1.36</v>
       </c>
       <c r="W62">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X62">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y62">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z62">
         <v>3</v>
@@ -10463,17 +10463,17 @@
         <v>3.7</v>
       </c>
       <c r="AD62">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE62">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF62">
+        <v>1.85</v>
+      </c>
+      <c r="AG62">
         <v>1.83</v>
       </c>
-      <c r="AG62">
-        <v>1.85</v>
-      </c>
       <c r="AH62" t="inlineStr">
         <is>
           <t>[]</t>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK62">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,7 +10578,7 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="O63">
         <v>2.9</v>
@@ -10590,13 +10590,13 @@
         <v>3.2</v>
       </c>
       <c r="R63">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="S63">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="T63">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="U63">
         <v>3.52</v>
@@ -10620,7 +10620,7 @@
         <v>2.53</v>
       </c>
       <c r="AB63">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AC63">
         <v>5</v>
@@ -10635,7 +10635,7 @@
         <v>2.05</v>
       </c>
       <c r="AG63">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O64">
         <v>3.4</v>
@@ -10762,7 +10762,7 @@
         <v>2.8</v>
       </c>
       <c r="U64">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="V64">
         <v>1.63</v>
@@ -10814,7 +10814,7 @@
         <v>1.29</v>
       </c>
       <c r="AK64">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10904,7 +10904,7 @@
         </is>
       </c>
       <c r="N65">
-        <v>5.02</v>
+        <v>4.5</v>
       </c>
       <c r="O65">
         <v>3.8</v>
@@ -10913,7 +10913,7 @@
         <v>1.57</v>
       </c>
       <c r="Q65">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="R65">
         <v>2.38</v>
@@ -10943,10 +10943,10 @@
         <v>3.84</v>
       </c>
       <c r="AA65">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AB65">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="AC65">
         <v>2.75</v>
@@ -10977,7 +10977,7 @@
         <v>2.28</v>
       </c>
       <c r="AK65">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11070,10 +11070,10 @@
         <v>2.35</v>
       </c>
       <c r="O66">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P66">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="Q66">
         <v>2.69</v>
@@ -11097,7 +11097,7 @@
         <v>1.08</v>
       </c>
       <c r="X66">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y66">
         <v>1.17</v>
@@ -11109,16 +11109,16 @@
         <v>1.7</v>
       </c>
       <c r="AB66">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AC66">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AD66">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE66">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF66">
         <v>1.53</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="O71">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="P71">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="Q71">
-        <v>2.16</v>
+        <v>2.7</v>
       </c>
       <c r="R71">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="S71">
+        <v>1.36</v>
+      </c>
+      <c r="T71">
+        <v>2.85</v>
+      </c>
+      <c r="U71">
+        <v>2.65</v>
+      </c>
+      <c r="V71">
+        <v>1.42</v>
+      </c>
+      <c r="W71">
+        <v>1.07</v>
+      </c>
+      <c r="X71">
+        <v>1.01</v>
+      </c>
+      <c r="Y71">
         <v>1.3</v>
       </c>
-      <c r="T71">
-        <v>3.2</v>
-      </c>
-      <c r="U71">
-        <v>2.73</v>
-      </c>
-      <c r="V71">
-        <v>1.44</v>
-      </c>
-      <c r="W71">
-        <v>1.06</v>
-      </c>
-      <c r="X71">
-        <v>1</v>
-      </c>
-      <c r="Y71">
-        <v>1.26</v>
-      </c>
       <c r="Z71">
-        <v>3.68</v>
+        <v>3.35</v>
       </c>
       <c r="AA71">
+        <v>1.9</v>
+      </c>
+      <c r="AB71">
         <v>1.85</v>
       </c>
-      <c r="AB71">
-        <v>1.93</v>
-      </c>
       <c r="AC71">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AD71">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE71">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF71">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AG71">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.09</v>
+        <v>1.31</v>
       </c>
       <c r="AK71">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,65 +12045,65 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="O72">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="P72">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="Q72">
-        <v>2.7</v>
+        <v>2.16</v>
       </c>
       <c r="R72">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="S72">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T72">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="U72">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="V72">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W72">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X72">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y72">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z72">
-        <v>3.35</v>
+        <v>3.68</v>
       </c>
       <c r="AA72">
+        <v>1.85</v>
+      </c>
+      <c r="AB72">
+        <v>1.93</v>
+      </c>
+      <c r="AC72">
+        <v>3.1</v>
+      </c>
+      <c r="AD72">
+        <v>1.33</v>
+      </c>
+      <c r="AE72">
+        <v>1.13</v>
+      </c>
+      <c r="AF72">
+        <v>1.77</v>
+      </c>
+      <c r="AG72">
         <v>1.9</v>
       </c>
-      <c r="AB72">
-        <v>1.85</v>
-      </c>
-      <c r="AC72">
-        <v>2.92</v>
-      </c>
-      <c r="AD72">
-        <v>1.31</v>
-      </c>
-      <c r="AE72">
-        <v>1.08</v>
-      </c>
-      <c r="AF72">
-        <v>1.7</v>
-      </c>
-      <c r="AG72">
-        <v>2</v>
-      </c>
       <c r="AH72" t="inlineStr">
         <is>
           <t>[]</t>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.31</v>
+        <v>1.09</v>
       </c>
       <c r="AK72">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12220,7 +12220,7 @@
         <v>2.55</v>
       </c>
       <c r="R73">
-        <v>2.53</v>
+        <v>2.32</v>
       </c>
       <c r="S73">
         <v>1.25</v>
@@ -12256,10 +12256,10 @@
         <v>2.29</v>
       </c>
       <c r="AD73">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AE73">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF73">
         <v>1.44</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="O74">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="P74">
-        <v>6.95</v>
+        <v>7.15</v>
       </c>
       <c r="Q74">
         <v>1.57</v>
@@ -12410,7 +12410,7 @@
         <v>8</v>
       </c>
       <c r="AA74">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AB74">
         <v>2.75</v>
@@ -12422,7 +12422,7 @@
         <v>1.95</v>
       </c>
       <c r="AE74">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AF74">
         <v>1.55</v>
@@ -13029,22 +13029,22 @@
         <v>3.73</v>
       </c>
       <c r="P78">
-        <v>2.37</v>
+        <v>2.17</v>
       </c>
       <c r="Q78">
         <v>2.7</v>
       </c>
       <c r="R78">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="S78">
         <v>1.2</v>
       </c>
       <c r="T78">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="U78">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V78">
         <v>1.73</v>
@@ -13065,22 +13065,22 @@
         <v>1.35</v>
       </c>
       <c r="AB78">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AC78">
         <v>1.96</v>
       </c>
       <c r="AD78">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AE78">
         <v>1.3</v>
       </c>
       <c r="AF78">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AG78">
-        <v>2.9</v>
+        <v>2.99</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13192,7 +13192,7 @@
         <v>3.5</v>
       </c>
       <c r="P79">
-        <v>3.3</v>
+        <v>3.03</v>
       </c>
       <c r="Q79">
         <v>2.31</v>
@@ -13201,16 +13201,16 @@
         <v>2.5</v>
       </c>
       <c r="S79">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T79">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U79">
         <v>2.27</v>
       </c>
       <c r="V79">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W79">
         <v>1.12</v>
@@ -13225,10 +13225,10 @@
         <v>4.8</v>
       </c>
       <c r="AA79">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB79">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="AC79">
         <v>2.28</v>
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="O80">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="P80">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="Q80">
         <v>4</v>
@@ -13364,16 +13364,16 @@
         <v>2.88</v>
       </c>
       <c r="S80">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T80">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="U80">
         <v>1.85</v>
       </c>
       <c r="V80">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="W80">
         <v>1.25</v>
@@ -13385,7 +13385,7 @@
         <v>1.06</v>
       </c>
       <c r="Z80">
-        <v>7.1</v>
+        <v>6.95</v>
       </c>
       <c r="AA80">
         <v>1.25</v>
@@ -13394,19 +13394,19 @@
         <v>3.28</v>
       </c>
       <c r="AC80">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AD80">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AE80">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AF80">
         <v>1.37</v>
       </c>
       <c r="AG80">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13512,16 +13512,16 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="O81">
-        <v>5.05</v>
+        <v>5.25</v>
       </c>
       <c r="P81">
-        <v>5.6</v>
+        <v>5.75</v>
       </c>
       <c r="Q81">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="R81">
         <v>3</v>
@@ -13548,28 +13548,28 @@
         <v>1.02</v>
       </c>
       <c r="Z81">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="AA81">
         <v>1.27</v>
       </c>
       <c r="AB81">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AC81">
         <v>1.62</v>
       </c>
       <c r="AD81">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="AE81">
         <v>1.54</v>
       </c>
       <c r="AF81">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AG81">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>1.08</v>
       </c>
       <c r="AK81">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13675,16 +13675,16 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="O82">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P82">
-        <v>2.37</v>
+        <v>2.41</v>
       </c>
       <c r="Q82">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="R82">
         <v>2.7</v>
@@ -13693,7 +13693,7 @@
         <v>1.15</v>
       </c>
       <c r="T82">
-        <v>4.75</v>
+        <v>4.45</v>
       </c>
       <c r="U82">
         <v>1.84</v>
@@ -13708,7 +13708,7 @@
         <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z82">
         <v>6.39</v>
@@ -13717,7 +13717,7 @@
         <v>1.3</v>
       </c>
       <c r="AB82">
-        <v>3.39</v>
+        <v>3.42</v>
       </c>
       <c r="AC82">
         <v>1.73</v>
@@ -13838,34 +13838,34 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="O83">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="P83">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="Q83">
         <v>1.85</v>
       </c>
       <c r="R83">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="S83">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T83">
         <v>4.6</v>
       </c>
       <c r="U83">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="V83">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="W83">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X83">
         <v>1.01</v>
@@ -13877,7 +13877,7 @@
         <v>8</v>
       </c>
       <c r="AA83">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AB83">
         <v>3.6</v>
@@ -13895,7 +13895,7 @@
         <v>1.36</v>
       </c>
       <c r="AG83">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>3</v>
+        <v>3.32</v>
       </c>
       <c r="O84">
-        <v>3.31</v>
+        <v>3.15</v>
       </c>
       <c r="P84">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="Q84">
         <v>3.8</v>
@@ -14025,7 +14025,7 @@
         <v>3</v>
       </c>
       <c r="V84">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W84">
         <v>1.04</v>
@@ -14058,7 +14058,7 @@
         <v>2</v>
       </c>
       <c r="AG84">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14816,10 +14816,10 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="O89">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P89">
         <v>4.6</v>
@@ -14834,13 +14834,13 @@
         <v>1.29</v>
       </c>
       <c r="T89">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U89">
-        <v>2.25</v>
+        <v>2.41</v>
       </c>
       <c r="V89">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W89">
         <v>1.08</v>
@@ -14855,13 +14855,13 @@
         <v>4.33</v>
       </c>
       <c r="AA89">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AB89">
         <v>2.15</v>
       </c>
       <c r="AC89">
-        <v>2.55</v>
+        <v>2.41</v>
       </c>
       <c r="AD89">
         <v>1.5</v>
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O100">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q100">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R100">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S100">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T100">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U100">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V100">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W100">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X100">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y100">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z100">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA100">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB100">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC100">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD100">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE100">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF100">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG100">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK100">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16772,10 +16772,10 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.55</v>
+        <v>2.39</v>
       </c>
       <c r="O101">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="P101">
         <v>2.85</v>
@@ -16793,10 +16793,10 @@
         <v>2.43</v>
       </c>
       <c r="U101">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="V101">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W101">
         <v>1.05</v>
@@ -16829,7 +16829,7 @@
         <v>2.01</v>
       </c>
       <c r="AG101">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O110">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q110">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R110">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S110">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T110">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U110">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V110">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W110">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X110">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y110">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z110">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA110">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB110">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC110">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD110">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE110">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF110">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG110">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK110">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -19057,7 +19057,7 @@
         <v>2.12</v>
       </c>
       <c r="O115">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P115">
         <v>3.05</v>
@@ -19078,10 +19078,10 @@
         <v>2.54</v>
       </c>
       <c r="V115">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="W115">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X115">
         <v>1.02</v>
@@ -19096,16 +19096,16 @@
         <v>1.72</v>
       </c>
       <c r="AB115">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AC115">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="AD115">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AE115">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AF115">
         <v>1.58</v>
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="O117">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="P117">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="Q117">
         <v>4.2</v>
@@ -19416,10 +19416,10 @@
         <v>1.11</v>
       </c>
       <c r="Z117">
-        <v>5.51</v>
+        <v>5.4</v>
       </c>
       <c r="AA117">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AB117">
         <v>2.55</v>
@@ -19453,7 +19453,7 @@
         <v>1.22</v>
       </c>
       <c r="AK117">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19869,19 +19869,19 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="O120">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="P120">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
       </c>
       <c r="R120">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="S120">
         <v>1.2</v>
@@ -20041,19 +20041,19 @@
         <v>4.2</v>
       </c>
       <c r="Q121">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="R121">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="S121">
         <v>1.44</v>
       </c>
       <c r="T121">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="U121">
-        <v>3.14</v>
+        <v>3.18</v>
       </c>
       <c r="V121">
         <v>1.33</v>
@@ -20068,7 +20068,7 @@
         <v>1.35</v>
       </c>
       <c r="Z121">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="AA121">
         <v>2.18</v>
@@ -20077,10 +20077,10 @@
         <v>1.75</v>
       </c>
       <c r="AC121">
-        <v>3.68</v>
+        <v>3.78</v>
       </c>
       <c r="AD121">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE121">
         <v>1.04</v>
@@ -22643,10 +22643,10 @@
         <v>2.3</v>
       </c>
       <c r="O137">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P137">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="Q137">
         <v>3.13</v>
@@ -22670,7 +22670,7 @@
         <v>1.08</v>
       </c>
       <c r="X137">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y137">
         <v>1.33</v>
@@ -22685,7 +22685,7 @@
         <v>1.75</v>
       </c>
       <c r="AC137">
-        <v>3.6</v>
+        <v>3.49</v>
       </c>
       <c r="AD137">
         <v>1.24</v>
@@ -22694,10 +22694,10 @@
         <v>1.1</v>
       </c>
       <c r="AF137">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AG137">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -644,16 +644,16 @@
         <v>1.9</v>
       </c>
       <c r="Q2">
-        <v>4.7</v>
+        <v>4.65</v>
       </c>
       <c r="R2">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="S2">
         <v>1.47</v>
       </c>
       <c r="T2">
-        <v>2.47</v>
+        <v>2.71</v>
       </c>
       <c r="U2">
         <v>3.16</v>
@@ -668,10 +668,10 @@
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="Z2">
-        <v>3.01</v>
+        <v>2.83</v>
       </c>
       <c r="AA2">
         <v>2.21</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AK2">
         <v>1.16</v>
@@ -961,16 +961,16 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O4">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="Q4">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="R4">
         <v>2.3</v>
@@ -982,19 +982,19 @@
         <v>3.2</v>
       </c>
       <c r="U4">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="V4">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W4">
         <v>1.07</v>
       </c>
       <c r="X4">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z4">
         <v>3.82</v>
@@ -1034,7 +1034,7 @@
         <v>1.23</v>
       </c>
       <c r="AK4">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O5">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P5">
-        <v>2.97</v>
+        <v>3.52</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1290,10 +1290,10 @@
         <v>3.05</v>
       </c>
       <c r="O6">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="P6">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="Q6">
         <v>3.55</v>
@@ -1308,7 +1308,7 @@
         <v>2.47</v>
       </c>
       <c r="U6">
-        <v>2.88</v>
+        <v>3.27</v>
       </c>
       <c r="V6">
         <v>1.31</v>
@@ -1341,7 +1341,7 @@
         <v>1.03</v>
       </c>
       <c r="AF6">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AG6">
         <v>1.83</v>
@@ -1456,7 +1456,7 @@
         <v>3</v>
       </c>
       <c r="P7">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O8">
         <v>3</v>
       </c>
       <c r="P8">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q8">
         <v>4</v>
@@ -1655,7 +1655,7 @@
         <v>2.19</v>
       </c>
       <c r="AB8">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC8">
         <v>3.9</v>
@@ -1667,7 +1667,7 @@
         <v>1.02</v>
       </c>
       <c r="AF8">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AG8">
         <v>1.8</v>
@@ -1785,55 +1785,55 @@
         <v>1.99</v>
       </c>
       <c r="Q9">
-        <v>3.88</v>
+        <v>3.6</v>
       </c>
       <c r="R9">
-        <v>2.11</v>
+        <v>2.01</v>
       </c>
       <c r="S9">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T9">
-        <v>2.79</v>
+        <v>2.67</v>
       </c>
       <c r="U9">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="V9">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W9">
         <v>1.07</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z9">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="AA9">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AB9">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AC9">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AD9">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE9">
         <v>1.07</v>
       </c>
       <c r="AF9">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG9">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>1.25</v>
       </c>
       <c r="AK9">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,16 +1939,16 @@
         </is>
       </c>
       <c r="N10">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="O10">
         <v>3.2</v>
       </c>
       <c r="P10">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="Q10">
-        <v>3.64</v>
+        <v>3.7</v>
       </c>
       <c r="R10">
         <v>2</v>
@@ -1957,13 +1957,13 @@
         <v>1.42</v>
       </c>
       <c r="T10">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="U10">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="V10">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W10">
         <v>1.05</v>
@@ -1972,19 +1972,19 @@
         <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z10">
-        <v>3.24</v>
+        <v>2.8</v>
       </c>
       <c r="AA10">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AB10">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AC10">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AD10">
         <v>1.21</v>
@@ -1996,7 +1996,7 @@
         <v>1.8</v>
       </c>
       <c r="AG10">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>1.3</v>
       </c>
       <c r="AK10">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2105,46 +2105,46 @@
         <v>2.55</v>
       </c>
       <c r="O11">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="P11">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="Q11">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="R11">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="S11">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="T11">
-        <v>2.47</v>
+        <v>2.36</v>
       </c>
       <c r="U11">
         <v>2.65</v>
       </c>
       <c r="V11">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W11">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X11">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y11">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z11">
-        <v>3.25</v>
+        <v>2.74</v>
       </c>
       <c r="AA11">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB11">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC11">
         <v>3.6</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AK11">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2268,10 +2268,10 @@
         <v>4.4</v>
       </c>
       <c r="O12">
-        <v>4.05</v>
+        <v>3.97</v>
       </c>
       <c r="P12">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="Q12">
         <v>4.55</v>
@@ -2286,10 +2286,10 @@
         <v>3.42</v>
       </c>
       <c r="U12">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="V12">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W12">
         <v>1.17</v>
@@ -2301,10 +2301,10 @@
         <v>1.15</v>
       </c>
       <c r="Z12">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA12">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AB12">
         <v>2.4</v>
@@ -2313,13 +2313,13 @@
         <v>2.3</v>
       </c>
       <c r="AD12">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE12">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF12">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG12">
         <v>2.3</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.4</v>
+        <v>2.93</v>
       </c>
       <c r="O13">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P13">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="Q13">
         <v>3.3</v>
@@ -2443,10 +2443,10 @@
         <v>2.04</v>
       </c>
       <c r="S13">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T13">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U13">
         <v>2.2</v>
@@ -2455,16 +2455,16 @@
         <v>1.6</v>
       </c>
       <c r="W13">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
         <v>1.17</v>
       </c>
       <c r="Z13">
-        <v>4.85</v>
+        <v>4.91</v>
       </c>
       <c r="AA13">
         <v>1.6</v>
@@ -2473,16 +2473,16 @@
         <v>2.15</v>
       </c>
       <c r="AC13">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AD13">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AE13">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AF13">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG13">
         <v>2.4</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="O14">
-        <v>3.85</v>
+        <v>3.67</v>
       </c>
       <c r="P14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q14">
         <v>1.9</v>
@@ -2609,7 +2609,7 @@
         <v>1.3</v>
       </c>
       <c r="T14">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="U14">
         <v>2.3</v>
@@ -2624,10 +2624,10 @@
         <v>1.04</v>
       </c>
       <c r="Y14">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z14">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AA14">
         <v>1.67</v>
@@ -2636,7 +2636,7 @@
         <v>2.17</v>
       </c>
       <c r="AC14">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="AD14">
         <v>1.46</v>
@@ -2645,7 +2645,7 @@
         <v>1.18</v>
       </c>
       <c r="AF14">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG14">
         <v>2.01</v>
@@ -2784,7 +2784,7 @@
         <v>1.04</v>
       </c>
       <c r="X15">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y15">
         <v>1.3</v>
@@ -2935,10 +2935,10 @@
         <v>1.22</v>
       </c>
       <c r="T16">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U16">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V16">
         <v>1.68</v>
@@ -2947,13 +2947,13 @@
         <v>1.17</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
         <v>1.1</v>
       </c>
       <c r="Z16">
-        <v>6.02</v>
+        <v>3.75</v>
       </c>
       <c r="AA16">
         <v>1.4</v>
@@ -2968,7 +2968,7 @@
         <v>1.71</v>
       </c>
       <c r="AE16">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF16">
         <v>1.4</v>
@@ -3086,7 +3086,7 @@
         <v>3.44</v>
       </c>
       <c r="P17">
-        <v>2.95</v>
+        <v>3.01</v>
       </c>
       <c r="Q17">
         <v>2.63</v>
@@ -3125,13 +3125,13 @@
         <v>2.1</v>
       </c>
       <c r="AC17">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="AD17">
         <v>1.4</v>
       </c>
       <c r="AE17">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF17">
         <v>1.55</v>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="O18">
         <v>3.54</v>
@@ -3279,22 +3279,22 @@
         <v>1.17</v>
       </c>
       <c r="Z18">
-        <v>4.58</v>
+        <v>4.67</v>
       </c>
       <c r="AA18">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AB18">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="AC18">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AD18">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AE18">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF18">
         <v>1.55</v>
@@ -3430,7 +3430,7 @@
         <v>2.25</v>
       </c>
       <c r="V19">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="W19">
         <v>1.11</v>
@@ -3445,7 +3445,7 @@
         <v>4.4</v>
       </c>
       <c r="AA19">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AB19">
         <v>2.45</v>
@@ -3569,16 +3569,16 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="O20">
         <v>3.51</v>
       </c>
       <c r="P20">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Q20">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="R20">
         <v>2.09</v>
@@ -3590,7 +3590,7 @@
         <v>2.68</v>
       </c>
       <c r="U20">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="V20">
         <v>1.35</v>
@@ -3602,10 +3602,10 @@
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z20">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AA20">
         <v>2.17</v>
@@ -3617,16 +3617,16 @@
         <v>3.68</v>
       </c>
       <c r="AD20">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE20">
         <v>1.03</v>
       </c>
       <c r="AF20">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AG20">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="O21">
         <v>3.3</v>
       </c>
       <c r="P21">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="Q21">
         <v>2.5</v>
@@ -3747,7 +3747,7 @@
         <v>2.2</v>
       </c>
       <c r="S21">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T21">
         <v>2.9</v>
@@ -3777,13 +3777,13 @@
         <v>1.89</v>
       </c>
       <c r="AC21">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="AD21">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AE21">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF21">
         <v>1.67</v>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK21">
         <v>1.73</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O22">
+        <v>3.4</v>
+      </c>
+      <c r="P22">
         <v>3.5</v>
-      </c>
-      <c r="P22">
-        <v>3.6</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="O23">
         <v>3.4</v>
       </c>
       <c r="P23">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="Q23">
         <v>3.7</v>
@@ -4094,19 +4094,19 @@
         <v>1.22</v>
       </c>
       <c r="Z23">
-        <v>4.07</v>
+        <v>4.11</v>
       </c>
       <c r="AA23">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AB23">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AC23">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AD23">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE23">
         <v>1.14</v>
@@ -4227,13 +4227,13 @@
         <v>3.52</v>
       </c>
       <c r="P24">
-        <v>3.27</v>
+        <v>4.2</v>
       </c>
       <c r="Q24">
         <v>2.19</v>
       </c>
       <c r="R24">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="S24">
         <v>1.22</v>
@@ -4242,10 +4242,10 @@
         <v>3.36</v>
       </c>
       <c r="U24">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="V24">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W24">
         <v>1.15</v>
@@ -4257,7 +4257,7 @@
         <v>1.14</v>
       </c>
       <c r="Z24">
-        <v>5</v>
+        <v>5.06</v>
       </c>
       <c r="AA24">
         <v>1.53</v>
@@ -4269,10 +4269,10 @@
         <v>2.5</v>
       </c>
       <c r="AD24">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="AE24">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AF24">
         <v>1.53</v>
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="O25">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="P25">
         <v>5.5</v>
@@ -4414,7 +4414,7 @@
         <v>1.13</v>
       </c>
       <c r="X25">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
         <v>1.13</v>
@@ -4429,10 +4429,10 @@
         <v>2.29</v>
       </c>
       <c r="AC25">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AD25">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AE25">
         <v>1.24</v>
@@ -4547,58 +4547,58 @@
         </is>
       </c>
       <c r="N26">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O26">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="P26">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Q26">
-        <v>6.73</v>
+        <v>7.5</v>
       </c>
       <c r="R26">
         <v>2.55</v>
       </c>
       <c r="S26">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T26">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="U26">
         <v>2.25</v>
       </c>
       <c r="V26">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W26">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z26">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AA26">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="AB26">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="AC26">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="AD26">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AE26">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF26">
         <v>1.89</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AK26">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="O27">
         <v>4.6</v>
@@ -4737,7 +4737,7 @@
         <v>1.8</v>
       </c>
       <c r="W27">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X27">
         <v>1.01</v>
@@ -4749,13 +4749,13 @@
         <v>6.15</v>
       </c>
       <c r="AA27">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AB27">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AC27">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AD27">
         <v>1.89</v>
@@ -4764,7 +4764,7 @@
         <v>1.34</v>
       </c>
       <c r="AF27">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AG27">
         <v>2.6</v>
@@ -4888,7 +4888,7 @@
         <v>2.35</v>
       </c>
       <c r="S28">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T28">
         <v>3.22</v>
@@ -4915,7 +4915,7 @@
         <v>1.66</v>
       </c>
       <c r="AB28">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AC28">
         <v>2.63</v>
@@ -4946,7 +4946,7 @@
         <v>1.09</v>
       </c>
       <c r="AK28">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,31 +5036,31 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="O29">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P29">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="Q29">
         <v>2.2</v>
       </c>
       <c r="R29">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="S29">
         <v>1.36</v>
       </c>
       <c r="T29">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U29">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="V29">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W29">
         <v>1.07</v>
@@ -5084,16 +5084,16 @@
         <v>3.3</v>
       </c>
       <c r="AD29">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE29">
         <v>1.1</v>
       </c>
       <c r="AF29">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG29">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AK29">
         <v>2.14</v>
@@ -5202,10 +5202,10 @@
         <v>2.18</v>
       </c>
       <c r="O30">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="P30">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="Q30">
         <v>2.61</v>
@@ -5214,7 +5214,7 @@
         <v>2.22</v>
       </c>
       <c r="S30">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T30">
         <v>3.28</v>
@@ -5226,13 +5226,13 @@
         <v>1.57</v>
       </c>
       <c r="W30">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z30">
         <v>4</v>
@@ -5241,7 +5241,7 @@
         <v>1.64</v>
       </c>
       <c r="AB30">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AC30">
         <v>2.38</v>
@@ -5250,7 +5250,7 @@
         <v>1.47</v>
       </c>
       <c r="AE30">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF30">
         <v>1.55</v>
@@ -5368,13 +5368,13 @@
         <v>5</v>
       </c>
       <c r="P31">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Q31">
         <v>6</v>
       </c>
       <c r="R31">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="S31">
         <v>1.21</v>
@@ -5383,10 +5383,10 @@
         <v>3.75</v>
       </c>
       <c r="U31">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="V31">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W31">
         <v>1.15</v>
@@ -5398,22 +5398,22 @@
         <v>1.08</v>
       </c>
       <c r="Z31">
-        <v>6.05</v>
+        <v>6.14</v>
       </c>
       <c r="AA31">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AB31">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="AC31">
         <v>2.1</v>
       </c>
       <c r="AD31">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AE31">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AF31">
         <v>1.65</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK31">
         <v>1.07</v>
@@ -5688,25 +5688,25 @@
         </is>
       </c>
       <c r="N33">
-        <v>5.5</v>
+        <v>6.05</v>
       </c>
       <c r="O33">
-        <v>4.45</v>
+        <v>4.62</v>
       </c>
       <c r="P33">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="Q33">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="R33">
         <v>2.55</v>
       </c>
       <c r="S33">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T33">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="U33">
         <v>2.05</v>
@@ -5724,7 +5724,7 @@
         <v>1.14</v>
       </c>
       <c r="Z33">
-        <v>5.72</v>
+        <v>5.83</v>
       </c>
       <c r="AA33">
         <v>1.41</v>
@@ -5733,19 +5733,19 @@
         <v>2.6</v>
       </c>
       <c r="AC33">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="AD33">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AE33">
         <v>1.29</v>
       </c>
       <c r="AF33">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG33">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>1.2</v>
       </c>
       <c r="AK33">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,7 +5851,7 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O34">
         <v>3.5</v>
@@ -5863,13 +5863,13 @@
         <v>2.8</v>
       </c>
       <c r="R34">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="S34">
         <v>1.35</v>
       </c>
       <c r="T34">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="U34">
         <v>2.45</v>
@@ -5881,22 +5881,22 @@
         <v>1.06</v>
       </c>
       <c r="X34">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y34">
         <v>1.2</v>
       </c>
       <c r="Z34">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="AA34">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB34">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AC34">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AD34">
         <v>1.33</v>
@@ -6053,7 +6053,7 @@
         <v>3.34</v>
       </c>
       <c r="AA35">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AB35">
         <v>1.9</v>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.37</v>
+        <v>2.43</v>
       </c>
       <c r="O36">
         <v>3.1</v>
@@ -6189,22 +6189,22 @@
         <v>3.04</v>
       </c>
       <c r="R36">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S36">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T36">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U36">
         <v>2.8</v>
       </c>
       <c r="V36">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W36">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X36">
         <v>1.06</v>
@@ -6213,16 +6213,16 @@
         <v>1.33</v>
       </c>
       <c r="Z36">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="AA36">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB36">
         <v>1.81</v>
       </c>
       <c r="AC36">
-        <v>3.59</v>
+        <v>3.62</v>
       </c>
       <c r="AD36">
         <v>1.25</v>
@@ -6231,10 +6231,10 @@
         <v>1.06</v>
       </c>
       <c r="AF36">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG36">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.4</v>
       </c>
       <c r="AK36">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6349,55 +6349,55 @@
         <v>0</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6524,16 +6524,16 @@
         <v>2.88</v>
       </c>
       <c r="U38">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="V38">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W38">
         <v>1.07</v>
       </c>
       <c r="X38">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y38">
         <v>1.24</v>
@@ -6542,13 +6542,13 @@
         <v>3.34</v>
       </c>
       <c r="AA38">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AB38">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AC38">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AD38">
         <v>1.3</v>
@@ -6560,7 +6560,7 @@
         <v>1.7</v>
       </c>
       <c r="AG38">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="O39">
-        <v>6.3</v>
+        <v>7</v>
       </c>
       <c r="P39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q39">
         <v>1.57</v>
@@ -6681,10 +6681,10 @@
         <v>2.8</v>
       </c>
       <c r="S39">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T39">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="U39">
         <v>2.16</v>
@@ -6696,13 +6696,13 @@
         <v>1.14</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z39">
-        <v>5.15</v>
+        <v>5.2</v>
       </c>
       <c r="AA39">
         <v>1.42</v>
@@ -6714,16 +6714,16 @@
         <v>2.25</v>
       </c>
       <c r="AD39">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AE39">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF39">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AG39">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AK39">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,7 +6829,7 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="O40">
         <v>3.58</v>
@@ -6838,16 +6838,16 @@
         <v>3.6</v>
       </c>
       <c r="Q40">
-        <v>2.31</v>
+        <v>2.17</v>
       </c>
       <c r="R40">
         <v>2.38</v>
       </c>
       <c r="S40">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T40">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U40">
         <v>2.32</v>
@@ -6856,7 +6856,7 @@
         <v>1.53</v>
       </c>
       <c r="W40">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X40">
         <v>1.01</v>
@@ -6883,7 +6883,7 @@
         <v>1.18</v>
       </c>
       <c r="AF40">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG40">
         <v>2.25</v>
@@ -6902,7 +6902,7 @@
         <v>1.25</v>
       </c>
       <c r="AK40">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="N41">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="O41">
         <v>3.4</v>
@@ -7001,46 +7001,46 @@
         <v>2</v>
       </c>
       <c r="Q41">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="R41">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S41">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T41">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="U41">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="V41">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W41">
         <v>1.07</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y41">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z41">
-        <v>4.5</v>
+        <v>3.92</v>
       </c>
       <c r="AA41">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AB41">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AC41">
         <v>2.7</v>
       </c>
       <c r="AD41">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE41">
         <v>1.12</v>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK41">
         <v>1.28</v>
@@ -7155,65 +7155,65 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="O42">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P42">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q42">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="R42">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="S42">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="T42">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="U42">
-        <v>2.25</v>
+        <v>2.71</v>
       </c>
       <c r="V42">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="W42">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X42">
         <v>1.04</v>
       </c>
       <c r="Y42">
+        <v>1.23</v>
+      </c>
+      <c r="Z42">
+        <v>3.42</v>
+      </c>
+      <c r="AA42">
+        <v>1.83</v>
+      </c>
+      <c r="AB42">
+        <v>1.85</v>
+      </c>
+      <c r="AC42">
+        <v>2.88</v>
+      </c>
+      <c r="AD42">
+        <v>1.36</v>
+      </c>
+      <c r="AE42">
         <v>1.16</v>
       </c>
-      <c r="Z42">
-        <v>4</v>
-      </c>
-      <c r="AA42">
-        <v>1.7</v>
-      </c>
-      <c r="AB42">
+      <c r="AF42">
+        <v>1.67</v>
+      </c>
+      <c r="AG42">
         <v>2.05</v>
       </c>
-      <c r="AC42">
-        <v>2.7</v>
-      </c>
-      <c r="AD42">
-        <v>1.4</v>
-      </c>
-      <c r="AE42">
-        <v>1.15</v>
-      </c>
-      <c r="AF42">
-        <v>1.57</v>
-      </c>
-      <c r="AG42">
-        <v>2.25</v>
-      </c>
       <c r="AH42" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="AK42">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,52 +7318,52 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="O43">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P43">
-        <v>4.37</v>
+        <v>5</v>
       </c>
       <c r="Q43">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="R43">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="S43">
         <v>1.3</v>
       </c>
       <c r="T43">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="U43">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V43">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W43">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X43">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y43">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z43">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AA43">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AB43">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="AC43">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="AD43">
         <v>1.36</v>
@@ -7372,10 +7372,10 @@
         <v>1.13</v>
       </c>
       <c r="AF43">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG43">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AK43">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="O44">
-        <v>3.61</v>
+        <v>3.3</v>
       </c>
       <c r="P44">
-        <v>4.01</v>
+        <v>3.93</v>
       </c>
       <c r="Q44">
         <v>2.48</v>
@@ -7502,13 +7502,13 @@
         <v>2.65</v>
       </c>
       <c r="U44">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="V44">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W44">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X44">
         <v>1.02</v>
@@ -7517,13 +7517,13 @@
         <v>1.3</v>
       </c>
       <c r="Z44">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AA44">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AB44">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AC44">
         <v>3.4</v>
@@ -7532,13 +7532,13 @@
         <v>1.27</v>
       </c>
       <c r="AE44">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF44">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AG44">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK44">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -8133,16 +8133,16 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="O48">
         <v>3</v>
       </c>
       <c r="P48">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="Q48">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="R48">
         <v>2.09</v>
@@ -8151,13 +8151,13 @@
         <v>1.47</v>
       </c>
       <c r="T48">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="U48">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="V48">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W48">
         <v>1.01</v>
@@ -8178,10 +8178,10 @@
         <v>1.66</v>
       </c>
       <c r="AC48">
-        <v>3.86</v>
+        <v>3.94</v>
       </c>
       <c r="AD48">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AE48">
         <v>1.02</v>
@@ -8190,7 +8190,7 @@
         <v>1.84</v>
       </c>
       <c r="AG48">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AK48">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8299,7 +8299,7 @@
         <v>3</v>
       </c>
       <c r="O49">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P49">
         <v>2.05</v>
@@ -8462,16 +8462,16 @@
         <v>1.13</v>
       </c>
       <c r="O50">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P50">
         <v>14</v>
       </c>
       <c r="Q50">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="R50">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="S50">
         <v>1.2</v>
@@ -8483,7 +8483,7 @@
         <v>2.06</v>
       </c>
       <c r="V50">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="W50">
         <v>1.18</v>
@@ -8495,22 +8495,22 @@
         <v>1.06</v>
       </c>
       <c r="Z50">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="AA50">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AB50">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="AC50">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AD50">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AE50">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AF50">
         <v>2.21</v>
@@ -8532,7 +8532,7 @@
         <v>1.08</v>
       </c>
       <c r="AK50">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="O51">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P51">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Q51">
         <v>2.4</v>
@@ -8652,16 +8652,16 @@
         <v>1.1</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y51">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA51">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AB51">
         <v>2.1</v>
@@ -8695,7 +8695,7 @@
         <v>1.21</v>
       </c>
       <c r="AK51">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="O52">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P52">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="Q52">
         <v>2.15</v>
@@ -8806,7 +8806,7 @@
         <v>3.25</v>
       </c>
       <c r="U52">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V52">
         <v>1.48</v>
@@ -8818,10 +8818,10 @@
         <v>1.04</v>
       </c>
       <c r="Y52">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="AA52">
         <v>1.72</v>
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK52">
         <v>2.22</v>
@@ -8948,58 +8948,58 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="O53">
-        <v>5.25</v>
+        <v>5.4</v>
       </c>
       <c r="P53">
-        <v>7.72</v>
+        <v>7.95</v>
       </c>
       <c r="Q53">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="R53">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="S53">
         <v>1.22</v>
       </c>
       <c r="T53">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U53">
         <v>1.95</v>
       </c>
       <c r="V53">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W53">
         <v>1.14</v>
       </c>
       <c r="X53">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y53">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z53">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="AA53">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AB53">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AC53">
         <v>2</v>
       </c>
       <c r="AD53">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AE53">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AF53">
         <v>1.74</v>
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AK53">
         <v>2.95</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="O54">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="P54">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="Q54">
         <v>2.63</v>
@@ -9132,7 +9132,7 @@
         <v>3.3</v>
       </c>
       <c r="U54">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="V54">
         <v>1.48</v>
@@ -9165,7 +9165,7 @@
         <v>1.1</v>
       </c>
       <c r="AF54">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AG54">
         <v>2.2</v>
@@ -9184,7 +9184,7 @@
         <v>1.3</v>
       </c>
       <c r="AK54">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9277,22 +9277,22 @@
         <v>1.75</v>
       </c>
       <c r="O55">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P55">
         <v>4</v>
       </c>
       <c r="Q55">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R55">
         <v>2.2</v>
       </c>
       <c r="S55">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T55">
-        <v>2.95</v>
+        <v>2.78</v>
       </c>
       <c r="U55">
         <v>2.75</v>
@@ -9301,34 +9301,34 @@
         <v>1.4</v>
       </c>
       <c r="W55">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X55">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z55">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AA55">
+        <v>1.9</v>
+      </c>
+      <c r="AB55">
         <v>1.87</v>
       </c>
-      <c r="AB55">
-        <v>1.92</v>
-      </c>
       <c r="AC55">
-        <v>3.6</v>
+        <v>3.08</v>
       </c>
       <c r="AD55">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AE55">
         <v>1.1</v>
       </c>
       <c r="AF55">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AG55">
         <v>1.91</v>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK55">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="O56">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="P56">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="Q56">
         <v>3.8</v>
@@ -9452,19 +9452,19 @@
         <v>1.83</v>
       </c>
       <c r="S56">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="T56">
         <v>2.4</v>
       </c>
       <c r="U56">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="V56">
         <v>1.22</v>
       </c>
       <c r="W56">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X56">
         <v>1.11</v>
@@ -9482,7 +9482,7 @@
         <v>1.44</v>
       </c>
       <c r="AC56">
-        <v>5.5</v>
+        <v>5.57</v>
       </c>
       <c r="AD56">
         <v>1.14</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="O57">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P57">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="O58">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P58">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="O59">
-        <v>3.92</v>
+        <v>4.1</v>
       </c>
       <c r="P59">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="Q59">
         <v>2.25</v>
@@ -9950,7 +9950,7 @@
         <v>2.04</v>
       </c>
       <c r="V59">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="W59">
         <v>1.17</v>
@@ -9971,13 +9971,13 @@
         <v>2.7</v>
       </c>
       <c r="AC59">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AD59">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AE59">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AF59">
         <v>1.4</v>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="O60">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="P60">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="Q60">
         <v>1.88</v>
@@ -10134,19 +10134,19 @@
         <v>2.5</v>
       </c>
       <c r="AC60">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AD60">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AE60">
         <v>1.24</v>
       </c>
       <c r="AF60">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AG60">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>1.14</v>
       </c>
       <c r="AK60">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,16 +10252,16 @@
         </is>
       </c>
       <c r="N61">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="O61">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P61">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Q61">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="R61">
         <v>2.5</v>
@@ -10279,7 +10279,7 @@
         <v>1.72</v>
       </c>
       <c r="W61">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X61">
         <v>1.02</v>
@@ -10288,16 +10288,16 @@
         <v>1.13</v>
       </c>
       <c r="Z61">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="AA61">
         <v>1.44</v>
       </c>
       <c r="AB61">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="AC61">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AD61">
         <v>1.76</v>
@@ -10306,7 +10306,7 @@
         <v>1.29</v>
       </c>
       <c r="AF61">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AG61">
         <v>2.8</v>
@@ -10415,7 +10415,7 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="O62">
         <v>3.2</v>
@@ -10427,7 +10427,7 @@
         <v>2.38</v>
       </c>
       <c r="R62">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S62">
         <v>1.43</v>
@@ -10442,25 +10442,25 @@
         <v>1.36</v>
       </c>
       <c r="W62">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X62">
         <v>1.06</v>
       </c>
       <c r="Y62">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Z62">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="AA62">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AB62">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC62">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="AD62">
         <v>1.21</v>
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK62">
         <v>1.73</v>
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="O63">
         <v>2.9</v>
       </c>
       <c r="P63">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="Q63">
         <v>3.2</v>
@@ -10620,7 +10620,7 @@
         <v>2.53</v>
       </c>
       <c r="AB63">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AC63">
         <v>5</v>
@@ -10629,7 +10629,7 @@
         <v>1.17</v>
       </c>
       <c r="AE63">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF63">
         <v>2.05</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="O64">
         <v>3.4</v>
       </c>
       <c r="P64">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q64">
         <v>3.12</v>
@@ -10771,7 +10771,7 @@
         <v>1.12</v>
       </c>
       <c r="X64">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y64">
         <v>1.11</v>
@@ -10786,7 +10786,7 @@
         <v>2.38</v>
       </c>
       <c r="AC64">
-        <v>2.21</v>
+        <v>1.92</v>
       </c>
       <c r="AD64">
         <v>1.47</v>
@@ -10904,7 +10904,7 @@
         </is>
       </c>
       <c r="N65">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="O65">
         <v>3.8</v>
@@ -10913,22 +10913,22 @@
         <v>1.57</v>
       </c>
       <c r="Q65">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="R65">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S65">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T65">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="U65">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="V65">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W65">
         <v>1.11</v>
@@ -10940,16 +10940,16 @@
         <v>1.22</v>
       </c>
       <c r="Z65">
-        <v>3.84</v>
+        <v>3.78</v>
       </c>
       <c r="AA65">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AB65">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="AC65">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AD65">
         <v>1.4</v>
@@ -11067,7 +11067,7 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="O66">
         <v>3.3</v>
@@ -11076,7 +11076,7 @@
         <v>2.6</v>
       </c>
       <c r="Q66">
-        <v>2.69</v>
+        <v>2.96</v>
       </c>
       <c r="R66">
         <v>2.37</v>
@@ -11088,7 +11088,7 @@
         <v>3.3</v>
       </c>
       <c r="U66">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="V66">
         <v>1.47</v>
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O67">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P67">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q67">
         <v>3.4</v>
@@ -11248,7 +11248,7 @@
         <v>1.22</v>
       </c>
       <c r="T67">
-        <v>3.66</v>
+        <v>3.75</v>
       </c>
       <c r="U67">
         <v>2.05</v>
@@ -11260,25 +11260,25 @@
         <v>1.18</v>
       </c>
       <c r="X67">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z67">
         <v>5</v>
       </c>
       <c r="AA67">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB67">
         <v>2.6</v>
       </c>
       <c r="AC67">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="AD67">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AE67">
         <v>1.25</v>
@@ -11287,7 +11287,7 @@
         <v>1.4</v>
       </c>
       <c r="AG67">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="O68">
         <v>3.4</v>
       </c>
       <c r="P68">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q68">
         <v>2.91</v>
@@ -11447,7 +11447,7 @@
         <v>1.18</v>
       </c>
       <c r="AF68">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG68">
         <v>2.5</v>
@@ -11565,55 +11565,55 @@
         <v>0</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>5.94</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T69">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U69">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V69">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W69">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z69">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD69">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE69">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF69">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK69">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="O71">
+        <v>3.2</v>
+      </c>
+      <c r="P71">
         <v>3.05</v>
-      </c>
-      <c r="P71">
-        <v>3.15</v>
       </c>
       <c r="Q71">
         <v>2.7</v>
@@ -11897,49 +11897,49 @@
         <v>2.02</v>
       </c>
       <c r="S71">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T71">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="U71">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="V71">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W71">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X71">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y71">
         <v>1.3</v>
       </c>
       <c r="Z71">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AA71">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB71">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC71">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="AD71">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE71">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF71">
         <v>1.7</v>
       </c>
       <c r="AG71">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,7 +11952,7 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AK71">
         <v>1.6</v>
@@ -12045,16 +12045,16 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="O72">
-        <v>3.7</v>
+        <v>3.84</v>
       </c>
       <c r="P72">
-        <v>4.6</v>
+        <v>4.85</v>
       </c>
       <c r="Q72">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="R72">
         <v>2.3</v>
@@ -12066,22 +12066,22 @@
         <v>3.2</v>
       </c>
       <c r="U72">
-        <v>2.73</v>
+        <v>2.55</v>
       </c>
       <c r="V72">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W72">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X72">
         <v>1</v>
       </c>
       <c r="Y72">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z72">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="AA72">
         <v>1.85</v>
@@ -12099,10 +12099,10 @@
         <v>1.13</v>
       </c>
       <c r="AF72">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AG72">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>1.09</v>
       </c>
       <c r="AK72">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12226,7 +12226,7 @@
         <v>1.25</v>
       </c>
       <c r="T73">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U73">
         <v>2.25</v>
@@ -12265,7 +12265,7 @@
         <v>1.44</v>
       </c>
       <c r="AG73">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12374,61 +12374,61 @@
         <v>1.29</v>
       </c>
       <c r="O74">
-        <v>6.5</v>
+        <v>11</v>
       </c>
       <c r="P74">
         <v>7.15</v>
       </c>
       <c r="Q74">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="R74">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="S74">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="T74">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="U74">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="V74">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="W74">
         <v>1.25</v>
       </c>
       <c r="X74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y74">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z74">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA74">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AB74">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="AC74">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AD74">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="AE74">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AF74">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AG74">
-        <v>2.25</v>
+        <v>1.4</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AK74">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12537,7 +12537,7 @@
         <v>2.65</v>
       </c>
       <c r="O75">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P75">
         <v>2.27</v>
@@ -12552,7 +12552,7 @@
         <v>1.41</v>
       </c>
       <c r="T75">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="U75">
         <v>2.99</v>
@@ -12567,7 +12567,7 @@
         <v>1.02</v>
       </c>
       <c r="Y75">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z75">
         <v>3.25</v>
@@ -12607,7 +12607,7 @@
         <v>1.53</v>
       </c>
       <c r="AK75">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12697,19 +12697,19 @@
         </is>
       </c>
       <c r="N76">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="O76">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="P76">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="Q76">
-        <v>4.26</v>
+        <v>4.21</v>
       </c>
       <c r="R76">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S76">
         <v>1.28</v>
@@ -12733,7 +12733,7 @@
         <v>1.2</v>
       </c>
       <c r="Z76">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="AA76">
         <v>1.61</v>
@@ -12742,7 +12742,7 @@
         <v>2.31</v>
       </c>
       <c r="AC76">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="AD76">
         <v>1.44</v>
@@ -12770,7 +12770,7 @@
         <v>1.85</v>
       </c>
       <c r="AK76">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>1.55</v>
       </c>
       <c r="O77">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="P77">
-        <v>5.3</v>
+        <v>5.39</v>
       </c>
       <c r="Q77">
         <v>1.95</v>
@@ -12881,10 +12881,10 @@
         <v>3.34</v>
       </c>
       <c r="U77">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="V77">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W77">
         <v>1.12</v>
@@ -12896,22 +12896,22 @@
         <v>1.17</v>
       </c>
       <c r="Z77">
-        <v>5.01</v>
+        <v>5.07</v>
       </c>
       <c r="AA77">
         <v>1.56</v>
       </c>
       <c r="AB77">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="AC77">
         <v>2.35</v>
       </c>
       <c r="AD77">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AE77">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF77">
         <v>1.57</v>
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="O84">
         <v>3.15</v>
       </c>
       <c r="P84">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="Q84">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="R84">
         <v>2</v>
       </c>
       <c r="S84">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="T84">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="U84">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="V84">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W84">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X84">
         <v>1.03</v>
       </c>
       <c r="Y84">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z84">
         <v>2.9</v>
       </c>
       <c r="AA84">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AB84">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC84">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
       <c r="AD84">
         <v>1.21</v>
       </c>
       <c r="AE84">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF84">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG84">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
         <v>1.26</v>
       </c>
       <c r="AK84">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14167,46 +14167,46 @@
         <v>1.76</v>
       </c>
       <c r="O85">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P85">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="Q85">
+        <v>2.38</v>
+      </c>
+      <c r="R85">
         <v>2.25</v>
       </c>
-      <c r="R85">
-        <v>2.15</v>
-      </c>
       <c r="S85">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T85">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="U85">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="V85">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W85">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X85">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y85">
         <v>1.23</v>
       </c>
       <c r="Z85">
-        <v>3.78</v>
+        <v>4.2</v>
       </c>
       <c r="AA85">
         <v>1.75</v>
       </c>
       <c r="AB85">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AC85">
         <v>2.87</v>
@@ -14221,7 +14221,7 @@
         <v>1.67</v>
       </c>
       <c r="AG85">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14327,22 +14327,22 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="O86">
-        <v>3.4</v>
+        <v>3.23</v>
       </c>
       <c r="P86">
         <v>4.3</v>
       </c>
       <c r="Q86">
-        <v>2.39</v>
+        <v>2.23</v>
       </c>
       <c r="R86">
         <v>1.99</v>
       </c>
       <c r="S86">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="T86">
         <v>2.59</v>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK86">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14490,16 +14490,16 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="O87">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P87">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="Q87">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="R87">
         <v>2.3</v>
@@ -14520,19 +14520,19 @@
         <v>1.11</v>
       </c>
       <c r="X87">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y87">
         <v>1.19</v>
       </c>
       <c r="Z87">
-        <v>3.82</v>
+        <v>4.1</v>
       </c>
       <c r="AA87">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AB87">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AC87">
         <v>2.69</v>
@@ -14541,7 +14541,7 @@
         <v>1.36</v>
       </c>
       <c r="AE87">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF87">
         <v>1.6</v>
@@ -14822,22 +14822,22 @@
         <v>4.2</v>
       </c>
       <c r="P89">
-        <v>4.6</v>
+        <v>4.25</v>
       </c>
       <c r="Q89">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R89">
         <v>2.38</v>
       </c>
       <c r="S89">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T89">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U89">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="V89">
         <v>1.54</v>
@@ -14855,13 +14855,13 @@
         <v>4.33</v>
       </c>
       <c r="AA89">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB89">
         <v>2.15</v>
       </c>
       <c r="AC89">
-        <v>2.41</v>
+        <v>2.55</v>
       </c>
       <c r="AD89">
         <v>1.5</v>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK89">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14979,7 +14979,7 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="O90">
         <v>3.4</v>
@@ -14988,13 +14988,13 @@
         <v>2.91</v>
       </c>
       <c r="Q90">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="R90">
         <v>2.28</v>
       </c>
       <c r="S90">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T90">
         <v>2.91</v>
@@ -15003,40 +15003,40 @@
         <v>2.59</v>
       </c>
       <c r="V90">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="W90">
         <v>1.1</v>
       </c>
       <c r="X90">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y90">
         <v>1.2</v>
       </c>
       <c r="Z90">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AA90">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB90">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AC90">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AD90">
         <v>1.33</v>
       </c>
       <c r="AE90">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF90">
         <v>1.6</v>
       </c>
       <c r="AG90">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AK90">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15142,7 +15142,7 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="O91">
         <v>3.1</v>
@@ -15151,7 +15151,7 @@
         <v>2.5</v>
       </c>
       <c r="Q91">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R91">
         <v>2</v>
@@ -15169,7 +15169,7 @@
         <v>1.29</v>
       </c>
       <c r="W91">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X91">
         <v>1.05</v>
@@ -15178,19 +15178,19 @@
         <v>1.39</v>
       </c>
       <c r="Z91">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="AA91">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AB91">
         <v>1.6</v>
       </c>
       <c r="AC91">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="AD91">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE91">
         <v>1.03</v>
@@ -15199,7 +15199,7 @@
         <v>1.95</v>
       </c>
       <c r="AG91">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         <v>1.33</v>
       </c>
       <c r="AK91">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O92">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q92">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R92">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S92">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T92">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U92">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V92">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W92">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X92">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y92">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z92">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA92">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AB92">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC92">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD92">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE92">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF92">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG92">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK92">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O93">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q93">
         <v>0</v>
@@ -15507,10 +15507,10 @@
         <v>0</v>
       </c>
       <c r="AA93">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB93">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC93">
         <v>0</v>
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O95">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P95">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="O96">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P96">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="Q96">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="R96">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="S96">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="T96">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="U96">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="V96">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W96">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X96">
+        <v>1.03</v>
+      </c>
+      <c r="Y96">
+        <v>1.4</v>
+      </c>
+      <c r="Z96">
+        <v>2.79</v>
+      </c>
+      <c r="AA96">
+        <v>2.34</v>
+      </c>
+      <c r="AB96">
+        <v>1.57</v>
+      </c>
+      <c r="AC96">
+        <v>4.2</v>
+      </c>
+      <c r="AD96">
+        <v>1.16</v>
+      </c>
+      <c r="AE96">
         <v>1.01</v>
       </c>
-      <c r="Y96">
-        <v>1.31</v>
-      </c>
-      <c r="Z96">
-        <v>2.92</v>
-      </c>
-      <c r="AA96">
-        <v>2.06</v>
-      </c>
-      <c r="AB96">
-        <v>1.67</v>
-      </c>
-      <c r="AC96">
-        <v>3.7</v>
-      </c>
-      <c r="AD96">
-        <v>1.2</v>
-      </c>
-      <c r="AE96">
-        <v>1.03</v>
-      </c>
       <c r="AF96">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG96">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK96">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16129,55 +16129,55 @@
         <v>0</v>
       </c>
       <c r="Q97">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="R97">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S97">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T97">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U97">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V97">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W97">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X97">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y97">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z97">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA97">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB97">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC97">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD97">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE97">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF97">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG97">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK97">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16458,7 +16458,7 @@
         <v>2.89</v>
       </c>
       <c r="R99">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="S99">
         <v>1.59</v>
@@ -16494,7 +16494,7 @@
         <v>4</v>
       </c>
       <c r="AD99">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AE99">
         <v>1.01</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="O100">
-        <v>3.5</v>
+        <v>2.85</v>
       </c>
       <c r="P100">
-        <v>3.6</v>
+        <v>2.84</v>
       </c>
       <c r="Q100">
-        <v>2.36</v>
+        <v>3.3</v>
       </c>
       <c r="R100">
-        <v>2.09</v>
+        <v>1.91</v>
       </c>
       <c r="S100">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="T100">
-        <v>2.73</v>
+        <v>2.43</v>
       </c>
       <c r="U100">
-        <v>2.83</v>
+        <v>3.42</v>
       </c>
       <c r="V100">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="W100">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X100">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y100">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="Z100">
-        <v>3.08</v>
+        <v>2.41</v>
       </c>
       <c r="AA100">
-        <v>1.94</v>
+        <v>2.44</v>
       </c>
       <c r="AB100">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="AC100">
-        <v>3.34</v>
+        <v>4.84</v>
       </c>
       <c r="AD100">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AE100">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF100">
-        <v>1.82</v>
+        <v>2.01</v>
       </c>
       <c r="AG100">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK100">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.39</v>
+        <v>1.8</v>
       </c>
       <c r="O101">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="P101">
-        <v>2.85</v>
+        <v>3.6</v>
       </c>
       <c r="Q101">
-        <v>3.3</v>
+        <v>2.36</v>
       </c>
       <c r="R101">
-        <v>1.91</v>
+        <v>2.09</v>
       </c>
       <c r="S101">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="T101">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="U101">
-        <v>3.42</v>
+        <v>2.86</v>
       </c>
       <c r="V101">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="W101">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X101">
+        <v>1.02</v>
+      </c>
+      <c r="Y101">
+        <v>1.28</v>
+      </c>
+      <c r="Z101">
+        <v>3.08</v>
+      </c>
+      <c r="AA101">
+        <v>1.96</v>
+      </c>
+      <c r="AB101">
+        <v>1.74</v>
+      </c>
+      <c r="AC101">
+        <v>3.34</v>
+      </c>
+      <c r="AD101">
+        <v>1.24</v>
+      </c>
+      <c r="AE101">
         <v>1.08</v>
       </c>
-      <c r="Y101">
-        <v>1.45</v>
-      </c>
-      <c r="Z101">
-        <v>2.41</v>
-      </c>
-      <c r="AA101">
-        <v>2.44</v>
-      </c>
-      <c r="AB101">
-        <v>1.48</v>
-      </c>
-      <c r="AC101">
-        <v>4.84</v>
-      </c>
-      <c r="AD101">
-        <v>1.16</v>
-      </c>
-      <c r="AE101">
-        <v>1.05</v>
-      </c>
       <c r="AF101">
-        <v>2.01</v>
+        <v>1.82</v>
       </c>
       <c r="AG101">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK101">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16938,10 +16938,10 @@
         <v>1.17</v>
       </c>
       <c r="O102">
-        <v>6.85</v>
+        <v>6.5</v>
       </c>
       <c r="P102">
-        <v>9.550000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="Q102">
         <v>1.45</v>
@@ -16968,31 +16968,31 @@
         <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Z102">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="AA102">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AB102">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AC102">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="AD102">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AE102">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AF102">
         <v>1.63</v>
       </c>
       <c r="AG102">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Q103">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R103">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S103">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T103">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U103">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V103">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W103">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X103">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y103">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z103">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA103">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB103">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC103">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD103">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE103">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF103">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG103">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK103">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S104">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T104">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U104">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V104">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W104">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X104">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y104">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z104">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA104">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB104">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC104">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD104">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE104">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF104">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG104">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK104">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17427,10 +17427,10 @@
         <v>4.36</v>
       </c>
       <c r="O105">
-        <v>3.7</v>
+        <v>3.61</v>
       </c>
       <c r="P105">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="Q105">
         <v>4.94</v>
@@ -17445,31 +17445,31 @@
         <v>2.94</v>
       </c>
       <c r="U105">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="V105">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W105">
         <v>1.05</v>
       </c>
       <c r="X105">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y105">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z105">
         <v>3.52</v>
       </c>
       <c r="AA105">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB105">
         <v>1.93</v>
       </c>
       <c r="AC105">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="AD105">
         <v>1.31</v>
@@ -17587,19 +17587,19 @@
         </is>
       </c>
       <c r="N106">
-        <v>4.55</v>
+        <v>4.33</v>
       </c>
       <c r="O106">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P106">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q106">
-        <v>5.05</v>
+        <v>4.9</v>
       </c>
       <c r="R106">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="S106">
         <v>1.36</v>
@@ -17614,7 +17614,7 @@
         <v>1.39</v>
       </c>
       <c r="W106">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X106">
         <v>1.05</v>
@@ -17626,19 +17626,19 @@
         <v>3.25</v>
       </c>
       <c r="AA106">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AB106">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AC106">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="AD106">
         <v>1.27</v>
       </c>
       <c r="AE106">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF106">
         <v>1.85</v>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AK106">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17756,13 +17756,13 @@
         <v>3.1</v>
       </c>
       <c r="P107">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="Q107">
         <v>3</v>
       </c>
       <c r="R107">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S107">
         <v>1.43</v>
@@ -17789,25 +17789,25 @@
         <v>2.9</v>
       </c>
       <c r="AA107">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AB107">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AC107">
         <v>3.9</v>
       </c>
       <c r="AD107">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE107">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF107">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AG107">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AK107">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="O108">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="P108">
-        <v>7.25</v>
+        <v>7.56</v>
       </c>
       <c r="Q108">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="R108">
-        <v>2.38</v>
+        <v>2.19</v>
       </c>
       <c r="S108">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T108">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="U108">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="V108">
         <v>1.45</v>
       </c>
       <c r="W108">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X108">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y108">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z108">
         <v>3.5</v>
       </c>
       <c r="AA108">
+        <v>1.83</v>
+      </c>
+      <c r="AB108">
         <v>1.87</v>
       </c>
-      <c r="AB108">
-        <v>1.9</v>
-      </c>
       <c r="AC108">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="AD108">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE108">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF108">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AG108">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>1.06</v>
       </c>
       <c r="AK108">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18278,10 +18278,10 @@
         <v>2.92</v>
       </c>
       <c r="AA110">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AB110">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC110">
         <v>3.58</v>
@@ -18290,13 +18290,13 @@
         <v>1.21</v>
       </c>
       <c r="AE110">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF110">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG110">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>3.25</v>
       </c>
       <c r="P111">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q111">
         <v>3.1</v>
@@ -18426,13 +18426,13 @@
         <v>2.56</v>
       </c>
       <c r="V111">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W111">
         <v>1.06</v>
       </c>
       <c r="X111">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y111">
         <v>1.21</v>
@@ -18472,7 +18472,7 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AK111">
         <v>1.43</v>
@@ -18565,10 +18565,10 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="O112">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="P112">
         <v>4.75</v>
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O114">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="P114">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Q114">
         <v>4.09</v>
@@ -18909,13 +18909,13 @@
         <v>1.33</v>
       </c>
       <c r="T114">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="U114">
         <v>2.56</v>
       </c>
       <c r="V114">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W114">
         <v>1.07</v>
@@ -18924,22 +18924,22 @@
         <v>1</v>
       </c>
       <c r="Y114">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z114">
         <v>3.7</v>
       </c>
       <c r="AA114">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB114">
         <v>1.95</v>
       </c>
       <c r="AC114">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AD114">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE114">
         <v>1.1</v>
@@ -18964,7 +18964,7 @@
         <v>1.22</v>
       </c>
       <c r="AK114">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19054,16 +19054,16 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="O115">
         <v>3.55</v>
       </c>
       <c r="P115">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="Q115">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="R115">
         <v>2.22</v>
@@ -19090,13 +19090,13 @@
         <v>1.21</v>
       </c>
       <c r="Z115">
-        <v>4.37</v>
+        <v>4.1</v>
       </c>
       <c r="AA115">
         <v>1.72</v>
       </c>
       <c r="AB115">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AC115">
         <v>2.66</v>
@@ -19105,13 +19105,13 @@
         <v>1.39</v>
       </c>
       <c r="AE115">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AF115">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG115">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19127,7 +19127,7 @@
         <v>1.28</v>
       </c>
       <c r="AK115">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="O116">
-        <v>7.05</v>
+        <v>6.5</v>
       </c>
       <c r="P116">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q116">
         <v>1.55</v>
@@ -19250,31 +19250,31 @@
         <v>1.03</v>
       </c>
       <c r="Y116">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z116">
         <v>5</v>
       </c>
       <c r="AA116">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AB116">
         <v>2.35</v>
       </c>
       <c r="AC116">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="AD116">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AE116">
         <v>1.18</v>
       </c>
       <c r="AF116">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AG116">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         </is>
       </c>
       <c r="N117">
-        <v>4</v>
+        <v>4.78</v>
       </c>
       <c r="O117">
         <v>4.05</v>
@@ -19392,34 +19392,34 @@
         <v>4.2</v>
       </c>
       <c r="R117">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S117">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="T117">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="U117">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="V117">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W117">
         <v>1.13</v>
       </c>
       <c r="X117">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y117">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z117">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AA117">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AB117">
         <v>2.55</v>
@@ -19428,10 +19428,10 @@
         <v>2.1</v>
       </c>
       <c r="AD117">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AE117">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF117">
         <v>1.55</v>
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="O118">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P118">
-        <v>4.69</v>
+        <v>4.63</v>
       </c>
       <c r="Q118">
         <v>0</v>
@@ -19869,13 +19869,13 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="O120">
         <v>3.85</v>
       </c>
       <c r="P120">
-        <v>3.15</v>
+        <v>2.87</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -19905,7 +19905,7 @@
         <v>1.08</v>
       </c>
       <c r="Z120">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AA120">
         <v>1.4</v>
@@ -19920,13 +19920,13 @@
         <v>1.71</v>
       </c>
       <c r="AE120">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AF120">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AG120">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -20044,13 +20044,13 @@
         <v>2.55</v>
       </c>
       <c r="R121">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="S121">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="T121">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="U121">
         <v>3.18</v>
@@ -20195,16 +20195,16 @@
         </is>
       </c>
       <c r="N122">
-        <v>3.55</v>
+        <v>4.27</v>
       </c>
       <c r="O122">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P122">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="Q122">
-        <v>4</v>
+        <v>4.95</v>
       </c>
       <c r="R122">
         <v>2.1</v>
@@ -20216,37 +20216,37 @@
         <v>2.65</v>
       </c>
       <c r="U122">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="V122">
         <v>1.35</v>
       </c>
       <c r="W122">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X122">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y122">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Z122">
-        <v>2.93</v>
+        <v>3.04</v>
       </c>
       <c r="AA122">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AB122">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC122">
-        <v>4</v>
+        <v>3.42</v>
       </c>
       <c r="AD122">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE122">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF122">
         <v>1.91</v>
@@ -20358,43 +20358,43 @@
         </is>
       </c>
       <c r="N123">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="O123">
-        <v>4.45</v>
+        <v>4.3</v>
       </c>
       <c r="P123">
-        <v>7.55</v>
+        <v>5.9</v>
       </c>
       <c r="Q123">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="R123">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="S123">
         <v>1.29</v>
       </c>
       <c r="T123">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U123">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="V123">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W123">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X123">
         <v>1.04</v>
       </c>
       <c r="Y123">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z123">
-        <v>3.95</v>
+        <v>3.88</v>
       </c>
       <c r="AA123">
         <v>1.73</v>
@@ -20403,7 +20403,7 @@
         <v>2</v>
       </c>
       <c r="AC123">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="AD123">
         <v>1.36</v>
@@ -20415,7 +20415,7 @@
         <v>1.95</v>
       </c>
       <c r="AG123">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK123">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="O126">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P126">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q126">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="R126">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S126">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T126">
-        <v>2.87</v>
+        <v>2.81</v>
       </c>
       <c r="U126">
-        <v>2.47</v>
+        <v>2.81</v>
       </c>
       <c r="V126">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="W126">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X126">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y126">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z126">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA126">
+        <v>1.8</v>
+      </c>
+      <c r="AB126">
         <v>1.75</v>
       </c>
-      <c r="AB126">
-        <v>2.01</v>
-      </c>
       <c r="AC126">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AD126">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AE126">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF126">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AG126">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AK126">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21010,16 +21010,16 @@
         </is>
       </c>
       <c r="N127">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="O127">
-        <v>4.85</v>
+        <v>4.6</v>
       </c>
       <c r="P127">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="Q127">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="R127">
         <v>2.6</v>
@@ -21031,13 +21031,13 @@
         <v>5</v>
       </c>
       <c r="U127">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V127">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="W127">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X127">
         <v>1.01</v>
@@ -21049,16 +21049,16 @@
         <v>8</v>
       </c>
       <c r="AA127">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AB127">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AC127">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="AD127">
-        <v>2.04</v>
+        <v>1.76</v>
       </c>
       <c r="AE127">
         <v>1.4</v>
@@ -21083,7 +21083,7 @@
         <v>1.1</v>
       </c>
       <c r="AK127">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21173,19 +21173,19 @@
         </is>
       </c>
       <c r="N128">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="O128">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P128">
-        <v>2.9</v>
+        <v>2.44</v>
       </c>
       <c r="Q128">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="R128">
-        <v>2.69</v>
+        <v>2.48</v>
       </c>
       <c r="S128">
         <v>1.17</v>
@@ -21212,7 +21212,7 @@
         <v>6.15</v>
       </c>
       <c r="AA128">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AB128">
         <v>2.92</v>
@@ -21336,7 +21336,7 @@
         </is>
       </c>
       <c r="N129">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="O129">
         <v>5</v>
@@ -21363,7 +21363,7 @@
         <v>1.83</v>
       </c>
       <c r="W129">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X129">
         <v>1.01</v>
@@ -21372,7 +21372,7 @@
         <v>1.06</v>
       </c>
       <c r="Z129">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="AA129">
         <v>1.24</v>
@@ -21409,7 +21409,7 @@
         <v>1.07</v>
       </c>
       <c r="AK129">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21499,31 +21499,31 @@
         </is>
       </c>
       <c r="N130">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="O130">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P130">
-        <v>3.25</v>
+        <v>3.29</v>
       </c>
       <c r="Q130">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="R130">
         <v>2.7</v>
       </c>
       <c r="S130">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="T130">
         <v>5</v>
       </c>
       <c r="U130">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V130">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="W130">
         <v>1.25</v>
@@ -21538,10 +21538,10 @@
         <v>8.5</v>
       </c>
       <c r="AA130">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AB130">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AC130">
         <v>1.68</v>
@@ -21550,10 +21550,10 @@
         <v>1.94</v>
       </c>
       <c r="AE130">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AF130">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AG130">
         <v>3.4</v>
@@ -21569,7 +21569,7 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AK130">
         <v>1.8</v>
@@ -21662,64 +21662,64 @@
         </is>
       </c>
       <c r="N131">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O131">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P131">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q131">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="R131">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S131">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T131">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U131">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V131">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W131">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X131">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y131">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z131">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA131">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB131">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC131">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD131">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE131">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF131">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG131">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK131">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O132">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P132">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q132">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R132">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S132">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T132">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U132">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V132">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W132">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X132">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y132">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z132">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AA132">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AB132">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC132">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD132">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE132">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF132">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG132">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AK132">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O133">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P133">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q133">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R133">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S133">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T133">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U133">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V133">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W133">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X133">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y133">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z133">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA133">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB133">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC133">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD133">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE133">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF133">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG133">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK133">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22314,22 +22314,22 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="O135">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P135">
         <v>3.8</v>
       </c>
       <c r="Q135">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="R135">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S135">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="T135">
         <v>2.88</v>
@@ -22347,7 +22347,7 @@
         <v>1.05</v>
       </c>
       <c r="Y135">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z135">
         <v>3.5</v>
@@ -22356,7 +22356,7 @@
         <v>1.82</v>
       </c>
       <c r="AB135">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AC135">
         <v>3.1</v>
@@ -22365,7 +22365,7 @@
         <v>1.33</v>
       </c>
       <c r="AE135">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF135">
         <v>1.73</v>
@@ -22387,7 +22387,7 @@
         <v>1.22</v>
       </c>
       <c r="AK135">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22492,10 +22492,10 @@
         <v>2.3</v>
       </c>
       <c r="S136">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T136">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="U136">
         <v>2.29</v>
@@ -22507,7 +22507,7 @@
         <v>1.12</v>
       </c>
       <c r="X136">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y136">
         <v>1.18</v>
@@ -22522,7 +22522,7 @@
         <v>2.15</v>
       </c>
       <c r="AC136">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AD136">
         <v>1.44</v>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK136">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22652,7 +22652,7 @@
         <v>3.13</v>
       </c>
       <c r="R137">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S137">
         <v>1.38</v>
@@ -22673,7 +22673,7 @@
         <v>1.03</v>
       </c>
       <c r="Y137">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z137">
         <v>3.25</v>
@@ -22688,16 +22688,16 @@
         <v>3.49</v>
       </c>
       <c r="AD137">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AE137">
         <v>1.1</v>
       </c>
       <c r="AF137">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG137">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK137">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22803,19 +22803,19 @@
         </is>
       </c>
       <c r="N138">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="O138">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P138">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="Q138">
         <v>6</v>
       </c>
       <c r="R138">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="S138">
         <v>1.33</v>
@@ -22836,10 +22836,10 @@
         <v>1.04</v>
       </c>
       <c r="Y138">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z138">
-        <v>3.66</v>
+        <v>3.69</v>
       </c>
       <c r="AA138">
         <v>1.86</v>
@@ -22848,7 +22848,7 @@
         <v>1.88</v>
       </c>
       <c r="AC138">
-        <v>3.18</v>
+        <v>3.04</v>
       </c>
       <c r="AD138">
         <v>1.29</v>
@@ -22860,7 +22860,7 @@
         <v>1.91</v>
       </c>
       <c r="AG138">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -23129,64 +23129,64 @@
         </is>
       </c>
       <c r="N140">
-        <v>4.7</v>
+        <v>3.35</v>
       </c>
       <c r="O140">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P140">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="Q140">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="R140">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S140">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T140">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U140">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="V140">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W140">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X140">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y140">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z140">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA140">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB140">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC140">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD140">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE140">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF140">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG140">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK140">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -23292,64 +23292,64 @@
         </is>
       </c>
       <c r="N141">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="O141">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P141">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q141">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R141">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S141">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T141">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U141">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V141">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W141">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X141">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y141">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z141">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA141">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB141">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC141">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD141">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE141">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF141">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG141">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK141">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23458,7 +23458,7 @@
         <v>1.64</v>
       </c>
       <c r="O142">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P142">
         <v>5.01</v>
@@ -23476,13 +23476,13 @@
         <v>2.88</v>
       </c>
       <c r="U142">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="V142">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W142">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X142">
         <v>1.06</v>
@@ -23497,16 +23497,16 @@
         <v>2.1</v>
       </c>
       <c r="AB142">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AC142">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AD142">
         <v>1.22</v>
       </c>
       <c r="AE142">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF142">
         <v>1.95</v>
@@ -23528,7 +23528,7 @@
         <v>1.25</v>
       </c>
       <c r="AK142">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23618,10 +23618,10 @@
         </is>
       </c>
       <c r="N143">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O143">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P143">
         <v>2.87</v>
@@ -23796,13 +23796,13 @@
         <v>2.45</v>
       </c>
       <c r="S144">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="T144">
         <v>2.59</v>
       </c>
       <c r="U144">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="V144">
         <v>1.36</v>
@@ -23835,10 +23835,10 @@
         <v>1.06</v>
       </c>
       <c r="AF144">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AG144">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AK144">
-        <v>3.18</v>
+        <v>3.38</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -24270,25 +24270,25 @@
         </is>
       </c>
       <c r="N147">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="O147">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P147">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="Q147">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="R147">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S147">
         <v>1.39</v>
       </c>
       <c r="T147">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="U147">
         <v>2.71</v>
@@ -24321,7 +24321,7 @@
         <v>1.32</v>
       </c>
       <c r="AE147">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF147">
         <v>1.85</v>
@@ -24343,7 +24343,7 @@
         <v>1.2</v>
       </c>
       <c r="AK147">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24436,10 +24436,10 @@
         <v>1.88</v>
       </c>
       <c r="O148">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P148">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q148">
         <v>2.57</v>
@@ -24457,7 +24457,7 @@
         <v>3.5</v>
       </c>
       <c r="V148">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W148">
         <v>1.02</v>
@@ -24472,19 +24472,19 @@
         <v>2.44</v>
       </c>
       <c r="AA148">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AB148">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AC148">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="AD148">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AE148">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AF148">
         <v>2.16</v>
@@ -24922,16 +24922,16 @@
         </is>
       </c>
       <c r="N151">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="O151">
         <v>3.1</v>
       </c>
       <c r="P151">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="Q151">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="R151">
         <v>2</v>
@@ -24952,19 +24952,19 @@
         <v>1.02</v>
       </c>
       <c r="X151">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y151">
         <v>1.32</v>
       </c>
       <c r="Z151">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="AA151">
         <v>2.2</v>
       </c>
       <c r="AB151">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC151">
         <v>3.42</v>
@@ -24973,10 +24973,10 @@
         <v>1.23</v>
       </c>
       <c r="AE151">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF151">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AG151">
         <v>1.89</v>
@@ -25085,13 +25085,13 @@
         </is>
       </c>
       <c r="N152">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O152">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P152">
-        <v>2.68</v>
+        <v>2.79</v>
       </c>
       <c r="Q152">
         <v>2.9</v>
@@ -25100,7 +25100,7 @@
         <v>2.16</v>
       </c>
       <c r="S152">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T152">
         <v>3.3</v>
@@ -25109,40 +25109,40 @@
         <v>2.36</v>
       </c>
       <c r="V152">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W152">
         <v>1.08</v>
       </c>
       <c r="X152">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y152">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z152">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA152">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AB152">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AC152">
         <v>2.78</v>
       </c>
       <c r="AD152">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE152">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AF152">
         <v>1.57</v>
       </c>
       <c r="AG152">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK152">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25580,7 +25580,7 @@
         <v>4.5</v>
       </c>
       <c r="P155">
-        <v>7</v>
+        <v>6.1</v>
       </c>
       <c r="Q155">
         <v>1.85</v>
@@ -25595,7 +25595,7 @@
         <v>3.36</v>
       </c>
       <c r="U155">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="V155">
         <v>1.53</v>
@@ -25737,13 +25737,13 @@
         </is>
       </c>
       <c r="N156">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O156">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P156">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q156">
         <v>3.1</v>
@@ -25752,10 +25752,10 @@
         <v>2.05</v>
       </c>
       <c r="S156">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T156">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="U156">
         <v>2.85</v>
@@ -25776,7 +25776,7 @@
         <v>3.25</v>
       </c>
       <c r="AA156">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AB156">
         <v>1.76</v>
@@ -25794,7 +25794,7 @@
         <v>1.73</v>
       </c>
       <c r="AG156">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK156">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25900,25 +25900,25 @@
         </is>
       </c>
       <c r="N157">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="O157">
         <v>3</v>
       </c>
       <c r="P157">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="Q157">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="R157">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="S157">
         <v>1.57</v>
       </c>
       <c r="T157">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="U157">
         <v>3.6</v>
@@ -25927,13 +25927,13 @@
         <v>1.25</v>
       </c>
       <c r="W157">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X157">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y157">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Z157">
         <v>2.5</v>
@@ -25945,16 +25945,16 @@
         <v>1.46</v>
       </c>
       <c r="AC157">
-        <v>5.1</v>
+        <v>5.16</v>
       </c>
       <c r="AD157">
         <v>1.17</v>
       </c>
       <c r="AE157">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF157">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="AG157">
         <v>1.67</v>
@@ -25970,7 +25970,7 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="AK157">
         <v>1.73</v>
@@ -26226,13 +26226,13 @@
         </is>
       </c>
       <c r="N159">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="O159">
         <v>3.4</v>
       </c>
       <c r="P159">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q159">
         <v>2.3</v>
@@ -26274,7 +26274,7 @@
         <v>3.24</v>
       </c>
       <c r="AD159">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE159">
         <v>1.08</v>
@@ -26389,13 +26389,13 @@
         </is>
       </c>
       <c r="N160">
-        <v>4.98</v>
+        <v>5</v>
       </c>
       <c r="O160">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P160">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="Q160">
         <v>4.8</v>
@@ -26416,19 +26416,19 @@
         <v>1.38</v>
       </c>
       <c r="W160">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X160">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y160">
         <v>1.29</v>
       </c>
       <c r="Z160">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AA160">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AB160">
         <v>1.87</v>
@@ -26555,7 +26555,7 @@
         <v>1.11</v>
       </c>
       <c r="O161">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="P161">
         <v>17</v>
@@ -26570,13 +26570,13 @@
         <v>1.19</v>
       </c>
       <c r="T161">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="U161">
         <v>2.08</v>
       </c>
       <c r="V161">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W161">
         <v>1.16</v>
@@ -26585,25 +26585,25 @@
         <v>1.01</v>
       </c>
       <c r="Y161">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z161">
         <v>5.75</v>
       </c>
       <c r="AA161">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AB161">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AC161">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AD161">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AE161">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AF161">
         <v>2.55</v>
@@ -26881,7 +26881,7 @@
         <v>2.2</v>
       </c>
       <c r="O163">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
       <c r="P163">
         <v>2.6</v>
@@ -26917,10 +26917,10 @@
         <v>0</v>
       </c>
       <c r="AA163">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB163">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC163">
         <v>0</v>
@@ -27041,58 +27041,58 @@
         </is>
       </c>
       <c r="N164">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="O164">
         <v>4.4</v>
       </c>
       <c r="P164">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="Q164">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="R164">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="S164">
         <v>1.14</v>
       </c>
       <c r="T164">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="U164">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="V164">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="W164">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="X164">
         <v>1.01</v>
       </c>
       <c r="Y164">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Z164">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="AA164">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AB164">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="AC164">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AD164">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AE164">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AF164">
         <v>1.33</v>
@@ -27114,7 +27114,7 @@
         <v>1.2</v>
       </c>
       <c r="AK164">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -27693,19 +27693,19 @@
         </is>
       </c>
       <c r="N168">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O168">
         <v>2.95</v>
       </c>
       <c r="P168">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="Q168">
         <v>2.9</v>
       </c>
       <c r="R168">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="S168">
         <v>1.52</v>
@@ -27732,13 +27732,13 @@
         <v>2.63</v>
       </c>
       <c r="AA168">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AB168">
         <v>1.53</v>
       </c>
       <c r="AC168">
-        <v>4.1</v>
+        <v>4.82</v>
       </c>
       <c r="AD168">
         <v>1.14</v>
@@ -27750,7 +27750,7 @@
         <v>2</v>
       </c>
       <c r="AG168">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
@@ -27856,13 +27856,13 @@
         </is>
       </c>
       <c r="N169">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="O169">
         <v>3</v>
       </c>
       <c r="P169">
-        <v>3.37</v>
+        <v>3.32</v>
       </c>
       <c r="Q169">
         <v>0</v>
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,64 +28508,64 @@
         </is>
       </c>
       <c r="N173">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="O173">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P173">
-        <v>2.87</v>
+        <v>2.6</v>
       </c>
       <c r="Q173">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="R173">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="S173">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T173">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="U173">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="V173">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="W173">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X173">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y173">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="Z173">
-        <v>2.88</v>
+        <v>2.49</v>
       </c>
       <c r="AA173">
-        <v>2.15</v>
+        <v>2.44</v>
       </c>
       <c r="AB173">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="AC173">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AD173">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AE173">
         <v>1.04</v>
       </c>
       <c r="AF173">
-        <v>1.8</v>
+        <v>2.01</v>
       </c>
       <c r="AG173">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28578,10 +28578,10 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AK173">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,31 +28671,31 @@
         </is>
       </c>
       <c r="N174">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="O174">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P174">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="Q174">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="R174">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="S174">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="T174">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="U174">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="V174">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W174">
         <v>1.05</v>
@@ -28704,31 +28704,31 @@
         <v>1.06</v>
       </c>
       <c r="Y174">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="Z174">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="AA174">
-        <v>2.45</v>
+        <v>2.24</v>
       </c>
       <c r="AB174">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AC174">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="AD174">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AE174">
         <v>1.04</v>
       </c>
       <c r="AF174">
-        <v>2.04</v>
+        <v>1.83</v>
       </c>
       <c r="AG174">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AH174" t="inlineStr">
         <is>
@@ -28744,7 +28744,7 @@
         <v>1.3</v>
       </c>
       <c r="AK174">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -29160,7 +29160,7 @@
         </is>
       </c>
       <c r="N177">
-        <v>3.85</v>
+        <v>3.28</v>
       </c>
       <c r="O177">
         <v>3.31</v>
@@ -29169,55 +29169,55 @@
         <v>1.76</v>
       </c>
       <c r="Q177">
-        <v>4.25</v>
+        <v>4.48</v>
       </c>
       <c r="R177">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="S177">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T177">
         <v>3.2</v>
       </c>
       <c r="U177">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="V177">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="W177">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X177">
         <v>1.03</v>
       </c>
       <c r="Y177">
+        <v>1.16</v>
+      </c>
+      <c r="Z177">
+        <v>4.1</v>
+      </c>
+      <c r="AA177">
+        <v>1.62</v>
+      </c>
+      <c r="AB177">
+        <v>2.12</v>
+      </c>
+      <c r="AC177">
+        <v>2.5</v>
+      </c>
+      <c r="AD177">
+        <v>1.4</v>
+      </c>
+      <c r="AE177">
         <v>1.17</v>
       </c>
-      <c r="Z177">
-        <v>4</v>
-      </c>
-      <c r="AA177">
-        <v>1.65</v>
-      </c>
-      <c r="AB177">
-        <v>2.08</v>
-      </c>
-      <c r="AC177">
-        <v>2.63</v>
-      </c>
-      <c r="AD177">
-        <v>1.5</v>
-      </c>
-      <c r="AE177">
-        <v>1.15</v>
-      </c>
       <c r="AF177">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="AG177">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,7 +29230,7 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK177">
         <v>1.22</v>
@@ -29649,16 +29649,16 @@
         </is>
       </c>
       <c r="N180">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="O180">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P180">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="Q180">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R180">
         <v>1.87</v>
@@ -29673,13 +29673,13 @@
         <v>3.5</v>
       </c>
       <c r="V180">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="W180">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X180">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y180">
         <v>1.5</v>
@@ -29688,13 +29688,13 @@
         <v>2.49</v>
       </c>
       <c r="AA180">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="AB180">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AC180">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AD180">
         <v>1.12</v>
@@ -29706,7 +29706,7 @@
         <v>2</v>
       </c>
       <c r="AG180">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AH180" t="inlineStr">
         <is>
@@ -29821,19 +29821,19 @@
         <v>2.58</v>
       </c>
       <c r="Q181">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="R181">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S181">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T181">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U181">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="V181">
         <v>1.42</v>
@@ -29845,7 +29845,7 @@
         <v>1.04</v>
       </c>
       <c r="Y181">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z181">
         <v>3.05</v>
@@ -29860,16 +29860,16 @@
         <v>3.3</v>
       </c>
       <c r="AD181">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE181">
-        <v>1.5</v>
+        <v>1.08</v>
       </c>
       <c r="AF181">
         <v>1.74</v>
       </c>
       <c r="AG181">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AH181" t="inlineStr">
         <is>
@@ -29885,7 +29885,7 @@
         <v>1.44</v>
       </c>
       <c r="AK181">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AL181">
         <v>0</v>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="O3">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P3">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="Q3">
-        <v>4.6</v>
+        <v>4.16</v>
       </c>
       <c r="R3">
         <v>2.06</v>
       </c>
       <c r="S3">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T3">
         <v>2.9</v>
       </c>
       <c r="U3">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="V3">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="W3">
         <v>1.05</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z3">
         <v>3.34</v>
       </c>
       <c r="AA3">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB3">
         <v>1.9</v>
       </c>
       <c r="AC3">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AD3">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE3">
         <v>1.07</v>
       </c>
       <c r="AF3">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG3">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="O4">
         <v>3.4</v>
       </c>
       <c r="P4">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="Q4">
         <v>2.63</v>
@@ -976,7 +976,7 @@
         <v>2.3</v>
       </c>
       <c r="S4">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T4">
         <v>3.2</v>
@@ -1034,7 +1034,7 @@
         <v>1.23</v>
       </c>
       <c r="AK4">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1776,25 +1776,25 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O9">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P9">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
       </c>
       <c r="R9">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="S9">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T9">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="U9">
         <v>2.88</v>
@@ -1809,22 +1809,22 @@
         <v>1.03</v>
       </c>
       <c r="Y9">
+        <v>1.3</v>
+      </c>
+      <c r="Z9">
+        <v>2.97</v>
+      </c>
+      <c r="AA9">
+        <v>2.01</v>
+      </c>
+      <c r="AB9">
+        <v>1.7</v>
+      </c>
+      <c r="AC9">
+        <v>3.45</v>
+      </c>
+      <c r="AD9">
         <v>1.29</v>
-      </c>
-      <c r="Z9">
-        <v>3.04</v>
-      </c>
-      <c r="AA9">
-        <v>2</v>
-      </c>
-      <c r="AB9">
-        <v>1.71</v>
-      </c>
-      <c r="AC9">
-        <v>3.5</v>
-      </c>
-      <c r="AD9">
-        <v>1.22</v>
       </c>
       <c r="AE9">
         <v>1.07</v>
@@ -1833,7 +1833,7 @@
         <v>1.78</v>
       </c>
       <c r="AG9">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="AK9">
         <v>1.3</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>4.4</v>
+        <v>4.41</v>
       </c>
       <c r="O12">
-        <v>3.97</v>
+        <v>4</v>
       </c>
       <c r="P12">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="Q12">
         <v>4.55</v>
@@ -2301,10 +2301,10 @@
         <v>1.15</v>
       </c>
       <c r="Z12">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA12">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="AB12">
         <v>2.4</v>
@@ -2316,13 +2316,13 @@
         <v>1.6</v>
       </c>
       <c r="AE12">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AF12">
         <v>1.5</v>
       </c>
       <c r="AG12">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.93</v>
+        <v>3.39</v>
       </c>
       <c r="O13">
         <v>3.05</v>
       </c>
       <c r="P13">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="Q13">
         <v>3.3</v>
@@ -2443,16 +2443,16 @@
         <v>2.04</v>
       </c>
       <c r="S13">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T13">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U13">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="V13">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="W13">
         <v>1.1</v>
@@ -2473,16 +2473,16 @@
         <v>2.15</v>
       </c>
       <c r="AC13">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AD13">
         <v>1.57</v>
       </c>
       <c r="AE13">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF13">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG13">
         <v>2.4</v>
@@ -3083,7 +3083,7 @@
         <v>2.15</v>
       </c>
       <c r="O17">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="P17">
         <v>3.01</v>
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="O18">
-        <v>3.54</v>
+        <v>3.85</v>
       </c>
       <c r="P18">
         <v>3.46</v>
@@ -3288,10 +3288,10 @@
         <v>2.17</v>
       </c>
       <c r="AC18">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="AD18">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AE18">
         <v>1.21</v>
@@ -3316,7 +3316,7 @@
         <v>1.24</v>
       </c>
       <c r="AK18">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3421,7 +3421,7 @@
         <v>2.4</v>
       </c>
       <c r="S19">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T19">
         <v>3.34</v>
@@ -3430,19 +3430,19 @@
         <v>2.25</v>
       </c>
       <c r="V19">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="W19">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
         <v>1.12</v>
       </c>
       <c r="Z19">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA19">
         <v>1.54</v>
@@ -3451,13 +3451,13 @@
         <v>2.45</v>
       </c>
       <c r="AC19">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AD19">
         <v>1.5</v>
       </c>
       <c r="AE19">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF19">
         <v>1.5</v>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="O20">
-        <v>3.51</v>
+        <v>3.6</v>
       </c>
       <c r="P20">
         <v>5.4</v>
@@ -3602,7 +3602,7 @@
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z20">
         <v>3.05</v>
@@ -3901,7 +3901,7 @@
         <v>3.4</v>
       </c>
       <c r="P22">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="O25">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="P25">
         <v>5.5</v>
@@ -4396,7 +4396,7 @@
         <v>1.91</v>
       </c>
       <c r="R25">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="S25">
         <v>1.25</v>
@@ -4432,7 +4432,7 @@
         <v>2.33</v>
       </c>
       <c r="AD25">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="AE25">
         <v>1.24</v>
@@ -4441,7 +4441,7 @@
         <v>1.65</v>
       </c>
       <c r="AG25">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4713,10 +4713,10 @@
         <v>1.53</v>
       </c>
       <c r="O27">
+        <v>4.7</v>
+      </c>
+      <c r="P27">
         <v>4.6</v>
-      </c>
-      <c r="P27">
-        <v>5.2</v>
       </c>
       <c r="Q27">
         <v>1.93</v>
@@ -4728,7 +4728,7 @@
         <v>1.18</v>
       </c>
       <c r="T27">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="U27">
         <v>1.95</v>
@@ -4764,10 +4764,10 @@
         <v>1.34</v>
       </c>
       <c r="AF27">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AG27">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AK27">
         <v>2.45</v>
@@ -4873,22 +4873,22 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="O28">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="P28">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="Q28">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="R28">
         <v>2.35</v>
       </c>
       <c r="S28">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T28">
         <v>3.22</v>
@@ -4903,16 +4903,16 @@
         <v>1.12</v>
       </c>
       <c r="X28">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y28">
         <v>1.2</v>
       </c>
       <c r="Z28">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="AA28">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AB28">
         <v>2.15</v>
@@ -4930,7 +4930,7 @@
         <v>1.73</v>
       </c>
       <c r="AG28">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="O29">
         <v>3.5</v>
       </c>
       <c r="P29">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="Q29">
         <v>2.2</v>
@@ -5060,7 +5060,7 @@
         <v>2.91</v>
       </c>
       <c r="V29">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="W29">
         <v>1.07</v>
@@ -5075,7 +5075,7 @@
         <v>3.2</v>
       </c>
       <c r="AA29">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AB29">
         <v>1.8</v>
@@ -5084,10 +5084,10 @@
         <v>3.3</v>
       </c>
       <c r="AD29">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE29">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF29">
         <v>1.83</v>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AK29">
         <v>2.14</v>
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="O30">
         <v>3.55</v>
@@ -5232,7 +5232,7 @@
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z30">
         <v>4</v>
@@ -5241,7 +5241,7 @@
         <v>1.64</v>
       </c>
       <c r="AB30">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AC30">
         <v>2.38</v>
@@ -5250,7 +5250,7 @@
         <v>1.47</v>
       </c>
       <c r="AE30">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF30">
         <v>1.55</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>6.05</v>
+        <v>5.82</v>
       </c>
       <c r="O33">
-        <v>4.62</v>
+        <v>4.45</v>
       </c>
       <c r="P33">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="Q33">
         <v>5</v>
@@ -5706,7 +5706,7 @@
         <v>1.2</v>
       </c>
       <c r="T33">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U33">
         <v>2.05</v>
@@ -5724,7 +5724,7 @@
         <v>1.14</v>
       </c>
       <c r="Z33">
-        <v>5.83</v>
+        <v>5.72</v>
       </c>
       <c r="AA33">
         <v>1.41</v>
@@ -5733,19 +5733,19 @@
         <v>2.6</v>
       </c>
       <c r="AC33">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="AD33">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AE33">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AF33">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AG33">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>1.2</v>
       </c>
       <c r="AK33">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O34">
         <v>3.5</v>
       </c>
       <c r="P34">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="Q34">
         <v>2.8</v>
@@ -5866,10 +5866,10 @@
         <v>2.33</v>
       </c>
       <c r="S34">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T34">
-        <v>2.86</v>
+        <v>3.02</v>
       </c>
       <c r="U34">
         <v>2.45</v>
@@ -5878,25 +5878,25 @@
         <v>1.48</v>
       </c>
       <c r="W34">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X34">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
         <v>1.2</v>
       </c>
       <c r="Z34">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="AA34">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB34">
         <v>2</v>
       </c>
       <c r="AC34">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="AD34">
         <v>1.33</v>
@@ -6017,7 +6017,7 @@
         <v>1.59</v>
       </c>
       <c r="O35">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="P35">
         <v>5.14</v>
@@ -6053,7 +6053,7 @@
         <v>3.34</v>
       </c>
       <c r="AA35">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AB35">
         <v>1.9</v>
@@ -6071,7 +6071,7 @@
         <v>1.85</v>
       </c>
       <c r="AG35">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="O36">
         <v>3.1</v>
@@ -6189,16 +6189,16 @@
         <v>3.04</v>
       </c>
       <c r="R36">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S36">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="T36">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="U36">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="V36">
         <v>1.35</v>
@@ -6210,31 +6210,31 @@
         <v>1.06</v>
       </c>
       <c r="Y36">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z36">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AA36">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AB36">
         <v>1.81</v>
       </c>
       <c r="AC36">
-        <v>3.62</v>
+        <v>3.34</v>
       </c>
       <c r="AD36">
         <v>1.25</v>
       </c>
       <c r="AE36">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF36">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG36">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AK36">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q37">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="R37">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S37">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T37">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="U37">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="V37">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W37">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y37">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z37">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA37">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AB37">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC37">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AD37">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE37">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF37">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG37">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK37">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="O39">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="P39">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="Q39">
         <v>1.57</v>
@@ -6711,7 +6711,7 @@
         <v>2.49</v>
       </c>
       <c r="AC39">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AD39">
         <v>1.66</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AK39">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="O40">
         <v>3.58</v>
       </c>
       <c r="P40">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Q40">
         <v>2.17</v>
@@ -6883,7 +6883,7 @@
         <v>1.18</v>
       </c>
       <c r="AF40">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG40">
         <v>2.25</v>
@@ -6902,7 +6902,7 @@
         <v>1.25</v>
       </c>
       <c r="AK40">
-        <v>1.89</v>
+        <v>2.01</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7807,28 +7807,28 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="O46">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P46">
         <v>5</v>
       </c>
       <c r="Q46">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="R46">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S46">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T46">
         <v>2.77</v>
       </c>
       <c r="U46">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="V46">
         <v>1.4</v>
@@ -7837,13 +7837,13 @@
         <v>1.05</v>
       </c>
       <c r="X46">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y46">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z46">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="AA46">
         <v>1.95</v>
@@ -7852,19 +7852,19 @@
         <v>1.86</v>
       </c>
       <c r="AC46">
-        <v>3.12</v>
+        <v>3.41</v>
       </c>
       <c r="AD46">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AE46">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF46">
         <v>1.87</v>
       </c>
       <c r="AG46">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AK46">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,19 +7970,19 @@
         </is>
       </c>
       <c r="N47">
-        <v>3.4</v>
+        <v>4.78</v>
       </c>
       <c r="O47">
-        <v>3.75</v>
+        <v>3.92</v>
       </c>
       <c r="P47">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Q47">
-        <v>4.23</v>
+        <v>4.29</v>
       </c>
       <c r="R47">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="S47">
         <v>1.28</v>
@@ -7994,19 +7994,19 @@
         <v>2.36</v>
       </c>
       <c r="V47">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W47">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X47">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z47">
-        <v>4.67</v>
+        <v>3.95</v>
       </c>
       <c r="AA47">
         <v>1.62</v>
@@ -8015,16 +8015,16 @@
         <v>2.26</v>
       </c>
       <c r="AC47">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="AD47">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AE47">
         <v>1.15</v>
       </c>
       <c r="AF47">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AG47">
         <v>2.25</v>
@@ -8468,55 +8468,55 @@
         <v>14</v>
       </c>
       <c r="Q50">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R50">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="S50">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T50">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="U50">
         <v>2.06</v>
       </c>
       <c r="V50">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="W50">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X50">
         <v>0</v>
       </c>
       <c r="Y50">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="Z50">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AA50">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AB50">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="AC50">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AD50">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AE50">
         <v>1.28</v>
       </c>
       <c r="AF50">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AG50">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>1.08</v>
       </c>
       <c r="AK50">
-        <v>6.15</v>
+        <v>6.2</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -9437,10 +9437,10 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="O56">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="P56">
         <v>2.23</v>
@@ -9464,13 +9464,13 @@
         <v>1.22</v>
       </c>
       <c r="W56">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X56">
         <v>1.11</v>
       </c>
       <c r="Y56">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Z56">
         <v>2.48</v>
@@ -9482,7 +9482,7 @@
         <v>1.44</v>
       </c>
       <c r="AC56">
-        <v>5.57</v>
+        <v>5.62</v>
       </c>
       <c r="AD56">
         <v>1.14</v>
@@ -9491,7 +9491,7 @@
         <v>1.04</v>
       </c>
       <c r="AF56">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AG56">
         <v>1.67</v>
@@ -9603,10 +9603,10 @@
         <v>2.83</v>
       </c>
       <c r="O57">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P57">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="O58">
         <v>3.6</v>
       </c>
       <c r="P58">
-        <v>4</v>
+        <v>4.49</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -9929,13 +9929,13 @@
         <v>1.8</v>
       </c>
       <c r="O59">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P59">
-        <v>3.82</v>
+        <v>3.85</v>
       </c>
       <c r="Q59">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="R59">
         <v>2.44</v>
@@ -9947,10 +9947,10 @@
         <v>4.5</v>
       </c>
       <c r="U59">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="V59">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="W59">
         <v>1.17</v>
@@ -9971,7 +9971,7 @@
         <v>2.7</v>
       </c>
       <c r="AC59">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AD59">
         <v>1.73</v>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK59">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="O60">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="P60">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Q60">
         <v>1.88</v>
@@ -10116,7 +10116,7 @@
         <v>1.68</v>
       </c>
       <c r="W60">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X60">
         <v>1.02</v>
@@ -10134,10 +10134,10 @@
         <v>2.5</v>
       </c>
       <c r="AC60">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="AD60">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AE60">
         <v>1.24</v>
@@ -10162,7 +10162,7 @@
         <v>1.14</v>
       </c>
       <c r="AK60">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,10 +10252,10 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="O61">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P61">
         <v>3.2</v>
@@ -10294,7 +10294,7 @@
         <v>1.44</v>
       </c>
       <c r="AB61">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AC61">
         <v>2.05</v>
@@ -10306,7 +10306,7 @@
         <v>1.29</v>
       </c>
       <c r="AF61">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AG61">
         <v>2.8</v>
@@ -10904,34 +10904,34 @@
         </is>
       </c>
       <c r="N65">
-        <v>4.3</v>
+        <v>5.15</v>
       </c>
       <c r="O65">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P65">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="Q65">
-        <v>5.25</v>
+        <v>4.42</v>
       </c>
       <c r="R65">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S65">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T65">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="U65">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="V65">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W65">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X65">
         <v>1.04</v>
@@ -10940,19 +10940,19 @@
         <v>1.22</v>
       </c>
       <c r="Z65">
-        <v>3.78</v>
+        <v>3.52</v>
       </c>
       <c r="AA65">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB65">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AC65">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AD65">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE65">
         <v>1.14</v>
@@ -10977,7 +10977,7 @@
         <v>2.28</v>
       </c>
       <c r="AK65">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11076,10 +11076,10 @@
         <v>2.6</v>
       </c>
       <c r="Q66">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="R66">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="S66">
         <v>1.29</v>
@@ -11088,7 +11088,7 @@
         <v>3.3</v>
       </c>
       <c r="U66">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V66">
         <v>1.47</v>
@@ -11109,7 +11109,7 @@
         <v>1.7</v>
       </c>
       <c r="AB66">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AC66">
         <v>2.8</v>
@@ -11140,7 +11140,7 @@
         <v>1.4</v>
       </c>
       <c r="AK66">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11233,7 +11233,7 @@
         <v>2.9</v>
       </c>
       <c r="O67">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="P67">
         <v>2.25</v>
@@ -11245,7 +11245,7 @@
         <v>2.4</v>
       </c>
       <c r="S67">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T67">
         <v>3.75</v>
@@ -11266,16 +11266,16 @@
         <v>1.15</v>
       </c>
       <c r="Z67">
-        <v>5</v>
+        <v>5.35</v>
       </c>
       <c r="AA67">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB67">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AC67">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="AD67">
         <v>1.69</v>
@@ -11287,7 +11287,7 @@
         <v>1.4</v>
       </c>
       <c r="AG67">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="O68">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P68">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q68">
         <v>2.91</v>
@@ -11426,7 +11426,7 @@
         <v>1.03</v>
       </c>
       <c r="Y68">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z68">
         <v>4.65</v>
@@ -11447,7 +11447,7 @@
         <v>1.18</v>
       </c>
       <c r="AF68">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG68">
         <v>2.5</v>
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>5.82</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q69">
-        <v>5.94</v>
+        <v>0</v>
       </c>
       <c r="R69">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S69">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T69">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U69">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="V69">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W69">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X69">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y69">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z69">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA69">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AB69">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC69">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AD69">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE69">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF69">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG69">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK69">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.15</v>
+        <v>1.63</v>
       </c>
       <c r="O71">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="P71">
-        <v>3.05</v>
+        <v>4.85</v>
       </c>
       <c r="Q71">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="R71">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="S71">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T71">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="U71">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="V71">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W71">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X71">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y71">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z71">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="AA71">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB71">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AC71">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AD71">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE71">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF71">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AG71">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.32</v>
+        <v>1.09</v>
       </c>
       <c r="AK71">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="O72">
-        <v>3.84</v>
+        <v>3.3</v>
       </c>
       <c r="P72">
-        <v>4.85</v>
+        <v>3.17</v>
       </c>
       <c r="Q72">
-        <v>2.1</v>
+        <v>2.86</v>
       </c>
       <c r="R72">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="S72">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="T72">
-        <v>3.2</v>
+        <v>2.73</v>
       </c>
       <c r="U72">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="V72">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="W72">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X72">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y72">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z72">
-        <v>3.67</v>
+        <v>3.4</v>
       </c>
       <c r="AA72">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB72">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AC72">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AD72">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE72">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF72">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AG72">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.09</v>
+        <v>1.32</v>
       </c>
       <c r="AK72">
-        <v>2.16</v>
+        <v>1.6</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12211,7 +12211,7 @@
         <v>2.05</v>
       </c>
       <c r="O73">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="P73">
         <v>2.76</v>
@@ -12220,7 +12220,7 @@
         <v>2.55</v>
       </c>
       <c r="R73">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="S73">
         <v>1.25</v>
@@ -12229,22 +12229,22 @@
         <v>3.8</v>
       </c>
       <c r="U73">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="V73">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W73">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X73">
         <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Z73">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AA73">
         <v>1.5</v>
@@ -12253,19 +12253,19 @@
         <v>2.55</v>
       </c>
       <c r="AC73">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="AD73">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AE73">
         <v>1.22</v>
       </c>
       <c r="AF73">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AG73">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12534,10 +12534,10 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="O75">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P75">
         <v>2.27</v>
@@ -12546,7 +12546,7 @@
         <v>3.35</v>
       </c>
       <c r="R75">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="S75">
         <v>1.41</v>
@@ -12555,10 +12555,10 @@
         <v>2.62</v>
       </c>
       <c r="U75">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="V75">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W75">
         <v>1.05</v>
@@ -12573,7 +12573,7 @@
         <v>3.25</v>
       </c>
       <c r="AA75">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AB75">
         <v>1.78</v>
@@ -12697,19 +12697,19 @@
         </is>
       </c>
       <c r="N76">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O76">
-        <v>3.5</v>
+        <v>3.61</v>
       </c>
       <c r="P76">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="Q76">
-        <v>4.21</v>
+        <v>4.26</v>
       </c>
       <c r="R76">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S76">
         <v>1.28</v>
@@ -12724,7 +12724,7 @@
         <v>1.53</v>
       </c>
       <c r="W76">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X76">
         <v>1.03</v>
@@ -12733,22 +12733,22 @@
         <v>1.2</v>
       </c>
       <c r="Z76">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AA76">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB76">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="AC76">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="AD76">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AE76">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AF76">
         <v>1.53</v>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.85</v>
+        <v>1.25</v>
       </c>
       <c r="AK76">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="O85">
         <v>3.5</v>
       </c>
       <c r="P85">
-        <v>3.8</v>
+        <v>3.93</v>
       </c>
       <c r="Q85">
         <v>2.38</v>
@@ -14185,13 +14185,13 @@
         <v>3.08</v>
       </c>
       <c r="U85">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="V85">
         <v>1.47</v>
       </c>
       <c r="W85">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X85">
         <v>1.02</v>
@@ -14200,16 +14200,16 @@
         <v>1.23</v>
       </c>
       <c r="Z85">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AA85">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AB85">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AC85">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="AD85">
         <v>1.36</v>
@@ -14234,7 +14234,7 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK85">
         <v>1.95</v>
@@ -14496,13 +14496,13 @@
         <v>3.3</v>
       </c>
       <c r="P87">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="Q87">
         <v>2.94</v>
       </c>
       <c r="R87">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S87">
         <v>1.32</v>
@@ -14520,19 +14520,19 @@
         <v>1.11</v>
       </c>
       <c r="X87">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y87">
         <v>1.19</v>
       </c>
       <c r="Z87">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AA87">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AB87">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AC87">
         <v>2.69</v>
@@ -14563,7 +14563,7 @@
         <v>1.38</v>
       </c>
       <c r="AK87">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14816,37 +14816,37 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="O89">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P89">
-        <v>4.25</v>
+        <v>5.25</v>
       </c>
       <c r="Q89">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R89">
         <v>2.38</v>
       </c>
       <c r="S89">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T89">
         <v>3.4</v>
       </c>
       <c r="U89">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="V89">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W89">
         <v>1.08</v>
       </c>
       <c r="X89">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y89">
         <v>1.18</v>
@@ -15142,10 +15142,10 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="O91">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P91">
         <v>2.5</v>
@@ -15187,19 +15187,19 @@
         <v>1.6</v>
       </c>
       <c r="AC91">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="AD91">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE91">
         <v>1.03</v>
       </c>
       <c r="AF91">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG91">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         <v>1.33</v>
       </c>
       <c r="AK91">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15305,25 +15305,25 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="O92">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="P92">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q92">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R92">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="S92">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="T92">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="U92">
         <v>3.3</v>
@@ -15332,28 +15332,28 @@
         <v>1.28</v>
       </c>
       <c r="W92">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X92">
         <v>1.06</v>
       </c>
       <c r="Y92">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="Z92">
         <v>2.55</v>
       </c>
       <c r="AA92">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AB92">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AC92">
         <v>4.4</v>
       </c>
       <c r="AD92">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE92">
         <v>1.03</v>
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O97">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q97">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="R97">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S97">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T97">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="U97">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V97">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W97">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X97">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y97">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z97">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA97">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB97">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AC97">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AD97">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE97">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF97">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG97">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK97">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16283,31 +16283,31 @@
         </is>
       </c>
       <c r="N98">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="O98">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P98">
+        <v>2.16</v>
+      </c>
+      <c r="Q98">
+        <v>3.8</v>
+      </c>
+      <c r="R98">
         <v>2.05</v>
       </c>
-      <c r="Q98">
-        <v>3.7</v>
-      </c>
-      <c r="R98">
-        <v>2</v>
-      </c>
       <c r="S98">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T98">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="U98">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="V98">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W98">
         <v>1.07</v>
@@ -16316,25 +16316,25 @@
         <v>1.06</v>
       </c>
       <c r="Y98">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z98">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AA98">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AB98">
         <v>1.66</v>
       </c>
       <c r="AC98">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AD98">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE98">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF98">
         <v>1.83</v>
@@ -16356,7 +16356,7 @@
         <v>1.64</v>
       </c>
       <c r="AK98">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16624,10 +16624,10 @@
         <v>1.91</v>
       </c>
       <c r="S100">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="T100">
-        <v>2.43</v>
+        <v>2.24</v>
       </c>
       <c r="U100">
         <v>3.42</v>
@@ -16636,7 +16636,7 @@
         <v>1.23</v>
       </c>
       <c r="W100">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X100">
         <v>1.08</v>
@@ -16654,7 +16654,7 @@
         <v>1.48</v>
       </c>
       <c r="AC100">
-        <v>4.84</v>
+        <v>4.5</v>
       </c>
       <c r="AD100">
         <v>1.16</v>
@@ -16666,7 +16666,7 @@
         <v>2.01</v>
       </c>
       <c r="AG100">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16772,25 +16772,25 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="O101">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P101">
         <v>3.6</v>
       </c>
       <c r="Q101">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="R101">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="S101">
         <v>1.37</v>
       </c>
       <c r="T101">
-        <v>2.88</v>
+        <v>2.71</v>
       </c>
       <c r="U101">
         <v>2.86</v>
@@ -16805,16 +16805,16 @@
         <v>1.02</v>
       </c>
       <c r="Y101">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z101">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AA101">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AB101">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AC101">
         <v>3.34</v>
@@ -16823,13 +16823,13 @@
         <v>1.24</v>
       </c>
       <c r="AE101">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF101">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG101">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK101">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -17104,19 +17104,19 @@
         <v>3.1</v>
       </c>
       <c r="P103">
-        <v>4.05</v>
+        <v>3.75</v>
       </c>
       <c r="Q103">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="R103">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S103">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T103">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="U103">
         <v>2.66</v>
@@ -17131,16 +17131,16 @@
         <v>1.03</v>
       </c>
       <c r="Y103">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z103">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA103">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="AB103">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AC103">
         <v>2.92</v>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK103">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17270,55 +17270,55 @@
         <v>2.69</v>
       </c>
       <c r="Q104">
-        <v>2.97</v>
+        <v>2.75</v>
       </c>
       <c r="R104">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="S104">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T104">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="U104">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="V104">
         <v>1.42</v>
       </c>
       <c r="W104">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X104">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y104">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z104">
         <v>3.5</v>
       </c>
       <c r="AA104">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AB104">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC104">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="AD104">
         <v>1.33</v>
       </c>
       <c r="AE104">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF104">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG104">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17596,10 +17596,10 @@
         <v>1.65</v>
       </c>
       <c r="Q106">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="R106">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="S106">
         <v>1.36</v>
@@ -17608,10 +17608,10 @@
         <v>2.88</v>
       </c>
       <c r="U106">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="V106">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W106">
         <v>1.08</v>
@@ -17626,25 +17626,25 @@
         <v>3.25</v>
       </c>
       <c r="AA106">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AB106">
         <v>1.83</v>
       </c>
       <c r="AC106">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="AD106">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE106">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF106">
         <v>1.85</v>
       </c>
       <c r="AG106">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>2.05</v>
+        <v>1.24</v>
       </c>
       <c r="AK106">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17913,31 +17913,31 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="O108">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="P108">
-        <v>7.56</v>
+        <v>7</v>
       </c>
       <c r="Q108">
         <v>1.92</v>
       </c>
       <c r="R108">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="S108">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T108">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="U108">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="V108">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="W108">
         <v>1.07</v>
@@ -17946,22 +17946,22 @@
         <v>1.04</v>
       </c>
       <c r="Y108">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z108">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AA108">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AB108">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC108">
-        <v>2.92</v>
+        <v>3.04</v>
       </c>
       <c r="AD108">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AE108">
         <v>1.08</v>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AK108">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18076,58 +18076,58 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="O109">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="P109">
-        <v>3.6</v>
+        <v>3.97</v>
       </c>
       <c r="Q109">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="R109">
         <v>2.06</v>
       </c>
       <c r="S109">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="T109">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="U109">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="V109">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W109">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X109">
         <v>1.06</v>
       </c>
       <c r="Y109">
+        <v>1.3</v>
+      </c>
+      <c r="Z109">
+        <v>3.25</v>
+      </c>
+      <c r="AA109">
+        <v>1.95</v>
+      </c>
+      <c r="AB109">
+        <v>1.75</v>
+      </c>
+      <c r="AC109">
+        <v>3.71</v>
+      </c>
+      <c r="AD109">
         <v>1.28</v>
       </c>
-      <c r="Z109">
-        <v>3.08</v>
-      </c>
-      <c r="AA109">
-        <v>2.02</v>
-      </c>
-      <c r="AB109">
-        <v>1.77</v>
-      </c>
-      <c r="AC109">
-        <v>3.64</v>
-      </c>
-      <c r="AD109">
-        <v>1.25</v>
-      </c>
       <c r="AE109">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AF109">
         <v>1.84</v>
@@ -18149,7 +18149,7 @@
         <v>1.22</v>
       </c>
       <c r="AK109">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18248,55 +18248,55 @@
         <v>3.15</v>
       </c>
       <c r="Q110">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="R110">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="S110">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T110">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U110">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="V110">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W110">
         <v>1.06</v>
       </c>
       <c r="X110">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y110">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z110">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AA110">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AB110">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AC110">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="AD110">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE110">
         <v>1.07</v>
       </c>
       <c r="AF110">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG110">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK110">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18405,10 +18405,10 @@
         <v>2.31</v>
       </c>
       <c r="O111">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P111">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="Q111">
         <v>3.1</v>
@@ -18417,22 +18417,22 @@
         <v>2.1</v>
       </c>
       <c r="S111">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T111">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="U111">
         <v>2.56</v>
       </c>
       <c r="V111">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W111">
         <v>1.06</v>
       </c>
       <c r="X111">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y111">
         <v>1.21</v>
@@ -18447,10 +18447,10 @@
         <v>1.86</v>
       </c>
       <c r="AC111">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="AD111">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE111">
         <v>1.12</v>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AK111">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18565,10 +18565,10 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="O112">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P112">
         <v>4.75</v>
@@ -18731,19 +18731,19 @@
         <v>2</v>
       </c>
       <c r="O113">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="P113">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Q113">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R113">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="S113">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="T113">
         <v>2.2</v>
@@ -18755,13 +18755,13 @@
         <v>1.21</v>
       </c>
       <c r="W113">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X113">
         <v>1.13</v>
       </c>
       <c r="Y113">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="Z113">
         <v>2.2</v>
@@ -18773,19 +18773,19 @@
         <v>1.38</v>
       </c>
       <c r="AC113">
-        <v>5.15</v>
+        <v>6.64</v>
       </c>
       <c r="AD113">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE113">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF113">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AG113">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18891,10 +18891,10 @@
         </is>
       </c>
       <c r="N114">
-        <v>3.4</v>
+        <v>3.07</v>
       </c>
       <c r="O114">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="P114">
         <v>2</v>
@@ -18921,34 +18921,34 @@
         <v>1.07</v>
       </c>
       <c r="X114">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y114">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z114">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="AA114">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB114">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AC114">
         <v>3.1</v>
       </c>
       <c r="AD114">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE114">
         <v>1.1</v>
       </c>
       <c r="AF114">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG114">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18964,7 +18964,7 @@
         <v>1.22</v>
       </c>
       <c r="AK114">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19063,10 +19063,10 @@
         <v>2.83</v>
       </c>
       <c r="Q115">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="R115">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="S115">
         <v>1.32</v>
@@ -19075,10 +19075,10 @@
         <v>3.25</v>
       </c>
       <c r="U115">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="V115">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W115">
         <v>1.09</v>
@@ -19087,19 +19087,19 @@
         <v>1.02</v>
       </c>
       <c r="Y115">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z115">
         <v>4.1</v>
       </c>
       <c r="AA115">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AB115">
         <v>2.15</v>
       </c>
       <c r="AC115">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="AD115">
         <v>1.39</v>
@@ -19124,7 +19124,7 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AK115">
         <v>1.74</v>
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="O116">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="P116">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q116">
         <v>1.55</v>
@@ -19250,19 +19250,19 @@
         <v>1.03</v>
       </c>
       <c r="Y116">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z116">
         <v>5</v>
       </c>
       <c r="AA116">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AB116">
         <v>2.35</v>
       </c>
       <c r="AC116">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AD116">
         <v>1.54</v>
@@ -19290,7 +19290,7 @@
         <v>1.02</v>
       </c>
       <c r="AK116">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19395,10 +19395,10 @@
         <v>2.5</v>
       </c>
       <c r="S117">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="T117">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="U117">
         <v>2.2</v>
@@ -19407,13 +19407,13 @@
         <v>1.63</v>
       </c>
       <c r="W117">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X117">
         <v>1.02</v>
       </c>
       <c r="Y117">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z117">
         <v>5</v>
@@ -19428,7 +19428,7 @@
         <v>2.1</v>
       </c>
       <c r="AD117">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AE117">
         <v>1.25</v>
@@ -19453,7 +19453,7 @@
         <v>1.22</v>
       </c>
       <c r="AK117">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="O118">
-        <v>3.5</v>
+        <v>3.23</v>
       </c>
       <c r="P118">
-        <v>4.63</v>
+        <v>4</v>
       </c>
       <c r="Q118">
         <v>0</v>
@@ -19706,37 +19706,37 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="O119">
         <v>2.75</v>
       </c>
       <c r="P119">
-        <v>2.8</v>
+        <v>2.97</v>
       </c>
       <c r="Q119">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="R119">
         <v>1.77</v>
       </c>
       <c r="S119">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="T119">
         <v>2.04</v>
       </c>
       <c r="U119">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="V119">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W119">
         <v>1.02</v>
       </c>
       <c r="X119">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Y119">
         <v>1.79</v>
@@ -19745,13 +19745,13 @@
         <v>1.98</v>
       </c>
       <c r="AA119">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AB119">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AC119">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="AD119">
         <v>1.08</v>
@@ -19760,10 +19760,10 @@
         <v>1.02</v>
       </c>
       <c r="AF119">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AG119">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -20038,13 +20038,13 @@
         <v>3.21</v>
       </c>
       <c r="P121">
-        <v>4.2</v>
+        <v>3.69</v>
       </c>
       <c r="Q121">
         <v>2.55</v>
       </c>
       <c r="R121">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="S121">
         <v>1.47</v>
@@ -20053,7 +20053,7 @@
         <v>2.6</v>
       </c>
       <c r="U121">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="V121">
         <v>1.33</v>
@@ -20068,13 +20068,13 @@
         <v>1.35</v>
       </c>
       <c r="Z121">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="AA121">
         <v>2.18</v>
       </c>
       <c r="AB121">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AC121">
         <v>3.78</v>
@@ -20195,28 +20195,28 @@
         </is>
       </c>
       <c r="N122">
-        <v>4.27</v>
+        <v>3.8</v>
       </c>
       <c r="O122">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P122">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="Q122">
-        <v>4.95</v>
+        <v>4.2</v>
       </c>
       <c r="R122">
         <v>2.1</v>
       </c>
       <c r="S122">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T122">
         <v>2.65</v>
       </c>
       <c r="U122">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="V122">
         <v>1.35</v>
@@ -20225,22 +20225,22 @@
         <v>1.03</v>
       </c>
       <c r="X122">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y122">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Z122">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="AA122">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AB122">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AC122">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="AD122">
         <v>1.22</v>
@@ -20268,7 +20268,7 @@
         <v>1.22</v>
       </c>
       <c r="AK122">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20358,22 +20358,22 @@
         </is>
       </c>
       <c r="N123">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="O123">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="P123">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="Q123">
         <v>1.86</v>
       </c>
       <c r="R123">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="S123">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T123">
         <v>3</v>
@@ -20382,13 +20382,13 @@
         <v>2.55</v>
       </c>
       <c r="V123">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W123">
         <v>1.07</v>
       </c>
       <c r="X123">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y123">
         <v>1.18</v>
@@ -20397,7 +20397,7 @@
         <v>3.88</v>
       </c>
       <c r="AA123">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB123">
         <v>2</v>
@@ -20406,7 +20406,7 @@
         <v>2.62</v>
       </c>
       <c r="AD123">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AE123">
         <v>1.14</v>
@@ -20415,7 +20415,7 @@
         <v>1.95</v>
       </c>
       <c r="AG123">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20521,25 +20521,25 @@
         </is>
       </c>
       <c r="N124">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="O124">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P124">
-        <v>6.9</v>
+        <v>5.8</v>
       </c>
       <c r="Q124">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="R124">
         <v>2</v>
       </c>
       <c r="S124">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="T124">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="U124">
         <v>3.5</v>
@@ -20557,22 +20557,22 @@
         <v>1.5</v>
       </c>
       <c r="Z124">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="AA124">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AB124">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AC124">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AD124">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AE124">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF124">
         <v>2.45</v>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK124">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20684,19 +20684,19 @@
         </is>
       </c>
       <c r="N125">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="O125">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="P125">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="Q125">
         <v>2.8</v>
       </c>
       <c r="R125">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="S125">
         <v>1.7</v>
@@ -20705,43 +20705,43 @@
         <v>1.99</v>
       </c>
       <c r="U125">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="V125">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W125">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X125">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Y125">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="Z125">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AA125">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AB125">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AC125">
-        <v>5.75</v>
+        <v>5.6</v>
       </c>
       <c r="AD125">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AE125">
         <v>1.02</v>
       </c>
       <c r="AF125">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AG125">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20757,7 +20757,7 @@
         <v>1.2</v>
       </c>
       <c r="AK125">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20850,10 +20850,10 @@
         <v>4.2</v>
       </c>
       <c r="O126">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P126">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="Q126">
         <v>5</v>
@@ -20865,7 +20865,7 @@
         <v>1.38</v>
       </c>
       <c r="T126">
-        <v>2.81</v>
+        <v>2.98</v>
       </c>
       <c r="U126">
         <v>2.81</v>
@@ -20874,28 +20874,28 @@
         <v>1.37</v>
       </c>
       <c r="W126">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X126">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y126">
         <v>1.26</v>
       </c>
       <c r="Z126">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AA126">
         <v>1.8</v>
       </c>
       <c r="AB126">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AC126">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="AD126">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE126">
         <v>1.1</v>
@@ -20904,7 +20904,7 @@
         <v>1.85</v>
       </c>
       <c r="AG126">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20920,7 +20920,7 @@
         <v>2.06</v>
       </c>
       <c r="AK126">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21662,37 +21662,37 @@
         </is>
       </c>
       <c r="N131">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="O131">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P131">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="Q131">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="R131">
         <v>2.1</v>
       </c>
       <c r="S131">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T131">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U131">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V131">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W131">
         <v>1.04</v>
       </c>
       <c r="X131">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y131">
         <v>1.35</v>
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="N132">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O132">
         <v>2.7</v>
       </c>
       <c r="P132">
-        <v>2.24</v>
+        <v>2.35</v>
       </c>
       <c r="Q132">
         <v>4.3</v>
@@ -21840,19 +21840,19 @@
         <v>1.77</v>
       </c>
       <c r="S132">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="T132">
-        <v>2.29</v>
+        <v>2.18</v>
       </c>
       <c r="U132">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="V132">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="W132">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X132">
         <v>1.06</v>
@@ -21864,7 +21864,7 @@
         <v>2.42</v>
       </c>
       <c r="AA132">
-        <v>2.52</v>
+        <v>2.35</v>
       </c>
       <c r="AB132">
         <v>1.43</v>
@@ -21879,7 +21879,7 @@
         <v>1.03</v>
       </c>
       <c r="AF132">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AG132">
         <v>1.64</v>
@@ -21988,28 +21988,28 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="O133">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="P133">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q133">
         <v>3.25</v>
       </c>
       <c r="R133">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="S133">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="T133">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="U133">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="V133">
         <v>1.26</v>
@@ -22027,10 +22027,10 @@
         <v>2.56</v>
       </c>
       <c r="AA133">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="AB133">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC133">
         <v>4.2</v>
@@ -22045,7 +22045,7 @@
         <v>1.85</v>
       </c>
       <c r="AG133">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22061,7 +22061,7 @@
         <v>1.33</v>
       </c>
       <c r="AK133">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22151,13 +22151,13 @@
         </is>
       </c>
       <c r="N134">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O134">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P134">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q134">
         <v>0</v>
@@ -22314,19 +22314,19 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="O135">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P135">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="Q135">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="R135">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S135">
         <v>1.38</v>
@@ -22347,10 +22347,10 @@
         <v>1.05</v>
       </c>
       <c r="Y135">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z135">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA135">
         <v>1.82</v>
@@ -22368,10 +22368,10 @@
         <v>1.11</v>
       </c>
       <c r="AF135">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG135">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>3.4</v>
       </c>
       <c r="P136">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="Q136">
         <v>2.45</v>
@@ -22522,7 +22522,7 @@
         <v>2.15</v>
       </c>
       <c r="AC136">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="AD136">
         <v>1.44</v>
@@ -22534,7 +22534,7 @@
         <v>1.53</v>
       </c>
       <c r="AG136">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AK136">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22643,13 +22643,13 @@
         <v>2.3</v>
       </c>
       <c r="O137">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P137">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="Q137">
-        <v>3.13</v>
+        <v>2.73</v>
       </c>
       <c r="R137">
         <v>2</v>
@@ -22685,10 +22685,10 @@
         <v>1.75</v>
       </c>
       <c r="AC137">
-        <v>3.49</v>
+        <v>3.55</v>
       </c>
       <c r="AD137">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE137">
         <v>1.1</v>
@@ -22713,7 +22713,7 @@
         <v>1.36</v>
       </c>
       <c r="AK137">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="N138">
-        <v>5.75</v>
+        <v>5.3</v>
       </c>
       <c r="O138">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="P138">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="Q138">
         <v>6</v>
@@ -22836,7 +22836,7 @@
         <v>1.04</v>
       </c>
       <c r="Y138">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z138">
         <v>3.69</v>
@@ -22966,64 +22966,64 @@
         </is>
       </c>
       <c r="N139">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="O139">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P139">
-        <v>6.95</v>
+        <v>6</v>
       </c>
       <c r="Q139">
         <v>2.1</v>
       </c>
       <c r="R139">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="S139">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="T139">
         <v>2.4</v>
       </c>
       <c r="U139">
-        <v>3.46</v>
+        <v>3.1</v>
       </c>
       <c r="V139">
         <v>1.24</v>
       </c>
       <c r="W139">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X139">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Y139">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="Z139">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="AA139">
-        <v>2.41</v>
+        <v>2.49</v>
       </c>
       <c r="AB139">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AC139">
         <v>4.6</v>
       </c>
       <c r="AD139">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AE139">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AF139">
         <v>2.4</v>
       </c>
       <c r="AG139">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>1.03</v>
       </c>
       <c r="AK139">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G140">
@@ -23129,64 +23129,64 @@
         </is>
       </c>
       <c r="N140">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="O140">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="P140">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="Q140">
-        <v>4.13</v>
+        <v>3.8</v>
       </c>
       <c r="R140">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="S140">
+        <v>1.4</v>
+      </c>
+      <c r="T140">
+        <v>2.92</v>
+      </c>
+      <c r="U140">
+        <v>2.77</v>
+      </c>
+      <c r="V140">
+        <v>1.38</v>
+      </c>
+      <c r="W140">
+        <v>1.05</v>
+      </c>
+      <c r="X140">
+        <v>1.05</v>
+      </c>
+      <c r="Y140">
+        <v>1.27</v>
+      </c>
+      <c r="Z140">
+        <v>3.14</v>
+      </c>
+      <c r="AA140">
+        <v>1.9</v>
+      </c>
+      <c r="AB140">
+        <v>1.8</v>
+      </c>
+      <c r="AC140">
+        <v>3.2</v>
+      </c>
+      <c r="AD140">
         <v>1.3</v>
       </c>
-      <c r="T140">
-        <v>3.32</v>
-      </c>
-      <c r="U140">
-        <v>2.52</v>
-      </c>
-      <c r="V140">
-        <v>1.47</v>
-      </c>
-      <c r="W140">
-        <v>1.12</v>
-      </c>
-      <c r="X140">
-        <v>1.04</v>
-      </c>
-      <c r="Y140">
-        <v>1.2</v>
-      </c>
-      <c r="Z140">
-        <v>4.1</v>
-      </c>
-      <c r="AA140">
-        <v>1.68</v>
-      </c>
-      <c r="AB140">
-        <v>2.06</v>
-      </c>
-      <c r="AC140">
-        <v>2.75</v>
-      </c>
-      <c r="AD140">
-        <v>1.4</v>
-      </c>
       <c r="AE140">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF140">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG140">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK140">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="G141">
@@ -23292,64 +23292,64 @@
         </is>
       </c>
       <c r="N141">
-        <v>3.01</v>
+        <v>3.75</v>
       </c>
       <c r="O141">
+        <v>3.6</v>
+      </c>
+      <c r="P141">
+        <v>1.64</v>
+      </c>
+      <c r="Q141">
+        <v>4.65</v>
+      </c>
+      <c r="R141">
+        <v>2.35</v>
+      </c>
+      <c r="S141">
+        <v>1.3</v>
+      </c>
+      <c r="T141">
         <v>3.2</v>
       </c>
-      <c r="P141">
-        <v>2.15</v>
-      </c>
-      <c r="Q141">
-        <v>3.5</v>
-      </c>
-      <c r="R141">
-        <v>2.15</v>
-      </c>
-      <c r="S141">
-        <v>1.38</v>
-      </c>
-      <c r="T141">
-        <v>2.66</v>
-      </c>
       <c r="U141">
-        <v>2.77</v>
+        <v>2.36</v>
       </c>
       <c r="V141">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="W141">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X141">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y141">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="Z141">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA141">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AB141">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AC141">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AD141">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AE141">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF141">
         <v>1.67</v>
       </c>
       <c r="AG141">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AK141">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23458,7 +23458,7 @@
         <v>1.64</v>
       </c>
       <c r="O142">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P142">
         <v>5.01</v>
@@ -23470,7 +23470,7 @@
         <v>2.1</v>
       </c>
       <c r="S142">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T142">
         <v>2.88</v>
@@ -23479,7 +23479,7 @@
         <v>3.05</v>
       </c>
       <c r="V142">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W142">
         <v>1.02</v>
@@ -23488,19 +23488,19 @@
         <v>1.06</v>
       </c>
       <c r="Y142">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z142">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AA142">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB142">
         <v>1.7</v>
       </c>
       <c r="AC142">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="AD142">
         <v>1.22</v>
@@ -23509,7 +23509,7 @@
         <v>1.03</v>
       </c>
       <c r="AF142">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG142">
         <v>1.7</v>
@@ -23790,7 +23790,7 @@
         <v>10.23</v>
       </c>
       <c r="Q144">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="R144">
         <v>2.45</v>
@@ -23799,7 +23799,7 @@
         <v>1.33</v>
       </c>
       <c r="T144">
-        <v>2.59</v>
+        <v>3</v>
       </c>
       <c r="U144">
         <v>2.78</v>
@@ -23823,10 +23823,10 @@
         <v>1.77</v>
       </c>
       <c r="AB144">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AC144">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="AD144">
         <v>1.28</v>
@@ -23835,10 +23835,10 @@
         <v>1.06</v>
       </c>
       <c r="AF144">
-        <v>2.54</v>
+        <v>2.1</v>
       </c>
       <c r="AG144">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23944,13 +23944,13 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="O145">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P145">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Q145">
         <v>2.09</v>
@@ -23962,7 +23962,7 @@
         <v>1.37</v>
       </c>
       <c r="T145">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="U145">
         <v>2.88</v>
@@ -23980,13 +23980,13 @@
         <v>1.27</v>
       </c>
       <c r="Z145">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="AA145">
         <v>1.89</v>
       </c>
       <c r="AB145">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AC145">
         <v>3.4</v>
@@ -23995,13 +23995,13 @@
         <v>1.3</v>
       </c>
       <c r="AE145">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF145">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG145">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24113,7 +24113,7 @@
         <v>3.42</v>
       </c>
       <c r="P146">
-        <v>3.28</v>
+        <v>3.75</v>
       </c>
       <c r="Q146">
         <v>2.49</v>
@@ -24122,10 +24122,10 @@
         <v>2.3</v>
       </c>
       <c r="S146">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T146">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="U146">
         <v>2.65</v>
@@ -24149,22 +24149,22 @@
         <v>1.9</v>
       </c>
       <c r="AB146">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AC146">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="AD146">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE146">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF146">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG146">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24596,13 +24596,13 @@
         </is>
       </c>
       <c r="N149">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="O149">
         <v>3.4</v>
       </c>
       <c r="P149">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="Q149">
         <v>2.5</v>
@@ -24629,7 +24629,7 @@
         <v>1.04</v>
       </c>
       <c r="Y149">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z149">
         <v>3.95</v>
@@ -24638,7 +24638,7 @@
         <v>1.7</v>
       </c>
       <c r="AB149">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AC149">
         <v>2.7</v>
@@ -24647,7 +24647,7 @@
         <v>1.4</v>
       </c>
       <c r="AE149">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF149">
         <v>1.57</v>
@@ -24669,7 +24669,7 @@
         <v>1.25</v>
       </c>
       <c r="AK149">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -24925,13 +24925,13 @@
         <v>2.24</v>
       </c>
       <c r="O151">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="P151">
         <v>3</v>
       </c>
       <c r="Q151">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="R151">
         <v>2</v>
@@ -24955,25 +24955,25 @@
         <v>1.05</v>
       </c>
       <c r="Y151">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z151">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="AA151">
         <v>2.2</v>
       </c>
       <c r="AB151">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC151">
         <v>3.42</v>
       </c>
       <c r="AD151">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AE151">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF151">
         <v>1.67</v>
@@ -24992,7 +24992,7 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK151">
         <v>1.5</v>
@@ -25085,13 +25085,13 @@
         </is>
       </c>
       <c r="N152">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="O152">
         <v>3.35</v>
       </c>
       <c r="P152">
-        <v>2.79</v>
+        <v>2.68</v>
       </c>
       <c r="Q152">
         <v>2.9</v>
@@ -25100,7 +25100,7 @@
         <v>2.16</v>
       </c>
       <c r="S152">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T152">
         <v>3.3</v>
@@ -25109,10 +25109,10 @@
         <v>2.36</v>
       </c>
       <c r="V152">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W152">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X152">
         <v>1</v>
@@ -25121,7 +25121,7 @@
         <v>1.2</v>
       </c>
       <c r="Z152">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AA152">
         <v>1.7</v>
@@ -25133,7 +25133,7 @@
         <v>2.78</v>
       </c>
       <c r="AD152">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE152">
         <v>1.15</v>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK152">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25251,10 +25251,10 @@
         <v>2.05</v>
       </c>
       <c r="O153">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="P153">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -25411,7 +25411,7 @@
         </is>
       </c>
       <c r="N154">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="O154">
         <v>2.75</v>
@@ -25423,49 +25423,49 @@
         <v>3.1</v>
       </c>
       <c r="R154">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="S154">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="T154">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="U154">
         <v>3.98</v>
       </c>
       <c r="V154">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W154">
         <v>1.03</v>
       </c>
       <c r="X154">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Y154">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="Z154">
         <v>2.1</v>
       </c>
       <c r="AA154">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AB154">
         <v>1.32</v>
       </c>
       <c r="AC154">
-        <v>6.45</v>
+        <v>6.5</v>
       </c>
       <c r="AD154">
         <v>1.1</v>
       </c>
       <c r="AE154">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF154">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AG154">
         <v>1.57</v>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK154">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25577,16 +25577,16 @@
         <v>1.36</v>
       </c>
       <c r="O155">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="P155">
-        <v>6.1</v>
+        <v>6.65</v>
       </c>
       <c r="Q155">
         <v>1.85</v>
       </c>
       <c r="R155">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="S155">
         <v>1.25</v>
@@ -25607,7 +25607,7 @@
         <v>1.03</v>
       </c>
       <c r="Y155">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z155">
         <v>4.5</v>
@@ -25616,7 +25616,7 @@
         <v>1.65</v>
       </c>
       <c r="AB155">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AC155">
         <v>2.6</v>
@@ -25625,13 +25625,13 @@
         <v>1.48</v>
       </c>
       <c r="AE155">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF155">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AG155">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25737,13 +25737,13 @@
         </is>
       </c>
       <c r="N156">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="O156">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P156">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q156">
         <v>3.1</v>
@@ -25761,7 +25761,7 @@
         <v>2.85</v>
       </c>
       <c r="V156">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W156">
         <v>1.07</v>
@@ -25794,7 +25794,7 @@
         <v>1.73</v>
       </c>
       <c r="AG156">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>1.3</v>
       </c>
       <c r="AK156">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25900,25 +25900,25 @@
         </is>
       </c>
       <c r="N157">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="O157">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="P157">
-        <v>3.9</v>
+        <v>3.18</v>
       </c>
       <c r="Q157">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R157">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="S157">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="T157">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="U157">
         <v>3.6</v>
@@ -25927,10 +25927,10 @@
         <v>1.25</v>
       </c>
       <c r="W157">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X157">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y157">
         <v>1.52</v>
@@ -25939,10 +25939,10 @@
         <v>2.5</v>
       </c>
       <c r="AA157">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AB157">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AC157">
         <v>5.16</v>
@@ -25954,7 +25954,7 @@
         <v>1.02</v>
       </c>
       <c r="AF157">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AG157">
         <v>1.67</v>
@@ -25970,7 +25970,7 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AK157">
         <v>1.73</v>
@@ -26063,55 +26063,55 @@
         </is>
       </c>
       <c r="N158">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="O158">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P158">
-        <v>5.95</v>
+        <v>4.5</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
       </c>
       <c r="R158">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="S158">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="T158">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="U158">
-        <v>3.5</v>
+        <v>3.32</v>
       </c>
       <c r="V158">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="W158">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X158">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y158">
+        <v>1.45</v>
+      </c>
+      <c r="Z158">
+        <v>2.63</v>
+      </c>
+      <c r="AA158">
+        <v>2.3</v>
+      </c>
+      <c r="AB158">
         <v>1.53</v>
       </c>
-      <c r="Z158">
-        <v>2.45</v>
-      </c>
-      <c r="AA158">
-        <v>2.5</v>
-      </c>
-      <c r="AB158">
-        <v>1.44</v>
-      </c>
       <c r="AC158">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="AD158">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AE158">
         <v>1.01</v>
@@ -26120,7 +26120,7 @@
         <v>2.2</v>
       </c>
       <c r="AG158">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>1.1</v>
       </c>
       <c r="AK158">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26226,13 +26226,13 @@
         </is>
       </c>
       <c r="N159">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O159">
         <v>3.4</v>
       </c>
       <c r="P159">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="Q159">
         <v>2.3</v>
@@ -26253,7 +26253,7 @@
         <v>1.37</v>
       </c>
       <c r="W159">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X159">
         <v>1.03</v>
@@ -26389,13 +26389,13 @@
         </is>
       </c>
       <c r="N160">
-        <v>5</v>
+        <v>4.98</v>
       </c>
       <c r="O160">
         <v>3.65</v>
       </c>
       <c r="P160">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="Q160">
         <v>4.8</v>
@@ -26440,7 +26440,7 @@
         <v>1.27</v>
       </c>
       <c r="AE160">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF160">
         <v>1.85</v>
@@ -26555,7 +26555,7 @@
         <v>1.11</v>
       </c>
       <c r="O161">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="P161">
         <v>17</v>
@@ -26570,7 +26570,7 @@
         <v>1.19</v>
       </c>
       <c r="T161">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="U161">
         <v>2.08</v>
@@ -26585,10 +26585,10 @@
         <v>1.01</v>
       </c>
       <c r="Y161">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z161">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AA161">
         <v>1.38</v>
@@ -26606,10 +26606,10 @@
         <v>1.29</v>
       </c>
       <c r="AF161">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AG161">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26715,16 +26715,16 @@
         </is>
       </c>
       <c r="N162">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="O162">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P162">
-        <v>6.5</v>
+        <v>6.83</v>
       </c>
       <c r="Q162">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="R162">
         <v>2.07</v>
@@ -26736,13 +26736,13 @@
         <v>2.28</v>
       </c>
       <c r="U162">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="V162">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W162">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X162">
         <v>1.06</v>
@@ -26757,22 +26757,22 @@
         <v>2.41</v>
       </c>
       <c r="AB162">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AC162">
-        <v>4.6</v>
+        <v>5.09</v>
       </c>
       <c r="AD162">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AE162">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF162">
         <v>2.45</v>
       </c>
       <c r="AG162">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26785,7 +26785,7 @@
         </is>
       </c>
       <c r="AJ162">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="AK162">
         <v>2.19</v>
@@ -27204,16 +27204,16 @@
         </is>
       </c>
       <c r="N165">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="O165">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="P165">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="Q165">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="R165">
         <v>1.85</v>
@@ -27222,7 +27222,7 @@
         <v>1.57</v>
       </c>
       <c r="T165">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="U165">
         <v>3.9</v>
@@ -27234,7 +27234,7 @@
         <v>1.03</v>
       </c>
       <c r="X165">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Y165">
         <v>1.6</v>
@@ -27249,13 +27249,13 @@
         <v>1.34</v>
       </c>
       <c r="AC165">
-        <v>6.03</v>
+        <v>6.14</v>
       </c>
       <c r="AD165">
         <v>1.11</v>
       </c>
       <c r="AE165">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF165">
         <v>2.3</v>
@@ -27370,7 +27370,7 @@
         <v>1.79</v>
       </c>
       <c r="O166">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P166">
         <v>3.17</v>
@@ -27379,7 +27379,7 @@
         <v>2.3</v>
       </c>
       <c r="R166">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="S166">
         <v>1.3</v>
@@ -27388,43 +27388,43 @@
         <v>3.2</v>
       </c>
       <c r="U166">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V166">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W166">
         <v>1.11</v>
       </c>
       <c r="X166">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y166">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z166">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AA166">
         <v>1.75</v>
       </c>
       <c r="AB166">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="AC166">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="AD166">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AE166">
         <v>1.12</v>
       </c>
       <c r="AF166">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AG166">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="AH166" t="inlineStr">
         <is>
@@ -27437,10 +27437,10 @@
         </is>
       </c>
       <c r="AJ166">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK166">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27530,19 +27530,19 @@
         </is>
       </c>
       <c r="N167">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="O167">
         <v>2.8</v>
       </c>
       <c r="P167">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="Q167">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="R167">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="S167">
         <v>1.67</v>
@@ -27569,7 +27569,7 @@
         <v>2.12</v>
       </c>
       <c r="AA167">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="AB167">
         <v>1.36</v>
@@ -27584,7 +27584,7 @@
         <v>1.03</v>
       </c>
       <c r="AF167">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AG167">
         <v>1.49</v>
@@ -27600,7 +27600,7 @@
         </is>
       </c>
       <c r="AJ167">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AK167">
         <v>1.73</v>
@@ -27856,7 +27856,7 @@
         </is>
       </c>
       <c r="N169">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="O169">
         <v>3</v>
@@ -28182,13 +28182,13 @@
         </is>
       </c>
       <c r="N171">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O171">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="P171">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="Q171">
         <v>2.62</v>
@@ -28203,22 +28203,22 @@
         <v>2.7</v>
       </c>
       <c r="U171">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="V171">
         <v>1.33</v>
       </c>
       <c r="W171">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X171">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y171">
         <v>1.31</v>
       </c>
       <c r="Z171">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="AA171">
         <v>2.05</v>
@@ -28255,7 +28255,7 @@
         <v>1.34</v>
       </c>
       <c r="AK171">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AL171">
         <v>0</v>
@@ -28348,7 +28348,7 @@
         <v>2.15</v>
       </c>
       <c r="O172">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="P172">
         <v>3.5</v>
@@ -28360,10 +28360,10 @@
         <v>1.95</v>
       </c>
       <c r="S172">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="T172">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="U172">
         <v>2.95</v>
@@ -28372,28 +28372,28 @@
         <v>1.3</v>
       </c>
       <c r="W172">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X172">
         <v>1.06</v>
       </c>
       <c r="Y172">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z172">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AA172">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AB172">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC172">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AD172">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE172">
         <v>1.06</v>
@@ -28834,34 +28834,34 @@
         </is>
       </c>
       <c r="N175">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="O175">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P175">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Q175">
         <v>4.4</v>
       </c>
       <c r="R175">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="S175">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="T175">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="U175">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="V175">
         <v>1.36</v>
       </c>
       <c r="W175">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X175">
         <v>1.06</v>
@@ -28879,13 +28879,13 @@
         <v>1.78</v>
       </c>
       <c r="AC175">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AD175">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AE175">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF175">
         <v>1.83</v>
@@ -29000,7 +29000,7 @@
         <v>1.17</v>
       </c>
       <c r="O176">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="P176">
         <v>11</v>
@@ -29012,16 +29012,16 @@
         <v>2.63</v>
       </c>
       <c r="S176">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T176">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U176">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="V176">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W176">
         <v>1.11</v>
@@ -29033,10 +29033,10 @@
         <v>1.15</v>
       </c>
       <c r="Z176">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AA176">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AB176">
         <v>2.3</v>
@@ -29054,7 +29054,7 @@
         <v>2.1</v>
       </c>
       <c r="AG176">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29486,13 +29486,13 @@
         </is>
       </c>
       <c r="N179">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="O179">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="P179">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="Q179">
         <v>2.4</v>
@@ -29501,13 +29501,13 @@
         <v>2.15</v>
       </c>
       <c r="S179">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T179">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="U179">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="V179">
         <v>1.37</v>
@@ -29522,25 +29522,25 @@
         <v>1.25</v>
       </c>
       <c r="Z179">
-        <v>3.81</v>
+        <v>3.5</v>
       </c>
       <c r="AA179">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AB179">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC179">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD179">
         <v>1.3</v>
       </c>
       <c r="AE179">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF179">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AG179">
         <v>1.95</v>
@@ -29559,7 +29559,7 @@
         <v>1.2</v>
       </c>
       <c r="AK179">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AL179">
         <v>0</v>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="O46">
         <v>3.7</v>
       </c>
       <c r="P46">
-        <v>5</v>
+        <v>5.11</v>
       </c>
       <c r="Q46">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="R46">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="S46">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T46">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="U46">
-        <v>2.77</v>
+        <v>3.01</v>
       </c>
       <c r="V46">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W46">
         <v>1.05</v>
       </c>
       <c r="X46">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y46">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z46">
-        <v>3.18</v>
+        <v>3.55</v>
       </c>
       <c r="AA46">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB46">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AC46">
-        <v>3.41</v>
+        <v>3.3</v>
       </c>
       <c r="AD46">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AE46">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF46">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG46">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK46">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -9437,16 +9437,16 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="O56">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="P56">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="Q56">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R56">
         <v>1.83</v>
@@ -9458,10 +9458,10 @@
         <v>2.4</v>
       </c>
       <c r="U56">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="V56">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W56">
         <v>1.04</v>
@@ -9473,28 +9473,28 @@
         <v>1.53</v>
       </c>
       <c r="Z56">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="AA56">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AB56">
         <v>1.44</v>
       </c>
       <c r="AC56">
-        <v>5.62</v>
+        <v>5.55</v>
       </c>
       <c r="AD56">
         <v>1.14</v>
       </c>
       <c r="AE56">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF56">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="AG56">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.63</v>
+        <v>2.15</v>
       </c>
       <c r="O71">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="P71">
-        <v>4.85</v>
+        <v>3.17</v>
       </c>
       <c r="Q71">
-        <v>2.1</v>
+        <v>2.86</v>
       </c>
       <c r="R71">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="S71">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T71">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="U71">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="V71">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="W71">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X71">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y71">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z71">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="AA71">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB71">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AC71">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AD71">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE71">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF71">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AG71">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.09</v>
+        <v>1.32</v>
       </c>
       <c r="AK71">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.15</v>
+        <v>1.63</v>
       </c>
       <c r="O72">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="P72">
-        <v>3.17</v>
+        <v>4.85</v>
       </c>
       <c r="Q72">
-        <v>2.86</v>
+        <v>2.1</v>
       </c>
       <c r="R72">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="S72">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="T72">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="U72">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="V72">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W72">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X72">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y72">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z72">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="AA72">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB72">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AC72">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AD72">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE72">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF72">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AG72">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.32</v>
+        <v>1.09</v>
       </c>
       <c r="AK72">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="O75">
-        <v>3.25</v>
+        <v>3.61</v>
       </c>
       <c r="P75">
-        <v>2.27</v>
+        <v>1.8</v>
       </c>
       <c r="Q75">
-        <v>3.35</v>
+        <v>4.26</v>
       </c>
       <c r="R75">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="S75">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="T75">
-        <v>2.62</v>
+        <v>3.3</v>
       </c>
       <c r="U75">
-        <v>3</v>
+        <v>2.34</v>
       </c>
       <c r="V75">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="W75">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X75">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y75">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z75">
-        <v>3.25</v>
+        <v>4.45</v>
       </c>
       <c r="AA75">
-        <v>2.06</v>
+        <v>1.62</v>
       </c>
       <c r="AB75">
-        <v>1.78</v>
+        <v>2.32</v>
       </c>
       <c r="AC75">
-        <v>3.24</v>
+        <v>2.44</v>
       </c>
       <c r="AD75">
-        <v>1.26</v>
+        <v>1.49</v>
       </c>
       <c r="AE75">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF75">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AG75">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AK75">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,80 +12697,80 @@
         </is>
       </c>
       <c r="N76">
-        <v>3.75</v>
+        <v>2.8</v>
       </c>
       <c r="O76">
-        <v>3.61</v>
+        <v>3.25</v>
       </c>
       <c r="P76">
-        <v>1.8</v>
+        <v>2.27</v>
       </c>
       <c r="Q76">
-        <v>4.26</v>
+        <v>3.35</v>
       </c>
       <c r="R76">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="S76">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="T76">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="U76">
-        <v>2.34</v>
+        <v>3</v>
       </c>
       <c r="V76">
+        <v>1.39</v>
+      </c>
+      <c r="W76">
+        <v>1.05</v>
+      </c>
+      <c r="X76">
+        <v>1.02</v>
+      </c>
+      <c r="Y76">
+        <v>1.3</v>
+      </c>
+      <c r="Z76">
+        <v>3.25</v>
+      </c>
+      <c r="AA76">
+        <v>2.06</v>
+      </c>
+      <c r="AB76">
+        <v>1.78</v>
+      </c>
+      <c r="AC76">
+        <v>3.24</v>
+      </c>
+      <c r="AD76">
+        <v>1.26</v>
+      </c>
+      <c r="AE76">
+        <v>1.11</v>
+      </c>
+      <c r="AF76">
+        <v>1.73</v>
+      </c>
+      <c r="AG76">
+        <v>1.95</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ76">
         <v>1.53</v>
       </c>
-      <c r="W76">
-        <v>1.14</v>
-      </c>
-      <c r="X76">
-        <v>1.03</v>
-      </c>
-      <c r="Y76">
-        <v>1.2</v>
-      </c>
-      <c r="Z76">
-        <v>4.45</v>
-      </c>
-      <c r="AA76">
-        <v>1.62</v>
-      </c>
-      <c r="AB76">
-        <v>2.32</v>
-      </c>
-      <c r="AC76">
-        <v>2.44</v>
-      </c>
-      <c r="AD76">
-        <v>1.49</v>
-      </c>
-      <c r="AE76">
-        <v>1.14</v>
-      </c>
-      <c r="AF76">
-        <v>1.53</v>
-      </c>
-      <c r="AG76">
-        <v>2.3</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ76">
-        <v>1.25</v>
-      </c>
       <c r="AK76">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -17750,37 +17750,37 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O107">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P107">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="Q107">
         <v>3</v>
       </c>
       <c r="R107">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S107">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T107">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="U107">
         <v>2.95</v>
       </c>
       <c r="V107">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W107">
         <v>1.05</v>
       </c>
       <c r="X107">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y107">
         <v>1.36</v>
@@ -17789,10 +17789,10 @@
         <v>2.9</v>
       </c>
       <c r="AA107">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AB107">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC107">
         <v>3.9</v>
@@ -17801,13 +17801,13 @@
         <v>1.27</v>
       </c>
       <c r="AE107">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF107">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AG107">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>1.36</v>
       </c>
       <c r="AK107">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="O109">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P109">
-        <v>3.97</v>
+        <v>3.71</v>
       </c>
       <c r="Q109">
         <v>2.52</v>
@@ -18091,10 +18091,10 @@
         <v>2.06</v>
       </c>
       <c r="S109">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T109">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="U109">
         <v>2.8</v>
@@ -18109,31 +18109,31 @@
         <v>1.06</v>
       </c>
       <c r="Y109">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z109">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="AA109">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AB109">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AC109">
-        <v>3.71</v>
+        <v>3.74</v>
       </c>
       <c r="AD109">
         <v>1.28</v>
       </c>
       <c r="AE109">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF109">
         <v>1.84</v>
       </c>
       <c r="AG109">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>1.22</v>
       </c>
       <c r="AK109">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18728,16 +18728,16 @@
         </is>
       </c>
       <c r="N113">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O113">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="P113">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="Q113">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="R113">
         <v>1.83</v>
@@ -18761,19 +18761,19 @@
         <v>1.13</v>
       </c>
       <c r="Y113">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Z113">
         <v>2.2</v>
       </c>
       <c r="AA113">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AB113">
         <v>1.38</v>
       </c>
       <c r="AC113">
-        <v>6.64</v>
+        <v>6.43</v>
       </c>
       <c r="AD113">
         <v>1.11</v>
@@ -18801,7 +18801,7 @@
         <v>1.4</v>
       </c>
       <c r="AK113">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -19706,52 +19706,52 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
       <c r="O119">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="P119">
         <v>2.97</v>
       </c>
       <c r="Q119">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="R119">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="S119">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="T119">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="U119">
         <v>4.33</v>
       </c>
       <c r="V119">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W119">
         <v>1.02</v>
       </c>
       <c r="X119">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Y119">
         <v>1.79</v>
       </c>
       <c r="Z119">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AA119">
         <v>3.28</v>
       </c>
       <c r="AB119">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AC119">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="AD119">
         <v>1.08</v>
@@ -20521,7 +20521,7 @@
         </is>
       </c>
       <c r="N124">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="O124">
         <v>3.55</v>
@@ -20548,10 +20548,10 @@
         <v>1.22</v>
       </c>
       <c r="W124">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X124">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="Y124">
         <v>1.5</v>
@@ -20684,13 +20684,13 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="O125">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="P125">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="Q125">
         <v>2.8</v>
@@ -20699,7 +20699,7 @@
         <v>1.71</v>
       </c>
       <c r="S125">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="T125">
         <v>1.99</v>
@@ -20711,13 +20711,13 @@
         <v>1.15</v>
       </c>
       <c r="W125">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X125">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Y125">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="Z125">
         <v>2</v>
@@ -20741,7 +20741,7 @@
         <v>2.35</v>
       </c>
       <c r="AG125">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -22966,55 +22966,55 @@
         </is>
       </c>
       <c r="N139">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="O139">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="P139">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="Q139">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="R139">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="S139">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="T139">
         <v>2.4</v>
       </c>
       <c r="U139">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="V139">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="W139">
         <v>1</v>
       </c>
       <c r="X139">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="Y139">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Z139">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AA139">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="AB139">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AC139">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AD139">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE139">
         <v>1.05</v>
@@ -23023,7 +23023,7 @@
         <v>2.4</v>
       </c>
       <c r="AG139">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AK139">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23618,13 +23618,13 @@
         </is>
       </c>
       <c r="N143">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="O143">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="P143">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -23944,25 +23944,25 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="O145">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P145">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="Q145">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="R145">
         <v>2.2</v>
       </c>
       <c r="S145">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T145">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="U145">
         <v>2.88</v>
@@ -23977,19 +23977,19 @@
         <v>1.03</v>
       </c>
       <c r="Y145">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z145">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AA145">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AB145">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AC145">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AD145">
         <v>1.3</v>
@@ -23998,10 +23998,10 @@
         <v>1.09</v>
       </c>
       <c r="AF145">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG145">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24110,7 +24110,7 @@
         <v>1.9</v>
       </c>
       <c r="O146">
-        <v>3.42</v>
+        <v>3.55</v>
       </c>
       <c r="P146">
         <v>3.75</v>
@@ -24119,19 +24119,19 @@
         <v>2.49</v>
       </c>
       <c r="R146">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="S146">
         <v>1.36</v>
       </c>
       <c r="T146">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="U146">
         <v>2.65</v>
       </c>
       <c r="V146">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W146">
         <v>1.06</v>
@@ -24146,7 +24146,7 @@
         <v>3.38</v>
       </c>
       <c r="AA146">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AB146">
         <v>1.94</v>
@@ -24155,10 +24155,10 @@
         <v>2.94</v>
       </c>
       <c r="AD146">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AE146">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF146">
         <v>1.7</v>
@@ -24270,13 +24270,13 @@
         </is>
       </c>
       <c r="N147">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="O147">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P147">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="Q147">
         <v>2.14</v>
@@ -24306,13 +24306,13 @@
         <v>1.25</v>
       </c>
       <c r="Z147">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AA147">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AB147">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC147">
         <v>3</v>
@@ -24321,7 +24321,7 @@
         <v>1.32</v>
       </c>
       <c r="AE147">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF147">
         <v>1.85</v>
@@ -24340,7 +24340,7 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK147">
         <v>2.25</v>
@@ -24433,19 +24433,19 @@
         </is>
       </c>
       <c r="N148">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="O148">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P148">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q148">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="R148">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="S148">
         <v>1.5</v>
@@ -24463,13 +24463,13 @@
         <v>1.02</v>
       </c>
       <c r="X148">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Y148">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="Z148">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AA148">
         <v>2.4</v>
@@ -24481,10 +24481,10 @@
         <v>5.25</v>
       </c>
       <c r="AD148">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AE148">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF148">
         <v>2.16</v>
@@ -24596,7 +24596,7 @@
         </is>
       </c>
       <c r="N149">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O149">
         <v>3.4</v>
@@ -24617,7 +24617,7 @@
         <v>3.3</v>
       </c>
       <c r="U149">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="V149">
         <v>1.5</v>
@@ -24626,7 +24626,7 @@
         <v>1.1</v>
       </c>
       <c r="X149">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y149">
         <v>1.22</v>
@@ -24638,13 +24638,13 @@
         <v>1.7</v>
       </c>
       <c r="AB149">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AC149">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AD149">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE149">
         <v>1.12</v>
@@ -24669,7 +24669,7 @@
         <v>1.25</v>
       </c>
       <c r="AK149">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -24759,64 +24759,64 @@
         </is>
       </c>
       <c r="N150">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O150">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P150">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q150">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R150">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S150">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T150">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U150">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V150">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W150">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X150">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y150">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z150">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA150">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB150">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC150">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD150">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE150">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF150">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG150">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH150" t="inlineStr">
         <is>
@@ -24829,10 +24829,10 @@
         </is>
       </c>
       <c r="AJ150">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK150">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL150">
         <v>0</v>
@@ -25251,10 +25251,10 @@
         <v>2.05</v>
       </c>
       <c r="O153">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="P153">
-        <v>3.85</v>
+        <v>3.67</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -25411,7 +25411,7 @@
         </is>
       </c>
       <c r="N154">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="O154">
         <v>2.75</v>
@@ -25423,13 +25423,13 @@
         <v>3.1</v>
       </c>
       <c r="R154">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="S154">
         <v>1.62</v>
       </c>
       <c r="T154">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="U154">
         <v>3.98</v>
@@ -25441,13 +25441,13 @@
         <v>1.03</v>
       </c>
       <c r="X154">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Y154">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="Z154">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AA154">
         <v>3.1</v>
@@ -25465,7 +25465,7 @@
         <v>1.02</v>
       </c>
       <c r="AF154">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="AG154">
         <v>1.57</v>
@@ -25484,7 +25484,7 @@
         <v>1.36</v>
       </c>
       <c r="AK154">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25737,13 +25737,13 @@
         </is>
       </c>
       <c r="N156">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="O156">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="P156">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="Q156">
         <v>3.1</v>
@@ -25758,7 +25758,7 @@
         <v>2.77</v>
       </c>
       <c r="U156">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="V156">
         <v>1.4</v>
@@ -25767,7 +25767,7 @@
         <v>1.07</v>
       </c>
       <c r="X156">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y156">
         <v>1.3</v>
@@ -25776,7 +25776,7 @@
         <v>3.25</v>
       </c>
       <c r="AA156">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AB156">
         <v>1.76</v>
@@ -25794,7 +25794,7 @@
         <v>1.73</v>
       </c>
       <c r="AG156">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>1.3</v>
       </c>
       <c r="AK156">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25900,7 +25900,7 @@
         </is>
       </c>
       <c r="N157">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="O157">
         <v>2.78</v>
@@ -25909,16 +25909,16 @@
         <v>3.18</v>
       </c>
       <c r="Q157">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="R157">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="S157">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="T157">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="U157">
         <v>3.6</v>
@@ -25933,25 +25933,25 @@
         <v>1.09</v>
       </c>
       <c r="Y157">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="Z157">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AA157">
-        <v>2.7</v>
+        <v>2.41</v>
       </c>
       <c r="AB157">
         <v>1.45</v>
       </c>
       <c r="AC157">
-        <v>5.16</v>
+        <v>5.23</v>
       </c>
       <c r="AD157">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AE157">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF157">
         <v>2.1</v>
@@ -26066,10 +26066,10 @@
         <v>1.6</v>
       </c>
       <c r="O158">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P158">
-        <v>4.5</v>
+        <v>5.89</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -26078,10 +26078,10 @@
         <v>1.98</v>
       </c>
       <c r="S158">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="T158">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="U158">
         <v>3.32</v>
@@ -26093,7 +26093,7 @@
         <v>1.01</v>
       </c>
       <c r="X158">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y158">
         <v>1.45</v>
@@ -26108,7 +26108,7 @@
         <v>1.53</v>
       </c>
       <c r="AC158">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AD158">
         <v>1.15</v>
@@ -26120,7 +26120,7 @@
         <v>2.2</v>
       </c>
       <c r="AG158">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AK158">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26718,31 +26718,31 @@
         <v>1.53</v>
       </c>
       <c r="O162">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P162">
         <v>6.83</v>
       </c>
       <c r="Q162">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R162">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="S162">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="T162">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="U162">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="V162">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="W162">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X162">
         <v>1.06</v>
@@ -26751,22 +26751,22 @@
         <v>1.48</v>
       </c>
       <c r="Z162">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="AA162">
-        <v>2.41</v>
+        <v>2.58</v>
       </c>
       <c r="AB162">
         <v>1.44</v>
       </c>
       <c r="AC162">
-        <v>5.09</v>
+        <v>5.4</v>
       </c>
       <c r="AD162">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AE162">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF162">
         <v>2.45</v>
@@ -26785,7 +26785,7 @@
         </is>
       </c>
       <c r="AJ162">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="AK162">
         <v>2.19</v>
@@ -27204,10 +27204,10 @@
         </is>
       </c>
       <c r="N165">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="O165">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="P165">
         <v>4.5</v>
@@ -27219,7 +27219,7 @@
         <v>1.85</v>
       </c>
       <c r="S165">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="T165">
         <v>2.11</v>
@@ -27234,7 +27234,7 @@
         <v>1.03</v>
       </c>
       <c r="X165">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Y165">
         <v>1.6</v>
@@ -27246,13 +27246,13 @@
         <v>3.1</v>
       </c>
       <c r="AB165">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AC165">
-        <v>6.14</v>
+        <v>6.23</v>
       </c>
       <c r="AD165">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AE165">
         <v>1.02</v>
@@ -27367,10 +27367,10 @@
         </is>
       </c>
       <c r="N166">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="O166">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P166">
         <v>3.17</v>
@@ -27421,10 +27421,10 @@
         <v>1.12</v>
       </c>
       <c r="AF166">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AG166">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="AH166" t="inlineStr">
         <is>
@@ -27440,7 +27440,7 @@
         <v>1.22</v>
       </c>
       <c r="AK166">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27530,37 +27530,37 @@
         </is>
       </c>
       <c r="N167">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="O167">
+        <v>2.75</v>
+      </c>
+      <c r="P167">
+        <v>4.2</v>
+      </c>
+      <c r="Q167">
         <v>2.8</v>
       </c>
-      <c r="P167">
-        <v>3.8</v>
-      </c>
-      <c r="Q167">
-        <v>2.75</v>
-      </c>
       <c r="R167">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="S167">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="T167">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="U167">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="V167">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="W167">
         <v>1.03</v>
       </c>
       <c r="X167">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Y167">
         <v>1.65</v>
@@ -27569,16 +27569,16 @@
         <v>2.12</v>
       </c>
       <c r="AA167">
-        <v>3.11</v>
+        <v>2.88</v>
       </c>
       <c r="AB167">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AC167">
-        <v>5.2</v>
+        <v>6.62</v>
       </c>
       <c r="AD167">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AE167">
         <v>1.03</v>
@@ -27699,19 +27699,19 @@
         <v>2.95</v>
       </c>
       <c r="P168">
-        <v>2.8</v>
+        <v>3.03</v>
       </c>
       <c r="Q168">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="R168">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="S168">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="T168">
-        <v>2.29</v>
+        <v>2.47</v>
       </c>
       <c r="U168">
         <v>3.38</v>
@@ -27726,19 +27726,19 @@
         <v>1.06</v>
       </c>
       <c r="Y168">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="Z168">
-        <v>2.63</v>
+        <v>2.49</v>
       </c>
       <c r="AA168">
-        <v>2.55</v>
+        <v>2.04</v>
       </c>
       <c r="AB168">
         <v>1.53</v>
       </c>
       <c r="AC168">
-        <v>4.82</v>
+        <v>3.4</v>
       </c>
       <c r="AD168">
         <v>1.14</v>
@@ -27747,10 +27747,10 @@
         <v>1.05</v>
       </c>
       <c r="AF168">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG168">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
@@ -27763,10 +27763,10 @@
         </is>
       </c>
       <c r="AJ168">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AK168">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -27856,10 +27856,10 @@
         </is>
       </c>
       <c r="N169">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="O169">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="P169">
         <v>3.32</v>
@@ -28019,64 +28019,64 @@
         </is>
       </c>
       <c r="N170">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O170">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P170">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q170">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R170">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S170">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T170">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U170">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V170">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W170">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X170">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y170">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z170">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA170">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB170">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC170">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD170">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE170">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF170">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG170">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH170" t="inlineStr">
         <is>
@@ -28089,10 +28089,10 @@
         </is>
       </c>
       <c r="AJ170">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK170">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -28188,7 +28188,7 @@
         <v>3.4</v>
       </c>
       <c r="P171">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="Q171">
         <v>2.62</v>
@@ -28197,7 +28197,7 @@
         <v>2.1</v>
       </c>
       <c r="S171">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T171">
         <v>2.7</v>
@@ -28206,10 +28206,10 @@
         <v>3</v>
       </c>
       <c r="V171">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W171">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X171">
         <v>1.04</v>
@@ -28218,16 +28218,16 @@
         <v>1.31</v>
       </c>
       <c r="Z171">
-        <v>2.94</v>
+        <v>3.26</v>
       </c>
       <c r="AA171">
         <v>2.05</v>
       </c>
       <c r="AB171">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC171">
-        <v>3.8</v>
+        <v>3.54</v>
       </c>
       <c r="AD171">
         <v>1.25</v>
@@ -28345,28 +28345,28 @@
         </is>
       </c>
       <c r="N172">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="O172">
         <v>3.2</v>
       </c>
       <c r="P172">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="Q172">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="R172">
         <v>1.95</v>
       </c>
       <c r="S172">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="T172">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="U172">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="V172">
         <v>1.3</v>
@@ -28378,28 +28378,28 @@
         <v>1.06</v>
       </c>
       <c r="Y172">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z172">
         <v>2.8</v>
       </c>
       <c r="AA172">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB172">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC172">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AD172">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE172">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF172">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG172">
         <v>1.85</v>
@@ -28418,7 +28418,7 @@
         <v>1.35</v>
       </c>
       <c r="AK172">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28508,28 +28508,28 @@
         </is>
       </c>
       <c r="N173">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="O173">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P173">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q173">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="R173">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="S173">
         <v>1.44</v>
       </c>
       <c r="T173">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="U173">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="V173">
         <v>1.25</v>
@@ -28541,16 +28541,16 @@
         <v>1.05</v>
       </c>
       <c r="Y173">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Z173">
         <v>2.49</v>
       </c>
       <c r="AA173">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="AB173">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AC173">
         <v>5</v>
@@ -28559,7 +28559,7 @@
         <v>1.12</v>
       </c>
       <c r="AE173">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF173">
         <v>2.01</v>
@@ -28578,7 +28578,7 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AK173">
         <v>1.44</v>
@@ -28671,28 +28671,28 @@
         </is>
       </c>
       <c r="N174">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="O174">
-        <v>3.05</v>
+        <v>2.35</v>
       </c>
       <c r="P174">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q174">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="R174">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="S174">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="T174">
-        <v>2.62</v>
+        <v>2.24</v>
       </c>
       <c r="U174">
-        <v>3.4</v>
+        <v>3.04</v>
       </c>
       <c r="V174">
         <v>1.29</v>
@@ -28710,10 +28710,10 @@
         <v>2.88</v>
       </c>
       <c r="AA174">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AB174">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC174">
         <v>4.2</v>
@@ -28725,10 +28725,10 @@
         <v>1.04</v>
       </c>
       <c r="AF174">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AG174">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AH174" t="inlineStr">
         <is>
@@ -28741,7 +28741,7 @@
         </is>
       </c>
       <c r="AJ174">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK174">
         <v>1.5</v>
@@ -28834,10 +28834,10 @@
         </is>
       </c>
       <c r="N175">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="O175">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P175">
         <v>1.8</v>
@@ -28846,37 +28846,37 @@
         <v>4.4</v>
       </c>
       <c r="R175">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="S175">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="T175">
         <v>2.85</v>
       </c>
       <c r="U175">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="V175">
         <v>1.36</v>
       </c>
       <c r="W175">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X175">
         <v>1.06</v>
       </c>
       <c r="Y175">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z175">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA175">
         <v>1.95</v>
       </c>
       <c r="AB175">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AC175">
         <v>3.4</v>
@@ -28888,10 +28888,10 @@
         <v>1.1</v>
       </c>
       <c r="AF175">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG175">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AK175">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -29000,10 +29000,10 @@
         <v>1.17</v>
       </c>
       <c r="O176">
-        <v>5.7</v>
+        <v>6.35</v>
       </c>
       <c r="P176">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q176">
         <v>1.61</v>
@@ -29012,19 +29012,19 @@
         <v>2.63</v>
       </c>
       <c r="S176">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T176">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U176">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="V176">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W176">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X176">
         <v>1.01</v>
@@ -29033,7 +29033,7 @@
         <v>1.15</v>
       </c>
       <c r="Z176">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AA176">
         <v>1.62</v>
@@ -29042,10 +29042,10 @@
         <v>2.3</v>
       </c>
       <c r="AC176">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AD176">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AE176">
         <v>1.16</v>
@@ -29169,10 +29169,10 @@
         <v>1.76</v>
       </c>
       <c r="Q177">
-        <v>4.48</v>
+        <v>4.2</v>
       </c>
       <c r="R177">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="S177">
         <v>1.27</v>
@@ -29181,13 +29181,13 @@
         <v>3.2</v>
       </c>
       <c r="U177">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="V177">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W177">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X177">
         <v>1.03</v>
@@ -29202,7 +29202,7 @@
         <v>1.62</v>
       </c>
       <c r="AB177">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AC177">
         <v>2.5</v>
@@ -29211,13 +29211,13 @@
         <v>1.4</v>
       </c>
       <c r="AE177">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF177">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG177">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29323,64 +29323,64 @@
         </is>
       </c>
       <c r="N178">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O178">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P178">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q178">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R178">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S178">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T178">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U178">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V178">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W178">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X178">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y178">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z178">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA178">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB178">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC178">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD178">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE178">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF178">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG178">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
@@ -29393,10 +29393,10 @@
         </is>
       </c>
       <c r="AJ178">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK178">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29489,58 +29489,58 @@
         <v>1.84</v>
       </c>
       <c r="O179">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P179">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q179">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="R179">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S179">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T179">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="U179">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="V179">
         <v>1.37</v>
       </c>
       <c r="W179">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X179">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y179">
         <v>1.25</v>
       </c>
       <c r="Z179">
-        <v>3.5</v>
+        <v>3.81</v>
       </c>
       <c r="AA179">
+        <v>1.82</v>
+      </c>
+      <c r="AB179">
         <v>1.85</v>
       </c>
-      <c r="AB179">
-        <v>1.9</v>
-      </c>
       <c r="AC179">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AD179">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE179">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF179">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AG179">
         <v>1.95</v>
@@ -29559,7 +29559,7 @@
         <v>1.2</v>
       </c>
       <c r="AK179">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29649,16 +29649,16 @@
         </is>
       </c>
       <c r="N180">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="O180">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="P180">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="Q180">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R180">
         <v>1.87</v>
@@ -29670,16 +29670,16 @@
         <v>2.33</v>
       </c>
       <c r="U180">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="V180">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="W180">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X180">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y180">
         <v>1.5</v>
@@ -29688,13 +29688,13 @@
         <v>2.49</v>
       </c>
       <c r="AA180">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="AB180">
         <v>1.49</v>
       </c>
       <c r="AC180">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="AD180">
         <v>1.12</v>
@@ -29719,10 +29719,10 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AK180">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AL180">
         <v>0</v>
@@ -29821,31 +29821,31 @@
         <v>2.58</v>
       </c>
       <c r="Q181">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="R181">
         <v>2.15</v>
       </c>
       <c r="S181">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T181">
-        <v>3.1</v>
+        <v>2.42</v>
       </c>
       <c r="U181">
-        <v>2.45</v>
+        <v>2.08</v>
       </c>
       <c r="V181">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="W181">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X181">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y181">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z181">
         <v>3.05</v>
@@ -29860,13 +29860,13 @@
         <v>3.3</v>
       </c>
       <c r="AD181">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE181">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF181">
-        <v>1.74</v>
+        <v>1.45</v>
       </c>
       <c r="AG181">
         <v>2.15</v>
@@ -29882,10 +29882,10 @@
         </is>
       </c>
       <c r="AJ181">
-        <v>1.44</v>
+        <v>1.09</v>
       </c>
       <c r="AK181">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL181">
         <v>0</v>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="N9">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="O9">
         <v>3.2</v>
@@ -1791,49 +1791,49 @@
         <v>2.1</v>
       </c>
       <c r="S9">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T9">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="U9">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="V9">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W9">
         <v>1.07</v>
       </c>
       <c r="X9">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z9">
         <v>2.97</v>
       </c>
       <c r="AA9">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AB9">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AC9">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="AD9">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE9">
         <v>1.07</v>
       </c>
       <c r="AF9">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AG9">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.55</v>
+        <v>1.29</v>
       </c>
       <c r="AK9">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="O27">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="P27">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="Q27">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="R27">
+        <v>2.35</v>
+      </c>
+      <c r="S27">
+        <v>1.3</v>
+      </c>
+      <c r="T27">
+        <v>3.22</v>
+      </c>
+      <c r="U27">
+        <v>2.4</v>
+      </c>
+      <c r="V27">
+        <v>1.5</v>
+      </c>
+      <c r="W27">
+        <v>1.12</v>
+      </c>
+      <c r="X27">
+        <v>1.04</v>
+      </c>
+      <c r="Y27">
+        <v>1.2</v>
+      </c>
+      <c r="Z27">
+        <v>4.33</v>
+      </c>
+      <c r="AA27">
+        <v>1.62</v>
+      </c>
+      <c r="AB27">
+        <v>2.15</v>
+      </c>
+      <c r="AC27">
         <v>2.63</v>
       </c>
-      <c r="S27">
-        <v>1.18</v>
-      </c>
-      <c r="T27">
-        <v>4.2</v>
-      </c>
-      <c r="U27">
-        <v>1.95</v>
-      </c>
-      <c r="V27">
-        <v>1.8</v>
-      </c>
-      <c r="W27">
-        <v>1.2</v>
-      </c>
-      <c r="X27">
-        <v>1.01</v>
-      </c>
-      <c r="Y27">
-        <v>1.1</v>
-      </c>
-      <c r="Z27">
-        <v>6.15</v>
-      </c>
-      <c r="AA27">
-        <v>1.36</v>
-      </c>
-      <c r="AB27">
-        <v>3.1</v>
-      </c>
-      <c r="AC27">
-        <v>1.9</v>
-      </c>
       <c r="AD27">
-        <v>1.89</v>
+        <v>1.44</v>
       </c>
       <c r="AE27">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="AF27">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AG27">
-        <v>2.63</v>
+        <v>2</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AK27">
-        <v>2.45</v>
+        <v>2.66</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,65 +4873,65 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="O28">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="P28">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="Q28">
+        <v>1.93</v>
+      </c>
+      <c r="R28">
+        <v>2.63</v>
+      </c>
+      <c r="S28">
+        <v>1.18</v>
+      </c>
+      <c r="T28">
+        <v>4.2</v>
+      </c>
+      <c r="U28">
         <v>1.95</v>
       </c>
-      <c r="R28">
-        <v>2.35</v>
-      </c>
-      <c r="S28">
-        <v>1.3</v>
-      </c>
-      <c r="T28">
-        <v>3.22</v>
-      </c>
-      <c r="U28">
-        <v>2.4</v>
-      </c>
       <c r="V28">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="W28">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="X28">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="Z28">
-        <v>4.33</v>
+        <v>6.15</v>
       </c>
       <c r="AA28">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AB28">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="AC28">
+        <v>1.9</v>
+      </c>
+      <c r="AD28">
+        <v>1.89</v>
+      </c>
+      <c r="AE28">
+        <v>1.34</v>
+      </c>
+      <c r="AF28">
+        <v>1.4</v>
+      </c>
+      <c r="AG28">
         <v>2.63</v>
       </c>
-      <c r="AD28">
-        <v>1.44</v>
-      </c>
-      <c r="AE28">
-        <v>1.17</v>
-      </c>
-      <c r="AF28">
-        <v>1.73</v>
-      </c>
-      <c r="AG28">
-        <v>2</v>
-      </c>
       <c r="AH28" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AK28">
-        <v>2.66</v>
+        <v>2.45</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.15</v>
+        <v>1.63</v>
       </c>
       <c r="O71">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="P71">
-        <v>3.17</v>
+        <v>4.85</v>
       </c>
       <c r="Q71">
-        <v>2.86</v>
+        <v>2.1</v>
       </c>
       <c r="R71">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="S71">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="T71">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="U71">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="V71">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W71">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X71">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y71">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z71">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="AA71">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB71">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AC71">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AD71">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE71">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF71">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AG71">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.32</v>
+        <v>1.09</v>
       </c>
       <c r="AK71">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.63</v>
+        <v>2.15</v>
       </c>
       <c r="O72">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="P72">
-        <v>4.85</v>
+        <v>3.17</v>
       </c>
       <c r="Q72">
-        <v>2.1</v>
+        <v>2.86</v>
       </c>
       <c r="R72">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="S72">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T72">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="U72">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="V72">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="W72">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X72">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y72">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z72">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="AA72">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB72">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AC72">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AD72">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE72">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF72">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AG72">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.09</v>
+        <v>1.32</v>
       </c>
       <c r="AK72">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -14979,31 +14979,31 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="O90">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P90">
-        <v>2.91</v>
+        <v>2.85</v>
       </c>
       <c r="Q90">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="R90">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S90">
         <v>1.33</v>
       </c>
       <c r="T90">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="U90">
         <v>2.59</v>
       </c>
       <c r="V90">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W90">
         <v>1.1</v>
@@ -15012,31 +15012,31 @@
         <v>1.05</v>
       </c>
       <c r="Y90">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z90">
-        <v>3.8</v>
+        <v>3.72</v>
       </c>
       <c r="AA90">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB90">
         <v>1.95</v>
       </c>
       <c r="AC90">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="AD90">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE90">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF90">
         <v>1.6</v>
       </c>
       <c r="AG90">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -16609,16 +16609,16 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.4</v>
+        <v>2.95</v>
       </c>
       <c r="O100">
         <v>2.85</v>
       </c>
       <c r="P100">
-        <v>2.84</v>
+        <v>2.44</v>
       </c>
       <c r="Q100">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="R100">
         <v>1.91</v>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK100">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16781,7 +16781,7 @@
         <v>3.6</v>
       </c>
       <c r="Q101">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="R101">
         <v>2.1</v>
@@ -16793,10 +16793,10 @@
         <v>2.71</v>
       </c>
       <c r="U101">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="V101">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W101">
         <v>1.07</v>
@@ -16808,10 +16808,10 @@
         <v>1.3</v>
       </c>
       <c r="Z101">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AA101">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AB101">
         <v>1.77</v>
@@ -16823,7 +16823,7 @@
         <v>1.24</v>
       </c>
       <c r="AE101">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF101">
         <v>1.83</v>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK101">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -18251,13 +18251,13 @@
         <v>2.73</v>
       </c>
       <c r="R110">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="S110">
         <v>1.4</v>
       </c>
       <c r="T110">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="U110">
         <v>3.04</v>
@@ -18287,16 +18287,16 @@
         <v>4.1</v>
       </c>
       <c r="AD110">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE110">
         <v>1.07</v>
       </c>
       <c r="AF110">
+        <v>1.85</v>
+      </c>
+      <c r="AG110">
         <v>1.83</v>
-      </c>
-      <c r="AG110">
-        <v>1.84</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>1.26</v>
       </c>
       <c r="AK110">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -20195,19 +20195,19 @@
         </is>
       </c>
       <c r="N122">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="O122">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P122">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="Q122">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="R122">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S122">
         <v>1.37</v>
@@ -20228,7 +20228,7 @@
         <v>1.02</v>
       </c>
       <c r="Y122">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Z122">
         <v>2.92</v>
@@ -20240,7 +20240,7 @@
         <v>1.69</v>
       </c>
       <c r="AC122">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AD122">
         <v>1.22</v>
@@ -20268,7 +20268,7 @@
         <v>1.22</v>
       </c>
       <c r="AK122">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20370,13 +20370,13 @@
         <v>1.86</v>
       </c>
       <c r="R123">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="S123">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T123">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U123">
         <v>2.55</v>
@@ -20385,10 +20385,10 @@
         <v>1.45</v>
       </c>
       <c r="W123">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X123">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y123">
         <v>1.18</v>
@@ -20397,7 +20397,7 @@
         <v>3.88</v>
       </c>
       <c r="AA123">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB123">
         <v>2</v>
@@ -20431,7 +20431,7 @@
         <v>1.14</v>
       </c>
       <c r="AK123">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -24270,64 +24270,64 @@
         </is>
       </c>
       <c r="N147">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="O147">
         <v>3.6</v>
       </c>
       <c r="P147">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="Q147">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="R147">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="S147">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="T147">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U147">
-        <v>2.71</v>
+        <v>2.66</v>
       </c>
       <c r="V147">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W147">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X147">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y147">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z147">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="AA147">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AB147">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC147">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AD147">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE147">
         <v>1.1</v>
       </c>
       <c r="AF147">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG147">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AK147">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24433,16 +24433,16 @@
         </is>
       </c>
       <c r="N148">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="O148">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P148">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="Q148">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="R148">
         <v>1.85</v>
@@ -24475,13 +24475,13 @@
         <v>2.4</v>
       </c>
       <c r="AB148">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AC148">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="AD148">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AE148">
         <v>1.02</v>
@@ -24503,7 +24503,7 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AK148">
         <v>1.71</v>
@@ -24922,13 +24922,13 @@
         </is>
       </c>
       <c r="N151">
-        <v>2.24</v>
+        <v>2.45</v>
       </c>
       <c r="O151">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="P151">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="Q151">
         <v>3.1</v>
@@ -24937,49 +24937,49 @@
         <v>2</v>
       </c>
       <c r="S151">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T151">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="U151">
-        <v>3.02</v>
+        <v>2.88</v>
       </c>
       <c r="V151">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="W151">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X151">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y151">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z151">
-        <v>2.97</v>
+        <v>3.15</v>
       </c>
       <c r="AA151">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB151">
+        <v>1.67</v>
+      </c>
+      <c r="AC151">
+        <v>3.2</v>
+      </c>
+      <c r="AD151">
+        <v>1.26</v>
+      </c>
+      <c r="AE151">
+        <v>1.06</v>
+      </c>
+      <c r="AF151">
         <v>1.62</v>
       </c>
-      <c r="AC151">
-        <v>3.42</v>
-      </c>
-      <c r="AD151">
-        <v>1.2</v>
-      </c>
-      <c r="AE151">
-        <v>1.04</v>
-      </c>
-      <c r="AF151">
-        <v>1.67</v>
-      </c>
       <c r="AG151">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -24995,7 +24995,7 @@
         <v>1.36</v>
       </c>
       <c r="AK151">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25085,19 +25085,19 @@
         </is>
       </c>
       <c r="N152">
-        <v>2.22</v>
+        <v>2.35</v>
       </c>
       <c r="O152">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P152">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="Q152">
         <v>2.9</v>
       </c>
       <c r="R152">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="S152">
         <v>1.31</v>
@@ -25112,37 +25112,37 @@
         <v>1.5</v>
       </c>
       <c r="W152">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X152">
         <v>1</v>
       </c>
       <c r="Y152">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z152">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="AA152">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AB152">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AC152">
-        <v>2.78</v>
+        <v>2.46</v>
       </c>
       <c r="AD152">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE152">
         <v>1.15</v>
       </c>
       <c r="AF152">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG152">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK152">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -26881,10 +26881,10 @@
         <v>2.2</v>
       </c>
       <c r="O163">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P163">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="Q163">
         <v>0</v>
@@ -27379,7 +27379,7 @@
         <v>2.3</v>
       </c>
       <c r="R166">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S166">
         <v>1.3</v>
@@ -27394,7 +27394,7 @@
         <v>1.44</v>
       </c>
       <c r="W166">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X166">
         <v>1.01</v>
@@ -27409,7 +27409,7 @@
         <v>1.75</v>
       </c>
       <c r="AB166">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AC166">
         <v>2.78</v>
@@ -27421,10 +27421,10 @@
         <v>1.12</v>
       </c>
       <c r="AF166">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AG166">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AH166" t="inlineStr">
         <is>
@@ -28508,16 +28508,16 @@
         </is>
       </c>
       <c r="N173">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="O173">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P173">
         <v>2.62</v>
       </c>
       <c r="Q173">
-        <v>3.38</v>
+        <v>3.55</v>
       </c>
       <c r="R173">
         <v>1.8</v>
@@ -28526,7 +28526,7 @@
         <v>1.44</v>
       </c>
       <c r="T173">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U173">
         <v>3.6</v>
@@ -28544,16 +28544,16 @@
         <v>1.47</v>
       </c>
       <c r="Z173">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="AA173">
         <v>2.43</v>
       </c>
       <c r="AB173">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AC173">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AD173">
         <v>1.12</v>
@@ -28562,10 +28562,10 @@
         <v>1.01</v>
       </c>
       <c r="AF173">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AG173">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>1.33</v>
       </c>
       <c r="AK173">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -28671,13 +28671,13 @@
         </is>
       </c>
       <c r="N174">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="O174">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="P174">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="Q174">
         <v>3.15</v>
@@ -28686,7 +28686,7 @@
         <v>1.79</v>
       </c>
       <c r="S174">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="T174">
         <v>2.24</v>
@@ -28695,10 +28695,10 @@
         <v>3.04</v>
       </c>
       <c r="V174">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W174">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X174">
         <v>1.06</v>
@@ -28710,16 +28710,16 @@
         <v>2.88</v>
       </c>
       <c r="AA174">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB174">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC174">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AD174">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE174">
         <v>1.04</v>
@@ -28741,7 +28741,7 @@
         </is>
       </c>
       <c r="AJ174">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AK174">
         <v>1.5</v>
@@ -29199,25 +29199,25 @@
         <v>4.1</v>
       </c>
       <c r="AA177">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AB177">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AC177">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="AD177">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE177">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF177">
         <v>1.6</v>
       </c>
       <c r="AG177">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.18</v>
+        <v>1.87</v>
       </c>
       <c r="AK177">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29824,40 +29824,40 @@
         <v>2.75</v>
       </c>
       <c r="R181">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="S181">
         <v>1.3</v>
       </c>
       <c r="T181">
-        <v>2.42</v>
+        <v>3.1</v>
       </c>
       <c r="U181">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="V181">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W181">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X181">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y181">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z181">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="AA181">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="AB181">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AC181">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="AD181">
         <v>1.33</v>
@@ -29882,10 +29882,10 @@
         </is>
       </c>
       <c r="AJ181">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="AK181">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AL181">
         <v>0</v>

--- a/jogos_2026-08-09.xlsx
+++ b/jogos_2026-08-09.xlsx
@@ -638,25 +638,25 @@
         <v>3.83</v>
       </c>
       <c r="O2">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P2">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="Q2">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="R2">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="S2">
         <v>1.47</v>
       </c>
       <c r="T2">
-        <v>2.71</v>
+        <v>2.47</v>
       </c>
       <c r="U2">
-        <v>3.16</v>
+        <v>3.29</v>
       </c>
       <c r="V2">
         <v>1.3</v>
@@ -665,7 +665,7 @@
         <v>1.01</v>
       </c>
       <c r="X2">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
         <v>1.33</v>
@@ -674,13 +674,13 @@
         <v>2.83</v>
       </c>
       <c r="AA2">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AB2">
         <v>1.65</v>
       </c>
       <c r="AC2">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="AD2">
         <v>1.18</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.76</v>
+        <v>1.34</v>
       </c>
       <c r="AK2">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
 